--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Competitive Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reconciliation Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Supply &amp; Absorption" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +21,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0;;&quot;—&quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,12 +61,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="FF808080"/>
       <sz val="8"/>
     </font>
@@ -75,8 +70,20 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -130,7 +137,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -250,41 +267,55 @@
     <xf numFmtId="165" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -650,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K142"/>
+  <dimension ref="B2:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4856,894 +4887,21 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="24" customHeight="1">
+    <row r="118">
       <c r="B118" s="33" t="inlineStr">
         <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="C118" s="33" t="n"/>
-      <c r="D118" s="33" t="inlineStr">
-        <is>
-          <t># Props</t>
-        </is>
-      </c>
-      <c r="E118" s="33" t="inlineStr">
-        <is>
-          <t>Total Units</t>
-        </is>
-      </c>
-      <c r="F118" s="33" t="inlineStr">
-        <is>
-          <t>Wtd Avg
-Occupancy</t>
-        </is>
-      </c>
-      <c r="G118" s="33" t="inlineStr">
-        <is>
-          <t>Currently
-Occupied</t>
-        </is>
-      </c>
-      <c r="H118" s="33" t="inlineStr">
-        <is>
-          <t>Target
-@ Goal</t>
-        </is>
-      </c>
-      <c r="I118" s="33" t="inlineStr">
-        <is>
-          <t>Units to
-95%</t>
-        </is>
-      </c>
-      <c r="J118" s="33" t="inlineStr">
-        <is>
-          <t>Units to
-92.5%</t>
-        </is>
-      </c>
-      <c r="K118" s="33" t="inlineStr">
-        <is>
-          <t>Units to
-90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="C119" s="34" t="n"/>
-      <c r="D119" s="34">
-        <f>COUNTIF($E$6:$E$115,B119)</f>
-        <v/>
-      </c>
-      <c r="E119" s="35">
-        <f>SUMIF($E$6:$E$115,B119,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F119" s="36">
-        <f t="array" ref="F119">IFERROR(SUMPRODUCT(($E$6:$E$115=B119)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B119)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G119" s="35">
-        <f>F119*E119</f>
-        <v/>
-      </c>
-      <c r="H119" s="35">
-        <f>E119*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I119" s="35">
-        <f>(E119*0.95)-G119</f>
-        <v/>
-      </c>
-      <c r="J119" s="35">
-        <f>(E119*0.925)-G119</f>
-        <v/>
-      </c>
-      <c r="K119" s="35">
-        <f>(E119*0.90)-G119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2026</t>
-        </is>
-      </c>
-      <c r="C120" s="34" t="n"/>
-      <c r="D120" s="34">
-        <f>COUNTIF($E$6:$E$115,B120)</f>
-        <v/>
-      </c>
-      <c r="E120" s="35">
-        <f>SUMIF($E$6:$E$115,B120,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F120" s="36">
-        <f t="array" ref="F120">IFERROR(SUMPRODUCT(($E$6:$E$115=B120)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B120)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G120" s="35">
-        <f>F120*E120</f>
-        <v/>
-      </c>
-      <c r="H120" s="35">
-        <f>E120*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I120" s="35">
-        <f>(E120*0.95)-G120</f>
-        <v/>
-      </c>
-      <c r="J120" s="35">
-        <f>(E120*0.925)-G120</f>
-        <v/>
-      </c>
-      <c r="K120" s="35">
-        <f>(E120*0.90)-G120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-      <c r="C121" s="34" t="n"/>
-      <c r="D121" s="34">
-        <f>COUNTIF($E$6:$E$115,B121)</f>
-        <v/>
-      </c>
-      <c r="E121" s="35">
-        <f>SUMIF($E$6:$E$115,B121,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F121" s="36">
-        <f t="array" ref="F121">IFERROR(SUMPRODUCT(($E$6:$E$115=B121)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B121)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G121" s="35">
-        <f>F121*E121</f>
-        <v/>
-      </c>
-      <c r="H121" s="35">
-        <f>E121*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I121" s="35">
-        <f>(E121*0.95)-G121</f>
-        <v/>
-      </c>
-      <c r="J121" s="35">
-        <f>(E121*0.925)-G121</f>
-        <v/>
-      </c>
-      <c r="K121" s="35">
-        <f>(E121*0.90)-G121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2025</t>
-        </is>
-      </c>
-      <c r="C122" s="34" t="n"/>
-      <c r="D122" s="34">
-        <f>COUNTIF($E$6:$E$115,B122)</f>
-        <v/>
-      </c>
-      <c r="E122" s="35">
-        <f>SUMIF($E$6:$E$115,B122,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F122" s="36">
-        <f t="array" ref="F122">IFERROR(SUMPRODUCT(($E$6:$E$115=B122)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B122)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G122" s="35">
-        <f>F122*E122</f>
-        <v/>
-      </c>
-      <c r="H122" s="35">
-        <f>E122*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I122" s="35">
-        <f>(E122*0.95)-G122</f>
-        <v/>
-      </c>
-      <c r="J122" s="35">
-        <f>(E122*0.925)-G122</f>
-        <v/>
-      </c>
-      <c r="K122" s="35">
-        <f>(E122*0.90)-G122</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="C123" s="34" t="n"/>
-      <c r="D123" s="34">
-        <f>COUNTIF($E$6:$E$115,B123)</f>
-        <v/>
-      </c>
-      <c r="E123" s="35">
-        <f>SUMIF($E$6:$E$115,B123,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F123" s="36">
-        <f t="array" ref="F123">IFERROR(SUMPRODUCT(($E$6:$E$115=B123)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B123)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G123" s="35">
-        <f>F123*E123</f>
-        <v/>
-      </c>
-      <c r="H123" s="35">
-        <f>E123*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I123" s="35">
-        <f>(E123*0.95)-G123</f>
-        <v/>
-      </c>
-      <c r="J123" s="35">
-        <f>(E123*0.925)-G123</f>
-        <v/>
-      </c>
-      <c r="K123" s="35">
-        <f>(E123*0.90)-G123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2025</t>
-        </is>
-      </c>
-      <c r="C124" s="34" t="n"/>
-      <c r="D124" s="34">
-        <f>COUNTIF($E$6:$E$115,B124)</f>
-        <v/>
-      </c>
-      <c r="E124" s="35">
-        <f>SUMIF($E$6:$E$115,B124,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F124" s="36">
-        <f t="array" ref="F124">IFERROR(SUMPRODUCT(($E$6:$E$115=B124)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B124)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G124" s="35">
-        <f>F124*E124</f>
-        <v/>
-      </c>
-      <c r="H124" s="35">
-        <f>E124*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I124" s="35">
-        <f>(E124*0.95)-G124</f>
-        <v/>
-      </c>
-      <c r="J124" s="35">
-        <f>(E124*0.925)-G124</f>
-        <v/>
-      </c>
-      <c r="K124" s="35">
-        <f>(E124*0.90)-G124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2024</t>
-        </is>
-      </c>
-      <c r="C125" s="34" t="n"/>
-      <c r="D125" s="34">
-        <f>COUNTIF($E$6:$E$115,B125)</f>
-        <v/>
-      </c>
-      <c r="E125" s="35">
-        <f>SUMIF($E$6:$E$115,B125,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F125" s="36">
-        <f t="array" ref="F125">IFERROR(SUMPRODUCT(($E$6:$E$115=B125)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B125)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G125" s="35">
-        <f>F125*E125</f>
-        <v/>
-      </c>
-      <c r="H125" s="35">
-        <f>E125*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I125" s="35">
-        <f>(E125*0.95)-G125</f>
-        <v/>
-      </c>
-      <c r="J125" s="35">
-        <f>(E125*0.925)-G125</f>
-        <v/>
-      </c>
-      <c r="K125" s="35">
-        <f>(E125*0.90)-G125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2024</t>
-        </is>
-      </c>
-      <c r="C126" s="34" t="n"/>
-      <c r="D126" s="34">
-        <f>COUNTIF($E$6:$E$115,B126)</f>
-        <v/>
-      </c>
-      <c r="E126" s="35">
-        <f>SUMIF($E$6:$E$115,B126,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F126" s="36">
-        <f t="array" ref="F126">IFERROR(SUMPRODUCT(($E$6:$E$115=B126)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B126)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G126" s="35">
-        <f>F126*E126</f>
-        <v/>
-      </c>
-      <c r="H126" s="35">
-        <f>E126*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I126" s="35">
-        <f>(E126*0.95)-G126</f>
-        <v/>
-      </c>
-      <c r="J126" s="35">
-        <f>(E126*0.925)-G126</f>
-        <v/>
-      </c>
-      <c r="K126" s="35">
-        <f>(E126*0.90)-G126</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2024</t>
-        </is>
-      </c>
-      <c r="C127" s="34" t="n"/>
-      <c r="D127" s="34">
-        <f>COUNTIF($E$6:$E$115,B127)</f>
-        <v/>
-      </c>
-      <c r="E127" s="35">
-        <f>SUMIF($E$6:$E$115,B127,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F127" s="36">
-        <f t="array" ref="F127">IFERROR(SUMPRODUCT(($E$6:$E$115=B127)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B127)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G127" s="35">
-        <f>F127*E127</f>
-        <v/>
-      </c>
-      <c r="H127" s="35">
-        <f>E127*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I127" s="35">
-        <f>(E127*0.95)-G127</f>
-        <v/>
-      </c>
-      <c r="J127" s="35">
-        <f>(E127*0.925)-G127</f>
-        <v/>
-      </c>
-      <c r="K127" s="35">
-        <f>(E127*0.90)-G127</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2024</t>
-        </is>
-      </c>
-      <c r="C128" s="34" t="n"/>
-      <c r="D128" s="34">
-        <f>COUNTIF($E$6:$E$115,B128)</f>
-        <v/>
-      </c>
-      <c r="E128" s="35">
-        <f>SUMIF($E$6:$E$115,B128,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F128" s="36">
-        <f t="array" ref="F128">IFERROR(SUMPRODUCT(($E$6:$E$115=B128)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B128)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G128" s="35">
-        <f>F128*E128</f>
-        <v/>
-      </c>
-      <c r="H128" s="35">
-        <f>E128*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I128" s="35">
-        <f>(E128*0.95)-G128</f>
-        <v/>
-      </c>
-      <c r="J128" s="35">
-        <f>(E128*0.925)-G128</f>
-        <v/>
-      </c>
-      <c r="K128" s="35">
-        <f>(E128*0.90)-G128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2023</t>
-        </is>
-      </c>
-      <c r="C129" s="34" t="n"/>
-      <c r="D129" s="34">
-        <f>COUNTIF($E$6:$E$115,B129)</f>
-        <v/>
-      </c>
-      <c r="E129" s="35">
-        <f>SUMIF($E$6:$E$115,B129,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F129" s="36">
-        <f t="array" ref="F129">IFERROR(SUMPRODUCT(($E$6:$E$115=B129)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B129)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G129" s="35">
-        <f>F129*E129</f>
-        <v/>
-      </c>
-      <c r="H129" s="35">
-        <f>E129*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I129" s="35">
-        <f>(E129*0.95)-G129</f>
-        <v/>
-      </c>
-      <c r="J129" s="35">
-        <f>(E129*0.925)-G129</f>
-        <v/>
-      </c>
-      <c r="K129" s="35">
-        <f>(E129*0.90)-G129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2023</t>
-        </is>
-      </c>
-      <c r="C130" s="34" t="n"/>
-      <c r="D130" s="34">
-        <f>COUNTIF($E$6:$E$115,B130)</f>
-        <v/>
-      </c>
-      <c r="E130" s="35">
-        <f>SUMIF($E$6:$E$115,B130,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F130" s="36">
-        <f t="array" ref="F130">IFERROR(SUMPRODUCT(($E$6:$E$115=B130)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B130)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G130" s="35">
-        <f>F130*E130</f>
-        <v/>
-      </c>
-      <c r="H130" s="35">
-        <f>E130*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I130" s="35">
-        <f>(E130*0.95)-G130</f>
-        <v/>
-      </c>
-      <c r="J130" s="35">
-        <f>(E130*0.925)-G130</f>
-        <v/>
-      </c>
-      <c r="K130" s="35">
-        <f>(E130*0.90)-G130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2023</t>
-        </is>
-      </c>
-      <c r="C131" s="34" t="n"/>
-      <c r="D131" s="34">
-        <f>COUNTIF($E$6:$E$115,B131)</f>
-        <v/>
-      </c>
-      <c r="E131" s="35">
-        <f>SUMIF($E$6:$E$115,B131,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F131" s="36">
-        <f t="array" ref="F131">IFERROR(SUMPRODUCT(($E$6:$E$115=B131)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B131)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G131" s="35">
-        <f>F131*E131</f>
-        <v/>
-      </c>
-      <c r="H131" s="35">
-        <f>E131*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I131" s="35">
-        <f>(E131*0.95)-G131</f>
-        <v/>
-      </c>
-      <c r="J131" s="35">
-        <f>(E131*0.925)-G131</f>
-        <v/>
-      </c>
-      <c r="K131" s="35">
-        <f>(E131*0.90)-G131</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2023</t>
-        </is>
-      </c>
-      <c r="C132" s="34" t="n"/>
-      <c r="D132" s="34">
-        <f>COUNTIF($E$6:$E$115,B132)</f>
-        <v/>
-      </c>
-      <c r="E132" s="35">
-        <f>SUMIF($E$6:$E$115,B132,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F132" s="36">
-        <f t="array" ref="F132">IFERROR(SUMPRODUCT(($E$6:$E$115=B132)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B132)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G132" s="35">
-        <f>F132*E132</f>
-        <v/>
-      </c>
-      <c r="H132" s="35">
-        <f>E132*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I132" s="35">
-        <f>(E132*0.95)-G132</f>
-        <v/>
-      </c>
-      <c r="J132" s="35">
-        <f>(E132*0.925)-G132</f>
-        <v/>
-      </c>
-      <c r="K132" s="35">
-        <f>(E132*0.90)-G132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="34" t="inlineStr">
-        <is>
-          <t>Q4 2022</t>
-        </is>
-      </c>
-      <c r="C133" s="34" t="n"/>
-      <c r="D133" s="34">
-        <f>COUNTIF($E$6:$E$115,B133)</f>
-        <v/>
-      </c>
-      <c r="E133" s="35">
-        <f>SUMIF($E$6:$E$115,B133,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F133" s="36">
-        <f t="array" ref="F133">IFERROR(SUMPRODUCT(($E$6:$E$115=B133)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B133)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G133" s="35">
-        <f>F133*E133</f>
-        <v/>
-      </c>
-      <c r="H133" s="35">
-        <f>E133*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I133" s="35">
-        <f>(E133*0.95)-G133</f>
-        <v/>
-      </c>
-      <c r="J133" s="35">
-        <f>(E133*0.925)-G133</f>
-        <v/>
-      </c>
-      <c r="K133" s="35">
-        <f>(E133*0.90)-G133</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="34" t="inlineStr">
-        <is>
-          <t>Q3 2022</t>
-        </is>
-      </c>
-      <c r="C134" s="34" t="n"/>
-      <c r="D134" s="34">
-        <f>COUNTIF($E$6:$E$115,B134)</f>
-        <v/>
-      </c>
-      <c r="E134" s="35">
-        <f>SUMIF($E$6:$E$115,B134,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F134" s="36">
-        <f t="array" ref="F134">IFERROR(SUMPRODUCT(($E$6:$E$115=B134)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B134)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G134" s="35">
-        <f>F134*E134</f>
-        <v/>
-      </c>
-      <c r="H134" s="35">
-        <f>E134*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I134" s="35">
-        <f>(E134*0.95)-G134</f>
-        <v/>
-      </c>
-      <c r="J134" s="35">
-        <f>(E134*0.925)-G134</f>
-        <v/>
-      </c>
-      <c r="K134" s="35">
-        <f>(E134*0.90)-G134</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="34" t="inlineStr">
-        <is>
-          <t>Q2 2022</t>
-        </is>
-      </c>
-      <c r="C135" s="34" t="n"/>
-      <c r="D135" s="34">
-        <f>COUNTIF($E$6:$E$115,B135)</f>
-        <v/>
-      </c>
-      <c r="E135" s="35">
-        <f>SUMIF($E$6:$E$115,B135,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F135" s="36">
-        <f t="array" ref="F135">IFERROR(SUMPRODUCT(($E$6:$E$115=B135)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B135)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G135" s="35">
-        <f>F135*E135</f>
-        <v/>
-      </c>
-      <c r="H135" s="35">
-        <f>E135*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I135" s="35">
-        <f>(E135*0.95)-G135</f>
-        <v/>
-      </c>
-      <c r="J135" s="35">
-        <f>(E135*0.925)-G135</f>
-        <v/>
-      </c>
-      <c r="K135" s="35">
-        <f>(E135*0.90)-G135</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="34" t="inlineStr">
-        <is>
-          <t>Q1 2022</t>
-        </is>
-      </c>
-      <c r="C136" s="34" t="n"/>
-      <c r="D136" s="34">
-        <f>COUNTIF($E$6:$E$115,B136)</f>
-        <v/>
-      </c>
-      <c r="E136" s="35">
-        <f>SUMIF($E$6:$E$115,B136,$D$6:$D$115)</f>
-        <v/>
-      </c>
-      <c r="F136" s="36">
-        <f t="array" ref="F136">IFERROR(SUMPRODUCT(($E$6:$E$115=B136)*IFERROR($D$6:$D$115*$F$6:$F$115,0))/SUMPRODUCT(($E$6:$E$115=B136)*ISNUMBER($F$6:$F$115)*$D$6:$D$115),0)</f>
-        <v/>
-      </c>
-      <c r="G136" s="35">
-        <f>F136*E136</f>
-        <v/>
-      </c>
-      <c r="H136" s="35">
-        <f>E136*Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="I136" s="35">
-        <f>(E136*0.95)-G136</f>
-        <v/>
-      </c>
-      <c r="J136" s="35">
-        <f>(E136*0.925)-G136</f>
-        <v/>
-      </c>
-      <c r="K136" s="35">
-        <f>(E136*0.90)-G136</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="37" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4">
-        <f>SUM(D119:D136)</f>
-        <v/>
-      </c>
-      <c r="E137" s="38">
-        <f>SUM(E119:E136)</f>
-        <v/>
-      </c>
-      <c r="F137" s="39">
-        <f>IFERROR(SUMPRODUCT($E$119:$E$136,F119:F136)/$E$137,0)</f>
-        <v/>
-      </c>
-      <c r="G137" s="38">
-        <f>SUM(G119:G136)</f>
-        <v/>
-      </c>
-      <c r="H137" s="38">
-        <f>SUM(H119:H136)</f>
-        <v/>
-      </c>
-      <c r="I137" s="38">
-        <f>SUM(I119:I136)</f>
-        <v/>
-      </c>
-      <c r="J137" s="38">
-        <f>SUM(J119:J136)</f>
-        <v/>
-      </c>
-      <c r="K137" s="38">
-        <f>SUM(K119:K136)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="G139" s="40" t="inlineStr">
-        <is>
-          <t>Total Current Inventory</t>
-        </is>
-      </c>
-      <c r="I139" s="41" t="n">
-        <v>26603</v>
-      </c>
-      <c r="J139" s="42">
-        <f>I139</f>
-        <v/>
-      </c>
-      <c r="K139" s="42">
-        <f>I139</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="G140" s="40" t="inlineStr">
-        <is>
-          <t>% to be Absorbed</t>
-        </is>
-      </c>
-      <c r="I140" s="43">
-        <f>IFERROR(I137/I139,0)</f>
-        <v/>
-      </c>
-      <c r="J140" s="43">
-        <f>IFERROR(J137/J139,0)</f>
-        <v/>
-      </c>
-      <c r="K140" s="43">
-        <f>IFERROR(K137/K139,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="44" t="inlineStr">
-        <is>
-          <t>* 5-Mile radius. Total inventory from CoStar Data Analytics. Proximity (mi) to be filled manually. Lease-up rent/occupancy should be verified with a HelloData pull.</t>
+          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) to be filled manually; lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B135:C135"/>
-    <mergeCell ref="B125:C125"/>
-    <mergeCell ref="B134:C134"/>
+  <mergeCells count="7">
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="B118:K118"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C71:K71"/>
+    <mergeCell ref="C2:G2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B142:K142"/>
-    <mergeCell ref="C59:K59"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="C71:K71"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B132:C132"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="G139:H139"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="B124:C124"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B123:C123"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="G140:H140"/>
     <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5764,7 +4922,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>ANALYSIS SETTINGS</t>
         </is>
@@ -5776,7 +4934,7 @@
           <t>Stabilized Occupancy Target</t>
         </is>
       </c>
-      <c r="B2" s="46" t="n">
+      <c r="B2" s="35" t="n">
         <v>0.95</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -5814,62 +4972,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="40" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="40" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="40" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="40" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="40" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="40" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="40" t="inlineStr">
+      <c r="H1" s="36" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="40" t="inlineStr">
+      <c r="I1" s="36" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="40" t="inlineStr">
+      <c r="J1" s="36" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="40" t="inlineStr">
+      <c r="K1" s="36" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="40" t="inlineStr">
+      <c r="L1" s="36" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5902,16 +5060,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="47" t="n">
+      <c r="G2" s="37" t="n">
         <v>0.924324</v>
       </c>
-      <c r="H2" s="47" t="n">
+      <c r="H2" s="37" t="n">
         <v>0.924</v>
       </c>
-      <c r="I2" s="42" t="n">
+      <c r="I2" s="38" t="n">
         <v>1750</v>
       </c>
-      <c r="J2" s="42" t="n">
+      <c r="J2" s="38" t="n">
         <v>1875</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -5952,12 +5110,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="47" t="n"/>
-      <c r="H3" s="47" t="n">
+      <c r="G3" s="37" t="n"/>
+      <c r="H3" s="37" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="42" t="n"/>
-      <c r="J3" s="42" t="n">
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="38" t="n">
         <v>2090</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -5998,16 +5156,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="47" t="n">
+      <c r="G4" s="37" t="n">
         <v>0.8518520000000001</v>
       </c>
-      <c r="H4" s="47" t="n">
+      <c r="H4" s="37" t="n">
         <v>0.877</v>
       </c>
-      <c r="I4" s="42" t="n">
+      <c r="I4" s="38" t="n">
         <v>1576</v>
       </c>
-      <c r="J4" s="42" t="n">
+      <c r="J4" s="38" t="n">
         <v>1211</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -6048,16 +5206,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G5" s="47" t="n">
+      <c r="G5" s="37" t="n">
         <v>0.7634730000000001</v>
       </c>
-      <c r="H5" s="47" t="n">
+      <c r="H5" s="37" t="n">
         <v>0.916</v>
       </c>
-      <c r="I5" s="42" t="n">
+      <c r="I5" s="38" t="n">
         <v>2026</v>
       </c>
-      <c r="J5" s="42" t="n">
+      <c r="J5" s="38" t="n">
         <v>1385</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -6098,16 +5256,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="37" t="n">
         <v>0.895833</v>
       </c>
-      <c r="H6" s="47" t="n">
+      <c r="H6" s="37" t="n">
         <v>0.966</v>
       </c>
-      <c r="I6" s="42" t="n">
+      <c r="I6" s="38" t="n">
         <v>1429</v>
       </c>
-      <c r="J6" s="42" t="n">
+      <c r="J6" s="38" t="n">
         <v>1313</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -6148,16 +5306,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G7" s="47" t="n">
+      <c r="G7" s="37" t="n">
         <v>0.949309</v>
       </c>
-      <c r="H7" s="47" t="n">
+      <c r="H7" s="37" t="n">
         <v>0.968</v>
       </c>
-      <c r="I7" s="42" t="n">
+      <c r="I7" s="38" t="n">
         <v>1576</v>
       </c>
-      <c r="J7" s="42" t="n">
+      <c r="J7" s="38" t="n">
         <v>1602</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -6198,16 +5356,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="37" t="n">
         <v>0.773196</v>
       </c>
-      <c r="H8" s="47" t="n">
+      <c r="H8" s="37" t="n">
         <v>0.918</v>
       </c>
-      <c r="I8" s="42" t="n">
+      <c r="I8" s="38" t="n">
         <v>1874</v>
       </c>
-      <c r="J8" s="42" t="n">
+      <c r="J8" s="38" t="n">
         <v>1794</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -6248,16 +5406,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="37" t="n">
         <v>0.784247</v>
       </c>
-      <c r="H9" s="47" t="n">
+      <c r="H9" s="37" t="n">
         <v>0.87</v>
       </c>
-      <c r="I9" s="42" t="n">
+      <c r="I9" s="38" t="n">
         <v>1516</v>
       </c>
-      <c r="J9" s="42" t="n">
+      <c r="J9" s="38" t="n">
         <v>1517</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -6298,16 +5456,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G10" s="47" t="n">
+      <c r="G10" s="37" t="n">
         <v>0.8992249999999999</v>
       </c>
-      <c r="H10" s="47" t="n">
+      <c r="H10" s="37" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="I10" s="42" t="n">
+      <c r="I10" s="38" t="n">
         <v>1567</v>
       </c>
-      <c r="J10" s="42" t="n">
+      <c r="J10" s="38" t="n">
         <v>1591</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -6348,16 +5506,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G11" s="47" t="n">
+      <c r="G11" s="37" t="n">
         <v>0.9520960000000001</v>
       </c>
-      <c r="H11" s="47" t="n">
+      <c r="H11" s="37" t="n">
         <v>0.946</v>
       </c>
-      <c r="I11" s="42" t="n">
+      <c r="I11" s="38" t="n">
         <v>1607</v>
       </c>
-      <c r="J11" s="42" t="n">
+      <c r="J11" s="38" t="n">
         <v>1388</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -6398,16 +5556,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G12" s="47" t="n">
+      <c r="G12" s="37" t="n">
         <v>0.920455</v>
       </c>
-      <c r="H12" s="47" t="n">
+      <c r="H12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="42" t="n">
+      <c r="I12" s="38" t="n">
         <v>1526</v>
       </c>
-      <c r="J12" s="42" t="n">
+      <c r="J12" s="38" t="n">
         <v>1263</v>
       </c>
       <c r="K12" t="inlineStr">
@@ -6448,16 +5606,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G13" s="47" t="n">
+      <c r="G13" s="37" t="n">
         <v>0.934483</v>
       </c>
-      <c r="H13" s="47" t="n">
+      <c r="H13" s="37" t="n">
         <v>0.959</v>
       </c>
-      <c r="I13" s="42" t="n">
+      <c r="I13" s="38" t="n">
         <v>2812</v>
       </c>
-      <c r="J13" s="42" t="n">
+      <c r="J13" s="38" t="n">
         <v>2575</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -6498,16 +5656,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G14" s="47" t="n">
+      <c r="G14" s="37" t="n">
         <v>0.935829</v>
       </c>
-      <c r="H14" s="47" t="n">
+      <c r="H14" s="37" t="n">
         <v>0.963</v>
       </c>
-      <c r="I14" s="42" t="n">
+      <c r="I14" s="38" t="n">
         <v>1964</v>
       </c>
-      <c r="J14" s="42" t="n">
+      <c r="J14" s="38" t="n">
         <v>1902</v>
       </c>
       <c r="K14" t="inlineStr">
@@ -6548,16 +5706,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G15" s="47" t="n">
+      <c r="G15" s="37" t="n">
         <v>0.892045</v>
       </c>
-      <c r="H15" s="47" t="n">
+      <c r="H15" s="37" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I15" s="42" t="n">
+      <c r="I15" s="38" t="n">
         <v>1632</v>
       </c>
-      <c r="J15" s="42" t="n">
+      <c r="J15" s="38" t="n">
         <v>1236</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -6598,16 +5756,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G16" s="47" t="n">
+      <c r="G16" s="37" t="n">
         <v>0.926471</v>
       </c>
-      <c r="H16" s="47" t="n">
+      <c r="H16" s="37" t="n">
         <v>0.967</v>
       </c>
-      <c r="I16" s="42" t="n">
+      <c r="I16" s="38" t="n">
         <v>1820</v>
       </c>
-      <c r="J16" s="42" t="n">
+      <c r="J16" s="38" t="n">
         <v>1597</v>
       </c>
       <c r="K16" t="inlineStr">
@@ -6648,16 +5806,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G17" s="47" t="n">
+      <c r="G17" s="37" t="n">
         <v>0.9494050000000001</v>
       </c>
-      <c r="H17" s="47" t="n">
+      <c r="H17" s="37" t="n">
         <v>0.949</v>
       </c>
-      <c r="I17" s="42" t="n">
+      <c r="I17" s="38" t="n">
         <v>1335</v>
       </c>
-      <c r="J17" s="42" t="n">
+      <c r="J17" s="38" t="n">
         <v>1325</v>
       </c>
       <c r="K17" t="inlineStr">
@@ -6698,14 +5856,14 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G18" s="47" t="n">
+      <c r="G18" s="37" t="n">
         <v>0.893204</v>
       </c>
-      <c r="H18" s="47" t="n"/>
-      <c r="I18" s="42" t="n">
+      <c r="H18" s="37" t="n"/>
+      <c r="I18" s="38" t="n">
         <v>2523</v>
       </c>
-      <c r="J18" s="42" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -6744,12 +5902,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G19" s="47" t="n"/>
-      <c r="H19" s="47" t="n">
+      <c r="G19" s="37" t="n"/>
+      <c r="H19" s="37" t="n">
         <v>0.926</v>
       </c>
-      <c r="I19" s="42" t="n"/>
-      <c r="J19" s="42" t="n">
+      <c r="I19" s="38" t="n"/>
+      <c r="J19" s="38" t="n">
         <v>1629</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -6790,16 +5948,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G20" s="47" t="n">
+      <c r="G20" s="37" t="n">
         <v>0.951977</v>
       </c>
-      <c r="H20" s="47" t="n">
+      <c r="H20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="42" t="n">
+      <c r="I20" s="38" t="n">
         <v>1574</v>
       </c>
-      <c r="J20" s="42" t="n">
+      <c r="J20" s="38" t="n">
         <v>1583</v>
       </c>
       <c r="K20" t="inlineStr">
@@ -6840,16 +5998,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G21" s="47" t="n">
+      <c r="G21" s="37" t="n">
         <v>0.902098</v>
       </c>
-      <c r="H21" s="47" t="n">
+      <c r="H21" s="37" t="n">
         <v>0.955</v>
       </c>
-      <c r="I21" s="42" t="n">
+      <c r="I21" s="38" t="n">
         <v>1338</v>
       </c>
-      <c r="J21" s="42" t="n">
+      <c r="J21" s="38" t="n">
         <v>1167</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -6890,16 +6048,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G22" s="47" t="n">
+      <c r="G22" s="37" t="n">
         <v>0.984375</v>
       </c>
-      <c r="H22" s="47" t="n">
+      <c r="H22" s="37" t="n">
         <v>0.984</v>
       </c>
-      <c r="I22" s="42" t="n">
+      <c r="I22" s="38" t="n">
         <v>2442</v>
       </c>
-      <c r="J22" s="42" t="n">
+      <c r="J22" s="38" t="n">
         <v>2261</v>
       </c>
       <c r="K22" t="inlineStr">
@@ -6940,16 +6098,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G23" s="47" t="n">
+      <c r="G23" s="37" t="n">
         <v>0.989362</v>
       </c>
-      <c r="H23" s="47" t="n">
+      <c r="H23" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="42" t="n">
+      <c r="I23" s="38" t="n">
         <v>1913</v>
       </c>
-      <c r="J23" s="42" t="n">
+      <c r="J23" s="38" t="n">
         <v>1982</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -6986,16 +6144,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G24" s="47" t="n">
+      <c r="G24" s="37" t="n">
         <v>0.4461540000000001</v>
       </c>
-      <c r="H24" s="47" t="n">
+      <c r="H24" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="42" t="n">
+      <c r="I24" s="38" t="n">
         <v>1829</v>
       </c>
-      <c r="J24" s="42" t="n">
+      <c r="J24" s="38" t="n">
         <v>1681</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -7036,16 +6194,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G25" s="47" t="n">
+      <c r="G25" s="37" t="n">
         <v>0.05660399999999999</v>
       </c>
-      <c r="H25" s="47" t="n">
+      <c r="H25" s="37" t="n">
         <v>0.208</v>
       </c>
-      <c r="I25" s="42" t="n">
+      <c r="I25" s="38" t="n">
         <v>2966</v>
       </c>
-      <c r="J25" s="42" t="n">
+      <c r="J25" s="38" t="n">
         <v>1938</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -7086,16 +6244,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G26" s="47" t="n">
+      <c r="G26" s="37" t="n">
         <v>0.273504</v>
       </c>
-      <c r="H26" s="47" t="n">
+      <c r="H26" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="42" t="n">
+      <c r="I26" s="38" t="n">
         <v>2537</v>
       </c>
-      <c r="J26" s="42" t="n">
+      <c r="J26" s="38" t="n">
         <v>2273</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -7136,16 +6294,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G27" s="47" t="n">
+      <c r="G27" s="37" t="n">
         <v>0.1333329999999999</v>
       </c>
-      <c r="H27" s="47" t="n">
+      <c r="H27" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="42" t="n">
+      <c r="I27" s="38" t="n">
         <v>1411</v>
       </c>
-      <c r="J27" s="42" t="n">
+      <c r="J27" s="38" t="n">
         <v>1145</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -7186,16 +6344,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G28" s="47" t="n">
+      <c r="G28" s="37" t="n">
         <v>0.297203</v>
       </c>
-      <c r="H28" s="47" t="n">
+      <c r="H28" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="42" t="n">
+      <c r="I28" s="38" t="n">
         <v>1728</v>
       </c>
-      <c r="J28" s="42" t="n">
+      <c r="J28" s="38" t="n">
         <v>1243</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -7236,16 +6394,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G29" s="47" t="n">
+      <c r="G29" s="37" t="n">
         <v>0.875</v>
       </c>
-      <c r="H29" s="47" t="n">
+      <c r="H29" s="37" t="n">
         <v>0.512</v>
       </c>
-      <c r="I29" s="42" t="n">
+      <c r="I29" s="38" t="n">
         <v>1506</v>
       </c>
-      <c r="J29" s="42" t="n">
+      <c r="J29" s="38" t="n">
         <v>1107</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -7286,14 +6444,14 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G30" s="47" t="n">
+      <c r="G30" s="37" t="n">
         <v>0.895349</v>
       </c>
-      <c r="H30" s="47" t="n"/>
-      <c r="I30" s="42" t="n">
+      <c r="H30" s="37" t="n"/>
+      <c r="I30" s="38" t="n">
         <v>2474</v>
       </c>
-      <c r="J30" s="42" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -7332,16 +6490,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G31" s="47" t="n">
+      <c r="G31" s="37" t="n">
         <v>0.52381</v>
       </c>
-      <c r="H31" s="47" t="n">
+      <c r="H31" s="37" t="n">
         <v>0.714</v>
       </c>
-      <c r="I31" s="42" t="n">
+      <c r="I31" s="38" t="n">
         <v>2319</v>
       </c>
-      <c r="J31" s="42" t="n">
+      <c r="J31" s="38" t="n">
         <v>1833</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -7382,16 +6540,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G32" s="47" t="n">
+      <c r="G32" s="37" t="n">
         <v>0.810458</v>
       </c>
-      <c r="H32" s="47" t="n">
+      <c r="H32" s="37" t="n">
         <v>0.856</v>
       </c>
-      <c r="I32" s="42" t="n">
+      <c r="I32" s="38" t="n">
         <v>1913</v>
       </c>
-      <c r="J32" s="42" t="n">
+      <c r="J32" s="38" t="n">
         <v>1538</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -7432,16 +6590,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G33" s="47" t="n">
+      <c r="G33" s="37" t="n">
         <v>0.857143</v>
       </c>
-      <c r="H33" s="47" t="n">
+      <c r="H33" s="37" t="n">
         <v>0.857</v>
       </c>
-      <c r="I33" s="42" t="n">
+      <c r="I33" s="38" t="n">
         <v>2325</v>
       </c>
-      <c r="J33" s="42" t="n">
+      <c r="J33" s="38" t="n">
         <v>2169</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -7482,16 +6640,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G34" s="47" t="n">
+      <c r="G34" s="37" t="n">
         <v>0.496503</v>
       </c>
-      <c r="H34" s="47" t="n">
+      <c r="H34" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="42" t="n">
+      <c r="I34" s="38" t="n">
         <v>2085</v>
       </c>
-      <c r="J34" s="42" t="n">
+      <c r="J34" s="38" t="n">
         <v>2095</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -7532,16 +6690,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G35" s="47" t="n">
+      <c r="G35" s="37" t="n">
         <v>0.802469</v>
       </c>
-      <c r="H35" s="47" t="n">
+      <c r="H35" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="42" t="n">
+      <c r="I35" s="38" t="n">
         <v>1747</v>
       </c>
-      <c r="J35" s="42" t="n">
+      <c r="J35" s="38" t="n">
         <v>1582</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -7582,16 +6740,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G36" s="47" t="n">
+      <c r="G36" s="37" t="n">
         <v>0.789474</v>
       </c>
-      <c r="H36" s="47" t="n">
+      <c r="H36" s="37" t="n">
         <v>0.784</v>
       </c>
-      <c r="I36" s="42" t="n">
+      <c r="I36" s="38" t="n">
         <v>1638</v>
       </c>
-      <c r="J36" s="42" t="n">
+      <c r="J36" s="38" t="n">
         <v>1433</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -7632,16 +6790,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G37" s="47" t="n">
+      <c r="G37" s="37" t="n">
         <v>0.3952100000000001</v>
       </c>
-      <c r="H37" s="47" t="n">
+      <c r="H37" s="37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="42" t="n">
+      <c r="I37" s="38" t="n">
         <v>1773</v>
       </c>
-      <c r="J37" s="42" t="n">
+      <c r="J37" s="38" t="n">
         <v>1632</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -7682,16 +6840,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G38" s="47" t="n">
+      <c r="G38" s="37" t="n">
         <v>0.37037</v>
       </c>
-      <c r="H38" s="47" t="n">
+      <c r="H38" s="37" t="n">
         <v>0.852</v>
       </c>
-      <c r="I38" s="42" t="n">
+      <c r="I38" s="38" t="n">
         <v>1632</v>
       </c>
-      <c r="J38" s="42" t="n">
+      <c r="J38" s="38" t="n">
         <v>1321</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -7732,16 +6890,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G39" s="47" t="n">
+      <c r="G39" s="37" t="n">
         <v>0.7393000000000001</v>
       </c>
-      <c r="H39" s="47" t="n">
+      <c r="H39" s="37" t="n">
         <v>0.673</v>
       </c>
-      <c r="I39" s="42" t="n">
+      <c r="I39" s="38" t="n">
         <v>1330</v>
       </c>
-      <c r="J39" s="42" t="n">
+      <c r="J39" s="38" t="n">
         <v>1253</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -7782,16 +6940,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G40" s="47" t="n">
+      <c r="G40" s="37" t="n">
         <v>0.583062</v>
       </c>
-      <c r="H40" s="47" t="n">
+      <c r="H40" s="37" t="n">
         <v>0.59</v>
       </c>
-      <c r="I40" s="42" t="n">
+      <c r="I40" s="38" t="n">
         <v>2076</v>
       </c>
-      <c r="J40" s="42" t="n">
+      <c r="J40" s="38" t="n">
         <v>1561</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -7832,12 +6990,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G41" s="47" t="n"/>
-      <c r="H41" s="47" t="n">
+      <c r="G41" s="37" t="n"/>
+      <c r="H41" s="37" t="n">
         <v>0.89</v>
       </c>
-      <c r="I41" s="42" t="n"/>
-      <c r="J41" s="42" t="n">
+      <c r="I41" s="38" t="n"/>
+      <c r="J41" s="38" t="n">
         <v>1438</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -7878,12 +7036,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G42" s="47" t="n"/>
-      <c r="H42" s="47" t="n">
+      <c r="G42" s="37" t="n"/>
+      <c r="H42" s="37" t="n">
         <v>0.256</v>
       </c>
-      <c r="I42" s="42" t="n"/>
-      <c r="J42" s="42" t="n">
+      <c r="I42" s="38" t="n"/>
+      <c r="J42" s="38" t="n">
         <v>1671</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -7924,12 +7082,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G43" s="47" t="n"/>
-      <c r="H43" s="47" t="n">
+      <c r="G43" s="37" t="n"/>
+      <c r="H43" s="37" t="n">
         <v>0.844</v>
       </c>
-      <c r="I43" s="42" t="n"/>
-      <c r="J43" s="42" t="n">
+      <c r="I43" s="38" t="n"/>
+      <c r="J43" s="38" t="n">
         <v>1025</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -7970,16 +7128,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G44" s="47" t="n">
+      <c r="G44" s="37" t="n">
         <v>0.797059</v>
       </c>
-      <c r="H44" s="47" t="n">
+      <c r="H44" s="37" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="I44" s="42" t="n">
+      <c r="I44" s="38" t="n">
         <v>1680</v>
       </c>
-      <c r="J44" s="42" t="n">
+      <c r="J44" s="38" t="n">
         <v>1356</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -8020,16 +7178,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G45" s="47" t="n">
+      <c r="G45" s="37" t="n">
         <v>0.891892</v>
       </c>
-      <c r="H45" s="47" t="n">
+      <c r="H45" s="37" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="I45" s="42" t="n">
+      <c r="I45" s="38" t="n">
         <v>1900</v>
       </c>
-      <c r="J45" s="42" t="n">
+      <c r="J45" s="38" t="n">
         <v>1769</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -8070,16 +7228,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G46" s="47" t="n">
+      <c r="G46" s="37" t="n">
         <v>0.879032</v>
       </c>
-      <c r="H46" s="47" t="n">
+      <c r="H46" s="37" t="n">
         <v>0.919</v>
       </c>
-      <c r="I46" s="42" t="n">
+      <c r="I46" s="38" t="n">
         <v>2183</v>
       </c>
-      <c r="J46" s="42" t="n">
+      <c r="J46" s="38" t="n">
         <v>2093</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -8120,16 +7278,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G47" s="47" t="n">
+      <c r="G47" s="37" t="n">
         <v>0.878788</v>
       </c>
-      <c r="H47" s="47" t="n">
+      <c r="H47" s="37" t="n">
         <v>0.889</v>
       </c>
-      <c r="I47" s="42" t="n">
+      <c r="I47" s="38" t="n">
         <v>1691</v>
       </c>
-      <c r="J47" s="42" t="n">
+      <c r="J47" s="38" t="n">
         <v>1646</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -8170,16 +7328,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G48" s="47" t="n">
+      <c r="G48" s="37" t="n">
         <v>0.829114</v>
       </c>
-      <c r="H48" s="47" t="n">
+      <c r="H48" s="37" t="n">
         <v>0.842</v>
       </c>
-      <c r="I48" s="42" t="n">
+      <c r="I48" s="38" t="n">
         <v>1663</v>
       </c>
-      <c r="J48" s="42" t="n">
+      <c r="J48" s="38" t="n">
         <v>1263</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -8220,16 +7378,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G49" s="47" t="n">
+      <c r="G49" s="37" t="n">
         <v>0.7833330000000001</v>
       </c>
-      <c r="H49" s="47" t="n">
+      <c r="H49" s="37" t="n">
         <v>0.836</v>
       </c>
-      <c r="I49" s="42" t="n">
+      <c r="I49" s="38" t="n">
         <v>1610</v>
       </c>
-      <c r="J49" s="42" t="n">
+      <c r="J49" s="38" t="n">
         <v>1339</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -8270,16 +7428,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G50" s="47" t="n">
+      <c r="G50" s="37" t="n">
         <v>0.855721</v>
       </c>
-      <c r="H50" s="47" t="n">
+      <c r="H50" s="37" t="n">
         <v>0.901</v>
       </c>
-      <c r="I50" s="42" t="n">
+      <c r="I50" s="38" t="n">
         <v>1542</v>
       </c>
-      <c r="J50" s="42" t="n">
+      <c r="J50" s="38" t="n">
         <v>1154</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -8320,16 +7478,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G51" s="47" t="n">
+      <c r="G51" s="37" t="n">
         <v>0.616708</v>
       </c>
-      <c r="H51" s="47" t="n">
+      <c r="H51" s="37" t="n">
         <v>0.514</v>
       </c>
-      <c r="I51" s="42" t="n">
+      <c r="I51" s="38" t="n">
         <v>1743</v>
       </c>
-      <c r="J51" s="42" t="n">
+      <c r="J51" s="38" t="n">
         <v>1676</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -8365,10 +7523,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G52" s="47" t="n"/>
-      <c r="H52" s="47" t="n"/>
-      <c r="I52" s="42" t="n"/>
-      <c r="J52" s="42" t="n"/>
+      <c r="G52" s="37" t="n"/>
+      <c r="H52" s="37" t="n"/>
+      <c r="I52" s="38" t="n"/>
+      <c r="J52" s="38" t="n"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8398,10 +7556,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G53" s="47" t="n"/>
-      <c r="H53" s="47" t="n"/>
-      <c r="I53" s="42" t="n"/>
-      <c r="J53" s="42" t="n"/>
+      <c r="G53" s="37" t="n"/>
+      <c r="H53" s="37" t="n"/>
+      <c r="I53" s="38" t="n"/>
+      <c r="J53" s="38" t="n"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8435,12 +7593,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G54" s="47" t="n"/>
-      <c r="H54" s="47" t="n"/>
-      <c r="I54" s="42" t="n">
+      <c r="G54" s="37" t="n"/>
+      <c r="H54" s="37" t="n"/>
+      <c r="I54" s="38" t="n">
         <v>1781</v>
       </c>
-      <c r="J54" s="42" t="n"/>
+      <c r="J54" s="38" t="n"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8474,12 +7632,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G55" s="47" t="n"/>
-      <c r="H55" s="47" t="n"/>
-      <c r="I55" s="42" t="n">
+      <c r="G55" s="37" t="n"/>
+      <c r="H55" s="37" t="n"/>
+      <c r="I55" s="38" t="n">
         <v>2788</v>
       </c>
-      <c r="J55" s="42" t="n"/>
+      <c r="J55" s="38" t="n"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8509,10 +7667,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G56" s="47" t="n"/>
-      <c r="H56" s="47" t="n"/>
-      <c r="I56" s="42" t="n"/>
-      <c r="J56" s="42" t="n"/>
+      <c r="G56" s="37" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="38" t="n"/>
+      <c r="J56" s="38" t="n"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8542,12 +7700,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G57" s="47" t="n"/>
-      <c r="H57" s="47" t="n"/>
-      <c r="I57" s="42" t="n">
+      <c r="G57" s="37" t="n"/>
+      <c r="H57" s="37" t="n"/>
+      <c r="I57" s="38" t="n">
         <v>1650</v>
       </c>
-      <c r="J57" s="42" t="n"/>
+      <c r="J57" s="38" t="n"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8581,10 +7739,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G58" s="47" t="n"/>
-      <c r="H58" s="47" t="n"/>
-      <c r="I58" s="42" t="n"/>
-      <c r="J58" s="42" t="n"/>
+      <c r="G58" s="37" t="n"/>
+      <c r="H58" s="37" t="n"/>
+      <c r="I58" s="38" t="n"/>
+      <c r="J58" s="38" t="n"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8614,10 +7772,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G59" s="47" t="n"/>
-      <c r="H59" s="47" t="n"/>
-      <c r="I59" s="42" t="n"/>
-      <c r="J59" s="42" t="n"/>
+      <c r="G59" s="37" t="n"/>
+      <c r="H59" s="37" t="n"/>
+      <c r="I59" s="38" t="n"/>
+      <c r="J59" s="38" t="n"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8647,10 +7805,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G60" s="47" t="n"/>
-      <c r="H60" s="47" t="n"/>
-      <c r="I60" s="42" t="n"/>
-      <c r="J60" s="42" t="n"/>
+      <c r="G60" s="37" t="n"/>
+      <c r="H60" s="37" t="n"/>
+      <c r="I60" s="38" t="n"/>
+      <c r="J60" s="38" t="n"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8684,10 +7842,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G61" s="47" t="n"/>
-      <c r="H61" s="47" t="n"/>
-      <c r="I61" s="42" t="n"/>
-      <c r="J61" s="42" t="n"/>
+      <c r="G61" s="37" t="n"/>
+      <c r="H61" s="37" t="n"/>
+      <c r="I61" s="38" t="n"/>
+      <c r="J61" s="38" t="n"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8714,10 +7872,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G62" s="47" t="n"/>
-      <c r="H62" s="47" t="n"/>
-      <c r="I62" s="42" t="n"/>
-      <c r="J62" s="42" t="n"/>
+      <c r="G62" s="37" t="n"/>
+      <c r="H62" s="37" t="n"/>
+      <c r="I62" s="38" t="n"/>
+      <c r="J62" s="38" t="n"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8747,10 +7905,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G63" s="47" t="n"/>
-      <c r="H63" s="47" t="n"/>
-      <c r="I63" s="42" t="n"/>
-      <c r="J63" s="42" t="n"/>
+      <c r="G63" s="37" t="n"/>
+      <c r="H63" s="37" t="n"/>
+      <c r="I63" s="38" t="n"/>
+      <c r="J63" s="38" t="n"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8777,10 +7935,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G64" s="47" t="n"/>
-      <c r="H64" s="47" t="n"/>
-      <c r="I64" s="42" t="n"/>
-      <c r="J64" s="42" t="n"/>
+      <c r="G64" s="37" t="n"/>
+      <c r="H64" s="37" t="n"/>
+      <c r="I64" s="38" t="n"/>
+      <c r="J64" s="38" t="n"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8810,10 +7968,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G65" s="47" t="n"/>
-      <c r="H65" s="47" t="n"/>
-      <c r="I65" s="42" t="n"/>
-      <c r="J65" s="42" t="n"/>
+      <c r="G65" s="37" t="n"/>
+      <c r="H65" s="37" t="n"/>
+      <c r="I65" s="38" t="n"/>
+      <c r="J65" s="38" t="n"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8843,10 +8001,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G66" s="47" t="n"/>
-      <c r="H66" s="47" t="n"/>
-      <c r="I66" s="42" t="n"/>
-      <c r="J66" s="42" t="n"/>
+      <c r="G66" s="37" t="n"/>
+      <c r="H66" s="37" t="n"/>
+      <c r="I66" s="38" t="n"/>
+      <c r="J66" s="38" t="n"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8873,10 +8031,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G67" s="47" t="n"/>
-      <c r="H67" s="47" t="n"/>
-      <c r="I67" s="42" t="n"/>
-      <c r="J67" s="42" t="n"/>
+      <c r="G67" s="37" t="n"/>
+      <c r="H67" s="37" t="n"/>
+      <c r="I67" s="38" t="n"/>
+      <c r="J67" s="38" t="n"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8907,10 +8065,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G68" s="47" t="n"/>
-      <c r="H68" s="47" t="n"/>
-      <c r="I68" s="42" t="n"/>
-      <c r="J68" s="42" t="n"/>
+      <c r="G68" s="37" t="n"/>
+      <c r="H68" s="37" t="n"/>
+      <c r="I68" s="38" t="n"/>
+      <c r="J68" s="38" t="n"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8941,10 +8099,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G69" s="47" t="n"/>
-      <c r="H69" s="47" t="n"/>
-      <c r="I69" s="42" t="n"/>
-      <c r="J69" s="42" t="n"/>
+      <c r="G69" s="37" t="n"/>
+      <c r="H69" s="37" t="n"/>
+      <c r="I69" s="38" t="n"/>
+      <c r="J69" s="38" t="n"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8975,10 +8133,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G70" s="47" t="n"/>
-      <c r="H70" s="47" t="n"/>
-      <c r="I70" s="42" t="n"/>
-      <c r="J70" s="42" t="n"/>
+      <c r="G70" s="37" t="n"/>
+      <c r="H70" s="37" t="n"/>
+      <c r="I70" s="38" t="n"/>
+      <c r="J70" s="38" t="n"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9006,10 +8164,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G71" s="47" t="n"/>
-      <c r="H71" s="47" t="n"/>
-      <c r="I71" s="42" t="n"/>
-      <c r="J71" s="42" t="n"/>
+      <c r="G71" s="37" t="n"/>
+      <c r="H71" s="37" t="n"/>
+      <c r="I71" s="38" t="n"/>
+      <c r="J71" s="38" t="n"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9040,10 +8198,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G72" s="47" t="n"/>
-      <c r="H72" s="47" t="n"/>
-      <c r="I72" s="42" t="n"/>
-      <c r="J72" s="42" t="n"/>
+      <c r="G72" s="37" t="n"/>
+      <c r="H72" s="37" t="n"/>
+      <c r="I72" s="38" t="n"/>
+      <c r="J72" s="38" t="n"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9071,10 +8229,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G73" s="47" t="n"/>
-      <c r="H73" s="47" t="n"/>
-      <c r="I73" s="42" t="n"/>
-      <c r="J73" s="42" t="n"/>
+      <c r="G73" s="37" t="n"/>
+      <c r="H73" s="37" t="n"/>
+      <c r="I73" s="38" t="n"/>
+      <c r="J73" s="38" t="n"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9105,10 +8263,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G74" s="47" t="n"/>
-      <c r="H74" s="47" t="n"/>
-      <c r="I74" s="42" t="n"/>
-      <c r="J74" s="42" t="n"/>
+      <c r="G74" s="37" t="n"/>
+      <c r="H74" s="37" t="n"/>
+      <c r="I74" s="38" t="n"/>
+      <c r="J74" s="38" t="n"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9139,10 +8297,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G75" s="47" t="n"/>
-      <c r="H75" s="47" t="n"/>
-      <c r="I75" s="42" t="n"/>
-      <c r="J75" s="42" t="n"/>
+      <c r="G75" s="37" t="n"/>
+      <c r="H75" s="37" t="n"/>
+      <c r="I75" s="38" t="n"/>
+      <c r="J75" s="38" t="n"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9170,10 +8328,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G76" s="47" t="n"/>
-      <c r="H76" s="47" t="n"/>
-      <c r="I76" s="42" t="n"/>
-      <c r="J76" s="42" t="n"/>
+      <c r="G76" s="37" t="n"/>
+      <c r="H76" s="37" t="n"/>
+      <c r="I76" s="38" t="n"/>
+      <c r="J76" s="38" t="n"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9201,10 +8359,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G77" s="47" t="n"/>
-      <c r="H77" s="47" t="n"/>
-      <c r="I77" s="42" t="n"/>
-      <c r="J77" s="42" t="n"/>
+      <c r="G77" s="37" t="n"/>
+      <c r="H77" s="37" t="n"/>
+      <c r="I77" s="38" t="n"/>
+      <c r="J77" s="38" t="n"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9235,10 +8393,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G78" s="47" t="n"/>
-      <c r="H78" s="47" t="n"/>
-      <c r="I78" s="42" t="n"/>
-      <c r="J78" s="42" t="n"/>
+      <c r="G78" s="37" t="n"/>
+      <c r="H78" s="37" t="n"/>
+      <c r="I78" s="38" t="n"/>
+      <c r="J78" s="38" t="n"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9269,10 +8427,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G79" s="47" t="n"/>
-      <c r="H79" s="47" t="n"/>
-      <c r="I79" s="42" t="n"/>
-      <c r="J79" s="42" t="n"/>
+      <c r="G79" s="37" t="n"/>
+      <c r="H79" s="37" t="n"/>
+      <c r="I79" s="38" t="n"/>
+      <c r="J79" s="38" t="n"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9300,10 +8458,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G80" s="47" t="n"/>
-      <c r="H80" s="47" t="n"/>
-      <c r="I80" s="42" t="n"/>
-      <c r="J80" s="42" t="n"/>
+      <c r="G80" s="37" t="n"/>
+      <c r="H80" s="37" t="n"/>
+      <c r="I80" s="38" t="n"/>
+      <c r="J80" s="38" t="n"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9334,10 +8492,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G81" s="47" t="n"/>
-      <c r="H81" s="47" t="n"/>
-      <c r="I81" s="42" t="n"/>
-      <c r="J81" s="42" t="n"/>
+      <c r="G81" s="37" t="n"/>
+      <c r="H81" s="37" t="n"/>
+      <c r="I81" s="38" t="n"/>
+      <c r="J81" s="38" t="n"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9368,10 +8526,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G82" s="47" t="n"/>
-      <c r="H82" s="47" t="n"/>
-      <c r="I82" s="42" t="n"/>
-      <c r="J82" s="42" t="n"/>
+      <c r="G82" s="37" t="n"/>
+      <c r="H82" s="37" t="n"/>
+      <c r="I82" s="38" t="n"/>
+      <c r="J82" s="38" t="n"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9402,10 +8560,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G83" s="47" t="n"/>
-      <c r="H83" s="47" t="n"/>
-      <c r="I83" s="42" t="n"/>
-      <c r="J83" s="42" t="n"/>
+      <c r="G83" s="37" t="n"/>
+      <c r="H83" s="37" t="n"/>
+      <c r="I83" s="38" t="n"/>
+      <c r="J83" s="38" t="n"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9436,10 +8594,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G84" s="47" t="n"/>
-      <c r="H84" s="47" t="n"/>
-      <c r="I84" s="42" t="n"/>
-      <c r="J84" s="42" t="n"/>
+      <c r="G84" s="37" t="n"/>
+      <c r="H84" s="37" t="n"/>
+      <c r="I84" s="38" t="n"/>
+      <c r="J84" s="38" t="n"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9470,10 +8628,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G85" s="47" t="n"/>
-      <c r="H85" s="47" t="n"/>
-      <c r="I85" s="42" t="n"/>
-      <c r="J85" s="42" t="n"/>
+      <c r="G85" s="37" t="n"/>
+      <c r="H85" s="37" t="n"/>
+      <c r="I85" s="38" t="n"/>
+      <c r="J85" s="38" t="n"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9501,10 +8659,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G86" s="47" t="n"/>
-      <c r="H86" s="47" t="n"/>
-      <c r="I86" s="42" t="n"/>
-      <c r="J86" s="42" t="n"/>
+      <c r="G86" s="37" t="n"/>
+      <c r="H86" s="37" t="n"/>
+      <c r="I86" s="38" t="n"/>
+      <c r="J86" s="38" t="n"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9535,10 +8693,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G87" s="47" t="n"/>
-      <c r="H87" s="47" t="n"/>
-      <c r="I87" s="42" t="n"/>
-      <c r="J87" s="42" t="n"/>
+      <c r="G87" s="37" t="n"/>
+      <c r="H87" s="37" t="n"/>
+      <c r="I87" s="38" t="n"/>
+      <c r="J87" s="38" t="n"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9569,10 +8727,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G88" s="47" t="n"/>
-      <c r="H88" s="47" t="n"/>
-      <c r="I88" s="42" t="n"/>
-      <c r="J88" s="42" t="n"/>
+      <c r="G88" s="37" t="n"/>
+      <c r="H88" s="37" t="n"/>
+      <c r="I88" s="38" t="n"/>
+      <c r="J88" s="38" t="n"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9600,10 +8758,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G89" s="47" t="n"/>
-      <c r="H89" s="47" t="n"/>
-      <c r="I89" s="42" t="n"/>
-      <c r="J89" s="42" t="n"/>
+      <c r="G89" s="37" t="n"/>
+      <c r="H89" s="37" t="n"/>
+      <c r="I89" s="38" t="n"/>
+      <c r="J89" s="38" t="n"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9631,10 +8789,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G90" s="47" t="n"/>
-      <c r="H90" s="47" t="n"/>
-      <c r="I90" s="42" t="n"/>
-      <c r="J90" s="42" t="n"/>
+      <c r="G90" s="37" t="n"/>
+      <c r="H90" s="37" t="n"/>
+      <c r="I90" s="38" t="n"/>
+      <c r="J90" s="38" t="n"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9665,10 +8823,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G91" s="47" t="n"/>
-      <c r="H91" s="47" t="n"/>
-      <c r="I91" s="42" t="n"/>
-      <c r="J91" s="42" t="n"/>
+      <c r="G91" s="37" t="n"/>
+      <c r="H91" s="37" t="n"/>
+      <c r="I91" s="38" t="n"/>
+      <c r="J91" s="38" t="n"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9699,10 +8857,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G92" s="47" t="n"/>
-      <c r="H92" s="47" t="n"/>
-      <c r="I92" s="42" t="n"/>
-      <c r="J92" s="42" t="n"/>
+      <c r="G92" s="37" t="n"/>
+      <c r="H92" s="37" t="n"/>
+      <c r="I92" s="38" t="n"/>
+      <c r="J92" s="38" t="n"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9730,10 +8888,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G93" s="47" t="n"/>
-      <c r="H93" s="47" t="n"/>
-      <c r="I93" s="42" t="n"/>
-      <c r="J93" s="42" t="n"/>
+      <c r="G93" s="37" t="n"/>
+      <c r="H93" s="37" t="n"/>
+      <c r="I93" s="38" t="n"/>
+      <c r="J93" s="38" t="n"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9764,10 +8922,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G94" s="47" t="n"/>
-      <c r="H94" s="47" t="n"/>
-      <c r="I94" s="42" t="n"/>
-      <c r="J94" s="42" t="n"/>
+      <c r="G94" s="37" t="n"/>
+      <c r="H94" s="37" t="n"/>
+      <c r="I94" s="38" t="n"/>
+      <c r="J94" s="38" t="n"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9798,10 +8956,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G95" s="47" t="n"/>
-      <c r="H95" s="47" t="n"/>
-      <c r="I95" s="42" t="n"/>
-      <c r="J95" s="42" t="n"/>
+      <c r="G95" s="37" t="n"/>
+      <c r="H95" s="37" t="n"/>
+      <c r="I95" s="38" t="n"/>
+      <c r="J95" s="38" t="n"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9832,10 +8990,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G96" s="47" t="n"/>
-      <c r="H96" s="47" t="n"/>
-      <c r="I96" s="42" t="n"/>
-      <c r="J96" s="42" t="n"/>
+      <c r="G96" s="37" t="n"/>
+      <c r="H96" s="37" t="n"/>
+      <c r="I96" s="38" t="n"/>
+      <c r="J96" s="38" t="n"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9863,10 +9021,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G97" s="47" t="n"/>
-      <c r="H97" s="47" t="n"/>
-      <c r="I97" s="42" t="n"/>
-      <c r="J97" s="42" t="n"/>
+      <c r="G97" s="37" t="n"/>
+      <c r="H97" s="37" t="n"/>
+      <c r="I97" s="38" t="n"/>
+      <c r="J97" s="38" t="n"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9894,10 +9052,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G98" s="47" t="n"/>
-      <c r="H98" s="47" t="n"/>
-      <c r="I98" s="42" t="n"/>
-      <c r="J98" s="42" t="n"/>
+      <c r="G98" s="37" t="n"/>
+      <c r="H98" s="37" t="n"/>
+      <c r="I98" s="38" t="n"/>
+      <c r="J98" s="38" t="n"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9928,10 +9086,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G99" s="47" t="n"/>
-      <c r="H99" s="47" t="n"/>
-      <c r="I99" s="42" t="n"/>
-      <c r="J99" s="42" t="n"/>
+      <c r="G99" s="37" t="n"/>
+      <c r="H99" s="37" t="n"/>
+      <c r="I99" s="38" t="n"/>
+      <c r="J99" s="38" t="n"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9962,10 +9120,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G100" s="47" t="n"/>
-      <c r="H100" s="47" t="n"/>
-      <c r="I100" s="42" t="n"/>
-      <c r="J100" s="42" t="n"/>
+      <c r="G100" s="37" t="n"/>
+      <c r="H100" s="37" t="n"/>
+      <c r="I100" s="38" t="n"/>
+      <c r="J100" s="38" t="n"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9996,10 +9154,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G101" s="47" t="n"/>
-      <c r="H101" s="47" t="n"/>
-      <c r="I101" s="42" t="n"/>
-      <c r="J101" s="42" t="n"/>
+      <c r="G101" s="37" t="n"/>
+      <c r="H101" s="37" t="n"/>
+      <c r="I101" s="38" t="n"/>
+      <c r="J101" s="38" t="n"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10030,10 +9188,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G102" s="47" t="n"/>
-      <c r="H102" s="47" t="n"/>
-      <c r="I102" s="42" t="n"/>
-      <c r="J102" s="42" t="n"/>
+      <c r="G102" s="37" t="n"/>
+      <c r="H102" s="37" t="n"/>
+      <c r="I102" s="38" t="n"/>
+      <c r="J102" s="38" t="n"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10064,10 +9222,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G103" s="47" t="n"/>
-      <c r="H103" s="47" t="n"/>
-      <c r="I103" s="42" t="n"/>
-      <c r="J103" s="42" t="n"/>
+      <c r="G103" s="37" t="n"/>
+      <c r="H103" s="37" t="n"/>
+      <c r="I103" s="38" t="n"/>
+      <c r="J103" s="38" t="n"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10095,10 +9253,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G104" s="47" t="n"/>
-      <c r="H104" s="47" t="n"/>
-      <c r="I104" s="42" t="n"/>
-      <c r="J104" s="42" t="n"/>
+      <c r="G104" s="37" t="n"/>
+      <c r="H104" s="37" t="n"/>
+      <c r="I104" s="38" t="n"/>
+      <c r="J104" s="38" t="n"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10129,10 +9287,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G105" s="47" t="n"/>
-      <c r="H105" s="47" t="n"/>
-      <c r="I105" s="42" t="n"/>
-      <c r="J105" s="42" t="n"/>
+      <c r="G105" s="37" t="n"/>
+      <c r="H105" s="37" t="n"/>
+      <c r="I105" s="38" t="n"/>
+      <c r="J105" s="38" t="n"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10147,4 +9305,2178 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:M98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY &amp; ABSORPTION FORECAST — 5-MILE MARKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Stabilization Target</t>
+        </is>
+      </c>
+      <c r="C3" s="40">
+        <f>Settings!$B$2</f>
+        <v/>
+      </c>
+      <c r="J3" s="36" t="inlineStr">
+        <is>
+          <t>PIPELINE INPUTS  (forward new supply — edit date / include)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>Demand Scenario (Bear/Base/Bull)</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J4" s="43" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="K4" s="43" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="L4" s="43" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="M4" s="43" t="inlineStr">
+        <is>
+          <t>Include?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Hist. Avg Annual Absorption (CoStar)</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>2525</v>
+      </c>
+      <c r="J5" s="45" t="inlineStr">
+        <is>
+          <t>Sheely Center Future Phase</t>
+        </is>
+      </c>
+      <c r="K5" s="46" t="n">
+        <v>697</v>
+      </c>
+      <c r="L5" s="47" t="inlineStr"/>
+      <c r="M5" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Bear — Annual Absorption (units)</t>
+        </is>
+      </c>
+      <c r="C6" s="44" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J6" s="45" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel C</t>
+        </is>
+      </c>
+      <c r="K6" s="46" t="n">
+        <v>500</v>
+      </c>
+      <c r="L6" s="47" t="inlineStr"/>
+      <c r="M6" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Base — Annual Absorption (units)</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>2525</v>
+      </c>
+      <c r="J7" s="45" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel B</t>
+        </is>
+      </c>
+      <c r="K7" s="46" t="n">
+        <v>478</v>
+      </c>
+      <c r="L7" s="47" t="inlineStr"/>
+      <c r="M7" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Bull — Annual Absorption (units)</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>3800</v>
+      </c>
+      <c r="J8" s="45" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel B</t>
+        </is>
+      </c>
+      <c r="K8" s="46" t="n">
+        <v>410</v>
+      </c>
+      <c r="L8" s="47" t="inlineStr"/>
+      <c r="M8" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>Selected Annual Demand</t>
+        </is>
+      </c>
+      <c r="C9" s="44">
+        <f>IF($C$4="Bear",$C$6,IF($C$4="Bull",$C$8,$C$7))</f>
+        <v/>
+      </c>
+      <c r="J9" s="45" t="inlineStr">
+        <is>
+          <t>The District at Westgate</t>
+        </is>
+      </c>
+      <c r="K9" s="46" t="n">
+        <v>384</v>
+      </c>
+      <c r="L9" s="47" t="inlineStr"/>
+      <c r="M9" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Selected Quarterly Demand</t>
+        </is>
+      </c>
+      <c r="C10" s="44">
+        <f>$C$9/4</f>
+        <v/>
+      </c>
+      <c r="J10" s="45" t="inlineStr">
+        <is>
+          <t>Picerne at Palm Valley</t>
+        </is>
+      </c>
+      <c r="K10" s="46" t="n">
+        <v>383</v>
+      </c>
+      <c r="L10" s="47" t="inlineStr"/>
+      <c r="M10" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="J11" s="45" t="inlineStr">
+        <is>
+          <t>Liv Avondale</t>
+        </is>
+      </c>
+      <c r="K11" s="46" t="n">
+        <v>333</v>
+      </c>
+      <c r="L11" s="47" t="inlineStr"/>
+      <c r="M11" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="J12" s="45" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel A</t>
+        </is>
+      </c>
+      <c r="K12" s="46" t="n">
+        <v>324</v>
+      </c>
+      <c r="L12" s="47" t="inlineStr"/>
+      <c r="M12" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="J13" s="45" t="inlineStr">
+        <is>
+          <t>The Waverly</t>
+        </is>
+      </c>
+      <c r="K13" s="46" t="n">
+        <v>323</v>
+      </c>
+      <c r="L13" s="47" t="inlineStr"/>
+      <c r="M13" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="J14" s="45" t="inlineStr">
+        <is>
+          <t>Fuze 623</t>
+        </is>
+      </c>
+      <c r="K14" s="46" t="n">
+        <v>321</v>
+      </c>
+      <c r="L14" s="47" t="inlineStr"/>
+      <c r="M14" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="J15" s="45" t="inlineStr">
+        <is>
+          <t>Anton Glendale</t>
+        </is>
+      </c>
+      <c r="K15" s="46" t="n">
+        <v>320</v>
+      </c>
+      <c r="L15" s="47" t="inlineStr"/>
+      <c r="M15" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="J16" s="45" t="inlineStr">
+        <is>
+          <t>Western Garden II</t>
+        </is>
+      </c>
+      <c r="K16" s="46" t="n">
+        <v>314</v>
+      </c>
+      <c r="L16" s="47" t="inlineStr"/>
+      <c r="M16" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="J17" s="45" t="inlineStr">
+        <is>
+          <t>Sanctuair at Centerscape</t>
+        </is>
+      </c>
+      <c r="K17" s="46" t="n">
+        <v>303</v>
+      </c>
+      <c r="L17" s="47" t="inlineStr"/>
+      <c r="M17" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="J18" s="45" t="inlineStr">
+        <is>
+          <t>Encore Avondale</t>
+        </is>
+      </c>
+      <c r="K18" s="46" t="n">
+        <v>300</v>
+      </c>
+      <c r="L18" s="47" t="inlineStr"/>
+      <c r="M18" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="J19" s="45" t="inlineStr">
+        <is>
+          <t>Banyan Avondale</t>
+        </is>
+      </c>
+      <c r="K19" s="46" t="n">
+        <v>296</v>
+      </c>
+      <c r="L19" s="47" t="inlineStr"/>
+      <c r="M19" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="J20" s="45" t="inlineStr">
+        <is>
+          <t>Rosilian Villas</t>
+        </is>
+      </c>
+      <c r="K20" s="46" t="n">
+        <v>291</v>
+      </c>
+      <c r="L20" s="47" t="inlineStr"/>
+      <c r="M20" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="J21" s="45" t="inlineStr">
+        <is>
+          <t>The Statler at Estrella Parkway</t>
+        </is>
+      </c>
+      <c r="K21" s="46" t="n">
+        <v>284</v>
+      </c>
+      <c r="L21" s="47" t="inlineStr"/>
+      <c r="M21" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="J22" s="45" t="inlineStr">
+        <is>
+          <t>Orion Avondale</t>
+        </is>
+      </c>
+      <c r="K22" s="46" t="n">
+        <v>268</v>
+      </c>
+      <c r="L22" s="47" t="inlineStr"/>
+      <c r="M22" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="J23" s="45" t="inlineStr">
+        <is>
+          <t>Tavalo at Avondale</t>
+        </is>
+      </c>
+      <c r="K23" s="46" t="n">
+        <v>266</v>
+      </c>
+      <c r="L23" s="47" t="inlineStr"/>
+      <c r="M23" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="J24" s="45" t="inlineStr">
+        <is>
+          <t>Marbella Ranch East Future Phase</t>
+        </is>
+      </c>
+      <c r="K24" s="46" t="n">
+        <v>266</v>
+      </c>
+      <c r="L24" s="47" t="inlineStr"/>
+      <c r="M24" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="J25" s="45" t="inlineStr">
+        <is>
+          <t>Crystal Cove</t>
+        </is>
+      </c>
+      <c r="K25" s="46" t="n">
+        <v>260</v>
+      </c>
+      <c r="L25" s="47" t="inlineStr"/>
+      <c r="M25" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="J26" s="45" t="inlineStr">
+        <is>
+          <t>Cornerstone at the Wigwam</t>
+        </is>
+      </c>
+      <c r="K26" s="46" t="n">
+        <v>212</v>
+      </c>
+      <c r="L26" s="47" t="inlineStr"/>
+      <c r="M26" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="J27" s="45" t="inlineStr">
+        <is>
+          <t>Radia Avondale Station III</t>
+        </is>
+      </c>
+      <c r="K27" s="46" t="n">
+        <v>212</v>
+      </c>
+      <c r="L27" s="47" t="inlineStr"/>
+      <c r="M27" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="J28" s="45" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel A</t>
+        </is>
+      </c>
+      <c r="K28" s="46" t="n">
+        <v>181</v>
+      </c>
+      <c r="L28" s="47" t="inlineStr"/>
+      <c r="M28" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="J29" s="45" t="inlineStr">
+        <is>
+          <t>Villages at River Grove</t>
+        </is>
+      </c>
+      <c r="K29" s="46" t="n">
+        <v>180</v>
+      </c>
+      <c r="L29" s="47" t="inlineStr"/>
+      <c r="M29" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="J30" s="45" t="inlineStr">
+        <is>
+          <t>District 99</t>
+        </is>
+      </c>
+      <c r="K30" s="46" t="n">
+        <v>172</v>
+      </c>
+      <c r="L30" s="47" t="inlineStr"/>
+      <c r="M30" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="J31" s="45" t="inlineStr">
+        <is>
+          <t>McDowell Villas</t>
+        </is>
+      </c>
+      <c r="K31" s="46" t="n">
+        <v>164</v>
+      </c>
+      <c r="L31" s="47" t="inlineStr"/>
+      <c r="M31" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="J32" s="45" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="K32" s="46" t="n">
+        <v>156</v>
+      </c>
+      <c r="L32" s="47" t="inlineStr"/>
+      <c r="M32" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="J33" s="45" t="inlineStr">
+        <is>
+          <t>Porter Kyle Development</t>
+        </is>
+      </c>
+      <c r="K33" s="46" t="n">
+        <v>135</v>
+      </c>
+      <c r="L33" s="47" t="inlineStr"/>
+      <c r="M33" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="J34" s="45" t="inlineStr">
+        <is>
+          <t>Ascent Goodyear</t>
+        </is>
+      </c>
+      <c r="K34" s="46" t="n">
+        <v>113</v>
+      </c>
+      <c r="L34" s="47" t="inlineStr"/>
+      <c r="M34" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="J35" s="45" t="inlineStr">
+        <is>
+          <t>Northern 107</t>
+        </is>
+      </c>
+      <c r="K35" s="46" t="n">
+        <v>74</v>
+      </c>
+      <c r="L35" s="47" t="inlineStr"/>
+      <c r="M35" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" s="45" t="inlineStr">
+        <is>
+          <t>Zenn @ Sierra Verde</t>
+        </is>
+      </c>
+      <c r="K36" s="46" t="n">
+        <v>66</v>
+      </c>
+      <c r="L36" s="47" t="inlineStr"/>
+      <c r="M36" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="J37" s="45" t="inlineStr">
+        <is>
+          <t>The BLVD Residential District</t>
+        </is>
+      </c>
+      <c r="K37" s="46" t="n"/>
+      <c r="L37" s="47" t="inlineStr"/>
+      <c r="M37" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="J38" s="45" t="inlineStr">
+        <is>
+          <t>The BLVD Park Avenue District</t>
+        </is>
+      </c>
+      <c r="K38" s="46" t="n"/>
+      <c r="L38" s="47" t="inlineStr"/>
+      <c r="M38" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="J39" s="45" t="inlineStr">
+        <is>
+          <t>Globe Land Investors Development</t>
+        </is>
+      </c>
+      <c r="K39" s="46" t="n"/>
+      <c r="L39" s="47" t="inlineStr"/>
+      <c r="M39" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="J40" s="45" t="inlineStr">
+        <is>
+          <t>Ball Park</t>
+        </is>
+      </c>
+      <c r="K40" s="46" t="n"/>
+      <c r="L40" s="47" t="inlineStr"/>
+      <c r="M40" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="J41" s="45" t="inlineStr">
+        <is>
+          <t>Vision 2 Parcel A</t>
+        </is>
+      </c>
+      <c r="K41" s="46" t="n"/>
+      <c r="L41" s="47" t="inlineStr"/>
+      <c r="M41" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="J42" s="45" t="inlineStr">
+        <is>
+          <t>Firststreet Verde</t>
+        </is>
+      </c>
+      <c r="K42" s="46" t="n"/>
+      <c r="L42" s="47" t="inlineStr"/>
+      <c r="M42" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="J43" s="45" t="inlineStr">
+        <is>
+          <t>Goodyear Civic Square at Estrella Falls</t>
+        </is>
+      </c>
+      <c r="K43" s="46" t="n"/>
+      <c r="L43" s="47" t="inlineStr"/>
+      <c r="M43" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="J44" s="45" t="inlineStr">
+        <is>
+          <t>I-10 Innovation Center II</t>
+        </is>
+      </c>
+      <c r="K44" s="46" t="n"/>
+      <c r="L44" s="47" t="inlineStr"/>
+      <c r="M44" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="J45" s="45" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel D</t>
+        </is>
+      </c>
+      <c r="K45" s="46" t="n"/>
+      <c r="L45" s="47" t="inlineStr"/>
+      <c r="M45" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="J46" s="45" t="inlineStr">
+        <is>
+          <t>SimonMed Development II</t>
+        </is>
+      </c>
+      <c r="K46" s="46" t="n"/>
+      <c r="L46" s="47" t="inlineStr"/>
+      <c r="M46" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="J47" s="45" t="inlineStr">
+        <is>
+          <t>182 South 95th Avenue</t>
+        </is>
+      </c>
+      <c r="K47" s="46" t="n"/>
+      <c r="L47" s="47" t="inlineStr"/>
+      <c r="M47" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="J48" s="45" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="K48" s="46" t="n"/>
+      <c r="L48" s="47" t="inlineStr"/>
+      <c r="M48" s="47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="J49" s="45" t="inlineStr">
+        <is>
+          <t>FUZE Ballpark</t>
+        </is>
+      </c>
+      <c r="K49" s="46" t="n">
+        <v>321</v>
+      </c>
+      <c r="L49" s="47" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="M49" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="J50" s="45" t="inlineStr">
+        <is>
+          <t>Zanjero III</t>
+        </is>
+      </c>
+      <c r="K50" s="46" t="n">
+        <v>301</v>
+      </c>
+      <c r="L50" s="47" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="M50" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="J51" s="45" t="inlineStr">
+        <is>
+          <t>Pointe Grand Estrella at Phoenix</t>
+        </is>
+      </c>
+      <c r="K51" s="46" t="n">
+        <v>288</v>
+      </c>
+      <c r="L51" s="47" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="M51" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="J52" s="45" t="inlineStr">
+        <is>
+          <t>Yardly Algodon</t>
+        </is>
+      </c>
+      <c r="K52" s="46" t="n">
+        <v>262</v>
+      </c>
+      <c r="L52" s="47" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="M52" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="J53" s="45" t="inlineStr">
+        <is>
+          <t>Cerro Vista</t>
+        </is>
+      </c>
+      <c r="K53" s="46" t="n">
+        <v>255</v>
+      </c>
+      <c r="L53" s="47" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="M53" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="J54" s="45" t="inlineStr">
+        <is>
+          <t>Marbella Ranch East I</t>
+        </is>
+      </c>
+      <c r="K54" s="46" t="n">
+        <v>144</v>
+      </c>
+      <c r="L54" s="47" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="M54" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="J55" s="45" t="inlineStr">
+        <is>
+          <t>Zen @ Angelina</t>
+        </is>
+      </c>
+      <c r="K55" s="46" t="n">
+        <v>130</v>
+      </c>
+      <c r="L55" s="47" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="M55" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="J56" s="45" t="inlineStr">
+        <is>
+          <t>HARMON Ascend</t>
+        </is>
+      </c>
+      <c r="K56" s="46" t="n">
+        <v>125</v>
+      </c>
+      <c r="L56" s="47" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="M56" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="J57" s="45" t="inlineStr">
+        <is>
+          <t>Villages at Northern</t>
+        </is>
+      </c>
+      <c r="K57" s="46" t="n">
+        <v>74</v>
+      </c>
+      <c r="L57" s="47" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="M57" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="J58" s="45" t="inlineStr">
+        <is>
+          <t>Prosper 47</t>
+        </is>
+      </c>
+      <c r="K58" s="46" t="n">
+        <v>47</v>
+      </c>
+      <c r="L58" s="47" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="M58" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>New Supply</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Absorption</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Occupied</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Overall Occ</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2023</t>
+        </is>
+      </c>
+      <c r="C61" s="49" t="n">
+        <v>738</v>
+      </c>
+      <c r="D61" s="49" t="n">
+        <v>221</v>
+      </c>
+      <c r="E61" s="49" t="n">
+        <v>15268</v>
+      </c>
+      <c r="F61" s="49" t="n">
+        <v>18615</v>
+      </c>
+      <c r="G61" s="50">
+        <f>IFERROR(E61/F61,0)</f>
+        <v/>
+      </c>
+      <c r="H61" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="48" t="inlineStr">
+        <is>
+          <t>Q4 2023</t>
+        </is>
+      </c>
+      <c r="C62" s="49" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D62" s="49" t="n">
+        <v>590</v>
+      </c>
+      <c r="E62" s="49" t="n">
+        <v>15857</v>
+      </c>
+      <c r="F62" s="49" t="n">
+        <v>19915</v>
+      </c>
+      <c r="G62" s="50">
+        <f>IFERROR(E62/F62,0)</f>
+        <v/>
+      </c>
+      <c r="H62" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="48" t="inlineStr">
+        <is>
+          <t>Q1 2024</t>
+        </is>
+      </c>
+      <c r="C63" s="49" t="n">
+        <v>600</v>
+      </c>
+      <c r="D63" s="49" t="n">
+        <v>791</v>
+      </c>
+      <c r="E63" s="49" t="n">
+        <v>16648</v>
+      </c>
+      <c r="F63" s="49" t="n">
+        <v>20515</v>
+      </c>
+      <c r="G63" s="50">
+        <f>IFERROR(E63/F63,0)</f>
+        <v/>
+      </c>
+      <c r="H63" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="48" t="inlineStr">
+        <is>
+          <t>Q2 2024</t>
+        </is>
+      </c>
+      <c r="C64" s="49" t="n">
+        <v>185</v>
+      </c>
+      <c r="D64" s="49" t="n">
+        <v>912</v>
+      </c>
+      <c r="E64" s="49" t="n">
+        <v>17560</v>
+      </c>
+      <c r="F64" s="49" t="n">
+        <v>20700</v>
+      </c>
+      <c r="G64" s="50">
+        <f>IFERROR(E64/F64,0)</f>
+        <v/>
+      </c>
+      <c r="H64" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2024</t>
+        </is>
+      </c>
+      <c r="C65" s="49" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D65" s="49" t="n">
+        <v>851</v>
+      </c>
+      <c r="E65" s="49" t="n">
+        <v>18411</v>
+      </c>
+      <c r="F65" s="49" t="n">
+        <v>22103</v>
+      </c>
+      <c r="G65" s="50">
+        <f>IFERROR(E65/F65,0)</f>
+        <v/>
+      </c>
+      <c r="H65" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="48" t="inlineStr">
+        <is>
+          <t>Q4 2024</t>
+        </is>
+      </c>
+      <c r="C66" s="49" t="n">
+        <v>669</v>
+      </c>
+      <c r="D66" s="49" t="n">
+        <v>529</v>
+      </c>
+      <c r="E66" s="49" t="n">
+        <v>18940</v>
+      </c>
+      <c r="F66" s="49" t="n">
+        <v>22772</v>
+      </c>
+      <c r="G66" s="50">
+        <f>IFERROR(E66/F66,0)</f>
+        <v/>
+      </c>
+      <c r="H66" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="48" t="inlineStr">
+        <is>
+          <t>Q1 2025</t>
+        </is>
+      </c>
+      <c r="C67" s="49" t="n">
+        <v>1748</v>
+      </c>
+      <c r="D67" s="49" t="n">
+        <v>641</v>
+      </c>
+      <c r="E67" s="49" t="n">
+        <v>19581</v>
+      </c>
+      <c r="F67" s="49" t="n">
+        <v>24520</v>
+      </c>
+      <c r="G67" s="50">
+        <f>IFERROR(E67/F67,0)</f>
+        <v/>
+      </c>
+      <c r="H67" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="48" t="inlineStr">
+        <is>
+          <t>Q2 2025</t>
+        </is>
+      </c>
+      <c r="C68" s="49" t="n">
+        <v>223</v>
+      </c>
+      <c r="D68" s="49" t="n">
+        <v>634</v>
+      </c>
+      <c r="E68" s="49" t="n">
+        <v>20215</v>
+      </c>
+      <c r="F68" s="49" t="n">
+        <v>24743</v>
+      </c>
+      <c r="G68" s="50">
+        <f>IFERROR(E68/F68,0)</f>
+        <v/>
+      </c>
+      <c r="H68" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2025</t>
+        </is>
+      </c>
+      <c r="C69" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="D69" s="49" t="n">
+        <v>498</v>
+      </c>
+      <c r="E69" s="49" t="n">
+        <v>20713</v>
+      </c>
+      <c r="F69" s="49" t="n">
+        <v>24827</v>
+      </c>
+      <c r="G69" s="50">
+        <f>IFERROR(E69/F69,0)</f>
+        <v/>
+      </c>
+      <c r="H69" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="48" t="inlineStr">
+        <is>
+          <t>Q4 2025</t>
+        </is>
+      </c>
+      <c r="C70" s="49" t="n">
+        <v>634</v>
+      </c>
+      <c r="D70" s="49" t="n">
+        <v>680</v>
+      </c>
+      <c r="E70" s="49" t="n">
+        <v>21394</v>
+      </c>
+      <c r="F70" s="49" t="n">
+        <v>25461</v>
+      </c>
+      <c r="G70" s="50">
+        <f>IFERROR(E70/F70,0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="48" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="C71" s="49" t="n">
+        <v>676</v>
+      </c>
+      <c r="D71" s="49" t="n">
+        <v>726</v>
+      </c>
+      <c r="E71" s="49" t="n">
+        <v>22120</v>
+      </c>
+      <c r="F71" s="49" t="n">
+        <v>26137</v>
+      </c>
+      <c r="G71" s="50">
+        <f>IFERROR(E71/F71,0)</f>
+        <v/>
+      </c>
+      <c r="H71" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="48" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C72" s="49" t="n">
+        <v>466</v>
+      </c>
+      <c r="D72" s="49" t="n">
+        <v>465</v>
+      </c>
+      <c r="E72" s="49" t="n">
+        <v>22585</v>
+      </c>
+      <c r="F72" s="49" t="n">
+        <v>26603</v>
+      </c>
+      <c r="G72" s="50">
+        <f>IFERROR(E72/F72,0)</f>
+        <v/>
+      </c>
+      <c r="H72" s="48" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="51" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="C73" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B73,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D73" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F73-E72))</f>
+        <v/>
+      </c>
+      <c r="E73" s="52">
+        <f>E72+D73</f>
+        <v/>
+      </c>
+      <c r="F73" s="52">
+        <f>F72+C73</f>
+        <v/>
+      </c>
+      <c r="G73" s="53">
+        <f>IFERROR(E73/F73,0)</f>
+        <v/>
+      </c>
+      <c r="H73" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="51" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="C74" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B74,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D74" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F74-E73))</f>
+        <v/>
+      </c>
+      <c r="E74" s="52">
+        <f>E73+D74</f>
+        <v/>
+      </c>
+      <c r="F74" s="52">
+        <f>F73+C74</f>
+        <v/>
+      </c>
+      <c r="G74" s="53">
+        <f>IFERROR(E74/F74,0)</f>
+        <v/>
+      </c>
+      <c r="H74" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="51" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="C75" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B75,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D75" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F75-E74))</f>
+        <v/>
+      </c>
+      <c r="E75" s="52">
+        <f>E74+D75</f>
+        <v/>
+      </c>
+      <c r="F75" s="52">
+        <f>F74+C75</f>
+        <v/>
+      </c>
+      <c r="G75" s="53">
+        <f>IFERROR(E75/F75,0)</f>
+        <v/>
+      </c>
+      <c r="H75" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="51" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="C76" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B76,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D76" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F76-E75))</f>
+        <v/>
+      </c>
+      <c r="E76" s="52">
+        <f>E75+D76</f>
+        <v/>
+      </c>
+      <c r="F76" s="52">
+        <f>F75+C76</f>
+        <v/>
+      </c>
+      <c r="G76" s="53">
+        <f>IFERROR(E76/F76,0)</f>
+        <v/>
+      </c>
+      <c r="H76" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="51" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="C77" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B77,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D77" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F77-E76))</f>
+        <v/>
+      </c>
+      <c r="E77" s="52">
+        <f>E76+D77</f>
+        <v/>
+      </c>
+      <c r="F77" s="52">
+        <f>F76+C77</f>
+        <v/>
+      </c>
+      <c r="G77" s="53">
+        <f>IFERROR(E77/F77,0)</f>
+        <v/>
+      </c>
+      <c r="H77" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="51" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="C78" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B78,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D78" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F78-E77))</f>
+        <v/>
+      </c>
+      <c r="E78" s="52">
+        <f>E77+D78</f>
+        <v/>
+      </c>
+      <c r="F78" s="52">
+        <f>F77+C78</f>
+        <v/>
+      </c>
+      <c r="G78" s="53">
+        <f>IFERROR(E78/F78,0)</f>
+        <v/>
+      </c>
+      <c r="H78" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="51" t="inlineStr">
+        <is>
+          <t>Q1 2028</t>
+        </is>
+      </c>
+      <c r="C79" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B79,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D79" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F79-E78))</f>
+        <v/>
+      </c>
+      <c r="E79" s="52">
+        <f>E78+D79</f>
+        <v/>
+      </c>
+      <c r="F79" s="52">
+        <f>F78+C79</f>
+        <v/>
+      </c>
+      <c r="G79" s="53">
+        <f>IFERROR(E79/F79,0)</f>
+        <v/>
+      </c>
+      <c r="H79" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="51" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="C80" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B80,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D80" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F80-E79))</f>
+        <v/>
+      </c>
+      <c r="E80" s="52">
+        <f>E79+D80</f>
+        <v/>
+      </c>
+      <c r="F80" s="52">
+        <f>F79+C80</f>
+        <v/>
+      </c>
+      <c r="G80" s="53">
+        <f>IFERROR(E80/F80,0)</f>
+        <v/>
+      </c>
+      <c r="H80" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="51" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="C81" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B81,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D81" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F81-E80))</f>
+        <v/>
+      </c>
+      <c r="E81" s="52">
+        <f>E80+D81</f>
+        <v/>
+      </c>
+      <c r="F81" s="52">
+        <f>F80+C81</f>
+        <v/>
+      </c>
+      <c r="G81" s="53">
+        <f>IFERROR(E81/F81,0)</f>
+        <v/>
+      </c>
+      <c r="H81" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="51" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="C82" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B82,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D82" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F82-E81))</f>
+        <v/>
+      </c>
+      <c r="E82" s="52">
+        <f>E81+D82</f>
+        <v/>
+      </c>
+      <c r="F82" s="52">
+        <f>F81+C82</f>
+        <v/>
+      </c>
+      <c r="G82" s="53">
+        <f>IFERROR(E82/F82,0)</f>
+        <v/>
+      </c>
+      <c r="H82" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="51" t="inlineStr">
+        <is>
+          <t>Q1 2029</t>
+        </is>
+      </c>
+      <c r="C83" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B83,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D83" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F83-E82))</f>
+        <v/>
+      </c>
+      <c r="E83" s="52">
+        <f>E82+D83</f>
+        <v/>
+      </c>
+      <c r="F83" s="52">
+        <f>F82+C83</f>
+        <v/>
+      </c>
+      <c r="G83" s="53">
+        <f>IFERROR(E83/F83,0)</f>
+        <v/>
+      </c>
+      <c r="H83" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="51" t="inlineStr">
+        <is>
+          <t>Q2 2029</t>
+        </is>
+      </c>
+      <c r="C84" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B84,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D84" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F84-E83))</f>
+        <v/>
+      </c>
+      <c r="E84" s="52">
+        <f>E83+D84</f>
+        <v/>
+      </c>
+      <c r="F84" s="52">
+        <f>F83+C84</f>
+        <v/>
+      </c>
+      <c r="G84" s="53">
+        <f>IFERROR(E84/F84,0)</f>
+        <v/>
+      </c>
+      <c r="H84" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="51" t="inlineStr">
+        <is>
+          <t>Q3 2029</t>
+        </is>
+      </c>
+      <c r="C85" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B85,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D85" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F85-E84))</f>
+        <v/>
+      </c>
+      <c r="E85" s="52">
+        <f>E84+D85</f>
+        <v/>
+      </c>
+      <c r="F85" s="52">
+        <f>F84+C85</f>
+        <v/>
+      </c>
+      <c r="G85" s="53">
+        <f>IFERROR(E85/F85,0)</f>
+        <v/>
+      </c>
+      <c r="H85" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="51" t="inlineStr">
+        <is>
+          <t>Q4 2029</t>
+        </is>
+      </c>
+      <c r="C86" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B86,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D86" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F86-E85))</f>
+        <v/>
+      </c>
+      <c r="E86" s="52">
+        <f>E85+D86</f>
+        <v/>
+      </c>
+      <c r="F86" s="52">
+        <f>F85+C86</f>
+        <v/>
+      </c>
+      <c r="G86" s="53">
+        <f>IFERROR(E86/F86,0)</f>
+        <v/>
+      </c>
+      <c r="H86" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="51" t="inlineStr">
+        <is>
+          <t>Q1 2030</t>
+        </is>
+      </c>
+      <c r="C87" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B87,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D87" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F87-E86))</f>
+        <v/>
+      </c>
+      <c r="E87" s="52">
+        <f>E86+D87</f>
+        <v/>
+      </c>
+      <c r="F87" s="52">
+        <f>F86+C87</f>
+        <v/>
+      </c>
+      <c r="G87" s="53">
+        <f>IFERROR(E87/F87,0)</f>
+        <v/>
+      </c>
+      <c r="H87" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="51" t="inlineStr">
+        <is>
+          <t>Q2 2030</t>
+        </is>
+      </c>
+      <c r="C88" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B88,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D88" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F88-E87))</f>
+        <v/>
+      </c>
+      <c r="E88" s="52">
+        <f>E87+D88</f>
+        <v/>
+      </c>
+      <c r="F88" s="52">
+        <f>F87+C88</f>
+        <v/>
+      </c>
+      <c r="G88" s="53">
+        <f>IFERROR(E88/F88,0)</f>
+        <v/>
+      </c>
+      <c r="H88" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="51" t="inlineStr">
+        <is>
+          <t>Q3 2030</t>
+        </is>
+      </c>
+      <c r="C89" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B89,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D89" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F89-E88))</f>
+        <v/>
+      </c>
+      <c r="E89" s="52">
+        <f>E88+D89</f>
+        <v/>
+      </c>
+      <c r="F89" s="52">
+        <f>F88+C89</f>
+        <v/>
+      </c>
+      <c r="G89" s="53">
+        <f>IFERROR(E89/F89,0)</f>
+        <v/>
+      </c>
+      <c r="H89" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="51" t="inlineStr">
+        <is>
+          <t>Q4 2030</t>
+        </is>
+      </c>
+      <c r="C90" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B90,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D90" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F90-E89))</f>
+        <v/>
+      </c>
+      <c r="E90" s="52">
+        <f>E89+D90</f>
+        <v/>
+      </c>
+      <c r="F90" s="52">
+        <f>F89+C90</f>
+        <v/>
+      </c>
+      <c r="G90" s="53">
+        <f>IFERROR(E90/F90,0)</f>
+        <v/>
+      </c>
+      <c r="H90" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="51" t="inlineStr">
+        <is>
+          <t>Q1 2031</t>
+        </is>
+      </c>
+      <c r="C91" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B91,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D91" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F91-E90))</f>
+        <v/>
+      </c>
+      <c r="E91" s="52">
+        <f>E90+D91</f>
+        <v/>
+      </c>
+      <c r="F91" s="52">
+        <f>F90+C91</f>
+        <v/>
+      </c>
+      <c r="G91" s="53">
+        <f>IFERROR(E91/F91,0)</f>
+        <v/>
+      </c>
+      <c r="H91" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="51" t="inlineStr">
+        <is>
+          <t>Q2 2031</t>
+        </is>
+      </c>
+      <c r="C92" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B92,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D92" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F92-E91))</f>
+        <v/>
+      </c>
+      <c r="E92" s="52">
+        <f>E91+D92</f>
+        <v/>
+      </c>
+      <c r="F92" s="52">
+        <f>F91+C92</f>
+        <v/>
+      </c>
+      <c r="G92" s="53">
+        <f>IFERROR(E92/F92,0)</f>
+        <v/>
+      </c>
+      <c r="H92" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="51" t="inlineStr">
+        <is>
+          <t>Q3 2031</t>
+        </is>
+      </c>
+      <c r="C93" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B93,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D93" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F93-E92))</f>
+        <v/>
+      </c>
+      <c r="E93" s="52">
+        <f>E92+D93</f>
+        <v/>
+      </c>
+      <c r="F93" s="52">
+        <f>F92+C93</f>
+        <v/>
+      </c>
+      <c r="G93" s="53">
+        <f>IFERROR(E93/F93,0)</f>
+        <v/>
+      </c>
+      <c r="H93" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="51" t="inlineStr">
+        <is>
+          <t>Q4 2031</t>
+        </is>
+      </c>
+      <c r="C94" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B94,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D94" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F94-E93))</f>
+        <v/>
+      </c>
+      <c r="E94" s="52">
+        <f>E93+D94</f>
+        <v/>
+      </c>
+      <c r="F94" s="52">
+        <f>F93+C94</f>
+        <v/>
+      </c>
+      <c r="G94" s="53">
+        <f>IFERROR(E94/F94,0)</f>
+        <v/>
+      </c>
+      <c r="H94" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="51" t="inlineStr">
+        <is>
+          <t>Q1 2032</t>
+        </is>
+      </c>
+      <c r="C95" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B95,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D95" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F95-E94))</f>
+        <v/>
+      </c>
+      <c r="E95" s="52">
+        <f>E94+D95</f>
+        <v/>
+      </c>
+      <c r="F95" s="52">
+        <f>F94+C95</f>
+        <v/>
+      </c>
+      <c r="G95" s="53">
+        <f>IFERROR(E95/F95,0)</f>
+        <v/>
+      </c>
+      <c r="H95" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="51" t="inlineStr">
+        <is>
+          <t>Q2 2032</t>
+        </is>
+      </c>
+      <c r="C96" s="52">
+        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B96,$M$5:$M$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="D96" s="52">
+        <f>MIN($C$10,MAX(0,$C$3*F96-E95))</f>
+        <v/>
+      </c>
+      <c r="E96" s="52">
+        <f>E95+D96</f>
+        <v/>
+      </c>
+      <c r="F96" s="52">
+        <f>F95+C96</f>
+        <v/>
+      </c>
+      <c r="G96" s="53">
+        <f>IFERROR(E96/F96,0)</f>
+        <v/>
+      </c>
+      <c r="H96" s="51" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="33" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi actuals. Forecast: inventory grows by scheduled pipeline deliveries (edit dates/include at right); absorption = min(quarterly demand, units to reach target); overall occ = occupied / inventory. Yellow cells are editable.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B98:H98"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Bear,Base,Bull"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +80,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -177,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -275,45 +281,67 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2793,15 +2821,15 @@
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>FUZE Ballpark</t>
+          <t>Zanjero III</t>
         </is>
       </c>
       <c r="D60" s="23" t="n">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="F60" s="24" t="n"/>
@@ -2812,7 +2840,7 @@
       </c>
       <c r="H60" s="22" t="inlineStr">
         <is>
-          <t>Zekelman Industries</t>
+          <t>Fore Property Company/Privately Owned</t>
         </is>
       </c>
       <c r="I60" s="21" t="n"/>
@@ -2829,15 +2857,15 @@
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Zanjero III</t>
+          <t>Zen @ Angelina</t>
         </is>
       </c>
       <c r="D61" s="23" t="n">
-        <v>301</v>
+        <v>130</v>
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="F61" s="24" t="n"/>
@@ -2848,16 +2876,20 @@
       </c>
       <c r="H61" s="22" t="inlineStr">
         <is>
-          <t>Fore Property Company/Privately Owned</t>
+          <t>F &amp; S Consulting &amp; Management, LLC</t>
         </is>
       </c>
       <c r="I61" s="21" t="n"/>
       <c r="J61" s="21" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K61" s="22" t="n"/>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K61" s="22" t="inlineStr">
+        <is>
+          <t>Year built: 2027/2028</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="21" t="n">
@@ -2865,15 +2897,15 @@
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pointe Grand Estrella at Phoenix</t>
+          <t>Yardly Algodon</t>
         </is>
       </c>
       <c r="D62" s="23" t="n">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F62" s="24" t="n"/>
@@ -2884,18 +2916,18 @@
       </c>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t>Hillpointe, LLC</t>
+          <t>Taylor Morrison, Inc.</t>
         </is>
       </c>
       <c r="I62" s="21" t="n"/>
       <c r="J62" s="21" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K62" s="22" t="inlineStr">
         <is>
-          <t>Year built: 2026/2027</t>
+          <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
         </is>
       </c>
     </row>
@@ -2905,15 +2937,15 @@
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Yardly Algodon</t>
+          <t>Cerro Vista</t>
         </is>
       </c>
       <c r="D63" s="23" t="n">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F63" s="24" t="n"/>
@@ -2924,20 +2956,16 @@
       </c>
       <c r="H63" s="22" t="inlineStr">
         <is>
-          <t>Taylor Morrison, Inc.</t>
+          <t>Virtua Partners</t>
         </is>
       </c>
       <c r="I63" s="21" t="n"/>
       <c r="J63" s="21" t="inlineStr">
         <is>
-          <t>Single Family</t>
-        </is>
-      </c>
-      <c r="K63" s="22" t="inlineStr">
-        <is>
-          <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
-        </is>
-      </c>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K63" s="22" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="21" t="n">
@@ -2945,15 +2973,15 @@
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>Cerro Vista</t>
+          <t>Pointe Grand Estrella at Phoenix</t>
         </is>
       </c>
       <c r="D64" s="23" t="n">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F64" s="24" t="n"/>
@@ -2964,16 +2992,20 @@
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t>Virtua Partners</t>
+          <t>Hillpointe, LLC</t>
         </is>
       </c>
       <c r="I64" s="21" t="n"/>
       <c r="J64" s="21" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
-      <c r="K64" s="22" t="n"/>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K64" s="22" t="inlineStr">
+        <is>
+          <t>Year built: 2026/2027</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="21" t="n">
@@ -2989,7 +3021,7 @@
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F65" s="24" t="n"/>
@@ -3017,15 +3049,15 @@
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Zen @ Angelina</t>
+          <t>Villages at Northern</t>
         </is>
       </c>
       <c r="D66" s="23" t="n">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F66" s="24" t="n"/>
@@ -3036,20 +3068,16 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t>F &amp; S Consulting &amp; Management, LLC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="21" t="n"/>
       <c r="J66" s="21" t="inlineStr">
         <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K66" s="22" t="inlineStr">
-        <is>
-          <t>Year built: 2027/2028</t>
-        </is>
-      </c>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K66" s="22" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="21" t="n">
@@ -3057,15 +3085,15 @@
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>HARMON Ascend</t>
+          <t>Prosper 47</t>
         </is>
       </c>
       <c r="D67" s="23" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F67" s="24" t="n"/>
@@ -3076,7 +3104,7 @@
       </c>
       <c r="H67" s="22" t="inlineStr">
         <is>
-          <t>Crescent Communities LLC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I67" s="21" t="n"/>
@@ -3085,7 +3113,11 @@
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K67" s="22" t="n"/>
+      <c r="K67" s="22" t="inlineStr">
+        <is>
+          <t>RealPage only (sub-50 unit)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="21" t="n">
@@ -3093,15 +3125,15 @@
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>Villages at Northern</t>
+          <t>HARMON Ascend</t>
         </is>
       </c>
       <c r="D68" s="23" t="n">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="F68" s="24" t="n"/>
@@ -3112,13 +3144,13 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Crescent Communities LLC</t>
         </is>
       </c>
       <c r="I68" s="21" t="n"/>
       <c r="J68" s="21" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K68" s="22" t="n"/>
@@ -3129,15 +3161,15 @@
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Prosper 47</t>
+          <t>FUZE Ballpark</t>
         </is>
       </c>
       <c r="D69" s="23" t="n">
-        <v>47</v>
+        <v>321</v>
       </c>
       <c r="E69" s="21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F69" s="24" t="n"/>
@@ -3148,20 +3180,16 @@
       </c>
       <c r="H69" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Zekelman Industries</t>
         </is>
       </c>
       <c r="I69" s="21" t="n"/>
       <c r="J69" s="21" t="inlineStr">
         <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K69" s="22" t="inlineStr">
-        <is>
-          <t>RealPage only (sub-50 unit)</t>
-        </is>
-      </c>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="26" t="n"/>
@@ -3177,15 +3205,15 @@
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>Sheely Center Future Phase</t>
+          <t>Northern 107</t>
         </is>
       </c>
       <c r="D72" s="30" t="n">
-        <v>697</v>
+        <v>74</v>
       </c>
       <c r="E72" s="28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F72" s="31" t="n"/>
@@ -3196,7 +3224,7 @@
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jacob Reuben</t>
         </is>
       </c>
       <c r="I72" s="28" t="n"/>
@@ -3205,11 +3233,7 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K72" s="29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+      <c r="K72" s="29" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="28" t="n">
@@ -3217,15 +3241,15 @@
       </c>
       <c r="C73" s="29" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel C</t>
+          <t>The Waverly</t>
         </is>
       </c>
       <c r="D73" s="30" t="n">
-        <v>500</v>
+        <v>323</v>
       </c>
       <c r="E73" s="28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F73" s="31" t="n"/>
@@ -3236,20 +3260,16 @@
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>Fisher Industries</t>
+          <t>Dominium</t>
         </is>
       </c>
       <c r="I73" s="28" t="n"/>
       <c r="J73" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K73" s="29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K73" s="29" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="28" t="n">
@@ -3257,15 +3277,15 @@
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel B</t>
+          <t>Encore Avondale</t>
         </is>
       </c>
       <c r="D74" s="30" t="n">
-        <v>478</v>
+        <v>300</v>
       </c>
       <c r="E74" s="28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F74" s="31" t="n"/>
@@ -3276,20 +3296,16 @@
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>Fisher Industries</t>
+          <t>Encore Enterprises</t>
         </is>
       </c>
       <c r="I74" s="28" t="n"/>
       <c r="J74" s="28" t="inlineStr">
         <is>
-          <t>High-Rise</t>
-        </is>
-      </c>
-      <c r="K74" s="29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K74" s="29" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="28" t="n">
@@ -3297,15 +3313,15 @@
       </c>
       <c r="C75" s="29" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel B</t>
+          <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
       <c r="D75" s="30" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="E75" s="28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F75" s="31" t="n"/>
@@ -3316,7 +3332,7 @@
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>Leon Capital Group</t>
         </is>
       </c>
       <c r="I75" s="28" t="n"/>
@@ -3325,11 +3341,7 @@
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K75" s="29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+      <c r="K75" s="29" t="n"/>
     </row>
     <row r="76">
       <c r="B76" s="28" t="n">
@@ -3337,15 +3349,15 @@
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>The District at Westgate</t>
+          <t>Ascent Goodyear</t>
         </is>
       </c>
       <c r="D76" s="30" t="n">
-        <v>384</v>
+        <v>113</v>
       </c>
       <c r="E76" s="28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F76" s="31" t="n"/>
@@ -3356,7 +3368,7 @@
       </c>
       <c r="H76" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>Ascent Companies</t>
         </is>
       </c>
       <c r="I76" s="28" t="n"/>
@@ -3365,11 +3377,7 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K76" s="29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+      <c r="K76" s="29" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="28" t="n">
@@ -3377,11 +3385,11 @@
       </c>
       <c r="C77" s="29" t="inlineStr">
         <is>
-          <t>Picerne at Palm Valley</t>
+          <t>Sheely Center Future Phase</t>
         </is>
       </c>
       <c r="D77" s="30" t="n">
-        <v>383</v>
+        <v>697</v>
       </c>
       <c r="E77" s="28" t="inlineStr">
         <is>
@@ -3396,7 +3404,7 @@
       </c>
       <c r="H77" s="29" t="inlineStr">
         <is>
-          <t>Picerne</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="28" t="n"/>
@@ -3417,11 +3425,11 @@
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>Liv Avondale</t>
+          <t>Urban 95 Parcel C</t>
         </is>
       </c>
       <c r="D78" s="30" t="n">
-        <v>333</v>
+        <v>500</v>
       </c>
       <c r="E78" s="28" t="inlineStr">
         <is>
@@ -3436,7 +3444,7 @@
       </c>
       <c r="H78" s="29" t="inlineStr">
         <is>
-          <t>Liv Communities LLC</t>
+          <t>Fisher Industries</t>
         </is>
       </c>
       <c r="I78" s="28" t="n"/>
@@ -3457,11 +3465,11 @@
       </c>
       <c r="C79" s="29" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel A</t>
+          <t>Urban 95 Parcel B</t>
         </is>
       </c>
       <c r="D79" s="30" t="n">
-        <v>324</v>
+        <v>478</v>
       </c>
       <c r="E79" s="28" t="inlineStr">
         <is>
@@ -3497,11 +3505,11 @@
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>The Waverly</t>
+          <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
       <c r="D80" s="30" t="n">
-        <v>323</v>
+        <v>410</v>
       </c>
       <c r="E80" s="28" t="inlineStr">
         <is>
@@ -3516,7 +3524,7 @@
       </c>
       <c r="H80" s="29" t="inlineStr">
         <is>
-          <t>Dominium</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I80" s="28" t="n"/>
@@ -3525,7 +3533,11 @@
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K80" s="29" t="n"/>
+      <c r="K80" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="28" t="n">
@@ -3533,11 +3545,11 @@
       </c>
       <c r="C81" s="29" t="inlineStr">
         <is>
-          <t>Fuze 623</t>
+          <t>The District at Westgate</t>
         </is>
       </c>
       <c r="D81" s="30" t="n">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="E81" s="28" t="inlineStr">
         <is>
@@ -3552,7 +3564,7 @@
       </c>
       <c r="H81" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I81" s="28" t="n"/>
@@ -3573,11 +3585,11 @@
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>Anton Glendale</t>
+          <t>Picerne at Palm Valley</t>
         </is>
       </c>
       <c r="D82" s="30" t="n">
-        <v>320</v>
+        <v>383</v>
       </c>
       <c r="E82" s="28" t="inlineStr">
         <is>
@@ -3592,13 +3604,13 @@
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Picerne</t>
         </is>
       </c>
       <c r="I82" s="28" t="n"/>
       <c r="J82" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K82" s="29" t="inlineStr">
@@ -3613,11 +3625,11 @@
       </c>
       <c r="C83" s="29" t="inlineStr">
         <is>
-          <t>Western Garden II</t>
+          <t>Liv Avondale</t>
         </is>
       </c>
       <c r="D83" s="30" t="n">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="E83" s="28" t="inlineStr">
         <is>
@@ -3632,13 +3644,13 @@
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>John F Long Properties LLLP</t>
+          <t>Liv Communities LLC</t>
         </is>
       </c>
       <c r="I83" s="28" t="n"/>
       <c r="J83" s="28" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K83" s="29" t="inlineStr">
@@ -3653,11 +3665,11 @@
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>Sanctuair at Centerscape</t>
+          <t>Urban 95 Parcel A</t>
         </is>
       </c>
       <c r="D84" s="30" t="n">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="E84" s="28" t="inlineStr">
         <is>
@@ -3672,13 +3684,13 @@
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>Sunbelt Investment Holdings Inc</t>
+          <t>Fisher Industries</t>
         </is>
       </c>
       <c r="I84" s="28" t="n"/>
       <c r="J84" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>High-Rise</t>
         </is>
       </c>
       <c r="K84" s="29" t="inlineStr">
@@ -3693,11 +3705,11 @@
       </c>
       <c r="C85" s="29" t="inlineStr">
         <is>
-          <t>Encore Avondale</t>
+          <t>Fuze 623</t>
         </is>
       </c>
       <c r="D85" s="30" t="n">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="E85" s="28" t="inlineStr">
         <is>
@@ -3712,16 +3724,20 @@
       </c>
       <c r="H85" s="29" t="inlineStr">
         <is>
-          <t>Encore Enterprises</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I85" s="28" t="n"/>
       <c r="J85" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K85" s="29" t="n"/>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K85" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="28" t="n">
@@ -3729,11 +3745,11 @@
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>Banyan Avondale</t>
+          <t>Anton Glendale</t>
         </is>
       </c>
       <c r="D86" s="30" t="n">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="E86" s="28" t="inlineStr">
         <is>
@@ -3754,7 +3770,7 @@
       <c r="I86" s="28" t="n"/>
       <c r="J86" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K86" s="29" t="inlineStr">
@@ -3769,11 +3785,11 @@
       </c>
       <c r="C87" s="29" t="inlineStr">
         <is>
-          <t>Rosilian Villas</t>
+          <t>Western Garden II</t>
         </is>
       </c>
       <c r="D87" s="30" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="E87" s="28" t="inlineStr">
         <is>
@@ -3788,13 +3804,13 @@
       </c>
       <c r="H87" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>John F Long Properties LLLP</t>
         </is>
       </c>
       <c r="I87" s="28" t="n"/>
       <c r="J87" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K87" s="29" t="inlineStr">
@@ -3809,11 +3825,11 @@
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>The Statler at Estrella Parkway</t>
+          <t>Sanctuair at Centerscape</t>
         </is>
       </c>
       <c r="D88" s="30" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="E88" s="28" t="inlineStr">
         <is>
@@ -3828,16 +3844,20 @@
       </c>
       <c r="H88" s="29" t="inlineStr">
         <is>
-          <t>Leon Capital Group</t>
+          <t>Sunbelt Investment Holdings Inc</t>
         </is>
       </c>
       <c r="I88" s="28" t="n"/>
       <c r="J88" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K88" s="29" t="n"/>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K88" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="28" t="n">
@@ -3845,11 +3865,11 @@
       </c>
       <c r="C89" s="29" t="inlineStr">
         <is>
-          <t>Orion Avondale</t>
+          <t>Banyan Avondale</t>
         </is>
       </c>
       <c r="D89" s="30" t="n">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="E89" s="28" t="inlineStr">
         <is>
@@ -3864,7 +3884,7 @@
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I89" s="28" t="n"/>
@@ -3885,11 +3905,11 @@
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>Tavalo at Avondale</t>
+          <t>Rosilian Villas</t>
         </is>
       </c>
       <c r="D90" s="30" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="E90" s="28" t="inlineStr">
         <is>
@@ -3904,13 +3924,13 @@
       </c>
       <c r="H90" s="29" t="inlineStr">
         <is>
-          <t>GTIS Partners LP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="28" t="n"/>
       <c r="J90" s="28" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K90" s="29" t="inlineStr">
@@ -3925,11 +3945,11 @@
       </c>
       <c r="C91" s="29" t="inlineStr">
         <is>
-          <t>Marbella Ranch East Future Phase</t>
+          <t>Orion Avondale</t>
         </is>
       </c>
       <c r="D91" s="30" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E91" s="28" t="inlineStr">
         <is>
@@ -3944,13 +3964,13 @@
       </c>
       <c r="H91" s="29" t="inlineStr">
         <is>
-          <t>Symmetry Companies</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I91" s="28" t="n"/>
       <c r="J91" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K91" s="29" t="inlineStr">
@@ -3965,11 +3985,11 @@
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>Crystal Cove</t>
+          <t>Tavalo at Avondale</t>
         </is>
       </c>
       <c r="D92" s="30" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E92" s="28" t="inlineStr">
         <is>
@@ -3984,13 +4004,13 @@
       </c>
       <c r="H92" s="29" t="inlineStr">
         <is>
-          <t>Sterling Real Estate Partners</t>
+          <t>GTIS Partners LP</t>
         </is>
       </c>
       <c r="I92" s="28" t="n"/>
       <c r="J92" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K92" s="29" t="inlineStr">
@@ -4005,11 +4025,11 @@
       </c>
       <c r="C93" s="29" t="inlineStr">
         <is>
-          <t>Cornerstone at the Wigwam</t>
+          <t>Marbella Ranch East Future Phase</t>
         </is>
       </c>
       <c r="D93" s="30" t="n">
-        <v>212</v>
+        <v>266</v>
       </c>
       <c r="E93" s="28" t="inlineStr">
         <is>
@@ -4024,13 +4044,13 @@
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Symmetry Companies</t>
         </is>
       </c>
       <c r="I93" s="28" t="n"/>
       <c r="J93" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K93" s="29" t="inlineStr">
@@ -4045,11 +4065,11 @@
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>Radia Avondale Station III</t>
+          <t>Crystal Cove</t>
         </is>
       </c>
       <c r="D94" s="30" t="n">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="E94" s="28" t="inlineStr">
         <is>
@@ -4064,13 +4084,13 @@
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sterling Real Estate Partners</t>
         </is>
       </c>
       <c r="I94" s="28" t="n"/>
       <c r="J94" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K94" s="29" t="inlineStr">
@@ -4085,11 +4105,11 @@
       </c>
       <c r="C95" s="29" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel A</t>
+          <t>Cornerstone at the Wigwam</t>
         </is>
       </c>
       <c r="D95" s="30" t="n">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="E95" s="28" t="inlineStr">
         <is>
@@ -4104,7 +4124,7 @@
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I95" s="28" t="n"/>
@@ -4125,11 +4145,11 @@
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>Villages at River Grove</t>
+          <t>Radia Avondale Station III</t>
         </is>
       </c>
       <c r="D96" s="30" t="n">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="E96" s="28" t="inlineStr">
         <is>
@@ -4150,7 +4170,7 @@
       <c r="I96" s="28" t="n"/>
       <c r="J96" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K96" s="29" t="inlineStr">
@@ -4165,11 +4185,11 @@
       </c>
       <c r="C97" s="29" t="inlineStr">
         <is>
-          <t>District 99</t>
+          <t>Celebration Plaza Parcel A</t>
         </is>
       </c>
       <c r="D97" s="30" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E97" s="28" t="inlineStr">
         <is>
@@ -4184,13 +4204,13 @@
       </c>
       <c r="H97" s="29" t="inlineStr">
         <is>
-          <t>Thompson Thrift</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I97" s="28" t="n"/>
       <c r="J97" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K97" s="29" t="inlineStr">
@@ -4205,11 +4225,11 @@
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>McDowell Villas</t>
+          <t>Villages at River Grove</t>
         </is>
       </c>
       <c r="D98" s="30" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E98" s="28" t="inlineStr">
         <is>
@@ -4224,13 +4244,13 @@
       </c>
       <c r="H98" s="29" t="inlineStr">
         <is>
-          <t>Trilogy Investment Company</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I98" s="28" t="n"/>
       <c r="J98" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K98" s="29" t="inlineStr">
@@ -4245,11 +4265,11 @@
       </c>
       <c r="C99" s="29" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>District 99</t>
         </is>
       </c>
       <c r="D99" s="30" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="E99" s="28" t="inlineStr">
         <is>
@@ -4264,13 +4284,13 @@
       </c>
       <c r="H99" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Thompson Thrift</t>
         </is>
       </c>
       <c r="I99" s="28" t="n"/>
       <c r="J99" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K99" s="29" t="inlineStr">
@@ -4285,11 +4305,11 @@
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>Porter Kyle Development</t>
+          <t>McDowell Villas</t>
         </is>
       </c>
       <c r="D100" s="30" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="E100" s="28" t="inlineStr">
         <is>
@@ -4304,7 +4324,7 @@
       </c>
       <c r="H100" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trilogy Investment Company</t>
         </is>
       </c>
       <c r="I100" s="28" t="n"/>
@@ -4325,11 +4345,11 @@
       </c>
       <c r="C101" s="29" t="inlineStr">
         <is>
-          <t>Ascent Goodyear</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="D101" s="30" t="n">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="E101" s="28" t="inlineStr">
         <is>
@@ -4344,7 +4364,7 @@
       </c>
       <c r="H101" s="29" t="inlineStr">
         <is>
-          <t>Ascent Companies</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I101" s="28" t="n"/>
@@ -4353,7 +4373,11 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K101" s="29" t="n"/>
+      <c r="K101" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="28" t="n">
@@ -4361,11 +4385,11 @@
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>Northern 107</t>
+          <t>Porter Kyle Development</t>
         </is>
       </c>
       <c r="D102" s="30" t="n">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="E102" s="28" t="inlineStr">
         <is>
@@ -4380,16 +4404,20 @@
       </c>
       <c r="H102" s="29" t="inlineStr">
         <is>
-          <t>Jacob Reuben</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I102" s="28" t="n"/>
       <c r="J102" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K102" s="29" t="n"/>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K102" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="28" t="n">
@@ -7504,19 +7532,24 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FUZE Ballpark</t>
+          <t>Zen @ Angelina</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6255 N Ball Park Blvd</t>
+          <t>956 Castillo Dr S</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="D52" t="n">
-        <v>2026</v>
+        <v>2027</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7532,24 +7565,33 @@
           <t>CoStar+RealPage</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Year built: 2027/2028</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Zen @ Angelina</t>
+          <t>Zanjero III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>956 Castillo Dr S</t>
+          <t>7151 N Zanjero Blvd</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>130</v>
+        <v>301</v>
       </c>
       <c r="D53" t="n">
-        <v>2027</v>
+        <v>2028</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7562,14 +7604,10 @@
       <c r="J53" s="38" t="n"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Year built: 2027/2028</t>
-        </is>
-      </c>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7587,6 +7625,11 @@
       </c>
       <c r="D54" t="n">
         <v>2026</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7613,20 +7656,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HARMON Ascend</t>
+          <t>Cerro Vista</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12805 W Indian School Rd</t>
+          <t>12116 W Van Buren St</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>125</v>
+        <v>255</v>
       </c>
       <c r="D55" t="n">
         <v>2026</v>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION</t>
@@ -7634,13 +7682,11 @@
       </c>
       <c r="G55" s="37" t="n"/>
       <c r="H55" s="37" t="n"/>
-      <c r="I55" s="38" t="n">
-        <v>2788</v>
-      </c>
+      <c r="I55" s="38" t="n"/>
       <c r="J55" s="38" t="n"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -7648,20 +7694,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cerro Vista</t>
+          <t>Pointe Grand Estrella at Phoenix</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12116 W Van Buren St</t>
+          <t>10649 W Buckeye Rd</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="D56" t="n">
         <v>2026</v>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION</t>
@@ -7669,31 +7720,42 @@
       </c>
       <c r="G56" s="37" t="n"/>
       <c r="H56" s="37" t="n"/>
-      <c r="I56" s="38" t="n"/>
+      <c r="I56" s="38" t="n">
+        <v>1650</v>
+      </c>
       <c r="J56" s="38" t="n"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>CoStar</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Year built: 2026/2027</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pointe Grand Estrella at Phoenix</t>
+          <t>Marbella Ranch East I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10649 W Buckeye Rd</t>
+          <t>7725 El Mirage Rd</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="D57" t="n">
-        <v>2026</v>
+        <v>2027</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7702,37 +7764,36 @@
       </c>
       <c r="G57" s="37" t="n"/>
       <c r="H57" s="37" t="n"/>
-      <c r="I57" s="38" t="n">
-        <v>1650</v>
-      </c>
+      <c r="I57" s="38" t="n"/>
       <c r="J57" s="38" t="n"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Year built: 2026/2027</t>
-        </is>
-      </c>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Marbella Ranch East I</t>
+          <t>Villages at Northern</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7725 El Mirage Rd</t>
+          <t>7910 N 107th Ave</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="D58" t="n">
         <v>2027</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7753,19 +7814,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Villages at Northern</t>
+          <t>Prosper 47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7910 N 107th Ave</t>
+          <t>13426 W Van Buren St</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D59" t="n">
         <v>2027</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7781,24 +7847,33 @@
           <t>RealPage</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>RealPage only (sub-50 unit)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Prosper 47</t>
+          <t>HARMON Ascend</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13426 W Van Buren St</t>
+          <t>12805 W Indian School Rd</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="D60" t="n">
-        <v>2027</v>
+        <v>2026</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7807,35 +7882,38 @@
       </c>
       <c r="G60" s="37" t="n"/>
       <c r="H60" s="37" t="n"/>
-      <c r="I60" s="38" t="n"/>
+      <c r="I60" s="38" t="n">
+        <v>2788</v>
+      </c>
       <c r="J60" s="38" t="n"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>RealPage only (sub-50 unit)</t>
-        </is>
-      </c>
+          <t>CoStar+RealPage</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zanjero III</t>
+          <t>FUZE Ballpark</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7151 N Zanjero Blvd</t>
+          <t>6255 N Ball Park Blvd</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="D61" t="n">
-        <v>2028</v>
+        <v>2026</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7848,7 +7926,7 @@
       <c r="J61" s="38" t="n"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>RealPage</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7866,6 +7944,11 @@
       </c>
       <c r="C62" t="n">
         <v>74</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7900,6 +7983,11 @@
       <c r="D63" t="n">
         <v>2028</v>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7930,6 +8018,11 @@
       <c r="C64" t="n">
         <v>284</v>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7963,6 +8056,11 @@
       <c r="D65" t="n">
         <v>2027</v>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>PROPOSED</t>
@@ -7995,6 +8093,11 @@
       </c>
       <c r="D66" t="n">
         <v>2027</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9313,2167 +9416,2349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M98"/>
+  <dimension ref="B2:W58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SUPPLY &amp; ABSORPTION FORECAST — 5-MILE MARKET</t>
+          <t>SUPPLY &amp; ABSORPTION  —  5-MILE MARKET (relative-year / TTM)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="39" t="inlineStr">
+      <c r="R3" s="39" t="inlineStr">
+        <is>
+          <t>PIPELINE INPUTS (forward new supply)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>As-of Quarter</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8105</v>
+      </c>
+      <c r="R4" s="42" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S4" s="42" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T4" s="42" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U4" s="42" t="inlineStr">
+        <is>
+          <t>Incl?</t>
+        </is>
+      </c>
+      <c r="V4" s="42" t="inlineStr">
+        <is>
+          <t>DelivIdx</t>
+        </is>
+      </c>
+      <c r="W4" s="42" t="inlineStr">
+        <is>
+          <t>HoldYr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Close Quarter (Y1 start)</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="E5">
+        <f>IFERROR(VALUE(RIGHT($C$5,4))*4+MATCH(LEFT($C$5,2),{"Q1","Q2","Q3","Q4"},0)-1,0)</f>
+        <v/>
+      </c>
+      <c r="R5" s="44" t="inlineStr">
+        <is>
+          <t>Sheely Center Future Phase</t>
+        </is>
+      </c>
+      <c r="S5" s="45" t="n">
+        <v>697</v>
+      </c>
+      <c r="T5" s="46" t="inlineStr"/>
+      <c r="U5" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V5" s="47">
+        <f>IFERROR(VALUE(RIGHT(T5,4))*4+MATCH(LEFT(T5,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W5" s="47">
+        <f>IF(V5="","",IF(V5&lt;=$E$4,0,MAX(1,INT((V5-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Stabilization Target</t>
         </is>
       </c>
-      <c r="C3" s="40">
+      <c r="C6" s="48">
         <f>Settings!$B$2</f>
         <v/>
       </c>
-      <c r="J3" s="36" t="inlineStr">
-        <is>
-          <t>PIPELINE INPUTS  (forward new supply — edit date / include)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="41" t="inlineStr">
-        <is>
-          <t>Demand Scenario (Bear/Base/Bull)</t>
-        </is>
-      </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="R6" s="44" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel C</t>
+        </is>
+      </c>
+      <c r="S6" s="45" t="n">
+        <v>500</v>
+      </c>
+      <c r="T6" s="46" t="inlineStr"/>
+      <c r="U6" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V6" s="47">
+        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W6" s="47">
+        <f>IF(V6="","",IF(V6&lt;=$E$4,0,MAX(1,INT((V6-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>Demand Scenario</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J4" s="43" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="K4" s="43" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="L4" s="43" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="M4" s="43" t="inlineStr">
-        <is>
-          <t>Include?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>Hist. Avg Annual Absorption (CoStar)</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="n">
+      <c r="R7" s="44" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel B</t>
+        </is>
+      </c>
+      <c r="S7" s="45" t="n">
+        <v>478</v>
+      </c>
+      <c r="T7" s="46" t="inlineStr"/>
+      <c r="U7" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V7" s="47">
+        <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W7" s="47">
+        <f>IF(V7="","",IF(V7&lt;=$E$4,0,MAX(1,INT((V7-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t>Bear Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R8" s="44" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel B</t>
+        </is>
+      </c>
+      <c r="S8" s="45" t="n">
+        <v>410</v>
+      </c>
+      <c r="T8" s="46" t="inlineStr"/>
+      <c r="U8" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V8" s="47">
+        <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W8" s="47">
+        <f>IF(V8="","",IF(V8&lt;=$E$4,0,MAX(1,INT((V8-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>Base Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="n">
         <v>2525</v>
       </c>
-      <c r="J5" s="45" t="inlineStr">
-        <is>
-          <t>Sheely Center Future Phase</t>
-        </is>
-      </c>
-      <c r="K5" s="46" t="n">
-        <v>697</v>
-      </c>
-      <c r="L5" s="47" t="inlineStr"/>
-      <c r="M5" s="47" t="inlineStr">
+      <c r="R9" s="44" t="inlineStr">
+        <is>
+          <t>The District at Westgate</t>
+        </is>
+      </c>
+      <c r="S9" s="45" t="n">
+        <v>384</v>
+      </c>
+      <c r="T9" s="46" t="inlineStr"/>
+      <c r="U9" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>Bear — Annual Absorption (units)</t>
-        </is>
-      </c>
-      <c r="C6" s="44" t="n">
-        <v>1250</v>
-      </c>
-      <c r="J6" s="45" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel C</t>
-        </is>
-      </c>
-      <c r="K6" s="46" t="n">
-        <v>500</v>
-      </c>
-      <c r="L6" s="47" t="inlineStr"/>
-      <c r="M6" s="47" t="inlineStr">
+      <c r="V9" s="47">
+        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W9" s="47">
+        <f>IF(V9="","",IF(V9&lt;=$E$4,0,MAX(1,INT((V9-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>Bull Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="n">
+        <v>3800</v>
+      </c>
+      <c r="R10" s="44" t="inlineStr">
+        <is>
+          <t>Picerne at Palm Valley</t>
+        </is>
+      </c>
+      <c r="S10" s="45" t="n">
+        <v>383</v>
+      </c>
+      <c r="T10" s="46" t="inlineStr"/>
+      <c r="U10" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>Base — Annual Absorption (units)</t>
-        </is>
-      </c>
-      <c r="C7" s="44" t="n">
-        <v>2525</v>
-      </c>
-      <c r="J7" s="45" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel B</t>
-        </is>
-      </c>
-      <c r="K7" s="46" t="n">
-        <v>478</v>
-      </c>
-      <c r="L7" s="47" t="inlineStr"/>
-      <c r="M7" s="47" t="inlineStr">
+      <c r="V10" s="47">
+        <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W10" s="47">
+        <f>IF(V10="","",IF(V10&lt;=$E$4,0,MAX(1,INT((V10-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>Selected Annual Demand</t>
+        </is>
+      </c>
+      <c r="C11" s="50">
+        <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
+        <v/>
+      </c>
+      <c r="R11" s="44" t="inlineStr">
+        <is>
+          <t>Liv Avondale</t>
+        </is>
+      </c>
+      <c r="S11" s="45" t="n">
+        <v>333</v>
+      </c>
+      <c r="T11" s="46" t="inlineStr"/>
+      <c r="U11" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>Bull — Annual Absorption (units)</t>
-        </is>
-      </c>
-      <c r="C8" s="44" t="n">
-        <v>3800</v>
-      </c>
-      <c r="J8" s="45" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel B</t>
-        </is>
-      </c>
-      <c r="K8" s="46" t="n">
-        <v>410</v>
-      </c>
-      <c r="L8" s="47" t="inlineStr"/>
-      <c r="M8" s="47" t="inlineStr">
+      <c r="V11" s="47">
+        <f>IFERROR(VALUE(RIGHT(T11,4))*4+MATCH(LEFT(T11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W11" s="47">
+        <f>IF(V11="","",IF(V11&lt;=$E$4,0,MAX(1,INT((V11-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>Occupied (as-of)</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="n">
+        <v>22585</v>
+      </c>
+      <c r="R12" s="44" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel A</t>
+        </is>
+      </c>
+      <c r="S12" s="45" t="n">
+        <v>324</v>
+      </c>
+      <c r="T12" s="46" t="inlineStr"/>
+      <c r="U12" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>Selected Annual Demand</t>
-        </is>
-      </c>
-      <c r="C9" s="44">
-        <f>IF($C$4="Bear",$C$6,IF($C$4="Bull",$C$8,$C$7))</f>
-        <v/>
-      </c>
-      <c r="J9" s="45" t="inlineStr">
-        <is>
-          <t>The District at Westgate</t>
-        </is>
-      </c>
-      <c r="K9" s="46" t="n">
-        <v>384</v>
-      </c>
-      <c r="L9" s="47" t="inlineStr"/>
-      <c r="M9" s="47" t="inlineStr">
+      <c r="V12" s="47">
+        <f>IFERROR(VALUE(RIGHT(T12,4))*4+MATCH(LEFT(T12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W12" s="47">
+        <f>IF(V12="","",IF(V12&lt;=$E$4,0,MAX(1,INT((V12-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t>Inventory (as-of)</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>26603</v>
+      </c>
+      <c r="R13" s="44" t="inlineStr">
+        <is>
+          <t>The Waverly</t>
+        </is>
+      </c>
+      <c r="S13" s="45" t="n">
+        <v>323</v>
+      </c>
+      <c r="T13" s="46" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U13" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="39" t="inlineStr">
-        <is>
-          <t>Selected Quarterly Demand</t>
-        </is>
-      </c>
-      <c r="C10" s="44">
-        <f>$C$9/4</f>
-        <v/>
-      </c>
-      <c r="J10" s="45" t="inlineStr">
-        <is>
-          <t>Picerne at Palm Valley</t>
-        </is>
-      </c>
-      <c r="K10" s="46" t="n">
-        <v>383</v>
-      </c>
-      <c r="L10" s="47" t="inlineStr"/>
-      <c r="M10" s="47" t="inlineStr">
+      <c r="V13" s="47">
+        <f>IFERROR(VALUE(RIGHT(T13,4))*4+MATCH(LEFT(T13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W13" s="47">
+        <f>IF(V13="","",IF(V13&lt;=$E$4,0,MAX(1,INT((V13-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="R14" s="44" t="inlineStr">
+        <is>
+          <t>Fuze 623</t>
+        </is>
+      </c>
+      <c r="S14" s="45" t="n">
+        <v>321</v>
+      </c>
+      <c r="T14" s="46" t="inlineStr"/>
+      <c r="U14" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="J11" s="45" t="inlineStr">
-        <is>
-          <t>Liv Avondale</t>
-        </is>
-      </c>
-      <c r="K11" s="46" t="n">
-        <v>333</v>
-      </c>
-      <c r="L11" s="47" t="inlineStr"/>
-      <c r="M11" s="47" t="inlineStr">
+      <c r="V14" s="47">
+        <f>IFERROR(VALUE(RIGHT(T14,4))*4+MATCH(LEFT(T14,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W14" s="47">
+        <f>IF(V14="","",IF(V14&lt;=$E$4,0,MAX(1,INT((V14-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="R15" s="44" t="inlineStr">
+        <is>
+          <t>Anton Glendale</t>
+        </is>
+      </c>
+      <c r="S15" s="45" t="n">
+        <v>320</v>
+      </c>
+      <c r="T15" s="46" t="inlineStr"/>
+      <c r="U15" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="J12" s="45" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel A</t>
-        </is>
-      </c>
-      <c r="K12" s="46" t="n">
-        <v>324</v>
-      </c>
-      <c r="L12" s="47" t="inlineStr"/>
-      <c r="M12" s="47" t="inlineStr">
+      <c r="V15" s="47">
+        <f>IFERROR(VALUE(RIGHT(T15,4))*4+MATCH(LEFT(T15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W15" s="47">
+        <f>IF(V15="","",IF(V15&lt;=$E$4,0,MAX(1,INT((V15-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="R16" s="44" t="inlineStr">
+        <is>
+          <t>Western Garden II</t>
+        </is>
+      </c>
+      <c r="S16" s="45" t="n">
+        <v>314</v>
+      </c>
+      <c r="T16" s="46" t="inlineStr"/>
+      <c r="U16" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="J13" s="45" t="inlineStr">
-        <is>
-          <t>The Waverly</t>
-        </is>
-      </c>
-      <c r="K13" s="46" t="n">
-        <v>323</v>
-      </c>
-      <c r="L13" s="47" t="inlineStr"/>
-      <c r="M13" s="47" t="inlineStr">
+      <c r="V16" s="47">
+        <f>IFERROR(VALUE(RIGHT(T16,4))*4+MATCH(LEFT(T16,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W16" s="47">
+        <f>IF(V16="","",IF(V16&lt;=$E$4,0,MAX(1,INT((V16-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t>5-MILE MARKET</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>-Y6</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>-Y5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-Y4</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-Y3</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>-Y2</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>-Y1</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Y0</t>
+        </is>
+      </c>
+      <c r="J17" s="51" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K17" s="51" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L17" s="51" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N17" s="51" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O17" s="51" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="R17" s="44" t="inlineStr">
+        <is>
+          <t>Sanctuair at Centerscape</t>
+        </is>
+      </c>
+      <c r="S17" s="45" t="n">
+        <v>303</v>
+      </c>
+      <c r="T17" s="46" t="inlineStr"/>
+      <c r="U17" s="46" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="J14" s="45" t="inlineStr">
-        <is>
-          <t>Fuze 623</t>
-        </is>
-      </c>
-      <c r="K14" s="46" t="n">
+      <c r="V17" s="47">
+        <f>IFERROR(VALUE(RIGHT(T17,4))*4+MATCH(LEFT(T17,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W17" s="47">
+        <f>IF(V17="","",IF(V17&lt;=$E$4,0,MAX(1,INT((V17-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2019–Q2 2020</t>
+        </is>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2020–Q2 2021</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2021–Q2 2022</t>
+        </is>
+      </c>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2022–Q2 2023</t>
+        </is>
+      </c>
+      <c r="G18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2023–Q2 2024</t>
+        </is>
+      </c>
+      <c r="H18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2024–Q2 2025</t>
+        </is>
+      </c>
+      <c r="I18" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2025–Q2 2026</t>
+        </is>
+      </c>
+      <c r="J18" s="52" t="inlineStr">
+        <is>
+          <t>Hold Yr 1</t>
+        </is>
+      </c>
+      <c r="K18" s="52" t="inlineStr">
+        <is>
+          <t>Hold Yr 2</t>
+        </is>
+      </c>
+      <c r="L18" s="52" t="inlineStr">
+        <is>
+          <t>Hold Yr 3</t>
+        </is>
+      </c>
+      <c r="M18" s="52" t="inlineStr">
+        <is>
+          <t>Hold Yr 4</t>
+        </is>
+      </c>
+      <c r="N18" s="52" t="inlineStr">
+        <is>
+          <t>Hold Yr 5</t>
+        </is>
+      </c>
+      <c r="O18" s="52" t="inlineStr">
+        <is>
+          <t>Hold Yr 6</t>
+        </is>
+      </c>
+      <c r="R18" s="44" t="inlineStr">
+        <is>
+          <t>Encore Avondale</t>
+        </is>
+      </c>
+      <c r="S18" s="45" t="n">
+        <v>300</v>
+      </c>
+      <c r="T18" s="46" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U18" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V18" s="47">
+        <f>IFERROR(VALUE(RIGHT(T18,4))*4+MATCH(LEFT(T18,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W18" s="47">
+        <f>IF(V18="","",IF(V18&lt;=$E$4,0,MAX(1,INT((V18-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>NEW SUPPLY (5-mi)</t>
+        </is>
+      </c>
+      <c r="C19" s="53" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D19" s="53" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E19" s="53" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F19" s="53" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G19" s="53" t="n">
+        <v>2823</v>
+      </c>
+      <c r="H19" s="53" t="n">
+        <v>4043</v>
+      </c>
+      <c r="I19" s="53" t="n">
+        <v>1860</v>
+      </c>
+      <c r="J19" s="54">
+        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,1,$U$5:$U$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="K19" s="54">
+        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,2,$U$5:$U$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="L19" s="54">
+        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,3,$U$5:$U$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="M19" s="54">
+        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,4,$U$5:$U$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="N19" s="54">
+        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,5,$U$5:$U$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="O19" s="54">
+        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,6,$U$5:$U$58,"Y")</f>
+        <v/>
+      </c>
+      <c r="R19" s="44" t="inlineStr">
+        <is>
+          <t>Banyan Avondale</t>
+        </is>
+      </c>
+      <c r="S19" s="45" t="n">
+        <v>296</v>
+      </c>
+      <c r="T19" s="46" t="inlineStr"/>
+      <c r="U19" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V19" s="47">
+        <f>IFERROR(VALUE(RIGHT(T19,4))*4+MATCH(LEFT(T19,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W19" s="47">
+        <f>IF(V19="","",IF(V19&lt;=$E$4,0,MAX(1,INT((V19-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>ABSORPTION (5-mi)</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="n">
+        <v>719</v>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>1876</v>
+      </c>
+      <c r="E20" s="53" t="n">
+        <v>1210</v>
+      </c>
+      <c r="F20" s="53" t="n">
+        <v>685</v>
+      </c>
+      <c r="G20" s="53" t="n">
+        <v>2514</v>
+      </c>
+      <c r="H20" s="53" t="n">
+        <v>2655</v>
+      </c>
+      <c r="I20" s="53" t="n">
+        <v>2369</v>
+      </c>
+      <c r="J20" s="54">
+        <f>J25-I25</f>
+        <v/>
+      </c>
+      <c r="K20" s="54">
+        <f>K25-J25</f>
+        <v/>
+      </c>
+      <c r="L20" s="54">
+        <f>L25-K25</f>
+        <v/>
+      </c>
+      <c r="M20" s="54">
+        <f>M25-L25</f>
+        <v/>
+      </c>
+      <c r="N20" s="54">
+        <f>N25-M25</f>
+        <v/>
+      </c>
+      <c r="O20" s="54">
+        <f>O25-N25</f>
+        <v/>
+      </c>
+      <c r="R20" s="44" t="inlineStr">
+        <is>
+          <t>Rosilian Villas</t>
+        </is>
+      </c>
+      <c r="S20" s="45" t="n">
+        <v>291</v>
+      </c>
+      <c r="T20" s="46" t="inlineStr"/>
+      <c r="U20" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V20" s="47">
+        <f>IFERROR(VALUE(RIGHT(T20,4))*4+MATCH(LEFT(T20,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W20" s="47">
+        <f>IF(V20="","",IF(V20&lt;=$E$4,0,MAX(1,INT((V20-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>OCCUPANCY (5-mi)</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="E21" s="55" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="F21" s="55" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="G21" s="55" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="H21" s="55" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="I21" s="55" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="J21" s="56">
+        <f>IFERROR(J25/J24,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="56">
+        <f>IFERROR(K25/K24,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="56">
+        <f>IFERROR(L25/L24,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="56">
+        <f>IFERROR(M25/M24,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="56">
+        <f>IFERROR(N25/N24,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="56">
+        <f>IFERROR(O25/O24,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="44" t="inlineStr">
+        <is>
+          <t>The Statler at Estrella Parkway</t>
+        </is>
+      </c>
+      <c r="S21" s="45" t="n">
+        <v>284</v>
+      </c>
+      <c r="T21" s="46" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U21" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V21" s="47">
+        <f>IFERROR(VALUE(RIGHT(T21,4))*4+MATCH(LEFT(T21,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W21" s="47">
+        <f>IF(V21="","",IF(V21&lt;=$E$4,0,MAX(1,INT((V21-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t>CUM. UNABSORBED (since -Y3)</t>
+        </is>
+      </c>
+      <c r="C22" s="57" t="n"/>
+      <c r="D22" s="57" t="n"/>
+      <c r="E22" s="57" t="n"/>
+      <c r="F22" s="57">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="57">
+        <f>F22+G19-G20</f>
+        <v/>
+      </c>
+      <c r="H22" s="57">
+        <f>G22+H19-H20</f>
+        <v/>
+      </c>
+      <c r="I22" s="57">
+        <f>H22+I19-I20</f>
+        <v/>
+      </c>
+      <c r="J22" s="57">
+        <f>I22+J19-J20</f>
+        <v/>
+      </c>
+      <c r="K22" s="57">
+        <f>J22+K19-K20</f>
+        <v/>
+      </c>
+      <c r="L22" s="57">
+        <f>K22+L19-L20</f>
+        <v/>
+      </c>
+      <c r="M22" s="57">
+        <f>L22+M19-M20</f>
+        <v/>
+      </c>
+      <c r="N22" s="57">
+        <f>M22+N19-N20</f>
+        <v/>
+      </c>
+      <c r="O22" s="57">
+        <f>N22+O19-O20</f>
+        <v/>
+      </c>
+      <c r="R22" s="44" t="inlineStr">
+        <is>
+          <t>Orion Avondale</t>
+        </is>
+      </c>
+      <c r="S22" s="45" t="n">
+        <v>268</v>
+      </c>
+      <c r="T22" s="46" t="inlineStr"/>
+      <c r="U22" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V22" s="47">
+        <f>IFERROR(VALUE(RIGHT(T22,4))*4+MATCH(LEFT(T22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W22" s="47">
+        <f>IF(V22="","",IF(V22&lt;=$E$4,0,MAX(1,INT((V22-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="R23" s="44" t="inlineStr">
+        <is>
+          <t>Tavalo at Avondale</t>
+        </is>
+      </c>
+      <c r="S23" s="45" t="n">
+        <v>266</v>
+      </c>
+      <c r="T23" s="46" t="inlineStr"/>
+      <c r="U23" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V23" s="47">
+        <f>IFERROR(VALUE(RIGHT(T23,4))*4+MATCH(LEFT(T23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W23" s="47">
+        <f>IF(V23="","",IF(V23&lt;=$E$4,0,MAX(1,INT((V23-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" hidden="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  inventory</t>
+        </is>
+      </c>
+      <c r="C24" s="57" t="n">
+        <v>12401</v>
+      </c>
+      <c r="D24" s="57" t="n">
+        <v>14261</v>
+      </c>
+      <c r="E24" s="57" t="n">
+        <v>15597</v>
+      </c>
+      <c r="F24" s="57" t="n">
+        <v>17877</v>
+      </c>
+      <c r="G24" s="57" t="n">
+        <v>20700</v>
+      </c>
+      <c r="H24" s="57" t="n">
+        <v>24743</v>
+      </c>
+      <c r="I24" s="57" t="n">
+        <v>26603</v>
+      </c>
+      <c r="J24" s="57">
+        <f>I24+J19</f>
+        <v/>
+      </c>
+      <c r="K24" s="57">
+        <f>J24+K19</f>
+        <v/>
+      </c>
+      <c r="L24" s="57">
+        <f>K24+L19</f>
+        <v/>
+      </c>
+      <c r="M24" s="57">
+        <f>L24+M19</f>
+        <v/>
+      </c>
+      <c r="N24" s="57">
+        <f>M24+N19</f>
+        <v/>
+      </c>
+      <c r="O24" s="57">
+        <f>N24+O19</f>
+        <v/>
+      </c>
+      <c r="R24" s="44" t="inlineStr">
+        <is>
+          <t>Marbella Ranch East Future Phase</t>
+        </is>
+      </c>
+      <c r="S24" s="45" t="n">
+        <v>266</v>
+      </c>
+      <c r="T24" s="46" t="inlineStr"/>
+      <c r="U24" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V24" s="47">
+        <f>IFERROR(VALUE(RIGHT(T24,4))*4+MATCH(LEFT(T24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W24" s="47">
+        <f>IF(V24="","",IF(V24&lt;=$E$4,0,MAX(1,INT((V24-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" hidden="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  occupied</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="n">
+        <v>11277</v>
+      </c>
+      <c r="D25" s="57" t="n">
+        <v>13152</v>
+      </c>
+      <c r="E25" s="57" t="n">
+        <v>14362</v>
+      </c>
+      <c r="F25" s="57" t="n">
+        <v>15047</v>
+      </c>
+      <c r="G25" s="57" t="n">
+        <v>17560</v>
+      </c>
+      <c r="H25" s="57" t="n">
+        <v>20215</v>
+      </c>
+      <c r="I25" s="57" t="n">
+        <v>22585</v>
+      </c>
+      <c r="J25" s="57">
+        <f>MIN($C$6*J24,I25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="K25" s="57">
+        <f>MIN($C$6*K24,J25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="L25" s="57">
+        <f>MIN($C$6*L24,K25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="M25" s="57">
+        <f>MIN($C$6*M24,L25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="N25" s="57">
+        <f>MIN($C$6*N24,M25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="O25" s="57">
+        <f>MIN($C$6*O24,N25+$C$11)</f>
+        <v/>
+      </c>
+      <c r="R25" s="44" t="inlineStr">
+        <is>
+          <t>Crystal Cove</t>
+        </is>
+      </c>
+      <c r="S25" s="45" t="n">
+        <v>260</v>
+      </c>
+      <c r="T25" s="46" t="inlineStr"/>
+      <c r="U25" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V25" s="47">
+        <f>IFERROR(VALUE(RIGHT(T25,4))*4+MATCH(LEFT(T25,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W25" s="47">
+        <f>IF(V25="","",IF(V25&lt;=$E$4,0,MAX(1,INT((V25-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="R26" s="44" t="inlineStr">
+        <is>
+          <t>Cornerstone at the Wigwam</t>
+        </is>
+      </c>
+      <c r="S26" s="45" t="n">
+        <v>212</v>
+      </c>
+      <c r="T26" s="46" t="inlineStr"/>
+      <c r="U26" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V26" s="47">
+        <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W26" s="47">
+        <f>IF(V26="","",IF(V26&lt;=$E$4,0,MAX(1,INT((V26-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
+        </is>
+      </c>
+      <c r="J27" s="58" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K27" s="58" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L27" s="58" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M27" s="58" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N27" s="58" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O27" s="58" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="R27" s="44" t="inlineStr">
+        <is>
+          <t>Radia Avondale Station III</t>
+        </is>
+      </c>
+      <c r="S27" s="45" t="n">
+        <v>212</v>
+      </c>
+      <c r="T27" s="46" t="inlineStr"/>
+      <c r="U27" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V27" s="47">
+        <f>IFERROR(VALUE(RIGHT(T27,4))*4+MATCH(LEFT(T27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W27" s="47">
+        <f>IF(V27="","",IF(V27&lt;=$E$4,0,MAX(1,INT((V27-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J28" s="59">
+        <f>MIN($C$6,($C$12+$C$8*1)/J24)</f>
+        <v/>
+      </c>
+      <c r="K28" s="59">
+        <f>MIN($C$6,($C$12+$C$8*2)/K24)</f>
+        <v/>
+      </c>
+      <c r="L28" s="59">
+        <f>MIN($C$6,($C$12+$C$8*3)/L24)</f>
+        <v/>
+      </c>
+      <c r="M28" s="59">
+        <f>MIN($C$6,($C$12+$C$8*4)/M24)</f>
+        <v/>
+      </c>
+      <c r="N28" s="59">
+        <f>MIN($C$6,($C$12+$C$8*5)/N24)</f>
+        <v/>
+      </c>
+      <c r="O28" s="59">
+        <f>MIN($C$6,($C$12+$C$8*6)/O24)</f>
+        <v/>
+      </c>
+      <c r="R28" s="44" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel A</t>
+        </is>
+      </c>
+      <c r="S28" s="45" t="n">
+        <v>181</v>
+      </c>
+      <c r="T28" s="46" t="inlineStr"/>
+      <c r="U28" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V28" s="47">
+        <f>IFERROR(VALUE(RIGHT(T28,4))*4+MATCH(LEFT(T28,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W28" s="47">
+        <f>IF(V28="","",IF(V28&lt;=$E$4,0,MAX(1,INT((V28-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J29" s="59">
+        <f>MIN($C$6,($C$12+$C$9*1)/J24)</f>
+        <v/>
+      </c>
+      <c r="K29" s="59">
+        <f>MIN($C$6,($C$12+$C$9*2)/K24)</f>
+        <v/>
+      </c>
+      <c r="L29" s="59">
+        <f>MIN($C$6,($C$12+$C$9*3)/L24)</f>
+        <v/>
+      </c>
+      <c r="M29" s="59">
+        <f>MIN($C$6,($C$12+$C$9*4)/M24)</f>
+        <v/>
+      </c>
+      <c r="N29" s="59">
+        <f>MIN($C$6,($C$12+$C$9*5)/N24)</f>
+        <v/>
+      </c>
+      <c r="O29" s="59">
+        <f>MIN($C$6,($C$12+$C$9*6)/O24)</f>
+        <v/>
+      </c>
+      <c r="R29" s="44" t="inlineStr">
+        <is>
+          <t>Villages at River Grove</t>
+        </is>
+      </c>
+      <c r="S29" s="45" t="n">
+        <v>180</v>
+      </c>
+      <c r="T29" s="46" t="inlineStr"/>
+      <c r="U29" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V29" s="47">
+        <f>IFERROR(VALUE(RIGHT(T29,4))*4+MATCH(LEFT(T29,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W29" s="47">
+        <f>IF(V29="","",IF(V29&lt;=$E$4,0,MAX(1,INT((V29-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="40" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J30" s="59">
+        <f>MIN($C$6,($C$12+$C$10*1)/J24)</f>
+        <v/>
+      </c>
+      <c r="K30" s="59">
+        <f>MIN($C$6,($C$12+$C$10*2)/K24)</f>
+        <v/>
+      </c>
+      <c r="L30" s="59">
+        <f>MIN($C$6,($C$12+$C$10*3)/L24)</f>
+        <v/>
+      </c>
+      <c r="M30" s="59">
+        <f>MIN($C$6,($C$12+$C$10*4)/M24)</f>
+        <v/>
+      </c>
+      <c r="N30" s="59">
+        <f>MIN($C$6,($C$12+$C$10*5)/N24)</f>
+        <v/>
+      </c>
+      <c r="O30" s="59">
+        <f>MIN($C$6,($C$12+$C$10*6)/O24)</f>
+        <v/>
+      </c>
+      <c r="R30" s="44" t="inlineStr">
+        <is>
+          <t>District 99</t>
+        </is>
+      </c>
+      <c r="S30" s="45" t="n">
+        <v>172</v>
+      </c>
+      <c r="T30" s="46" t="inlineStr"/>
+      <c r="U30" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V30" s="47">
+        <f>IFERROR(VALUE(RIGHT(T30,4))*4+MATCH(LEFT(T30,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W30" s="47">
+        <f>IF(V30="","",IF(V30&lt;=$E$4,0,MAX(1,INT((V30-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="R31" s="44" t="inlineStr">
+        <is>
+          <t>McDowell Villas</t>
+        </is>
+      </c>
+      <c r="S31" s="45" t="n">
+        <v>164</v>
+      </c>
+      <c r="T31" s="46" t="inlineStr"/>
+      <c r="U31" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V31" s="47">
+        <f>IFERROR(VALUE(RIGHT(T31,4))*4+MATCH(LEFT(T31,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W31" s="47">
+        <f>IF(V31="","",IF(V31&lt;=$E$4,0,MAX(1,INT((V31-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="40" t="inlineStr">
+        <is>
+          <t>MARKET RENT GROWTH (editable assumptions)</t>
+        </is>
+      </c>
+      <c r="J32" s="60" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K32" s="60" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L32" s="60" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M32" s="60" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N32" s="60" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O32" s="60" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="R32" s="44" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="S32" s="45" t="n">
+        <v>156</v>
+      </c>
+      <c r="T32" s="46" t="inlineStr"/>
+      <c r="U32" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V32" s="47">
+        <f>IFERROR(VALUE(RIGHT(T32,4))*4+MATCH(LEFT(T32,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W32" s="47">
+        <f>IF(V32="","",IF(V32&lt;=$E$4,0,MAX(1,INT((V32-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J33" s="61" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K33" s="61" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="L33" s="61" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M33" s="61" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="N33" s="61" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O33" s="61" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="R33" s="44" t="inlineStr">
+        <is>
+          <t>Porter Kyle Development</t>
+        </is>
+      </c>
+      <c r="S33" s="45" t="n">
+        <v>135</v>
+      </c>
+      <c r="T33" s="46" t="inlineStr"/>
+      <c r="U33" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V33" s="47">
+        <f>IFERROR(VALUE(RIGHT(T33,4))*4+MATCH(LEFT(T33,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W33" s="47">
+        <f>IF(V33="","",IF(V33&lt;=$E$4,0,MAX(1,INT((V33-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="40" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J34" s="61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K34" s="61" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L34" s="61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M34" s="61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N34" s="61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O34" s="61" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R34" s="44" t="inlineStr">
+        <is>
+          <t>Ascent Goodyear</t>
+        </is>
+      </c>
+      <c r="S34" s="45" t="n">
+        <v>113</v>
+      </c>
+      <c r="T34" s="46" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U34" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V34" s="47">
+        <f>IFERROR(VALUE(RIGHT(T34,4))*4+MATCH(LEFT(T34,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="47">
+        <f>IF(V34="","",IF(V34&lt;=$E$4,0,MAX(1,INT((V34-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J35" s="61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K35" s="61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L35" s="61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M35" s="61" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N35" s="61" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O35" s="61" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R35" s="44" t="inlineStr">
+        <is>
+          <t>Northern 107</t>
+        </is>
+      </c>
+      <c r="S35" s="45" t="n">
+        <v>74</v>
+      </c>
+      <c r="T35" s="46" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="U35" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V35" s="47">
+        <f>IFERROR(VALUE(RIGHT(T35,4))*4+MATCH(LEFT(T35,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="47">
+        <f>IF(V35="","",IF(V35&lt;=$E$4,0,MAX(1,INT((V35-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="40" t="inlineStr">
+        <is>
+          <t>CONCESSIONS (months, editable)</t>
+        </is>
+      </c>
+      <c r="R36" s="44" t="inlineStr">
+        <is>
+          <t>Zenn @ Sierra Verde</t>
+        </is>
+      </c>
+      <c r="S36" s="45" t="n">
+        <v>66</v>
+      </c>
+      <c r="T36" s="46" t="inlineStr"/>
+      <c r="U36" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V36" s="47">
+        <f>IFERROR(VALUE(RIGHT(T36,4))*4+MATCH(LEFT(T36,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W36" s="47">
+        <f>IF(V36="","",IF(V36&lt;=$E$4,0,MAX(1,INT((V36-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="40" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J37" s="61" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K37" s="61" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L37" s="61" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M37" s="61" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N37" s="61" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O37" s="61" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R37" s="44" t="inlineStr">
+        <is>
+          <t>The BLVD Residential District</t>
+        </is>
+      </c>
+      <c r="S37" s="45" t="n"/>
+      <c r="T37" s="46" t="inlineStr"/>
+      <c r="U37" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V37" s="47">
+        <f>IFERROR(VALUE(RIGHT(T37,4))*4+MATCH(LEFT(T37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W37" s="47">
+        <f>IF(V37="","",IF(V37&lt;=$E$4,0,MAX(1,INT((V37-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J38" s="61" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K38" s="61" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L38" s="61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M38" s="61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N38" s="61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O38" s="61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R38" s="44" t="inlineStr">
+        <is>
+          <t>The BLVD Park Avenue District</t>
+        </is>
+      </c>
+      <c r="S38" s="45" t="n"/>
+      <c r="T38" s="46" t="inlineStr"/>
+      <c r="U38" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V38" s="47">
+        <f>IFERROR(VALUE(RIGHT(T38,4))*4+MATCH(LEFT(T38,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W38" s="47">
+        <f>IF(V38="","",IF(V38&lt;=$E$4,0,MAX(1,INT((V38-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="40" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J39" s="61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K39" s="61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L39" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="44" t="inlineStr">
+        <is>
+          <t>Globe Land Investors Development</t>
+        </is>
+      </c>
+      <c r="S39" s="45" t="n"/>
+      <c r="T39" s="46" t="inlineStr"/>
+      <c r="U39" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V39" s="47">
+        <f>IFERROR(VALUE(RIGHT(T39,4))*4+MATCH(LEFT(T39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W39" s="47">
+        <f>IF(V39="","",IF(V39&lt;=$E$4,0,MAX(1,INT((V39-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="40" t="inlineStr">
+        <is>
+          <t>EFFECTIVE RENT GROWTH (derived)</t>
+        </is>
+      </c>
+      <c r="R40" s="44" t="inlineStr">
+        <is>
+          <t>Ball Park</t>
+        </is>
+      </c>
+      <c r="S40" s="45" t="n"/>
+      <c r="T40" s="46" t="inlineStr"/>
+      <c r="U40" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V40" s="47">
+        <f>IFERROR(VALUE(RIGHT(T40,4))*4+MATCH(LEFT(T40,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W40" s="47">
+        <f>IF(V40="","",IF(V40&lt;=$E$4,0,MAX(1,INT((V40-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="40" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J41" s="59">
+        <f>(1+J33)*(1-J37)-1</f>
+        <v/>
+      </c>
+      <c r="K41" s="59">
+        <f>(1+K33)*(1-K37)/(1-J37)-1</f>
+        <v/>
+      </c>
+      <c r="L41" s="59">
+        <f>(1+L33)*(1-L37)/(1-K37)-1</f>
+        <v/>
+      </c>
+      <c r="M41" s="59">
+        <f>(1+M33)*(1-M37)/(1-L37)-1</f>
+        <v/>
+      </c>
+      <c r="N41" s="59">
+        <f>(1+N33)*(1-N37)/(1-M37)-1</f>
+        <v/>
+      </c>
+      <c r="O41" s="59">
+        <f>(1+O33)*(1-O37)/(1-N37)-1</f>
+        <v/>
+      </c>
+      <c r="R41" s="44" t="inlineStr">
+        <is>
+          <t>Vision 2 Parcel A</t>
+        </is>
+      </c>
+      <c r="S41" s="45" t="n"/>
+      <c r="T41" s="46" t="inlineStr"/>
+      <c r="U41" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V41" s="47">
+        <f>IFERROR(VALUE(RIGHT(T41,4))*4+MATCH(LEFT(T41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W41" s="47">
+        <f>IF(V41="","",IF(V41&lt;=$E$4,0,MAX(1,INT((V41-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="40" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J42" s="59">
+        <f>(1+J34)*(1-J38)-1</f>
+        <v/>
+      </c>
+      <c r="K42" s="59">
+        <f>(1+K34)*(1-K38)/(1-J38)-1</f>
+        <v/>
+      </c>
+      <c r="L42" s="59">
+        <f>(1+L34)*(1-L38)/(1-K38)-1</f>
+        <v/>
+      </c>
+      <c r="M42" s="59">
+        <f>(1+M34)*(1-M38)/(1-L38)-1</f>
+        <v/>
+      </c>
+      <c r="N42" s="59">
+        <f>(1+N34)*(1-N38)/(1-M38)-1</f>
+        <v/>
+      </c>
+      <c r="O42" s="59">
+        <f>(1+O34)*(1-O38)/(1-N38)-1</f>
+        <v/>
+      </c>
+      <c r="R42" s="44" t="inlineStr">
+        <is>
+          <t>Firststreet Verde</t>
+        </is>
+      </c>
+      <c r="S42" s="45" t="n"/>
+      <c r="T42" s="46" t="inlineStr"/>
+      <c r="U42" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V42" s="47">
+        <f>IFERROR(VALUE(RIGHT(T42,4))*4+MATCH(LEFT(T42,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W42" s="47">
+        <f>IF(V42="","",IF(V42&lt;=$E$4,0,MAX(1,INT((V42-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J43" s="59">
+        <f>(1+J35)*(1-J39)-1</f>
+        <v/>
+      </c>
+      <c r="K43" s="59">
+        <f>(1+K35)*(1-K39)/(1-J39)-1</f>
+        <v/>
+      </c>
+      <c r="L43" s="59">
+        <f>(1+L35)*(1-L39)/(1-K39)-1</f>
+        <v/>
+      </c>
+      <c r="M43" s="59">
+        <f>(1+M35)*(1-M39)/(1-L39)-1</f>
+        <v/>
+      </c>
+      <c r="N43" s="59">
+        <f>(1+N35)*(1-N39)/(1-M39)-1</f>
+        <v/>
+      </c>
+      <c r="O43" s="59">
+        <f>(1+O35)*(1-O39)/(1-N39)-1</f>
+        <v/>
+      </c>
+      <c r="R43" s="44" t="inlineStr">
+        <is>
+          <t>Goodyear Civic Square at Estrella Falls</t>
+        </is>
+      </c>
+      <c r="S43" s="45" t="n"/>
+      <c r="T43" s="46" t="inlineStr"/>
+      <c r="U43" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V43" s="47">
+        <f>IFERROR(VALUE(RIGHT(T43,4))*4+MATCH(LEFT(T43,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W43" s="47">
+        <f>IF(V43="","",IF(V43&lt;=$E$4,0,MAX(1,INT((V43-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="33" t="inlineStr">
+        <is>
+          <t>Reconciliation: scheduled pipeline (Incl=Y) vs CoStar Under Construction = 1,251 units.</t>
+        </is>
+      </c>
+      <c r="R44" s="44" t="inlineStr">
+        <is>
+          <t>I-10 Innovation Center II</t>
+        </is>
+      </c>
+      <c r="S44" s="45" t="n"/>
+      <c r="T44" s="46" t="inlineStr"/>
+      <c r="U44" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V44" s="47">
+        <f>IFERROR(VALUE(RIGHT(T44,4))*4+MATCH(LEFT(T44,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W44" s="47">
+        <f>IF(V44="","",IF(V44&lt;=$E$4,0,MAX(1,INT((V44-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="33" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += scheduled pipeline; occupied += selected demand (capped at target). Edit yellow cells (close quarter, demand scenario/levels, pipeline dates &amp; include, rent-growth &amp; concessions).</t>
+        </is>
+      </c>
+      <c r="R45" s="44" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel D</t>
+        </is>
+      </c>
+      <c r="S45" s="45" t="n"/>
+      <c r="T45" s="46" t="inlineStr"/>
+      <c r="U45" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V45" s="47">
+        <f>IFERROR(VALUE(RIGHT(T45,4))*4+MATCH(LEFT(T45,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W45" s="47">
+        <f>IF(V45="","",IF(V45&lt;=$E$4,0,MAX(1,INT((V45-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="R46" s="44" t="inlineStr">
+        <is>
+          <t>SimonMed Development II</t>
+        </is>
+      </c>
+      <c r="S46" s="45" t="n"/>
+      <c r="T46" s="46" t="inlineStr"/>
+      <c r="U46" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V46" s="47">
+        <f>IFERROR(VALUE(RIGHT(T46,4))*4+MATCH(LEFT(T46,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W46" s="47">
+        <f>IF(V46="","",IF(V46&lt;=$E$4,0,MAX(1,INT((V46-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="R47" s="44" t="inlineStr">
+        <is>
+          <t>182 South 95th Avenue</t>
+        </is>
+      </c>
+      <c r="S47" s="45" t="n"/>
+      <c r="T47" s="46" t="inlineStr"/>
+      <c r="U47" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V47" s="47">
+        <f>IFERROR(VALUE(RIGHT(T47,4))*4+MATCH(LEFT(T47,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W47" s="47">
+        <f>IF(V47="","",IF(V47&lt;=$E$4,0,MAX(1,INT((V47-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="R48" s="44" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="S48" s="45" t="n"/>
+      <c r="T48" s="46" t="inlineStr"/>
+      <c r="U48" s="46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V48" s="47">
+        <f>IFERROR(VALUE(RIGHT(T48,4))*4+MATCH(LEFT(T48,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W48" s="47">
+        <f>IF(V48="","",IF(V48&lt;=$E$4,0,MAX(1,INT((V48-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="R49" s="44" t="inlineStr">
+        <is>
+          <t>FUZE Ballpark</t>
+        </is>
+      </c>
+      <c r="S49" s="45" t="n">
         <v>321</v>
       </c>
-      <c r="L14" s="47" t="inlineStr"/>
-      <c r="M14" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="J15" s="45" t="inlineStr">
-        <is>
-          <t>Anton Glendale</t>
-        </is>
-      </c>
-      <c r="K15" s="46" t="n">
-        <v>320</v>
-      </c>
-      <c r="L15" s="47" t="inlineStr"/>
-      <c r="M15" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="J16" s="45" t="inlineStr">
-        <is>
-          <t>Western Garden II</t>
-        </is>
-      </c>
-      <c r="K16" s="46" t="n">
-        <v>314</v>
-      </c>
-      <c r="L16" s="47" t="inlineStr"/>
-      <c r="M16" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="J17" s="45" t="inlineStr">
-        <is>
-          <t>Sanctuair at Centerscape</t>
-        </is>
-      </c>
-      <c r="K17" s="46" t="n">
-        <v>303</v>
-      </c>
-      <c r="L17" s="47" t="inlineStr"/>
-      <c r="M17" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="J18" s="45" t="inlineStr">
-        <is>
-          <t>Encore Avondale</t>
-        </is>
-      </c>
-      <c r="K18" s="46" t="n">
-        <v>300</v>
-      </c>
-      <c r="L18" s="47" t="inlineStr"/>
-      <c r="M18" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="J19" s="45" t="inlineStr">
-        <is>
-          <t>Banyan Avondale</t>
-        </is>
-      </c>
-      <c r="K19" s="46" t="n">
-        <v>296</v>
-      </c>
-      <c r="L19" s="47" t="inlineStr"/>
-      <c r="M19" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="J20" s="45" t="inlineStr">
-        <is>
-          <t>Rosilian Villas</t>
-        </is>
-      </c>
-      <c r="K20" s="46" t="n">
-        <v>291</v>
-      </c>
-      <c r="L20" s="47" t="inlineStr"/>
-      <c r="M20" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="J21" s="45" t="inlineStr">
-        <is>
-          <t>The Statler at Estrella Parkway</t>
-        </is>
-      </c>
-      <c r="K21" s="46" t="n">
-        <v>284</v>
-      </c>
-      <c r="L21" s="47" t="inlineStr"/>
-      <c r="M21" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="J22" s="45" t="inlineStr">
-        <is>
-          <t>Orion Avondale</t>
-        </is>
-      </c>
-      <c r="K22" s="46" t="n">
-        <v>268</v>
-      </c>
-      <c r="L22" s="47" t="inlineStr"/>
-      <c r="M22" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="J23" s="45" t="inlineStr">
-        <is>
-          <t>Tavalo at Avondale</t>
-        </is>
-      </c>
-      <c r="K23" s="46" t="n">
-        <v>266</v>
-      </c>
-      <c r="L23" s="47" t="inlineStr"/>
-      <c r="M23" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="J24" s="45" t="inlineStr">
-        <is>
-          <t>Marbella Ranch East Future Phase</t>
-        </is>
-      </c>
-      <c r="K24" s="46" t="n">
-        <v>266</v>
-      </c>
-      <c r="L24" s="47" t="inlineStr"/>
-      <c r="M24" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="J25" s="45" t="inlineStr">
-        <is>
-          <t>Crystal Cove</t>
-        </is>
-      </c>
-      <c r="K25" s="46" t="n">
-        <v>260</v>
-      </c>
-      <c r="L25" s="47" t="inlineStr"/>
-      <c r="M25" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="J26" s="45" t="inlineStr">
-        <is>
-          <t>Cornerstone at the Wigwam</t>
-        </is>
-      </c>
-      <c r="K26" s="46" t="n">
-        <v>212</v>
-      </c>
-      <c r="L26" s="47" t="inlineStr"/>
-      <c r="M26" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="J27" s="45" t="inlineStr">
-        <is>
-          <t>Radia Avondale Station III</t>
-        </is>
-      </c>
-      <c r="K27" s="46" t="n">
-        <v>212</v>
-      </c>
-      <c r="L27" s="47" t="inlineStr"/>
-      <c r="M27" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="J28" s="45" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel A</t>
-        </is>
-      </c>
-      <c r="K28" s="46" t="n">
-        <v>181</v>
-      </c>
-      <c r="L28" s="47" t="inlineStr"/>
-      <c r="M28" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="J29" s="45" t="inlineStr">
-        <is>
-          <t>Villages at River Grove</t>
-        </is>
-      </c>
-      <c r="K29" s="46" t="n">
-        <v>180</v>
-      </c>
-      <c r="L29" s="47" t="inlineStr"/>
-      <c r="M29" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="J30" s="45" t="inlineStr">
-        <is>
-          <t>District 99</t>
-        </is>
-      </c>
-      <c r="K30" s="46" t="n">
-        <v>172</v>
-      </c>
-      <c r="L30" s="47" t="inlineStr"/>
-      <c r="M30" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="J31" s="45" t="inlineStr">
-        <is>
-          <t>McDowell Villas</t>
-        </is>
-      </c>
-      <c r="K31" s="46" t="n">
-        <v>164</v>
-      </c>
-      <c r="L31" s="47" t="inlineStr"/>
-      <c r="M31" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="J32" s="45" t="inlineStr">
-        <is>
-          <t>Avondale</t>
-        </is>
-      </c>
-      <c r="K32" s="46" t="n">
-        <v>156</v>
-      </c>
-      <c r="L32" s="47" t="inlineStr"/>
-      <c r="M32" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="J33" s="45" t="inlineStr">
-        <is>
-          <t>Porter Kyle Development</t>
-        </is>
-      </c>
-      <c r="K33" s="46" t="n">
-        <v>135</v>
-      </c>
-      <c r="L33" s="47" t="inlineStr"/>
-      <c r="M33" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="J34" s="45" t="inlineStr">
-        <is>
-          <t>Ascent Goodyear</t>
-        </is>
-      </c>
-      <c r="K34" s="46" t="n">
-        <v>113</v>
-      </c>
-      <c r="L34" s="47" t="inlineStr"/>
-      <c r="M34" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="J35" s="45" t="inlineStr">
-        <is>
-          <t>Northern 107</t>
-        </is>
-      </c>
-      <c r="K35" s="46" t="n">
+      <c r="T49" s="46" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="U49" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V49" s="47">
+        <f>IFERROR(VALUE(RIGHT(T49,4))*4+MATCH(LEFT(T49,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W49" s="47">
+        <f>IF(V49="","",IF(V49&lt;=$E$4,0,MAX(1,INT((V49-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="R50" s="44" t="inlineStr">
+        <is>
+          <t>Zanjero III</t>
+        </is>
+      </c>
+      <c r="S50" s="45" t="n">
+        <v>301</v>
+      </c>
+      <c r="T50" s="46" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="U50" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V50" s="47">
+        <f>IFERROR(VALUE(RIGHT(T50,4))*4+MATCH(LEFT(T50,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W50" s="47">
+        <f>IF(V50="","",IF(V50&lt;=$E$4,0,MAX(1,INT((V50-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="R51" s="44" t="inlineStr">
+        <is>
+          <t>Pointe Grand Estrella at Phoenix</t>
+        </is>
+      </c>
+      <c r="S51" s="45" t="n">
+        <v>288</v>
+      </c>
+      <c r="T51" s="46" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="U51" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V51" s="47">
+        <f>IFERROR(VALUE(RIGHT(T51,4))*4+MATCH(LEFT(T51,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W51" s="47">
+        <f>IF(V51="","",IF(V51&lt;=$E$4,0,MAX(1,INT((V51-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="R52" s="44" t="inlineStr">
+        <is>
+          <t>Yardly Algodon</t>
+        </is>
+      </c>
+      <c r="S52" s="45" t="n">
+        <v>262</v>
+      </c>
+      <c r="T52" s="46" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="U52" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V52" s="47">
+        <f>IFERROR(VALUE(RIGHT(T52,4))*4+MATCH(LEFT(T52,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W52" s="47">
+        <f>IF(V52="","",IF(V52&lt;=$E$4,0,MAX(1,INT((V52-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="R53" s="44" t="inlineStr">
+        <is>
+          <t>Cerro Vista</t>
+        </is>
+      </c>
+      <c r="S53" s="45" t="n">
+        <v>255</v>
+      </c>
+      <c r="T53" s="46" t="inlineStr">
+        <is>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="U53" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V53" s="47">
+        <f>IFERROR(VALUE(RIGHT(T53,4))*4+MATCH(LEFT(T53,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W53" s="47">
+        <f>IF(V53="","",IF(V53&lt;=$E$4,0,MAX(1,INT((V53-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="R54" s="44" t="inlineStr">
+        <is>
+          <t>Marbella Ranch East I</t>
+        </is>
+      </c>
+      <c r="S54" s="45" t="n">
+        <v>144</v>
+      </c>
+      <c r="T54" s="46" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="U54" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V54" s="47">
+        <f>IFERROR(VALUE(RIGHT(T54,4))*4+MATCH(LEFT(T54,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W54" s="47">
+        <f>IF(V54="","",IF(V54&lt;=$E$4,0,MAX(1,INT((V54-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="R55" s="44" t="inlineStr">
+        <is>
+          <t>Zen @ Angelina</t>
+        </is>
+      </c>
+      <c r="S55" s="45" t="n">
+        <v>130</v>
+      </c>
+      <c r="T55" s="46" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="U55" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V55" s="47">
+        <f>IFERROR(VALUE(RIGHT(T55,4))*4+MATCH(LEFT(T55,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W55" s="47">
+        <f>IF(V55="","",IF(V55&lt;=$E$4,0,MAX(1,INT((V55-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="R56" s="44" t="inlineStr">
+        <is>
+          <t>HARMON Ascend</t>
+        </is>
+      </c>
+      <c r="S56" s="45" t="n">
+        <v>125</v>
+      </c>
+      <c r="T56" s="46" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="U56" s="46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V56" s="47">
+        <f>IFERROR(VALUE(RIGHT(T56,4))*4+MATCH(LEFT(T56,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W56" s="47">
+        <f>IF(V56="","",IF(V56&lt;=$E$4,0,MAX(1,INT((V56-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="R57" s="44" t="inlineStr">
+        <is>
+          <t>Villages at Northern</t>
+        </is>
+      </c>
+      <c r="S57" s="45" t="n">
         <v>74</v>
       </c>
-      <c r="L35" s="47" t="inlineStr"/>
-      <c r="M35" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="J36" s="45" t="inlineStr">
-        <is>
-          <t>Zenn @ Sierra Verde</t>
-        </is>
-      </c>
-      <c r="K36" s="46" t="n">
-        <v>66</v>
-      </c>
-      <c r="L36" s="47" t="inlineStr"/>
-      <c r="M36" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="J37" s="45" t="inlineStr">
-        <is>
-          <t>The BLVD Residential District</t>
-        </is>
-      </c>
-      <c r="K37" s="46" t="n"/>
-      <c r="L37" s="47" t="inlineStr"/>
-      <c r="M37" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="J38" s="45" t="inlineStr">
-        <is>
-          <t>The BLVD Park Avenue District</t>
-        </is>
-      </c>
-      <c r="K38" s="46" t="n"/>
-      <c r="L38" s="47" t="inlineStr"/>
-      <c r="M38" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="J39" s="45" t="inlineStr">
-        <is>
-          <t>Globe Land Investors Development</t>
-        </is>
-      </c>
-      <c r="K39" s="46" t="n"/>
-      <c r="L39" s="47" t="inlineStr"/>
-      <c r="M39" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="J40" s="45" t="inlineStr">
-        <is>
-          <t>Ball Park</t>
-        </is>
-      </c>
-      <c r="K40" s="46" t="n"/>
-      <c r="L40" s="47" t="inlineStr"/>
-      <c r="M40" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="J41" s="45" t="inlineStr">
-        <is>
-          <t>Vision 2 Parcel A</t>
-        </is>
-      </c>
-      <c r="K41" s="46" t="n"/>
-      <c r="L41" s="47" t="inlineStr"/>
-      <c r="M41" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="J42" s="45" t="inlineStr">
-        <is>
-          <t>Firststreet Verde</t>
-        </is>
-      </c>
-      <c r="K42" s="46" t="n"/>
-      <c r="L42" s="47" t="inlineStr"/>
-      <c r="M42" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="J43" s="45" t="inlineStr">
-        <is>
-          <t>Goodyear Civic Square at Estrella Falls</t>
-        </is>
-      </c>
-      <c r="K43" s="46" t="n"/>
-      <c r="L43" s="47" t="inlineStr"/>
-      <c r="M43" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="J44" s="45" t="inlineStr">
-        <is>
-          <t>I-10 Innovation Center II</t>
-        </is>
-      </c>
-      <c r="K44" s="46" t="n"/>
-      <c r="L44" s="47" t="inlineStr"/>
-      <c r="M44" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="J45" s="45" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel D</t>
-        </is>
-      </c>
-      <c r="K45" s="46" t="n"/>
-      <c r="L45" s="47" t="inlineStr"/>
-      <c r="M45" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="J46" s="45" t="inlineStr">
-        <is>
-          <t>SimonMed Development II</t>
-        </is>
-      </c>
-      <c r="K46" s="46" t="n"/>
-      <c r="L46" s="47" t="inlineStr"/>
-      <c r="M46" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="J47" s="45" t="inlineStr">
-        <is>
-          <t>182 South 95th Avenue</t>
-        </is>
-      </c>
-      <c r="K47" s="46" t="n"/>
-      <c r="L47" s="47" t="inlineStr"/>
-      <c r="M47" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="J48" s="45" t="inlineStr">
-        <is>
-          <t>Envision Encore</t>
-        </is>
-      </c>
-      <c r="K48" s="46" t="n"/>
-      <c r="L48" s="47" t="inlineStr"/>
-      <c r="M48" s="47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="J49" s="45" t="inlineStr">
-        <is>
-          <t>FUZE Ballpark</t>
-        </is>
-      </c>
-      <c r="K49" s="46" t="n">
-        <v>321</v>
-      </c>
-      <c r="L49" s="47" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="M49" s="47" t="inlineStr">
+      <c r="T57" s="46" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="U57" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="50">
-      <c r="J50" s="45" t="inlineStr">
-        <is>
-          <t>Zanjero III</t>
-        </is>
-      </c>
-      <c r="K50" s="46" t="n">
-        <v>301</v>
-      </c>
-      <c r="L50" s="47" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="M50" s="47" t="inlineStr">
+      <c r="V57" s="47">
+        <f>IFERROR(VALUE(RIGHT(T57,4))*4+MATCH(LEFT(T57,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W57" s="47">
+        <f>IF(V57="","",IF(V57&lt;=$E$4,0,MAX(1,INT((V57-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="R58" s="44" t="inlineStr">
+        <is>
+          <t>Prosper 47</t>
+        </is>
+      </c>
+      <c r="S58" s="45" t="n">
+        <v>47</v>
+      </c>
+      <c r="T58" s="46" t="inlineStr">
+        <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="U58" s="46" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-    </row>
-    <row r="51">
-      <c r="J51" s="45" t="inlineStr">
-        <is>
-          <t>Pointe Grand Estrella at Phoenix</t>
-        </is>
-      </c>
-      <c r="K51" s="46" t="n">
-        <v>288</v>
-      </c>
-      <c r="L51" s="47" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="M51" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="J52" s="45" t="inlineStr">
-        <is>
-          <t>Yardly Algodon</t>
-        </is>
-      </c>
-      <c r="K52" s="46" t="n">
-        <v>262</v>
-      </c>
-      <c r="L52" s="47" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="M52" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="J53" s="45" t="inlineStr">
-        <is>
-          <t>Cerro Vista</t>
-        </is>
-      </c>
-      <c r="K53" s="46" t="n">
-        <v>255</v>
-      </c>
-      <c r="L53" s="47" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="M53" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="J54" s="45" t="inlineStr">
-        <is>
-          <t>Marbella Ranch East I</t>
-        </is>
-      </c>
-      <c r="K54" s="46" t="n">
-        <v>144</v>
-      </c>
-      <c r="L54" s="47" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="M54" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="J55" s="45" t="inlineStr">
-        <is>
-          <t>Zen @ Angelina</t>
-        </is>
-      </c>
-      <c r="K55" s="46" t="n">
-        <v>130</v>
-      </c>
-      <c r="L55" s="47" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="M55" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="J56" s="45" t="inlineStr">
-        <is>
-          <t>HARMON Ascend</t>
-        </is>
-      </c>
-      <c r="K56" s="46" t="n">
-        <v>125</v>
-      </c>
-      <c r="L56" s="47" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="M56" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="J57" s="45" t="inlineStr">
-        <is>
-          <t>Villages at Northern</t>
-        </is>
-      </c>
-      <c r="K57" s="46" t="n">
-        <v>74</v>
-      </c>
-      <c r="L57" s="47" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="M57" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="J58" s="45" t="inlineStr">
-        <is>
-          <t>Prosper 47</t>
-        </is>
-      </c>
-      <c r="K58" s="46" t="n">
-        <v>47</v>
-      </c>
-      <c r="L58" s="47" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="M58" s="47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>New Supply</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Absorption</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Occupied</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Overall Occ</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2023</t>
-        </is>
-      </c>
-      <c r="C61" s="49" t="n">
-        <v>738</v>
-      </c>
-      <c r="D61" s="49" t="n">
-        <v>221</v>
-      </c>
-      <c r="E61" s="49" t="n">
-        <v>15268</v>
-      </c>
-      <c r="F61" s="49" t="n">
-        <v>18615</v>
-      </c>
-      <c r="G61" s="50">
-        <f>IFERROR(E61/F61,0)</f>
-        <v/>
-      </c>
-      <c r="H61" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="48" t="inlineStr">
-        <is>
-          <t>Q4 2023</t>
-        </is>
-      </c>
-      <c r="C62" s="49" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D62" s="49" t="n">
-        <v>590</v>
-      </c>
-      <c r="E62" s="49" t="n">
-        <v>15857</v>
-      </c>
-      <c r="F62" s="49" t="n">
-        <v>19915</v>
-      </c>
-      <c r="G62" s="50">
-        <f>IFERROR(E62/F62,0)</f>
-        <v/>
-      </c>
-      <c r="H62" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2024</t>
-        </is>
-      </c>
-      <c r="C63" s="49" t="n">
-        <v>600</v>
-      </c>
-      <c r="D63" s="49" t="n">
-        <v>791</v>
-      </c>
-      <c r="E63" s="49" t="n">
-        <v>16648</v>
-      </c>
-      <c r="F63" s="49" t="n">
-        <v>20515</v>
-      </c>
-      <c r="G63" s="50">
-        <f>IFERROR(E63/F63,0)</f>
-        <v/>
-      </c>
-      <c r="H63" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="48" t="inlineStr">
-        <is>
-          <t>Q2 2024</t>
-        </is>
-      </c>
-      <c r="C64" s="49" t="n">
-        <v>185</v>
-      </c>
-      <c r="D64" s="49" t="n">
-        <v>912</v>
-      </c>
-      <c r="E64" s="49" t="n">
-        <v>17560</v>
-      </c>
-      <c r="F64" s="49" t="n">
-        <v>20700</v>
-      </c>
-      <c r="G64" s="50">
-        <f>IFERROR(E64/F64,0)</f>
-        <v/>
-      </c>
-      <c r="H64" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2024</t>
-        </is>
-      </c>
-      <c r="C65" s="49" t="n">
-        <v>1403</v>
-      </c>
-      <c r="D65" s="49" t="n">
-        <v>851</v>
-      </c>
-      <c r="E65" s="49" t="n">
-        <v>18411</v>
-      </c>
-      <c r="F65" s="49" t="n">
-        <v>22103</v>
-      </c>
-      <c r="G65" s="50">
-        <f>IFERROR(E65/F65,0)</f>
-        <v/>
-      </c>
-      <c r="H65" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="48" t="inlineStr">
-        <is>
-          <t>Q4 2024</t>
-        </is>
-      </c>
-      <c r="C66" s="49" t="n">
-        <v>669</v>
-      </c>
-      <c r="D66" s="49" t="n">
-        <v>529</v>
-      </c>
-      <c r="E66" s="49" t="n">
-        <v>18940</v>
-      </c>
-      <c r="F66" s="49" t="n">
-        <v>22772</v>
-      </c>
-      <c r="G66" s="50">
-        <f>IFERROR(E66/F66,0)</f>
-        <v/>
-      </c>
-      <c r="H66" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2025</t>
-        </is>
-      </c>
-      <c r="C67" s="49" t="n">
-        <v>1748</v>
-      </c>
-      <c r="D67" s="49" t="n">
-        <v>641</v>
-      </c>
-      <c r="E67" s="49" t="n">
-        <v>19581</v>
-      </c>
-      <c r="F67" s="49" t="n">
-        <v>24520</v>
-      </c>
-      <c r="G67" s="50">
-        <f>IFERROR(E67/F67,0)</f>
-        <v/>
-      </c>
-      <c r="H67" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="48" t="inlineStr">
-        <is>
-          <t>Q2 2025</t>
-        </is>
-      </c>
-      <c r="C68" s="49" t="n">
-        <v>223</v>
-      </c>
-      <c r="D68" s="49" t="n">
-        <v>634</v>
-      </c>
-      <c r="E68" s="49" t="n">
-        <v>20215</v>
-      </c>
-      <c r="F68" s="49" t="n">
-        <v>24743</v>
-      </c>
-      <c r="G68" s="50">
-        <f>IFERROR(E68/F68,0)</f>
-        <v/>
-      </c>
-      <c r="H68" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="48" t="inlineStr">
-        <is>
-          <t>Q3 2025</t>
-        </is>
-      </c>
-      <c r="C69" s="49" t="n">
-        <v>84</v>
-      </c>
-      <c r="D69" s="49" t="n">
-        <v>498</v>
-      </c>
-      <c r="E69" s="49" t="n">
-        <v>20713</v>
-      </c>
-      <c r="F69" s="49" t="n">
-        <v>24827</v>
-      </c>
-      <c r="G69" s="50">
-        <f>IFERROR(E69/F69,0)</f>
-        <v/>
-      </c>
-      <c r="H69" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="48" t="inlineStr">
-        <is>
-          <t>Q4 2025</t>
-        </is>
-      </c>
-      <c r="C70" s="49" t="n">
-        <v>634</v>
-      </c>
-      <c r="D70" s="49" t="n">
-        <v>680</v>
-      </c>
-      <c r="E70" s="49" t="n">
-        <v>21394</v>
-      </c>
-      <c r="F70" s="49" t="n">
-        <v>25461</v>
-      </c>
-      <c r="G70" s="50">
-        <f>IFERROR(E70/F70,0)</f>
-        <v/>
-      </c>
-      <c r="H70" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="48" t="inlineStr">
-        <is>
-          <t>Q1 2026</t>
-        </is>
-      </c>
-      <c r="C71" s="49" t="n">
-        <v>676</v>
-      </c>
-      <c r="D71" s="49" t="n">
-        <v>726</v>
-      </c>
-      <c r="E71" s="49" t="n">
-        <v>22120</v>
-      </c>
-      <c r="F71" s="49" t="n">
-        <v>26137</v>
-      </c>
-      <c r="G71" s="50">
-        <f>IFERROR(E71/F71,0)</f>
-        <v/>
-      </c>
-      <c r="H71" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="48" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="C72" s="49" t="n">
-        <v>466</v>
-      </c>
-      <c r="D72" s="49" t="n">
-        <v>465</v>
-      </c>
-      <c r="E72" s="49" t="n">
-        <v>22585</v>
-      </c>
-      <c r="F72" s="49" t="n">
-        <v>26603</v>
-      </c>
-      <c r="G72" s="50">
-        <f>IFERROR(E72/F72,0)</f>
-        <v/>
-      </c>
-      <c r="H72" s="48" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="C73" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B73,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D73" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F73-E72))</f>
-        <v/>
-      </c>
-      <c r="E73" s="52">
-        <f>E72+D73</f>
-        <v/>
-      </c>
-      <c r="F73" s="52">
-        <f>F72+C73</f>
-        <v/>
-      </c>
-      <c r="G73" s="53">
-        <f>IFERROR(E73/F73,0)</f>
-        <v/>
-      </c>
-      <c r="H73" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="51" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="C74" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B74,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D74" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F74-E73))</f>
-        <v/>
-      </c>
-      <c r="E74" s="52">
-        <f>E73+D74</f>
-        <v/>
-      </c>
-      <c r="F74" s="52">
-        <f>F73+C74</f>
-        <v/>
-      </c>
-      <c r="G74" s="53">
-        <f>IFERROR(E74/F74,0)</f>
-        <v/>
-      </c>
-      <c r="H74" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="51" t="inlineStr">
-        <is>
-          <t>Q1 2027</t>
-        </is>
-      </c>
-      <c r="C75" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B75,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D75" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F75-E74))</f>
-        <v/>
-      </c>
-      <c r="E75" s="52">
-        <f>E74+D75</f>
-        <v/>
-      </c>
-      <c r="F75" s="52">
-        <f>F74+C75</f>
-        <v/>
-      </c>
-      <c r="G75" s="53">
-        <f>IFERROR(E75/F75,0)</f>
-        <v/>
-      </c>
-      <c r="H75" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="51" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="C76" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B76,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D76" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F76-E75))</f>
-        <v/>
-      </c>
-      <c r="E76" s="52">
-        <f>E75+D76</f>
-        <v/>
-      </c>
-      <c r="F76" s="52">
-        <f>F75+C76</f>
-        <v/>
-      </c>
-      <c r="G76" s="53">
-        <f>IFERROR(E76/F76,0)</f>
-        <v/>
-      </c>
-      <c r="H76" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="C77" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B77,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D77" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F77-E76))</f>
-        <v/>
-      </c>
-      <c r="E77" s="52">
-        <f>E76+D77</f>
-        <v/>
-      </c>
-      <c r="F77" s="52">
-        <f>F76+C77</f>
-        <v/>
-      </c>
-      <c r="G77" s="53">
-        <f>IFERROR(E77/F77,0)</f>
-        <v/>
-      </c>
-      <c r="H77" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="51" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="C78" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B78,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D78" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F78-E77))</f>
-        <v/>
-      </c>
-      <c r="E78" s="52">
-        <f>E77+D78</f>
-        <v/>
-      </c>
-      <c r="F78" s="52">
-        <f>F77+C78</f>
-        <v/>
-      </c>
-      <c r="G78" s="53">
-        <f>IFERROR(E78/F78,0)</f>
-        <v/>
-      </c>
-      <c r="H78" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="51" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="C79" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B79,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D79" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F79-E78))</f>
-        <v/>
-      </c>
-      <c r="E79" s="52">
-        <f>E78+D79</f>
-        <v/>
-      </c>
-      <c r="F79" s="52">
-        <f>F78+C79</f>
-        <v/>
-      </c>
-      <c r="G79" s="53">
-        <f>IFERROR(E79/F79,0)</f>
-        <v/>
-      </c>
-      <c r="H79" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="51" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="C80" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B80,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D80" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F80-E79))</f>
-        <v/>
-      </c>
-      <c r="E80" s="52">
-        <f>E79+D80</f>
-        <v/>
-      </c>
-      <c r="F80" s="52">
-        <f>F79+C80</f>
-        <v/>
-      </c>
-      <c r="G80" s="53">
-        <f>IFERROR(E80/F80,0)</f>
-        <v/>
-      </c>
-      <c r="H80" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="C81" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B81,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D81" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F81-E80))</f>
-        <v/>
-      </c>
-      <c r="E81" s="52">
-        <f>E80+D81</f>
-        <v/>
-      </c>
-      <c r="F81" s="52">
-        <f>F80+C81</f>
-        <v/>
-      </c>
-      <c r="G81" s="53">
-        <f>IFERROR(E81/F81,0)</f>
-        <v/>
-      </c>
-      <c r="H81" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="51" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="C82" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B82,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D82" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F82-E81))</f>
-        <v/>
-      </c>
-      <c r="E82" s="52">
-        <f>E81+D82</f>
-        <v/>
-      </c>
-      <c r="F82" s="52">
-        <f>F81+C82</f>
-        <v/>
-      </c>
-      <c r="G82" s="53">
-        <f>IFERROR(E82/F82,0)</f>
-        <v/>
-      </c>
-      <c r="H82" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="51" t="inlineStr">
-        <is>
-          <t>Q1 2029</t>
-        </is>
-      </c>
-      <c r="C83" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B83,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D83" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F83-E82))</f>
-        <v/>
-      </c>
-      <c r="E83" s="52">
-        <f>E82+D83</f>
-        <v/>
-      </c>
-      <c r="F83" s="52">
-        <f>F82+C83</f>
-        <v/>
-      </c>
-      <c r="G83" s="53">
-        <f>IFERROR(E83/F83,0)</f>
-        <v/>
-      </c>
-      <c r="H83" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="51" t="inlineStr">
-        <is>
-          <t>Q2 2029</t>
-        </is>
-      </c>
-      <c r="C84" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B84,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D84" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F84-E83))</f>
-        <v/>
-      </c>
-      <c r="E84" s="52">
-        <f>E83+D84</f>
-        <v/>
-      </c>
-      <c r="F84" s="52">
-        <f>F83+C84</f>
-        <v/>
-      </c>
-      <c r="G84" s="53">
-        <f>IFERROR(E84/F84,0)</f>
-        <v/>
-      </c>
-      <c r="H84" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2029</t>
-        </is>
-      </c>
-      <c r="C85" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B85,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D85" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F85-E84))</f>
-        <v/>
-      </c>
-      <c r="E85" s="52">
-        <f>E84+D85</f>
-        <v/>
-      </c>
-      <c r="F85" s="52">
-        <f>F84+C85</f>
-        <v/>
-      </c>
-      <c r="G85" s="53">
-        <f>IFERROR(E85/F85,0)</f>
-        <v/>
-      </c>
-      <c r="H85" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="51" t="inlineStr">
-        <is>
-          <t>Q4 2029</t>
-        </is>
-      </c>
-      <c r="C86" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B86,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D86" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F86-E85))</f>
-        <v/>
-      </c>
-      <c r="E86" s="52">
-        <f>E85+D86</f>
-        <v/>
-      </c>
-      <c r="F86" s="52">
-        <f>F85+C86</f>
-        <v/>
-      </c>
-      <c r="G86" s="53">
-        <f>IFERROR(E86/F86,0)</f>
-        <v/>
-      </c>
-      <c r="H86" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="51" t="inlineStr">
-        <is>
-          <t>Q1 2030</t>
-        </is>
-      </c>
-      <c r="C87" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B87,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D87" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F87-E86))</f>
-        <v/>
-      </c>
-      <c r="E87" s="52">
-        <f>E86+D87</f>
-        <v/>
-      </c>
-      <c r="F87" s="52">
-        <f>F86+C87</f>
-        <v/>
-      </c>
-      <c r="G87" s="53">
-        <f>IFERROR(E87/F87,0)</f>
-        <v/>
-      </c>
-      <c r="H87" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="51" t="inlineStr">
-        <is>
-          <t>Q2 2030</t>
-        </is>
-      </c>
-      <c r="C88" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B88,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D88" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F88-E87))</f>
-        <v/>
-      </c>
-      <c r="E88" s="52">
-        <f>E87+D88</f>
-        <v/>
-      </c>
-      <c r="F88" s="52">
-        <f>F87+C88</f>
-        <v/>
-      </c>
-      <c r="G88" s="53">
-        <f>IFERROR(E88/F88,0)</f>
-        <v/>
-      </c>
-      <c r="H88" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2030</t>
-        </is>
-      </c>
-      <c r="C89" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B89,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D89" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F89-E88))</f>
-        <v/>
-      </c>
-      <c r="E89" s="52">
-        <f>E88+D89</f>
-        <v/>
-      </c>
-      <c r="F89" s="52">
-        <f>F88+C89</f>
-        <v/>
-      </c>
-      <c r="G89" s="53">
-        <f>IFERROR(E89/F89,0)</f>
-        <v/>
-      </c>
-      <c r="H89" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="51" t="inlineStr">
-        <is>
-          <t>Q4 2030</t>
-        </is>
-      </c>
-      <c r="C90" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B90,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D90" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F90-E89))</f>
-        <v/>
-      </c>
-      <c r="E90" s="52">
-        <f>E89+D90</f>
-        <v/>
-      </c>
-      <c r="F90" s="52">
-        <f>F89+C90</f>
-        <v/>
-      </c>
-      <c r="G90" s="53">
-        <f>IFERROR(E90/F90,0)</f>
-        <v/>
-      </c>
-      <c r="H90" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="51" t="inlineStr">
-        <is>
-          <t>Q1 2031</t>
-        </is>
-      </c>
-      <c r="C91" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B91,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D91" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F91-E90))</f>
-        <v/>
-      </c>
-      <c r="E91" s="52">
-        <f>E90+D91</f>
-        <v/>
-      </c>
-      <c r="F91" s="52">
-        <f>F90+C91</f>
-        <v/>
-      </c>
-      <c r="G91" s="53">
-        <f>IFERROR(E91/F91,0)</f>
-        <v/>
-      </c>
-      <c r="H91" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="51" t="inlineStr">
-        <is>
-          <t>Q2 2031</t>
-        </is>
-      </c>
-      <c r="C92" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B92,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D92" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F92-E91))</f>
-        <v/>
-      </c>
-      <c r="E92" s="52">
-        <f>E91+D92</f>
-        <v/>
-      </c>
-      <c r="F92" s="52">
-        <f>F91+C92</f>
-        <v/>
-      </c>
-      <c r="G92" s="53">
-        <f>IFERROR(E92/F92,0)</f>
-        <v/>
-      </c>
-      <c r="H92" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2031</t>
-        </is>
-      </c>
-      <c r="C93" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B93,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D93" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F93-E92))</f>
-        <v/>
-      </c>
-      <c r="E93" s="52">
-        <f>E92+D93</f>
-        <v/>
-      </c>
-      <c r="F93" s="52">
-        <f>F92+C93</f>
-        <v/>
-      </c>
-      <c r="G93" s="53">
-        <f>IFERROR(E93/F93,0)</f>
-        <v/>
-      </c>
-      <c r="H93" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="51" t="inlineStr">
-        <is>
-          <t>Q4 2031</t>
-        </is>
-      </c>
-      <c r="C94" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B94,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D94" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F94-E93))</f>
-        <v/>
-      </c>
-      <c r="E94" s="52">
-        <f>E93+D94</f>
-        <v/>
-      </c>
-      <c r="F94" s="52">
-        <f>F93+C94</f>
-        <v/>
-      </c>
-      <c r="G94" s="53">
-        <f>IFERROR(E94/F94,0)</f>
-        <v/>
-      </c>
-      <c r="H94" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="51" t="inlineStr">
-        <is>
-          <t>Q1 2032</t>
-        </is>
-      </c>
-      <c r="C95" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B95,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D95" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F95-E94))</f>
-        <v/>
-      </c>
-      <c r="E95" s="52">
-        <f>E94+D95</f>
-        <v/>
-      </c>
-      <c r="F95" s="52">
-        <f>F94+C95</f>
-        <v/>
-      </c>
-      <c r="G95" s="53">
-        <f>IFERROR(E95/F95,0)</f>
-        <v/>
-      </c>
-      <c r="H95" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="51" t="inlineStr">
-        <is>
-          <t>Q2 2032</t>
-        </is>
-      </c>
-      <c r="C96" s="52">
-        <f>SUMIFS($K$5:$K$58,$L$5:$L$58,B96,$M$5:$M$58,"Y")</f>
-        <v/>
-      </c>
-      <c r="D96" s="52">
-        <f>MIN($C$10,MAX(0,$C$3*F96-E95))</f>
-        <v/>
-      </c>
-      <c r="E96" s="52">
-        <f>E95+D96</f>
-        <v/>
-      </c>
-      <c r="F96" s="52">
-        <f>F95+C96</f>
-        <v/>
-      </c>
-      <c r="G96" s="53">
-        <f>IFERROR(E96/F96,0)</f>
-        <v/>
-      </c>
-      <c r="H96" s="51" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="33" t="inlineStr">
-        <is>
-          <t>Historical = CoStar 5-mi actuals. Forecast: inventory grows by scheduled pipeline deliveries (edit dates/include at right); absorption = min(quarterly demand, units to reach target); overall occ = occupied / inventory. Yellow cells are editable.</t>
-        </is>
+      <c r="V58" s="47">
+        <f>IFERROR(VALUE(RIGHT(T58,4))*4+MATCH(LEFT(T58,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W58" s="47">
+        <f>IF(V58="","",IF(V58&lt;=$E$4,0,MAX(1,INT((V58-$E$5)/4)+1)))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="B98:H98"/>
+  <mergeCells count="1">
+    <mergeCell ref="B2:O2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -298,9 +298,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -317,6 +314,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9416,7 +9416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:W58"/>
+  <dimension ref="B2:X61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -9437,9 +9437,10 @@
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
     <col width="8" customWidth="1" min="22" max="22"/>
     <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="2" ht="22" customHeight="1">
@@ -9452,7 +9453,7 @@
     <row r="3">
       <c r="R3" s="39" t="inlineStr">
         <is>
-          <t>PIPELINE INPUTS (forward new supply)</t>
+          <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
         </is>
       </c>
     </row>
@@ -9487,15 +9488,10 @@
       </c>
       <c r="U4" s="42" t="inlineStr">
         <is>
-          <t>Incl?</t>
+          <t>DelivIdx</t>
         </is>
       </c>
       <c r="V4" s="42" t="inlineStr">
-        <is>
-          <t>DelivIdx</t>
-        </is>
-      </c>
-      <c r="W4" s="42" t="inlineStr">
         <is>
           <t>HoldYr</t>
         </is>
@@ -9516,26 +9512,24 @@
         <f>IFERROR(VALUE(RIGHT($C$5,4))*4+MATCH(LEFT($C$5,2),{"Q1","Q2","Q3","Q4"},0)-1,0)</f>
         <v/>
       </c>
-      <c r="R5" s="44" t="inlineStr">
-        <is>
-          <t>Sheely Center Future Phase</t>
-        </is>
-      </c>
-      <c r="S5" s="45" t="n">
-        <v>697</v>
-      </c>
-      <c r="T5" s="46" t="inlineStr"/>
-      <c r="U5" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V5" s="47">
+      <c r="R5" s="44">
+        <f>'Competitive Analysis'!C69</f>
+        <v/>
+      </c>
+      <c r="S5" s="45">
+        <f>'Competitive Analysis'!D69</f>
+        <v/>
+      </c>
+      <c r="T5" s="46">
+        <f>'Competitive Analysis'!E69</f>
+        <v/>
+      </c>
+      <c r="U5" s="46">
         <f>IFERROR(VALUE(RIGHT(T5,4))*4+MATCH(LEFT(T5,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W5" s="47">
-        <f>IF(V5="","",IF(V5&lt;=$E$4,0,MAX(1,INT((V5-$E$5)/4)+1)))</f>
+      <c r="V5" s="46">
+        <f>IF(S5="","",IF(U5&lt;=$E$4,0,MAX(1,INT((U5-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9545,30 +9539,32 @@
           <t>Stabilization Target</t>
         </is>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="47">
         <f>Settings!$B$2</f>
         <v/>
       </c>
-      <c r="R6" s="44" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel C</t>
-        </is>
-      </c>
-      <c r="S6" s="45" t="n">
-        <v>500</v>
-      </c>
-      <c r="T6" s="46" t="inlineStr"/>
-      <c r="U6" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V6" s="47">
+      <c r="E6">
+        <f>IF($C$7="Bear",3,IF($C$7="Base",2,1))</f>
+        <v/>
+      </c>
+      <c r="R6" s="44">
+        <f>'Competitive Analysis'!C60</f>
+        <v/>
+      </c>
+      <c r="S6" s="45">
+        <f>'Competitive Analysis'!D60</f>
+        <v/>
+      </c>
+      <c r="T6" s="46">
+        <f>'Competitive Analysis'!E60</f>
+        <v/>
+      </c>
+      <c r="U6" s="46">
         <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W6" s="47">
-        <f>IF(V6="","",IF(V6&lt;=$E$4,0,MAX(1,INT((V6-$E$5)/4)+1)))</f>
+      <c r="V6" s="46">
+        <f>IF(S6="","",IF(U6&lt;=$E$4,0,MAX(1,INT((U6-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9583,26 +9579,24 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="R7" s="44" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel B</t>
-        </is>
-      </c>
-      <c r="S7" s="45" t="n">
-        <v>478</v>
-      </c>
-      <c r="T7" s="46" t="inlineStr"/>
-      <c r="U7" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V7" s="47">
+      <c r="R7" s="44">
+        <f>'Competitive Analysis'!C64</f>
+        <v/>
+      </c>
+      <c r="S7" s="45">
+        <f>'Competitive Analysis'!D64</f>
+        <v/>
+      </c>
+      <c r="T7" s="46">
+        <f>'Competitive Analysis'!E64</f>
+        <v/>
+      </c>
+      <c r="U7" s="46">
         <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W7" s="47">
-        <f>IF(V7="","",IF(V7&lt;=$E$4,0,MAX(1,INT((V7-$E$5)/4)+1)))</f>
+      <c r="V7" s="46">
+        <f>IF(S7="","",IF(U7&lt;=$E$4,0,MAX(1,INT((U7-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9612,29 +9606,27 @@
           <t>Bear Annual Absorption</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="48" t="n">
         <v>1250</v>
       </c>
-      <c r="R8" s="44" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel B</t>
-        </is>
-      </c>
-      <c r="S8" s="45" t="n">
-        <v>410</v>
-      </c>
-      <c r="T8" s="46" t="inlineStr"/>
-      <c r="U8" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V8" s="47">
+      <c r="R8" s="44">
+        <f>'Competitive Analysis'!C62</f>
+        <v/>
+      </c>
+      <c r="S8" s="45">
+        <f>'Competitive Analysis'!D62</f>
+        <v/>
+      </c>
+      <c r="T8" s="46">
+        <f>'Competitive Analysis'!E62</f>
+        <v/>
+      </c>
+      <c r="U8" s="46">
         <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W8" s="47">
-        <f>IF(V8="","",IF(V8&lt;=$E$4,0,MAX(1,INT((V8-$E$5)/4)+1)))</f>
+      <c r="V8" s="46">
+        <f>IF(S8="","",IF(U8&lt;=$E$4,0,MAX(1,INT((U8-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9644,29 +9636,27 @@
           <t>Base Annual Absorption</t>
         </is>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="48" t="n">
         <v>2525</v>
       </c>
-      <c r="R9" s="44" t="inlineStr">
-        <is>
-          <t>The District at Westgate</t>
-        </is>
-      </c>
-      <c r="S9" s="45" t="n">
-        <v>384</v>
-      </c>
-      <c r="T9" s="46" t="inlineStr"/>
-      <c r="U9" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V9" s="47">
+      <c r="R9" s="44">
+        <f>'Competitive Analysis'!C63</f>
+        <v/>
+      </c>
+      <c r="S9" s="45">
+        <f>'Competitive Analysis'!D63</f>
+        <v/>
+      </c>
+      <c r="T9" s="46">
+        <f>'Competitive Analysis'!E63</f>
+        <v/>
+      </c>
+      <c r="U9" s="46">
         <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W9" s="47">
-        <f>IF(V9="","",IF(V9&lt;=$E$4,0,MAX(1,INT((V9-$E$5)/4)+1)))</f>
+      <c r="V9" s="46">
+        <f>IF(S9="","",IF(U9&lt;=$E$4,0,MAX(1,INT((U9-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9676,29 +9666,27 @@
           <t>Bull Annual Absorption</t>
         </is>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="48" t="n">
         <v>3800</v>
       </c>
-      <c r="R10" s="44" t="inlineStr">
-        <is>
-          <t>Picerne at Palm Valley</t>
-        </is>
-      </c>
-      <c r="S10" s="45" t="n">
-        <v>383</v>
-      </c>
-      <c r="T10" s="46" t="inlineStr"/>
-      <c r="U10" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V10" s="47">
+      <c r="R10" s="44">
+        <f>'Competitive Analysis'!C65</f>
+        <v/>
+      </c>
+      <c r="S10" s="45">
+        <f>'Competitive Analysis'!D65</f>
+        <v/>
+      </c>
+      <c r="T10" s="46">
+        <f>'Competitive Analysis'!E65</f>
+        <v/>
+      </c>
+      <c r="U10" s="46">
         <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W10" s="47">
-        <f>IF(V10="","",IF(V10&lt;=$E$4,0,MAX(1,INT((V10-$E$5)/4)+1)))</f>
+      <c r="V10" s="46">
+        <f>IF(S10="","",IF(U10&lt;=$E$4,0,MAX(1,INT((U10-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9708,30 +9696,28 @@
           <t>Selected Annual Demand</t>
         </is>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="49">
         <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
         <v/>
       </c>
-      <c r="R11" s="44" t="inlineStr">
-        <is>
-          <t>Liv Avondale</t>
-        </is>
-      </c>
-      <c r="S11" s="45" t="n">
-        <v>333</v>
-      </c>
-      <c r="T11" s="46" t="inlineStr"/>
-      <c r="U11" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V11" s="47">
+      <c r="R11" s="44">
+        <f>'Competitive Analysis'!C61</f>
+        <v/>
+      </c>
+      <c r="S11" s="45">
+        <f>'Competitive Analysis'!D61</f>
+        <v/>
+      </c>
+      <c r="T11" s="46">
+        <f>'Competitive Analysis'!E61</f>
+        <v/>
+      </c>
+      <c r="U11" s="46">
         <f>IFERROR(VALUE(RIGHT(T11,4))*4+MATCH(LEFT(T11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W11" s="47">
-        <f>IF(V11="","",IF(V11&lt;=$E$4,0,MAX(1,INT((V11-$E$5)/4)+1)))</f>
+      <c r="V11" s="46">
+        <f>IF(S11="","",IF(U11&lt;=$E$4,0,MAX(1,INT((U11-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9741,29 +9727,27 @@
           <t>Occupied (as-of)</t>
         </is>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="49" t="n">
         <v>22585</v>
       </c>
-      <c r="R12" s="44" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel A</t>
-        </is>
-      </c>
-      <c r="S12" s="45" t="n">
-        <v>324</v>
-      </c>
-      <c r="T12" s="46" t="inlineStr"/>
-      <c r="U12" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V12" s="47">
+      <c r="R12" s="44">
+        <f>'Competitive Analysis'!C68</f>
+        <v/>
+      </c>
+      <c r="S12" s="45">
+        <f>'Competitive Analysis'!D68</f>
+        <v/>
+      </c>
+      <c r="T12" s="46">
+        <f>'Competitive Analysis'!E68</f>
+        <v/>
+      </c>
+      <c r="U12" s="46">
         <f>IFERROR(VALUE(RIGHT(T12,4))*4+MATCH(LEFT(T12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W12" s="47">
-        <f>IF(V12="","",IF(V12&lt;=$E$4,0,MAX(1,INT((V12-$E$5)/4)+1)))</f>
+      <c r="V12" s="46">
+        <f>IF(S12="","",IF(U12&lt;=$E$4,0,MAX(1,INT((U12-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
@@ -9773,106 +9757,57 @@
           <t>Inventory (as-of)</t>
         </is>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="49" t="n">
         <v>26603</v>
       </c>
-      <c r="R13" s="44" t="inlineStr">
-        <is>
-          <t>The Waverly</t>
-        </is>
-      </c>
-      <c r="S13" s="45" t="n">
-        <v>323</v>
-      </c>
-      <c r="T13" s="46" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U13" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V13" s="47">
+      <c r="R13" s="44">
+        <f>'Competitive Analysis'!C66</f>
+        <v/>
+      </c>
+      <c r="S13" s="45">
+        <f>'Competitive Analysis'!D66</f>
+        <v/>
+      </c>
+      <c r="T13" s="46">
+        <f>'Competitive Analysis'!E66</f>
+        <v/>
+      </c>
+      <c r="U13" s="46">
         <f>IFERROR(VALUE(RIGHT(T13,4))*4+MATCH(LEFT(T13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W13" s="47">
-        <f>IF(V13="","",IF(V13&lt;=$E$4,0,MAX(1,INT((V13-$E$5)/4)+1)))</f>
+      <c r="V13" s="46">
+        <f>IF(S13="","",IF(U13&lt;=$E$4,0,MAX(1,INT((U13-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="R14" s="44" t="inlineStr">
-        <is>
-          <t>Fuze 623</t>
-        </is>
-      </c>
-      <c r="S14" s="45" t="n">
-        <v>321</v>
-      </c>
-      <c r="T14" s="46" t="inlineStr"/>
-      <c r="U14" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V14" s="47">
+      <c r="R14" s="44">
+        <f>'Competitive Analysis'!C67</f>
+        <v/>
+      </c>
+      <c r="S14" s="45">
+        <f>'Competitive Analysis'!D67</f>
+        <v/>
+      </c>
+      <c r="T14" s="46">
+        <f>'Competitive Analysis'!E67</f>
+        <v/>
+      </c>
+      <c r="U14" s="46">
         <f>IFERROR(VALUE(RIGHT(T14,4))*4+MATCH(LEFT(T14,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W14" s="47">
-        <f>IF(V14="","",IF(V14&lt;=$E$4,0,MAX(1,INT((V14-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="R15" s="44" t="inlineStr">
-        <is>
-          <t>Anton Glendale</t>
-        </is>
-      </c>
-      <c r="S15" s="45" t="n">
-        <v>320</v>
-      </c>
-      <c r="T15" s="46" t="inlineStr"/>
-      <c r="U15" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V15" s="47">
-        <f>IFERROR(VALUE(RIGHT(T15,4))*4+MATCH(LEFT(T15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W15" s="47">
-        <f>IF(V15="","",IF(V15&lt;=$E$4,0,MAX(1,INT((V15-$E$5)/4)+1)))</f>
+      <c r="V14" s="46">
+        <f>IF(S14="","",IF(U14&lt;=$E$4,0,MAX(1,INT((U14-$E$5)/4)+1)))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="R16" s="44" t="inlineStr">
-        <is>
-          <t>Western Garden II</t>
-        </is>
-      </c>
-      <c r="S16" s="45" t="n">
-        <v>314</v>
-      </c>
-      <c r="T16" s="46" t="inlineStr"/>
-      <c r="U16" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V16" s="47">
-        <f>IFERROR(VALUE(RIGHT(T16,4))*4+MATCH(LEFT(T16,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W16" s="47">
-        <f>IF(V16="","",IF(V16&lt;=$E$4,0,MAX(1,INT((V16-$E$5)/4)+1)))</f>
-        <v/>
+      <c r="R16" s="39" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -9916,149 +9851,162 @@
           <t>Y0</t>
         </is>
       </c>
-      <c r="J17" s="51" t="inlineStr">
+      <c r="J17" s="50" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K17" s="51" t="inlineStr">
+      <c r="K17" s="50" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L17" s="51" t="inlineStr">
+      <c r="L17" s="50" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M17" s="51" t="inlineStr">
+      <c r="M17" s="50" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N17" s="51" t="inlineStr">
+      <c r="N17" s="50" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O17" s="51" t="inlineStr">
+      <c r="O17" s="50" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
-      <c r="R17" s="44" t="inlineStr">
-        <is>
-          <t>Sanctuair at Centerscape</t>
-        </is>
-      </c>
-      <c r="S17" s="45" t="n">
-        <v>303</v>
-      </c>
-      <c r="T17" s="46" t="inlineStr"/>
-      <c r="U17" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V17" s="47">
-        <f>IFERROR(VALUE(RIGHT(T17,4))*4+MATCH(LEFT(T17,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W17" s="47">
-        <f>IF(V17="","",IF(V17&lt;=$E$4,0,MAX(1,INT((V17-$E$5)/4)+1)))</f>
-        <v/>
+      <c r="R17" s="42" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S17" s="42" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T17" s="42" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U17" s="42" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
+      </c>
+      <c r="V17" s="42" t="inlineStr">
+        <is>
+          <t>DelivIdx</t>
+        </is>
+      </c>
+      <c r="W17" s="42" t="inlineStr">
+        <is>
+          <t>HoldYr</t>
+        </is>
+      </c>
+      <c r="X17" s="42" t="inlineStr">
+        <is>
+          <t>Built?</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="52" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>Q3 2019–Q2 2020</t>
         </is>
       </c>
-      <c r="D18" s="52" t="inlineStr">
+      <c r="D18" s="51" t="inlineStr">
         <is>
           <t>Q3 2020–Q2 2021</t>
         </is>
       </c>
-      <c r="E18" s="52" t="inlineStr">
+      <c r="E18" s="51" t="inlineStr">
         <is>
           <t>Q3 2021–Q2 2022</t>
         </is>
       </c>
-      <c r="F18" s="52" t="inlineStr">
+      <c r="F18" s="51" t="inlineStr">
         <is>
           <t>Q3 2022–Q2 2023</t>
         </is>
       </c>
-      <c r="G18" s="52" t="inlineStr">
+      <c r="G18" s="51" t="inlineStr">
         <is>
           <t>Q3 2023–Q2 2024</t>
         </is>
       </c>
-      <c r="H18" s="52" t="inlineStr">
+      <c r="H18" s="51" t="inlineStr">
         <is>
           <t>Q3 2024–Q2 2025</t>
         </is>
       </c>
-      <c r="I18" s="52" t="inlineStr">
+      <c r="I18" s="51" t="inlineStr">
         <is>
           <t>Q3 2025–Q2 2026</t>
         </is>
       </c>
-      <c r="J18" s="52" t="inlineStr">
+      <c r="J18" s="51" t="inlineStr">
         <is>
           <t>Hold Yr 1</t>
         </is>
       </c>
-      <c r="K18" s="52" t="inlineStr">
+      <c r="K18" s="51" t="inlineStr">
         <is>
           <t>Hold Yr 2</t>
         </is>
       </c>
-      <c r="L18" s="52" t="inlineStr">
+      <c r="L18" s="51" t="inlineStr">
         <is>
           <t>Hold Yr 3</t>
         </is>
       </c>
-      <c r="M18" s="52" t="inlineStr">
+      <c r="M18" s="51" t="inlineStr">
         <is>
           <t>Hold Yr 4</t>
         </is>
       </c>
-      <c r="N18" s="52" t="inlineStr">
+      <c r="N18" s="51" t="inlineStr">
         <is>
           <t>Hold Yr 5</t>
         </is>
       </c>
-      <c r="O18" s="52" t="inlineStr">
+      <c r="O18" s="51" t="inlineStr">
         <is>
           <t>Hold Yr 6</t>
         </is>
       </c>
       <c r="R18" s="44" t="inlineStr">
         <is>
-          <t>Encore Avondale</t>
+          <t>Sheely Center Future Phase</t>
         </is>
       </c>
       <c r="S18" s="45" t="n">
-        <v>300</v>
-      </c>
-      <c r="T18" s="46" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U18" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V18" s="47">
+        <v>697</v>
+      </c>
+      <c r="T18" s="52" t="inlineStr"/>
+      <c r="U18" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V18" s="46">
         <f>IFERROR(VALUE(RIGHT(T18,4))*4+MATCH(LEFT(T18,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W18" s="47">
+      <c r="W18" s="46">
         <f>IF(V18="","",IF(V18&lt;=$E$4,0,MAX(1,INT((V18-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X18" s="46">
+        <f>IF(U18="None",0,IF($E$6&gt;=IF(U18="Bear",3,IF(U18="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10090,49 +10038,53 @@
         <v>1860</v>
       </c>
       <c r="J19" s="54">
-        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,1,$U$5:$U$58,"Y")</f>
+        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,1)+SUMIFS($S$18:$S$61,$W$18:$W$61,1,$X$18:$X$61,1)</f>
         <v/>
       </c>
       <c r="K19" s="54">
-        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,2,$U$5:$U$58,"Y")</f>
+        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,2)+SUMIFS($S$18:$S$61,$W$18:$W$61,2,$X$18:$X$61,1)</f>
         <v/>
       </c>
       <c r="L19" s="54">
-        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,3,$U$5:$U$58,"Y")</f>
+        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,3)+SUMIFS($S$18:$S$61,$W$18:$W$61,3,$X$18:$X$61,1)</f>
         <v/>
       </c>
       <c r="M19" s="54">
-        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,4,$U$5:$U$58,"Y")</f>
+        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,4)+SUMIFS($S$18:$S$61,$W$18:$W$61,4,$X$18:$X$61,1)</f>
         <v/>
       </c>
       <c r="N19" s="54">
-        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,5,$U$5:$U$58,"Y")</f>
+        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,5)+SUMIFS($S$18:$S$61,$W$18:$W$61,5,$X$18:$X$61,1)</f>
         <v/>
       </c>
       <c r="O19" s="54">
-        <f>SUMIFS($S$5:$S$58,$W$5:$W$58,6,$U$5:$U$58,"Y")</f>
+        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,6)+SUMIFS($S$18:$S$61,$W$18:$W$61,6,$X$18:$X$61,1)</f>
         <v/>
       </c>
       <c r="R19" s="44" t="inlineStr">
         <is>
-          <t>Banyan Avondale</t>
+          <t>Urban 95 Parcel C</t>
         </is>
       </c>
       <c r="S19" s="45" t="n">
-        <v>296</v>
-      </c>
-      <c r="T19" s="46" t="inlineStr"/>
-      <c r="U19" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V19" s="47">
+        <v>500</v>
+      </c>
+      <c r="T19" s="52" t="inlineStr"/>
+      <c r="U19" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V19" s="46">
         <f>IFERROR(VALUE(RIGHT(T19,4))*4+MATCH(LEFT(T19,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W19" s="47">
+      <c r="W19" s="46">
         <f>IF(V19="","",IF(V19&lt;=$E$4,0,MAX(1,INT((V19-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X19" s="46">
+        <f>IF(U19="None",0,IF($E$6&gt;=IF(U19="Bear",3,IF(U19="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10189,24 +10141,28 @@
       </c>
       <c r="R20" s="44" t="inlineStr">
         <is>
-          <t>Rosilian Villas</t>
+          <t>Urban 95 Parcel B</t>
         </is>
       </c>
       <c r="S20" s="45" t="n">
-        <v>291</v>
-      </c>
-      <c r="T20" s="46" t="inlineStr"/>
-      <c r="U20" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V20" s="47">
+        <v>478</v>
+      </c>
+      <c r="T20" s="52" t="inlineStr"/>
+      <c r="U20" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V20" s="46">
         <f>IFERROR(VALUE(RIGHT(T20,4))*4+MATCH(LEFT(T20,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W20" s="47">
+      <c r="W20" s="46">
         <f>IF(V20="","",IF(V20&lt;=$E$4,0,MAX(1,INT((V20-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X20" s="46">
+        <f>IF(U20="None",0,IF($E$6&gt;=IF(U20="Bear",3,IF(U20="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10263,28 +10219,28 @@
       </c>
       <c r="R21" s="44" t="inlineStr">
         <is>
-          <t>The Statler at Estrella Parkway</t>
+          <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
       <c r="S21" s="45" t="n">
-        <v>284</v>
-      </c>
-      <c r="T21" s="46" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U21" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V21" s="47">
+        <v>410</v>
+      </c>
+      <c r="T21" s="52" t="inlineStr"/>
+      <c r="U21" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V21" s="46">
         <f>IFERROR(VALUE(RIGHT(T21,4))*4+MATCH(LEFT(T21,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W21" s="47">
+      <c r="W21" s="46">
         <f>IF(V21="","",IF(V21&lt;=$E$4,0,MAX(1,INT((V21-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X21" s="46">
+        <f>IF(U21="None",0,IF($E$6&gt;=IF(U21="Bear",3,IF(U21="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10339,48 +10295,56 @@
       </c>
       <c r="R22" s="44" t="inlineStr">
         <is>
-          <t>Orion Avondale</t>
+          <t>The District at Westgate</t>
         </is>
       </c>
       <c r="S22" s="45" t="n">
-        <v>268</v>
-      </c>
-      <c r="T22" s="46" t="inlineStr"/>
-      <c r="U22" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V22" s="47">
+        <v>384</v>
+      </c>
+      <c r="T22" s="52" t="inlineStr"/>
+      <c r="U22" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V22" s="46">
         <f>IFERROR(VALUE(RIGHT(T22,4))*4+MATCH(LEFT(T22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W22" s="47">
+      <c r="W22" s="46">
         <f>IF(V22="","",IF(V22&lt;=$E$4,0,MAX(1,INT((V22-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X22" s="46">
+        <f>IF(U22="None",0,IF($E$6&gt;=IF(U22="Bear",3,IF(U22="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="R23" s="44" t="inlineStr">
         <is>
-          <t>Tavalo at Avondale</t>
+          <t>Picerne at Palm Valley</t>
         </is>
       </c>
       <c r="S23" s="45" t="n">
-        <v>266</v>
-      </c>
-      <c r="T23" s="46" t="inlineStr"/>
-      <c r="U23" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V23" s="47">
+        <v>383</v>
+      </c>
+      <c r="T23" s="52" t="inlineStr"/>
+      <c r="U23" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V23" s="46">
         <f>IFERROR(VALUE(RIGHT(T23,4))*4+MATCH(LEFT(T23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W23" s="47">
+      <c r="W23" s="46">
         <f>IF(V23="","",IF(V23&lt;=$E$4,0,MAX(1,INT((V23-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X23" s="46">
+        <f>IF(U23="None",0,IF($E$6&gt;=IF(U23="Bear",3,IF(U23="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10437,24 +10401,28 @@
       </c>
       <c r="R24" s="44" t="inlineStr">
         <is>
-          <t>Marbella Ranch East Future Phase</t>
+          <t>Liv Avondale</t>
         </is>
       </c>
       <c r="S24" s="45" t="n">
-        <v>266</v>
-      </c>
-      <c r="T24" s="46" t="inlineStr"/>
-      <c r="U24" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V24" s="47">
+        <v>333</v>
+      </c>
+      <c r="T24" s="52" t="inlineStr"/>
+      <c r="U24" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V24" s="46">
         <f>IFERROR(VALUE(RIGHT(T24,4))*4+MATCH(LEFT(T24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W24" s="47">
+      <c r="W24" s="46">
         <f>IF(V24="","",IF(V24&lt;=$E$4,0,MAX(1,INT((V24-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X24" s="46">
+        <f>IF(U24="None",0,IF($E$6&gt;=IF(U24="Bear",3,IF(U24="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10511,48 +10479,60 @@
       </c>
       <c r="R25" s="44" t="inlineStr">
         <is>
-          <t>Crystal Cove</t>
+          <t>Urban 95 Parcel A</t>
         </is>
       </c>
       <c r="S25" s="45" t="n">
-        <v>260</v>
-      </c>
-      <c r="T25" s="46" t="inlineStr"/>
-      <c r="U25" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V25" s="47">
+        <v>324</v>
+      </c>
+      <c r="T25" s="52" t="inlineStr"/>
+      <c r="U25" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V25" s="46">
         <f>IFERROR(VALUE(RIGHT(T25,4))*4+MATCH(LEFT(T25,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W25" s="47">
+      <c r="W25" s="46">
         <f>IF(V25="","",IF(V25&lt;=$E$4,0,MAX(1,INT((V25-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X25" s="46">
+        <f>IF(U25="None",0,IF($E$6&gt;=IF(U25="Bear",3,IF(U25="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="R26" s="44" t="inlineStr">
         <is>
-          <t>Cornerstone at the Wigwam</t>
+          <t>The Waverly</t>
         </is>
       </c>
       <c r="S26" s="45" t="n">
-        <v>212</v>
-      </c>
-      <c r="T26" s="46" t="inlineStr"/>
-      <c r="U26" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V26" s="47">
+        <v>323</v>
+      </c>
+      <c r="T26" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U26" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V26" s="46">
         <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W26" s="47">
+      <c r="W26" s="46">
         <f>IF(V26="","",IF(V26&lt;=$E$4,0,MAX(1,INT((V26-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X26" s="46">
+        <f>IF(U26="None",0,IF($E$6&gt;=IF(U26="Bear",3,IF(U26="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10594,24 +10574,28 @@
       </c>
       <c r="R27" s="44" t="inlineStr">
         <is>
-          <t>Radia Avondale Station III</t>
+          <t>Fuze 623</t>
         </is>
       </c>
       <c r="S27" s="45" t="n">
-        <v>212</v>
-      </c>
-      <c r="T27" s="46" t="inlineStr"/>
-      <c r="U27" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V27" s="47">
+        <v>321</v>
+      </c>
+      <c r="T27" s="52" t="inlineStr"/>
+      <c r="U27" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V27" s="46">
         <f>IFERROR(VALUE(RIGHT(T27,4))*4+MATCH(LEFT(T27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W27" s="47">
+      <c r="W27" s="46">
         <f>IF(V27="","",IF(V27&lt;=$E$4,0,MAX(1,INT((V27-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X27" s="46">
+        <f>IF(U27="None",0,IF($E$6&gt;=IF(U27="Bear",3,IF(U27="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10647,24 +10631,28 @@
       </c>
       <c r="R28" s="44" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel A</t>
+          <t>Anton Glendale</t>
         </is>
       </c>
       <c r="S28" s="45" t="n">
-        <v>181</v>
-      </c>
-      <c r="T28" s="46" t="inlineStr"/>
-      <c r="U28" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V28" s="47">
+        <v>320</v>
+      </c>
+      <c r="T28" s="52" t="inlineStr"/>
+      <c r="U28" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V28" s="46">
         <f>IFERROR(VALUE(RIGHT(T28,4))*4+MATCH(LEFT(T28,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W28" s="47">
+      <c r="W28" s="46">
         <f>IF(V28="","",IF(V28&lt;=$E$4,0,MAX(1,INT((V28-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X28" s="46">
+        <f>IF(U28="None",0,IF($E$6&gt;=IF(U28="Bear",3,IF(U28="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10700,24 +10688,28 @@
       </c>
       <c r="R29" s="44" t="inlineStr">
         <is>
-          <t>Villages at River Grove</t>
+          <t>Western Garden II</t>
         </is>
       </c>
       <c r="S29" s="45" t="n">
-        <v>180</v>
-      </c>
-      <c r="T29" s="46" t="inlineStr"/>
-      <c r="U29" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V29" s="47">
+        <v>314</v>
+      </c>
+      <c r="T29" s="52" t="inlineStr"/>
+      <c r="U29" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V29" s="46">
         <f>IFERROR(VALUE(RIGHT(T29,4))*4+MATCH(LEFT(T29,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W29" s="47">
+      <c r="W29" s="46">
         <f>IF(V29="","",IF(V29&lt;=$E$4,0,MAX(1,INT((V29-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X29" s="46">
+        <f>IF(U29="None",0,IF($E$6&gt;=IF(U29="Bear",3,IF(U29="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10753,48 +10745,60 @@
       </c>
       <c r="R30" s="44" t="inlineStr">
         <is>
-          <t>District 99</t>
+          <t>Sanctuair at Centerscape</t>
         </is>
       </c>
       <c r="S30" s="45" t="n">
-        <v>172</v>
-      </c>
-      <c r="T30" s="46" t="inlineStr"/>
-      <c r="U30" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V30" s="47">
+        <v>303</v>
+      </c>
+      <c r="T30" s="52" t="inlineStr"/>
+      <c r="U30" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V30" s="46">
         <f>IFERROR(VALUE(RIGHT(T30,4))*4+MATCH(LEFT(T30,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W30" s="47">
+      <c r="W30" s="46">
         <f>IF(V30="","",IF(V30&lt;=$E$4,0,MAX(1,INT((V30-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X30" s="46">
+        <f>IF(U30="None",0,IF($E$6&gt;=IF(U30="Bear",3,IF(U30="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="R31" s="44" t="inlineStr">
         <is>
-          <t>McDowell Villas</t>
+          <t>Encore Avondale</t>
         </is>
       </c>
       <c r="S31" s="45" t="n">
-        <v>164</v>
-      </c>
-      <c r="T31" s="46" t="inlineStr"/>
-      <c r="U31" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V31" s="47">
+        <v>300</v>
+      </c>
+      <c r="T31" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U31" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V31" s="46">
         <f>IFERROR(VALUE(RIGHT(T31,4))*4+MATCH(LEFT(T31,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W31" s="47">
+      <c r="W31" s="46">
         <f>IF(V31="","",IF(V31&lt;=$E$4,0,MAX(1,INT((V31-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X31" s="46">
+        <f>IF(U31="None",0,IF($E$6&gt;=IF(U31="Bear",3,IF(U31="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10836,24 +10840,28 @@
       </c>
       <c r="R32" s="44" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>Banyan Avondale</t>
         </is>
       </c>
       <c r="S32" s="45" t="n">
-        <v>156</v>
-      </c>
-      <c r="T32" s="46" t="inlineStr"/>
-      <c r="U32" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V32" s="47">
+        <v>296</v>
+      </c>
+      <c r="T32" s="52" t="inlineStr"/>
+      <c r="U32" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V32" s="46">
         <f>IFERROR(VALUE(RIGHT(T32,4))*4+MATCH(LEFT(T32,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W32" s="47">
+      <c r="W32" s="46">
         <f>IF(V32="","",IF(V32&lt;=$E$4,0,MAX(1,INT((V32-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X32" s="46">
+        <f>IF(U32="None",0,IF($E$6&gt;=IF(U32="Bear",3,IF(U32="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10883,24 +10891,28 @@
       </c>
       <c r="R33" s="44" t="inlineStr">
         <is>
-          <t>Porter Kyle Development</t>
+          <t>Rosilian Villas</t>
         </is>
       </c>
       <c r="S33" s="45" t="n">
-        <v>135</v>
-      </c>
-      <c r="T33" s="46" t="inlineStr"/>
-      <c r="U33" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V33" s="47">
+        <v>291</v>
+      </c>
+      <c r="T33" s="52" t="inlineStr"/>
+      <c r="U33" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V33" s="46">
         <f>IFERROR(VALUE(RIGHT(T33,4))*4+MATCH(LEFT(T33,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W33" s="47">
+      <c r="W33" s="46">
         <f>IF(V33="","",IF(V33&lt;=$E$4,0,MAX(1,INT((V33-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X33" s="46">
+        <f>IF(U33="None",0,IF($E$6&gt;=IF(U33="Bear",3,IF(U33="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10930,28 +10942,32 @@
       </c>
       <c r="R34" s="44" t="inlineStr">
         <is>
-          <t>Ascent Goodyear</t>
+          <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
       <c r="S34" s="45" t="n">
-        <v>113</v>
-      </c>
-      <c r="T34" s="46" t="inlineStr">
+        <v>284</v>
+      </c>
+      <c r="T34" s="52" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U34" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V34" s="47">
+      <c r="U34" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V34" s="46">
         <f>IFERROR(VALUE(RIGHT(T34,4))*4+MATCH(LEFT(T34,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W34" s="47">
+      <c r="W34" s="46">
         <f>IF(V34="","",IF(V34&lt;=$E$4,0,MAX(1,INT((V34-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X34" s="46">
+        <f>IF(U34="None",0,IF($E$6&gt;=IF(U34="Bear",3,IF(U34="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -10981,28 +10997,28 @@
       </c>
       <c r="R35" s="44" t="inlineStr">
         <is>
-          <t>Northern 107</t>
+          <t>Orion Avondale</t>
         </is>
       </c>
       <c r="S35" s="45" t="n">
-        <v>74</v>
-      </c>
-      <c r="T35" s="46" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="U35" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V35" s="47">
+        <v>268</v>
+      </c>
+      <c r="T35" s="52" t="inlineStr"/>
+      <c r="U35" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V35" s="46">
         <f>IFERROR(VALUE(RIGHT(T35,4))*4+MATCH(LEFT(T35,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W35" s="47">
+      <c r="W35" s="46">
         <f>IF(V35="","",IF(V35&lt;=$E$4,0,MAX(1,INT((V35-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X35" s="46">
+        <f>IF(U35="None",0,IF($E$6&gt;=IF(U35="Bear",3,IF(U35="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11014,24 +11030,28 @@
       </c>
       <c r="R36" s="44" t="inlineStr">
         <is>
-          <t>Zenn @ Sierra Verde</t>
+          <t>Tavalo at Avondale</t>
         </is>
       </c>
       <c r="S36" s="45" t="n">
-        <v>66</v>
-      </c>
-      <c r="T36" s="46" t="inlineStr"/>
-      <c r="U36" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V36" s="47">
+        <v>266</v>
+      </c>
+      <c r="T36" s="52" t="inlineStr"/>
+      <c r="U36" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V36" s="46">
         <f>IFERROR(VALUE(RIGHT(T36,4))*4+MATCH(LEFT(T36,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W36" s="47">
+      <c r="W36" s="46">
         <f>IF(V36="","",IF(V36&lt;=$E$4,0,MAX(1,INT((V36-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X36" s="46">
+        <f>IF(U36="None",0,IF($E$6&gt;=IF(U36="Bear",3,IF(U36="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11061,22 +11081,28 @@
       </c>
       <c r="R37" s="44" t="inlineStr">
         <is>
-          <t>The BLVD Residential District</t>
-        </is>
-      </c>
-      <c r="S37" s="45" t="n"/>
-      <c r="T37" s="46" t="inlineStr"/>
-      <c r="U37" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V37" s="47">
+          <t>Marbella Ranch East Future Phase</t>
+        </is>
+      </c>
+      <c r="S37" s="45" t="n">
+        <v>266</v>
+      </c>
+      <c r="T37" s="52" t="inlineStr"/>
+      <c r="U37" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V37" s="46">
         <f>IFERROR(VALUE(RIGHT(T37,4))*4+MATCH(LEFT(T37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W37" s="47">
+      <c r="W37" s="46">
         <f>IF(V37="","",IF(V37&lt;=$E$4,0,MAX(1,INT((V37-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X37" s="46">
+        <f>IF(U37="None",0,IF($E$6&gt;=IF(U37="Bear",3,IF(U37="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11106,22 +11132,28 @@
       </c>
       <c r="R38" s="44" t="inlineStr">
         <is>
-          <t>The BLVD Park Avenue District</t>
-        </is>
-      </c>
-      <c r="S38" s="45" t="n"/>
-      <c r="T38" s="46" t="inlineStr"/>
-      <c r="U38" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V38" s="47">
+          <t>Crystal Cove</t>
+        </is>
+      </c>
+      <c r="S38" s="45" t="n">
+        <v>260</v>
+      </c>
+      <c r="T38" s="52" t="inlineStr"/>
+      <c r="U38" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V38" s="46">
         <f>IFERROR(VALUE(RIGHT(T38,4))*4+MATCH(LEFT(T38,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W38" s="47">
+      <c r="W38" s="46">
         <f>IF(V38="","",IF(V38&lt;=$E$4,0,MAX(1,INT((V38-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X38" s="46">
+        <f>IF(U38="None",0,IF($E$6&gt;=IF(U38="Bear",3,IF(U38="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11151,22 +11183,28 @@
       </c>
       <c r="R39" s="44" t="inlineStr">
         <is>
-          <t>Globe Land Investors Development</t>
-        </is>
-      </c>
-      <c r="S39" s="45" t="n"/>
-      <c r="T39" s="46" t="inlineStr"/>
-      <c r="U39" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V39" s="47">
+          <t>Cornerstone at the Wigwam</t>
+        </is>
+      </c>
+      <c r="S39" s="45" t="n">
+        <v>212</v>
+      </c>
+      <c r="T39" s="52" t="inlineStr"/>
+      <c r="U39" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V39" s="46">
         <f>IFERROR(VALUE(RIGHT(T39,4))*4+MATCH(LEFT(T39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W39" s="47">
+      <c r="W39" s="46">
         <f>IF(V39="","",IF(V39&lt;=$E$4,0,MAX(1,INT((V39-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X39" s="46">
+        <f>IF(U39="None",0,IF($E$6&gt;=IF(U39="Bear",3,IF(U39="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11178,22 +11216,28 @@
       </c>
       <c r="R40" s="44" t="inlineStr">
         <is>
-          <t>Ball Park</t>
-        </is>
-      </c>
-      <c r="S40" s="45" t="n"/>
-      <c r="T40" s="46" t="inlineStr"/>
-      <c r="U40" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V40" s="47">
+          <t>Radia Avondale Station III</t>
+        </is>
+      </c>
+      <c r="S40" s="45" t="n">
+        <v>212</v>
+      </c>
+      <c r="T40" s="52" t="inlineStr"/>
+      <c r="U40" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V40" s="46">
         <f>IFERROR(VALUE(RIGHT(T40,4))*4+MATCH(LEFT(T40,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W40" s="47">
+      <c r="W40" s="46">
         <f>IF(V40="","",IF(V40&lt;=$E$4,0,MAX(1,INT((V40-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X40" s="46">
+        <f>IF(U40="None",0,IF($E$6&gt;=IF(U40="Bear",3,IF(U40="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11229,22 +11273,28 @@
       </c>
       <c r="R41" s="44" t="inlineStr">
         <is>
-          <t>Vision 2 Parcel A</t>
-        </is>
-      </c>
-      <c r="S41" s="45" t="n"/>
-      <c r="T41" s="46" t="inlineStr"/>
-      <c r="U41" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V41" s="47">
+          <t>Celebration Plaza Parcel A</t>
+        </is>
+      </c>
+      <c r="S41" s="45" t="n">
+        <v>181</v>
+      </c>
+      <c r="T41" s="52" t="inlineStr"/>
+      <c r="U41" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V41" s="46">
         <f>IFERROR(VALUE(RIGHT(T41,4))*4+MATCH(LEFT(T41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W41" s="47">
+      <c r="W41" s="46">
         <f>IF(V41="","",IF(V41&lt;=$E$4,0,MAX(1,INT((V41-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X41" s="46">
+        <f>IF(U41="None",0,IF($E$6&gt;=IF(U41="Bear",3,IF(U41="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11280,22 +11330,28 @@
       </c>
       <c r="R42" s="44" t="inlineStr">
         <is>
-          <t>Firststreet Verde</t>
-        </is>
-      </c>
-      <c r="S42" s="45" t="n"/>
-      <c r="T42" s="46" t="inlineStr"/>
-      <c r="U42" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V42" s="47">
+          <t>Villages at River Grove</t>
+        </is>
+      </c>
+      <c r="S42" s="45" t="n">
+        <v>180</v>
+      </c>
+      <c r="T42" s="52" t="inlineStr"/>
+      <c r="U42" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V42" s="46">
         <f>IFERROR(VALUE(RIGHT(T42,4))*4+MATCH(LEFT(T42,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W42" s="47">
+      <c r="W42" s="46">
         <f>IF(V42="","",IF(V42&lt;=$E$4,0,MAX(1,INT((V42-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X42" s="46">
+        <f>IF(U42="None",0,IF($E$6&gt;=IF(U42="Bear",3,IF(U42="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11331,422 +11387,531 @@
       </c>
       <c r="R43" s="44" t="inlineStr">
         <is>
-          <t>Goodyear Civic Square at Estrella Falls</t>
-        </is>
-      </c>
-      <c r="S43" s="45" t="n"/>
-      <c r="T43" s="46" t="inlineStr"/>
-      <c r="U43" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V43" s="47">
+          <t>District 99</t>
+        </is>
+      </c>
+      <c r="S43" s="45" t="n">
+        <v>172</v>
+      </c>
+      <c r="T43" s="52" t="inlineStr"/>
+      <c r="U43" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V43" s="46">
         <f>IFERROR(VALUE(RIGHT(T43,4))*4+MATCH(LEFT(T43,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W43" s="47">
+      <c r="W43" s="46">
         <f>IF(V43="","",IF(V43&lt;=$E$4,0,MAX(1,INT((V43-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X43" s="46">
+        <f>IF(U43="None",0,IF($E$6&gt;=IF(U43="Bear",3,IF(U43="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>Reconciliation: scheduled pipeline (Incl=Y) vs CoStar Under Construction = 1,251 units.</t>
+          <t>Reconciliation: UC pipeline scheduled = 1,947 units vs CoStar current Under Construction = 1,251 units.</t>
         </is>
       </c>
       <c r="R44" s="44" t="inlineStr">
         <is>
-          <t>I-10 Innovation Center II</t>
-        </is>
-      </c>
-      <c r="S44" s="45" t="n"/>
-      <c r="T44" s="46" t="inlineStr"/>
-      <c r="U44" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V44" s="47">
+          <t>McDowell Villas</t>
+        </is>
+      </c>
+      <c r="S44" s="45" t="n">
+        <v>164</v>
+      </c>
+      <c r="T44" s="52" t="inlineStr"/>
+      <c r="U44" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V44" s="46">
         <f>IFERROR(VALUE(RIGHT(T44,4))*4+MATCH(LEFT(T44,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W44" s="47">
+      <c r="W44" s="46">
         <f>IF(V44="","",IF(V44&lt;=$E$4,0,MAX(1,INT((V44-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X44" s="46">
+        <f>IF(U44="None",0,IF($E$6&gt;=IF(U44="Bear",3,IF(U44="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += scheduled pipeline; occupied += selected demand (capped at target). Edit yellow cells (close quarter, demand scenario/levels, pipeline dates &amp; include, rent-growth &amp; concessions).</t>
+          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
         </is>
       </c>
       <c r="R45" s="44" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel D</t>
-        </is>
-      </c>
-      <c r="S45" s="45" t="n"/>
-      <c r="T45" s="46" t="inlineStr"/>
-      <c r="U45" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V45" s="47">
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="S45" s="45" t="n">
+        <v>156</v>
+      </c>
+      <c r="T45" s="52" t="inlineStr"/>
+      <c r="U45" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V45" s="46">
         <f>IFERROR(VALUE(RIGHT(T45,4))*4+MATCH(LEFT(T45,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W45" s="47">
+      <c r="W45" s="46">
         <f>IF(V45="","",IF(V45&lt;=$E$4,0,MAX(1,INT((V45-$E$5)/4)+1)))</f>
         <v/>
       </c>
+      <c r="X45" s="46">
+        <f>IF(U45="None",0,IF($E$6&gt;=IF(U45="Bear",3,IF(U45="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
+      <c r="B46" s="33" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
+        </is>
+      </c>
       <c r="R46" s="44" t="inlineStr">
         <is>
-          <t>SimonMed Development II</t>
-        </is>
-      </c>
-      <c r="S46" s="45" t="n"/>
-      <c r="T46" s="46" t="inlineStr"/>
-      <c r="U46" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V46" s="47">
+          <t>Porter Kyle Development</t>
+        </is>
+      </c>
+      <c r="S46" s="45" t="n">
+        <v>135</v>
+      </c>
+      <c r="T46" s="52" t="inlineStr"/>
+      <c r="U46" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V46" s="46">
         <f>IFERROR(VALUE(RIGHT(T46,4))*4+MATCH(LEFT(T46,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W46" s="47">
+      <c r="W46" s="46">
         <f>IF(V46="","",IF(V46&lt;=$E$4,0,MAX(1,INT((V46-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X46" s="46">
+        <f>IF(U46="None",0,IF($E$6&gt;=IF(U46="Bear",3,IF(U46="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="R47" s="44" t="inlineStr">
         <is>
-          <t>182 South 95th Avenue</t>
-        </is>
-      </c>
-      <c r="S47" s="45" t="n"/>
-      <c r="T47" s="46" t="inlineStr"/>
-      <c r="U47" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V47" s="47">
+          <t>Ascent Goodyear</t>
+        </is>
+      </c>
+      <c r="S47" s="45" t="n">
+        <v>113</v>
+      </c>
+      <c r="T47" s="52" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U47" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V47" s="46">
         <f>IFERROR(VALUE(RIGHT(T47,4))*4+MATCH(LEFT(T47,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W47" s="47">
+      <c r="W47" s="46">
         <f>IF(V47="","",IF(V47&lt;=$E$4,0,MAX(1,INT((V47-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X47" s="46">
+        <f>IF(U47="None",0,IF($E$6&gt;=IF(U47="Bear",3,IF(U47="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="R48" s="44" t="inlineStr">
         <is>
-          <t>Envision Encore</t>
-        </is>
-      </c>
-      <c r="S48" s="45" t="n"/>
-      <c r="T48" s="46" t="inlineStr"/>
-      <c r="U48" s="46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="V48" s="47">
+          <t>Northern 107</t>
+        </is>
+      </c>
+      <c r="S48" s="45" t="n">
+        <v>74</v>
+      </c>
+      <c r="T48" s="52" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="U48" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V48" s="46">
         <f>IFERROR(VALUE(RIGHT(T48,4))*4+MATCH(LEFT(T48,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W48" s="47">
+      <c r="W48" s="46">
         <f>IF(V48="","",IF(V48&lt;=$E$4,0,MAX(1,INT((V48-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X48" s="46">
+        <f>IF(U48="None",0,IF($E$6&gt;=IF(U48="Bear",3,IF(U48="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="R49" s="44" t="inlineStr">
         <is>
-          <t>FUZE Ballpark</t>
+          <t>Zenn @ Sierra Verde</t>
         </is>
       </c>
       <c r="S49" s="45" t="n">
-        <v>321</v>
-      </c>
-      <c r="T49" s="46" t="inlineStr">
-        <is>
-          <t>Q3 2026</t>
-        </is>
-      </c>
-      <c r="U49" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V49" s="47">
+        <v>66</v>
+      </c>
+      <c r="T49" s="52" t="inlineStr"/>
+      <c r="U49" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V49" s="46">
         <f>IFERROR(VALUE(RIGHT(T49,4))*4+MATCH(LEFT(T49,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W49" s="47">
+      <c r="W49" s="46">
         <f>IF(V49="","",IF(V49&lt;=$E$4,0,MAX(1,INT((V49-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X49" s="46">
+        <f>IF(U49="None",0,IF($E$6&gt;=IF(U49="Bear",3,IF(U49="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="R50" s="44" t="inlineStr">
         <is>
-          <t>Zanjero III</t>
-        </is>
-      </c>
-      <c r="S50" s="45" t="n">
-        <v>301</v>
-      </c>
-      <c r="T50" s="46" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="U50" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V50" s="47">
+          <t>The BLVD Residential District</t>
+        </is>
+      </c>
+      <c r="S50" s="45" t="n"/>
+      <c r="T50" s="52" t="inlineStr"/>
+      <c r="U50" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V50" s="46">
         <f>IFERROR(VALUE(RIGHT(T50,4))*4+MATCH(LEFT(T50,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W50" s="47">
+      <c r="W50" s="46">
         <f>IF(V50="","",IF(V50&lt;=$E$4,0,MAX(1,INT((V50-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X50" s="46">
+        <f>IF(U50="None",0,IF($E$6&gt;=IF(U50="Bear",3,IF(U50="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="R51" s="44" t="inlineStr">
         <is>
-          <t>Pointe Grand Estrella at Phoenix</t>
-        </is>
-      </c>
-      <c r="S51" s="45" t="n">
-        <v>288</v>
-      </c>
-      <c r="T51" s="46" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="U51" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V51" s="47">
+          <t>The BLVD Park Avenue District</t>
+        </is>
+      </c>
+      <c r="S51" s="45" t="n"/>
+      <c r="T51" s="52" t="inlineStr"/>
+      <c r="U51" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V51" s="46">
         <f>IFERROR(VALUE(RIGHT(T51,4))*4+MATCH(LEFT(T51,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W51" s="47">
+      <c r="W51" s="46">
         <f>IF(V51="","",IF(V51&lt;=$E$4,0,MAX(1,INT((V51-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X51" s="46">
+        <f>IF(U51="None",0,IF($E$6&gt;=IF(U51="Bear",3,IF(U51="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="R52" s="44" t="inlineStr">
         <is>
-          <t>Yardly Algodon</t>
-        </is>
-      </c>
-      <c r="S52" s="45" t="n">
-        <v>262</v>
-      </c>
-      <c r="T52" s="46" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="U52" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V52" s="47">
+          <t>Globe Land Investors Development</t>
+        </is>
+      </c>
+      <c r="S52" s="45" t="n"/>
+      <c r="T52" s="52" t="inlineStr"/>
+      <c r="U52" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V52" s="46">
         <f>IFERROR(VALUE(RIGHT(T52,4))*4+MATCH(LEFT(T52,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W52" s="47">
+      <c r="W52" s="46">
         <f>IF(V52="","",IF(V52&lt;=$E$4,0,MAX(1,INT((V52-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X52" s="46">
+        <f>IF(U52="None",0,IF($E$6&gt;=IF(U52="Bear",3,IF(U52="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="R53" s="44" t="inlineStr">
         <is>
-          <t>Cerro Vista</t>
-        </is>
-      </c>
-      <c r="S53" s="45" t="n">
-        <v>255</v>
-      </c>
-      <c r="T53" s="46" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="U53" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V53" s="47">
+          <t>Ball Park</t>
+        </is>
+      </c>
+      <c r="S53" s="45" t="n"/>
+      <c r="T53" s="52" t="inlineStr"/>
+      <c r="U53" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V53" s="46">
         <f>IFERROR(VALUE(RIGHT(T53,4))*4+MATCH(LEFT(T53,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W53" s="47">
+      <c r="W53" s="46">
         <f>IF(V53="","",IF(V53&lt;=$E$4,0,MAX(1,INT((V53-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X53" s="46">
+        <f>IF(U53="None",0,IF($E$6&gt;=IF(U53="Bear",3,IF(U53="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="R54" s="44" t="inlineStr">
         <is>
-          <t>Marbella Ranch East I</t>
-        </is>
-      </c>
-      <c r="S54" s="45" t="n">
-        <v>144</v>
-      </c>
-      <c r="T54" s="46" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="U54" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V54" s="47">
+          <t>Vision 2 Parcel A</t>
+        </is>
+      </c>
+      <c r="S54" s="45" t="n"/>
+      <c r="T54" s="52" t="inlineStr"/>
+      <c r="U54" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V54" s="46">
         <f>IFERROR(VALUE(RIGHT(T54,4))*4+MATCH(LEFT(T54,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W54" s="47">
+      <c r="W54" s="46">
         <f>IF(V54="","",IF(V54&lt;=$E$4,0,MAX(1,INT((V54-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X54" s="46">
+        <f>IF(U54="None",0,IF($E$6&gt;=IF(U54="Bear",3,IF(U54="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="R55" s="44" t="inlineStr">
         <is>
-          <t>Zen @ Angelina</t>
-        </is>
-      </c>
-      <c r="S55" s="45" t="n">
-        <v>130</v>
-      </c>
-      <c r="T55" s="46" t="inlineStr">
-        <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="U55" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V55" s="47">
+          <t>Firststreet Verde</t>
+        </is>
+      </c>
+      <c r="S55" s="45" t="n"/>
+      <c r="T55" s="52" t="inlineStr"/>
+      <c r="U55" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V55" s="46">
         <f>IFERROR(VALUE(RIGHT(T55,4))*4+MATCH(LEFT(T55,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W55" s="47">
+      <c r="W55" s="46">
         <f>IF(V55="","",IF(V55&lt;=$E$4,0,MAX(1,INT((V55-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X55" s="46">
+        <f>IF(U55="None",0,IF($E$6&gt;=IF(U55="Bear",3,IF(U55="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="R56" s="44" t="inlineStr">
         <is>
-          <t>HARMON Ascend</t>
-        </is>
-      </c>
-      <c r="S56" s="45" t="n">
-        <v>125</v>
-      </c>
-      <c r="T56" s="46" t="inlineStr">
-        <is>
-          <t>Q1 2027</t>
-        </is>
-      </c>
-      <c r="U56" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V56" s="47">
+          <t>Goodyear Civic Square at Estrella Falls</t>
+        </is>
+      </c>
+      <c r="S56" s="45" t="n"/>
+      <c r="T56" s="52" t="inlineStr"/>
+      <c r="U56" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V56" s="46">
         <f>IFERROR(VALUE(RIGHT(T56,4))*4+MATCH(LEFT(T56,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W56" s="47">
+      <c r="W56" s="46">
         <f>IF(V56="","",IF(V56&lt;=$E$4,0,MAX(1,INT((V56-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X56" s="46">
+        <f>IF(U56="None",0,IF($E$6&gt;=IF(U56="Bear",3,IF(U56="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="R57" s="44" t="inlineStr">
         <is>
-          <t>Villages at Northern</t>
-        </is>
-      </c>
-      <c r="S57" s="45" t="n">
-        <v>74</v>
-      </c>
-      <c r="T57" s="46" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="U57" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V57" s="47">
+          <t>I-10 Innovation Center II</t>
+        </is>
+      </c>
+      <c r="S57" s="45" t="n"/>
+      <c r="T57" s="52" t="inlineStr"/>
+      <c r="U57" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V57" s="46">
         <f>IFERROR(VALUE(RIGHT(T57,4))*4+MATCH(LEFT(T57,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W57" s="47">
+      <c r="W57" s="46">
         <f>IF(V57="","",IF(V57&lt;=$E$4,0,MAX(1,INT((V57-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X57" s="46">
+        <f>IF(U57="None",0,IF($E$6&gt;=IF(U57="Bear",3,IF(U57="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="R58" s="44" t="inlineStr">
         <is>
-          <t>Prosper 47</t>
-        </is>
-      </c>
-      <c r="S58" s="45" t="n">
-        <v>47</v>
-      </c>
-      <c r="T58" s="46" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="U58" s="46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V58" s="47">
+          <t>Celebration Plaza Parcel D</t>
+        </is>
+      </c>
+      <c r="S58" s="45" t="n"/>
+      <c r="T58" s="52" t="inlineStr"/>
+      <c r="U58" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V58" s="46">
         <f>IFERROR(VALUE(RIGHT(T58,4))*4+MATCH(LEFT(T58,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
         <v/>
       </c>
-      <c r="W58" s="47">
+      <c r="W58" s="46">
         <f>IF(V58="","",IF(V58&lt;=$E$4,0,MAX(1,INT((V58-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X58" s="46">
+        <f>IF(U58="None",0,IF($E$6&gt;=IF(U58="Bear",3,IF(U58="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="R59" s="44" t="inlineStr">
+        <is>
+          <t>SimonMed Development II</t>
+        </is>
+      </c>
+      <c r="S59" s="45" t="n"/>
+      <c r="T59" s="52" t="inlineStr"/>
+      <c r="U59" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V59" s="46">
+        <f>IFERROR(VALUE(RIGHT(T59,4))*4+MATCH(LEFT(T59,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W59" s="46">
+        <f>IF(V59="","",IF(V59&lt;=$E$4,0,MAX(1,INT((V59-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X59" s="46">
+        <f>IF(U59="None",0,IF($E$6&gt;=IF(U59="Bear",3,IF(U59="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="R60" s="44" t="inlineStr">
+        <is>
+          <t>182 South 95th Avenue</t>
+        </is>
+      </c>
+      <c r="S60" s="45" t="n"/>
+      <c r="T60" s="52" t="inlineStr"/>
+      <c r="U60" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V60" s="46">
+        <f>IFERROR(VALUE(RIGHT(T60,4))*4+MATCH(LEFT(T60,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W60" s="46">
+        <f>IF(V60="","",IF(V60&lt;=$E$4,0,MAX(1,INT((V60-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X60" s="46">
+        <f>IF(U60="None",0,IF($E$6&gt;=IF(U60="Bear",3,IF(U60="Base",2,1)),1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="R61" s="44" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="S61" s="45" t="n"/>
+      <c r="T61" s="52" t="inlineStr"/>
+      <c r="U61" s="52" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="V61" s="46">
+        <f>IFERROR(VALUE(RIGHT(T61,4))*4+MATCH(LEFT(T61,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W61" s="46">
+        <f>IF(V61="","",IF(V61&lt;=$E$4,0,MAX(1,INT((V61-$E$5)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X61" s="46">
+        <f>IF(U61="None",0,IF($E$6&gt;=IF(U61="Bear",3,IF(U61="Base",2,1)),1,0))</f>
         <v/>
       </c>
     </row>
@@ -11758,8 +11923,8 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Y,N"</formula1>
+    <dataValidation sqref="U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Bear,Base,Bull,None"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -183,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -332,6 +333,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -10116,27 +10129,27 @@
         <v>2369</v>
       </c>
       <c r="J20" s="54">
-        <f>J25-I25</f>
+        <f>J29-I29</f>
         <v/>
       </c>
       <c r="K20" s="54">
-        <f>K25-J25</f>
+        <f>K29-J29</f>
         <v/>
       </c>
       <c r="L20" s="54">
-        <f>L25-K25</f>
+        <f>L29-K29</f>
         <v/>
       </c>
       <c r="M20" s="54">
-        <f>M25-L25</f>
+        <f>M29-L29</f>
         <v/>
       </c>
       <c r="N20" s="54">
-        <f>N25-M25</f>
+        <f>N29-M29</f>
         <v/>
       </c>
       <c r="O20" s="54">
-        <f>O25-N25</f>
+        <f>O29-N29</f>
         <v/>
       </c>
       <c r="R20" s="44" t="inlineStr">
@@ -10194,27 +10207,27 @@
         <v>0.849</v>
       </c>
       <c r="J21" s="56">
-        <f>IFERROR(J25/J24,0)</f>
+        <f>IFERROR(J29/J28,0)</f>
         <v/>
       </c>
       <c r="K21" s="56">
-        <f>IFERROR(K25/K24,0)</f>
+        <f>IFERROR(K29/K28,0)</f>
         <v/>
       </c>
       <c r="L21" s="56">
-        <f>IFERROR(L25/L24,0)</f>
+        <f>IFERROR(L29/L28,0)</f>
         <v/>
       </c>
       <c r="M21" s="56">
-        <f>IFERROR(M25/M24,0)</f>
+        <f>IFERROR(M29/M28,0)</f>
         <v/>
       </c>
       <c r="N21" s="56">
-        <f>IFERROR(N25/N24,0)</f>
+        <f>IFERROR(N29/N28,0)</f>
         <v/>
       </c>
       <c r="O21" s="56">
-        <f>IFERROR(O25/O24,0)</f>
+        <f>IFERROR(O29/O28,0)</f>
         <v/>
       </c>
       <c r="R21" s="44" t="inlineStr">
@@ -10321,6 +10334,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>SUBJECT (Bella Mirage)</t>
+        </is>
+      </c>
       <c r="R23" s="44" t="inlineStr">
         <is>
           <t>Picerne at Palm Valley</t>
@@ -10348,57 +10366,39 @@
         <v/>
       </c>
     </row>
-    <row r="24" hidden="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  inventory</t>
-        </is>
-      </c>
-      <c r="C24" s="57" t="n">
-        <v>12401</v>
-      </c>
-      <c r="D24" s="57" t="n">
-        <v>14261</v>
-      </c>
-      <c r="E24" s="57" t="n">
-        <v>15597</v>
-      </c>
-      <c r="F24" s="57" t="n">
-        <v>17877</v>
-      </c>
-      <c r="G24" s="57" t="n">
-        <v>20700</v>
-      </c>
-      <c r="H24" s="57" t="n">
-        <v>24743</v>
-      </c>
-      <c r="I24" s="57" t="n">
-        <v>26603</v>
-      </c>
-      <c r="J24" s="57">
-        <f>I24+J19</f>
-        <v/>
-      </c>
-      <c r="K24" s="57">
-        <f>J24+K19</f>
-        <v/>
-      </c>
-      <c r="L24" s="57">
-        <f>K24+L19</f>
-        <v/>
-      </c>
-      <c r="M24" s="57">
-        <f>L24+M19</f>
-        <v/>
-      </c>
-      <c r="N24" s="57">
-        <f>M24+N19</f>
-        <v/>
-      </c>
-      <c r="O24" s="57">
-        <f>N24+O19</f>
-        <v/>
-      </c>
+    <row r="24">
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Market Rent  (HD→CoStar)</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="n">
+        <v>1088</v>
+      </c>
+      <c r="D24" s="58" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E24" s="58" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F24" s="58" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G24" s="58" t="n">
+        <v>1497</v>
+      </c>
+      <c r="H24" s="58" t="n">
+        <v>1444</v>
+      </c>
+      <c r="I24" s="58" t="n">
+        <v>1332</v>
+      </c>
+      <c r="J24" s="59" t="n"/>
+      <c r="K24" s="59" t="n"/>
+      <c r="L24" s="59" t="n"/>
+      <c r="M24" s="59" t="n"/>
+      <c r="N24" s="59" t="n"/>
+      <c r="O24" s="59" t="n"/>
       <c r="R24" s="44" t="inlineStr">
         <is>
           <t>Liv Avondale</t>
@@ -10426,57 +10426,39 @@
         <v/>
       </c>
     </row>
-    <row r="25" hidden="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  occupied</t>
-        </is>
-      </c>
-      <c r="C25" s="57" t="n">
-        <v>11277</v>
-      </c>
-      <c r="D25" s="57" t="n">
-        <v>13152</v>
-      </c>
-      <c r="E25" s="57" t="n">
-        <v>14362</v>
-      </c>
-      <c r="F25" s="57" t="n">
-        <v>15047</v>
-      </c>
-      <c r="G25" s="57" t="n">
-        <v>17560</v>
-      </c>
-      <c r="H25" s="57" t="n">
-        <v>20215</v>
-      </c>
-      <c r="I25" s="57" t="n">
-        <v>22585</v>
-      </c>
-      <c r="J25" s="57">
-        <f>MIN($C$6*J24,I25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="K25" s="57">
-        <f>MIN($C$6*K24,J25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="L25" s="57">
-        <f>MIN($C$6*L24,K25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="M25" s="57">
-        <f>MIN($C$6*M24,L25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="N25" s="57">
-        <f>MIN($C$6*N24,M25+$C$11)</f>
-        <v/>
-      </c>
-      <c r="O25" s="57">
-        <f>MIN($C$6*O24,N25+$C$11)</f>
-        <v/>
-      </c>
+    <row r="25">
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Effective Rent</t>
+        </is>
+      </c>
+      <c r="C25" s="58" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D25" s="58" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E25" s="58" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F25" s="58" t="n">
+        <v>1555</v>
+      </c>
+      <c r="G25" s="58" t="n">
+        <v>1402</v>
+      </c>
+      <c r="H25" s="58" t="n">
+        <v>1369</v>
+      </c>
+      <c r="I25" s="58" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J25" s="59" t="n"/>
+      <c r="K25" s="59" t="n"/>
+      <c r="L25" s="59" t="n"/>
+      <c r="M25" s="59" t="n"/>
+      <c r="N25" s="59" t="n"/>
+      <c r="O25" s="59" t="n"/>
       <c r="R25" s="44" t="inlineStr">
         <is>
           <t>Urban 95 Parcel A</t>
@@ -10505,6 +10487,32 @@
       </c>
     </row>
     <row r="26">
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Occupancy (T12 financials)</t>
+        </is>
+      </c>
+      <c r="C26" s="60" t="n"/>
+      <c r="D26" s="60" t="n"/>
+      <c r="E26" s="60" t="n"/>
+      <c r="F26" s="60" t="n">
+        <v>0.8788971182681028</v>
+      </c>
+      <c r="G26" s="60" t="n">
+        <v>0.9173713229249606</v>
+      </c>
+      <c r="H26" s="60" t="n">
+        <v>0.9334854638634199</v>
+      </c>
+      <c r="I26" s="60" t="n">
+        <v>0.9206643232607364</v>
+      </c>
+      <c r="J26" s="61" t="n"/>
+      <c r="K26" s="61" t="n"/>
+      <c r="L26" s="61" t="n"/>
+      <c r="M26" s="61" t="n"/>
+      <c r="N26" s="61" t="n"/>
+      <c r="O26" s="61" t="n"/>
       <c r="R26" s="44" t="inlineStr">
         <is>
           <t>The Waverly</t>
@@ -10537,41 +10545,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="40" t="inlineStr">
-        <is>
-          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
-        </is>
-      </c>
-      <c r="J27" s="58" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K27" s="58" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L27" s="58" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M27" s="58" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N27" s="58" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O27" s="58" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
       <c r="R27" s="44" t="inlineStr">
         <is>
           <t>Fuze 623</t>
@@ -10599,34 +10572,55 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="40" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J28" s="59">
-        <f>MIN($C$6,($C$12+$C$8*1)/J24)</f>
-        <v/>
-      </c>
-      <c r="K28" s="59">
-        <f>MIN($C$6,($C$12+$C$8*2)/K24)</f>
-        <v/>
-      </c>
-      <c r="L28" s="59">
-        <f>MIN($C$6,($C$12+$C$8*3)/L24)</f>
-        <v/>
-      </c>
-      <c r="M28" s="59">
-        <f>MIN($C$6,($C$12+$C$8*4)/M24)</f>
-        <v/>
-      </c>
-      <c r="N28" s="59">
-        <f>MIN($C$6,($C$12+$C$8*5)/N24)</f>
-        <v/>
-      </c>
-      <c r="O28" s="59">
-        <f>MIN($C$6,($C$12+$C$8*6)/O24)</f>
+    <row r="28" hidden="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  inventory</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="n">
+        <v>12401</v>
+      </c>
+      <c r="D28" s="57" t="n">
+        <v>14261</v>
+      </c>
+      <c r="E28" s="57" t="n">
+        <v>15597</v>
+      </c>
+      <c r="F28" s="57" t="n">
+        <v>17877</v>
+      </c>
+      <c r="G28" s="57" t="n">
+        <v>20700</v>
+      </c>
+      <c r="H28" s="57" t="n">
+        <v>24743</v>
+      </c>
+      <c r="I28" s="57" t="n">
+        <v>26603</v>
+      </c>
+      <c r="J28" s="57">
+        <f>I28+J19</f>
+        <v/>
+      </c>
+      <c r="K28" s="57">
+        <f>J28+K19</f>
+        <v/>
+      </c>
+      <c r="L28" s="57">
+        <f>K28+L19</f>
+        <v/>
+      </c>
+      <c r="M28" s="57">
+        <f>L28+M19</f>
+        <v/>
+      </c>
+      <c r="N28" s="57">
+        <f>M28+N19</f>
+        <v/>
+      </c>
+      <c r="O28" s="57">
+        <f>N28+O19</f>
         <v/>
       </c>
       <c r="R28" s="44" t="inlineStr">
@@ -10656,34 +10650,55 @@
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="40" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J29" s="59">
-        <f>MIN($C$6,($C$12+$C$9*1)/J24)</f>
-        <v/>
-      </c>
-      <c r="K29" s="59">
-        <f>MIN($C$6,($C$12+$C$9*2)/K24)</f>
-        <v/>
-      </c>
-      <c r="L29" s="59">
-        <f>MIN($C$6,($C$12+$C$9*3)/L24)</f>
-        <v/>
-      </c>
-      <c r="M29" s="59">
-        <f>MIN($C$6,($C$12+$C$9*4)/M24)</f>
-        <v/>
-      </c>
-      <c r="N29" s="59">
-        <f>MIN($C$6,($C$12+$C$9*5)/N24)</f>
-        <v/>
-      </c>
-      <c r="O29" s="59">
-        <f>MIN($C$6,($C$12+$C$9*6)/O24)</f>
+    <row r="29" hidden="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  occupied</t>
+        </is>
+      </c>
+      <c r="C29" s="57" t="n">
+        <v>11277</v>
+      </c>
+      <c r="D29" s="57" t="n">
+        <v>13152</v>
+      </c>
+      <c r="E29" s="57" t="n">
+        <v>14362</v>
+      </c>
+      <c r="F29" s="57" t="n">
+        <v>15047</v>
+      </c>
+      <c r="G29" s="57" t="n">
+        <v>17560</v>
+      </c>
+      <c r="H29" s="57" t="n">
+        <v>20215</v>
+      </c>
+      <c r="I29" s="57" t="n">
+        <v>22585</v>
+      </c>
+      <c r="J29" s="57">
+        <f>MIN($C$6*J28,I29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="K29" s="57">
+        <f>MIN($C$6*K28,J29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="L29" s="57">
+        <f>MIN($C$6*L28,K29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="M29" s="57">
+        <f>MIN($C$6*M28,L29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="N29" s="57">
+        <f>MIN($C$6*N28,M29+$C$11)</f>
+        <v/>
+      </c>
+      <c r="O29" s="57">
+        <f>MIN($C$6*O28,N29+$C$11)</f>
         <v/>
       </c>
       <c r="R29" s="44" t="inlineStr">
@@ -10714,35 +10729,6 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="40" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J30" s="59">
-        <f>MIN($C$6,($C$12+$C$10*1)/J24)</f>
-        <v/>
-      </c>
-      <c r="K30" s="59">
-        <f>MIN($C$6,($C$12+$C$10*2)/K24)</f>
-        <v/>
-      </c>
-      <c r="L30" s="59">
-        <f>MIN($C$6,($C$12+$C$10*3)/L24)</f>
-        <v/>
-      </c>
-      <c r="M30" s="59">
-        <f>MIN($C$6,($C$12+$C$10*4)/M24)</f>
-        <v/>
-      </c>
-      <c r="N30" s="59">
-        <f>MIN($C$6,($C$12+$C$10*5)/N24)</f>
-        <v/>
-      </c>
-      <c r="O30" s="59">
-        <f>MIN($C$6,($C$12+$C$10*6)/O24)</f>
-        <v/>
-      </c>
       <c r="R30" s="44" t="inlineStr">
         <is>
           <t>Sanctuair at Centerscape</t>
@@ -10771,6 +10757,41 @@
       </c>
     </row>
     <row r="31">
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
+        </is>
+      </c>
+      <c r="J31" s="62" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K31" s="62" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L31" s="62" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M31" s="62" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N31" s="62" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O31" s="62" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
       <c r="R31" s="44" t="inlineStr">
         <is>
           <t>Encore Avondale</t>
@@ -10805,38 +10826,32 @@
     <row r="32">
       <c r="B32" s="40" t="inlineStr">
         <is>
-          <t>MARKET RENT GROWTH (editable assumptions)</t>
-        </is>
-      </c>
-      <c r="J32" s="60" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K32" s="60" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L32" s="60" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M32" s="60" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N32" s="60" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O32" s="60" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J32" s="63">
+        <f>MIN($C$6,($C$12+$C$8*1)/J28)</f>
+        <v/>
+      </c>
+      <c r="K32" s="63">
+        <f>MIN($C$6,($C$12+$C$8*2)/K28)</f>
+        <v/>
+      </c>
+      <c r="L32" s="63">
+        <f>MIN($C$6,($C$12+$C$8*3)/L28)</f>
+        <v/>
+      </c>
+      <c r="M32" s="63">
+        <f>MIN($C$6,($C$12+$C$8*4)/M28)</f>
+        <v/>
+      </c>
+      <c r="N32" s="63">
+        <f>MIN($C$6,($C$12+$C$8*5)/N28)</f>
+        <v/>
+      </c>
+      <c r="O32" s="63">
+        <f>MIN($C$6,($C$12+$C$8*6)/O28)</f>
+        <v/>
       </c>
       <c r="R32" s="44" t="inlineStr">
         <is>
@@ -10868,26 +10883,32 @@
     <row r="33">
       <c r="B33" s="40" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J33" s="61" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="K33" s="61" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="L33" s="61" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M33" s="61" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="N33" s="61" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O33" s="61" t="n">
-        <v>0.0175</v>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J33" s="63">
+        <f>MIN($C$6,($C$12+$C$9*1)/J28)</f>
+        <v/>
+      </c>
+      <c r="K33" s="63">
+        <f>MIN($C$6,($C$12+$C$9*2)/K28)</f>
+        <v/>
+      </c>
+      <c r="L33" s="63">
+        <f>MIN($C$6,($C$12+$C$9*3)/L28)</f>
+        <v/>
+      </c>
+      <c r="M33" s="63">
+        <f>MIN($C$6,($C$12+$C$9*4)/M28)</f>
+        <v/>
+      </c>
+      <c r="N33" s="63">
+        <f>MIN($C$6,($C$12+$C$9*5)/N28)</f>
+        <v/>
+      </c>
+      <c r="O33" s="63">
+        <f>MIN($C$6,($C$12+$C$9*6)/O28)</f>
+        <v/>
       </c>
       <c r="R33" s="44" t="inlineStr">
         <is>
@@ -10919,26 +10940,32 @@
     <row r="34">
       <c r="B34" s="40" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J34" s="61" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K34" s="61" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L34" s="61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M34" s="61" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N34" s="61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O34" s="61" t="n">
-        <v>0.03</v>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J34" s="63">
+        <f>MIN($C$6,($C$12+$C$10*1)/J28)</f>
+        <v/>
+      </c>
+      <c r="K34" s="63">
+        <f>MIN($C$6,($C$12+$C$10*2)/K28)</f>
+        <v/>
+      </c>
+      <c r="L34" s="63">
+        <f>MIN($C$6,($C$12+$C$10*3)/L28)</f>
+        <v/>
+      </c>
+      <c r="M34" s="63">
+        <f>MIN($C$6,($C$12+$C$10*4)/M28)</f>
+        <v/>
+      </c>
+      <c r="N34" s="63">
+        <f>MIN($C$6,($C$12+$C$10*5)/N28)</f>
+        <v/>
+      </c>
+      <c r="O34" s="63">
+        <f>MIN($C$6,($C$12+$C$10*6)/O28)</f>
+        <v/>
       </c>
       <c r="R34" s="44" t="inlineStr">
         <is>
@@ -10972,29 +10999,6 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="40" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J35" s="61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K35" s="61" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L35" s="61" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M35" s="61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N35" s="61" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O35" s="61" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R35" s="44" t="inlineStr">
         <is>
           <t>Orion Avondale</t>
@@ -11025,7 +11029,37 @@
     <row r="36">
       <c r="B36" s="40" t="inlineStr">
         <is>
-          <t>CONCESSIONS (months, editable)</t>
+          <t>MARKET RENT GROWTH (editable assumptions)</t>
+        </is>
+      </c>
+      <c r="J36" s="64" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K36" s="64" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L36" s="64" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M36" s="64" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N36" s="64" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O36" s="64" t="inlineStr">
+        <is>
+          <t>Y6</t>
         </is>
       </c>
       <c r="R36" s="44" t="inlineStr">
@@ -11061,23 +11095,23 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="J37" s="61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K37" s="61" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L37" s="61" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="M37" s="61" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="N37" s="61" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O37" s="61" t="n">
-        <v>0.035</v>
+      <c r="J37" s="65" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K37" s="65" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="L37" s="65" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M37" s="65" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="N37" s="65" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O37" s="65" t="n">
+        <v>0.0175</v>
       </c>
       <c r="R37" s="44" t="inlineStr">
         <is>
@@ -11112,23 +11146,23 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="J38" s="61" t="n">
+      <c r="J38" s="65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K38" s="65" t="n">
         <v>0.03</v>
       </c>
-      <c r="K38" s="61" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L38" s="61" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M38" s="61" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N38" s="61" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O38" s="61" t="n">
-        <v>0.005</v>
+      <c r="L38" s="65" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M38" s="65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N38" s="65" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O38" s="65" t="n">
+        <v>0.03</v>
       </c>
       <c r="R38" s="44" t="inlineStr">
         <is>
@@ -11163,23 +11197,23 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="J39" s="61" t="n">
+      <c r="J39" s="65" t="n">
         <v>0.02</v>
       </c>
-      <c r="K39" s="61" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L39" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="61" t="n">
-        <v>0</v>
+      <c r="K39" s="65" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L39" s="65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M39" s="65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N39" s="65" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O39" s="65" t="n">
+        <v>0.04</v>
       </c>
       <c r="R39" s="44" t="inlineStr">
         <is>
@@ -11211,7 +11245,7 @@
     <row r="40">
       <c r="B40" s="40" t="inlineStr">
         <is>
-          <t>EFFECTIVE RENT GROWTH (derived)</t>
+          <t>CONCESSIONS (months, editable)</t>
         </is>
       </c>
       <c r="R40" s="44" t="inlineStr">
@@ -11247,29 +11281,23 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="J41" s="59">
-        <f>(1+J33)*(1-J37)-1</f>
-        <v/>
-      </c>
-      <c r="K41" s="59">
-        <f>(1+K33)*(1-K37)/(1-J37)-1</f>
-        <v/>
-      </c>
-      <c r="L41" s="59">
-        <f>(1+L33)*(1-L37)/(1-K37)-1</f>
-        <v/>
-      </c>
-      <c r="M41" s="59">
-        <f>(1+M33)*(1-M37)/(1-L37)-1</f>
-        <v/>
-      </c>
-      <c r="N41" s="59">
-        <f>(1+N33)*(1-N37)/(1-M37)-1</f>
-        <v/>
-      </c>
-      <c r="O41" s="59">
-        <f>(1+O33)*(1-O37)/(1-N37)-1</f>
-        <v/>
+      <c r="J41" s="65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K41" s="65" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L41" s="65" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M41" s="65" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N41" s="65" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O41" s="65" t="n">
+        <v>0.035</v>
       </c>
       <c r="R41" s="44" t="inlineStr">
         <is>
@@ -11304,29 +11332,23 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="J42" s="59">
-        <f>(1+J34)*(1-J38)-1</f>
-        <v/>
-      </c>
-      <c r="K42" s="59">
-        <f>(1+K34)*(1-K38)/(1-J38)-1</f>
-        <v/>
-      </c>
-      <c r="L42" s="59">
-        <f>(1+L34)*(1-L38)/(1-K38)-1</f>
-        <v/>
-      </c>
-      <c r="M42" s="59">
-        <f>(1+M34)*(1-M38)/(1-L38)-1</f>
-        <v/>
-      </c>
-      <c r="N42" s="59">
-        <f>(1+N34)*(1-N38)/(1-M38)-1</f>
-        <v/>
-      </c>
-      <c r="O42" s="59">
-        <f>(1+O34)*(1-O38)/(1-N38)-1</f>
-        <v/>
+      <c r="J42" s="65" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K42" s="65" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L42" s="65" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M42" s="65" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N42" s="65" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O42" s="65" t="n">
+        <v>0.005</v>
       </c>
       <c r="R42" s="44" t="inlineStr">
         <is>
@@ -11361,29 +11383,23 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="J43" s="59">
-        <f>(1+J35)*(1-J39)-1</f>
-        <v/>
-      </c>
-      <c r="K43" s="59">
-        <f>(1+K35)*(1-K39)/(1-J39)-1</f>
-        <v/>
-      </c>
-      <c r="L43" s="59">
-        <f>(1+L35)*(1-L39)/(1-K39)-1</f>
-        <v/>
-      </c>
-      <c r="M43" s="59">
-        <f>(1+M35)*(1-M39)/(1-L39)-1</f>
-        <v/>
-      </c>
-      <c r="N43" s="59">
-        <f>(1+N35)*(1-N39)/(1-M39)-1</f>
-        <v/>
-      </c>
-      <c r="O43" s="59">
-        <f>(1+O35)*(1-O39)/(1-N39)-1</f>
-        <v/>
+      <c r="J43" s="65" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K43" s="65" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L43" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="65" t="n">
+        <v>0</v>
       </c>
       <c r="R43" s="44" t="inlineStr">
         <is>
@@ -11413,9 +11429,9 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="33" t="inlineStr">
-        <is>
-          <t>Reconciliation: UC pipeline scheduled = 1,947 units vs CoStar current Under Construction = 1,251 units.</t>
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
       <c r="R44" s="44" t="inlineStr">
@@ -11446,10 +11462,34 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="33" t="inlineStr">
-        <is>
-          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
-        </is>
+      <c r="B45" s="40" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J45" s="63">
+        <f>(1+J37)*(1-J41)-1</f>
+        <v/>
+      </c>
+      <c r="K45" s="63">
+        <f>(1+K37)*(1-K41)/(1-J41)-1</f>
+        <v/>
+      </c>
+      <c r="L45" s="63">
+        <f>(1+L37)*(1-L41)/(1-K41)-1</f>
+        <v/>
+      </c>
+      <c r="M45" s="63">
+        <f>(1+M37)*(1-M41)/(1-L41)-1</f>
+        <v/>
+      </c>
+      <c r="N45" s="63">
+        <f>(1+N37)*(1-N41)/(1-M41)-1</f>
+        <v/>
+      </c>
+      <c r="O45" s="63">
+        <f>(1+O37)*(1-O41)/(1-N41)-1</f>
+        <v/>
       </c>
       <c r="R45" s="44" t="inlineStr">
         <is>
@@ -11479,10 +11519,34 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="33" t="inlineStr">
-        <is>
-          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
-        </is>
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J46" s="63">
+        <f>(1+J38)*(1-J42)-1</f>
+        <v/>
+      </c>
+      <c r="K46" s="63">
+        <f>(1+K38)*(1-K42)/(1-J42)-1</f>
+        <v/>
+      </c>
+      <c r="L46" s="63">
+        <f>(1+L38)*(1-L42)/(1-K42)-1</f>
+        <v/>
+      </c>
+      <c r="M46" s="63">
+        <f>(1+M38)*(1-M42)/(1-L42)-1</f>
+        <v/>
+      </c>
+      <c r="N46" s="63">
+        <f>(1+N38)*(1-N42)/(1-M42)-1</f>
+        <v/>
+      </c>
+      <c r="O46" s="63">
+        <f>(1+O38)*(1-O42)/(1-N42)-1</f>
+        <v/>
       </c>
       <c r="R46" s="44" t="inlineStr">
         <is>
@@ -11512,6 +11576,35 @@
       </c>
     </row>
     <row r="47">
+      <c r="B47" s="40" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J47" s="63">
+        <f>(1+J39)*(1-J43)-1</f>
+        <v/>
+      </c>
+      <c r="K47" s="63">
+        <f>(1+K39)*(1-K43)/(1-J43)-1</f>
+        <v/>
+      </c>
+      <c r="L47" s="63">
+        <f>(1+L39)*(1-L43)/(1-K43)-1</f>
+        <v/>
+      </c>
+      <c r="M47" s="63">
+        <f>(1+M39)*(1-M43)/(1-L43)-1</f>
+        <v/>
+      </c>
+      <c r="N47" s="63">
+        <f>(1+N39)*(1-N43)/(1-M43)-1</f>
+        <v/>
+      </c>
+      <c r="O47" s="63">
+        <f>(1+O39)*(1-O43)/(1-N43)-1</f>
+        <v/>
+      </c>
       <c r="R47" s="44" t="inlineStr">
         <is>
           <t>Ascent Goodyear</t>
@@ -11544,6 +11637,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="B48" s="33" t="inlineStr">
+        <is>
+          <t>Reconciliation: UC pipeline scheduled = 1,947 units vs CoStar current Under Construction = 1,251 units.</t>
+        </is>
+      </c>
       <c r="R48" s="44" t="inlineStr">
         <is>
           <t>Northern 107</t>
@@ -11576,6 +11674,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="B49" s="33" t="inlineStr">
+        <is>
+          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
+        </is>
+      </c>
       <c r="R49" s="44" t="inlineStr">
         <is>
           <t>Zenn @ Sierra Verde</t>
@@ -11604,6 +11707,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
+        </is>
+      </c>
       <c r="R50" s="44" t="inlineStr">
         <is>
           <t>The BLVD Residential District</t>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Competitive Analysis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Supply &amp; Absorption" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reconciliation Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Supply &amp; Absorption" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,18 +68,24 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
       <sz val="8"/>
     </font>
     <font>
@@ -184,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -275,22 +280,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -302,13 +300,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -326,10 +327,10 @@
     <xf numFmtId="3" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -339,6 +340,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -353,10 +361,15 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -751,9 +764,10 @@
           <t>2022–2026 New Construction  |  5-mile radius  |  As of 2026 Q2 QTD  |  Stabilization Target:</t>
         </is>
       </c>
-      <c r="G3" s="3">
-        <f>TEXT(Settings!$B$2,"0%")&amp;" target"</f>
-        <v/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>95% target</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -4955,36 +4969,2671 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="B1:Z61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9.5" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="9.5" customWidth="1" min="7" max="7"/>
+    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9.5" customWidth="1" min="9" max="9"/>
+    <col width="9.5" customWidth="1" min="10" max="10"/>
+    <col width="9.5" customWidth="1" min="11" max="11"/>
+    <col width="9.5" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="9.5" customWidth="1" min="14" max="14"/>
+    <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="8" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="7" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="6" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
-        <is>
-          <t>ANALYSIS SETTINGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Stabilized Occupancy Target</t>
-        </is>
-      </c>
-      <c r="B2" s="35" t="n">
+      <c r="Z1" t="n">
+        <v>8105</v>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>SUPPLY &amp; ABSORPTION  —  5-MILE MARKET (relative-year / TTM)</t>
+        </is>
+      </c>
+      <c r="Z2">
+        <f>IFERROR(VALUE(RIGHT($C$5,4))*4+MATCH(LEFT($C$5,2),{"Q1","Q2","Q3","Q4"},0)-1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="R3" s="34" t="inlineStr">
+        <is>
+          <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
+        </is>
+      </c>
+      <c r="Z3">
+        <f>IF($C$7="Bear",3,IF($C$7="Base",2,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="35" t="inlineStr">
+        <is>
+          <t>As-of Quarter</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="R4" s="37" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S4" s="37" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T4" s="37" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Close Quarter (Y1 start)</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>Q4 2026</t>
+        </is>
+      </c>
+      <c r="R5" s="39">
+        <f>'Competitive Analysis'!C69</f>
+        <v/>
+      </c>
+      <c r="S5" s="40">
+        <f>'Competitive Analysis'!D69</f>
+        <v/>
+      </c>
+      <c r="T5" s="41">
+        <f>'Competitive Analysis'!E69</f>
+        <v/>
+      </c>
+      <c r="V5">
+        <f>IFERROR(VALUE(RIGHT(T5,4))*4+MATCH(LEFT(T5,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W5">
+        <f>IF(V5="","",IF(V5&lt;=$Z$1,0,MAX(1,INT((V5-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>Stabilization Target</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="n">
         <v>0.95</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Target occupancy for absorption calculation</t>
-        </is>
+      <c r="R6" s="39">
+        <f>'Competitive Analysis'!C60</f>
+        <v/>
+      </c>
+      <c r="S6" s="40">
+        <f>'Competitive Analysis'!D60</f>
+        <v/>
+      </c>
+      <c r="T6" s="41">
+        <f>'Competitive Analysis'!E60</f>
+        <v/>
+      </c>
+      <c r="V6">
+        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W6">
+        <f>IF(V6="","",IF(V6&lt;=$Z$1,0,MAX(1,INT((V6-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>Demand Scenario</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="R7" s="39">
+        <f>'Competitive Analysis'!C64</f>
+        <v/>
+      </c>
+      <c r="S7" s="40">
+        <f>'Competitive Analysis'!D64</f>
+        <v/>
+      </c>
+      <c r="T7" s="41">
+        <f>'Competitive Analysis'!E64</f>
+        <v/>
+      </c>
+      <c r="V7">
+        <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W7">
+        <f>IF(V7="","",IF(V7&lt;=$Z$1,0,MAX(1,INT((V7-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Bear Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>1250</v>
+      </c>
+      <c r="R8" s="39">
+        <f>'Competitive Analysis'!C62</f>
+        <v/>
+      </c>
+      <c r="S8" s="40">
+        <f>'Competitive Analysis'!D62</f>
+        <v/>
+      </c>
+      <c r="T8" s="41">
+        <f>'Competitive Analysis'!E62</f>
+        <v/>
+      </c>
+      <c r="V8">
+        <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W8">
+        <f>IF(V8="","",IF(V8&lt;=$Z$1,0,MAX(1,INT((V8-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Base Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>2525</v>
+      </c>
+      <c r="R9" s="39">
+        <f>'Competitive Analysis'!C63</f>
+        <v/>
+      </c>
+      <c r="S9" s="40">
+        <f>'Competitive Analysis'!D63</f>
+        <v/>
+      </c>
+      <c r="T9" s="41">
+        <f>'Competitive Analysis'!E63</f>
+        <v/>
+      </c>
+      <c r="V9">
+        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W9">
+        <f>IF(V9="","",IF(V9&lt;=$Z$1,0,MAX(1,INT((V9-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Bull Annual Absorption</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>3800</v>
+      </c>
+      <c r="R10" s="39">
+        <f>'Competitive Analysis'!C65</f>
+        <v/>
+      </c>
+      <c r="S10" s="40">
+        <f>'Competitive Analysis'!D65</f>
+        <v/>
+      </c>
+      <c r="T10" s="41">
+        <f>'Competitive Analysis'!E65</f>
+        <v/>
+      </c>
+      <c r="V10">
+        <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W10">
+        <f>IF(V10="","",IF(V10&lt;=$Z$1,0,MAX(1,INT((V10-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Selected Annual Demand</t>
+        </is>
+      </c>
+      <c r="C11" s="44">
+        <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
+        <v/>
+      </c>
+      <c r="R11" s="39">
+        <f>'Competitive Analysis'!C61</f>
+        <v/>
+      </c>
+      <c r="S11" s="40">
+        <f>'Competitive Analysis'!D61</f>
+        <v/>
+      </c>
+      <c r="T11" s="41">
+        <f>'Competitive Analysis'!E61</f>
+        <v/>
+      </c>
+      <c r="V11">
+        <f>IFERROR(VALUE(RIGHT(T11,4))*4+MATCH(LEFT(T11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W11">
+        <f>IF(V11="","",IF(V11&lt;=$Z$1,0,MAX(1,INT((V11-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>UC scheduled vs CoStar UC</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>1,947 / 1,251</t>
+        </is>
+      </c>
+      <c r="R12" s="39">
+        <f>'Competitive Analysis'!C68</f>
+        <v/>
+      </c>
+      <c r="S12" s="40">
+        <f>'Competitive Analysis'!D68</f>
+        <v/>
+      </c>
+      <c r="T12" s="41">
+        <f>'Competitive Analysis'!E68</f>
+        <v/>
+      </c>
+      <c r="V12">
+        <f>IFERROR(VALUE(RIGHT(T12,4))*4+MATCH(LEFT(T12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W12">
+        <f>IF(V12="","",IF(V12&lt;=$Z$1,0,MAX(1,INT((V12-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Subject rent source</t>
+        </is>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>HelloData → CoStar</t>
+        </is>
+      </c>
+      <c r="R13" s="39">
+        <f>'Competitive Analysis'!C66</f>
+        <v/>
+      </c>
+      <c r="S13" s="40">
+        <f>'Competitive Analysis'!D66</f>
+        <v/>
+      </c>
+      <c r="T13" s="41">
+        <f>'Competitive Analysis'!E66</f>
+        <v/>
+      </c>
+      <c r="V13">
+        <f>IFERROR(VALUE(RIGHT(T13,4))*4+MATCH(LEFT(T13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W13">
+        <f>IF(V13="","",IF(V13&lt;=$Z$1,0,MAX(1,INT((V13-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="R14" s="39">
+        <f>'Competitive Analysis'!C67</f>
+        <v/>
+      </c>
+      <c r="S14" s="40">
+        <f>'Competitive Analysis'!D67</f>
+        <v/>
+      </c>
+      <c r="T14" s="41">
+        <f>'Competitive Analysis'!E67</f>
+        <v/>
+      </c>
+      <c r="V14">
+        <f>IFERROR(VALUE(RIGHT(T14,4))*4+MATCH(LEFT(T14,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W14">
+        <f>IF(V14="","",IF(V14&lt;=$Z$1,0,MAX(1,INT((V14-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="R16" s="34" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>5-MILE MARKET</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>-Y6</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>-Y5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>-Y4</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>-Y3</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>-Y2</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>-Y1</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Y0</t>
+        </is>
+      </c>
+      <c r="J17" s="46" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K17" s="46" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L17" s="46" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M17" s="46" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N17" s="46" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O17" s="46" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="R17" s="37" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S17" s="37" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T17" s="37" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U17" s="37" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2019–Q2 2020</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2020–Q2 2021</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2021–Q2 2022</t>
+        </is>
+      </c>
+      <c r="F18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2022–Q2 2023</t>
+        </is>
+      </c>
+      <c r="G18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2023–Q2 2024</t>
+        </is>
+      </c>
+      <c r="H18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2024–Q2 2025</t>
+        </is>
+      </c>
+      <c r="I18" s="47" t="inlineStr">
+        <is>
+          <t>Q3 2025–Q2 2026</t>
+        </is>
+      </c>
+      <c r="J18" s="47" t="inlineStr">
+        <is>
+          <t>Hold Yr 1</t>
+        </is>
+      </c>
+      <c r="K18" s="47" t="inlineStr">
+        <is>
+          <t>Hold Yr 2</t>
+        </is>
+      </c>
+      <c r="L18" s="47" t="inlineStr">
+        <is>
+          <t>Hold Yr 3</t>
+        </is>
+      </c>
+      <c r="M18" s="47" t="inlineStr">
+        <is>
+          <t>Hold Yr 4</t>
+        </is>
+      </c>
+      <c r="N18" s="47" t="inlineStr">
+        <is>
+          <t>Hold Yr 5</t>
+        </is>
+      </c>
+      <c r="O18" s="47" t="inlineStr">
+        <is>
+          <t>Hold Yr 6</t>
+        </is>
+      </c>
+      <c r="R18" s="39" t="inlineStr">
+        <is>
+          <t>Sheely Center Future Phase</t>
+        </is>
+      </c>
+      <c r="S18" s="40" t="n">
+        <v>697</v>
+      </c>
+      <c r="T18" s="48" t="inlineStr"/>
+      <c r="U18" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V18">
+        <f>IFERROR(VALUE(RIGHT(T18,4))*4+MATCH(LEFT(T18,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W18">
+        <f>IF(V18="","",IF(V18&lt;=$Z$1,0,MAX(1,INT((V18-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>IF(U18="All",1,IF(U18="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U18="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>NEW SUPPLY (5-mi)</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E19" s="49" t="n">
+        <v>1336</v>
+      </c>
+      <c r="F19" s="49" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G19" s="49" t="n">
+        <v>2823</v>
+      </c>
+      <c r="H19" s="49" t="n">
+        <v>4043</v>
+      </c>
+      <c r="I19" s="49" t="n">
+        <v>1860</v>
+      </c>
+      <c r="J19" s="50">
+        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,1)+SUMIFS($S$18:$S$61,$W$18:$W$61,1,$X$18:$X$61,1)</f>
+        <v/>
+      </c>
+      <c r="K19" s="50">
+        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,2)+SUMIFS($S$18:$S$61,$W$18:$W$61,2,$X$18:$X$61,1)</f>
+        <v/>
+      </c>
+      <c r="L19" s="50">
+        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,3)+SUMIFS($S$18:$S$61,$W$18:$W$61,3,$X$18:$X$61,1)</f>
+        <v/>
+      </c>
+      <c r="M19" s="50">
+        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,4)+SUMIFS($S$18:$S$61,$W$18:$W$61,4,$X$18:$X$61,1)</f>
+        <v/>
+      </c>
+      <c r="N19" s="50">
+        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,5)+SUMIFS($S$18:$S$61,$W$18:$W$61,5,$X$18:$X$61,1)</f>
+        <v/>
+      </c>
+      <c r="O19" s="50">
+        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,6)+SUMIFS($S$18:$S$61,$W$18:$W$61,6,$X$18:$X$61,1)</f>
+        <v/>
+      </c>
+      <c r="R19" s="39" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel C</t>
+        </is>
+      </c>
+      <c r="S19" s="40" t="n">
+        <v>500</v>
+      </c>
+      <c r="T19" s="48" t="inlineStr"/>
+      <c r="U19" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V19">
+        <f>IFERROR(VALUE(RIGHT(T19,4))*4+MATCH(LEFT(T19,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W19">
+        <f>IF(V19="","",IF(V19&lt;=$Z$1,0,MAX(1,INT((V19-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>IF(U19="All",1,IF(U19="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U19="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>ABSORPTION (5-mi)</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n">
+        <v>719</v>
+      </c>
+      <c r="D20" s="49" t="n">
+        <v>1876</v>
+      </c>
+      <c r="E20" s="49" t="n">
+        <v>1210</v>
+      </c>
+      <c r="F20" s="49" t="n">
+        <v>685</v>
+      </c>
+      <c r="G20" s="49" t="n">
+        <v>2514</v>
+      </c>
+      <c r="H20" s="49" t="n">
+        <v>2655</v>
+      </c>
+      <c r="I20" s="49" t="n">
+        <v>2369</v>
+      </c>
+      <c r="J20" s="50">
+        <f>J31-I31</f>
+        <v/>
+      </c>
+      <c r="K20" s="50">
+        <f>K31-J31</f>
+        <v/>
+      </c>
+      <c r="L20" s="50">
+        <f>L31-K31</f>
+        <v/>
+      </c>
+      <c r="M20" s="50">
+        <f>M31-L31</f>
+        <v/>
+      </c>
+      <c r="N20" s="50">
+        <f>N31-M31</f>
+        <v/>
+      </c>
+      <c r="O20" s="50">
+        <f>O31-N31</f>
+        <v/>
+      </c>
+      <c r="R20" s="39" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel B</t>
+        </is>
+      </c>
+      <c r="S20" s="40" t="n">
+        <v>478</v>
+      </c>
+      <c r="T20" s="48" t="inlineStr"/>
+      <c r="U20" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V20">
+        <f>IFERROR(VALUE(RIGHT(T20,4))*4+MATCH(LEFT(T20,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W20">
+        <f>IF(V20="","",IF(V20&lt;=$Z$1,0,MAX(1,INT((V20-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>IF(U20="All",1,IF(U20="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U20="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>OCCUPANCY (5-mi)</t>
+        </is>
+      </c>
+      <c r="C21" s="51" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D21" s="51" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="E21" s="51" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="F21" s="51" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="G21" s="51" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="H21" s="51" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="I21" s="51" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="J21" s="52">
+        <f>IFERROR(J31/J30,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="52">
+        <f>IFERROR(K31/K30,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="52">
+        <f>IFERROR(L31/L30,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="52">
+        <f>IFERROR(M31/M30,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="52">
+        <f>IFERROR(N31/N30,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="52">
+        <f>IFERROR(O31/O30,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="39" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel B</t>
+        </is>
+      </c>
+      <c r="S21" s="40" t="n">
+        <v>410</v>
+      </c>
+      <c r="T21" s="48" t="inlineStr"/>
+      <c r="U21" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V21">
+        <f>IFERROR(VALUE(RIGHT(T21,4))*4+MATCH(LEFT(T21,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W21">
+        <f>IF(V21="","",IF(V21&lt;=$Z$1,0,MAX(1,INT((V21-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>IF(U21="All",1,IF(U21="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U21="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>CUM. UNABSORBED (since -Y3)</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="53">
+        <f>F22+G19-G20</f>
+        <v/>
+      </c>
+      <c r="H22" s="53">
+        <f>G22+H19-H20</f>
+        <v/>
+      </c>
+      <c r="I22" s="53">
+        <f>H22+I19-I20</f>
+        <v/>
+      </c>
+      <c r="J22" s="53">
+        <f>I22+J19-J20</f>
+        <v/>
+      </c>
+      <c r="K22" s="53">
+        <f>J22+K19-K20</f>
+        <v/>
+      </c>
+      <c r="L22" s="53">
+        <f>K22+L19-L20</f>
+        <v/>
+      </c>
+      <c r="M22" s="53">
+        <f>L22+M19-M20</f>
+        <v/>
+      </c>
+      <c r="N22" s="53">
+        <f>M22+N19-N20</f>
+        <v/>
+      </c>
+      <c r="O22" s="53">
+        <f>N22+O19-O20</f>
+        <v/>
+      </c>
+      <c r="R22" s="39" t="inlineStr">
+        <is>
+          <t>The District at Westgate</t>
+        </is>
+      </c>
+      <c r="S22" s="40" t="n">
+        <v>384</v>
+      </c>
+      <c r="T22" s="48" t="inlineStr"/>
+      <c r="U22" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V22">
+        <f>IFERROR(VALUE(RIGHT(T22,4))*4+MATCH(LEFT(T22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W22">
+        <f>IF(V22="","",IF(V22&lt;=$Z$1,0,MAX(1,INT((V22-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>IF(U22="All",1,IF(U22="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U22="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>SUBJECT (Bella Mirage)</t>
+        </is>
+      </c>
+      <c r="R23" s="39" t="inlineStr">
+        <is>
+          <t>Picerne at Palm Valley</t>
+        </is>
+      </c>
+      <c r="S23" s="40" t="n">
+        <v>383</v>
+      </c>
+      <c r="T23" s="48" t="inlineStr"/>
+      <c r="U23" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V23">
+        <f>IFERROR(VALUE(RIGHT(T23,4))*4+MATCH(LEFT(T23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W23">
+        <f>IF(V23="","",IF(V23&lt;=$Z$1,0,MAX(1,INT((V23-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>IF(U23="All",1,IF(U23="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U23="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
+        </is>
+      </c>
+      <c r="C24" s="54" t="n">
+        <v>1088</v>
+      </c>
+      <c r="D24" s="54" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E24" s="54" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F24" s="54" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>1497</v>
+      </c>
+      <c r="H24" s="54" t="n">
+        <v>1444</v>
+      </c>
+      <c r="I24" s="54" t="n">
+        <v>1332</v>
+      </c>
+      <c r="J24" s="55" t="n"/>
+      <c r="K24" s="55" t="n"/>
+      <c r="L24" s="55" t="n"/>
+      <c r="M24" s="55" t="n"/>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="R24" s="39" t="inlineStr">
+        <is>
+          <t>Liv Avondale</t>
+        </is>
+      </c>
+      <c r="S24" s="40" t="n">
+        <v>333</v>
+      </c>
+      <c r="T24" s="48" t="inlineStr"/>
+      <c r="U24" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V24">
+        <f>IFERROR(VALUE(RIGHT(T24,4))*4+MATCH(LEFT(T24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W24">
+        <f>IF(V24="","",IF(V24&lt;=$Z$1,0,MAX(1,INT((V24-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>IF(U24="All",1,IF(U24="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U24="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Market Rent YoY %</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="57">
+        <f>IFERROR(D24/C24-1,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="57">
+        <f>IFERROR(E24/D24-1,"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="57">
+        <f>IFERROR(F24/E24-1,"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="57">
+        <f>IFERROR(G24/F24-1,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="57">
+        <f>IFERROR(H24/G24-1,"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="57">
+        <f>IFERROR(I24/H24-1,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="58" t="n"/>
+      <c r="K25" s="58" t="n"/>
+      <c r="L25" s="58" t="n"/>
+      <c r="M25" s="58" t="n"/>
+      <c r="N25" s="58" t="n"/>
+      <c r="O25" s="58" t="n"/>
+      <c r="R25" s="39" t="inlineStr">
+        <is>
+          <t>Urban 95 Parcel A</t>
+        </is>
+      </c>
+      <c r="S25" s="40" t="n">
+        <v>324</v>
+      </c>
+      <c r="T25" s="48" t="inlineStr"/>
+      <c r="U25" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V25">
+        <f>IFERROR(VALUE(RIGHT(T25,4))*4+MATCH(LEFT(T25,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W25">
+        <f>IF(V25="","",IF(V25&lt;=$Z$1,0,MAX(1,INT((V25-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>IF(U25="All",1,IF(U25="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U25="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Effective Rent</t>
+        </is>
+      </c>
+      <c r="C26" s="54" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D26" s="54" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E26" s="54" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F26" s="54" t="n">
+        <v>1555</v>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>1402</v>
+      </c>
+      <c r="H26" s="54" t="n">
+        <v>1369</v>
+      </c>
+      <c r="I26" s="54" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J26" s="55" t="n"/>
+      <c r="K26" s="55" t="n"/>
+      <c r="L26" s="55" t="n"/>
+      <c r="M26" s="55" t="n"/>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="R26" s="39" t="inlineStr">
+        <is>
+          <t>The Waverly</t>
+        </is>
+      </c>
+      <c r="S26" s="40" t="n">
+        <v>323</v>
+      </c>
+      <c r="T26" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U26" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V26">
+        <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W26">
+        <f>IF(V26="","",IF(V26&lt;=$Z$1,0,MAX(1,INT((V26-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>IF(U26="All",1,IF(U26="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U26="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Effective Rent YoY %</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="n"/>
+      <c r="D27" s="57">
+        <f>IFERROR(D26/C26-1,"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="57">
+        <f>IFERROR(E26/D26-1,"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="57">
+        <f>IFERROR(F26/E26-1,"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="57">
+        <f>IFERROR(G26/F26-1,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="57">
+        <f>IFERROR(H26/G26-1,"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="57">
+        <f>IFERROR(I26/H26-1,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="58" t="n"/>
+      <c r="K27" s="58" t="n"/>
+      <c r="L27" s="58" t="n"/>
+      <c r="M27" s="58" t="n"/>
+      <c r="N27" s="58" t="n"/>
+      <c r="O27" s="58" t="n"/>
+      <c r="R27" s="39" t="inlineStr">
+        <is>
+          <t>Fuze 623</t>
+        </is>
+      </c>
+      <c r="S27" s="40" t="n">
+        <v>321</v>
+      </c>
+      <c r="T27" s="48" t="inlineStr"/>
+      <c r="U27" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V27">
+        <f>IFERROR(VALUE(RIGHT(T27,4))*4+MATCH(LEFT(T27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W27">
+        <f>IF(V27="","",IF(V27&lt;=$Z$1,0,MAX(1,INT((V27-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>IF(U27="All",1,IF(U27="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U27="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
+        </is>
+      </c>
+      <c r="C28" s="59" t="n">
+        <v>0.9503496503496502</v>
+      </c>
+      <c r="D28" s="59" t="n">
+        <v>0.957692307692308</v>
+      </c>
+      <c r="E28" s="59" t="n">
+        <v>0.9458041958041957</v>
+      </c>
+      <c r="F28" s="59" t="n">
+        <v>0.8788971182681028</v>
+      </c>
+      <c r="G28" s="59" t="n">
+        <v>0.9173713229249606</v>
+      </c>
+      <c r="H28" s="59" t="n">
+        <v>0.9334854638634199</v>
+      </c>
+      <c r="I28" s="59" t="n">
+        <v>0.9206643232607364</v>
+      </c>
+      <c r="J28" s="60" t="n"/>
+      <c r="K28" s="60" t="n"/>
+      <c r="L28" s="60" t="n"/>
+      <c r="M28" s="60" t="n"/>
+      <c r="N28" s="60" t="n"/>
+      <c r="O28" s="60" t="n"/>
+      <c r="R28" s="39" t="inlineStr">
+        <is>
+          <t>Anton Glendale</t>
+        </is>
+      </c>
+      <c r="S28" s="40" t="n">
+        <v>320</v>
+      </c>
+      <c r="T28" s="48" t="inlineStr"/>
+      <c r="U28" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V28">
+        <f>IFERROR(VALUE(RIGHT(T28,4))*4+MATCH(LEFT(T28,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W28">
+        <f>IF(V28="","",IF(V28&lt;=$Z$1,0,MAX(1,INT((V28-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>IF(U28="All",1,IF(U28="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U28="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="R29" s="39" t="inlineStr">
+        <is>
+          <t>Western Garden II</t>
+        </is>
+      </c>
+      <c r="S29" s="40" t="n">
+        <v>314</v>
+      </c>
+      <c r="T29" s="48" t="inlineStr"/>
+      <c r="U29" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V29">
+        <f>IFERROR(VALUE(RIGHT(T29,4))*4+MATCH(LEFT(T29,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W29">
+        <f>IF(V29="","",IF(V29&lt;=$Z$1,0,MAX(1,INT((V29-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>IF(U29="All",1,IF(U29="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U29="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" hidden="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  inventory</t>
+        </is>
+      </c>
+      <c r="C30" s="53" t="n">
+        <v>12401</v>
+      </c>
+      <c r="D30" s="53" t="n">
+        <v>14261</v>
+      </c>
+      <c r="E30" s="53" t="n">
+        <v>15597</v>
+      </c>
+      <c r="F30" s="53" t="n">
+        <v>17877</v>
+      </c>
+      <c r="G30" s="53" t="n">
+        <v>20700</v>
+      </c>
+      <c r="H30" s="53" t="n">
+        <v>24743</v>
+      </c>
+      <c r="I30" s="53" t="n">
+        <v>26603</v>
+      </c>
+      <c r="J30" s="53">
+        <f>I30+J19</f>
+        <v/>
+      </c>
+      <c r="K30" s="53">
+        <f>J30+K19</f>
+        <v/>
+      </c>
+      <c r="L30" s="53">
+        <f>K30+L19</f>
+        <v/>
+      </c>
+      <c r="M30" s="53">
+        <f>L30+M19</f>
+        <v/>
+      </c>
+      <c r="N30" s="53">
+        <f>M30+N19</f>
+        <v/>
+      </c>
+      <c r="O30" s="53">
+        <f>N30+O19</f>
+        <v/>
+      </c>
+      <c r="R30" s="39" t="inlineStr">
+        <is>
+          <t>Sanctuair at Centerscape</t>
+        </is>
+      </c>
+      <c r="S30" s="40" t="n">
+        <v>303</v>
+      </c>
+      <c r="T30" s="48" t="inlineStr"/>
+      <c r="U30" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V30">
+        <f>IFERROR(VALUE(RIGHT(T30,4))*4+MATCH(LEFT(T30,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W30">
+        <f>IF(V30="","",IF(V30&lt;=$Z$1,0,MAX(1,INT((V30-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>IF(U30="All",1,IF(U30="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U30="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" hidden="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  occupied</t>
+        </is>
+      </c>
+      <c r="C31" s="53" t="n">
+        <v>11277</v>
+      </c>
+      <c r="D31" s="53" t="n">
+        <v>13152</v>
+      </c>
+      <c r="E31" s="53" t="n">
+        <v>14362</v>
+      </c>
+      <c r="F31" s="53" t="n">
+        <v>15047</v>
+      </c>
+      <c r="G31" s="53" t="n">
+        <v>17560</v>
+      </c>
+      <c r="H31" s="53" t="n">
+        <v>20215</v>
+      </c>
+      <c r="I31" s="53" t="n">
+        <v>22585</v>
+      </c>
+      <c r="J31" s="53">
+        <f>MIN($C$6*J30,I31+$C$11)</f>
+        <v/>
+      </c>
+      <c r="K31" s="53">
+        <f>MIN($C$6*K30,J31+$C$11)</f>
+        <v/>
+      </c>
+      <c r="L31" s="53">
+        <f>MIN($C$6*L30,K31+$C$11)</f>
+        <v/>
+      </c>
+      <c r="M31" s="53">
+        <f>MIN($C$6*M30,L31+$C$11)</f>
+        <v/>
+      </c>
+      <c r="N31" s="53">
+        <f>MIN($C$6*N30,M31+$C$11)</f>
+        <v/>
+      </c>
+      <c r="O31" s="53">
+        <f>MIN($C$6*O30,N31+$C$11)</f>
+        <v/>
+      </c>
+      <c r="R31" s="39" t="inlineStr">
+        <is>
+          <t>Encore Avondale</t>
+        </is>
+      </c>
+      <c r="S31" s="40" t="n">
+        <v>300</v>
+      </c>
+      <c r="T31" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U31" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V31">
+        <f>IFERROR(VALUE(RIGHT(T31,4))*4+MATCH(LEFT(T31,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W31">
+        <f>IF(V31="","",IF(V31&lt;=$Z$1,0,MAX(1,INT((V31-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>IF(U31="All",1,IF(U31="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U31="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="R32" s="39" t="inlineStr">
+        <is>
+          <t>Banyan Avondale</t>
+        </is>
+      </c>
+      <c r="S32" s="40" t="n">
+        <v>296</v>
+      </c>
+      <c r="T32" s="48" t="inlineStr"/>
+      <c r="U32" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V32">
+        <f>IFERROR(VALUE(RIGHT(T32,4))*4+MATCH(LEFT(T32,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W32">
+        <f>IF(V32="","",IF(V32&lt;=$Z$1,0,MAX(1,INT((V32-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>IF(U32="All",1,IF(U32="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U32="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
+        </is>
+      </c>
+      <c r="J33" s="61" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K33" s="61" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L33" s="61" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M33" s="61" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N33" s="61" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O33" s="61" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="R33" s="39" t="inlineStr">
+        <is>
+          <t>Rosilian Villas</t>
+        </is>
+      </c>
+      <c r="S33" s="40" t="n">
+        <v>291</v>
+      </c>
+      <c r="T33" s="48" t="inlineStr"/>
+      <c r="U33" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V33">
+        <f>IFERROR(VALUE(RIGHT(T33,4))*4+MATCH(LEFT(T33,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W33">
+        <f>IF(V33="","",IF(V33&lt;=$Z$1,0,MAX(1,INT((V33-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>IF(U33="All",1,IF(U33="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U33="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="35" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J34" s="62">
+        <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
+        <v/>
+      </c>
+      <c r="K34" s="62">
+        <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
+        <v/>
+      </c>
+      <c r="L34" s="62">
+        <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
+        <v/>
+      </c>
+      <c r="M34" s="62">
+        <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
+        <v/>
+      </c>
+      <c r="N34" s="62">
+        <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
+        <v/>
+      </c>
+      <c r="O34" s="62">
+        <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
+        <v/>
+      </c>
+      <c r="R34" s="39" t="inlineStr">
+        <is>
+          <t>The Statler at Estrella Parkway</t>
+        </is>
+      </c>
+      <c r="S34" s="40" t="n">
+        <v>284</v>
+      </c>
+      <c r="T34" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U34" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V34">
+        <f>IFERROR(VALUE(RIGHT(T34,4))*4+MATCH(LEFT(T34,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W34">
+        <f>IF(V34="","",IF(V34&lt;=$Z$1,0,MAX(1,INT((V34-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>IF(U34="All",1,IF(U34="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U34="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="35" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J35" s="62">
+        <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
+        <v/>
+      </c>
+      <c r="K35" s="62">
+        <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
+        <v/>
+      </c>
+      <c r="L35" s="62">
+        <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
+        <v/>
+      </c>
+      <c r="M35" s="62">
+        <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
+        <v/>
+      </c>
+      <c r="N35" s="62">
+        <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
+        <v/>
+      </c>
+      <c r="O35" s="62">
+        <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
+        <v/>
+      </c>
+      <c r="R35" s="39" t="inlineStr">
+        <is>
+          <t>Orion Avondale</t>
+        </is>
+      </c>
+      <c r="S35" s="40" t="n">
+        <v>268</v>
+      </c>
+      <c r="T35" s="48" t="inlineStr"/>
+      <c r="U35" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V35">
+        <f>IFERROR(VALUE(RIGHT(T35,4))*4+MATCH(LEFT(T35,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W35">
+        <f>IF(V35="","",IF(V35&lt;=$Z$1,0,MAX(1,INT((V35-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>IF(U35="All",1,IF(U35="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U35="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="35" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J36" s="62">
+        <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
+        <v/>
+      </c>
+      <c r="K36" s="62">
+        <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
+        <v/>
+      </c>
+      <c r="L36" s="62">
+        <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
+        <v/>
+      </c>
+      <c r="M36" s="62">
+        <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
+        <v/>
+      </c>
+      <c r="N36" s="62">
+        <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
+        <v/>
+      </c>
+      <c r="O36" s="62">
+        <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
+        <v/>
+      </c>
+      <c r="R36" s="39" t="inlineStr">
+        <is>
+          <t>Tavalo at Avondale</t>
+        </is>
+      </c>
+      <c r="S36" s="40" t="n">
+        <v>266</v>
+      </c>
+      <c r="T36" s="48" t="inlineStr"/>
+      <c r="U36" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V36">
+        <f>IFERROR(VALUE(RIGHT(T36,4))*4+MATCH(LEFT(T36,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W36">
+        <f>IF(V36="","",IF(V36&lt;=$Z$1,0,MAX(1,INT((V36-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X36">
+        <f>IF(U36="All",1,IF(U36="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U36="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="R37" s="39" t="inlineStr">
+        <is>
+          <t>Marbella Ranch East Future Phase</t>
+        </is>
+      </c>
+      <c r="S37" s="40" t="n">
+        <v>266</v>
+      </c>
+      <c r="T37" s="48" t="inlineStr"/>
+      <c r="U37" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V37">
+        <f>IFERROR(VALUE(RIGHT(T37,4))*4+MATCH(LEFT(T37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W37">
+        <f>IF(V37="","",IF(V37&lt;=$Z$1,0,MAX(1,INT((V37-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X37">
+        <f>IF(U37="All",1,IF(U37="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U37="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>MARKET RENT GROWTH (editable assumptions)</t>
+        </is>
+      </c>
+      <c r="J38" s="63" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K38" s="63" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L38" s="63" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M38" s="63" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N38" s="63" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O38" s="63" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="R38" s="39" t="inlineStr">
+        <is>
+          <t>Crystal Cove</t>
+        </is>
+      </c>
+      <c r="S38" s="40" t="n">
+        <v>260</v>
+      </c>
+      <c r="T38" s="48" t="inlineStr"/>
+      <c r="U38" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V38">
+        <f>IFERROR(VALUE(RIGHT(T38,4))*4+MATCH(LEFT(T38,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W38">
+        <f>IF(V38="","",IF(V38&lt;=$Z$1,0,MAX(1,INT((V38-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X38">
+        <f>IF(U38="All",1,IF(U38="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U38="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J39" s="64" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K39" s="64" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="L39" s="64" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M39" s="64" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="N39" s="64" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O39" s="64" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="R39" s="39" t="inlineStr">
+        <is>
+          <t>Cornerstone at the Wigwam</t>
+        </is>
+      </c>
+      <c r="S39" s="40" t="n">
+        <v>212</v>
+      </c>
+      <c r="T39" s="48" t="inlineStr"/>
+      <c r="U39" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V39">
+        <f>IFERROR(VALUE(RIGHT(T39,4))*4+MATCH(LEFT(T39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W39">
+        <f>IF(V39="","",IF(V39&lt;=$Z$1,0,MAX(1,INT((V39-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X39">
+        <f>IF(U39="All",1,IF(U39="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U39="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J40" s="64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K40" s="64" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L40" s="64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M40" s="64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N40" s="64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O40" s="64" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R40" s="39" t="inlineStr">
+        <is>
+          <t>Radia Avondale Station III</t>
+        </is>
+      </c>
+      <c r="S40" s="40" t="n">
+        <v>212</v>
+      </c>
+      <c r="T40" s="48" t="inlineStr"/>
+      <c r="U40" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V40">
+        <f>IFERROR(VALUE(RIGHT(T40,4))*4+MATCH(LEFT(T40,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W40">
+        <f>IF(V40="","",IF(V40&lt;=$Z$1,0,MAX(1,INT((V40-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X40">
+        <f>IF(U40="All",1,IF(U40="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U40="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J41" s="64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K41" s="64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L41" s="64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M41" s="64" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N41" s="64" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O41" s="64" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R41" s="39" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel A</t>
+        </is>
+      </c>
+      <c r="S41" s="40" t="n">
+        <v>181</v>
+      </c>
+      <c r="T41" s="48" t="inlineStr"/>
+      <c r="U41" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V41">
+        <f>IFERROR(VALUE(RIGHT(T41,4))*4+MATCH(LEFT(T41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W41">
+        <f>IF(V41="","",IF(V41&lt;=$Z$1,0,MAX(1,INT((V41-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X41">
+        <f>IF(U41="All",1,IF(U41="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U41="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="35" t="inlineStr">
+        <is>
+          <t>CONCESSIONS (months, editable)</t>
+        </is>
+      </c>
+      <c r="R42" s="39" t="inlineStr">
+        <is>
+          <t>Villages at River Grove</t>
+        </is>
+      </c>
+      <c r="S42" s="40" t="n">
+        <v>180</v>
+      </c>
+      <c r="T42" s="48" t="inlineStr"/>
+      <c r="U42" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V42">
+        <f>IFERROR(VALUE(RIGHT(T42,4))*4+MATCH(LEFT(T42,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W42">
+        <f>IF(V42="","",IF(V42&lt;=$Z$1,0,MAX(1,INT((V42-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X42">
+        <f>IF(U42="All",1,IF(U42="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U42="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J43" s="64" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K43" s="64" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L43" s="64" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M43" s="64" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N43" s="64" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O43" s="64" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="R43" s="39" t="inlineStr">
+        <is>
+          <t>District 99</t>
+        </is>
+      </c>
+      <c r="S43" s="40" t="n">
+        <v>172</v>
+      </c>
+      <c r="T43" s="48" t="inlineStr"/>
+      <c r="U43" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V43">
+        <f>IFERROR(VALUE(RIGHT(T43,4))*4+MATCH(LEFT(T43,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W43">
+        <f>IF(V43="","",IF(V43&lt;=$Z$1,0,MAX(1,INT((V43-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>IF(U43="All",1,IF(U43="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U43="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J44" s="64" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K44" s="64" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L44" s="64" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M44" s="64" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N44" s="64" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O44" s="64" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="R44" s="39" t="inlineStr">
+        <is>
+          <t>McDowell Villas</t>
+        </is>
+      </c>
+      <c r="S44" s="40" t="n">
+        <v>164</v>
+      </c>
+      <c r="T44" s="48" t="inlineStr"/>
+      <c r="U44" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V44">
+        <f>IFERROR(VALUE(RIGHT(T44,4))*4+MATCH(LEFT(T44,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W44">
+        <f>IF(V44="","",IF(V44&lt;=$Z$1,0,MAX(1,INT((V44-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X44">
+        <f>IF(U44="All",1,IF(U44="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U44="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J45" s="64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K45" s="64" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L45" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="39" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="S45" s="40" t="n">
+        <v>156</v>
+      </c>
+      <c r="T45" s="48" t="inlineStr"/>
+      <c r="U45" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V45">
+        <f>IFERROR(VALUE(RIGHT(T45,4))*4+MATCH(LEFT(T45,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W45">
+        <f>IF(V45="","",IF(V45&lt;=$Z$1,0,MAX(1,INT((V45-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>IF(U45="All",1,IF(U45="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U45="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>EFFECTIVE RENT GROWTH (derived)</t>
+        </is>
+      </c>
+      <c r="R46" s="39" t="inlineStr">
+        <is>
+          <t>Porter Kyle Development</t>
+        </is>
+      </c>
+      <c r="S46" s="40" t="n">
+        <v>135</v>
+      </c>
+      <c r="T46" s="48" t="inlineStr"/>
+      <c r="U46" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V46">
+        <f>IFERROR(VALUE(RIGHT(T46,4))*4+MATCH(LEFT(T46,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W46">
+        <f>IF(V46="","",IF(V46&lt;=$Z$1,0,MAX(1,INT((V46-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>IF(U46="All",1,IF(U46="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U46="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J47" s="62">
+        <f>(1+J39)*(1-J43)-1</f>
+        <v/>
+      </c>
+      <c r="K47" s="62">
+        <f>(1+K39)*(1-K43)/(1-J43)-1</f>
+        <v/>
+      </c>
+      <c r="L47" s="62">
+        <f>(1+L39)*(1-L43)/(1-K43)-1</f>
+        <v/>
+      </c>
+      <c r="M47" s="62">
+        <f>(1+M39)*(1-M43)/(1-L43)-1</f>
+        <v/>
+      </c>
+      <c r="N47" s="62">
+        <f>(1+N39)*(1-N43)/(1-M43)-1</f>
+        <v/>
+      </c>
+      <c r="O47" s="62">
+        <f>(1+O39)*(1-O43)/(1-N43)-1</f>
+        <v/>
+      </c>
+      <c r="R47" s="39" t="inlineStr">
+        <is>
+          <t>Ascent Goodyear</t>
+        </is>
+      </c>
+      <c r="S47" s="40" t="n">
+        <v>113</v>
+      </c>
+      <c r="T47" s="48" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U47" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V47">
+        <f>IFERROR(VALUE(RIGHT(T47,4))*4+MATCH(LEFT(T47,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W47">
+        <f>IF(V47="","",IF(V47&lt;=$Z$1,0,MAX(1,INT((V47-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X47">
+        <f>IF(U47="All",1,IF(U47="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U47="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="35" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J48" s="62">
+        <f>(1+J40)*(1-J44)-1</f>
+        <v/>
+      </c>
+      <c r="K48" s="62">
+        <f>(1+K40)*(1-K44)/(1-J44)-1</f>
+        <v/>
+      </c>
+      <c r="L48" s="62">
+        <f>(1+L40)*(1-L44)/(1-K44)-1</f>
+        <v/>
+      </c>
+      <c r="M48" s="62">
+        <f>(1+M40)*(1-M44)/(1-L44)-1</f>
+        <v/>
+      </c>
+      <c r="N48" s="62">
+        <f>(1+N40)*(1-N44)/(1-M44)-1</f>
+        <v/>
+      </c>
+      <c r="O48" s="62">
+        <f>(1+O40)*(1-O44)/(1-N44)-1</f>
+        <v/>
+      </c>
+      <c r="R48" s="39" t="inlineStr">
+        <is>
+          <t>Northern 107</t>
+        </is>
+      </c>
+      <c r="S48" s="40" t="n">
+        <v>74</v>
+      </c>
+      <c r="T48" s="48" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="U48" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V48">
+        <f>IFERROR(VALUE(RIGHT(T48,4))*4+MATCH(LEFT(T48,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W48">
+        <f>IF(V48="","",IF(V48&lt;=$Z$1,0,MAX(1,INT((V48-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X48">
+        <f>IF(U48="All",1,IF(U48="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U48="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="35" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J49" s="62">
+        <f>(1+J41)*(1-J45)-1</f>
+        <v/>
+      </c>
+      <c r="K49" s="62">
+        <f>(1+K41)*(1-K45)/(1-J45)-1</f>
+        <v/>
+      </c>
+      <c r="L49" s="62">
+        <f>(1+L41)*(1-L45)/(1-K45)-1</f>
+        <v/>
+      </c>
+      <c r="M49" s="62">
+        <f>(1+M41)*(1-M45)/(1-L45)-1</f>
+        <v/>
+      </c>
+      <c r="N49" s="62">
+        <f>(1+N41)*(1-N45)/(1-M45)-1</f>
+        <v/>
+      </c>
+      <c r="O49" s="62">
+        <f>(1+O41)*(1-O45)/(1-N45)-1</f>
+        <v/>
+      </c>
+      <c r="R49" s="39" t="inlineStr">
+        <is>
+          <t>Zenn @ Sierra Verde</t>
+        </is>
+      </c>
+      <c r="S49" s="40" t="n">
+        <v>66</v>
+      </c>
+      <c r="T49" s="48" t="inlineStr"/>
+      <c r="U49" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V49">
+        <f>IFERROR(VALUE(RIGHT(T49,4))*4+MATCH(LEFT(T49,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W49">
+        <f>IF(V49="","",IF(V49&lt;=$Z$1,0,MAX(1,INT((V49-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X49">
+        <f>IF(U49="All",1,IF(U49="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U49="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>Reconciliation: UC pipeline scheduled = 1,947 units vs CoStar current Under Construction = 1,251 units.</t>
+        </is>
+      </c>
+      <c r="R50" s="39" t="inlineStr">
+        <is>
+          <t>The BLVD Residential District</t>
+        </is>
+      </c>
+      <c r="S50" s="40" t="n"/>
+      <c r="T50" s="48" t="inlineStr"/>
+      <c r="U50" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V50">
+        <f>IFERROR(VALUE(RIGHT(T50,4))*4+MATCH(LEFT(T50,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W50">
+        <f>IF(V50="","",IF(V50&lt;=$Z$1,0,MAX(1,INT((V50-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X50">
+        <f>IF(U50="All",1,IF(U50="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U50="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
+        </is>
+      </c>
+      <c r="R51" s="39" t="inlineStr">
+        <is>
+          <t>The BLVD Park Avenue District</t>
+        </is>
+      </c>
+      <c r="S51" s="40" t="n"/>
+      <c r="T51" s="48" t="inlineStr"/>
+      <c r="U51" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V51">
+        <f>IFERROR(VALUE(RIGHT(T51,4))*4+MATCH(LEFT(T51,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W51">
+        <f>IF(V51="","",IF(V51&lt;=$Z$1,0,MAX(1,INT((V51-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X51">
+        <f>IF(U51="All",1,IF(U51="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U51="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
+        </is>
+      </c>
+      <c r="R52" s="39" t="inlineStr">
+        <is>
+          <t>Globe Land Investors Development</t>
+        </is>
+      </c>
+      <c r="S52" s="40" t="n"/>
+      <c r="T52" s="48" t="inlineStr"/>
+      <c r="U52" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V52">
+        <f>IFERROR(VALUE(RIGHT(T52,4))*4+MATCH(LEFT(T52,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W52">
+        <f>IF(V52="","",IF(V52&lt;=$Z$1,0,MAX(1,INT((V52-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X52">
+        <f>IF(U52="All",1,IF(U52="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U52="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="R53" s="39" t="inlineStr">
+        <is>
+          <t>Ball Park</t>
+        </is>
+      </c>
+      <c r="S53" s="40" t="n"/>
+      <c r="T53" s="48" t="inlineStr"/>
+      <c r="U53" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V53">
+        <f>IFERROR(VALUE(RIGHT(T53,4))*4+MATCH(LEFT(T53,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W53">
+        <f>IF(V53="","",IF(V53&lt;=$Z$1,0,MAX(1,INT((V53-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X53">
+        <f>IF(U53="All",1,IF(U53="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U53="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="R54" s="39" t="inlineStr">
+        <is>
+          <t>Vision 2 Parcel A</t>
+        </is>
+      </c>
+      <c r="S54" s="40" t="n"/>
+      <c r="T54" s="48" t="inlineStr"/>
+      <c r="U54" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V54">
+        <f>IFERROR(VALUE(RIGHT(T54,4))*4+MATCH(LEFT(T54,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W54">
+        <f>IF(V54="","",IF(V54&lt;=$Z$1,0,MAX(1,INT((V54-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X54">
+        <f>IF(U54="All",1,IF(U54="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U54="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="R55" s="39" t="inlineStr">
+        <is>
+          <t>Firststreet Verde</t>
+        </is>
+      </c>
+      <c r="S55" s="40" t="n"/>
+      <c r="T55" s="48" t="inlineStr"/>
+      <c r="U55" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V55">
+        <f>IFERROR(VALUE(RIGHT(T55,4))*4+MATCH(LEFT(T55,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W55">
+        <f>IF(V55="","",IF(V55&lt;=$Z$1,0,MAX(1,INT((V55-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X55">
+        <f>IF(U55="All",1,IF(U55="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U55="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="R56" s="39" t="inlineStr">
+        <is>
+          <t>Goodyear Civic Square at Estrella Falls</t>
+        </is>
+      </c>
+      <c r="S56" s="40" t="n"/>
+      <c r="T56" s="48" t="inlineStr"/>
+      <c r="U56" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V56">
+        <f>IFERROR(VALUE(RIGHT(T56,4))*4+MATCH(LEFT(T56,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W56">
+        <f>IF(V56="","",IF(V56&lt;=$Z$1,0,MAX(1,INT((V56-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X56">
+        <f>IF(U56="All",1,IF(U56="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U56="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="R57" s="39" t="inlineStr">
+        <is>
+          <t>I-10 Innovation Center II</t>
+        </is>
+      </c>
+      <c r="S57" s="40" t="n"/>
+      <c r="T57" s="48" t="inlineStr"/>
+      <c r="U57" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V57">
+        <f>IFERROR(VALUE(RIGHT(T57,4))*4+MATCH(LEFT(T57,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W57">
+        <f>IF(V57="","",IF(V57&lt;=$Z$1,0,MAX(1,INT((V57-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X57">
+        <f>IF(U57="All",1,IF(U57="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U57="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="R58" s="39" t="inlineStr">
+        <is>
+          <t>Celebration Plaza Parcel D</t>
+        </is>
+      </c>
+      <c r="S58" s="40" t="n"/>
+      <c r="T58" s="48" t="inlineStr"/>
+      <c r="U58" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V58">
+        <f>IFERROR(VALUE(RIGHT(T58,4))*4+MATCH(LEFT(T58,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W58">
+        <f>IF(V58="","",IF(V58&lt;=$Z$1,0,MAX(1,INT((V58-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X58">
+        <f>IF(U58="All",1,IF(U58="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U58="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="R59" s="39" t="inlineStr">
+        <is>
+          <t>SimonMed Development II</t>
+        </is>
+      </c>
+      <c r="S59" s="40" t="n"/>
+      <c r="T59" s="48" t="inlineStr"/>
+      <c r="U59" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V59">
+        <f>IFERROR(VALUE(RIGHT(T59,4))*4+MATCH(LEFT(T59,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W59">
+        <f>IF(V59="","",IF(V59&lt;=$Z$1,0,MAX(1,INT((V59-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X59">
+        <f>IF(U59="All",1,IF(U59="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U59="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="R60" s="39" t="inlineStr">
+        <is>
+          <t>182 South 95th Avenue</t>
+        </is>
+      </c>
+      <c r="S60" s="40" t="n"/>
+      <c r="T60" s="48" t="inlineStr"/>
+      <c r="U60" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V60">
+        <f>IFERROR(VALUE(RIGHT(T60,4))*4+MATCH(LEFT(T60,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W60">
+        <f>IF(V60="","",IF(V60&lt;=$Z$1,0,MAX(1,INT((V60-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X60">
+        <f>IF(U60="All",1,IF(U60="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U60="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="R61" s="39" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="S61" s="40" t="n"/>
+      <c r="T61" s="48" t="inlineStr"/>
+      <c r="U61" s="48" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V61">
+        <f>IFERROR(VALUE(RIGHT(T61,4))*4+MATCH(LEFT(T61,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W61">
+        <f>IF(V61="","",IF(V61&lt;=$Z$1,0,MAX(1,INT((V61-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X61">
+        <f>IF(U61="All",1,IF(U61="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U61="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:O2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Bear,Base,Bull"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Bear only,Bear+Base,All,None"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5013,62 +7662,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="36" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="36" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="36" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="36" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="36" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="36" t="inlineStr">
+      <c r="G1" s="65" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="36" t="inlineStr">
+      <c r="H1" s="65" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="36" t="inlineStr">
+      <c r="I1" s="65" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="36" t="inlineStr">
+      <c r="J1" s="65" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="36" t="inlineStr">
+      <c r="K1" s="65" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="36" t="inlineStr">
+      <c r="L1" s="65" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5101,16 +7750,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="37" t="n">
+      <c r="G2" s="66" t="n">
         <v>0.924324</v>
       </c>
-      <c r="H2" s="37" t="n">
+      <c r="H2" s="66" t="n">
         <v>0.924</v>
       </c>
-      <c r="I2" s="38" t="n">
+      <c r="I2" s="67" t="n">
         <v>1750</v>
       </c>
-      <c r="J2" s="38" t="n">
+      <c r="J2" s="67" t="n">
         <v>1875</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -5151,12 +7800,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="37" t="n"/>
-      <c r="H3" s="37" t="n">
+      <c r="G3" s="66" t="n"/>
+      <c r="H3" s="66" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="38" t="n"/>
-      <c r="J3" s="38" t="n">
+      <c r="I3" s="67" t="n"/>
+      <c r="J3" s="67" t="n">
         <v>2090</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -5197,16 +7846,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="37" t="n">
+      <c r="G4" s="66" t="n">
         <v>0.8518520000000001</v>
       </c>
-      <c r="H4" s="37" t="n">
+      <c r="H4" s="66" t="n">
         <v>0.877</v>
       </c>
-      <c r="I4" s="38" t="n">
+      <c r="I4" s="67" t="n">
         <v>1576</v>
       </c>
-      <c r="J4" s="38" t="n">
+      <c r="J4" s="67" t="n">
         <v>1211</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -5247,16 +7896,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G5" s="37" t="n">
+      <c r="G5" s="66" t="n">
         <v>0.7634730000000001</v>
       </c>
-      <c r="H5" s="37" t="n">
+      <c r="H5" s="66" t="n">
         <v>0.916</v>
       </c>
-      <c r="I5" s="38" t="n">
+      <c r="I5" s="67" t="n">
         <v>2026</v>
       </c>
-      <c r="J5" s="38" t="n">
+      <c r="J5" s="67" t="n">
         <v>1385</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -5297,16 +7946,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G6" s="37" t="n">
+      <c r="G6" s="66" t="n">
         <v>0.895833</v>
       </c>
-      <c r="H6" s="37" t="n">
+      <c r="H6" s="66" t="n">
         <v>0.966</v>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="67" t="n">
         <v>1429</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="67" t="n">
         <v>1313</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -5347,16 +7996,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G7" s="66" t="n">
         <v>0.949309</v>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="66" t="n">
         <v>0.968</v>
       </c>
-      <c r="I7" s="38" t="n">
+      <c r="I7" s="67" t="n">
         <v>1576</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="67" t="n">
         <v>1602</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -5397,16 +8046,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G8" s="37" t="n">
+      <c r="G8" s="66" t="n">
         <v>0.773196</v>
       </c>
-      <c r="H8" s="37" t="n">
+      <c r="H8" s="66" t="n">
         <v>0.918</v>
       </c>
-      <c r="I8" s="38" t="n">
+      <c r="I8" s="67" t="n">
         <v>1874</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="67" t="n">
         <v>1794</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -5447,16 +8096,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G9" s="37" t="n">
+      <c r="G9" s="66" t="n">
         <v>0.784247</v>
       </c>
-      <c r="H9" s="37" t="n">
+      <c r="H9" s="66" t="n">
         <v>0.87</v>
       </c>
-      <c r="I9" s="38" t="n">
+      <c r="I9" s="67" t="n">
         <v>1516</v>
       </c>
-      <c r="J9" s="38" t="n">
+      <c r="J9" s="67" t="n">
         <v>1517</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -5497,16 +8146,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G10" s="37" t="n">
+      <c r="G10" s="66" t="n">
         <v>0.8992249999999999</v>
       </c>
-      <c r="H10" s="37" t="n">
+      <c r="H10" s="66" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="I10" s="38" t="n">
+      <c r="I10" s="67" t="n">
         <v>1567</v>
       </c>
-      <c r="J10" s="38" t="n">
+      <c r="J10" s="67" t="n">
         <v>1591</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -5547,16 +8196,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G11" s="37" t="n">
+      <c r="G11" s="66" t="n">
         <v>0.9520960000000001</v>
       </c>
-      <c r="H11" s="37" t="n">
+      <c r="H11" s="66" t="n">
         <v>0.946</v>
       </c>
-      <c r="I11" s="38" t="n">
+      <c r="I11" s="67" t="n">
         <v>1607</v>
       </c>
-      <c r="J11" s="38" t="n">
+      <c r="J11" s="67" t="n">
         <v>1388</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -5597,16 +8246,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G12" s="37" t="n">
+      <c r="G12" s="66" t="n">
         <v>0.920455</v>
       </c>
-      <c r="H12" s="37" t="n">
+      <c r="H12" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="38" t="n">
+      <c r="I12" s="67" t="n">
         <v>1526</v>
       </c>
-      <c r="J12" s="38" t="n">
+      <c r="J12" s="67" t="n">
         <v>1263</v>
       </c>
       <c r="K12" t="inlineStr">
@@ -5647,16 +8296,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G13" s="37" t="n">
+      <c r="G13" s="66" t="n">
         <v>0.934483</v>
       </c>
-      <c r="H13" s="37" t="n">
+      <c r="H13" s="66" t="n">
         <v>0.959</v>
       </c>
-      <c r="I13" s="38" t="n">
+      <c r="I13" s="67" t="n">
         <v>2812</v>
       </c>
-      <c r="J13" s="38" t="n">
+      <c r="J13" s="67" t="n">
         <v>2575</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -5697,16 +8346,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G14" s="37" t="n">
+      <c r="G14" s="66" t="n">
         <v>0.935829</v>
       </c>
-      <c r="H14" s="37" t="n">
+      <c r="H14" s="66" t="n">
         <v>0.963</v>
       </c>
-      <c r="I14" s="38" t="n">
+      <c r="I14" s="67" t="n">
         <v>1964</v>
       </c>
-      <c r="J14" s="38" t="n">
+      <c r="J14" s="67" t="n">
         <v>1902</v>
       </c>
       <c r="K14" t="inlineStr">
@@ -5747,16 +8396,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G15" s="37" t="n">
+      <c r="G15" s="66" t="n">
         <v>0.892045</v>
       </c>
-      <c r="H15" s="37" t="n">
+      <c r="H15" s="66" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I15" s="38" t="n">
+      <c r="I15" s="67" t="n">
         <v>1632</v>
       </c>
-      <c r="J15" s="38" t="n">
+      <c r="J15" s="67" t="n">
         <v>1236</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -5797,16 +8446,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G16" s="37" t="n">
+      <c r="G16" s="66" t="n">
         <v>0.926471</v>
       </c>
-      <c r="H16" s="37" t="n">
+      <c r="H16" s="66" t="n">
         <v>0.967</v>
       </c>
-      <c r="I16" s="38" t="n">
+      <c r="I16" s="67" t="n">
         <v>1820</v>
       </c>
-      <c r="J16" s="38" t="n">
+      <c r="J16" s="67" t="n">
         <v>1597</v>
       </c>
       <c r="K16" t="inlineStr">
@@ -5847,16 +8496,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G17" s="37" t="n">
+      <c r="G17" s="66" t="n">
         <v>0.9494050000000001</v>
       </c>
-      <c r="H17" s="37" t="n">
+      <c r="H17" s="66" t="n">
         <v>0.949</v>
       </c>
-      <c r="I17" s="38" t="n">
+      <c r="I17" s="67" t="n">
         <v>1335</v>
       </c>
-      <c r="J17" s="38" t="n">
+      <c r="J17" s="67" t="n">
         <v>1325</v>
       </c>
       <c r="K17" t="inlineStr">
@@ -5897,14 +8546,14 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G18" s="37" t="n">
+      <c r="G18" s="66" t="n">
         <v>0.893204</v>
       </c>
-      <c r="H18" s="37" t="n"/>
-      <c r="I18" s="38" t="n">
+      <c r="H18" s="66" t="n"/>
+      <c r="I18" s="67" t="n">
         <v>2523</v>
       </c>
-      <c r="J18" s="38" t="n"/>
+      <c r="J18" s="67" t="n"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -5943,12 +8592,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G19" s="37" t="n"/>
-      <c r="H19" s="37" t="n">
+      <c r="G19" s="66" t="n"/>
+      <c r="H19" s="66" t="n">
         <v>0.926</v>
       </c>
-      <c r="I19" s="38" t="n"/>
-      <c r="J19" s="38" t="n">
+      <c r="I19" s="67" t="n"/>
+      <c r="J19" s="67" t="n">
         <v>1629</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -5989,16 +8638,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G20" s="37" t="n">
+      <c r="G20" s="66" t="n">
         <v>0.951977</v>
       </c>
-      <c r="H20" s="37" t="n">
+      <c r="H20" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="38" t="n">
+      <c r="I20" s="67" t="n">
         <v>1574</v>
       </c>
-      <c r="J20" s="38" t="n">
+      <c r="J20" s="67" t="n">
         <v>1583</v>
       </c>
       <c r="K20" t="inlineStr">
@@ -6039,16 +8688,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G21" s="66" t="n">
         <v>0.902098</v>
       </c>
-      <c r="H21" s="37" t="n">
+      <c r="H21" s="66" t="n">
         <v>0.955</v>
       </c>
-      <c r="I21" s="38" t="n">
+      <c r="I21" s="67" t="n">
         <v>1338</v>
       </c>
-      <c r="J21" s="38" t="n">
+      <c r="J21" s="67" t="n">
         <v>1167</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -6089,16 +8738,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G22" s="37" t="n">
+      <c r="G22" s="66" t="n">
         <v>0.984375</v>
       </c>
-      <c r="H22" s="37" t="n">
+      <c r="H22" s="66" t="n">
         <v>0.984</v>
       </c>
-      <c r="I22" s="38" t="n">
+      <c r="I22" s="67" t="n">
         <v>2442</v>
       </c>
-      <c r="J22" s="38" t="n">
+      <c r="J22" s="67" t="n">
         <v>2261</v>
       </c>
       <c r="K22" t="inlineStr">
@@ -6139,16 +8788,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G23" s="37" t="n">
+      <c r="G23" s="66" t="n">
         <v>0.989362</v>
       </c>
-      <c r="H23" s="37" t="n">
+      <c r="H23" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="38" t="n">
+      <c r="I23" s="67" t="n">
         <v>1913</v>
       </c>
-      <c r="J23" s="38" t="n">
+      <c r="J23" s="67" t="n">
         <v>1982</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -6185,16 +8834,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G24" s="37" t="n">
+      <c r="G24" s="66" t="n">
         <v>0.4461540000000001</v>
       </c>
-      <c r="H24" s="37" t="n">
+      <c r="H24" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="38" t="n">
+      <c r="I24" s="67" t="n">
         <v>1829</v>
       </c>
-      <c r="J24" s="38" t="n">
+      <c r="J24" s="67" t="n">
         <v>1681</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -6235,16 +8884,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G25" s="37" t="n">
+      <c r="G25" s="66" t="n">
         <v>0.05660399999999999</v>
       </c>
-      <c r="H25" s="37" t="n">
+      <c r="H25" s="66" t="n">
         <v>0.208</v>
       </c>
-      <c r="I25" s="38" t="n">
+      <c r="I25" s="67" t="n">
         <v>2966</v>
       </c>
-      <c r="J25" s="38" t="n">
+      <c r="J25" s="67" t="n">
         <v>1938</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -6285,16 +8934,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G26" s="37" t="n">
+      <c r="G26" s="66" t="n">
         <v>0.273504</v>
       </c>
-      <c r="H26" s="37" t="n">
+      <c r="H26" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="38" t="n">
+      <c r="I26" s="67" t="n">
         <v>2537</v>
       </c>
-      <c r="J26" s="38" t="n">
+      <c r="J26" s="67" t="n">
         <v>2273</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -6335,16 +8984,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G27" s="37" t="n">
+      <c r="G27" s="66" t="n">
         <v>0.1333329999999999</v>
       </c>
-      <c r="H27" s="37" t="n">
+      <c r="H27" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="38" t="n">
+      <c r="I27" s="67" t="n">
         <v>1411</v>
       </c>
-      <c r="J27" s="38" t="n">
+      <c r="J27" s="67" t="n">
         <v>1145</v>
       </c>
       <c r="K27" t="inlineStr">
@@ -6385,16 +9034,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G28" s="37" t="n">
+      <c r="G28" s="66" t="n">
         <v>0.297203</v>
       </c>
-      <c r="H28" s="37" t="n">
+      <c r="H28" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="38" t="n">
+      <c r="I28" s="67" t="n">
         <v>1728</v>
       </c>
-      <c r="J28" s="38" t="n">
+      <c r="J28" s="67" t="n">
         <v>1243</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -6435,16 +9084,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G29" s="66" t="n">
         <v>0.875</v>
       </c>
-      <c r="H29" s="37" t="n">
+      <c r="H29" s="66" t="n">
         <v>0.512</v>
       </c>
-      <c r="I29" s="38" t="n">
+      <c r="I29" s="67" t="n">
         <v>1506</v>
       </c>
-      <c r="J29" s="38" t="n">
+      <c r="J29" s="67" t="n">
         <v>1107</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -6485,14 +9134,14 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G30" s="37" t="n">
+      <c r="G30" s="66" t="n">
         <v>0.895349</v>
       </c>
-      <c r="H30" s="37" t="n"/>
-      <c r="I30" s="38" t="n">
+      <c r="H30" s="66" t="n"/>
+      <c r="I30" s="67" t="n">
         <v>2474</v>
       </c>
-      <c r="J30" s="38" t="n"/>
+      <c r="J30" s="67" t="n"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -6531,16 +9180,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G31" s="37" t="n">
+      <c r="G31" s="66" t="n">
         <v>0.52381</v>
       </c>
-      <c r="H31" s="37" t="n">
+      <c r="H31" s="66" t="n">
         <v>0.714</v>
       </c>
-      <c r="I31" s="38" t="n">
+      <c r="I31" s="67" t="n">
         <v>2319</v>
       </c>
-      <c r="J31" s="38" t="n">
+      <c r="J31" s="67" t="n">
         <v>1833</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -6581,16 +9230,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G32" s="37" t="n">
+      <c r="G32" s="66" t="n">
         <v>0.810458</v>
       </c>
-      <c r="H32" s="37" t="n">
+      <c r="H32" s="66" t="n">
         <v>0.856</v>
       </c>
-      <c r="I32" s="38" t="n">
+      <c r="I32" s="67" t="n">
         <v>1913</v>
       </c>
-      <c r="J32" s="38" t="n">
+      <c r="J32" s="67" t="n">
         <v>1538</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -6631,16 +9280,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G33" s="37" t="n">
+      <c r="G33" s="66" t="n">
         <v>0.857143</v>
       </c>
-      <c r="H33" s="37" t="n">
+      <c r="H33" s="66" t="n">
         <v>0.857</v>
       </c>
-      <c r="I33" s="38" t="n">
+      <c r="I33" s="67" t="n">
         <v>2325</v>
       </c>
-      <c r="J33" s="38" t="n">
+      <c r="J33" s="67" t="n">
         <v>2169</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -6681,16 +9330,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G34" s="37" t="n">
+      <c r="G34" s="66" t="n">
         <v>0.496503</v>
       </c>
-      <c r="H34" s="37" t="n">
+      <c r="H34" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="38" t="n">
+      <c r="I34" s="67" t="n">
         <v>2085</v>
       </c>
-      <c r="J34" s="38" t="n">
+      <c r="J34" s="67" t="n">
         <v>2095</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -6731,16 +9380,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G35" s="37" t="n">
+      <c r="G35" s="66" t="n">
         <v>0.802469</v>
       </c>
-      <c r="H35" s="37" t="n">
+      <c r="H35" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="38" t="n">
+      <c r="I35" s="67" t="n">
         <v>1747</v>
       </c>
-      <c r="J35" s="38" t="n">
+      <c r="J35" s="67" t="n">
         <v>1582</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -6781,16 +9430,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G36" s="37" t="n">
+      <c r="G36" s="66" t="n">
         <v>0.789474</v>
       </c>
-      <c r="H36" s="37" t="n">
+      <c r="H36" s="66" t="n">
         <v>0.784</v>
       </c>
-      <c r="I36" s="38" t="n">
+      <c r="I36" s="67" t="n">
         <v>1638</v>
       </c>
-      <c r="J36" s="38" t="n">
+      <c r="J36" s="67" t="n">
         <v>1433</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -6831,16 +9480,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G37" s="37" t="n">
+      <c r="G37" s="66" t="n">
         <v>0.3952100000000001</v>
       </c>
-      <c r="H37" s="37" t="n">
+      <c r="H37" s="66" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="38" t="n">
+      <c r="I37" s="67" t="n">
         <v>1773</v>
       </c>
-      <c r="J37" s="38" t="n">
+      <c r="J37" s="67" t="n">
         <v>1632</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -6881,16 +9530,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G38" s="37" t="n">
+      <c r="G38" s="66" t="n">
         <v>0.37037</v>
       </c>
-      <c r="H38" s="37" t="n">
+      <c r="H38" s="66" t="n">
         <v>0.852</v>
       </c>
-      <c r="I38" s="38" t="n">
+      <c r="I38" s="67" t="n">
         <v>1632</v>
       </c>
-      <c r="J38" s="38" t="n">
+      <c r="J38" s="67" t="n">
         <v>1321</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -6931,16 +9580,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G39" s="37" t="n">
+      <c r="G39" s="66" t="n">
         <v>0.7393000000000001</v>
       </c>
-      <c r="H39" s="37" t="n">
+      <c r="H39" s="66" t="n">
         <v>0.673</v>
       </c>
-      <c r="I39" s="38" t="n">
+      <c r="I39" s="67" t="n">
         <v>1330</v>
       </c>
-      <c r="J39" s="38" t="n">
+      <c r="J39" s="67" t="n">
         <v>1253</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -6981,16 +9630,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G40" s="37" t="n">
+      <c r="G40" s="66" t="n">
         <v>0.583062</v>
       </c>
-      <c r="H40" s="37" t="n">
+      <c r="H40" s="66" t="n">
         <v>0.59</v>
       </c>
-      <c r="I40" s="38" t="n">
+      <c r="I40" s="67" t="n">
         <v>2076</v>
       </c>
-      <c r="J40" s="38" t="n">
+      <c r="J40" s="67" t="n">
         <v>1561</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -7031,12 +9680,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G41" s="37" t="n"/>
-      <c r="H41" s="37" t="n">
+      <c r="G41" s="66" t="n"/>
+      <c r="H41" s="66" t="n">
         <v>0.89</v>
       </c>
-      <c r="I41" s="38" t="n"/>
-      <c r="J41" s="38" t="n">
+      <c r="I41" s="67" t="n"/>
+      <c r="J41" s="67" t="n">
         <v>1438</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -7077,12 +9726,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G42" s="37" t="n"/>
-      <c r="H42" s="37" t="n">
+      <c r="G42" s="66" t="n"/>
+      <c r="H42" s="66" t="n">
         <v>0.256</v>
       </c>
-      <c r="I42" s="38" t="n"/>
-      <c r="J42" s="38" t="n">
+      <c r="I42" s="67" t="n"/>
+      <c r="J42" s="67" t="n">
         <v>1671</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -7123,12 +9772,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G43" s="37" t="n"/>
-      <c r="H43" s="37" t="n">
+      <c r="G43" s="66" t="n"/>
+      <c r="H43" s="66" t="n">
         <v>0.844</v>
       </c>
-      <c r="I43" s="38" t="n"/>
-      <c r="J43" s="38" t="n">
+      <c r="I43" s="67" t="n"/>
+      <c r="J43" s="67" t="n">
         <v>1025</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -7169,16 +9818,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G44" s="37" t="n">
+      <c r="G44" s="66" t="n">
         <v>0.797059</v>
       </c>
-      <c r="H44" s="37" t="n">
+      <c r="H44" s="66" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="I44" s="38" t="n">
+      <c r="I44" s="67" t="n">
         <v>1680</v>
       </c>
-      <c r="J44" s="38" t="n">
+      <c r="J44" s="67" t="n">
         <v>1356</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -7219,16 +9868,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G45" s="37" t="n">
+      <c r="G45" s="66" t="n">
         <v>0.891892</v>
       </c>
-      <c r="H45" s="37" t="n">
+      <c r="H45" s="66" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="I45" s="38" t="n">
+      <c r="I45" s="67" t="n">
         <v>1900</v>
       </c>
-      <c r="J45" s="38" t="n">
+      <c r="J45" s="67" t="n">
         <v>1769</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -7269,16 +9918,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G46" s="37" t="n">
+      <c r="G46" s="66" t="n">
         <v>0.879032</v>
       </c>
-      <c r="H46" s="37" t="n">
+      <c r="H46" s="66" t="n">
         <v>0.919</v>
       </c>
-      <c r="I46" s="38" t="n">
+      <c r="I46" s="67" t="n">
         <v>2183</v>
       </c>
-      <c r="J46" s="38" t="n">
+      <c r="J46" s="67" t="n">
         <v>2093</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -7319,16 +9968,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G47" s="37" t="n">
+      <c r="G47" s="66" t="n">
         <v>0.878788</v>
       </c>
-      <c r="H47" s="37" t="n">
+      <c r="H47" s="66" t="n">
         <v>0.889</v>
       </c>
-      <c r="I47" s="38" t="n">
+      <c r="I47" s="67" t="n">
         <v>1691</v>
       </c>
-      <c r="J47" s="38" t="n">
+      <c r="J47" s="67" t="n">
         <v>1646</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -7369,16 +10018,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G48" s="37" t="n">
+      <c r="G48" s="66" t="n">
         <v>0.829114</v>
       </c>
-      <c r="H48" s="37" t="n">
+      <c r="H48" s="66" t="n">
         <v>0.842</v>
       </c>
-      <c r="I48" s="38" t="n">
+      <c r="I48" s="67" t="n">
         <v>1663</v>
       </c>
-      <c r="J48" s="38" t="n">
+      <c r="J48" s="67" t="n">
         <v>1263</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -7419,16 +10068,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G49" s="37" t="n">
+      <c r="G49" s="66" t="n">
         <v>0.7833330000000001</v>
       </c>
-      <c r="H49" s="37" t="n">
+      <c r="H49" s="66" t="n">
         <v>0.836</v>
       </c>
-      <c r="I49" s="38" t="n">
+      <c r="I49" s="67" t="n">
         <v>1610</v>
       </c>
-      <c r="J49" s="38" t="n">
+      <c r="J49" s="67" t="n">
         <v>1339</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -7469,16 +10118,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G50" s="37" t="n">
+      <c r="G50" s="66" t="n">
         <v>0.855721</v>
       </c>
-      <c r="H50" s="37" t="n">
+      <c r="H50" s="66" t="n">
         <v>0.901</v>
       </c>
-      <c r="I50" s="38" t="n">
+      <c r="I50" s="67" t="n">
         <v>1542</v>
       </c>
-      <c r="J50" s="38" t="n">
+      <c r="J50" s="67" t="n">
         <v>1154</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -7519,16 +10168,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G51" s="37" t="n">
+      <c r="G51" s="66" t="n">
         <v>0.616708</v>
       </c>
-      <c r="H51" s="37" t="n">
+      <c r="H51" s="66" t="n">
         <v>0.514</v>
       </c>
-      <c r="I51" s="38" t="n">
+      <c r="I51" s="67" t="n">
         <v>1743</v>
       </c>
-      <c r="J51" s="38" t="n">
+      <c r="J51" s="67" t="n">
         <v>1676</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -7569,10 +10218,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G52" s="37" t="n"/>
-      <c r="H52" s="37" t="n"/>
-      <c r="I52" s="38" t="n"/>
-      <c r="J52" s="38" t="n"/>
+      <c r="G52" s="66" t="n"/>
+      <c r="H52" s="66" t="n"/>
+      <c r="I52" s="67" t="n"/>
+      <c r="J52" s="67" t="n"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -7611,10 +10260,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G53" s="37" t="n"/>
-      <c r="H53" s="37" t="n"/>
-      <c r="I53" s="38" t="n"/>
-      <c r="J53" s="38" t="n"/>
+      <c r="G53" s="66" t="n"/>
+      <c r="H53" s="66" t="n"/>
+      <c r="I53" s="67" t="n"/>
+      <c r="J53" s="67" t="n"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7649,12 +10298,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G54" s="37" t="n"/>
-      <c r="H54" s="37" t="n"/>
-      <c r="I54" s="38" t="n">
+      <c r="G54" s="66" t="n"/>
+      <c r="H54" s="66" t="n"/>
+      <c r="I54" s="67" t="n">
         <v>1781</v>
       </c>
-      <c r="J54" s="38" t="n"/>
+      <c r="J54" s="67" t="n"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -7693,10 +10342,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G55" s="37" t="n"/>
-      <c r="H55" s="37" t="n"/>
-      <c r="I55" s="38" t="n"/>
-      <c r="J55" s="38" t="n"/>
+      <c r="G55" s="66" t="n"/>
+      <c r="H55" s="66" t="n"/>
+      <c r="I55" s="67" t="n"/>
+      <c r="J55" s="67" t="n"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -7731,12 +10380,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G56" s="37" t="n"/>
-      <c r="H56" s="37" t="n"/>
-      <c r="I56" s="38" t="n">
+      <c r="G56" s="66" t="n"/>
+      <c r="H56" s="66" t="n"/>
+      <c r="I56" s="67" t="n">
         <v>1650</v>
       </c>
-      <c r="J56" s="38" t="n"/>
+      <c r="J56" s="67" t="n"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -7775,10 +10424,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G57" s="37" t="n"/>
-      <c r="H57" s="37" t="n"/>
-      <c r="I57" s="38" t="n"/>
-      <c r="J57" s="38" t="n"/>
+      <c r="G57" s="66" t="n"/>
+      <c r="H57" s="66" t="n"/>
+      <c r="I57" s="67" t="n"/>
+      <c r="J57" s="67" t="n"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7813,10 +10462,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G58" s="37" t="n"/>
-      <c r="H58" s="37" t="n"/>
-      <c r="I58" s="38" t="n"/>
-      <c r="J58" s="38" t="n"/>
+      <c r="G58" s="66" t="n"/>
+      <c r="H58" s="66" t="n"/>
+      <c r="I58" s="67" t="n"/>
+      <c r="J58" s="67" t="n"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7851,10 +10500,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G59" s="37" t="n"/>
-      <c r="H59" s="37" t="n"/>
-      <c r="I59" s="38" t="n"/>
-      <c r="J59" s="38" t="n"/>
+      <c r="G59" s="66" t="n"/>
+      <c r="H59" s="66" t="n"/>
+      <c r="I59" s="67" t="n"/>
+      <c r="J59" s="67" t="n"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -7893,12 +10542,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G60" s="37" t="n"/>
-      <c r="H60" s="37" t="n"/>
-      <c r="I60" s="38" t="n">
+      <c r="G60" s="66" t="n"/>
+      <c r="H60" s="66" t="n"/>
+      <c r="I60" s="67" t="n">
         <v>2788</v>
       </c>
-      <c r="J60" s="38" t="n"/>
+      <c r="J60" s="67" t="n"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -7933,10 +10582,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G61" s="37" t="n"/>
-      <c r="H61" s="37" t="n"/>
-      <c r="I61" s="38" t="n"/>
-      <c r="J61" s="38" t="n"/>
+      <c r="G61" s="66" t="n"/>
+      <c r="H61" s="66" t="n"/>
+      <c r="I61" s="67" t="n"/>
+      <c r="J61" s="67" t="n"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -7968,10 +10617,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G62" s="37" t="n"/>
-      <c r="H62" s="37" t="n"/>
-      <c r="I62" s="38" t="n"/>
-      <c r="J62" s="38" t="n"/>
+      <c r="G62" s="66" t="n"/>
+      <c r="H62" s="66" t="n"/>
+      <c r="I62" s="67" t="n"/>
+      <c r="J62" s="67" t="n"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8006,10 +10655,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G63" s="37" t="n"/>
-      <c r="H63" s="37" t="n"/>
-      <c r="I63" s="38" t="n"/>
-      <c r="J63" s="38" t="n"/>
+      <c r="G63" s="66" t="n"/>
+      <c r="H63" s="66" t="n"/>
+      <c r="I63" s="67" t="n"/>
+      <c r="J63" s="67" t="n"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8041,10 +10690,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G64" s="37" t="n"/>
-      <c r="H64" s="37" t="n"/>
-      <c r="I64" s="38" t="n"/>
-      <c r="J64" s="38" t="n"/>
+      <c r="G64" s="66" t="n"/>
+      <c r="H64" s="66" t="n"/>
+      <c r="I64" s="67" t="n"/>
+      <c r="J64" s="67" t="n"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8079,10 +10728,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G65" s="37" t="n"/>
-      <c r="H65" s="37" t="n"/>
-      <c r="I65" s="38" t="n"/>
-      <c r="J65" s="38" t="n"/>
+      <c r="G65" s="66" t="n"/>
+      <c r="H65" s="66" t="n"/>
+      <c r="I65" s="67" t="n"/>
+      <c r="J65" s="67" t="n"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -8117,10 +10766,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G66" s="37" t="n"/>
-      <c r="H66" s="37" t="n"/>
-      <c r="I66" s="38" t="n"/>
-      <c r="J66" s="38" t="n"/>
+      <c r="G66" s="66" t="n"/>
+      <c r="H66" s="66" t="n"/>
+      <c r="I66" s="67" t="n"/>
+      <c r="J66" s="67" t="n"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8147,10 +10796,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G67" s="37" t="n"/>
-      <c r="H67" s="37" t="n"/>
-      <c r="I67" s="38" t="n"/>
-      <c r="J67" s="38" t="n"/>
+      <c r="G67" s="66" t="n"/>
+      <c r="H67" s="66" t="n"/>
+      <c r="I67" s="67" t="n"/>
+      <c r="J67" s="67" t="n"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8181,10 +10830,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G68" s="37" t="n"/>
-      <c r="H68" s="37" t="n"/>
-      <c r="I68" s="38" t="n"/>
-      <c r="J68" s="38" t="n"/>
+      <c r="G68" s="66" t="n"/>
+      <c r="H68" s="66" t="n"/>
+      <c r="I68" s="67" t="n"/>
+      <c r="J68" s="67" t="n"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8215,10 +10864,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G69" s="37" t="n"/>
-      <c r="H69" s="37" t="n"/>
-      <c r="I69" s="38" t="n"/>
-      <c r="J69" s="38" t="n"/>
+      <c r="G69" s="66" t="n"/>
+      <c r="H69" s="66" t="n"/>
+      <c r="I69" s="67" t="n"/>
+      <c r="J69" s="67" t="n"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8249,10 +10898,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G70" s="37" t="n"/>
-      <c r="H70" s="37" t="n"/>
-      <c r="I70" s="38" t="n"/>
-      <c r="J70" s="38" t="n"/>
+      <c r="G70" s="66" t="n"/>
+      <c r="H70" s="66" t="n"/>
+      <c r="I70" s="67" t="n"/>
+      <c r="J70" s="67" t="n"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8280,10 +10929,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G71" s="37" t="n"/>
-      <c r="H71" s="37" t="n"/>
-      <c r="I71" s="38" t="n"/>
-      <c r="J71" s="38" t="n"/>
+      <c r="G71" s="66" t="n"/>
+      <c r="H71" s="66" t="n"/>
+      <c r="I71" s="67" t="n"/>
+      <c r="J71" s="67" t="n"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8314,10 +10963,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G72" s="37" t="n"/>
-      <c r="H72" s="37" t="n"/>
-      <c r="I72" s="38" t="n"/>
-      <c r="J72" s="38" t="n"/>
+      <c r="G72" s="66" t="n"/>
+      <c r="H72" s="66" t="n"/>
+      <c r="I72" s="67" t="n"/>
+      <c r="J72" s="67" t="n"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8345,10 +10994,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G73" s="37" t="n"/>
-      <c r="H73" s="37" t="n"/>
-      <c r="I73" s="38" t="n"/>
-      <c r="J73" s="38" t="n"/>
+      <c r="G73" s="66" t="n"/>
+      <c r="H73" s="66" t="n"/>
+      <c r="I73" s="67" t="n"/>
+      <c r="J73" s="67" t="n"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8379,10 +11028,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G74" s="37" t="n"/>
-      <c r="H74" s="37" t="n"/>
-      <c r="I74" s="38" t="n"/>
-      <c r="J74" s="38" t="n"/>
+      <c r="G74" s="66" t="n"/>
+      <c r="H74" s="66" t="n"/>
+      <c r="I74" s="67" t="n"/>
+      <c r="J74" s="67" t="n"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8413,10 +11062,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G75" s="37" t="n"/>
-      <c r="H75" s="37" t="n"/>
-      <c r="I75" s="38" t="n"/>
-      <c r="J75" s="38" t="n"/>
+      <c r="G75" s="66" t="n"/>
+      <c r="H75" s="66" t="n"/>
+      <c r="I75" s="67" t="n"/>
+      <c r="J75" s="67" t="n"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8444,10 +11093,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G76" s="37" t="n"/>
-      <c r="H76" s="37" t="n"/>
-      <c r="I76" s="38" t="n"/>
-      <c r="J76" s="38" t="n"/>
+      <c r="G76" s="66" t="n"/>
+      <c r="H76" s="66" t="n"/>
+      <c r="I76" s="67" t="n"/>
+      <c r="J76" s="67" t="n"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8475,10 +11124,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G77" s="37" t="n"/>
-      <c r="H77" s="37" t="n"/>
-      <c r="I77" s="38" t="n"/>
-      <c r="J77" s="38" t="n"/>
+      <c r="G77" s="66" t="n"/>
+      <c r="H77" s="66" t="n"/>
+      <c r="I77" s="67" t="n"/>
+      <c r="J77" s="67" t="n"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8509,10 +11158,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G78" s="37" t="n"/>
-      <c r="H78" s="37" t="n"/>
-      <c r="I78" s="38" t="n"/>
-      <c r="J78" s="38" t="n"/>
+      <c r="G78" s="66" t="n"/>
+      <c r="H78" s="66" t="n"/>
+      <c r="I78" s="67" t="n"/>
+      <c r="J78" s="67" t="n"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8543,10 +11192,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G79" s="37" t="n"/>
-      <c r="H79" s="37" t="n"/>
-      <c r="I79" s="38" t="n"/>
-      <c r="J79" s="38" t="n"/>
+      <c r="G79" s="66" t="n"/>
+      <c r="H79" s="66" t="n"/>
+      <c r="I79" s="67" t="n"/>
+      <c r="J79" s="67" t="n"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8574,10 +11223,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G80" s="37" t="n"/>
-      <c r="H80" s="37" t="n"/>
-      <c r="I80" s="38" t="n"/>
-      <c r="J80" s="38" t="n"/>
+      <c r="G80" s="66" t="n"/>
+      <c r="H80" s="66" t="n"/>
+      <c r="I80" s="67" t="n"/>
+      <c r="J80" s="67" t="n"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8608,10 +11257,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G81" s="37" t="n"/>
-      <c r="H81" s="37" t="n"/>
-      <c r="I81" s="38" t="n"/>
-      <c r="J81" s="38" t="n"/>
+      <c r="G81" s="66" t="n"/>
+      <c r="H81" s="66" t="n"/>
+      <c r="I81" s="67" t="n"/>
+      <c r="J81" s="67" t="n"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8642,10 +11291,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G82" s="37" t="n"/>
-      <c r="H82" s="37" t="n"/>
-      <c r="I82" s="38" t="n"/>
-      <c r="J82" s="38" t="n"/>
+      <c r="G82" s="66" t="n"/>
+      <c r="H82" s="66" t="n"/>
+      <c r="I82" s="67" t="n"/>
+      <c r="J82" s="67" t="n"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8676,10 +11325,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G83" s="37" t="n"/>
-      <c r="H83" s="37" t="n"/>
-      <c r="I83" s="38" t="n"/>
-      <c r="J83" s="38" t="n"/>
+      <c r="G83" s="66" t="n"/>
+      <c r="H83" s="66" t="n"/>
+      <c r="I83" s="67" t="n"/>
+      <c r="J83" s="67" t="n"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8710,10 +11359,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G84" s="37" t="n"/>
-      <c r="H84" s="37" t="n"/>
-      <c r="I84" s="38" t="n"/>
-      <c r="J84" s="38" t="n"/>
+      <c r="G84" s="66" t="n"/>
+      <c r="H84" s="66" t="n"/>
+      <c r="I84" s="67" t="n"/>
+      <c r="J84" s="67" t="n"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8744,10 +11393,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G85" s="37" t="n"/>
-      <c r="H85" s="37" t="n"/>
-      <c r="I85" s="38" t="n"/>
-      <c r="J85" s="38" t="n"/>
+      <c r="G85" s="66" t="n"/>
+      <c r="H85" s="66" t="n"/>
+      <c r="I85" s="67" t="n"/>
+      <c r="J85" s="67" t="n"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8775,10 +11424,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G86" s="37" t="n"/>
-      <c r="H86" s="37" t="n"/>
-      <c r="I86" s="38" t="n"/>
-      <c r="J86" s="38" t="n"/>
+      <c r="G86" s="66" t="n"/>
+      <c r="H86" s="66" t="n"/>
+      <c r="I86" s="67" t="n"/>
+      <c r="J86" s="67" t="n"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8809,10 +11458,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G87" s="37" t="n"/>
-      <c r="H87" s="37" t="n"/>
-      <c r="I87" s="38" t="n"/>
-      <c r="J87" s="38" t="n"/>
+      <c r="G87" s="66" t="n"/>
+      <c r="H87" s="66" t="n"/>
+      <c r="I87" s="67" t="n"/>
+      <c r="J87" s="67" t="n"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8843,10 +11492,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G88" s="37" t="n"/>
-      <c r="H88" s="37" t="n"/>
-      <c r="I88" s="38" t="n"/>
-      <c r="J88" s="38" t="n"/>
+      <c r="G88" s="66" t="n"/>
+      <c r="H88" s="66" t="n"/>
+      <c r="I88" s="67" t="n"/>
+      <c r="J88" s="67" t="n"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8874,10 +11523,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G89" s="37" t="n"/>
-      <c r="H89" s="37" t="n"/>
-      <c r="I89" s="38" t="n"/>
-      <c r="J89" s="38" t="n"/>
+      <c r="G89" s="66" t="n"/>
+      <c r="H89" s="66" t="n"/>
+      <c r="I89" s="67" t="n"/>
+      <c r="J89" s="67" t="n"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8905,10 +11554,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G90" s="37" t="n"/>
-      <c r="H90" s="37" t="n"/>
-      <c r="I90" s="38" t="n"/>
-      <c r="J90" s="38" t="n"/>
+      <c r="G90" s="66" t="n"/>
+      <c r="H90" s="66" t="n"/>
+      <c r="I90" s="67" t="n"/>
+      <c r="J90" s="67" t="n"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8939,10 +11588,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G91" s="37" t="n"/>
-      <c r="H91" s="37" t="n"/>
-      <c r="I91" s="38" t="n"/>
-      <c r="J91" s="38" t="n"/>
+      <c r="G91" s="66" t="n"/>
+      <c r="H91" s="66" t="n"/>
+      <c r="I91" s="67" t="n"/>
+      <c r="J91" s="67" t="n"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -8973,10 +11622,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G92" s="37" t="n"/>
-      <c r="H92" s="37" t="n"/>
-      <c r="I92" s="38" t="n"/>
-      <c r="J92" s="38" t="n"/>
+      <c r="G92" s="66" t="n"/>
+      <c r="H92" s="66" t="n"/>
+      <c r="I92" s="67" t="n"/>
+      <c r="J92" s="67" t="n"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9004,10 +11653,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G93" s="37" t="n"/>
-      <c r="H93" s="37" t="n"/>
-      <c r="I93" s="38" t="n"/>
-      <c r="J93" s="38" t="n"/>
+      <c r="G93" s="66" t="n"/>
+      <c r="H93" s="66" t="n"/>
+      <c r="I93" s="67" t="n"/>
+      <c r="J93" s="67" t="n"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9038,10 +11687,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G94" s="37" t="n"/>
-      <c r="H94" s="37" t="n"/>
-      <c r="I94" s="38" t="n"/>
-      <c r="J94" s="38" t="n"/>
+      <c r="G94" s="66" t="n"/>
+      <c r="H94" s="66" t="n"/>
+      <c r="I94" s="67" t="n"/>
+      <c r="J94" s="67" t="n"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9072,10 +11721,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G95" s="37" t="n"/>
-      <c r="H95" s="37" t="n"/>
-      <c r="I95" s="38" t="n"/>
-      <c r="J95" s="38" t="n"/>
+      <c r="G95" s="66" t="n"/>
+      <c r="H95" s="66" t="n"/>
+      <c r="I95" s="67" t="n"/>
+      <c r="J95" s="67" t="n"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9106,10 +11755,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G96" s="37" t="n"/>
-      <c r="H96" s="37" t="n"/>
-      <c r="I96" s="38" t="n"/>
-      <c r="J96" s="38" t="n"/>
+      <c r="G96" s="66" t="n"/>
+      <c r="H96" s="66" t="n"/>
+      <c r="I96" s="67" t="n"/>
+      <c r="J96" s="67" t="n"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9137,10 +11786,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G97" s="37" t="n"/>
-      <c r="H97" s="37" t="n"/>
-      <c r="I97" s="38" t="n"/>
-      <c r="J97" s="38" t="n"/>
+      <c r="G97" s="66" t="n"/>
+      <c r="H97" s="66" t="n"/>
+      <c r="I97" s="67" t="n"/>
+      <c r="J97" s="67" t="n"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9168,10 +11817,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G98" s="37" t="n"/>
-      <c r="H98" s="37" t="n"/>
-      <c r="I98" s="38" t="n"/>
-      <c r="J98" s="38" t="n"/>
+      <c r="G98" s="66" t="n"/>
+      <c r="H98" s="66" t="n"/>
+      <c r="I98" s="67" t="n"/>
+      <c r="J98" s="67" t="n"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9202,10 +11851,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G99" s="37" t="n"/>
-      <c r="H99" s="37" t="n"/>
-      <c r="I99" s="38" t="n"/>
-      <c r="J99" s="38" t="n"/>
+      <c r="G99" s="66" t="n"/>
+      <c r="H99" s="66" t="n"/>
+      <c r="I99" s="67" t="n"/>
+      <c r="J99" s="67" t="n"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9236,10 +11885,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G100" s="37" t="n"/>
-      <c r="H100" s="37" t="n"/>
-      <c r="I100" s="38" t="n"/>
-      <c r="J100" s="38" t="n"/>
+      <c r="G100" s="66" t="n"/>
+      <c r="H100" s="66" t="n"/>
+      <c r="I100" s="67" t="n"/>
+      <c r="J100" s="67" t="n"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9270,10 +11919,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G101" s="37" t="n"/>
-      <c r="H101" s="37" t="n"/>
-      <c r="I101" s="38" t="n"/>
-      <c r="J101" s="38" t="n"/>
+      <c r="G101" s="66" t="n"/>
+      <c r="H101" s="66" t="n"/>
+      <c r="I101" s="67" t="n"/>
+      <c r="J101" s="67" t="n"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9304,10 +11953,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G102" s="37" t="n"/>
-      <c r="H102" s="37" t="n"/>
-      <c r="I102" s="38" t="n"/>
-      <c r="J102" s="38" t="n"/>
+      <c r="G102" s="66" t="n"/>
+      <c r="H102" s="66" t="n"/>
+      <c r="I102" s="67" t="n"/>
+      <c r="J102" s="67" t="n"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9338,10 +11987,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G103" s="37" t="n"/>
-      <c r="H103" s="37" t="n"/>
-      <c r="I103" s="38" t="n"/>
-      <c r="J103" s="38" t="n"/>
+      <c r="G103" s="66" t="n"/>
+      <c r="H103" s="66" t="n"/>
+      <c r="I103" s="67" t="n"/>
+      <c r="J103" s="67" t="n"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9369,10 +12018,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G104" s="37" t="n"/>
-      <c r="H104" s="37" t="n"/>
-      <c r="I104" s="38" t="n"/>
-      <c r="J104" s="38" t="n"/>
+      <c r="G104" s="66" t="n"/>
+      <c r="H104" s="66" t="n"/>
+      <c r="I104" s="67" t="n"/>
+      <c r="J104" s="67" t="n"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9403,10 +12052,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G105" s="37" t="n"/>
-      <c r="H105" s="37" t="n"/>
-      <c r="I105" s="38" t="n"/>
-      <c r="J105" s="38" t="n"/>
+      <c r="G105" s="66" t="n"/>
+      <c r="H105" s="66" t="n"/>
+      <c r="I105" s="67" t="n"/>
+      <c r="J105" s="67" t="n"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -9421,2620 +12070,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:X61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="9.5" customWidth="1" min="3" max="3"/>
-    <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="9.5" customWidth="1" min="5" max="5"/>
-    <col width="9.5" customWidth="1" min="6" max="6"/>
-    <col width="9.5" customWidth="1" min="7" max="7"/>
-    <col width="9.5" customWidth="1" min="8" max="8"/>
-    <col width="9.5" customWidth="1" min="9" max="9"/>
-    <col width="9.5" customWidth="1" min="10" max="10"/>
-    <col width="9.5" customWidth="1" min="11" max="11"/>
-    <col width="9.5" customWidth="1" min="12" max="12"/>
-    <col width="9.5" customWidth="1" min="13" max="13"/>
-    <col width="9.5" customWidth="1" min="14" max="14"/>
-    <col width="9.5" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="7" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="7" customWidth="1" min="23" max="23"/>
-    <col width="6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="22" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>SUPPLY &amp; ABSORPTION  —  5-MILE MARKET (relative-year / TTM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="R3" s="39" t="inlineStr">
-        <is>
-          <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>As-of Quarter</t>
-        </is>
-      </c>
-      <c r="C4" s="41" t="inlineStr">
-        <is>
-          <t>Q2 2026</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8105</v>
-      </c>
-      <c r="R4" s="42" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="S4" s="42" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="T4" s="42" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="U4" s="42" t="inlineStr">
-        <is>
-          <t>DelivIdx</t>
-        </is>
-      </c>
-      <c r="V4" s="42" t="inlineStr">
-        <is>
-          <t>HoldYr</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>Close Quarter (Y1 start)</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>Q4 2026</t>
-        </is>
-      </c>
-      <c r="E5">
-        <f>IFERROR(VALUE(RIGHT($C$5,4))*4+MATCH(LEFT($C$5,2),{"Q1","Q2","Q3","Q4"},0)-1,0)</f>
-        <v/>
-      </c>
-      <c r="R5" s="44">
-        <f>'Competitive Analysis'!C69</f>
-        <v/>
-      </c>
-      <c r="S5" s="45">
-        <f>'Competitive Analysis'!D69</f>
-        <v/>
-      </c>
-      <c r="T5" s="46">
-        <f>'Competitive Analysis'!E69</f>
-        <v/>
-      </c>
-      <c r="U5" s="46">
-        <f>IFERROR(VALUE(RIGHT(T5,4))*4+MATCH(LEFT(T5,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V5" s="46">
-        <f>IF(S5="","",IF(U5&lt;=$E$4,0,MAX(1,INT((U5-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>Stabilization Target</t>
-        </is>
-      </c>
-      <c r="C6" s="47">
-        <f>Settings!$B$2</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>IF($C$7="Bear",3,IF($C$7="Base",2,1))</f>
-        <v/>
-      </c>
-      <c r="R6" s="44">
-        <f>'Competitive Analysis'!C60</f>
-        <v/>
-      </c>
-      <c r="S6" s="45">
-        <f>'Competitive Analysis'!D60</f>
-        <v/>
-      </c>
-      <c r="T6" s="46">
-        <f>'Competitive Analysis'!E60</f>
-        <v/>
-      </c>
-      <c r="U6" s="46">
-        <f>IFERROR(VALUE(RIGHT(T6,4))*4+MATCH(LEFT(T6,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V6" s="46">
-        <f>IF(S6="","",IF(U6&lt;=$E$4,0,MAX(1,INT((U6-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="40" t="inlineStr">
-        <is>
-          <t>Demand Scenario</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="R7" s="44">
-        <f>'Competitive Analysis'!C64</f>
-        <v/>
-      </c>
-      <c r="S7" s="45">
-        <f>'Competitive Analysis'!D64</f>
-        <v/>
-      </c>
-      <c r="T7" s="46">
-        <f>'Competitive Analysis'!E64</f>
-        <v/>
-      </c>
-      <c r="U7" s="46">
-        <f>IFERROR(VALUE(RIGHT(T7,4))*4+MATCH(LEFT(T7,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V7" s="46">
-        <f>IF(S7="","",IF(U7&lt;=$E$4,0,MAX(1,INT((U7-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="40" t="inlineStr">
-        <is>
-          <t>Bear Annual Absorption</t>
-        </is>
-      </c>
-      <c r="C8" s="48" t="n">
-        <v>1250</v>
-      </c>
-      <c r="R8" s="44">
-        <f>'Competitive Analysis'!C62</f>
-        <v/>
-      </c>
-      <c r="S8" s="45">
-        <f>'Competitive Analysis'!D62</f>
-        <v/>
-      </c>
-      <c r="T8" s="46">
-        <f>'Competitive Analysis'!E62</f>
-        <v/>
-      </c>
-      <c r="U8" s="46">
-        <f>IFERROR(VALUE(RIGHT(T8,4))*4+MATCH(LEFT(T8,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V8" s="46">
-        <f>IF(S8="","",IF(U8&lt;=$E$4,0,MAX(1,INT((U8-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>Base Annual Absorption</t>
-        </is>
-      </c>
-      <c r="C9" s="48" t="n">
-        <v>2525</v>
-      </c>
-      <c r="R9" s="44">
-        <f>'Competitive Analysis'!C63</f>
-        <v/>
-      </c>
-      <c r="S9" s="45">
-        <f>'Competitive Analysis'!D63</f>
-        <v/>
-      </c>
-      <c r="T9" s="46">
-        <f>'Competitive Analysis'!E63</f>
-        <v/>
-      </c>
-      <c r="U9" s="46">
-        <f>IFERROR(VALUE(RIGHT(T9,4))*4+MATCH(LEFT(T9,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V9" s="46">
-        <f>IF(S9="","",IF(U9&lt;=$E$4,0,MAX(1,INT((U9-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>Bull Annual Absorption</t>
-        </is>
-      </c>
-      <c r="C10" s="48" t="n">
-        <v>3800</v>
-      </c>
-      <c r="R10" s="44">
-        <f>'Competitive Analysis'!C65</f>
-        <v/>
-      </c>
-      <c r="S10" s="45">
-        <f>'Competitive Analysis'!D65</f>
-        <v/>
-      </c>
-      <c r="T10" s="46">
-        <f>'Competitive Analysis'!E65</f>
-        <v/>
-      </c>
-      <c r="U10" s="46">
-        <f>IFERROR(VALUE(RIGHT(T10,4))*4+MATCH(LEFT(T10,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V10" s="46">
-        <f>IF(S10="","",IF(U10&lt;=$E$4,0,MAX(1,INT((U10-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>Selected Annual Demand</t>
-        </is>
-      </c>
-      <c r="C11" s="49">
-        <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
-        <v/>
-      </c>
-      <c r="R11" s="44">
-        <f>'Competitive Analysis'!C61</f>
-        <v/>
-      </c>
-      <c r="S11" s="45">
-        <f>'Competitive Analysis'!D61</f>
-        <v/>
-      </c>
-      <c r="T11" s="46">
-        <f>'Competitive Analysis'!E61</f>
-        <v/>
-      </c>
-      <c r="U11" s="46">
-        <f>IFERROR(VALUE(RIGHT(T11,4))*4+MATCH(LEFT(T11,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V11" s="46">
-        <f>IF(S11="","",IF(U11&lt;=$E$4,0,MAX(1,INT((U11-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="40" t="inlineStr">
-        <is>
-          <t>Occupied (as-of)</t>
-        </is>
-      </c>
-      <c r="C12" s="49" t="n">
-        <v>22585</v>
-      </c>
-      <c r="R12" s="44">
-        <f>'Competitive Analysis'!C68</f>
-        <v/>
-      </c>
-      <c r="S12" s="45">
-        <f>'Competitive Analysis'!D68</f>
-        <v/>
-      </c>
-      <c r="T12" s="46">
-        <f>'Competitive Analysis'!E68</f>
-        <v/>
-      </c>
-      <c r="U12" s="46">
-        <f>IFERROR(VALUE(RIGHT(T12,4))*4+MATCH(LEFT(T12,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V12" s="46">
-        <f>IF(S12="","",IF(U12&lt;=$E$4,0,MAX(1,INT((U12-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="40" t="inlineStr">
-        <is>
-          <t>Inventory (as-of)</t>
-        </is>
-      </c>
-      <c r="C13" s="49" t="n">
-        <v>26603</v>
-      </c>
-      <c r="R13" s="44">
-        <f>'Competitive Analysis'!C66</f>
-        <v/>
-      </c>
-      <c r="S13" s="45">
-        <f>'Competitive Analysis'!D66</f>
-        <v/>
-      </c>
-      <c r="T13" s="46">
-        <f>'Competitive Analysis'!E66</f>
-        <v/>
-      </c>
-      <c r="U13" s="46">
-        <f>IFERROR(VALUE(RIGHT(T13,4))*4+MATCH(LEFT(T13,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V13" s="46">
-        <f>IF(S13="","",IF(U13&lt;=$E$4,0,MAX(1,INT((U13-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="R14" s="44">
-        <f>'Competitive Analysis'!C67</f>
-        <v/>
-      </c>
-      <c r="S14" s="45">
-        <f>'Competitive Analysis'!D67</f>
-        <v/>
-      </c>
-      <c r="T14" s="46">
-        <f>'Competitive Analysis'!E67</f>
-        <v/>
-      </c>
-      <c r="U14" s="46">
-        <f>IFERROR(VALUE(RIGHT(T14,4))*4+MATCH(LEFT(T14,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="V14" s="46">
-        <f>IF(S14="","",IF(U14&lt;=$E$4,0,MAX(1,INT((U14-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="R16" s="39" t="inlineStr">
-        <is>
-          <t>PROPOSED PIPELINE (scenario toggle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>5-MILE MARKET</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>-Y6</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>-Y5</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>-Y4</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>-Y3</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>-Y2</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>-Y1</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Y0</t>
-        </is>
-      </c>
-      <c r="J17" s="50" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K17" s="50" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L17" s="50" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M17" s="50" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N17" s="50" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O17" s="50" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="R17" s="42" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="S17" s="42" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="T17" s="42" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="U17" s="42" t="inlineStr">
-        <is>
-          <t>Built In</t>
-        </is>
-      </c>
-      <c r="V17" s="42" t="inlineStr">
-        <is>
-          <t>DelivIdx</t>
-        </is>
-      </c>
-      <c r="W17" s="42" t="inlineStr">
-        <is>
-          <t>HoldYr</t>
-        </is>
-      </c>
-      <c r="X17" s="42" t="inlineStr">
-        <is>
-          <t>Built?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2019–Q2 2020</t>
-        </is>
-      </c>
-      <c r="D18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2020–Q2 2021</t>
-        </is>
-      </c>
-      <c r="E18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2021–Q2 2022</t>
-        </is>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2022–Q2 2023</t>
-        </is>
-      </c>
-      <c r="G18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2023–Q2 2024</t>
-        </is>
-      </c>
-      <c r="H18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2024–Q2 2025</t>
-        </is>
-      </c>
-      <c r="I18" s="51" t="inlineStr">
-        <is>
-          <t>Q3 2025–Q2 2026</t>
-        </is>
-      </c>
-      <c r="J18" s="51" t="inlineStr">
-        <is>
-          <t>Hold Yr 1</t>
-        </is>
-      </c>
-      <c r="K18" s="51" t="inlineStr">
-        <is>
-          <t>Hold Yr 2</t>
-        </is>
-      </c>
-      <c r="L18" s="51" t="inlineStr">
-        <is>
-          <t>Hold Yr 3</t>
-        </is>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>Hold Yr 4</t>
-        </is>
-      </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>Hold Yr 5</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="inlineStr">
-        <is>
-          <t>Hold Yr 6</t>
-        </is>
-      </c>
-      <c r="R18" s="44" t="inlineStr">
-        <is>
-          <t>Sheely Center Future Phase</t>
-        </is>
-      </c>
-      <c r="S18" s="45" t="n">
-        <v>697</v>
-      </c>
-      <c r="T18" s="52" t="inlineStr"/>
-      <c r="U18" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V18" s="46">
-        <f>IFERROR(VALUE(RIGHT(T18,4))*4+MATCH(LEFT(T18,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W18" s="46">
-        <f>IF(V18="","",IF(V18&lt;=$E$4,0,MAX(1,INT((V18-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X18" s="46">
-        <f>IF(U18="None",0,IF($E$6&gt;=IF(U18="Bear",3,IF(U18="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>NEW SUPPLY (5-mi)</t>
-        </is>
-      </c>
-      <c r="C19" s="53" t="n">
-        <v>1133</v>
-      </c>
-      <c r="D19" s="53" t="n">
-        <v>1860</v>
-      </c>
-      <c r="E19" s="53" t="n">
-        <v>1336</v>
-      </c>
-      <c r="F19" s="53" t="n">
-        <v>2280</v>
-      </c>
-      <c r="G19" s="53" t="n">
-        <v>2823</v>
-      </c>
-      <c r="H19" s="53" t="n">
-        <v>4043</v>
-      </c>
-      <c r="I19" s="53" t="n">
-        <v>1860</v>
-      </c>
-      <c r="J19" s="54">
-        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,1)+SUMIFS($S$18:$S$61,$W$18:$W$61,1,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="K19" s="54">
-        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,2)+SUMIFS($S$18:$S$61,$W$18:$W$61,2,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="L19" s="54">
-        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,3)+SUMIFS($S$18:$S$61,$W$18:$W$61,3,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="M19" s="54">
-        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,4)+SUMIFS($S$18:$S$61,$W$18:$W$61,4,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="N19" s="54">
-        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,5)+SUMIFS($S$18:$S$61,$W$18:$W$61,5,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="O19" s="54">
-        <f>SUMIFS($S$5:$S$14,$V$5:$V$14,6)+SUMIFS($S$18:$S$61,$W$18:$W$61,6,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="R19" s="44" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel C</t>
-        </is>
-      </c>
-      <c r="S19" s="45" t="n">
-        <v>500</v>
-      </c>
-      <c r="T19" s="52" t="inlineStr"/>
-      <c r="U19" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V19" s="46">
-        <f>IFERROR(VALUE(RIGHT(T19,4))*4+MATCH(LEFT(T19,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W19" s="46">
-        <f>IF(V19="","",IF(V19&lt;=$E$4,0,MAX(1,INT((V19-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X19" s="46">
-        <f>IF(U19="None",0,IF($E$6&gt;=IF(U19="Bear",3,IF(U19="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="40" t="inlineStr">
-        <is>
-          <t>ABSORPTION (5-mi)</t>
-        </is>
-      </c>
-      <c r="C20" s="53" t="n">
-        <v>719</v>
-      </c>
-      <c r="D20" s="53" t="n">
-        <v>1876</v>
-      </c>
-      <c r="E20" s="53" t="n">
-        <v>1210</v>
-      </c>
-      <c r="F20" s="53" t="n">
-        <v>685</v>
-      </c>
-      <c r="G20" s="53" t="n">
-        <v>2514</v>
-      </c>
-      <c r="H20" s="53" t="n">
-        <v>2655</v>
-      </c>
-      <c r="I20" s="53" t="n">
-        <v>2369</v>
-      </c>
-      <c r="J20" s="54">
-        <f>J29-I29</f>
-        <v/>
-      </c>
-      <c r="K20" s="54">
-        <f>K29-J29</f>
-        <v/>
-      </c>
-      <c r="L20" s="54">
-        <f>L29-K29</f>
-        <v/>
-      </c>
-      <c r="M20" s="54">
-        <f>M29-L29</f>
-        <v/>
-      </c>
-      <c r="N20" s="54">
-        <f>N29-M29</f>
-        <v/>
-      </c>
-      <c r="O20" s="54">
-        <f>O29-N29</f>
-        <v/>
-      </c>
-      <c r="R20" s="44" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel B</t>
-        </is>
-      </c>
-      <c r="S20" s="45" t="n">
-        <v>478</v>
-      </c>
-      <c r="T20" s="52" t="inlineStr"/>
-      <c r="U20" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V20" s="46">
-        <f>IFERROR(VALUE(RIGHT(T20,4))*4+MATCH(LEFT(T20,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W20" s="46">
-        <f>IF(V20="","",IF(V20&lt;=$E$4,0,MAX(1,INT((V20-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X20" s="46">
-        <f>IF(U20="None",0,IF($E$6&gt;=IF(U20="Bear",3,IF(U20="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>OCCUPANCY (5-mi)</t>
-        </is>
-      </c>
-      <c r="C21" s="55" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="D21" s="55" t="n">
-        <v>0.922</v>
-      </c>
-      <c r="E21" s="55" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="F21" s="55" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="G21" s="55" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="H21" s="55" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="I21" s="55" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="J21" s="56">
-        <f>IFERROR(J29/J28,0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="56">
-        <f>IFERROR(K29/K28,0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="56">
-        <f>IFERROR(L29/L28,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="56">
-        <f>IFERROR(M29/M28,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="56">
-        <f>IFERROR(N29/N28,0)</f>
-        <v/>
-      </c>
-      <c r="O21" s="56">
-        <f>IFERROR(O29/O28,0)</f>
-        <v/>
-      </c>
-      <c r="R21" s="44" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel B</t>
-        </is>
-      </c>
-      <c r="S21" s="45" t="n">
-        <v>410</v>
-      </c>
-      <c r="T21" s="52" t="inlineStr"/>
-      <c r="U21" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V21" s="46">
-        <f>IFERROR(VALUE(RIGHT(T21,4))*4+MATCH(LEFT(T21,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W21" s="46">
-        <f>IF(V21="","",IF(V21&lt;=$E$4,0,MAX(1,INT((V21-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X21" s="46">
-        <f>IF(U21="None",0,IF($E$6&gt;=IF(U21="Bear",3,IF(U21="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="40" t="inlineStr">
-        <is>
-          <t>CUM. UNABSORBED (since -Y3)</t>
-        </is>
-      </c>
-      <c r="C22" s="57" t="n"/>
-      <c r="D22" s="57" t="n"/>
-      <c r="E22" s="57" t="n"/>
-      <c r="F22" s="57">
-        <f>F19-F20</f>
-        <v/>
-      </c>
-      <c r="G22" s="57">
-        <f>F22+G19-G20</f>
-        <v/>
-      </c>
-      <c r="H22" s="57">
-        <f>G22+H19-H20</f>
-        <v/>
-      </c>
-      <c r="I22" s="57">
-        <f>H22+I19-I20</f>
-        <v/>
-      </c>
-      <c r="J22" s="57">
-        <f>I22+J19-J20</f>
-        <v/>
-      </c>
-      <c r="K22" s="57">
-        <f>J22+K19-K20</f>
-        <v/>
-      </c>
-      <c r="L22" s="57">
-        <f>K22+L19-L20</f>
-        <v/>
-      </c>
-      <c r="M22" s="57">
-        <f>L22+M19-M20</f>
-        <v/>
-      </c>
-      <c r="N22" s="57">
-        <f>M22+N19-N20</f>
-        <v/>
-      </c>
-      <c r="O22" s="57">
-        <f>N22+O19-O20</f>
-        <v/>
-      </c>
-      <c r="R22" s="44" t="inlineStr">
-        <is>
-          <t>The District at Westgate</t>
-        </is>
-      </c>
-      <c r="S22" s="45" t="n">
-        <v>384</v>
-      </c>
-      <c r="T22" s="52" t="inlineStr"/>
-      <c r="U22" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V22" s="46">
-        <f>IFERROR(VALUE(RIGHT(T22,4))*4+MATCH(LEFT(T22,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W22" s="46">
-        <f>IF(V22="","",IF(V22&lt;=$E$4,0,MAX(1,INT((V22-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X22" s="46">
-        <f>IF(U22="None",0,IF($E$6&gt;=IF(U22="Bear",3,IF(U22="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>SUBJECT (Bella Mirage)</t>
-        </is>
-      </c>
-      <c r="R23" s="44" t="inlineStr">
-        <is>
-          <t>Picerne at Palm Valley</t>
-        </is>
-      </c>
-      <c r="S23" s="45" t="n">
-        <v>383</v>
-      </c>
-      <c r="T23" s="52" t="inlineStr"/>
-      <c r="U23" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V23" s="46">
-        <f>IFERROR(VALUE(RIGHT(T23,4))*4+MATCH(LEFT(T23,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W23" s="46">
-        <f>IF(V23="","",IF(V23&lt;=$E$4,0,MAX(1,INT((V23-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X23" s="46">
-        <f>IF(U23="None",0,IF($E$6&gt;=IF(U23="Bear",3,IF(U23="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Market Rent  (HD→CoStar)</t>
-        </is>
-      </c>
-      <c r="C24" s="58" t="n">
-        <v>1088</v>
-      </c>
-      <c r="D24" s="58" t="n">
-        <v>1437</v>
-      </c>
-      <c r="E24" s="58" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F24" s="58" t="n">
-        <v>1572</v>
-      </c>
-      <c r="G24" s="58" t="n">
-        <v>1497</v>
-      </c>
-      <c r="H24" s="58" t="n">
-        <v>1444</v>
-      </c>
-      <c r="I24" s="58" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J24" s="59" t="n"/>
-      <c r="K24" s="59" t="n"/>
-      <c r="L24" s="59" t="n"/>
-      <c r="M24" s="59" t="n"/>
-      <c r="N24" s="59" t="n"/>
-      <c r="O24" s="59" t="n"/>
-      <c r="R24" s="44" t="inlineStr">
-        <is>
-          <t>Liv Avondale</t>
-        </is>
-      </c>
-      <c r="S24" s="45" t="n">
-        <v>333</v>
-      </c>
-      <c r="T24" s="52" t="inlineStr"/>
-      <c r="U24" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V24" s="46">
-        <f>IFERROR(VALUE(RIGHT(T24,4))*4+MATCH(LEFT(T24,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W24" s="46">
-        <f>IF(V24="","",IF(V24&lt;=$E$4,0,MAX(1,INT((V24-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X24" s="46">
-        <f>IF(U24="None",0,IF($E$6&gt;=IF(U24="Bear",3,IF(U24="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Effective Rent</t>
-        </is>
-      </c>
-      <c r="C25" s="58" t="n">
-        <v>1086</v>
-      </c>
-      <c r="D25" s="58" t="n">
-        <v>1434</v>
-      </c>
-      <c r="E25" s="58" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F25" s="58" t="n">
-        <v>1555</v>
-      </c>
-      <c r="G25" s="58" t="n">
-        <v>1402</v>
-      </c>
-      <c r="H25" s="58" t="n">
-        <v>1369</v>
-      </c>
-      <c r="I25" s="58" t="n">
-        <v>1301</v>
-      </c>
-      <c r="J25" s="59" t="n"/>
-      <c r="K25" s="59" t="n"/>
-      <c r="L25" s="59" t="n"/>
-      <c r="M25" s="59" t="n"/>
-      <c r="N25" s="59" t="n"/>
-      <c r="O25" s="59" t="n"/>
-      <c r="R25" s="44" t="inlineStr">
-        <is>
-          <t>Urban 95 Parcel A</t>
-        </is>
-      </c>
-      <c r="S25" s="45" t="n">
-        <v>324</v>
-      </c>
-      <c r="T25" s="52" t="inlineStr"/>
-      <c r="U25" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V25" s="46">
-        <f>IFERROR(VALUE(RIGHT(T25,4))*4+MATCH(LEFT(T25,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W25" s="46">
-        <f>IF(V25="","",IF(V25&lt;=$E$4,0,MAX(1,INT((V25-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X25" s="46">
-        <f>IF(U25="None",0,IF($E$6&gt;=IF(U25="Bear",3,IF(U25="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Occupancy (T12 financials)</t>
-        </is>
-      </c>
-      <c r="C26" s="60" t="n"/>
-      <c r="D26" s="60" t="n"/>
-      <c r="E26" s="60" t="n"/>
-      <c r="F26" s="60" t="n">
-        <v>0.8788971182681028</v>
-      </c>
-      <c r="G26" s="60" t="n">
-        <v>0.9173713229249606</v>
-      </c>
-      <c r="H26" s="60" t="n">
-        <v>0.9334854638634199</v>
-      </c>
-      <c r="I26" s="60" t="n">
-        <v>0.9206643232607364</v>
-      </c>
-      <c r="J26" s="61" t="n"/>
-      <c r="K26" s="61" t="n"/>
-      <c r="L26" s="61" t="n"/>
-      <c r="M26" s="61" t="n"/>
-      <c r="N26" s="61" t="n"/>
-      <c r="O26" s="61" t="n"/>
-      <c r="R26" s="44" t="inlineStr">
-        <is>
-          <t>The Waverly</t>
-        </is>
-      </c>
-      <c r="S26" s="45" t="n">
-        <v>323</v>
-      </c>
-      <c r="T26" s="52" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U26" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V26" s="46">
-        <f>IFERROR(VALUE(RIGHT(T26,4))*4+MATCH(LEFT(T26,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W26" s="46">
-        <f>IF(V26="","",IF(V26&lt;=$E$4,0,MAX(1,INT((V26-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X26" s="46">
-        <f>IF(U26="None",0,IF($E$6&gt;=IF(U26="Bear",3,IF(U26="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="R27" s="44" t="inlineStr">
-        <is>
-          <t>Fuze 623</t>
-        </is>
-      </c>
-      <c r="S27" s="45" t="n">
-        <v>321</v>
-      </c>
-      <c r="T27" s="52" t="inlineStr"/>
-      <c r="U27" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V27" s="46">
-        <f>IFERROR(VALUE(RIGHT(T27,4))*4+MATCH(LEFT(T27,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W27" s="46">
-        <f>IF(V27="","",IF(V27&lt;=$E$4,0,MAX(1,INT((V27-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X27" s="46">
-        <f>IF(U27="None",0,IF($E$6&gt;=IF(U27="Bear",3,IF(U27="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" hidden="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  inventory</t>
-        </is>
-      </c>
-      <c r="C28" s="57" t="n">
-        <v>12401</v>
-      </c>
-      <c r="D28" s="57" t="n">
-        <v>14261</v>
-      </c>
-      <c r="E28" s="57" t="n">
-        <v>15597</v>
-      </c>
-      <c r="F28" s="57" t="n">
-        <v>17877</v>
-      </c>
-      <c r="G28" s="57" t="n">
-        <v>20700</v>
-      </c>
-      <c r="H28" s="57" t="n">
-        <v>24743</v>
-      </c>
-      <c r="I28" s="57" t="n">
-        <v>26603</v>
-      </c>
-      <c r="J28" s="57">
-        <f>I28+J19</f>
-        <v/>
-      </c>
-      <c r="K28" s="57">
-        <f>J28+K19</f>
-        <v/>
-      </c>
-      <c r="L28" s="57">
-        <f>K28+L19</f>
-        <v/>
-      </c>
-      <c r="M28" s="57">
-        <f>L28+M19</f>
-        <v/>
-      </c>
-      <c r="N28" s="57">
-        <f>M28+N19</f>
-        <v/>
-      </c>
-      <c r="O28" s="57">
-        <f>N28+O19</f>
-        <v/>
-      </c>
-      <c r="R28" s="44" t="inlineStr">
-        <is>
-          <t>Anton Glendale</t>
-        </is>
-      </c>
-      <c r="S28" s="45" t="n">
-        <v>320</v>
-      </c>
-      <c r="T28" s="52" t="inlineStr"/>
-      <c r="U28" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V28" s="46">
-        <f>IFERROR(VALUE(RIGHT(T28,4))*4+MATCH(LEFT(T28,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W28" s="46">
-        <f>IF(V28="","",IF(V28&lt;=$E$4,0,MAX(1,INT((V28-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X28" s="46">
-        <f>IF(U28="None",0,IF($E$6&gt;=IF(U28="Bear",3,IF(U28="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" hidden="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  occupied</t>
-        </is>
-      </c>
-      <c r="C29" s="57" t="n">
-        <v>11277</v>
-      </c>
-      <c r="D29" s="57" t="n">
-        <v>13152</v>
-      </c>
-      <c r="E29" s="57" t="n">
-        <v>14362</v>
-      </c>
-      <c r="F29" s="57" t="n">
-        <v>15047</v>
-      </c>
-      <c r="G29" s="57" t="n">
-        <v>17560</v>
-      </c>
-      <c r="H29" s="57" t="n">
-        <v>20215</v>
-      </c>
-      <c r="I29" s="57" t="n">
-        <v>22585</v>
-      </c>
-      <c r="J29" s="57">
-        <f>MIN($C$6*J28,I29+$C$11)</f>
-        <v/>
-      </c>
-      <c r="K29" s="57">
-        <f>MIN($C$6*K28,J29+$C$11)</f>
-        <v/>
-      </c>
-      <c r="L29" s="57">
-        <f>MIN($C$6*L28,K29+$C$11)</f>
-        <v/>
-      </c>
-      <c r="M29" s="57">
-        <f>MIN($C$6*M28,L29+$C$11)</f>
-        <v/>
-      </c>
-      <c r="N29" s="57">
-        <f>MIN($C$6*N28,M29+$C$11)</f>
-        <v/>
-      </c>
-      <c r="O29" s="57">
-        <f>MIN($C$6*O28,N29+$C$11)</f>
-        <v/>
-      </c>
-      <c r="R29" s="44" t="inlineStr">
-        <is>
-          <t>Western Garden II</t>
-        </is>
-      </c>
-      <c r="S29" s="45" t="n">
-        <v>314</v>
-      </c>
-      <c r="T29" s="52" t="inlineStr"/>
-      <c r="U29" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V29" s="46">
-        <f>IFERROR(VALUE(RIGHT(T29,4))*4+MATCH(LEFT(T29,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W29" s="46">
-        <f>IF(V29="","",IF(V29&lt;=$E$4,0,MAX(1,INT((V29-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X29" s="46">
-        <f>IF(U29="None",0,IF($E$6&gt;=IF(U29="Bear",3,IF(U29="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="R30" s="44" t="inlineStr">
-        <is>
-          <t>Sanctuair at Centerscape</t>
-        </is>
-      </c>
-      <c r="S30" s="45" t="n">
-        <v>303</v>
-      </c>
-      <c r="T30" s="52" t="inlineStr"/>
-      <c r="U30" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V30" s="46">
-        <f>IFERROR(VALUE(RIGHT(T30,4))*4+MATCH(LEFT(T30,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W30" s="46">
-        <f>IF(V30="","",IF(V30&lt;=$E$4,0,MAX(1,INT((V30-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X30" s="46">
-        <f>IF(U30="None",0,IF($E$6&gt;=IF(U30="Bear",3,IF(U30="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="40" t="inlineStr">
-        <is>
-          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
-        </is>
-      </c>
-      <c r="J31" s="62" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K31" s="62" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L31" s="62" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M31" s="62" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N31" s="62" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O31" s="62" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="R31" s="44" t="inlineStr">
-        <is>
-          <t>Encore Avondale</t>
-        </is>
-      </c>
-      <c r="S31" s="45" t="n">
-        <v>300</v>
-      </c>
-      <c r="T31" s="52" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U31" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V31" s="46">
-        <f>IFERROR(VALUE(RIGHT(T31,4))*4+MATCH(LEFT(T31,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W31" s="46">
-        <f>IF(V31="","",IF(V31&lt;=$E$4,0,MAX(1,INT((V31-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X31" s="46">
-        <f>IF(U31="None",0,IF($E$6&gt;=IF(U31="Bear",3,IF(U31="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="40" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J32" s="63">
-        <f>MIN($C$6,($C$12+$C$8*1)/J28)</f>
-        <v/>
-      </c>
-      <c r="K32" s="63">
-        <f>MIN($C$6,($C$12+$C$8*2)/K28)</f>
-        <v/>
-      </c>
-      <c r="L32" s="63">
-        <f>MIN($C$6,($C$12+$C$8*3)/L28)</f>
-        <v/>
-      </c>
-      <c r="M32" s="63">
-        <f>MIN($C$6,($C$12+$C$8*4)/M28)</f>
-        <v/>
-      </c>
-      <c r="N32" s="63">
-        <f>MIN($C$6,($C$12+$C$8*5)/N28)</f>
-        <v/>
-      </c>
-      <c r="O32" s="63">
-        <f>MIN($C$6,($C$12+$C$8*6)/O28)</f>
-        <v/>
-      </c>
-      <c r="R32" s="44" t="inlineStr">
-        <is>
-          <t>Banyan Avondale</t>
-        </is>
-      </c>
-      <c r="S32" s="45" t="n">
-        <v>296</v>
-      </c>
-      <c r="T32" s="52" t="inlineStr"/>
-      <c r="U32" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V32" s="46">
-        <f>IFERROR(VALUE(RIGHT(T32,4))*4+MATCH(LEFT(T32,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W32" s="46">
-        <f>IF(V32="","",IF(V32&lt;=$E$4,0,MAX(1,INT((V32-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X32" s="46">
-        <f>IF(U32="None",0,IF($E$6&gt;=IF(U32="Bear",3,IF(U32="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="40" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J33" s="63">
-        <f>MIN($C$6,($C$12+$C$9*1)/J28)</f>
-        <v/>
-      </c>
-      <c r="K33" s="63">
-        <f>MIN($C$6,($C$12+$C$9*2)/K28)</f>
-        <v/>
-      </c>
-      <c r="L33" s="63">
-        <f>MIN($C$6,($C$12+$C$9*3)/L28)</f>
-        <v/>
-      </c>
-      <c r="M33" s="63">
-        <f>MIN($C$6,($C$12+$C$9*4)/M28)</f>
-        <v/>
-      </c>
-      <c r="N33" s="63">
-        <f>MIN($C$6,($C$12+$C$9*5)/N28)</f>
-        <v/>
-      </c>
-      <c r="O33" s="63">
-        <f>MIN($C$6,($C$12+$C$9*6)/O28)</f>
-        <v/>
-      </c>
-      <c r="R33" s="44" t="inlineStr">
-        <is>
-          <t>Rosilian Villas</t>
-        </is>
-      </c>
-      <c r="S33" s="45" t="n">
-        <v>291</v>
-      </c>
-      <c r="T33" s="52" t="inlineStr"/>
-      <c r="U33" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V33" s="46">
-        <f>IFERROR(VALUE(RIGHT(T33,4))*4+MATCH(LEFT(T33,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W33" s="46">
-        <f>IF(V33="","",IF(V33&lt;=$E$4,0,MAX(1,INT((V33-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X33" s="46">
-        <f>IF(U33="None",0,IF($E$6&gt;=IF(U33="Bear",3,IF(U33="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="40" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J34" s="63">
-        <f>MIN($C$6,($C$12+$C$10*1)/J28)</f>
-        <v/>
-      </c>
-      <c r="K34" s="63">
-        <f>MIN($C$6,($C$12+$C$10*2)/K28)</f>
-        <v/>
-      </c>
-      <c r="L34" s="63">
-        <f>MIN($C$6,($C$12+$C$10*3)/L28)</f>
-        <v/>
-      </c>
-      <c r="M34" s="63">
-        <f>MIN($C$6,($C$12+$C$10*4)/M28)</f>
-        <v/>
-      </c>
-      <c r="N34" s="63">
-        <f>MIN($C$6,($C$12+$C$10*5)/N28)</f>
-        <v/>
-      </c>
-      <c r="O34" s="63">
-        <f>MIN($C$6,($C$12+$C$10*6)/O28)</f>
-        <v/>
-      </c>
-      <c r="R34" s="44" t="inlineStr">
-        <is>
-          <t>The Statler at Estrella Parkway</t>
-        </is>
-      </c>
-      <c r="S34" s="45" t="n">
-        <v>284</v>
-      </c>
-      <c r="T34" s="52" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U34" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V34" s="46">
-        <f>IFERROR(VALUE(RIGHT(T34,4))*4+MATCH(LEFT(T34,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W34" s="46">
-        <f>IF(V34="","",IF(V34&lt;=$E$4,0,MAX(1,INT((V34-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X34" s="46">
-        <f>IF(U34="None",0,IF($E$6&gt;=IF(U34="Bear",3,IF(U34="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="R35" s="44" t="inlineStr">
-        <is>
-          <t>Orion Avondale</t>
-        </is>
-      </c>
-      <c r="S35" s="45" t="n">
-        <v>268</v>
-      </c>
-      <c r="T35" s="52" t="inlineStr"/>
-      <c r="U35" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V35" s="46">
-        <f>IFERROR(VALUE(RIGHT(T35,4))*4+MATCH(LEFT(T35,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W35" s="46">
-        <f>IF(V35="","",IF(V35&lt;=$E$4,0,MAX(1,INT((V35-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X35" s="46">
-        <f>IF(U35="None",0,IF($E$6&gt;=IF(U35="Bear",3,IF(U35="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="40" t="inlineStr">
-        <is>
-          <t>MARKET RENT GROWTH (editable assumptions)</t>
-        </is>
-      </c>
-      <c r="J36" s="64" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K36" s="64" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L36" s="64" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M36" s="64" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N36" s="64" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O36" s="64" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
-      </c>
-      <c r="R36" s="44" t="inlineStr">
-        <is>
-          <t>Tavalo at Avondale</t>
-        </is>
-      </c>
-      <c r="S36" s="45" t="n">
-        <v>266</v>
-      </c>
-      <c r="T36" s="52" t="inlineStr"/>
-      <c r="U36" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V36" s="46">
-        <f>IFERROR(VALUE(RIGHT(T36,4))*4+MATCH(LEFT(T36,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W36" s="46">
-        <f>IF(V36="","",IF(V36&lt;=$E$4,0,MAX(1,INT((V36-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X36" s="46">
-        <f>IF(U36="None",0,IF($E$6&gt;=IF(U36="Bear",3,IF(U36="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="40" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J37" s="65" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="K37" s="65" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="L37" s="65" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M37" s="65" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="N37" s="65" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O37" s="65" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="R37" s="44" t="inlineStr">
-        <is>
-          <t>Marbella Ranch East Future Phase</t>
-        </is>
-      </c>
-      <c r="S37" s="45" t="n">
-        <v>266</v>
-      </c>
-      <c r="T37" s="52" t="inlineStr"/>
-      <c r="U37" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V37" s="46">
-        <f>IFERROR(VALUE(RIGHT(T37,4))*4+MATCH(LEFT(T37,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W37" s="46">
-        <f>IF(V37="","",IF(V37&lt;=$E$4,0,MAX(1,INT((V37-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X37" s="46">
-        <f>IF(U37="None",0,IF($E$6&gt;=IF(U37="Bear",3,IF(U37="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J38" s="65" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K38" s="65" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L38" s="65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M38" s="65" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N38" s="65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O38" s="65" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="R38" s="44" t="inlineStr">
-        <is>
-          <t>Crystal Cove</t>
-        </is>
-      </c>
-      <c r="S38" s="45" t="n">
-        <v>260</v>
-      </c>
-      <c r="T38" s="52" t="inlineStr"/>
-      <c r="U38" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V38" s="46">
-        <f>IFERROR(VALUE(RIGHT(T38,4))*4+MATCH(LEFT(T38,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W38" s="46">
-        <f>IF(V38="","",IF(V38&lt;=$E$4,0,MAX(1,INT((V38-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X38" s="46">
-        <f>IF(U38="None",0,IF($E$6&gt;=IF(U38="Bear",3,IF(U38="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="40" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J39" s="65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K39" s="65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L39" s="65" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M39" s="65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N39" s="65" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O39" s="65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="R39" s="44" t="inlineStr">
-        <is>
-          <t>Cornerstone at the Wigwam</t>
-        </is>
-      </c>
-      <c r="S39" s="45" t="n">
-        <v>212</v>
-      </c>
-      <c r="T39" s="52" t="inlineStr"/>
-      <c r="U39" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V39" s="46">
-        <f>IFERROR(VALUE(RIGHT(T39,4))*4+MATCH(LEFT(T39,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W39" s="46">
-        <f>IF(V39="","",IF(V39&lt;=$E$4,0,MAX(1,INT((V39-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X39" s="46">
-        <f>IF(U39="None",0,IF($E$6&gt;=IF(U39="Bear",3,IF(U39="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>CONCESSIONS (months, editable)</t>
-        </is>
-      </c>
-      <c r="R40" s="44" t="inlineStr">
-        <is>
-          <t>Radia Avondale Station III</t>
-        </is>
-      </c>
-      <c r="S40" s="45" t="n">
-        <v>212</v>
-      </c>
-      <c r="T40" s="52" t="inlineStr"/>
-      <c r="U40" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V40" s="46">
-        <f>IFERROR(VALUE(RIGHT(T40,4))*4+MATCH(LEFT(T40,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W40" s="46">
-        <f>IF(V40="","",IF(V40&lt;=$E$4,0,MAX(1,INT((V40-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X40" s="46">
-        <f>IF(U40="None",0,IF($E$6&gt;=IF(U40="Bear",3,IF(U40="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J41" s="65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K41" s="65" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L41" s="65" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="M41" s="65" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="N41" s="65" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O41" s="65" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="R41" s="44" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel A</t>
-        </is>
-      </c>
-      <c r="S41" s="45" t="n">
-        <v>181</v>
-      </c>
-      <c r="T41" s="52" t="inlineStr"/>
-      <c r="U41" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V41" s="46">
-        <f>IFERROR(VALUE(RIGHT(T41,4))*4+MATCH(LEFT(T41,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W41" s="46">
-        <f>IF(V41="","",IF(V41&lt;=$E$4,0,MAX(1,INT((V41-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X41" s="46">
-        <f>IF(U41="None",0,IF($E$6&gt;=IF(U41="Bear",3,IF(U41="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="40" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J42" s="65" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K42" s="65" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L42" s="65" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M42" s="65" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N42" s="65" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O42" s="65" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="R42" s="44" t="inlineStr">
-        <is>
-          <t>Villages at River Grove</t>
-        </is>
-      </c>
-      <c r="S42" s="45" t="n">
-        <v>180</v>
-      </c>
-      <c r="T42" s="52" t="inlineStr"/>
-      <c r="U42" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V42" s="46">
-        <f>IFERROR(VALUE(RIGHT(T42,4))*4+MATCH(LEFT(T42,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W42" s="46">
-        <f>IF(V42="","",IF(V42&lt;=$E$4,0,MAX(1,INT((V42-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X42" s="46">
-        <f>IF(U42="None",0,IF($E$6&gt;=IF(U42="Bear",3,IF(U42="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="40" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J43" s="65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K43" s="65" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L43" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="44" t="inlineStr">
-        <is>
-          <t>District 99</t>
-        </is>
-      </c>
-      <c r="S43" s="45" t="n">
-        <v>172</v>
-      </c>
-      <c r="T43" s="52" t="inlineStr"/>
-      <c r="U43" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V43" s="46">
-        <f>IFERROR(VALUE(RIGHT(T43,4))*4+MATCH(LEFT(T43,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W43" s="46">
-        <f>IF(V43="","",IF(V43&lt;=$E$4,0,MAX(1,INT((V43-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X43" s="46">
-        <f>IF(U43="None",0,IF($E$6&gt;=IF(U43="Bear",3,IF(U43="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="40" t="inlineStr">
-        <is>
-          <t>EFFECTIVE RENT GROWTH (derived)</t>
-        </is>
-      </c>
-      <c r="R44" s="44" t="inlineStr">
-        <is>
-          <t>McDowell Villas</t>
-        </is>
-      </c>
-      <c r="S44" s="45" t="n">
-        <v>164</v>
-      </c>
-      <c r="T44" s="52" t="inlineStr"/>
-      <c r="U44" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V44" s="46">
-        <f>IFERROR(VALUE(RIGHT(T44,4))*4+MATCH(LEFT(T44,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W44" s="46">
-        <f>IF(V44="","",IF(V44&lt;=$E$4,0,MAX(1,INT((V44-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X44" s="46">
-        <f>IF(U44="None",0,IF($E$6&gt;=IF(U44="Bear",3,IF(U44="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="40" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J45" s="63">
-        <f>(1+J37)*(1-J41)-1</f>
-        <v/>
-      </c>
-      <c r="K45" s="63">
-        <f>(1+K37)*(1-K41)/(1-J41)-1</f>
-        <v/>
-      </c>
-      <c r="L45" s="63">
-        <f>(1+L37)*(1-L41)/(1-K41)-1</f>
-        <v/>
-      </c>
-      <c r="M45" s="63">
-        <f>(1+M37)*(1-M41)/(1-L41)-1</f>
-        <v/>
-      </c>
-      <c r="N45" s="63">
-        <f>(1+N37)*(1-N41)/(1-M41)-1</f>
-        <v/>
-      </c>
-      <c r="O45" s="63">
-        <f>(1+O37)*(1-O41)/(1-N41)-1</f>
-        <v/>
-      </c>
-      <c r="R45" s="44" t="inlineStr">
-        <is>
-          <t>Avondale</t>
-        </is>
-      </c>
-      <c r="S45" s="45" t="n">
-        <v>156</v>
-      </c>
-      <c r="T45" s="52" t="inlineStr"/>
-      <c r="U45" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V45" s="46">
-        <f>IFERROR(VALUE(RIGHT(T45,4))*4+MATCH(LEFT(T45,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W45" s="46">
-        <f>IF(V45="","",IF(V45&lt;=$E$4,0,MAX(1,INT((V45-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X45" s="46">
-        <f>IF(U45="None",0,IF($E$6&gt;=IF(U45="Bear",3,IF(U45="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="40" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J46" s="63">
-        <f>(1+J38)*(1-J42)-1</f>
-        <v/>
-      </c>
-      <c r="K46" s="63">
-        <f>(1+K38)*(1-K42)/(1-J42)-1</f>
-        <v/>
-      </c>
-      <c r="L46" s="63">
-        <f>(1+L38)*(1-L42)/(1-K42)-1</f>
-        <v/>
-      </c>
-      <c r="M46" s="63">
-        <f>(1+M38)*(1-M42)/(1-L42)-1</f>
-        <v/>
-      </c>
-      <c r="N46" s="63">
-        <f>(1+N38)*(1-N42)/(1-M42)-1</f>
-        <v/>
-      </c>
-      <c r="O46" s="63">
-        <f>(1+O38)*(1-O42)/(1-N42)-1</f>
-        <v/>
-      </c>
-      <c r="R46" s="44" t="inlineStr">
-        <is>
-          <t>Porter Kyle Development</t>
-        </is>
-      </c>
-      <c r="S46" s="45" t="n">
-        <v>135</v>
-      </c>
-      <c r="T46" s="52" t="inlineStr"/>
-      <c r="U46" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V46" s="46">
-        <f>IFERROR(VALUE(RIGHT(T46,4))*4+MATCH(LEFT(T46,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W46" s="46">
-        <f>IF(V46="","",IF(V46&lt;=$E$4,0,MAX(1,INT((V46-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X46" s="46">
-        <f>IF(U46="None",0,IF($E$6&gt;=IF(U46="Bear",3,IF(U46="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="40" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J47" s="63">
-        <f>(1+J39)*(1-J43)-1</f>
-        <v/>
-      </c>
-      <c r="K47" s="63">
-        <f>(1+K39)*(1-K43)/(1-J43)-1</f>
-        <v/>
-      </c>
-      <c r="L47" s="63">
-        <f>(1+L39)*(1-L43)/(1-K43)-1</f>
-        <v/>
-      </c>
-      <c r="M47" s="63">
-        <f>(1+M39)*(1-M43)/(1-L43)-1</f>
-        <v/>
-      </c>
-      <c r="N47" s="63">
-        <f>(1+N39)*(1-N43)/(1-M43)-1</f>
-        <v/>
-      </c>
-      <c r="O47" s="63">
-        <f>(1+O39)*(1-O43)/(1-N43)-1</f>
-        <v/>
-      </c>
-      <c r="R47" s="44" t="inlineStr">
-        <is>
-          <t>Ascent Goodyear</t>
-        </is>
-      </c>
-      <c r="S47" s="45" t="n">
-        <v>113</v>
-      </c>
-      <c r="T47" s="52" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U47" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V47" s="46">
-        <f>IFERROR(VALUE(RIGHT(T47,4))*4+MATCH(LEFT(T47,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W47" s="46">
-        <f>IF(V47="","",IF(V47&lt;=$E$4,0,MAX(1,INT((V47-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X47" s="46">
-        <f>IF(U47="None",0,IF($E$6&gt;=IF(U47="Bear",3,IF(U47="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>Reconciliation: UC pipeline scheduled = 1,947 units vs CoStar current Under Construction = 1,251 units.</t>
-        </is>
-      </c>
-      <c r="R48" s="44" t="inlineStr">
-        <is>
-          <t>Northern 107</t>
-        </is>
-      </c>
-      <c r="S48" s="45" t="n">
-        <v>74</v>
-      </c>
-      <c r="T48" s="52" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="U48" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V48" s="46">
-        <f>IFERROR(VALUE(RIGHT(T48,4))*4+MATCH(LEFT(T48,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W48" s="46">
-        <f>IF(V48="","",IF(V48&lt;=$E$4,0,MAX(1,INT((V48-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X48" s="46">
-        <f>IF(U48="None",0,IF($E$6&gt;=IF(U48="Bear",3,IF(U48="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="33" t="inlineStr">
-        <is>
-          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
-        </is>
-      </c>
-      <c r="R49" s="44" t="inlineStr">
-        <is>
-          <t>Zenn @ Sierra Verde</t>
-        </is>
-      </c>
-      <c r="S49" s="45" t="n">
-        <v>66</v>
-      </c>
-      <c r="T49" s="52" t="inlineStr"/>
-      <c r="U49" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V49" s="46">
-        <f>IFERROR(VALUE(RIGHT(T49,4))*4+MATCH(LEFT(T49,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W49" s="46">
-        <f>IF(V49="","",IF(V49&lt;=$E$4,0,MAX(1,INT((V49-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X49" s="46">
-        <f>IF(U49="None",0,IF($E$6&gt;=IF(U49="Bear",3,IF(U49="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
-        </is>
-      </c>
-      <c r="R50" s="44" t="inlineStr">
-        <is>
-          <t>The BLVD Residential District</t>
-        </is>
-      </c>
-      <c r="S50" s="45" t="n"/>
-      <c r="T50" s="52" t="inlineStr"/>
-      <c r="U50" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V50" s="46">
-        <f>IFERROR(VALUE(RIGHT(T50,4))*4+MATCH(LEFT(T50,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W50" s="46">
-        <f>IF(V50="","",IF(V50&lt;=$E$4,0,MAX(1,INT((V50-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X50" s="46">
-        <f>IF(U50="None",0,IF($E$6&gt;=IF(U50="Bear",3,IF(U50="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="R51" s="44" t="inlineStr">
-        <is>
-          <t>The BLVD Park Avenue District</t>
-        </is>
-      </c>
-      <c r="S51" s="45" t="n"/>
-      <c r="T51" s="52" t="inlineStr"/>
-      <c r="U51" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V51" s="46">
-        <f>IFERROR(VALUE(RIGHT(T51,4))*4+MATCH(LEFT(T51,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W51" s="46">
-        <f>IF(V51="","",IF(V51&lt;=$E$4,0,MAX(1,INT((V51-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X51" s="46">
-        <f>IF(U51="None",0,IF($E$6&gt;=IF(U51="Bear",3,IF(U51="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="R52" s="44" t="inlineStr">
-        <is>
-          <t>Globe Land Investors Development</t>
-        </is>
-      </c>
-      <c r="S52" s="45" t="n"/>
-      <c r="T52" s="52" t="inlineStr"/>
-      <c r="U52" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V52" s="46">
-        <f>IFERROR(VALUE(RIGHT(T52,4))*4+MATCH(LEFT(T52,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W52" s="46">
-        <f>IF(V52="","",IF(V52&lt;=$E$4,0,MAX(1,INT((V52-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X52" s="46">
-        <f>IF(U52="None",0,IF($E$6&gt;=IF(U52="Bear",3,IF(U52="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="R53" s="44" t="inlineStr">
-        <is>
-          <t>Ball Park</t>
-        </is>
-      </c>
-      <c r="S53" s="45" t="n"/>
-      <c r="T53" s="52" t="inlineStr"/>
-      <c r="U53" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V53" s="46">
-        <f>IFERROR(VALUE(RIGHT(T53,4))*4+MATCH(LEFT(T53,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W53" s="46">
-        <f>IF(V53="","",IF(V53&lt;=$E$4,0,MAX(1,INT((V53-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X53" s="46">
-        <f>IF(U53="None",0,IF($E$6&gt;=IF(U53="Bear",3,IF(U53="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="R54" s="44" t="inlineStr">
-        <is>
-          <t>Vision 2 Parcel A</t>
-        </is>
-      </c>
-      <c r="S54" s="45" t="n"/>
-      <c r="T54" s="52" t="inlineStr"/>
-      <c r="U54" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V54" s="46">
-        <f>IFERROR(VALUE(RIGHT(T54,4))*4+MATCH(LEFT(T54,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W54" s="46">
-        <f>IF(V54="","",IF(V54&lt;=$E$4,0,MAX(1,INT((V54-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X54" s="46">
-        <f>IF(U54="None",0,IF($E$6&gt;=IF(U54="Bear",3,IF(U54="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="R55" s="44" t="inlineStr">
-        <is>
-          <t>Firststreet Verde</t>
-        </is>
-      </c>
-      <c r="S55" s="45" t="n"/>
-      <c r="T55" s="52" t="inlineStr"/>
-      <c r="U55" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V55" s="46">
-        <f>IFERROR(VALUE(RIGHT(T55,4))*4+MATCH(LEFT(T55,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W55" s="46">
-        <f>IF(V55="","",IF(V55&lt;=$E$4,0,MAX(1,INT((V55-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X55" s="46">
-        <f>IF(U55="None",0,IF($E$6&gt;=IF(U55="Bear",3,IF(U55="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="R56" s="44" t="inlineStr">
-        <is>
-          <t>Goodyear Civic Square at Estrella Falls</t>
-        </is>
-      </c>
-      <c r="S56" s="45" t="n"/>
-      <c r="T56" s="52" t="inlineStr"/>
-      <c r="U56" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V56" s="46">
-        <f>IFERROR(VALUE(RIGHT(T56,4))*4+MATCH(LEFT(T56,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W56" s="46">
-        <f>IF(V56="","",IF(V56&lt;=$E$4,0,MAX(1,INT((V56-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X56" s="46">
-        <f>IF(U56="None",0,IF($E$6&gt;=IF(U56="Bear",3,IF(U56="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="R57" s="44" t="inlineStr">
-        <is>
-          <t>I-10 Innovation Center II</t>
-        </is>
-      </c>
-      <c r="S57" s="45" t="n"/>
-      <c r="T57" s="52" t="inlineStr"/>
-      <c r="U57" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V57" s="46">
-        <f>IFERROR(VALUE(RIGHT(T57,4))*4+MATCH(LEFT(T57,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W57" s="46">
-        <f>IF(V57="","",IF(V57&lt;=$E$4,0,MAX(1,INT((V57-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X57" s="46">
-        <f>IF(U57="None",0,IF($E$6&gt;=IF(U57="Bear",3,IF(U57="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="R58" s="44" t="inlineStr">
-        <is>
-          <t>Celebration Plaza Parcel D</t>
-        </is>
-      </c>
-      <c r="S58" s="45" t="n"/>
-      <c r="T58" s="52" t="inlineStr"/>
-      <c r="U58" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V58" s="46">
-        <f>IFERROR(VALUE(RIGHT(T58,4))*4+MATCH(LEFT(T58,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W58" s="46">
-        <f>IF(V58="","",IF(V58&lt;=$E$4,0,MAX(1,INT((V58-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X58" s="46">
-        <f>IF(U58="None",0,IF($E$6&gt;=IF(U58="Bear",3,IF(U58="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="R59" s="44" t="inlineStr">
-        <is>
-          <t>SimonMed Development II</t>
-        </is>
-      </c>
-      <c r="S59" s="45" t="n"/>
-      <c r="T59" s="52" t="inlineStr"/>
-      <c r="U59" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V59" s="46">
-        <f>IFERROR(VALUE(RIGHT(T59,4))*4+MATCH(LEFT(T59,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W59" s="46">
-        <f>IF(V59="","",IF(V59&lt;=$E$4,0,MAX(1,INT((V59-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X59" s="46">
-        <f>IF(U59="None",0,IF($E$6&gt;=IF(U59="Bear",3,IF(U59="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="R60" s="44" t="inlineStr">
-        <is>
-          <t>182 South 95th Avenue</t>
-        </is>
-      </c>
-      <c r="S60" s="45" t="n"/>
-      <c r="T60" s="52" t="inlineStr"/>
-      <c r="U60" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V60" s="46">
-        <f>IFERROR(VALUE(RIGHT(T60,4))*4+MATCH(LEFT(T60,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W60" s="46">
-        <f>IF(V60="","",IF(V60&lt;=$E$4,0,MAX(1,INT((V60-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X60" s="46">
-        <f>IF(U60="None",0,IF($E$6&gt;=IF(U60="Bear",3,IF(U60="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="R61" s="44" t="inlineStr">
-        <is>
-          <t>Envision Encore</t>
-        </is>
-      </c>
-      <c r="S61" s="45" t="n"/>
-      <c r="T61" s="52" t="inlineStr"/>
-      <c r="U61" s="52" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="V61" s="46">
-        <f>IFERROR(VALUE(RIGHT(T61,4))*4+MATCH(LEFT(T61,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W61" s="46">
-        <f>IF(V61="","",IF(V61&lt;=$E$4,0,MAX(1,INT((V61-$E$5)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X61" s="46">
-        <f>IF(U61="None",0,IF($E$6&gt;=IF(U61="Bear",3,IF(U61="Base",2,1)),1,0))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:O2"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Bear,Base,Bull"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Bear,Base,Bull,None"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,11 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
@@ -309,9 +314,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -333,9 +335,6 @@
     <xf numFmtId="164" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -355,6 +354,9 @@
     <xf numFmtId="164" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -365,6 +367,7 @@
     <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -836,39 +839,35 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>Luna Bear 94</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>185</v>
+        <v>94</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q1 2022</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.924324</v>
+        <v>0.989362</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>1750</v>
+        <v>1913</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Larson Capital Management</t>
+          <t>Luna Bear Properties LLC</t>
         </is>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>Rent: CoStar ask $1,750 vs RealPage eff $1,875</t>
-        </is>
-      </c>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="7" t="n">
@@ -876,26 +875,26 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Ironwood at River Run</t>
+          <t>Cyrene at Estrella</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q1 2022</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.961</v>
+        <v>0.984375</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>2090</v>
+        <v>2442</v>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Rockpoint Group</t>
+          <t>BGO</t>
         </is>
       </c>
       <c r="I7" s="7" t="n"/>
@@ -906,7 +905,7 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated</t>
+          <t>Year built: 2022/2023; Delivery quarter estimated; Rent: CoStar ask $2,442 vs RealPage eff $2,261</t>
         </is>
       </c>
     </row>
@@ -916,26 +915,26 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Prose Desert River</t>
+          <t>Sunset View Apartments</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>384</v>
+        <v>286</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Q1 2023</t>
+          <t>Q2 2022</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.895833</v>
+        <v>0.902098</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1429</v>
+        <v>1338</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Alliance Residential Company</t>
+          <t>Sunrise Multifamily LLC</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>
@@ -946,7 +945,7 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 90% vs RealPage 97%; Rent: CoStar ask $1,429 vs RealPage eff $1,313</t>
+          <t>Occ: CoStar 90% vs RealPage 96%; Rent: CoStar ask $1,338 vs RealPage eff $1,167</t>
         </is>
       </c>
     </row>
@@ -956,26 +955,26 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>District at Civic Square</t>
+          <t>Avari Apartments</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Q1 2023</t>
+          <t>Q3 2022</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.920455</v>
+        <v>0.951977</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>1526</v>
+        <v>1574</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Billah Khan</t>
+          <t>Brett C. &amp; Lorraine M. Heers</t>
         </is>
       </c>
       <c r="I9" s="7" t="n"/>
@@ -986,7 +985,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 92% vs RealPage 100%; Rent: CoStar ask $1,526 vs RealPage eff $1,263</t>
+          <t>Year built: 2022/2023; Delivery quarter estimated; Occ: CoStar 95% vs RealPage 100%</t>
         </is>
       </c>
     </row>
@@ -996,11 +995,11 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Acero Roosevelt</t>
+          <t>Prose Desert River</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -1008,14 +1007,14 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.892045</v>
+        <v>0.895833</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1632</v>
+        <v>1429</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>IDM Companies</t>
+          <t>Alliance Residential Company</t>
         </is>
       </c>
       <c r="I10" s="7" t="n"/>
@@ -1026,7 +1025,7 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 89% vs RealPage 94%; Rent: CoStar ask $1,632 vs RealPage eff $1,236</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 90% vs RealPage 97%; Rent: CoStar ask $1,429 vs RealPage eff $1,313</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1035,11 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Cabana Bullard</t>
+          <t>District at Civic Square</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -1048,25 +1047,25 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.9494050000000001</v>
+        <v>0.920455</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>1335</v>
+        <v>1526</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Greenlight Communities</t>
+          <t>Billah Khan</t>
         </is>
       </c>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 92% vs RealPage 100%; Rent: CoStar ask $1,526 vs RealPage eff $1,263</t>
         </is>
       </c>
     </row>
@@ -1076,11 +1075,11 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Bungalows at Camelback</t>
+          <t>Acero Roosevelt</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -1088,14 +1087,14 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.7634730000000001</v>
+        <v>0.892045</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>2026</v>
+        <v>1632</v>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Cavan Companies</t>
+          <t>IDM Companies</t>
         </is>
       </c>
       <c r="I12" s="7" t="n"/>
@@ -1106,7 +1105,7 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 76% vs RealPage 92%; Rent: CoStar ask $2,026 vs RealPage eff $1,385</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 89% vs RealPage 94%; Rent: CoStar ask $1,632 vs RealPage eff $1,236</t>
         </is>
       </c>
     </row>
@@ -1116,11 +1115,11 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Cuvee Apartments</t>
+          <t>Cabana Bullard</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1128,20 +1127,20 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.926</v>
+        <v>0.9494050000000001</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>1629</v>
+        <v>1335</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Pillar Communities</t>
+          <t>Greenlight Communities</t>
         </is>
       </c>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
@@ -1156,11 +1155,11 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Springs At Westgate</t>
+          <t>Bungalows at Camelback</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1168,14 +1167,14 @@
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0.784247</v>
+        <v>0.7634730000000001</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>1516</v>
+        <v>2026</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Continental Properties Company, Inc.</t>
+          <t>Cavan Companies</t>
         </is>
       </c>
       <c r="I14" s="7" t="n"/>
@@ -1186,7 +1185,7 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Units: CoStar 292 vs RealPage 239; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 87%</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 76% vs RealPage 92%; Rent: CoStar ask $2,026 vs RealPage eff $1,385</t>
         </is>
       </c>
     </row>
@@ -1196,11 +1195,11 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>BB Living at Civic Square</t>
+          <t>Cuvee Apartments</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1208,25 +1207,25 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.934483</v>
+        <v>0.926</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>2812</v>
+        <v>1629</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>BB Living</t>
+          <t>Pillar Communities</t>
         </is>
       </c>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 93% vs RealPage 96%; Rent: CoStar ask $2,812 vs RealPage eff $2,575</t>
+          <t>Delivery quarter estimated</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1235,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Village at Paseo de Luces</t>
+          <t>Springs At Westgate</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1248,14 +1247,14 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>0.926471</v>
+        <v>0.784247</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>1820</v>
+        <v>1516</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Empire Group of Companies</t>
+          <t>Continental Properties Company, Inc.</t>
         </is>
       </c>
       <c r="I16" s="7" t="n"/>
@@ -1266,7 +1265,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 93% vs RealPage 97%; Rent: CoStar ask $1,820 vs RealPage eff $1,597</t>
+          <t>Year built: 2023/2024; Units: CoStar 292 vs RealPage 239; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 87%</t>
         </is>
       </c>
     </row>
@@ -1276,11 +1275,11 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Parc Lofts</t>
+          <t>BB Living at Civic Square</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1288,25 +1287,25 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.8992249999999999</v>
+        <v>0.934483</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>1567</v>
+        <v>2812</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Millburn &amp; Company</t>
+          <t>BB Living</t>
         </is>
       </c>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 90% vs RealPage 94%</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 93% vs RealPage 96%; Rent: CoStar ask $2,812 vs RealPage eff $2,575</t>
         </is>
       </c>
     </row>
@@ -1316,11 +1315,11 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Christopher Todd Communities at McDowell</t>
+          <t>Village at Paseo de Luces</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -1328,14 +1327,14 @@
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.949309</v>
+        <v>0.926471</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>1576</v>
+        <v>1820</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Christopher Todd Communities</t>
+          <t>Empire Group of Companies</t>
         </is>
       </c>
       <c r="I18" s="7" t="n"/>
@@ -1346,7 +1345,7 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 93% vs RealPage 97%; Rent: CoStar ask $1,820 vs RealPage eff $1,597</t>
         </is>
       </c>
     </row>
@@ -1356,11 +1355,11 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Village Camelback Park</t>
+          <t>Parc Lofts</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1368,25 +1367,25 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.773196</v>
+        <v>0.8992249999999999</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>1874</v>
+        <v>1567</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>The Empire Group</t>
+          <t>Millburn &amp; Company</t>
         </is>
       </c>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 77% vs RealPage 92%</t>
+          <t>Delivery quarter estimated; Occ: CoStar 90% vs RealPage 94%</t>
         </is>
       </c>
     </row>
@@ -1396,11 +1395,11 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Village at the BLVD</t>
+          <t>Christopher Todd Communities at McDowell</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -1408,25 +1407,25 @@
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>0.935829</v>
+        <v>0.949309</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>1964</v>
+        <v>1576</v>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Empire Group of Companies</t>
+          <t>Christopher Todd Communities</t>
         </is>
       </c>
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 94% vs RealPage 96%</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated</t>
         </is>
       </c>
     </row>
@@ -1436,11 +1435,11 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>The Crofton at Sheely Farms</t>
+          <t>Village Camelback Park</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -1448,25 +1447,25 @@
         </is>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.9520960000000001</v>
+        <v>0.773196</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>1607</v>
+        <v>1874</v>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Atlantic Creek Real Estate Partners</t>
+          <t>The Empire Group</t>
         </is>
       </c>
       <c r="I21" s="7" t="n"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Rent: CoStar ask $1,607 vs RealPage eff $1,388</t>
+          <t>Delivery quarter estimated; Occ: CoStar 77% vs RealPage 92%</t>
         </is>
       </c>
     </row>
@@ -1476,11 +1475,11 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>TerraLane at Park McDowell</t>
+          <t>Village at the BLVD</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -1488,25 +1487,25 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>0.8518520000000001</v>
+        <v>0.935829</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>1576</v>
+        <v>1964</v>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>TerraLane Communities</t>
+          <t>Empire Group of Companies</t>
         </is>
       </c>
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 85% vs RealPage 88%; Rent: CoStar ask $1,576 vs RealPage eff $1,211</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 94% vs RealPage 96%</t>
         </is>
       </c>
     </row>
@@ -1516,11 +1515,11 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Ironwood Homes at River Run</t>
+          <t>The Crofton at Sheely Farms</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -1528,14 +1527,14 @@
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>0.893204</v>
+        <v>0.9520960000000001</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>2523</v>
+        <v>1607</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Sunstone Properties Trust</t>
+          <t>Atlantic Creek Real Estate Partners</t>
         </is>
       </c>
       <c r="I23" s="7" t="n"/>
@@ -1546,7 +1545,7 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated</t>
+          <t>Delivery quarter estimated; Rent: CoStar ask $1,607 vs RealPage eff $1,388</t>
         </is>
       </c>
     </row>
@@ -1556,37 +1555,37 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Avari Apartments</t>
+          <t>TerraLane at Park McDowell</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>354</v>
+        <v>162</v>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Q3 2022</t>
+          <t>Q1 2023</t>
         </is>
       </c>
       <c r="F24" s="10" t="n">
-        <v>0.951977</v>
+        <v>0.8518520000000001</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Brett C. &amp; Lorraine M. Heers</t>
+          <t>TerraLane Communities</t>
         </is>
       </c>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2022/2023; Delivery quarter estimated; Occ: CoStar 95% vs RealPage 100%</t>
+          <t>Delivery quarter estimated; Occ: CoStar 85% vs RealPage 88%; Rent: CoStar ask $1,576 vs RealPage eff $1,211</t>
         </is>
       </c>
     </row>
@@ -1596,26 +1595,26 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sunset View Apartments</t>
+          <t>Ironwood Homes at River Run</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Q2 2022</t>
+          <t>Q1 2023</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>0.902098</v>
+        <v>0.893204</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>1338</v>
+        <v>2523</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Sunrise Multifamily LLC</t>
+          <t>Sunstone Properties Trust</t>
         </is>
       </c>
       <c r="I25" s="7" t="n"/>
@@ -1626,7 +1625,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>Occ: CoStar 90% vs RealPage 96%; Rent: CoStar ask $1,338 vs RealPage eff $1,167</t>
+          <t>Delivery quarter estimated</t>
         </is>
       </c>
     </row>
@@ -1636,35 +1635,39 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Luna Bear 94</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Q1 2022</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.989362</v>
+        <v>0.924324</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>1913</v>
+        <v>1750</v>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Luna Bear Properties LLC</t>
+          <t>Larson Capital Management</t>
         </is>
       </c>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Single Family</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="n"/>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Rent: CoStar ask $1,750 vs RealPage eff $1,875</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="7" t="n">
@@ -1672,26 +1675,26 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Cyrene at Estrella</t>
+          <t>Ironwood at River Run</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Q1 2022</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>0.984375</v>
+        <v>0.961</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>2442</v>
+        <v>2090</v>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>BGO</t>
+          <t>Rockpoint Group</t>
         </is>
       </c>
       <c r="I27" s="7" t="n"/>
@@ -1702,7 +1705,7 @@
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2022/2023; Delivery quarter estimated; Rent: CoStar ask $2,442 vs RealPage eff $2,261</t>
+          <t>Delivery quarter estimated</t>
         </is>
       </c>
     </row>
@@ -1720,37 +1723,37 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Flatz 623</t>
+          <t>Radia Avondale Station</t>
         </is>
       </c>
       <c r="D30" s="16" t="n">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q1 2024</t>
         </is>
       </c>
       <c r="F30" s="17" t="n">
-        <v>0.1333329999999999</v>
+        <v>0.616708</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>1411</v>
+        <v>1743</v>
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Zekelman Industries</t>
+          <t>Goodman Real Estate Inc.</t>
         </is>
       </c>
       <c r="I30" s="14" t="n"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 13% vs RealPage 0%; Rent: CoStar ask $1,411 vs RealPage eff $1,145; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 407 vs RealPage 212; Year built: 2024/2025; Delivery quarter estimated; Occ: CoStar 62% vs RealPage 51%; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -1760,26 +1763,26 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Stately Avondale</t>
+          <t>Alta 99th</t>
         </is>
       </c>
       <c r="D31" s="16" t="n">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q1 2024</t>
         </is>
       </c>
       <c r="F31" s="17" t="n">
-        <v>0.297203</v>
+        <v>0.855721</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>1728</v>
+        <v>1542</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>Ascent Companies</t>
+          <t>Wood Partners</t>
         </is>
       </c>
       <c r="I31" s="14" t="n"/>
@@ -1790,7 +1793,7 @@
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2026/2027; Delivery quarter estimated; Occ: CoStar 30% vs RealPage 0%; Rent: CoStar ask $1,728 vs RealPage eff $1,243; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 86% vs RealPage 90%; Rent: CoStar ask $1,542 vs RealPage eff $1,154; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -1800,37 +1803,37 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Avilla Western Garden</t>
+          <t>Alta Avondale</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F32" s="17" t="n">
-        <v>0.4461540000000001</v>
+        <v>0.7833330000000001</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>1829</v>
+        <v>1610</v>
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>NexMetro Communities</t>
+          <t>Wood Partners</t>
         </is>
       </c>
       <c r="I32" s="14" t="n"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 45% vs RealPage 0%; Rent: CoStar ask $1,829 vs RealPage eff $1,681; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2024/2025; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 84%; Rent: CoStar ask $1,610 vs RealPage eff $1,339; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -1840,37 +1843,37 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Rev3 at Avondale Station</t>
+          <t>Livano Avondale</t>
         </is>
       </c>
       <c r="D33" s="16" t="n">
-        <v>117</v>
+        <v>316</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F33" s="17" t="n">
-        <v>0.273504</v>
+        <v>0.829114</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>2537</v>
+        <v>1663</v>
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Trilogy Investment Company</t>
+          <t>LIV Development</t>
         </is>
       </c>
       <c r="I33" s="14" t="n"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 117 vs RealPage 107; Delivery quarter estimated; Occ: CoStar 27% vs RealPage 0%; Rent: CoStar ask $2,537 vs RealPage eff $2,273; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2024/2025; Delivery quarter estimated; Rent: CoStar ask $1,663 vs RealPage eff $1,263; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -1880,26 +1883,26 @@
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Liberty at Estrella Falls</t>
+          <t>Cardinal 95</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F34" s="17" t="n">
-        <v>0.05660399999999999</v>
+        <v>0.878788</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>2966</v>
+        <v>1691</v>
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Ronald D Newman</t>
+          <t>Quarry Capital</t>
         </is>
       </c>
       <c r="I34" s="14" t="n"/>
@@ -1910,7 +1913,7 @@
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 6% vs RealPage 21%; Rent: CoStar ask $2,966 vs RealPage eff $1,938; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -1920,37 +1923,37 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Broadstone Ascend</t>
+          <t>Moderne at Roosevelt</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>432</v>
+        <v>185</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>Q4 2025</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F35" s="17" t="n">
-        <v>0.875</v>
+        <v>0.891892</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>1506</v>
+        <v>1900</v>
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Alliance Residential Company</t>
+          <t>MODERNE Communities</t>
         </is>
       </c>
       <c r="I35" s="14" t="n"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Low-Rise</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 88% vs RealPage 51%; Rent: CoStar ask $1,506 vs RealPage eff $1,107; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2024/2025; Occ: CoStar 89% vs RealPage 94%; Rent: CoStar ask $1,900 vs RealPage eff $1,769; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -1960,37 +1963,37 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Villas Litchfield Park</t>
+          <t>Canopy at the Trails</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2024</t>
         </is>
       </c>
       <c r="F36" s="17" t="n">
-        <v>0.810458</v>
+        <v>0.879032</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>1913</v>
+        <v>2183</v>
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Family Development</t>
+          <t>Mark-Taylor Companies</t>
         </is>
       </c>
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 81% vs RealPage 86%; Rent: CoStar ask $1,913 vs RealPage eff $1,538; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 88% vs RealPage 92%; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2000,37 +2003,37 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Villas on Van Buren</t>
+          <t>Meritum Sheely Farms</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>143</v>
+        <v>680</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q4 2024</t>
         </is>
       </c>
       <c r="F37" s="17" t="n">
-        <v>0.496503</v>
+        <v>0.797059</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>2085</v>
+        <v>1680</v>
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Sunstone Properties Trust</t>
+          <t>IDM Companies</t>
         </is>
       </c>
       <c r="I37" s="14" t="n"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K37" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 50% vs RealPage 0%; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2024/2025; Delivery quarter estimated; Rent: CoStar ask $1,680 vs RealPage eff $1,356; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2040,37 +2043,37 @@
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Pradera Estates</t>
+          <t>Alta Goodyear</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="F38" s="17" t="n">
-        <v>0.895349</v>
+        <v>0.789474</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>2474</v>
+        <v>1638</v>
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Wood Partners</t>
         </is>
       </c>
       <c r="I38" s="14" t="n"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Rent: CoStar ask $1,638 vs RealPage eff $1,433; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2080,37 +2083,37 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Rev3 Encanto West</t>
+          <t>Agave Ranch</t>
         </is>
       </c>
       <c r="D39" s="16" t="n">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="F39" s="17" t="n">
-        <v>0.52381</v>
+        <v>0.802469</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>2319</v>
+        <v>1747</v>
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Trilogy Investment Company</t>
+          <t>The Garrett Companies</t>
         </is>
       </c>
       <c r="I39" s="14" t="n"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 84 vs RealPage 78; Year built: 2025/2026; Occ: CoStar 52% vs RealPage 71%; Rent: CoStar ask $2,319 vs RealPage eff $1,833; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 80% vs RealPage 0%; Rent: CoStar ask $1,747 vs RealPage eff $1,582; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2120,37 +2123,37 @@
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Avalon Townhomes</t>
+          <t>Avondale Commons</t>
         </is>
       </c>
       <c r="D40" s="16" t="n">
-        <v>70</v>
+        <v>324</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Q3 2025</t>
+          <t>Q2 2025</t>
         </is>
       </c>
       <c r="F40" s="17" t="n">
-        <v>0.857143</v>
+        <v>0.37037</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>2325</v>
+        <v>1632</v>
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>LVP Partners Group</t>
+          <t>Overland Group</t>
         </is>
       </c>
       <c r="I40" s="14" t="n"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Rent: CoStar ask $2,325 vs RealPage eff $2,169; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 37% vs RealPage 85%; Rent: CoStar ask $1,632 vs RealPage eff $1,321; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2160,11 +2163,11 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Alta Goodyear</t>
+          <t>Broadstone Westgate</t>
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
@@ -2172,14 +2175,14 @@
         </is>
       </c>
       <c r="F41" s="17" t="n">
-        <v>0.789474</v>
+        <v>0.89</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>1638</v>
+        <v>1438</v>
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>Wood Partners</t>
+          <t>Alliance Residential Company/American Realty Advisors</t>
         </is>
       </c>
       <c r="I41" s="14" t="n"/>
@@ -2190,7 +2193,7 @@
       </c>
       <c r="K41" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Rent: CoStar ask $1,638 vs RealPage eff $1,433; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2200,11 +2203,11 @@
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Agave Ranch</t>
+          <t>The Douglas</t>
         </is>
       </c>
       <c r="D42" s="16" t="n">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
@@ -2212,25 +2215,25 @@
         </is>
       </c>
       <c r="F42" s="17" t="n">
-        <v>0.802469</v>
+        <v>0.583062</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>1747</v>
+        <v>2076</v>
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>The Garrett Companies</t>
+          <t>UrbanStreet Group</t>
         </is>
       </c>
       <c r="I42" s="14" t="n"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 80% vs RealPage 0%; Rent: CoStar ask $1,747 vs RealPage eff $1,582; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Rent: CoStar ask $2,076 vs RealPage eff $1,561; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2240,11 +2243,11 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>Avondale Commons</t>
+          <t>Streamliner Aldea</t>
         </is>
       </c>
       <c r="D43" s="16" t="n">
-        <v>324</v>
+        <v>282</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
@@ -2252,25 +2255,25 @@
         </is>
       </c>
       <c r="F43" s="17" t="n">
-        <v>0.37037</v>
+        <v>0.844</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>1632</v>
+        <v>1025</v>
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>Overland Group</t>
+          <t>Greenlight Communities LLC</t>
         </is>
       </c>
       <c r="I43" s="14" t="n"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 37% vs RealPage 85%; Rent: CoStar ask $1,632 vs RealPage eff $1,321; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2280,11 +2283,11 @@
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Broadstone Westgate</t>
+          <t>Cabana Aldea</t>
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>308</v>
+        <v>257</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
@@ -2292,25 +2295,25 @@
         </is>
       </c>
       <c r="F44" s="17" t="n">
-        <v>0.89</v>
+        <v>0.7393000000000001</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>1438</v>
+        <v>1330</v>
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Alliance Residential Company/American Realty Advisors</t>
+          <t>Greenlight Communities</t>
         </is>
       </c>
       <c r="I44" s="14" t="n"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 74% vs RealPage 67%; Rent: CoStar ask $1,330 vs RealPage eff $1,253; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2323,11 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>The Douglas</t>
+          <t>Somerset Upscale Apartments</t>
         </is>
       </c>
       <c r="D45" s="16" t="n">
-        <v>307</v>
+        <v>234</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
@@ -2332,25 +2335,25 @@
         </is>
       </c>
       <c r="F45" s="17" t="n">
-        <v>0.583062</v>
+        <v>0.256</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>2076</v>
+        <v>1671</v>
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>UrbanStreet Group</t>
+          <t>Ridgehouse Companies</t>
         </is>
       </c>
       <c r="I45" s="14" t="n"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Rent: CoStar ask $2,076 vs RealPage eff $1,561; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2360,11 +2363,11 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Streamliner Aldea</t>
+          <t>Village at Skyline Ranch</t>
         </is>
       </c>
       <c r="D46" s="16" t="n">
-        <v>282</v>
+        <v>167</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
@@ -2372,25 +2375,25 @@
         </is>
       </c>
       <c r="F46" s="17" t="n">
-        <v>0.844</v>
+        <v>0.3952100000000001</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>1025</v>
+        <v>1773</v>
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Greenlight Communities LLC</t>
+          <t>Empire Group of Companies</t>
         </is>
       </c>
       <c r="I46" s="14" t="n"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K46" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 40% vs RealPage 0%; Rent: CoStar ask $1,773 vs RealPage eff $1,632; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2400,37 +2403,37 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Cabana Aldea</t>
+          <t>Villas Litchfield Park</t>
         </is>
       </c>
       <c r="D47" s="16" t="n">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="F47" s="17" t="n">
-        <v>0.7393000000000001</v>
+        <v>0.810458</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1330</v>
+        <v>1913</v>
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>Greenlight Communities</t>
+          <t>Family Development</t>
         </is>
       </c>
       <c r="I47" s="14" t="n"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 74% vs RealPage 67%; Rent: CoStar ask $1,330 vs RealPage eff $1,253; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 81% vs RealPage 86%; Rent: CoStar ask $1,913 vs RealPage eff $1,538; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2440,37 +2443,37 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Somerset Upscale Apartments</t>
+          <t>Villas on Van Buren</t>
         </is>
       </c>
       <c r="D48" s="16" t="n">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="F48" s="17" t="n">
-        <v>0.256</v>
+        <v>0.496503</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1671</v>
+        <v>2085</v>
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Ridgehouse Companies</t>
+          <t>Sunstone Properties Trust</t>
         </is>
       </c>
       <c r="I48" s="14" t="n"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K48" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 50% vs RealPage 0%; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2480,37 +2483,37 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Village at Skyline Ranch</t>
+          <t>Pradera Estates</t>
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>Q2 2025</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="F49" s="17" t="n">
-        <v>0.3952100000000001</v>
+        <v>0.895349</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>1773</v>
+        <v>2474</v>
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Empire Group of Companies</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="I49" s="14" t="n"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 40% vs RealPage 0%; Rent: CoStar ask $1,773 vs RealPage eff $1,632; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2520,37 +2523,37 @@
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Meritum Sheely Farms</t>
+          <t>Rev3 Encanto West</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>680</v>
+        <v>84</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Q4 2024</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="F50" s="17" t="n">
-        <v>0.797059</v>
+        <v>0.52381</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>1680</v>
+        <v>2319</v>
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>IDM Companies</t>
+          <t>Trilogy Investment Company</t>
         </is>
       </c>
       <c r="I50" s="14" t="n"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2024/2025; Delivery quarter estimated; Rent: CoStar ask $1,680 vs RealPage eff $1,356; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 84 vs RealPage 78; Year built: 2025/2026; Occ: CoStar 52% vs RealPage 71%; Rent: CoStar ask $2,319 vs RealPage eff $1,833; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2560,37 +2563,37 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Alta Avondale</t>
+          <t>Avalon Townhomes</t>
         </is>
       </c>
       <c r="D51" s="16" t="n">
-        <v>360</v>
+        <v>70</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q3 2025</t>
         </is>
       </c>
       <c r="F51" s="17" t="n">
-        <v>0.7833330000000001</v>
+        <v>0.857143</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>1610</v>
+        <v>2325</v>
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Wood Partners</t>
+          <t>LVP Partners Group</t>
         </is>
       </c>
       <c r="I51" s="14" t="n"/>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2024/2025; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 84%; Rent: CoStar ask $1,610 vs RealPage eff $1,339; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Rent: CoStar ask $2,325 vs RealPage eff $2,169; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2600,37 +2603,37 @@
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Livano Avondale</t>
+          <t>Broadstone Ascend</t>
         </is>
       </c>
       <c r="D52" s="16" t="n">
-        <v>316</v>
+        <v>432</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q4 2025</t>
         </is>
       </c>
       <c r="F52" s="17" t="n">
-        <v>0.829114</v>
+        <v>0.875</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>1663</v>
+        <v>1506</v>
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>LIV Development</t>
+          <t>Alliance Residential Company</t>
         </is>
       </c>
       <c r="I52" s="14" t="n"/>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2024/2025; Delivery quarter estimated; Rent: CoStar ask $1,663 vs RealPage eff $1,263; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 88% vs RealPage 51%; Rent: CoStar ask $1,506 vs RealPage eff $1,107; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2640,37 +2643,37 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Cardinal 95</t>
+          <t>Flatz 623</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>198</v>
+        <v>360</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="F53" s="17" t="n">
-        <v>0.878788</v>
+        <v>0.1333329999999999</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>1691</v>
+        <v>1411</v>
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Quarry Capital</t>
+          <t>Zekelman Industries</t>
         </is>
       </c>
       <c r="I53" s="14" t="n"/>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Low-Rise</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 13% vs RealPage 0%; Rent: CoStar ask $1,411 vs RealPage eff $1,145; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2680,37 +2683,37 @@
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Moderne at Roosevelt</t>
+          <t>Stately Avondale</t>
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="F54" s="17" t="n">
-        <v>0.891892</v>
+        <v>0.297203</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>1900</v>
+        <v>1728</v>
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>MODERNE Communities</t>
+          <t>Ascent Companies</t>
         </is>
       </c>
       <c r="I54" s="14" t="n"/>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>Year built: 2024/2025; Occ: CoStar 89% vs RealPage 94%; Rent: CoStar ask $1,900 vs RealPage eff $1,769; Verify rent/occ w/ HelloData</t>
+          <t>Year built: 2026/2027; Delivery quarter estimated; Occ: CoStar 30% vs RealPage 0%; Rent: CoStar ask $1,728 vs RealPage eff $1,243; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2720,37 +2723,37 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Canopy at the Trails</t>
+          <t>Avilla Western Garden</t>
         </is>
       </c>
       <c r="D55" s="16" t="n">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>Q2 2024</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="F55" s="17" t="n">
-        <v>0.879032</v>
+        <v>0.4461540000000001</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>2183</v>
+        <v>1829</v>
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Mark-Taylor Companies</t>
+          <t>NexMetro Communities</t>
         </is>
       </c>
       <c r="I55" s="14" t="n"/>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K55" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 88% vs RealPage 92%; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 45% vs RealPage 0%; Rent: CoStar ask $1,829 vs RealPage eff $1,681; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2760,37 +2763,37 @@
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Radia Avondale Station</t>
+          <t>Rev3 at Avondale Station</t>
         </is>
       </c>
       <c r="D56" s="16" t="n">
-        <v>407</v>
+        <v>117</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Q1 2024</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="F56" s="17" t="n">
-        <v>0.616708</v>
+        <v>0.273504</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>1743</v>
+        <v>2537</v>
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Goodman Real Estate Inc.</t>
+          <t>Trilogy Investment Company</t>
         </is>
       </c>
       <c r="I56" s="14" t="n"/>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K56" s="15" t="inlineStr">
         <is>
-          <t>Units: CoStar 407 vs RealPage 212; Year built: 2024/2025; Delivery quarter estimated; Occ: CoStar 62% vs RealPage 51%; Verify rent/occ w/ HelloData</t>
+          <t>Units: CoStar 117 vs RealPage 107; Delivery quarter estimated; Occ: CoStar 27% vs RealPage 0%; Rent: CoStar ask $2,537 vs RealPage eff $2,273; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2800,26 +2803,26 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>Alta 99th</t>
+          <t>Liberty at Estrella Falls</t>
         </is>
       </c>
       <c r="D57" s="16" t="n">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>Q1 2024</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="F57" s="17" t="n">
-        <v>0.855721</v>
+        <v>0.05660399999999999</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>1542</v>
+        <v>2966</v>
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Wood Partners</t>
+          <t>Ronald D Newman</t>
         </is>
       </c>
       <c r="I57" s="14" t="n"/>
@@ -2830,7 +2833,7 @@
       </c>
       <c r="K57" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 86% vs RealPage 90%; Rent: CoStar ask $1,542 vs RealPage eff $1,154; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Occ: CoStar 6% vs RealPage 21%; Rent: CoStar ask $2,966 vs RealPage eff $1,938; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2848,15 +2851,15 @@
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>Zanjero III</t>
+          <t>FUZE Ballpark</t>
         </is>
       </c>
       <c r="D60" s="23" t="n">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F60" s="24" t="n"/>
@@ -2867,7 +2870,7 @@
       </c>
       <c r="H60" s="22" t="inlineStr">
         <is>
-          <t>Fore Property Company/Privately Owned</t>
+          <t>Zekelman Industries</t>
         </is>
       </c>
       <c r="I60" s="21" t="n"/>
@@ -2884,15 +2887,15 @@
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>Zen @ Angelina</t>
+          <t>HARMON Ascend</t>
         </is>
       </c>
       <c r="D61" s="23" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="F61" s="24" t="n"/>
@@ -2903,7 +2906,7 @@
       </c>
       <c r="H61" s="22" t="inlineStr">
         <is>
-          <t>F &amp; S Consulting &amp; Management, LLC</t>
+          <t>Crescent Communities LLC</t>
         </is>
       </c>
       <c r="I61" s="21" t="n"/>
@@ -2912,11 +2915,7 @@
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K61" s="22" t="inlineStr">
-        <is>
-          <t>Year built: 2027/2028</t>
-        </is>
-      </c>
+      <c r="K61" s="22" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="21" t="n">
@@ -2924,15 +2923,15 @@
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Yardly Algodon</t>
+          <t>Pointe Grand Estrella at Phoenix</t>
         </is>
       </c>
       <c r="D62" s="23" t="n">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F62" s="24" t="n"/>
@@ -2943,18 +2942,18 @@
       </c>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t>Taylor Morrison, Inc.</t>
+          <t>Hillpointe, LLC</t>
         </is>
       </c>
       <c r="I62" s="21" t="n"/>
       <c r="J62" s="21" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K62" s="22" t="inlineStr">
         <is>
-          <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
+          <t>Year built: 2026/2027</t>
         </is>
       </c>
     </row>
@@ -2964,15 +2963,15 @@
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Cerro Vista</t>
+          <t>Marbella Ranch East I</t>
         </is>
       </c>
       <c r="D63" s="23" t="n">
-        <v>255</v>
+        <v>144</v>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F63" s="24" t="n"/>
@@ -2983,13 +2982,13 @@
       </c>
       <c r="H63" s="22" t="inlineStr">
         <is>
-          <t>Virtua Partners</t>
+          <t>Symmetry Companies</t>
         </is>
       </c>
       <c r="I63" s="21" t="n"/>
       <c r="J63" s="21" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K63" s="22" t="n"/>
@@ -3000,11 +2999,11 @@
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>Pointe Grand Estrella at Phoenix</t>
+          <t>Villages at Northern</t>
         </is>
       </c>
       <c r="D64" s="23" t="n">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
@@ -3019,7 +3018,7 @@
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t>Hillpointe, LLC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I64" s="21" t="n"/>
@@ -3028,11 +3027,7 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K64" s="22" t="inlineStr">
-        <is>
-          <t>Year built: 2026/2027</t>
-        </is>
-      </c>
+      <c r="K64" s="22" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="21" t="n">
@@ -3040,11 +3035,11 @@
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Marbella Ranch East I</t>
+          <t>Prosper 47</t>
         </is>
       </c>
       <c r="D65" s="23" t="n">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
@@ -3059,16 +3054,20 @@
       </c>
       <c r="H65" s="22" t="inlineStr">
         <is>
-          <t>Symmetry Companies</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I65" s="21" t="n"/>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K65" s="22" t="n"/>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K65" s="22" t="inlineStr">
+        <is>
+          <t>RealPage only (sub-50 unit)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="21" t="n">
@@ -3076,15 +3075,15 @@
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Villages at Northern</t>
+          <t>Yardly Algodon</t>
         </is>
       </c>
       <c r="D66" s="23" t="n">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F66" s="24" t="n"/>
@@ -3095,16 +3094,20 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Taylor Morrison, Inc.</t>
         </is>
       </c>
       <c r="I66" s="21" t="n"/>
       <c r="J66" s="21" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K66" s="22" t="n"/>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="K66" s="22" t="inlineStr">
+        <is>
+          <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="21" t="n">
@@ -3112,15 +3115,15 @@
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Prosper 47</t>
+          <t>Cerro Vista</t>
         </is>
       </c>
       <c r="D67" s="23" t="n">
-        <v>47</v>
+        <v>255</v>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F67" s="24" t="n"/>
@@ -3131,20 +3134,16 @@
       </c>
       <c r="H67" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Virtua Partners</t>
         </is>
       </c>
       <c r="I67" s="21" t="n"/>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K67" s="22" t="inlineStr">
-        <is>
-          <t>RealPage only (sub-50 unit)</t>
-        </is>
-      </c>
+          <t>Low-Rise</t>
+        </is>
+      </c>
+      <c r="K67" s="22" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="21" t="n">
@@ -3152,15 +3151,15 @@
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>HARMON Ascend</t>
+          <t>Zanjero III</t>
         </is>
       </c>
       <c r="D68" s="23" t="n">
-        <v>125</v>
+        <v>301</v>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>Q1 2027</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="F68" s="24" t="n"/>
@@ -3171,13 +3170,13 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t>Crescent Communities LLC</t>
+          <t>Fore Property Company/Privately Owned</t>
         </is>
       </c>
       <c r="I68" s="21" t="n"/>
       <c r="J68" s="21" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K68" s="22" t="n"/>
@@ -3188,15 +3187,15 @@
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>FUZE Ballpark</t>
+          <t>Zen @ Angelina</t>
         </is>
       </c>
       <c r="D69" s="23" t="n">
-        <v>321</v>
+        <v>130</v>
       </c>
       <c r="E69" s="21" t="inlineStr">
         <is>
-          <t>Q3 2026</t>
+          <t>Q2 2028</t>
         </is>
       </c>
       <c r="F69" s="24" t="n"/>
@@ -3207,16 +3206,20 @@
       </c>
       <c r="H69" s="22" t="inlineStr">
         <is>
-          <t>Zekelman Industries</t>
+          <t>F &amp; S Consulting &amp; Management, LLC</t>
         </is>
       </c>
       <c r="I69" s="21" t="n"/>
       <c r="J69" s="21" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K69" s="22" t="n"/>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="inlineStr">
+        <is>
+          <t>Year built: 2027/2028</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="26" t="n"/>
@@ -3232,15 +3235,15 @@
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>Northern 107</t>
+          <t>The Waverly</t>
         </is>
       </c>
       <c r="D72" s="30" t="n">
-        <v>74</v>
+        <v>323</v>
       </c>
       <c r="E72" s="28" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F72" s="31" t="n"/>
@@ -3251,13 +3254,13 @@
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>Jacob Reuben</t>
+          <t>Dominium</t>
         </is>
       </c>
       <c r="I72" s="28" t="n"/>
       <c r="J72" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K72" s="29" t="n"/>
@@ -3268,11 +3271,11 @@
       </c>
       <c r="C73" s="29" t="inlineStr">
         <is>
-          <t>The Waverly</t>
+          <t>Encore Avondale</t>
         </is>
       </c>
       <c r="D73" s="30" t="n">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="E73" s="28" t="inlineStr">
         <is>
@@ -3287,7 +3290,7 @@
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>Dominium</t>
+          <t>Encore Enterprises</t>
         </is>
       </c>
       <c r="I73" s="28" t="n"/>
@@ -3304,11 +3307,11 @@
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>Encore Avondale</t>
+          <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
       <c r="D74" s="30" t="n">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E74" s="28" t="inlineStr">
         <is>
@@ -3323,7 +3326,7 @@
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>Encore Enterprises</t>
+          <t>Leon Capital Group</t>
         </is>
       </c>
       <c r="I74" s="28" t="n"/>
@@ -3340,11 +3343,11 @@
       </c>
       <c r="C75" s="29" t="inlineStr">
         <is>
-          <t>The Statler at Estrella Parkway</t>
+          <t>Ascent Goodyear</t>
         </is>
       </c>
       <c r="D75" s="30" t="n">
-        <v>284</v>
+        <v>113</v>
       </c>
       <c r="E75" s="28" t="inlineStr">
         <is>
@@ -3359,13 +3362,13 @@
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>Leon Capital Group</t>
+          <t>Ascent Companies</t>
         </is>
       </c>
       <c r="I75" s="28" t="n"/>
       <c r="J75" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K75" s="29" t="n"/>
@@ -3376,15 +3379,15 @@
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>Ascent Goodyear</t>
+          <t>Northern 107</t>
         </is>
       </c>
       <c r="D76" s="30" t="n">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E76" s="28" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F76" s="31" t="n"/>
@@ -3395,7 +3398,7 @@
       </c>
       <c r="H76" s="29" t="inlineStr">
         <is>
-          <t>Ascent Companies</t>
+          <t>Jacob Reuben</t>
         </is>
       </c>
       <c r="I76" s="28" t="n"/>
@@ -4966,7 +4969,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:Z61"/>
@@ -4990,19 +4993,19 @@
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="8" customWidth="1" min="22" max="22"/>
     <col hidden="1" width="7" customWidth="1" min="23" max="23"/>
     <col hidden="1" width="6" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="14.4" customHeight="1">
       <c r="Z1" t="n">
         <v>8105</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SUPPLY &amp; ABSORPTION  —  5-MILE MARKET (relative-year / TTM)</t>
@@ -5013,7 +5016,7 @@
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.4" customHeight="1">
       <c r="R3" s="34" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
@@ -5024,7 +5027,7 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="14.4" customHeight="1">
       <c r="B4" s="35" t="inlineStr">
         <is>
           <t>As-of Quarter</t>
@@ -5051,7 +5054,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="14.4" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Close Quarter (Y1 start)</t>
@@ -5063,15 +5066,15 @@
         </is>
       </c>
       <c r="R5" s="39">
-        <f>'Competitive Analysis'!C69</f>
+        <f>'Competitive Analysis'!C60</f>
         <v/>
       </c>
       <c r="S5" s="40">
-        <f>'Competitive Analysis'!D69</f>
+        <f>'Competitive Analysis'!D60</f>
         <v/>
       </c>
       <c r="T5" s="41">
-        <f>'Competitive Analysis'!E69</f>
+        <f>'Competitive Analysis'!E60</f>
         <v/>
       </c>
       <c r="V5">
@@ -5083,7 +5086,7 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="14.4" customHeight="1">
       <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Stabilization Target</t>
@@ -5093,15 +5096,15 @@
         <v>0.95</v>
       </c>
       <c r="R6" s="39">
-        <f>'Competitive Analysis'!C60</f>
+        <f>'Competitive Analysis'!C68</f>
         <v/>
       </c>
       <c r="S6" s="40">
-        <f>'Competitive Analysis'!D60</f>
+        <f>'Competitive Analysis'!D68</f>
         <v/>
       </c>
       <c r="T6" s="41">
-        <f>'Competitive Analysis'!E60</f>
+        <f>'Competitive Analysis'!E68</f>
         <v/>
       </c>
       <c r="V6">
@@ -5113,7 +5116,7 @@
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.4" customHeight="1">
       <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Demand Scenario</t>
@@ -5125,15 +5128,15 @@
         </is>
       </c>
       <c r="R7" s="39">
-        <f>'Competitive Analysis'!C64</f>
+        <f>'Competitive Analysis'!C62</f>
         <v/>
       </c>
       <c r="S7" s="40">
-        <f>'Competitive Analysis'!D64</f>
+        <f>'Competitive Analysis'!D62</f>
         <v/>
       </c>
       <c r="T7" s="41">
-        <f>'Competitive Analysis'!E64</f>
+        <f>'Competitive Analysis'!E62</f>
         <v/>
       </c>
       <c r="V7">
@@ -5145,7 +5148,7 @@
         <v/>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.4" customHeight="1">
       <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Bear Annual Absorption</t>
@@ -5155,15 +5158,15 @@
         <v>1250</v>
       </c>
       <c r="R8" s="39">
-        <f>'Competitive Analysis'!C62</f>
+        <f>'Competitive Analysis'!C66</f>
         <v/>
       </c>
       <c r="S8" s="40">
-        <f>'Competitive Analysis'!D62</f>
+        <f>'Competitive Analysis'!D66</f>
         <v/>
       </c>
       <c r="T8" s="41">
-        <f>'Competitive Analysis'!E62</f>
+        <f>'Competitive Analysis'!E66</f>
         <v/>
       </c>
       <c r="V8">
@@ -5175,7 +5178,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.4" customHeight="1">
       <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Base Annual Absorption</t>
@@ -5185,15 +5188,15 @@
         <v>2525</v>
       </c>
       <c r="R9" s="39">
-        <f>'Competitive Analysis'!C63</f>
+        <f>'Competitive Analysis'!C67</f>
         <v/>
       </c>
       <c r="S9" s="40">
-        <f>'Competitive Analysis'!D63</f>
+        <f>'Competitive Analysis'!D67</f>
         <v/>
       </c>
       <c r="T9" s="41">
-        <f>'Competitive Analysis'!E63</f>
+        <f>'Competitive Analysis'!E67</f>
         <v/>
       </c>
       <c r="V9">
@@ -5205,7 +5208,7 @@
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.4" customHeight="1">
       <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Bull Annual Absorption</t>
@@ -5215,15 +5218,15 @@
         <v>3800</v>
       </c>
       <c r="R10" s="39">
-        <f>'Competitive Analysis'!C65</f>
+        <f>'Competitive Analysis'!C63</f>
         <v/>
       </c>
       <c r="S10" s="40">
-        <f>'Competitive Analysis'!D65</f>
+        <f>'Competitive Analysis'!D63</f>
         <v/>
       </c>
       <c r="T10" s="41">
-        <f>'Competitive Analysis'!E65</f>
+        <f>'Competitive Analysis'!E63</f>
         <v/>
       </c>
       <c r="V10">
@@ -5235,7 +5238,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.4" customHeight="1">
       <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Selected Annual Demand</t>
@@ -5246,15 +5249,15 @@
         <v/>
       </c>
       <c r="R11" s="39">
-        <f>'Competitive Analysis'!C61</f>
+        <f>'Competitive Analysis'!C69</f>
         <v/>
       </c>
       <c r="S11" s="40">
-        <f>'Competitive Analysis'!D61</f>
+        <f>'Competitive Analysis'!D69</f>
         <v/>
       </c>
       <c r="T11" s="41">
-        <f>'Competitive Analysis'!E61</f>
+        <f>'Competitive Analysis'!E69</f>
         <v/>
       </c>
       <c r="V11">
@@ -5266,27 +5269,17 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>UC scheduled vs CoStar UC</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>1,947 / 1,251</t>
-        </is>
-      </c>
+    <row r="12" ht="14.4" customHeight="1">
       <c r="R12" s="39">
-        <f>'Competitive Analysis'!C68</f>
+        <f>'Competitive Analysis'!C61</f>
         <v/>
       </c>
       <c r="S12" s="40">
-        <f>'Competitive Analysis'!D68</f>
+        <f>'Competitive Analysis'!D61</f>
         <v/>
       </c>
       <c r="T12" s="41">
-        <f>'Competitive Analysis'!E68</f>
+        <f>'Competitive Analysis'!E61</f>
         <v/>
       </c>
       <c r="V12">
@@ -5298,27 +5291,17 @@
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>Subject rent source</t>
-        </is>
-      </c>
-      <c r="C13" s="45" t="inlineStr">
-        <is>
-          <t>HelloData → CoStar</t>
-        </is>
-      </c>
+    <row r="13" ht="14.4" customHeight="1">
       <c r="R13" s="39">
-        <f>'Competitive Analysis'!C66</f>
+        <f>'Competitive Analysis'!C64</f>
         <v/>
       </c>
       <c r="S13" s="40">
-        <f>'Competitive Analysis'!D66</f>
+        <f>'Competitive Analysis'!D64</f>
         <v/>
       </c>
       <c r="T13" s="41">
-        <f>'Competitive Analysis'!E66</f>
+        <f>'Competitive Analysis'!E64</f>
         <v/>
       </c>
       <c r="V13">
@@ -5330,17 +5313,17 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.4" customHeight="1">
       <c r="R14" s="39">
-        <f>'Competitive Analysis'!C67</f>
+        <f>'Competitive Analysis'!C65</f>
         <v/>
       </c>
       <c r="S14" s="40">
-        <f>'Competitive Analysis'!D67</f>
+        <f>'Competitive Analysis'!D65</f>
         <v/>
       </c>
       <c r="T14" s="41">
-        <f>'Competitive Analysis'!E67</f>
+        <f>'Competitive Analysis'!E65</f>
         <v/>
       </c>
       <c r="V14">
@@ -5352,14 +5335,15 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="15" ht="14.4" customHeight="1"/>
+    <row r="16" ht="14.4" customHeight="1">
       <c r="R16" s="34" t="inlineStr">
         <is>
           <t>PROPOSED PIPELINE (scenario toggle)</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="14.4" customHeight="1">
       <c r="B17" s="35" t="inlineStr">
         <is>
           <t>5-MILE MARKET</t>
@@ -5400,32 +5384,32 @@
           <t>Y0</t>
         </is>
       </c>
-      <c r="J17" s="46" t="inlineStr">
+      <c r="J17" s="45" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K17" s="46" t="inlineStr">
+      <c r="K17" s="45" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L17" s="46" t="inlineStr">
+      <c r="L17" s="45" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M17" s="46" t="inlineStr">
+      <c r="M17" s="45" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N17" s="46" t="inlineStr">
+      <c r="N17" s="45" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O17" s="46" t="inlineStr">
+      <c r="O17" s="45" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
@@ -5451,68 +5435,68 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="C18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2019–Q2 2020</t>
-        </is>
-      </c>
-      <c r="D18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2020–Q2 2021</t>
-        </is>
-      </c>
-      <c r="E18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2021–Q2 2022</t>
-        </is>
-      </c>
-      <c r="F18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2022–Q2 2023</t>
-        </is>
-      </c>
-      <c r="G18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2023–Q2 2024</t>
-        </is>
-      </c>
-      <c r="H18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2024–Q2 2025</t>
-        </is>
-      </c>
-      <c r="I18" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2025–Q2 2026</t>
-        </is>
-      </c>
-      <c r="J18" s="47" t="inlineStr">
+    <row r="18" ht="14.4" customHeight="1">
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'19-Q2'20</t>
+        </is>
+      </c>
+      <c r="D18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'20-Q2'21</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'21-Q2'22</t>
+        </is>
+      </c>
+      <c r="F18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'22-Q2'23</t>
+        </is>
+      </c>
+      <c r="G18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'23-Q2'24</t>
+        </is>
+      </c>
+      <c r="H18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'24-Q2'25</t>
+        </is>
+      </c>
+      <c r="I18" s="46" t="inlineStr">
+        <is>
+          <t>Q3'25-Q2'26</t>
+        </is>
+      </c>
+      <c r="J18" s="46" t="inlineStr">
         <is>
           <t>Hold Yr 1</t>
         </is>
       </c>
-      <c r="K18" s="47" t="inlineStr">
+      <c r="K18" s="46" t="inlineStr">
         <is>
           <t>Hold Yr 2</t>
         </is>
       </c>
-      <c r="L18" s="47" t="inlineStr">
+      <c r="L18" s="46" t="inlineStr">
         <is>
           <t>Hold Yr 3</t>
         </is>
       </c>
-      <c r="M18" s="47" t="inlineStr">
+      <c r="M18" s="46" t="inlineStr">
         <is>
           <t>Hold Yr 4</t>
         </is>
       </c>
-      <c r="N18" s="47" t="inlineStr">
+      <c r="N18" s="46" t="inlineStr">
         <is>
           <t>Hold Yr 5</t>
         </is>
       </c>
-      <c r="O18" s="47" t="inlineStr">
+      <c r="O18" s="46" t="inlineStr">
         <is>
           <t>Hold Yr 6</t>
         </is>
@@ -5525,8 +5509,8 @@
       <c r="S18" s="40" t="n">
         <v>697</v>
       </c>
-      <c r="T18" s="48" t="inlineStr"/>
-      <c r="U18" s="48" t="inlineStr">
+      <c r="T18" s="47" t="inlineStr"/>
+      <c r="U18" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5544,54 +5528,54 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="14.4" customHeight="1">
       <c r="B19" s="35" t="inlineStr">
         <is>
           <t>NEW SUPPLY (5-mi)</t>
         </is>
       </c>
-      <c r="C19" s="49" t="n">
+      <c r="C19" s="48" t="n">
         <v>1133</v>
       </c>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="48" t="n">
         <v>1860</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="48" t="n">
         <v>1336</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="48" t="n">
         <v>2280</v>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="G19" s="48" t="n">
         <v>2823</v>
       </c>
-      <c r="H19" s="49" t="n">
+      <c r="H19" s="48" t="n">
         <v>4043</v>
       </c>
-      <c r="I19" s="49" t="n">
+      <c r="I19" s="48" t="n">
         <v>1860</v>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="49">
         <f>SUMIFS($S$5:$S$14,$W$5:$W$14,1)+SUMIFS($S$18:$S$61,$W$18:$W$61,1,$X$18:$X$61,1)</f>
         <v/>
       </c>
-      <c r="K19" s="50">
+      <c r="K19" s="49">
         <f>SUMIFS($S$5:$S$14,$W$5:$W$14,2)+SUMIFS($S$18:$S$61,$W$18:$W$61,2,$X$18:$X$61,1)</f>
         <v/>
       </c>
-      <c r="L19" s="50">
+      <c r="L19" s="49">
         <f>SUMIFS($S$5:$S$14,$W$5:$W$14,3)+SUMIFS($S$18:$S$61,$W$18:$W$61,3,$X$18:$X$61,1)</f>
         <v/>
       </c>
-      <c r="M19" s="50">
+      <c r="M19" s="49">
         <f>SUMIFS($S$5:$S$14,$W$5:$W$14,4)+SUMIFS($S$18:$S$61,$W$18:$W$61,4,$X$18:$X$61,1)</f>
         <v/>
       </c>
-      <c r="N19" s="50">
+      <c r="N19" s="49">
         <f>SUMIFS($S$5:$S$14,$W$5:$W$14,5)+SUMIFS($S$18:$S$61,$W$18:$W$61,5,$X$18:$X$61,1)</f>
         <v/>
       </c>
-      <c r="O19" s="50">
+      <c r="O19" s="49">
         <f>SUMIFS($S$5:$S$14,$W$5:$W$14,6)+SUMIFS($S$18:$S$61,$W$18:$W$61,6,$X$18:$X$61,1)</f>
         <v/>
       </c>
@@ -5603,8 +5587,8 @@
       <c r="S19" s="40" t="n">
         <v>500</v>
       </c>
-      <c r="T19" s="48" t="inlineStr"/>
-      <c r="U19" s="48" t="inlineStr">
+      <c r="T19" s="47" t="inlineStr"/>
+      <c r="U19" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5622,54 +5606,54 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="14.4" customHeight="1">
       <c r="B20" s="35" t="inlineStr">
         <is>
           <t>ABSORPTION (5-mi)</t>
         </is>
       </c>
-      <c r="C20" s="49" t="n">
+      <c r="C20" s="48" t="n">
         <v>719</v>
       </c>
-      <c r="D20" s="49" t="n">
+      <c r="D20" s="48" t="n">
         <v>1876</v>
       </c>
-      <c r="E20" s="49" t="n">
+      <c r="E20" s="48" t="n">
         <v>1210</v>
       </c>
-      <c r="F20" s="49" t="n">
+      <c r="F20" s="48" t="n">
         <v>685</v>
       </c>
-      <c r="G20" s="49" t="n">
+      <c r="G20" s="48" t="n">
         <v>2514</v>
       </c>
-      <c r="H20" s="49" t="n">
+      <c r="H20" s="48" t="n">
         <v>2655</v>
       </c>
-      <c r="I20" s="49" t="n">
+      <c r="I20" s="48" t="n">
         <v>2369</v>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="49">
         <f>J31-I31</f>
         <v/>
       </c>
-      <c r="K20" s="50">
+      <c r="K20" s="49">
         <f>K31-J31</f>
         <v/>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="49">
         <f>L31-K31</f>
         <v/>
       </c>
-      <c r="M20" s="50">
+      <c r="M20" s="49">
         <f>M31-L31</f>
         <v/>
       </c>
-      <c r="N20" s="50">
+      <c r="N20" s="49">
         <f>N31-M31</f>
         <v/>
       </c>
-      <c r="O20" s="50">
+      <c r="O20" s="49">
         <f>O31-N31</f>
         <v/>
       </c>
@@ -5681,8 +5665,8 @@
       <c r="S20" s="40" t="n">
         <v>478</v>
       </c>
-      <c r="T20" s="48" t="inlineStr"/>
-      <c r="U20" s="48" t="inlineStr">
+      <c r="T20" s="47" t="inlineStr"/>
+      <c r="U20" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5700,54 +5684,54 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="14.4" customHeight="1">
       <c r="B21" s="35" t="inlineStr">
         <is>
           <t>OCCUPANCY (5-mi)</t>
         </is>
       </c>
-      <c r="C21" s="51" t="n">
+      <c r="C21" s="50" t="n">
         <v>0.909</v>
       </c>
-      <c r="D21" s="51" t="n">
+      <c r="D21" s="50" t="n">
         <v>0.922</v>
       </c>
-      <c r="E21" s="51" t="n">
+      <c r="E21" s="50" t="n">
         <v>0.921</v>
       </c>
-      <c r="F21" s="51" t="n">
+      <c r="F21" s="50" t="n">
         <v>0.842</v>
       </c>
-      <c r="G21" s="51" t="n">
+      <c r="G21" s="50" t="n">
         <v>0.848</v>
       </c>
-      <c r="H21" s="51" t="n">
+      <c r="H21" s="50" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="I21" s="51" t="n">
+      <c r="I21" s="50" t="n">
         <v>0.849</v>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="51">
         <f>IFERROR(J31/J30,0)</f>
         <v/>
       </c>
-      <c r="K21" s="52">
+      <c r="K21" s="51">
         <f>IFERROR(K31/K30,0)</f>
         <v/>
       </c>
-      <c r="L21" s="52">
+      <c r="L21" s="51">
         <f>IFERROR(L31/L30,0)</f>
         <v/>
       </c>
-      <c r="M21" s="52">
+      <c r="M21" s="51">
         <f>IFERROR(M31/M30,0)</f>
         <v/>
       </c>
-      <c r="N21" s="52">
+      <c r="N21" s="51">
         <f>IFERROR(N31/N30,0)</f>
         <v/>
       </c>
-      <c r="O21" s="52">
+      <c r="O21" s="51">
         <f>IFERROR(O31/O30,0)</f>
         <v/>
       </c>
@@ -5759,8 +5743,8 @@
       <c r="S21" s="40" t="n">
         <v>410</v>
       </c>
-      <c r="T21" s="48" t="inlineStr"/>
-      <c r="U21" s="48" t="inlineStr">
+      <c r="T21" s="47" t="inlineStr"/>
+      <c r="U21" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5778,54 +5762,11 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.4" customHeight="1">
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>CUM. UNABSORBED (since -Y3)</t>
-        </is>
-      </c>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
-      <c r="E22" s="53" t="n"/>
-      <c r="F22" s="53">
-        <f>F19-F20</f>
-        <v/>
-      </c>
-      <c r="G22" s="53">
-        <f>F22+G19-G20</f>
-        <v/>
-      </c>
-      <c r="H22" s="53">
-        <f>G22+H19-H20</f>
-        <v/>
-      </c>
-      <c r="I22" s="53">
-        <f>H22+I19-I20</f>
-        <v/>
-      </c>
-      <c r="J22" s="53">
-        <f>I22+J19-J20</f>
-        <v/>
-      </c>
-      <c r="K22" s="53">
-        <f>J22+K19-K20</f>
-        <v/>
-      </c>
-      <c r="L22" s="53">
-        <f>K22+L19-L20</f>
-        <v/>
-      </c>
-      <c r="M22" s="53">
-        <f>L22+M19-M20</f>
-        <v/>
-      </c>
-      <c r="N22" s="53">
-        <f>M22+N19-N20</f>
-        <v/>
-      </c>
-      <c r="O22" s="53">
-        <f>N22+O19-O20</f>
-        <v/>
+          <t>SUBJECT (Bella Mirage)</t>
+        </is>
       </c>
       <c r="R22" s="39" t="inlineStr">
         <is>
@@ -5835,8 +5776,8 @@
       <c r="S22" s="40" t="n">
         <v>384</v>
       </c>
-      <c r="T22" s="48" t="inlineStr"/>
-      <c r="U22" s="48" t="inlineStr">
+      <c r="T22" s="47" t="inlineStr"/>
+      <c r="U22" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5854,12 +5795,39 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="14.4" customHeight="1">
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>SUBJECT (Bella Mirage)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="n">
+        <v>1088</v>
+      </c>
+      <c r="D23" s="52" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E23" s="52" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F23" s="52" t="n">
+        <v>1572</v>
+      </c>
+      <c r="G23" s="52" t="n">
+        <v>1497</v>
+      </c>
+      <c r="H23" s="52" t="n">
+        <v>1444</v>
+      </c>
+      <c r="I23" s="52" t="n">
+        <v>1332</v>
+      </c>
+      <c r="J23" s="53" t="n"/>
+      <c r="K23" s="53" t="n"/>
+      <c r="L23" s="53" t="n"/>
+      <c r="M23" s="53" t="n"/>
+      <c r="N23" s="53" t="n"/>
+      <c r="O23" s="53" t="n"/>
       <c r="R23" s="39" t="inlineStr">
         <is>
           <t>Picerne at Palm Valley</t>
@@ -5868,8 +5836,8 @@
       <c r="S23" s="40" t="n">
         <v>383</v>
       </c>
-      <c r="T23" s="48" t="inlineStr"/>
-      <c r="U23" s="48" t="inlineStr">
+      <c r="T23" s="47" t="inlineStr"/>
+      <c r="U23" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5887,39 +5855,43 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
-        </is>
-      </c>
-      <c r="C24" s="54" t="n">
-        <v>1088</v>
-      </c>
-      <c r="D24" s="54" t="n">
-        <v>1437</v>
-      </c>
-      <c r="E24" s="54" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F24" s="54" t="n">
-        <v>1572</v>
-      </c>
-      <c r="G24" s="54" t="n">
-        <v>1497</v>
-      </c>
-      <c r="H24" s="54" t="n">
-        <v>1444</v>
-      </c>
-      <c r="I24" s="54" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J24" s="55" t="n"/>
-      <c r="K24" s="55" t="n"/>
-      <c r="L24" s="55" t="n"/>
-      <c r="M24" s="55" t="n"/>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="n"/>
+    <row r="24" ht="14.4" customHeight="1">
+      <c r="B24" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Market Rent YoY %</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55">
+        <f>IFERROR(D23/C23-1,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="55">
+        <f>IFERROR(E23/D23-1,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="55">
+        <f>IFERROR(F23/E23-1,"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="55">
+        <f>IFERROR(G23/F23-1,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="55">
+        <f>IFERROR(H23/G23-1,"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="55">
+        <f>IFERROR(I23/H23-1,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="56" t="n"/>
+      <c r="K24" s="56" t="n"/>
+      <c r="L24" s="56" t="n"/>
+      <c r="M24" s="56" t="n"/>
+      <c r="N24" s="56" t="n"/>
+      <c r="O24" s="56" t="n"/>
       <c r="R24" s="39" t="inlineStr">
         <is>
           <t>Liv Avondale</t>
@@ -5928,8 +5900,8 @@
       <c r="S24" s="40" t="n">
         <v>333</v>
       </c>
-      <c r="T24" s="48" t="inlineStr"/>
-      <c r="U24" s="48" t="inlineStr">
+      <c r="T24" s="47" t="inlineStr"/>
+      <c r="U24" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5947,43 +5919,39 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Market Rent YoY %</t>
-        </is>
-      </c>
-      <c r="C25" s="57" t="n"/>
-      <c r="D25" s="57">
-        <f>IFERROR(D24/C24-1,"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="57">
-        <f>IFERROR(E24/D24-1,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="57">
-        <f>IFERROR(F24/E24-1,"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="57">
-        <f>IFERROR(G24/F24-1,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="57">
-        <f>IFERROR(H24/G24-1,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="57">
-        <f>IFERROR(I24/H24-1,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="58" t="n"/>
-      <c r="K25" s="58" t="n"/>
-      <c r="L25" s="58" t="n"/>
-      <c r="M25" s="58" t="n"/>
-      <c r="N25" s="58" t="n"/>
-      <c r="O25" s="58" t="n"/>
+    <row r="25" ht="14.4" customHeight="1">
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Effective Rent</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D25" s="52" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E25" s="52" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F25" s="52" t="n">
+        <v>1555</v>
+      </c>
+      <c r="G25" s="52" t="n">
+        <v>1402</v>
+      </c>
+      <c r="H25" s="52" t="n">
+        <v>1369</v>
+      </c>
+      <c r="I25" s="52" t="n">
+        <v>1301</v>
+      </c>
+      <c r="J25" s="53" t="n"/>
+      <c r="K25" s="53" t="n"/>
+      <c r="L25" s="53" t="n"/>
+      <c r="M25" s="53" t="n"/>
+      <c r="N25" s="53" t="n"/>
+      <c r="O25" s="53" t="n"/>
       <c r="R25" s="39" t="inlineStr">
         <is>
           <t>Urban 95 Parcel A</t>
@@ -5992,8 +5960,8 @@
       <c r="S25" s="40" t="n">
         <v>324</v>
       </c>
-      <c r="T25" s="48" t="inlineStr"/>
-      <c r="U25" s="48" t="inlineStr">
+      <c r="T25" s="47" t="inlineStr"/>
+      <c r="U25" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6011,39 +5979,43 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Effective Rent</t>
-        </is>
-      </c>
-      <c r="C26" s="54" t="n">
-        <v>1086</v>
-      </c>
-      <c r="D26" s="54" t="n">
-        <v>1434</v>
-      </c>
-      <c r="E26" s="54" t="n">
-        <v>1730</v>
-      </c>
-      <c r="F26" s="54" t="n">
-        <v>1555</v>
-      </c>
-      <c r="G26" s="54" t="n">
-        <v>1402</v>
-      </c>
-      <c r="H26" s="54" t="n">
-        <v>1369</v>
-      </c>
-      <c r="I26" s="54" t="n">
-        <v>1301</v>
-      </c>
-      <c r="J26" s="55" t="n"/>
-      <c r="K26" s="55" t="n"/>
-      <c r="L26" s="55" t="n"/>
-      <c r="M26" s="55" t="n"/>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="n"/>
+    <row r="26" ht="14.4" customHeight="1">
+      <c r="B26" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Effective Rent YoY %</t>
+        </is>
+      </c>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55">
+        <f>IFERROR(D25/C25-1,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="55">
+        <f>IFERROR(E25/D25-1,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="55">
+        <f>IFERROR(F25/E25-1,"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="55">
+        <f>IFERROR(G25/F25-1,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="55">
+        <f>IFERROR(H25/G25-1,"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="55">
+        <f>IFERROR(I25/H25-1,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="56" t="n"/>
+      <c r="K26" s="56" t="n"/>
+      <c r="L26" s="56" t="n"/>
+      <c r="M26" s="56" t="n"/>
+      <c r="N26" s="56" t="n"/>
+      <c r="O26" s="56" t="n"/>
       <c r="R26" s="39" t="inlineStr">
         <is>
           <t>The Waverly</t>
@@ -6052,12 +6024,12 @@
       <c r="S26" s="40" t="n">
         <v>323</v>
       </c>
-      <c r="T26" s="48" t="inlineStr">
+      <c r="T26" s="47" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U26" s="48" t="inlineStr">
+      <c r="U26" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6075,36 +6047,32 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Effective Rent YoY %</t>
-        </is>
-      </c>
-      <c r="C27" s="57" t="n"/>
-      <c r="D27" s="57">
-        <f>IFERROR(D26/C26-1,"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="57">
-        <f>IFERROR(E26/D26-1,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="57">
-        <f>IFERROR(F26/E26-1,"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="57">
-        <f>IFERROR(G26/F26-1,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="57">
-        <f>IFERROR(H26/G26-1,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="57">
-        <f>IFERROR(I26/H26-1,"")</f>
-        <v/>
+    <row r="27" ht="14.4" customHeight="1">
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
+        </is>
+      </c>
+      <c r="C27" s="57" t="n">
+        <v>0.9503496503496502</v>
+      </c>
+      <c r="D27" s="57" t="n">
+        <v>0.957692307692308</v>
+      </c>
+      <c r="E27" s="57" t="n">
+        <v>0.9458041958041957</v>
+      </c>
+      <c r="F27" s="57" t="n">
+        <v>0.8788971182681028</v>
+      </c>
+      <c r="G27" s="57" t="n">
+        <v>0.9173713229249606</v>
+      </c>
+      <c r="H27" s="57" t="n">
+        <v>0.9334854638634199</v>
+      </c>
+      <c r="I27" s="57" t="n">
+        <v>0.9206643232607364</v>
       </c>
       <c r="J27" s="58" t="n"/>
       <c r="K27" s="58" t="n"/>
@@ -6120,8 +6088,8 @@
       <c r="S27" s="40" t="n">
         <v>321</v>
       </c>
-      <c r="T27" s="48" t="inlineStr"/>
-      <c r="U27" s="48" t="inlineStr">
+      <c r="T27" s="47" t="inlineStr"/>
+      <c r="U27" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6139,39 +6107,37 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="14.4" customHeight="1">
       <c r="B28" s="35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
-        </is>
-      </c>
-      <c r="C28" s="59" t="n">
-        <v>0.9503496503496502</v>
-      </c>
-      <c r="D28" s="59" t="n">
-        <v>0.957692307692308</v>
-      </c>
-      <c r="E28" s="59" t="n">
-        <v>0.9458041958041957</v>
-      </c>
-      <c r="F28" s="59" t="n">
-        <v>0.8788971182681028</v>
-      </c>
-      <c r="G28" s="59" t="n">
-        <v>0.9173713229249606</v>
-      </c>
-      <c r="H28" s="59" t="n">
-        <v>0.9334854638634199</v>
-      </c>
-      <c r="I28" s="59" t="n">
-        <v>0.9206643232607364</v>
-      </c>
-      <c r="J28" s="60" t="n"/>
-      <c r="K28" s="60" t="n"/>
-      <c r="L28" s="60" t="n"/>
-      <c r="M28" s="60" t="n"/>
-      <c r="N28" s="60" t="n"/>
-      <c r="O28" s="60" t="n"/>
+          <t xml:space="preserve">  Concession %</t>
+        </is>
+      </c>
+      <c r="C28" s="57" t="n">
+        <v>0.00570570212563039</v>
+      </c>
+      <c r="D28" s="57" t="n">
+        <v>0.005404400758959575</v>
+      </c>
+      <c r="E28" s="57" t="n"/>
+      <c r="F28" s="57" t="n">
+        <v>0.03835640964430642</v>
+      </c>
+      <c r="G28" s="57" t="n">
+        <v>0.06343995398468492</v>
+      </c>
+      <c r="H28" s="57" t="n">
+        <v>0.07904205281810649</v>
+      </c>
+      <c r="I28" s="57" t="n">
+        <v>0.07045035055908758</v>
+      </c>
+      <c r="J28" s="58" t="n"/>
+      <c r="K28" s="58" t="n"/>
+      <c r="L28" s="58" t="n"/>
+      <c r="M28" s="58" t="n"/>
+      <c r="N28" s="58" t="n"/>
+      <c r="O28" s="58" t="n"/>
       <c r="R28" s="39" t="inlineStr">
         <is>
           <t>Anton Glendale</t>
@@ -6180,8 +6146,8 @@
       <c r="S28" s="40" t="n">
         <v>320</v>
       </c>
-      <c r="T28" s="48" t="inlineStr"/>
-      <c r="U28" s="48" t="inlineStr">
+      <c r="T28" s="47" t="inlineStr"/>
+      <c r="U28" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6199,7 +6165,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="14.4" customHeight="1">
       <c r="R29" s="39" t="inlineStr">
         <is>
           <t>Western Garden II</t>
@@ -6208,8 +6174,8 @@
       <c r="S29" s="40" t="n">
         <v>314</v>
       </c>
-      <c r="T29" s="48" t="inlineStr"/>
-      <c r="U29" s="48" t="inlineStr">
+      <c r="T29" s="47" t="inlineStr"/>
+      <c r="U29" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6227,54 +6193,54 @@
         <v/>
       </c>
     </row>
-    <row r="30" hidden="1">
+    <row r="30" hidden="1" ht="14.4" customHeight="1">
       <c r="B30" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  inventory</t>
         </is>
       </c>
-      <c r="C30" s="53" t="n">
+      <c r="C30" s="59" t="n">
         <v>12401</v>
       </c>
-      <c r="D30" s="53" t="n">
+      <c r="D30" s="59" t="n">
         <v>14261</v>
       </c>
-      <c r="E30" s="53" t="n">
+      <c r="E30" s="59" t="n">
         <v>15597</v>
       </c>
-      <c r="F30" s="53" t="n">
+      <c r="F30" s="59" t="n">
         <v>17877</v>
       </c>
-      <c r="G30" s="53" t="n">
+      <c r="G30" s="59" t="n">
         <v>20700</v>
       </c>
-      <c r="H30" s="53" t="n">
+      <c r="H30" s="59" t="n">
         <v>24743</v>
       </c>
-      <c r="I30" s="53" t="n">
+      <c r="I30" s="59" t="n">
         <v>26603</v>
       </c>
-      <c r="J30" s="53">
+      <c r="J30" s="59">
         <f>I30+J19</f>
         <v/>
       </c>
-      <c r="K30" s="53">
+      <c r="K30" s="59">
         <f>J30+K19</f>
         <v/>
       </c>
-      <c r="L30" s="53">
+      <c r="L30" s="59">
         <f>K30+L19</f>
         <v/>
       </c>
-      <c r="M30" s="53">
+      <c r="M30" s="59">
         <f>L30+M19</f>
         <v/>
       </c>
-      <c r="N30" s="53">
+      <c r="N30" s="59">
         <f>M30+N19</f>
         <v/>
       </c>
-      <c r="O30" s="53">
+      <c r="O30" s="59">
         <f>N30+O19</f>
         <v/>
       </c>
@@ -6286,8 +6252,8 @@
       <c r="S30" s="40" t="n">
         <v>303</v>
       </c>
-      <c r="T30" s="48" t="inlineStr"/>
-      <c r="U30" s="48" t="inlineStr">
+      <c r="T30" s="47" t="inlineStr"/>
+      <c r="U30" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6305,54 +6271,54 @@
         <v/>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31" hidden="1" ht="14.4" customHeight="1">
       <c r="B31" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  occupied</t>
         </is>
       </c>
-      <c r="C31" s="53" t="n">
+      <c r="C31" s="59" t="n">
         <v>11277</v>
       </c>
-      <c r="D31" s="53" t="n">
+      <c r="D31" s="59" t="n">
         <v>13152</v>
       </c>
-      <c r="E31" s="53" t="n">
+      <c r="E31" s="59" t="n">
         <v>14362</v>
       </c>
-      <c r="F31" s="53" t="n">
+      <c r="F31" s="59" t="n">
         <v>15047</v>
       </c>
-      <c r="G31" s="53" t="n">
+      <c r="G31" s="59" t="n">
         <v>17560</v>
       </c>
-      <c r="H31" s="53" t="n">
+      <c r="H31" s="59" t="n">
         <v>20215</v>
       </c>
-      <c r="I31" s="53" t="n">
+      <c r="I31" s="59" t="n">
         <v>22585</v>
       </c>
-      <c r="J31" s="53">
+      <c r="J31" s="59">
         <f>MIN($C$6*J30,I31+$C$11)</f>
         <v/>
       </c>
-      <c r="K31" s="53">
+      <c r="K31" s="59">
         <f>MIN($C$6*K30,J31+$C$11)</f>
         <v/>
       </c>
-      <c r="L31" s="53">
+      <c r="L31" s="59">
         <f>MIN($C$6*L30,K31+$C$11)</f>
         <v/>
       </c>
-      <c r="M31" s="53">
+      <c r="M31" s="59">
         <f>MIN($C$6*M30,L31+$C$11)</f>
         <v/>
       </c>
-      <c r="N31" s="53">
+      <c r="N31" s="59">
         <f>MIN($C$6*N30,M31+$C$11)</f>
         <v/>
       </c>
-      <c r="O31" s="53">
+      <c r="O31" s="59">
         <f>MIN($C$6*O30,N31+$C$11)</f>
         <v/>
       </c>
@@ -6364,12 +6330,12 @@
       <c r="S31" s="40" t="n">
         <v>300</v>
       </c>
-      <c r="T31" s="48" t="inlineStr">
+      <c r="T31" s="47" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U31" s="48" t="inlineStr">
+      <c r="U31" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6387,7 +6353,7 @@
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="14.4" customHeight="1">
       <c r="R32" s="39" t="inlineStr">
         <is>
           <t>Banyan Avondale</t>
@@ -6396,8 +6362,8 @@
       <c r="S32" s="40" t="n">
         <v>296</v>
       </c>
-      <c r="T32" s="48" t="inlineStr"/>
-      <c r="U32" s="48" t="inlineStr">
+      <c r="T32" s="47" t="inlineStr"/>
+      <c r="U32" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6415,38 +6381,38 @@
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="14.4" customHeight="1">
       <c r="B33" s="35" t="inlineStr">
         <is>
           <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
         </is>
       </c>
-      <c r="J33" s="61" t="inlineStr">
+      <c r="J33" s="60" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K33" s="61" t="inlineStr">
+      <c r="K33" s="60" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L33" s="61" t="inlineStr">
+      <c r="L33" s="60" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M33" s="61" t="inlineStr">
+      <c r="M33" s="60" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N33" s="61" t="inlineStr">
+      <c r="N33" s="60" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O33" s="61" t="inlineStr">
+      <c r="O33" s="60" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
@@ -6459,8 +6425,8 @@
       <c r="S33" s="40" t="n">
         <v>291</v>
       </c>
-      <c r="T33" s="48" t="inlineStr"/>
-      <c r="U33" s="48" t="inlineStr">
+      <c r="T33" s="47" t="inlineStr"/>
+      <c r="U33" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6478,33 +6444,33 @@
         <v/>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="14.4" customHeight="1">
       <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J34" s="62">
+      <c r="J34" s="61">
         <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
         <v/>
       </c>
-      <c r="K34" s="62">
+      <c r="K34" s="61">
         <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
         <v/>
       </c>
-      <c r="L34" s="62">
+      <c r="L34" s="61">
         <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
         <v/>
       </c>
-      <c r="M34" s="62">
+      <c r="M34" s="61">
         <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
         <v/>
       </c>
-      <c r="N34" s="62">
+      <c r="N34" s="61">
         <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
         <v/>
       </c>
-      <c r="O34" s="62">
+      <c r="O34" s="61">
         <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
         <v/>
       </c>
@@ -6516,12 +6482,12 @@
       <c r="S34" s="40" t="n">
         <v>284</v>
       </c>
-      <c r="T34" s="48" t="inlineStr">
+      <c r="T34" s="47" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U34" s="48" t="inlineStr">
+      <c r="U34" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6539,33 +6505,33 @@
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="14.4" customHeight="1">
       <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J35" s="62">
+      <c r="J35" s="61">
         <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
         <v/>
       </c>
-      <c r="K35" s="62">
+      <c r="K35" s="61">
         <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
         <v/>
       </c>
-      <c r="L35" s="62">
+      <c r="L35" s="61">
         <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
         <v/>
       </c>
-      <c r="M35" s="62">
+      <c r="M35" s="61">
         <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
         <v/>
       </c>
-      <c r="N35" s="62">
+      <c r="N35" s="61">
         <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
         <v/>
       </c>
-      <c r="O35" s="62">
+      <c r="O35" s="61">
         <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
         <v/>
       </c>
@@ -6577,8 +6543,8 @@
       <c r="S35" s="40" t="n">
         <v>268</v>
       </c>
-      <c r="T35" s="48" t="inlineStr"/>
-      <c r="U35" s="48" t="inlineStr">
+      <c r="T35" s="47" t="inlineStr"/>
+      <c r="U35" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6596,33 +6562,33 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="14.4" customHeight="1">
       <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J36" s="62">
+      <c r="J36" s="61">
         <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
         <v/>
       </c>
-      <c r="K36" s="62">
+      <c r="K36" s="61">
         <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
         <v/>
       </c>
-      <c r="L36" s="62">
+      <c r="L36" s="61">
         <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
         <v/>
       </c>
-      <c r="M36" s="62">
+      <c r="M36" s="61">
         <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
         <v/>
       </c>
-      <c r="N36" s="62">
+      <c r="N36" s="61">
         <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
         <v/>
       </c>
-      <c r="O36" s="62">
+      <c r="O36" s="61">
         <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
         <v/>
       </c>
@@ -6634,8 +6600,8 @@
       <c r="S36" s="40" t="n">
         <v>266</v>
       </c>
-      <c r="T36" s="48" t="inlineStr"/>
-      <c r="U36" s="48" t="inlineStr">
+      <c r="T36" s="47" t="inlineStr"/>
+      <c r="U36" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6653,7 +6619,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="14.4" customHeight="1">
       <c r="R37" s="39" t="inlineStr">
         <is>
           <t>Marbella Ranch East Future Phase</t>
@@ -6662,8 +6628,8 @@
       <c r="S37" s="40" t="n">
         <v>266</v>
       </c>
-      <c r="T37" s="48" t="inlineStr"/>
-      <c r="U37" s="48" t="inlineStr">
+      <c r="T37" s="47" t="inlineStr"/>
+      <c r="U37" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6681,38 +6647,38 @@
         <v/>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="14.4" customHeight="1">
       <c r="B38" s="35" t="inlineStr">
         <is>
           <t>MARKET RENT GROWTH (editable assumptions)</t>
         </is>
       </c>
-      <c r="J38" s="63" t="inlineStr">
+      <c r="J38" s="62" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K38" s="63" t="inlineStr">
+      <c r="K38" s="62" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L38" s="63" t="inlineStr">
+      <c r="L38" s="62" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M38" s="63" t="inlineStr">
+      <c r="M38" s="62" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N38" s="63" t="inlineStr">
+      <c r="N38" s="62" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O38" s="63" t="inlineStr">
+      <c r="O38" s="62" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
@@ -6725,8 +6691,8 @@
       <c r="S38" s="40" t="n">
         <v>260</v>
       </c>
-      <c r="T38" s="48" t="inlineStr"/>
-      <c r="U38" s="48" t="inlineStr">
+      <c r="T38" s="47" t="inlineStr"/>
+      <c r="U38" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6744,28 +6710,28 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="14.4" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J39" s="64" t="n">
+      <c r="J39" s="63" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="K39" s="64" t="n">
+      <c r="K39" s="63" t="n">
         <v>0.0175</v>
       </c>
-      <c r="L39" s="64" t="n">
+      <c r="L39" s="63" t="n">
         <v>0.0275</v>
       </c>
-      <c r="M39" s="64" t="n">
+      <c r="M39" s="63" t="n">
         <v>0.0375</v>
       </c>
-      <c r="N39" s="64" t="n">
+      <c r="N39" s="63" t="n">
         <v>0.0275</v>
       </c>
-      <c r="O39" s="64" t="n">
+      <c r="O39" s="63" t="n">
         <v>0.0175</v>
       </c>
       <c r="R39" s="39" t="inlineStr">
@@ -6776,8 +6742,8 @@
       <c r="S39" s="40" t="n">
         <v>212</v>
       </c>
-      <c r="T39" s="48" t="inlineStr"/>
-      <c r="U39" s="48" t="inlineStr">
+      <c r="T39" s="47" t="inlineStr"/>
+      <c r="U39" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6795,28 +6761,28 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="14.4" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J40" s="64" t="n">
+      <c r="J40" s="63" t="n">
         <v>0.01</v>
       </c>
-      <c r="K40" s="64" t="n">
+      <c r="K40" s="63" t="n">
         <v>0.03</v>
       </c>
-      <c r="L40" s="64" t="n">
+      <c r="L40" s="63" t="n">
         <v>0.04</v>
       </c>
-      <c r="M40" s="64" t="n">
+      <c r="M40" s="63" t="n">
         <v>0.05</v>
       </c>
-      <c r="N40" s="64" t="n">
+      <c r="N40" s="63" t="n">
         <v>0.04</v>
       </c>
-      <c r="O40" s="64" t="n">
+      <c r="O40" s="63" t="n">
         <v>0.03</v>
       </c>
       <c r="R40" s="39" t="inlineStr">
@@ -6827,8 +6793,8 @@
       <c r="S40" s="40" t="n">
         <v>212</v>
       </c>
-      <c r="T40" s="48" t="inlineStr"/>
-      <c r="U40" s="48" t="inlineStr">
+      <c r="T40" s="47" t="inlineStr"/>
+      <c r="U40" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6846,28 +6812,28 @@
         <v/>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="14.4" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J41" s="64" t="n">
+      <c r="J41" s="63" t="n">
         <v>0.02</v>
       </c>
-      <c r="K41" s="64" t="n">
+      <c r="K41" s="63" t="n">
         <v>0.04</v>
       </c>
-      <c r="L41" s="64" t="n">
+      <c r="L41" s="63" t="n">
         <v>0.05</v>
       </c>
-      <c r="M41" s="64" t="n">
+      <c r="M41" s="63" t="n">
         <v>0.06</v>
       </c>
-      <c r="N41" s="64" t="n">
+      <c r="N41" s="63" t="n">
         <v>0.05</v>
       </c>
-      <c r="O41" s="64" t="n">
+      <c r="O41" s="63" t="n">
         <v>0.04</v>
       </c>
       <c r="R41" s="39" t="inlineStr">
@@ -6878,8 +6844,8 @@
       <c r="S41" s="40" t="n">
         <v>181</v>
       </c>
-      <c r="T41" s="48" t="inlineStr"/>
-      <c r="U41" s="48" t="inlineStr">
+      <c r="T41" s="47" t="inlineStr"/>
+      <c r="U41" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6897,10 +6863,10 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="14.4" customHeight="1">
       <c r="B42" s="35" t="inlineStr">
         <is>
-          <t>CONCESSIONS (months, editable)</t>
+          <t>CONCESSIONS % — forward assumption (editable)</t>
         </is>
       </c>
       <c r="R42" s="39" t="inlineStr">
@@ -6911,8 +6877,8 @@
       <c r="S42" s="40" t="n">
         <v>180</v>
       </c>
-      <c r="T42" s="48" t="inlineStr"/>
-      <c r="U42" s="48" t="inlineStr">
+      <c r="T42" s="47" t="inlineStr"/>
+      <c r="U42" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6930,28 +6896,28 @@
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="14.4" customHeight="1">
       <c r="B43" s="35" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J43" s="64" t="n">
+      <c r="J43" s="63" t="n">
         <v>0.06</v>
       </c>
-      <c r="K43" s="64" t="n">
+      <c r="K43" s="63" t="n">
         <v>0.045</v>
       </c>
-      <c r="L43" s="64" t="n">
+      <c r="L43" s="63" t="n">
         <v>0.035</v>
       </c>
-      <c r="M43" s="64" t="n">
+      <c r="M43" s="63" t="n">
         <v>0.035</v>
       </c>
-      <c r="N43" s="64" t="n">
+      <c r="N43" s="63" t="n">
         <v>0.035</v>
       </c>
-      <c r="O43" s="64" t="n">
+      <c r="O43" s="63" t="n">
         <v>0.035</v>
       </c>
       <c r="R43" s="39" t="inlineStr">
@@ -6962,8 +6928,8 @@
       <c r="S43" s="40" t="n">
         <v>172</v>
       </c>
-      <c r="T43" s="48" t="inlineStr"/>
-      <c r="U43" s="48" t="inlineStr">
+      <c r="T43" s="47" t="inlineStr"/>
+      <c r="U43" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6981,28 +6947,28 @@
         <v/>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="14.4" customHeight="1">
       <c r="B44" s="35" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J44" s="64" t="n">
+      <c r="J44" s="63" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" s="64" t="n">
+      <c r="K44" s="63" t="n">
         <v>0.015</v>
       </c>
-      <c r="L44" s="64" t="n">
+      <c r="L44" s="63" t="n">
         <v>0.005</v>
       </c>
-      <c r="M44" s="64" t="n">
+      <c r="M44" s="63" t="n">
         <v>0.005</v>
       </c>
-      <c r="N44" s="64" t="n">
+      <c r="N44" s="63" t="n">
         <v>0.005</v>
       </c>
-      <c r="O44" s="64" t="n">
+      <c r="O44" s="63" t="n">
         <v>0.005</v>
       </c>
       <c r="R44" s="39" t="inlineStr">
@@ -7013,8 +6979,8 @@
       <c r="S44" s="40" t="n">
         <v>164</v>
       </c>
-      <c r="T44" s="48" t="inlineStr"/>
-      <c r="U44" s="48" t="inlineStr">
+      <c r="T44" s="47" t="inlineStr"/>
+      <c r="U44" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7032,28 +6998,28 @@
         <v/>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="14.4" customHeight="1">
       <c r="B45" s="35" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J45" s="64" t="n">
+      <c r="J45" s="63" t="n">
         <v>0.02</v>
       </c>
-      <c r="K45" s="64" t="n">
+      <c r="K45" s="63" t="n">
         <v>0.005</v>
       </c>
-      <c r="L45" s="64" t="n">
+      <c r="L45" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="64" t="n">
+      <c r="M45" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="64" t="n">
+      <c r="N45" s="63" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="64" t="n">
+      <c r="O45" s="63" t="n">
         <v>0</v>
       </c>
       <c r="R45" s="39" t="inlineStr">
@@ -7064,8 +7030,8 @@
       <c r="S45" s="40" t="n">
         <v>156</v>
       </c>
-      <c r="T45" s="48" t="inlineStr"/>
-      <c r="U45" s="48" t="inlineStr">
+      <c r="T45" s="47" t="inlineStr"/>
+      <c r="U45" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7083,7 +7049,7 @@
         <v/>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="14.4" customHeight="1">
       <c r="B46" s="35" t="inlineStr">
         <is>
           <t>EFFECTIVE RENT GROWTH (derived)</t>
@@ -7097,8 +7063,8 @@
       <c r="S46" s="40" t="n">
         <v>135</v>
       </c>
-      <c r="T46" s="48" t="inlineStr"/>
-      <c r="U46" s="48" t="inlineStr">
+      <c r="T46" s="47" t="inlineStr"/>
+      <c r="U46" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7116,33 +7082,33 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="14.4" customHeight="1">
       <c r="B47" s="35" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J47" s="62">
+      <c r="J47" s="61">
         <f>(1+J39)*(1-J43)-1</f>
         <v/>
       </c>
-      <c r="K47" s="62">
+      <c r="K47" s="61">
         <f>(1+K39)*(1-K43)/(1-J43)-1</f>
         <v/>
       </c>
-      <c r="L47" s="62">
+      <c r="L47" s="61">
         <f>(1+L39)*(1-L43)/(1-K43)-1</f>
         <v/>
       </c>
-      <c r="M47" s="62">
+      <c r="M47" s="61">
         <f>(1+M39)*(1-M43)/(1-L43)-1</f>
         <v/>
       </c>
-      <c r="N47" s="62">
+      <c r="N47" s="61">
         <f>(1+N39)*(1-N43)/(1-M43)-1</f>
         <v/>
       </c>
-      <c r="O47" s="62">
+      <c r="O47" s="61">
         <f>(1+O39)*(1-O43)/(1-N43)-1</f>
         <v/>
       </c>
@@ -7154,12 +7120,12 @@
       <c r="S47" s="40" t="n">
         <v>113</v>
       </c>
-      <c r="T47" s="48" t="inlineStr">
+      <c r="T47" s="47" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U47" s="48" t="inlineStr">
+      <c r="U47" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7177,33 +7143,33 @@
         <v/>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="14.4" customHeight="1">
       <c r="B48" s="35" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J48" s="62">
+      <c r="J48" s="61">
         <f>(1+J40)*(1-J44)-1</f>
         <v/>
       </c>
-      <c r="K48" s="62">
+      <c r="K48" s="61">
         <f>(1+K40)*(1-K44)/(1-J44)-1</f>
         <v/>
       </c>
-      <c r="L48" s="62">
+      <c r="L48" s="61">
         <f>(1+L40)*(1-L44)/(1-K44)-1</f>
         <v/>
       </c>
-      <c r="M48" s="62">
+      <c r="M48" s="61">
         <f>(1+M40)*(1-M44)/(1-L44)-1</f>
         <v/>
       </c>
-      <c r="N48" s="62">
+      <c r="N48" s="61">
         <f>(1+N40)*(1-N44)/(1-M44)-1</f>
         <v/>
       </c>
-      <c r="O48" s="62">
+      <c r="O48" s="61">
         <f>(1+O40)*(1-O44)/(1-N44)-1</f>
         <v/>
       </c>
@@ -7215,12 +7181,12 @@
       <c r="S48" s="40" t="n">
         <v>74</v>
       </c>
-      <c r="T48" s="48" t="inlineStr">
+      <c r="T48" s="47" t="inlineStr">
         <is>
           <t>Q4 2028</t>
         </is>
       </c>
-      <c r="U48" s="48" t="inlineStr">
+      <c r="U48" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7238,33 +7204,33 @@
         <v/>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="14.4" customHeight="1">
       <c r="B49" s="35" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J49" s="62">
+      <c r="J49" s="61">
         <f>(1+J41)*(1-J45)-1</f>
         <v/>
       </c>
-      <c r="K49" s="62">
+      <c r="K49" s="61">
         <f>(1+K41)*(1-K45)/(1-J45)-1</f>
         <v/>
       </c>
-      <c r="L49" s="62">
+      <c r="L49" s="61">
         <f>(1+L41)*(1-L45)/(1-K45)-1</f>
         <v/>
       </c>
-      <c r="M49" s="62">
+      <c r="M49" s="61">
         <f>(1+M41)*(1-M45)/(1-L45)-1</f>
         <v/>
       </c>
-      <c r="N49" s="62">
+      <c r="N49" s="61">
         <f>(1+N41)*(1-N45)/(1-M45)-1</f>
         <v/>
       </c>
-      <c r="O49" s="62">
+      <c r="O49" s="61">
         <f>(1+O41)*(1-O45)/(1-N45)-1</f>
         <v/>
       </c>
@@ -7276,8 +7242,8 @@
       <c r="S49" s="40" t="n">
         <v>66</v>
       </c>
-      <c r="T49" s="48" t="inlineStr"/>
-      <c r="U49" s="48" t="inlineStr">
+      <c r="T49" s="47" t="inlineStr"/>
+      <c r="U49" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7295,20 +7261,15 @@
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="33" t="inlineStr">
-        <is>
-          <t>Reconciliation: UC pipeline scheduled = 1,947 units vs CoStar current Under Construction = 1,251 units.</t>
-        </is>
-      </c>
+    <row r="50" ht="14.4" customHeight="1">
       <c r="R50" s="39" t="inlineStr">
         <is>
           <t>The BLVD Residential District</t>
         </is>
       </c>
       <c r="S50" s="40" t="n"/>
-      <c r="T50" s="48" t="inlineStr"/>
-      <c r="U50" s="48" t="inlineStr">
+      <c r="T50" s="47" t="inlineStr"/>
+      <c r="U50" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7326,10 +7287,10 @@
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="33" t="inlineStr">
-        <is>
-          <t>Note: as-of quarter (2026 Q2 QTD) is partial (quarter-to-date). Occupancy is point-in-time (valid); Y0 supply/absorption sums for that quarter are partial.</t>
+    <row r="51" ht="14.4" customHeight="1">
+      <c r="B51" s="62" t="inlineStr">
+        <is>
+          <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
         </is>
       </c>
       <c r="R51" s="39" t="inlineStr">
@@ -7338,8 +7299,8 @@
         </is>
       </c>
       <c r="S51" s="40" t="n"/>
-      <c r="T51" s="48" t="inlineStr"/>
-      <c r="U51" s="48" t="inlineStr">
+      <c r="T51" s="47" t="inlineStr"/>
+      <c r="U51" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7357,10 +7318,15 @@
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="33" t="inlineStr">
-        <is>
-          <t>Historical = CoStar 5-mi TTM actuals. Forecast: inventory += UC (linked from Competitive Analysis) + proposed built this scenario; occupied += selected demand (capped at target). Yellow cells are editable.</t>
+    <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="inlineStr">
+        <is>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="R52" s="39" t="inlineStr">
@@ -7369,8 +7335,8 @@
         </is>
       </c>
       <c r="S52" s="40" t="n"/>
-      <c r="T52" s="48" t="inlineStr"/>
-      <c r="U52" s="48" t="inlineStr">
+      <c r="T52" s="47" t="inlineStr"/>
+      <c r="U52" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7388,15 +7354,25 @@
         <v/>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
+        </is>
+      </c>
+      <c r="E53" s="64" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
       <c r="R53" s="39" t="inlineStr">
         <is>
           <t>Ball Park</t>
         </is>
       </c>
       <c r="S53" s="40" t="n"/>
-      <c r="T53" s="48" t="inlineStr"/>
-      <c r="U53" s="48" t="inlineStr">
+      <c r="T53" s="47" t="inlineStr"/>
+      <c r="U53" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7414,15 +7390,25 @@
         <v/>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
+        </is>
+      </c>
+      <c r="E54" s="64" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
       <c r="R54" s="39" t="inlineStr">
         <is>
           <t>Vision 2 Parcel A</t>
         </is>
       </c>
       <c r="S54" s="40" t="n"/>
-      <c r="T54" s="48" t="inlineStr"/>
-      <c r="U54" s="48" t="inlineStr">
+      <c r="T54" s="47" t="inlineStr"/>
+      <c r="U54" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7440,15 +7426,25 @@
         <v/>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
+        </is>
+      </c>
+      <c r="E55" s="64" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
       <c r="R55" s="39" t="inlineStr">
         <is>
           <t>Firststreet Verde</t>
         </is>
       </c>
       <c r="S55" s="40" t="n"/>
-      <c r="T55" s="48" t="inlineStr"/>
-      <c r="U55" s="48" t="inlineStr">
+      <c r="T55" s="47" t="inlineStr"/>
+      <c r="U55" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7466,15 +7462,25 @@
         <v/>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
+        </is>
+      </c>
+      <c r="E56" s="64" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
       <c r="R56" s="39" t="inlineStr">
         <is>
           <t>Goodyear Civic Square at Estrella Falls</t>
         </is>
       </c>
       <c r="S56" s="40" t="n"/>
-      <c r="T56" s="48" t="inlineStr"/>
-      <c r="U56" s="48" t="inlineStr">
+      <c r="T56" s="47" t="inlineStr"/>
+      <c r="U56" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7492,15 +7498,25 @@
         <v/>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
+        </is>
+      </c>
+      <c r="E57" s="64" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
       <c r="R57" s="39" t="inlineStr">
         <is>
           <t>I-10 Innovation Center II</t>
         </is>
       </c>
       <c r="S57" s="40" t="n"/>
-      <c r="T57" s="48" t="inlineStr"/>
-      <c r="U57" s="48" t="inlineStr">
+      <c r="T57" s="47" t="inlineStr"/>
+      <c r="U57" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7518,15 +7534,25 @@
         <v/>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B58" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
+        </is>
+      </c>
+      <c r="E58" s="64" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
       <c r="R58" s="39" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel D</t>
         </is>
       </c>
       <c r="S58" s="40" t="n"/>
-      <c r="T58" s="48" t="inlineStr"/>
-      <c r="U58" s="48" t="inlineStr">
+      <c r="T58" s="47" t="inlineStr"/>
+      <c r="U58" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7544,15 +7570,25 @@
         <v/>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
+        </is>
+      </c>
+      <c r="E59" s="64" t="inlineStr">
+        <is>
+          <t>1,947 / 1,251</t>
+        </is>
+      </c>
       <c r="R59" s="39" t="inlineStr">
         <is>
           <t>SimonMed Development II</t>
         </is>
       </c>
       <c r="S59" s="40" t="n"/>
-      <c r="T59" s="48" t="inlineStr"/>
-      <c r="U59" s="48" t="inlineStr">
+      <c r="T59" s="47" t="inlineStr"/>
+      <c r="U59" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7570,15 +7606,20 @@
         <v/>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B60" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
+        </is>
+      </c>
       <c r="R60" s="39" t="inlineStr">
         <is>
           <t>182 South 95th Avenue</t>
         </is>
       </c>
       <c r="S60" s="40" t="n"/>
-      <c r="T60" s="48" t="inlineStr"/>
-      <c r="U60" s="48" t="inlineStr">
+      <c r="T60" s="47" t="inlineStr"/>
+      <c r="U60" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7596,15 +7637,15 @@
         <v/>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="14.4" customHeight="1">
       <c r="R61" s="39" t="inlineStr">
         <is>
           <t>Envision Encore</t>
         </is>
       </c>
       <c r="S61" s="40" t="n"/>
-      <c r="T61" s="48" t="inlineStr"/>
-      <c r="U61" s="48" t="inlineStr">
+      <c r="T61" s="47" t="inlineStr"/>
+      <c r="U61" s="47" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7622,6 +7663,7 @@
         <v/>
       </c>
     </row>
+    <row r="62" ht="14.4" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:O2"/>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -320,13 +320,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K118"/>
+  <dimension ref="B2:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Units: CoStar 292 vs RealPage 239; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 87%</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 87%</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="K53" s="15" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 13% vs RealPage 0%; Rent: CoStar ask $1,411 vs RealPage eff $1,145; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       <c r="B59" s="19" t="n"/>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>UNDER CONSTRUCTION (10 properties, 1,947 units)</t>
+          <t>UNDER CONSTRUCTION (11 properties, 2,307 units)</t>
         </is>
       </c>
     </row>
@@ -2851,11 +2851,11 @@
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>FUZE Ballpark</t>
+          <t>Flatz623</t>
         </is>
       </c>
       <c r="D60" s="23" t="n">
-        <v>321</v>
+        <v>360</v>
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       <c r="I60" s="21" t="n"/>
       <c r="J60" s="21" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Low-Rise</t>
         </is>
       </c>
       <c r="K60" s="22" t="n"/>
@@ -2887,15 +2887,15 @@
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>HARMON Ascend</t>
+          <t>FUZE Ballpark</t>
         </is>
       </c>
       <c r="D61" s="23" t="n">
-        <v>125</v>
+        <v>321</v>
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
-          <t>Q1 2027</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F61" s="24" t="n"/>
@@ -2906,13 +2906,13 @@
       </c>
       <c r="H61" s="22" t="inlineStr">
         <is>
-          <t>Crescent Communities LLC</t>
+          <t>Zekelman Industries</t>
         </is>
       </c>
       <c r="I61" s="21" t="n"/>
       <c r="J61" s="21" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K61" s="22" t="n"/>
@@ -2923,15 +2923,15 @@
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>Pointe Grand Estrella at Phoenix</t>
+          <t>HARMON Ascend</t>
         </is>
       </c>
       <c r="D62" s="23" t="n">
-        <v>288</v>
+        <v>125</v>
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
+          <t>Q1 2027</t>
         </is>
       </c>
       <c r="F62" s="24" t="n"/>
@@ -2942,20 +2942,16 @@
       </c>
       <c r="H62" s="22" t="inlineStr">
         <is>
-          <t>Hillpointe, LLC</t>
+          <t>Crescent Communities LLC</t>
         </is>
       </c>
       <c r="I62" s="21" t="n"/>
       <c r="J62" s="21" t="inlineStr">
         <is>
-          <t>Garden</t>
-        </is>
-      </c>
-      <c r="K62" s="22" t="inlineStr">
-        <is>
-          <t>Year built: 2026/2027</t>
-        </is>
-      </c>
+          <t>Townhome</t>
+        </is>
+      </c>
+      <c r="K62" s="22" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="21" t="n">
@@ -2963,11 +2959,11 @@
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>Marbella Ranch East I</t>
+          <t>Pointe Grand Estrella at Phoenix</t>
         </is>
       </c>
       <c r="D63" s="23" t="n">
-        <v>144</v>
+        <v>288</v>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
@@ -2982,7 +2978,7 @@
       </c>
       <c r="H63" s="22" t="inlineStr">
         <is>
-          <t>Symmetry Companies</t>
+          <t>Hillpointe, LLC</t>
         </is>
       </c>
       <c r="I63" s="21" t="n"/>
@@ -2991,7 +2987,11 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K63" s="22" t="n"/>
+      <c r="K63" s="22" t="inlineStr">
+        <is>
+          <t>Year built: 2026/2027</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="21" t="n">
@@ -2999,11 +2999,11 @@
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>Villages at Northern</t>
+          <t>Marbella Ranch East I</t>
         </is>
       </c>
       <c r="D64" s="23" t="n">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H64" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Symmetry Companies</t>
         </is>
       </c>
       <c r="I64" s="21" t="n"/>
@@ -3035,11 +3035,11 @@
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>Prosper 47</t>
+          <t>Villages at Northern</t>
         </is>
       </c>
       <c r="D65" s="23" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
@@ -3060,14 +3060,10 @@
       <c r="I65" s="21" t="n"/>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>Townhome</t>
-        </is>
-      </c>
-      <c r="K65" s="22" t="inlineStr">
-        <is>
-          <t>RealPage only (sub-50 unit)</t>
-        </is>
-      </c>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K65" s="22" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="21" t="n">
@@ -3075,15 +3071,15 @@
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>Yardly Algodon</t>
+          <t>Prosper 47</t>
         </is>
       </c>
       <c r="D66" s="23" t="n">
-        <v>262</v>
+        <v>47</v>
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="F66" s="24" t="n"/>
@@ -3094,18 +3090,18 @@
       </c>
       <c r="H66" s="22" t="inlineStr">
         <is>
-          <t>Taylor Morrison, Inc.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I66" s="21" t="n"/>
       <c r="J66" s="21" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K66" s="22" t="inlineStr">
         <is>
-          <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
+          <t>RealPage only (sub-50 unit)</t>
         </is>
       </c>
     </row>
@@ -3115,11 +3111,11 @@
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>Cerro Vista</t>
+          <t>Yardly Algodon</t>
         </is>
       </c>
       <c r="D67" s="23" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
@@ -3134,16 +3130,20 @@
       </c>
       <c r="H67" s="22" t="inlineStr">
         <is>
-          <t>Virtua Partners</t>
+          <t>Taylor Morrison, Inc.</t>
         </is>
       </c>
       <c r="I67" s="21" t="n"/>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>Low-Rise</t>
-        </is>
-      </c>
-      <c r="K67" s="22" t="n"/>
+          <t>Single Family</t>
+        </is>
+      </c>
+      <c r="K67" s="22" t="inlineStr">
+        <is>
+          <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="21" t="n">
@@ -3151,15 +3151,15 @@
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>Zanjero III</t>
+          <t>Cerro Vista</t>
         </is>
       </c>
       <c r="D68" s="23" t="n">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F68" s="24" t="n"/>
@@ -3170,13 +3170,13 @@
       </c>
       <c r="H68" s="22" t="inlineStr">
         <is>
-          <t>Fore Property Company/Privately Owned</t>
+          <t>Virtua Partners</t>
         </is>
       </c>
       <c r="I68" s="21" t="n"/>
       <c r="J68" s="21" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Low-Rise</t>
         </is>
       </c>
       <c r="K68" s="22" t="n"/>
@@ -3187,11 +3187,11 @@
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>Zen @ Angelina</t>
+          <t>Zanjero III</t>
         </is>
       </c>
       <c r="D69" s="23" t="n">
-        <v>130</v>
+        <v>301</v>
       </c>
       <c r="E69" s="21" t="inlineStr">
         <is>
@@ -3206,64 +3206,64 @@
       </c>
       <c r="H69" s="22" t="inlineStr">
         <is>
-          <t>F &amp; S Consulting &amp; Management, LLC</t>
+          <t>Fore Property Company/Privately Owned</t>
         </is>
       </c>
       <c r="I69" s="21" t="n"/>
       <c r="J69" s="21" t="inlineStr">
         <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>Zen @ Angelina</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>130</v>
+      </c>
+      <c r="E70" s="21" t="inlineStr">
+        <is>
+          <t>Q2 2028</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="n"/>
+      <c r="G70" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>F &amp; S Consulting &amp; Management, LLC</t>
+        </is>
+      </c>
+      <c r="I70" s="21" t="n"/>
+      <c r="J70" s="21" t="inlineStr">
+        <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K69" s="22" t="inlineStr">
+      <c r="K70" s="22" t="inlineStr">
         <is>
           <t>Year built: 2027/2028</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="26" t="n"/>
-      <c r="C71" s="27" t="inlineStr">
-        <is>
-          <t>PROPOSED (44 properties, 8,986 units)</t>
-        </is>
-      </c>
-    </row>
     <row r="72">
-      <c r="B72" s="28" t="n">
-        <v>61</v>
-      </c>
-      <c r="C72" s="29" t="inlineStr">
-        <is>
-          <t>The Waverly</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="n">
-        <v>323</v>
-      </c>
-      <c r="E72" s="28" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="n"/>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="29" t="inlineStr">
-        <is>
-          <t>Dominium</t>
-        </is>
-      </c>
-      <c r="I72" s="28" t="n"/>
-      <c r="J72" s="28" t="inlineStr">
-        <is>
-          <t>Mid-Rise</t>
-        </is>
-      </c>
-      <c r="K72" s="29" t="n"/>
+      <c r="B72" s="26" t="n"/>
+      <c r="C72" s="27" t="inlineStr">
+        <is>
+          <t>PROPOSED (45 properties, 9,225 units)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="28" t="n">
@@ -3271,11 +3271,11 @@
       </c>
       <c r="C73" s="29" t="inlineStr">
         <is>
-          <t>Encore Avondale</t>
+          <t>The Waverly</t>
         </is>
       </c>
       <c r="D73" s="30" t="n">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="E73" s="28" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>Encore Enterprises</t>
+          <t>Dominium</t>
         </is>
       </c>
       <c r="I73" s="28" t="n"/>
@@ -3307,11 +3307,11 @@
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>The Statler at Estrella Parkway</t>
+          <t>Encore Avondale</t>
         </is>
       </c>
       <c r="D74" s="30" t="n">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="E74" s="28" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>Leon Capital Group</t>
+          <t>Encore Enterprises</t>
         </is>
       </c>
       <c r="I74" s="28" t="n"/>
@@ -3343,11 +3343,11 @@
       </c>
       <c r="C75" s="29" t="inlineStr">
         <is>
-          <t>Ascent Goodyear</t>
+          <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
       <c r="D75" s="30" t="n">
-        <v>113</v>
+        <v>284</v>
       </c>
       <c r="E75" s="28" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>Ascent Companies</t>
+          <t>Leon Capital Group</t>
         </is>
       </c>
       <c r="I75" s="28" t="n"/>
       <c r="J75" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K75" s="29" t="n"/>
@@ -3379,15 +3379,15 @@
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>Northern 107</t>
+          <t>Ascent Goodyear</t>
         </is>
       </c>
       <c r="D76" s="30" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E76" s="28" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2028</t>
         </is>
       </c>
       <c r="F76" s="31" t="n"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H76" s="29" t="inlineStr">
         <is>
-          <t>Jacob Reuben</t>
+          <t>Ascent Companies</t>
         </is>
       </c>
       <c r="I76" s="28" t="n"/>
@@ -3415,15 +3415,15 @@
       </c>
       <c r="C77" s="29" t="inlineStr">
         <is>
-          <t>Sheely Center Future Phase</t>
+          <t>Northern 107</t>
         </is>
       </c>
       <c r="D77" s="30" t="n">
-        <v>697</v>
+        <v>74</v>
       </c>
       <c r="E77" s="28" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F77" s="31" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="H77" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jacob Reuben</t>
         </is>
       </c>
       <c r="I77" s="28" t="n"/>
@@ -3443,11 +3443,7 @@
           <t>Garden</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+      <c r="K77" s="29" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="28" t="n">
@@ -3455,11 +3451,11 @@
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel C</t>
+          <t>Sheely Center Future Phase</t>
         </is>
       </c>
       <c r="D78" s="30" t="n">
-        <v>500</v>
+        <v>697</v>
       </c>
       <c r="E78" s="28" t="inlineStr">
         <is>
@@ -3474,7 +3470,7 @@
       </c>
       <c r="H78" s="29" t="inlineStr">
         <is>
-          <t>Fisher Industries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="28" t="n"/>
@@ -3495,11 +3491,11 @@
       </c>
       <c r="C79" s="29" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel B</t>
+          <t>Urban 95 Parcel C</t>
         </is>
       </c>
       <c r="D79" s="30" t="n">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="E79" s="28" t="inlineStr">
         <is>
@@ -3520,7 +3516,7 @@
       <c r="I79" s="28" t="n"/>
       <c r="J79" s="28" t="inlineStr">
         <is>
-          <t>High-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K79" s="29" t="inlineStr">
@@ -3535,11 +3531,11 @@
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel B</t>
+          <t>Urban 95 Parcel B</t>
         </is>
       </c>
       <c r="D80" s="30" t="n">
-        <v>410</v>
+        <v>478</v>
       </c>
       <c r="E80" s="28" t="inlineStr">
         <is>
@@ -3554,13 +3550,13 @@
       </c>
       <c r="H80" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>Fisher Industries</t>
         </is>
       </c>
       <c r="I80" s="28" t="n"/>
       <c r="J80" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>High-Rise</t>
         </is>
       </c>
       <c r="K80" s="29" t="inlineStr">
@@ -3575,11 +3571,11 @@
       </c>
       <c r="C81" s="29" t="inlineStr">
         <is>
-          <t>The District at Westgate</t>
+          <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
       <c r="D81" s="30" t="n">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="E81" s="28" t="inlineStr">
         <is>
@@ -3600,7 +3596,7 @@
       <c r="I81" s="28" t="n"/>
       <c r="J81" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K81" s="29" t="inlineStr">
@@ -3615,11 +3611,11 @@
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>Picerne at Palm Valley</t>
+          <t>The District at Westgate</t>
         </is>
       </c>
       <c r="D82" s="30" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E82" s="28" t="inlineStr">
         <is>
@@ -3634,7 +3630,7 @@
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>Picerne</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I82" s="28" t="n"/>
@@ -3655,11 +3651,11 @@
       </c>
       <c r="C83" s="29" t="inlineStr">
         <is>
-          <t>Liv Avondale</t>
+          <t>Picerne at Palm Valley</t>
         </is>
       </c>
       <c r="D83" s="30" t="n">
-        <v>333</v>
+        <v>383</v>
       </c>
       <c r="E83" s="28" t="inlineStr">
         <is>
@@ -3674,7 +3670,7 @@
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>Liv Communities LLC</t>
+          <t>Picerne</t>
         </is>
       </c>
       <c r="I83" s="28" t="n"/>
@@ -3695,11 +3691,11 @@
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel A</t>
+          <t>Liv Avondale</t>
         </is>
       </c>
       <c r="D84" s="30" t="n">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E84" s="28" t="inlineStr">
         <is>
@@ -3714,13 +3710,13 @@
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>Fisher Industries</t>
+          <t>Liv Communities LLC</t>
         </is>
       </c>
       <c r="I84" s="28" t="n"/>
       <c r="J84" s="28" t="inlineStr">
         <is>
-          <t>High-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K84" s="29" t="inlineStr">
@@ -3735,11 +3731,11 @@
       </c>
       <c r="C85" s="29" t="inlineStr">
         <is>
-          <t>Fuze 623</t>
+          <t>Urban 95 Parcel A</t>
         </is>
       </c>
       <c r="D85" s="30" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E85" s="28" t="inlineStr">
         <is>
@@ -3754,13 +3750,13 @@
       </c>
       <c r="H85" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fisher Industries</t>
         </is>
       </c>
       <c r="I85" s="28" t="n"/>
       <c r="J85" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>High-Rise</t>
         </is>
       </c>
       <c r="K85" s="29" t="inlineStr">
@@ -3775,11 +3771,11 @@
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>Anton Glendale</t>
+          <t>Fuze 623</t>
         </is>
       </c>
       <c r="D86" s="30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E86" s="28" t="inlineStr">
         <is>
@@ -3800,7 +3796,7 @@
       <c r="I86" s="28" t="n"/>
       <c r="J86" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K86" s="29" t="inlineStr">
@@ -3815,11 +3811,11 @@
       </c>
       <c r="C87" s="29" t="inlineStr">
         <is>
-          <t>Western Garden II</t>
+          <t>Anton Glendale</t>
         </is>
       </c>
       <c r="D87" s="30" t="n">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E87" s="28" t="inlineStr">
         <is>
@@ -3834,13 +3830,13 @@
       </c>
       <c r="H87" s="29" t="inlineStr">
         <is>
-          <t>John F Long Properties LLLP</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I87" s="28" t="n"/>
       <c r="J87" s="28" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K87" s="29" t="inlineStr">
@@ -3855,11 +3851,11 @@
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>Sanctuair at Centerscape</t>
+          <t>Western Garden II</t>
         </is>
       </c>
       <c r="D88" s="30" t="n">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E88" s="28" t="inlineStr">
         <is>
@@ -3874,13 +3870,13 @@
       </c>
       <c r="H88" s="29" t="inlineStr">
         <is>
-          <t>Sunbelt Investment Holdings Inc</t>
+          <t>John F Long Properties LLLP</t>
         </is>
       </c>
       <c r="I88" s="28" t="n"/>
       <c r="J88" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K88" s="29" t="inlineStr">
@@ -3895,11 +3891,11 @@
       </c>
       <c r="C89" s="29" t="inlineStr">
         <is>
-          <t>Banyan Avondale</t>
+          <t>Sanctuair at Centerscape</t>
         </is>
       </c>
       <c r="D89" s="30" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E89" s="28" t="inlineStr">
         <is>
@@ -3914,13 +3910,13 @@
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sunbelt Investment Holdings Inc</t>
         </is>
       </c>
       <c r="I89" s="28" t="n"/>
       <c r="J89" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K89" s="29" t="inlineStr">
@@ -3935,11 +3931,11 @@
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>Rosilian Villas</t>
+          <t>Banyan Avondale</t>
         </is>
       </c>
       <c r="D90" s="30" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E90" s="28" t="inlineStr">
         <is>
@@ -3960,7 +3956,7 @@
       <c r="I90" s="28" t="n"/>
       <c r="J90" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K90" s="29" t="inlineStr">
@@ -3975,11 +3971,11 @@
       </c>
       <c r="C91" s="29" t="inlineStr">
         <is>
-          <t>Orion Avondale</t>
+          <t>Rosilian Villas</t>
         </is>
       </c>
       <c r="D91" s="30" t="n">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="E91" s="28" t="inlineStr">
         <is>
@@ -3994,13 +3990,13 @@
       </c>
       <c r="H91" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I91" s="28" t="n"/>
       <c r="J91" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K91" s="29" t="inlineStr">
@@ -4015,11 +4011,11 @@
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>Tavalo at Avondale</t>
+          <t>Orion Avondale</t>
         </is>
       </c>
       <c r="D92" s="30" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E92" s="28" t="inlineStr">
         <is>
@@ -4034,13 +4030,13 @@
       </c>
       <c r="H92" s="29" t="inlineStr">
         <is>
-          <t>GTIS Partners LP</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I92" s="28" t="n"/>
       <c r="J92" s="28" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K92" s="29" t="inlineStr">
@@ -4055,7 +4051,7 @@
       </c>
       <c r="C93" s="29" t="inlineStr">
         <is>
-          <t>Marbella Ranch East Future Phase</t>
+          <t>Tavalo at Avondale</t>
         </is>
       </c>
       <c r="D93" s="30" t="n">
@@ -4074,13 +4070,13 @@
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>Symmetry Companies</t>
+          <t>GTIS Partners LP</t>
         </is>
       </c>
       <c r="I93" s="28" t="n"/>
       <c r="J93" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K93" s="29" t="inlineStr">
@@ -4095,11 +4091,11 @@
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>Crystal Cove</t>
+          <t>Marbella Ranch East Future Phase</t>
         </is>
       </c>
       <c r="D94" s="30" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E94" s="28" t="inlineStr">
         <is>
@@ -4114,7 +4110,7 @@
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>Sterling Real Estate Partners</t>
+          <t>Symmetry Companies</t>
         </is>
       </c>
       <c r="I94" s="28" t="n"/>
@@ -4135,11 +4131,11 @@
       </c>
       <c r="C95" s="29" t="inlineStr">
         <is>
-          <t>Cornerstone at the Wigwam</t>
+          <t>Crystal Cove</t>
         </is>
       </c>
       <c r="D95" s="30" t="n">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="E95" s="28" t="inlineStr">
         <is>
@@ -4154,13 +4150,13 @@
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sterling Real Estate Partners</t>
         </is>
       </c>
       <c r="I95" s="28" t="n"/>
       <c r="J95" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K95" s="29" t="inlineStr">
@@ -4175,11 +4171,11 @@
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>Radia Avondale Station III</t>
+          <t>SimonMed Development I</t>
         </is>
       </c>
       <c r="D96" s="30" t="n">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="E96" s="28" t="inlineStr">
         <is>
@@ -4215,11 +4211,11 @@
       </c>
       <c r="C97" s="29" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel A</t>
+          <t>Cornerstone at the Wigwam</t>
         </is>
       </c>
       <c r="D97" s="30" t="n">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="E97" s="28" t="inlineStr">
         <is>
@@ -4234,7 +4230,7 @@
       </c>
       <c r="H97" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I97" s="28" t="n"/>
@@ -4255,11 +4251,11 @@
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>Villages at River Grove</t>
+          <t>Radia Avondale Station III</t>
         </is>
       </c>
       <c r="D98" s="30" t="n">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="E98" s="28" t="inlineStr">
         <is>
@@ -4280,7 +4276,7 @@
       <c r="I98" s="28" t="n"/>
       <c r="J98" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K98" s="29" t="inlineStr">
@@ -4295,11 +4291,11 @@
       </c>
       <c r="C99" s="29" t="inlineStr">
         <is>
-          <t>District 99</t>
+          <t>Celebration Plaza Parcel A</t>
         </is>
       </c>
       <c r="D99" s="30" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E99" s="28" t="inlineStr">
         <is>
@@ -4314,13 +4310,13 @@
       </c>
       <c r="H99" s="29" t="inlineStr">
         <is>
-          <t>Thompson Thrift</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I99" s="28" t="n"/>
       <c r="J99" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K99" s="29" t="inlineStr">
@@ -4335,11 +4331,11 @@
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>McDowell Villas</t>
+          <t>Villages at River Grove</t>
         </is>
       </c>
       <c r="D100" s="30" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="E100" s="28" t="inlineStr">
         <is>
@@ -4354,13 +4350,13 @@
       </c>
       <c r="H100" s="29" t="inlineStr">
         <is>
-          <t>Trilogy Investment Company</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I100" s="28" t="n"/>
       <c r="J100" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K100" s="29" t="inlineStr">
@@ -4375,11 +4371,11 @@
       </c>
       <c r="C101" s="29" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>District 99</t>
         </is>
       </c>
       <c r="D101" s="30" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="E101" s="28" t="inlineStr">
         <is>
@@ -4394,13 +4390,13 @@
       </c>
       <c r="H101" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Thompson Thrift</t>
         </is>
       </c>
       <c r="I101" s="28" t="n"/>
       <c r="J101" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K101" s="29" t="inlineStr">
@@ -4415,11 +4411,11 @@
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>Porter Kyle Development</t>
+          <t>McDowell Villas</t>
         </is>
       </c>
       <c r="D102" s="30" t="n">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="E102" s="28" t="inlineStr">
         <is>
@@ -4434,7 +4430,7 @@
       </c>
       <c r="H102" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trilogy Investment Company</t>
         </is>
       </c>
       <c r="I102" s="28" t="n"/>
@@ -4455,11 +4451,11 @@
       </c>
       <c r="C103" s="29" t="inlineStr">
         <is>
-          <t>Zenn @ Sierra Verde</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="D103" s="30" t="n">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="E103" s="28" t="inlineStr">
         <is>
@@ -4480,7 +4476,7 @@
       <c r="I103" s="28" t="n"/>
       <c r="J103" s="28" t="inlineStr">
         <is>
-          <t>Townhome</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K103" s="29" t="inlineStr">
@@ -4495,10 +4491,12 @@
       </c>
       <c r="C104" s="29" t="inlineStr">
         <is>
-          <t>The BLVD Residential District</t>
-        </is>
-      </c>
-      <c r="D104" s="30" t="n"/>
+          <t>Porter Kyle Development</t>
+        </is>
+      </c>
+      <c r="D104" s="30" t="n">
+        <v>135</v>
+      </c>
       <c r="E104" s="28" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -4518,7 +4516,7 @@
       <c r="I104" s="28" t="n"/>
       <c r="J104" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K104" s="29" t="inlineStr">
@@ -4533,10 +4531,12 @@
       </c>
       <c r="C105" s="29" t="inlineStr">
         <is>
-          <t>The BLVD Park Avenue District</t>
-        </is>
-      </c>
-      <c r="D105" s="30" t="n"/>
+          <t>Zenn @ Sierra Verde</t>
+        </is>
+      </c>
+      <c r="D105" s="30" t="n">
+        <v>66</v>
+      </c>
       <c r="E105" s="28" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -4556,7 +4556,7 @@
       <c r="I105" s="28" t="n"/>
       <c r="J105" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Townhome</t>
         </is>
       </c>
       <c r="K105" s="29" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>Globe Land Investors Development</t>
+          <t>The BLVD Residential District</t>
         </is>
       </c>
       <c r="D106" s="30" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="H106" s="29" t="inlineStr">
         <is>
-          <t>Globe Corporation</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I106" s="28" t="n"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="C107" s="29" t="inlineStr">
         <is>
-          <t>Ball Park</t>
+          <t>The BLVD Park Avenue District</t>
         </is>
       </c>
       <c r="D107" s="30" t="n"/>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="H107" s="29" t="inlineStr">
         <is>
-          <t>VT LandGroup</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I107" s="28" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>Vision 2 Parcel A</t>
+          <t>Globe Land Investors Development</t>
         </is>
       </c>
       <c r="D108" s="30" t="n"/>
@@ -4664,13 +4664,13 @@
       </c>
       <c r="H108" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Globe Corporation</t>
         </is>
       </c>
       <c r="I108" s="28" t="n"/>
       <c r="J108" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K108" s="29" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C109" s="29" t="inlineStr">
         <is>
-          <t>Firststreet Verde</t>
+          <t>Ball Park</t>
         </is>
       </c>
       <c r="D109" s="30" t="n"/>
@@ -4702,13 +4702,13 @@
       </c>
       <c r="H109" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VT LandGroup</t>
         </is>
       </c>
       <c r="I109" s="28" t="n"/>
       <c r="J109" s="28" t="inlineStr">
         <is>
-          <t>Single Family</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K109" s="29" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>Goodyear Civic Square at Estrella Falls</t>
+          <t>Vision 2 Parcel A</t>
         </is>
       </c>
       <c r="D110" s="30" t="n"/>
@@ -4746,7 +4746,7 @@
       <c r="I110" s="28" t="n"/>
       <c r="J110" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Mid-Rise</t>
         </is>
       </c>
       <c r="K110" s="29" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C111" s="29" t="inlineStr">
         <is>
-          <t>I-10 Innovation Center II</t>
+          <t>Firststreet Verde</t>
         </is>
       </c>
       <c r="D111" s="30" t="n"/>
@@ -4778,13 +4778,13 @@
       </c>
       <c r="H111" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I111" s="28" t="n"/>
       <c r="J111" s="28" t="inlineStr">
         <is>
-          <t>Garden</t>
+          <t>Single Family</t>
         </is>
       </c>
       <c r="K111" s="29" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel D</t>
+          <t>Goodyear Civic Square at Estrella Falls</t>
         </is>
       </c>
       <c r="D112" s="30" t="n"/>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>Privately Owned</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I112" s="28" t="n"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C113" s="29" t="inlineStr">
         <is>
-          <t>SimonMed Development II</t>
+          <t>I-10 Innovation Center II</t>
         </is>
       </c>
       <c r="D113" s="30" t="n"/>
@@ -4854,13 +4854,13 @@
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I113" s="28" t="n"/>
       <c r="J113" s="28" t="inlineStr">
         <is>
-          <t>Mid-Rise</t>
+          <t>Garden</t>
         </is>
       </c>
       <c r="K113" s="29" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C114" s="29" t="inlineStr">
         <is>
-          <t>182 South 95th Avenue</t>
+          <t>Celebration Plaza Parcel D</t>
         </is>
       </c>
       <c r="D114" s="30" t="n"/>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="H114" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Privately Owned</t>
         </is>
       </c>
       <c r="I114" s="28" t="n"/>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="C115" s="29" t="inlineStr">
         <is>
-          <t>Envision Encore</t>
+          <t>SimonMed Development II</t>
         </is>
       </c>
       <c r="D115" s="30" t="n"/>
@@ -4936,17 +4936,93 @@
       <c r="I115" s="28" t="n"/>
       <c r="J115" s="28" t="inlineStr">
         <is>
+          <t>Mid-Rise</t>
+        </is>
+      </c>
+      <c r="K115" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="28" t="n">
+        <v>105</v>
+      </c>
+      <c r="C116" s="29" t="inlineStr">
+        <is>
+          <t>182 South 95th Avenue</t>
+        </is>
+      </c>
+      <c r="D116" s="30" t="n"/>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F116" s="31" t="n"/>
+      <c r="G116" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H116" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I116" s="28" t="n"/>
+      <c r="J116" s="28" t="inlineStr">
+        <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K115" s="29" t="inlineStr">
+      <c r="K116" s="29" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="B118" s="33" t="inlineStr">
+    <row r="117">
+      <c r="B117" s="28" t="n">
+        <v>106</v>
+      </c>
+      <c r="C117" s="29" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="D117" s="30" t="n"/>
+      <c r="E117" s="28" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F117" s="31" t="n"/>
+      <c r="G117" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H117" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="28" t="n"/>
+      <c r="J117" s="28" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="K117" s="29" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="33" t="inlineStr">
         <is>
           <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) to be filled manually; lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
@@ -4955,11 +5031,11 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C59:K59"/>
-    <mergeCell ref="B118:K118"/>
+    <mergeCell ref="C72:K72"/>
     <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C71:K71"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B120:K120"/>
     <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4972,7 +5048,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Z61"/>
+  <dimension ref="B1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -5096,15 +5172,15 @@
         <v>0.95</v>
       </c>
       <c r="R6" s="39">
-        <f>'Competitive Analysis'!C68</f>
+        <f>'Competitive Analysis'!C61</f>
         <v/>
       </c>
       <c r="S6" s="40">
-        <f>'Competitive Analysis'!D68</f>
+        <f>'Competitive Analysis'!D61</f>
         <v/>
       </c>
       <c r="T6" s="41">
-        <f>'Competitive Analysis'!E68</f>
+        <f>'Competitive Analysis'!E61</f>
         <v/>
       </c>
       <c r="V6">
@@ -5128,15 +5204,15 @@
         </is>
       </c>
       <c r="R7" s="39">
-        <f>'Competitive Analysis'!C62</f>
+        <f>'Competitive Analysis'!C69</f>
         <v/>
       </c>
       <c r="S7" s="40">
-        <f>'Competitive Analysis'!D62</f>
+        <f>'Competitive Analysis'!D69</f>
         <v/>
       </c>
       <c r="T7" s="41">
-        <f>'Competitive Analysis'!E62</f>
+        <f>'Competitive Analysis'!E69</f>
         <v/>
       </c>
       <c r="V7">
@@ -5158,15 +5234,15 @@
         <v>1250</v>
       </c>
       <c r="R8" s="39">
-        <f>'Competitive Analysis'!C66</f>
+        <f>'Competitive Analysis'!C63</f>
         <v/>
       </c>
       <c r="S8" s="40">
-        <f>'Competitive Analysis'!D66</f>
+        <f>'Competitive Analysis'!D63</f>
         <v/>
       </c>
       <c r="T8" s="41">
-        <f>'Competitive Analysis'!E66</f>
+        <f>'Competitive Analysis'!E63</f>
         <v/>
       </c>
       <c r="V8">
@@ -5218,15 +5294,15 @@
         <v>3800</v>
       </c>
       <c r="R10" s="39">
-        <f>'Competitive Analysis'!C63</f>
+        <f>'Competitive Analysis'!C68</f>
         <v/>
       </c>
       <c r="S10" s="40">
-        <f>'Competitive Analysis'!D63</f>
+        <f>'Competitive Analysis'!D68</f>
         <v/>
       </c>
       <c r="T10" s="41">
-        <f>'Competitive Analysis'!E63</f>
+        <f>'Competitive Analysis'!E68</f>
         <v/>
       </c>
       <c r="V10">
@@ -5249,15 +5325,15 @@
         <v/>
       </c>
       <c r="R11" s="39">
-        <f>'Competitive Analysis'!C69</f>
+        <f>'Competitive Analysis'!C64</f>
         <v/>
       </c>
       <c r="S11" s="40">
-        <f>'Competitive Analysis'!D69</f>
+        <f>'Competitive Analysis'!D64</f>
         <v/>
       </c>
       <c r="T11" s="41">
-        <f>'Competitive Analysis'!E69</f>
+        <f>'Competitive Analysis'!E64</f>
         <v/>
       </c>
       <c r="V11">
@@ -5271,15 +5347,15 @@
     </row>
     <row r="12" ht="14.4" customHeight="1">
       <c r="R12" s="39">
-        <f>'Competitive Analysis'!C61</f>
+        <f>'Competitive Analysis'!C70</f>
         <v/>
       </c>
       <c r="S12" s="40">
-        <f>'Competitive Analysis'!D61</f>
+        <f>'Competitive Analysis'!D70</f>
         <v/>
       </c>
       <c r="T12" s="41">
-        <f>'Competitive Analysis'!E61</f>
+        <f>'Competitive Analysis'!E70</f>
         <v/>
       </c>
       <c r="V12">
@@ -5293,15 +5369,15 @@
     </row>
     <row r="13" ht="14.4" customHeight="1">
       <c r="R13" s="39">
-        <f>'Competitive Analysis'!C64</f>
+        <f>'Competitive Analysis'!C62</f>
         <v/>
       </c>
       <c r="S13" s="40">
-        <f>'Competitive Analysis'!D64</f>
+        <f>'Competitive Analysis'!D62</f>
         <v/>
       </c>
       <c r="T13" s="41">
-        <f>'Competitive Analysis'!E64</f>
+        <f>'Competitive Analysis'!E62</f>
         <v/>
       </c>
       <c r="V13">
@@ -5335,14 +5411,29 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="14.4" customHeight="1"/>
-    <row r="16" ht="14.4" customHeight="1">
-      <c r="R16" s="34" t="inlineStr">
-        <is>
-          <t>PROPOSED PIPELINE (scenario toggle)</t>
-        </is>
-      </c>
-    </row>
+    <row r="15" ht="14.4" customHeight="1">
+      <c r="R15" s="39">
+        <f>'Competitive Analysis'!C66</f>
+        <v/>
+      </c>
+      <c r="S15" s="40">
+        <f>'Competitive Analysis'!D66</f>
+        <v/>
+      </c>
+      <c r="T15" s="41">
+        <f>'Competitive Analysis'!E66</f>
+        <v/>
+      </c>
+      <c r="V15">
+        <f>IFERROR(VALUE(RIGHT(T15,4))*4+MATCH(LEFT(T15,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W15">
+        <f>IF(V15="","",IF(V15&lt;=$Z$1,0,MAX(1,INT((V15-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="14.4" customHeight="1"/>
     <row r="17" ht="14.4" customHeight="1">
       <c r="B17" s="35" t="inlineStr">
         <is>
@@ -5414,24 +5505,9 @@
           <t>Y6</t>
         </is>
       </c>
-      <c r="R17" s="37" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="S17" s="37" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="T17" s="37" t="inlineStr">
-        <is>
-          <t>Est. Delivery</t>
-        </is>
-      </c>
-      <c r="U17" s="37" t="inlineStr">
-        <is>
-          <t>Built In</t>
+      <c r="R17" s="34" t="inlineStr">
+        <is>
+          <t>PROPOSED PIPELINE (scenario toggle)</t>
         </is>
       </c>
     </row>
@@ -5501,31 +5577,25 @@
           <t>Hold Yr 6</t>
         </is>
       </c>
-      <c r="R18" s="39" t="inlineStr">
-        <is>
-          <t>Sheely Center Future Phase</t>
-        </is>
-      </c>
-      <c r="S18" s="40" t="n">
-        <v>697</v>
-      </c>
-      <c r="T18" s="47" t="inlineStr"/>
-      <c r="U18" s="47" t="inlineStr">
-        <is>
-          <t>Bear only</t>
-        </is>
-      </c>
-      <c r="V18">
-        <f>IFERROR(VALUE(RIGHT(T18,4))*4+MATCH(LEFT(T18,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
-        <v/>
-      </c>
-      <c r="W18">
-        <f>IF(V18="","",IF(V18&lt;=$Z$1,0,MAX(1,INT((V18-$Z$2)/4)+1)))</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>IF(U18="All",1,IF(U18="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U18="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
-        <v/>
+      <c r="R18" s="37" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="S18" s="37" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="T18" s="37" t="inlineStr">
+        <is>
+          <t>Est. Delivery</t>
+        </is>
+      </c>
+      <c r="U18" s="37" t="inlineStr">
+        <is>
+          <t>Built In</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="14.4" customHeight="1">
@@ -5534,61 +5604,61 @@
           <t>NEW SUPPLY (5-mi)</t>
         </is>
       </c>
-      <c r="C19" s="48" t="n">
+      <c r="C19" s="47" t="n">
         <v>1133</v>
       </c>
-      <c r="D19" s="48" t="n">
+      <c r="D19" s="47" t="n">
         <v>1860</v>
       </c>
-      <c r="E19" s="48" t="n">
+      <c r="E19" s="47" t="n">
         <v>1336</v>
       </c>
-      <c r="F19" s="48" t="n">
+      <c r="F19" s="47" t="n">
         <v>2280</v>
       </c>
-      <c r="G19" s="48" t="n">
+      <c r="G19" s="47" t="n">
         <v>2823</v>
       </c>
-      <c r="H19" s="48" t="n">
+      <c r="H19" s="47" t="n">
         <v>4043</v>
       </c>
-      <c r="I19" s="48" t="n">
+      <c r="I19" s="47" t="n">
         <v>1860</v>
       </c>
-      <c r="J19" s="49">
-        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,1)+SUMIFS($S$18:$S$61,$W$18:$W$61,1,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="K19" s="49">
-        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,2)+SUMIFS($S$18:$S$61,$W$18:$W$61,2,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="L19" s="49">
-        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,3)+SUMIFS($S$18:$S$61,$W$18:$W$61,3,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="M19" s="49">
-        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,4)+SUMIFS($S$18:$S$61,$W$18:$W$61,4,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="N19" s="49">
-        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,5)+SUMIFS($S$18:$S$61,$W$18:$W$61,5,$X$18:$X$61,1)</f>
-        <v/>
-      </c>
-      <c r="O19" s="49">
-        <f>SUMIFS($S$5:$S$14,$W$5:$W$14,6)+SUMIFS($S$18:$S$61,$W$18:$W$61,6,$X$18:$X$61,1)</f>
+      <c r="J19" s="48">
+        <f>SUMIFS($S$5:$S$15,$W$5:$W$15,1)+SUMIFS($S$19:$S$63,$W$19:$W$63,1,$X$19:$X$63,1)</f>
+        <v/>
+      </c>
+      <c r="K19" s="48">
+        <f>SUMIFS($S$5:$S$15,$W$5:$W$15,2)+SUMIFS($S$19:$S$63,$W$19:$W$63,2,$X$19:$X$63,1)</f>
+        <v/>
+      </c>
+      <c r="L19" s="48">
+        <f>SUMIFS($S$5:$S$15,$W$5:$W$15,3)+SUMIFS($S$19:$S$63,$W$19:$W$63,3,$X$19:$X$63,1)</f>
+        <v/>
+      </c>
+      <c r="M19" s="48">
+        <f>SUMIFS($S$5:$S$15,$W$5:$W$15,4)+SUMIFS($S$19:$S$63,$W$19:$W$63,4,$X$19:$X$63,1)</f>
+        <v/>
+      </c>
+      <c r="N19" s="48">
+        <f>SUMIFS($S$5:$S$15,$W$5:$W$15,5)+SUMIFS($S$19:$S$63,$W$19:$W$63,5,$X$19:$X$63,1)</f>
+        <v/>
+      </c>
+      <c r="O19" s="48">
+        <f>SUMIFS($S$5:$S$15,$W$5:$W$15,6)+SUMIFS($S$19:$S$63,$W$19:$W$63,6,$X$19:$X$63,1)</f>
         <v/>
       </c>
       <c r="R19" s="39" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel C</t>
+          <t>Sheely Center Future Phase</t>
         </is>
       </c>
       <c r="S19" s="40" t="n">
-        <v>500</v>
-      </c>
-      <c r="T19" s="47" t="inlineStr"/>
-      <c r="U19" s="47" t="inlineStr">
+        <v>697</v>
+      </c>
+      <c r="T19" s="49" t="inlineStr"/>
+      <c r="U19" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5612,61 +5682,61 @@
           <t>ABSORPTION (5-mi)</t>
         </is>
       </c>
-      <c r="C20" s="48" t="n">
+      <c r="C20" s="47" t="n">
         <v>719</v>
       </c>
-      <c r="D20" s="48" t="n">
+      <c r="D20" s="47" t="n">
         <v>1876</v>
       </c>
-      <c r="E20" s="48" t="n">
+      <c r="E20" s="47" t="n">
         <v>1210</v>
       </c>
-      <c r="F20" s="48" t="n">
+      <c r="F20" s="47" t="n">
         <v>685</v>
       </c>
-      <c r="G20" s="48" t="n">
+      <c r="G20" s="47" t="n">
         <v>2514</v>
       </c>
-      <c r="H20" s="48" t="n">
+      <c r="H20" s="47" t="n">
         <v>2655</v>
       </c>
-      <c r="I20" s="48" t="n">
+      <c r="I20" s="47" t="n">
         <v>2369</v>
       </c>
-      <c r="J20" s="49">
+      <c r="J20" s="48">
         <f>J31-I31</f>
         <v/>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="48">
         <f>K31-J31</f>
         <v/>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="48">
         <f>L31-K31</f>
         <v/>
       </c>
-      <c r="M20" s="49">
+      <c r="M20" s="48">
         <f>M31-L31</f>
         <v/>
       </c>
-      <c r="N20" s="49">
+      <c r="N20" s="48">
         <f>N31-M31</f>
         <v/>
       </c>
-      <c r="O20" s="49">
+      <c r="O20" s="48">
         <f>O31-N31</f>
         <v/>
       </c>
       <c r="R20" s="39" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel B</t>
+          <t>Urban 95 Parcel C</t>
         </is>
       </c>
       <c r="S20" s="40" t="n">
-        <v>478</v>
-      </c>
-      <c r="T20" s="47" t="inlineStr"/>
-      <c r="U20" s="47" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="T20" s="49" t="inlineStr"/>
+      <c r="U20" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5737,14 +5807,14 @@
       </c>
       <c r="R21" s="39" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel B</t>
+          <t>Urban 95 Parcel B</t>
         </is>
       </c>
       <c r="S21" s="40" t="n">
-        <v>410</v>
-      </c>
-      <c r="T21" s="47" t="inlineStr"/>
-      <c r="U21" s="47" t="inlineStr">
+        <v>478</v>
+      </c>
+      <c r="T21" s="49" t="inlineStr"/>
+      <c r="U21" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5770,14 +5840,14 @@
       </c>
       <c r="R22" s="39" t="inlineStr">
         <is>
-          <t>The District at Westgate</t>
+          <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
       <c r="S22" s="40" t="n">
-        <v>384</v>
-      </c>
-      <c r="T22" s="47" t="inlineStr"/>
-      <c r="U22" s="47" t="inlineStr">
+        <v>410</v>
+      </c>
+      <c r="T22" s="49" t="inlineStr"/>
+      <c r="U22" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5830,14 +5900,14 @@
       <c r="O23" s="53" t="n"/>
       <c r="R23" s="39" t="inlineStr">
         <is>
-          <t>Picerne at Palm Valley</t>
+          <t>The District at Westgate</t>
         </is>
       </c>
       <c r="S23" s="40" t="n">
-        <v>383</v>
-      </c>
-      <c r="T23" s="47" t="inlineStr"/>
-      <c r="U23" s="47" t="inlineStr">
+        <v>384</v>
+      </c>
+      <c r="T23" s="49" t="inlineStr"/>
+      <c r="U23" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5894,14 +5964,14 @@
       <c r="O24" s="56" t="n"/>
       <c r="R24" s="39" t="inlineStr">
         <is>
-          <t>Liv Avondale</t>
+          <t>Picerne at Palm Valley</t>
         </is>
       </c>
       <c r="S24" s="40" t="n">
-        <v>333</v>
-      </c>
-      <c r="T24" s="47" t="inlineStr"/>
-      <c r="U24" s="47" t="inlineStr">
+        <v>383</v>
+      </c>
+      <c r="T24" s="49" t="inlineStr"/>
+      <c r="U24" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5954,14 +6024,14 @@
       <c r="O25" s="53" t="n"/>
       <c r="R25" s="39" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel A</t>
+          <t>Liv Avondale</t>
         </is>
       </c>
       <c r="S25" s="40" t="n">
-        <v>324</v>
-      </c>
-      <c r="T25" s="47" t="inlineStr"/>
-      <c r="U25" s="47" t="inlineStr">
+        <v>333</v>
+      </c>
+      <c r="T25" s="49" t="inlineStr"/>
+      <c r="U25" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6018,18 +6088,14 @@
       <c r="O26" s="56" t="n"/>
       <c r="R26" s="39" t="inlineStr">
         <is>
-          <t>The Waverly</t>
+          <t>Urban 95 Parcel A</t>
         </is>
       </c>
       <c r="S26" s="40" t="n">
-        <v>323</v>
-      </c>
-      <c r="T26" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U26" s="47" t="inlineStr">
+        <v>324</v>
+      </c>
+      <c r="T26" s="49" t="inlineStr"/>
+      <c r="U26" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6082,14 +6148,18 @@
       <c r="O27" s="58" t="n"/>
       <c r="R27" s="39" t="inlineStr">
         <is>
-          <t>Fuze 623</t>
+          <t>The Waverly</t>
         </is>
       </c>
       <c r="S27" s="40" t="n">
-        <v>321</v>
-      </c>
-      <c r="T27" s="47" t="inlineStr"/>
-      <c r="U27" s="47" t="inlineStr">
+        <v>323</v>
+      </c>
+      <c r="T27" s="49" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U27" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6140,14 +6210,14 @@
       <c r="O28" s="58" t="n"/>
       <c r="R28" s="39" t="inlineStr">
         <is>
-          <t>Anton Glendale</t>
+          <t>Fuze 623</t>
         </is>
       </c>
       <c r="S28" s="40" t="n">
-        <v>320</v>
-      </c>
-      <c r="T28" s="47" t="inlineStr"/>
-      <c r="U28" s="47" t="inlineStr">
+        <v>321</v>
+      </c>
+      <c r="T28" s="49" t="inlineStr"/>
+      <c r="U28" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6168,14 +6238,14 @@
     <row r="29" ht="14.4" customHeight="1">
       <c r="R29" s="39" t="inlineStr">
         <is>
-          <t>Western Garden II</t>
+          <t>Anton Glendale</t>
         </is>
       </c>
       <c r="S29" s="40" t="n">
-        <v>314</v>
-      </c>
-      <c r="T29" s="47" t="inlineStr"/>
-      <c r="U29" s="47" t="inlineStr">
+        <v>320</v>
+      </c>
+      <c r="T29" s="49" t="inlineStr"/>
+      <c r="U29" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6246,14 +6316,14 @@
       </c>
       <c r="R30" s="39" t="inlineStr">
         <is>
-          <t>Sanctuair at Centerscape</t>
+          <t>Western Garden II</t>
         </is>
       </c>
       <c r="S30" s="40" t="n">
-        <v>303</v>
-      </c>
-      <c r="T30" s="47" t="inlineStr"/>
-      <c r="U30" s="47" t="inlineStr">
+        <v>314</v>
+      </c>
+      <c r="T30" s="49" t="inlineStr"/>
+      <c r="U30" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6324,18 +6394,14 @@
       </c>
       <c r="R31" s="39" t="inlineStr">
         <is>
-          <t>Encore Avondale</t>
+          <t>Sanctuair at Centerscape</t>
         </is>
       </c>
       <c r="S31" s="40" t="n">
-        <v>300</v>
-      </c>
-      <c r="T31" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U31" s="47" t="inlineStr">
+        <v>303</v>
+      </c>
+      <c r="T31" s="49" t="inlineStr"/>
+      <c r="U31" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6356,14 +6422,18 @@
     <row r="32" ht="14.4" customHeight="1">
       <c r="R32" s="39" t="inlineStr">
         <is>
-          <t>Banyan Avondale</t>
+          <t>Encore Avondale</t>
         </is>
       </c>
       <c r="S32" s="40" t="n">
-        <v>296</v>
-      </c>
-      <c r="T32" s="47" t="inlineStr"/>
-      <c r="U32" s="47" t="inlineStr">
+        <v>300</v>
+      </c>
+      <c r="T32" s="49" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U32" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6419,14 +6489,14 @@
       </c>
       <c r="R33" s="39" t="inlineStr">
         <is>
-          <t>Rosilian Villas</t>
+          <t>Banyan Avondale</t>
         </is>
       </c>
       <c r="S33" s="40" t="n">
-        <v>291</v>
-      </c>
-      <c r="T33" s="47" t="inlineStr"/>
-      <c r="U33" s="47" t="inlineStr">
+        <v>296</v>
+      </c>
+      <c r="T33" s="49" t="inlineStr"/>
+      <c r="U33" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6476,18 +6546,14 @@
       </c>
       <c r="R34" s="39" t="inlineStr">
         <is>
-          <t>The Statler at Estrella Parkway</t>
+          <t>Rosilian Villas</t>
         </is>
       </c>
       <c r="S34" s="40" t="n">
-        <v>284</v>
-      </c>
-      <c r="T34" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U34" s="47" t="inlineStr">
+        <v>291</v>
+      </c>
+      <c r="T34" s="49" t="inlineStr"/>
+      <c r="U34" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6537,14 +6603,18 @@
       </c>
       <c r="R35" s="39" t="inlineStr">
         <is>
-          <t>Orion Avondale</t>
+          <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
       <c r="S35" s="40" t="n">
-        <v>268</v>
-      </c>
-      <c r="T35" s="47" t="inlineStr"/>
-      <c r="U35" s="47" t="inlineStr">
+        <v>284</v>
+      </c>
+      <c r="T35" s="49" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U35" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6594,14 +6664,14 @@
       </c>
       <c r="R36" s="39" t="inlineStr">
         <is>
-          <t>Tavalo at Avondale</t>
+          <t>Orion Avondale</t>
         </is>
       </c>
       <c r="S36" s="40" t="n">
-        <v>266</v>
-      </c>
-      <c r="T36" s="47" t="inlineStr"/>
-      <c r="U36" s="47" t="inlineStr">
+        <v>268</v>
+      </c>
+      <c r="T36" s="49" t="inlineStr"/>
+      <c r="U36" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6622,14 +6692,14 @@
     <row r="37" ht="14.4" customHeight="1">
       <c r="R37" s="39" t="inlineStr">
         <is>
-          <t>Marbella Ranch East Future Phase</t>
+          <t>Tavalo at Avondale</t>
         </is>
       </c>
       <c r="S37" s="40" t="n">
         <v>266</v>
       </c>
-      <c r="T37" s="47" t="inlineStr"/>
-      <c r="U37" s="47" t="inlineStr">
+      <c r="T37" s="49" t="inlineStr"/>
+      <c r="U37" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6685,14 +6755,14 @@
       </c>
       <c r="R38" s="39" t="inlineStr">
         <is>
-          <t>Crystal Cove</t>
+          <t>Marbella Ranch East Future Phase</t>
         </is>
       </c>
       <c r="S38" s="40" t="n">
-        <v>260</v>
-      </c>
-      <c r="T38" s="47" t="inlineStr"/>
-      <c r="U38" s="47" t="inlineStr">
+        <v>266</v>
+      </c>
+      <c r="T38" s="49" t="inlineStr"/>
+      <c r="U38" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6736,14 +6806,14 @@
       </c>
       <c r="R39" s="39" t="inlineStr">
         <is>
-          <t>Cornerstone at the Wigwam</t>
+          <t>Crystal Cove</t>
         </is>
       </c>
       <c r="S39" s="40" t="n">
-        <v>212</v>
-      </c>
-      <c r="T39" s="47" t="inlineStr"/>
-      <c r="U39" s="47" t="inlineStr">
+        <v>260</v>
+      </c>
+      <c r="T39" s="49" t="inlineStr"/>
+      <c r="U39" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6787,14 +6857,14 @@
       </c>
       <c r="R40" s="39" t="inlineStr">
         <is>
-          <t>Radia Avondale Station III</t>
+          <t>SimonMed Development I</t>
         </is>
       </c>
       <c r="S40" s="40" t="n">
-        <v>212</v>
-      </c>
-      <c r="T40" s="47" t="inlineStr"/>
-      <c r="U40" s="47" t="inlineStr">
+        <v>239</v>
+      </c>
+      <c r="T40" s="49" t="inlineStr"/>
+      <c r="U40" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6838,14 +6908,14 @@
       </c>
       <c r="R41" s="39" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel A</t>
+          <t>Cornerstone at the Wigwam</t>
         </is>
       </c>
       <c r="S41" s="40" t="n">
-        <v>181</v>
-      </c>
-      <c r="T41" s="47" t="inlineStr"/>
-      <c r="U41" s="47" t="inlineStr">
+        <v>212</v>
+      </c>
+      <c r="T41" s="49" t="inlineStr"/>
+      <c r="U41" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6871,14 +6941,14 @@
       </c>
       <c r="R42" s="39" t="inlineStr">
         <is>
-          <t>Villages at River Grove</t>
+          <t>Radia Avondale Station III</t>
         </is>
       </c>
       <c r="S42" s="40" t="n">
-        <v>180</v>
-      </c>
-      <c r="T42" s="47" t="inlineStr"/>
-      <c r="U42" s="47" t="inlineStr">
+        <v>212</v>
+      </c>
+      <c r="T42" s="49" t="inlineStr"/>
+      <c r="U42" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6922,14 +6992,14 @@
       </c>
       <c r="R43" s="39" t="inlineStr">
         <is>
-          <t>District 99</t>
+          <t>Celebration Plaza Parcel A</t>
         </is>
       </c>
       <c r="S43" s="40" t="n">
-        <v>172</v>
-      </c>
-      <c r="T43" s="47" t="inlineStr"/>
-      <c r="U43" s="47" t="inlineStr">
+        <v>181</v>
+      </c>
+      <c r="T43" s="49" t="inlineStr"/>
+      <c r="U43" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6973,14 +7043,14 @@
       </c>
       <c r="R44" s="39" t="inlineStr">
         <is>
-          <t>McDowell Villas</t>
+          <t>Villages at River Grove</t>
         </is>
       </c>
       <c r="S44" s="40" t="n">
-        <v>164</v>
-      </c>
-      <c r="T44" s="47" t="inlineStr"/>
-      <c r="U44" s="47" t="inlineStr">
+        <v>180</v>
+      </c>
+      <c r="T44" s="49" t="inlineStr"/>
+      <c r="U44" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7024,14 +7094,14 @@
       </c>
       <c r="R45" s="39" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>District 99</t>
         </is>
       </c>
       <c r="S45" s="40" t="n">
-        <v>156</v>
-      </c>
-      <c r="T45" s="47" t="inlineStr"/>
-      <c r="U45" s="47" t="inlineStr">
+        <v>172</v>
+      </c>
+      <c r="T45" s="49" t="inlineStr"/>
+      <c r="U45" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7057,14 +7127,14 @@
       </c>
       <c r="R46" s="39" t="inlineStr">
         <is>
-          <t>Porter Kyle Development</t>
+          <t>McDowell Villas</t>
         </is>
       </c>
       <c r="S46" s="40" t="n">
-        <v>135</v>
-      </c>
-      <c r="T46" s="47" t="inlineStr"/>
-      <c r="U46" s="47" t="inlineStr">
+        <v>164</v>
+      </c>
+      <c r="T46" s="49" t="inlineStr"/>
+      <c r="U46" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7114,18 +7184,14 @@
       </c>
       <c r="R47" s="39" t="inlineStr">
         <is>
-          <t>Ascent Goodyear</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="S47" s="40" t="n">
-        <v>113</v>
-      </c>
-      <c r="T47" s="47" t="inlineStr">
-        <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="U47" s="47" t="inlineStr">
+        <v>156</v>
+      </c>
+      <c r="T47" s="49" t="inlineStr"/>
+      <c r="U47" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7175,18 +7241,14 @@
       </c>
       <c r="R48" s="39" t="inlineStr">
         <is>
-          <t>Northern 107</t>
+          <t>Porter Kyle Development</t>
         </is>
       </c>
       <c r="S48" s="40" t="n">
-        <v>74</v>
-      </c>
-      <c r="T48" s="47" t="inlineStr">
-        <is>
-          <t>Q4 2028</t>
-        </is>
-      </c>
-      <c r="U48" s="47" t="inlineStr">
+        <v>135</v>
+      </c>
+      <c r="T48" s="49" t="inlineStr"/>
+      <c r="U48" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7236,14 +7298,18 @@
       </c>
       <c r="R49" s="39" t="inlineStr">
         <is>
-          <t>Zenn @ Sierra Verde</t>
+          <t>Ascent Goodyear</t>
         </is>
       </c>
       <c r="S49" s="40" t="n">
-        <v>66</v>
-      </c>
-      <c r="T49" s="47" t="inlineStr"/>
-      <c r="U49" s="47" t="inlineStr">
+        <v>113</v>
+      </c>
+      <c r="T49" s="49" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
+      </c>
+      <c r="U49" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7264,12 +7330,18 @@
     <row r="50" ht="14.4" customHeight="1">
       <c r="R50" s="39" t="inlineStr">
         <is>
-          <t>The BLVD Residential District</t>
-        </is>
-      </c>
-      <c r="S50" s="40" t="n"/>
-      <c r="T50" s="47" t="inlineStr"/>
-      <c r="U50" s="47" t="inlineStr">
+          <t>Northern 107</t>
+        </is>
+      </c>
+      <c r="S50" s="40" t="n">
+        <v>74</v>
+      </c>
+      <c r="T50" s="49" t="inlineStr">
+        <is>
+          <t>Q4 2028</t>
+        </is>
+      </c>
+      <c r="U50" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7295,12 +7367,14 @@
       </c>
       <c r="R51" s="39" t="inlineStr">
         <is>
-          <t>The BLVD Park Avenue District</t>
-        </is>
-      </c>
-      <c r="S51" s="40" t="n"/>
-      <c r="T51" s="47" t="inlineStr"/>
-      <c r="U51" s="47" t="inlineStr">
+          <t>Zenn @ Sierra Verde</t>
+        </is>
+      </c>
+      <c r="S51" s="40" t="n">
+        <v>66</v>
+      </c>
+      <c r="T51" s="49" t="inlineStr"/>
+      <c r="U51" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7331,12 +7405,12 @@
       </c>
       <c r="R52" s="39" t="inlineStr">
         <is>
-          <t>Globe Land Investors Development</t>
+          <t>The BLVD Residential District</t>
         </is>
       </c>
       <c r="S52" s="40" t="n"/>
-      <c r="T52" s="47" t="inlineStr"/>
-      <c r="U52" s="47" t="inlineStr">
+      <c r="T52" s="49" t="inlineStr"/>
+      <c r="U52" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7367,12 +7441,12 @@
       </c>
       <c r="R53" s="39" t="inlineStr">
         <is>
-          <t>Ball Park</t>
+          <t>The BLVD Park Avenue District</t>
         </is>
       </c>
       <c r="S53" s="40" t="n"/>
-      <c r="T53" s="47" t="inlineStr"/>
-      <c r="U53" s="47" t="inlineStr">
+      <c r="T53" s="49" t="inlineStr"/>
+      <c r="U53" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7403,12 +7477,12 @@
       </c>
       <c r="R54" s="39" t="inlineStr">
         <is>
-          <t>Vision 2 Parcel A</t>
+          <t>Globe Land Investors Development</t>
         </is>
       </c>
       <c r="S54" s="40" t="n"/>
-      <c r="T54" s="47" t="inlineStr"/>
-      <c r="U54" s="47" t="inlineStr">
+      <c r="T54" s="49" t="inlineStr"/>
+      <c r="U54" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7439,12 +7513,12 @@
       </c>
       <c r="R55" s="39" t="inlineStr">
         <is>
-          <t>Firststreet Verde</t>
+          <t>Ball Park</t>
         </is>
       </c>
       <c r="S55" s="40" t="n"/>
-      <c r="T55" s="47" t="inlineStr"/>
-      <c r="U55" s="47" t="inlineStr">
+      <c r="T55" s="49" t="inlineStr"/>
+      <c r="U55" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7475,12 +7549,12 @@
       </c>
       <c r="R56" s="39" t="inlineStr">
         <is>
-          <t>Goodyear Civic Square at Estrella Falls</t>
+          <t>Vision 2 Parcel A</t>
         </is>
       </c>
       <c r="S56" s="40" t="n"/>
-      <c r="T56" s="47" t="inlineStr"/>
-      <c r="U56" s="47" t="inlineStr">
+      <c r="T56" s="49" t="inlineStr"/>
+      <c r="U56" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7511,12 +7585,12 @@
       </c>
       <c r="R57" s="39" t="inlineStr">
         <is>
-          <t>I-10 Innovation Center II</t>
+          <t>Firststreet Verde</t>
         </is>
       </c>
       <c r="S57" s="40" t="n"/>
-      <c r="T57" s="47" t="inlineStr"/>
-      <c r="U57" s="47" t="inlineStr">
+      <c r="T57" s="49" t="inlineStr"/>
+      <c r="U57" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7547,12 +7621,12 @@
       </c>
       <c r="R58" s="39" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel D</t>
+          <t>Goodyear Civic Square at Estrella Falls</t>
         </is>
       </c>
       <c r="S58" s="40" t="n"/>
-      <c r="T58" s="47" t="inlineStr"/>
-      <c r="U58" s="47" t="inlineStr">
+      <c r="T58" s="49" t="inlineStr"/>
+      <c r="U58" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7578,17 +7652,17 @@
       </c>
       <c r="E59" s="64" t="inlineStr">
         <is>
-          <t>1,947 / 1,251</t>
+          <t>2,307 / 1,251</t>
         </is>
       </c>
       <c r="R59" s="39" t="inlineStr">
         <is>
-          <t>SimonMed Development II</t>
+          <t>I-10 Innovation Center II</t>
         </is>
       </c>
       <c r="S59" s="40" t="n"/>
-      <c r="T59" s="47" t="inlineStr"/>
-      <c r="U59" s="47" t="inlineStr">
+      <c r="T59" s="49" t="inlineStr"/>
+      <c r="U59" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7614,12 +7688,12 @@
       </c>
       <c r="R60" s="39" t="inlineStr">
         <is>
-          <t>182 South 95th Avenue</t>
+          <t>Celebration Plaza Parcel D</t>
         </is>
       </c>
       <c r="S60" s="40" t="n"/>
-      <c r="T60" s="47" t="inlineStr"/>
-      <c r="U60" s="47" t="inlineStr">
+      <c r="T60" s="49" t="inlineStr"/>
+      <c r="U60" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7640,12 +7714,12 @@
     <row r="61" ht="14.4" customHeight="1">
       <c r="R61" s="39" t="inlineStr">
         <is>
-          <t>Envision Encore</t>
+          <t>SimonMed Development II</t>
         </is>
       </c>
       <c r="S61" s="40" t="n"/>
-      <c r="T61" s="47" t="inlineStr"/>
-      <c r="U61" s="47" t="inlineStr">
+      <c r="T61" s="49" t="inlineStr"/>
+      <c r="U61" s="49" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7663,7 +7737,58 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="14.4" customHeight="1"/>
+    <row r="62" ht="14.4" customHeight="1">
+      <c r="R62" s="39" t="inlineStr">
+        <is>
+          <t>182 South 95th Avenue</t>
+        </is>
+      </c>
+      <c r="S62" s="40" t="n"/>
+      <c r="T62" s="49" t="inlineStr"/>
+      <c r="U62" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V62">
+        <f>IFERROR(VALUE(RIGHT(T62,4))*4+MATCH(LEFT(T62,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W62">
+        <f>IF(V62="","",IF(V62&lt;=$Z$1,0,MAX(1,INT((V62-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X62">
+        <f>IF(U62="All",1,IF(U62="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U62="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="R63" s="39" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="S63" s="40" t="n"/>
+      <c r="T63" s="49" t="inlineStr"/>
+      <c r="U63" s="49" t="inlineStr">
+        <is>
+          <t>Bear only</t>
+        </is>
+      </c>
+      <c r="V63">
+        <f>IFERROR(VALUE(RIGHT(T63,4))*4+MATCH(LEFT(T63,2),{"Q1","Q2","Q3","Q4"},0)-1,"")</f>
+        <v/>
+      </c>
+      <c r="W63">
+        <f>IF(V63="","",IF(V63&lt;=$Z$1,0,MAX(1,INT((V63-$Z$2)/4)+1)))</f>
+        <v/>
+      </c>
+      <c r="X63">
+        <f>IF(U63="All",1,IF(U63="Bear+Base",IF($Z$3&gt;=2,1,0),IF(U63="Bear only",IF($Z$3&gt;=3,1,0),0)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:O2"/>
@@ -7672,7 +7797,7 @@
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Bear,Base,Bull"</formula1>
     </dataValidation>
-    <dataValidation sqref="U18 U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U19 U20 U21 U22 U23 U24 U25 U26 U27 U28 U29 U30 U31 U32 U33 U34 U35 U36 U37 U38 U39 U40 U41 U42 U43 U44 U45 U46 U47 U48 U49 U50 U51 U52 U53 U54 U55 U56 U57 U58 U59 U60 U61 U62 U63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Bear only,Bear+Base,All,None"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7686,7 +7811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8157,7 +8282,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Year built: 2023/2024; Units: CoStar 292 vs RealPage 239; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 87%</t>
+          <t>Year built: 2023/2024; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 87%</t>
         </is>
       </c>
     </row>
@@ -9029,23 +9154,19 @@
       <c r="G27" s="66" t="n">
         <v>0.1333329999999999</v>
       </c>
-      <c r="H27" s="66" t="n">
-        <v>0</v>
-      </c>
+      <c r="H27" s="66" t="n"/>
       <c r="I27" s="67" t="n">
         <v>1411</v>
       </c>
-      <c r="J27" s="67" t="n">
-        <v>1145</v>
-      </c>
+      <c r="J27" s="67" t="n"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Delivery quarter estimated; Occ: CoStar 13% vs RealPage 0%; Rent: CoStar ask $1,411 vs RealPage eff $1,145; Verify rent/occ w/ HelloData</t>
+          <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
@@ -10638,34 +10759,41 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Northern 107</t>
+          <t>Flatz623</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>N 107th Ave</t>
+          <t>11850 W Fillmore St</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>74</v>
+        <v>360</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2026</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Q4 2028</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
       <c r="G62" s="66" t="n"/>
-      <c r="H62" s="66" t="n"/>
+      <c r="H62" s="66" t="n">
+        <v>0</v>
+      </c>
       <c r="I62" s="67" t="n"/>
-      <c r="J62" s="67" t="n"/>
+      <c r="J62" s="67" t="n">
+        <v>1145</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>RealPage</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -10673,23 +10801,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>The Waverly</t>
+          <t>Northern 107</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>391 S 99th Ave</t>
+          <t>N 107th Ave</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>323</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2028</v>
+        <v>74</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
+          <t>Q4 2028</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -10703,7 +10828,7 @@
       <c r="J63" s="67" t="n"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -10711,16 +10836,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>The Statler at Estrella Parkway</t>
+          <t>The Waverly</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>240 N Estrella Pky</t>
+          <t>391 S 99th Ave</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>284</v>
+        <v>323</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2028</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -10738,7 +10866,7 @@
       <c r="J64" s="67" t="n"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -10746,19 +10874,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Encore Avondale</t>
+          <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11295 W Roosevelt St</t>
+          <t>240 N Estrella Pky</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>300</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2027</v>
+        <v>284</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -10776,7 +10901,7 @@
       <c r="J65" s="67" t="n"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>CoStar+RealPage</t>
+          <t>CoStar</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -10784,16 +10909,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ascent Goodyear</t>
+          <t>Encore Avondale</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15681 W Roosevelt St</t>
+          <t>11295 W Roosevelt St</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>113</v>
+        <v>300</v>
       </c>
       <c r="D66" t="n">
         <v>2027</v>
@@ -10814,7 +10939,7 @@
       <c r="J66" s="67" t="n"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>CoStar</t>
+          <t>CoStar+RealPage</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -10822,16 +10947,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>District 99</t>
+          <t>Ascent Goodyear</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>N 99th Ave &amp; W McDowell Rd</t>
+          <t>15681 W Roosevelt St</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>172</v>
+        <v>113</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Q3 2028</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -10844,28 +10977,24 @@
       <c r="J67" s="67" t="n"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>RealPage</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>RealPage pipeline (not yet in CoStar)</t>
-        </is>
-      </c>
+          <t>CoStar</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Liv Avondale</t>
+          <t>District 99</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>W Indian School Rd &amp; N 99th Ave</t>
+          <t>N 99th Ave &amp; W McDowell Rd</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>333</v>
+        <v>172</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -10890,16 +11019,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sanctuair at Centerscape</t>
+          <t>Liv Avondale</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1450 N 145th Ave</t>
+          <t>W Indian School Rd &amp; N 99th Ave</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -10924,16 +11053,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cornerstone at the Wigwam</t>
+          <t>Sanctuair at Centerscape</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Litchfield Rd &amp; Wigwam Blvd</t>
+          <t>1450 N 145th Ave</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -10958,13 +11087,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The BLVD Residential District</t>
+          <t>Cornerstone at the Wigwam</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>W Roosevelt St &amp; W Hilton Way</t>
-        </is>
+          <t>Litchfield Rd &amp; Wigwam Blvd</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>212</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -10989,16 +11121,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Crystal Cove</t>
+          <t>The BLVD Residential District</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>290 E La Canada Blvd</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>260</v>
+          <t>W Roosevelt St &amp; W Hilton Way</t>
+        </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -11023,13 +11152,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>The BLVD Park Avenue District</t>
+          <t>Crystal Cove</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>N Avondale Blvd &amp; W Van Buren St</t>
-        </is>
+          <t>290 E La Canada Blvd</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>260</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -11054,16 +11186,13 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Western Garden II</t>
+          <t>The BLVD Park Avenue District</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3301 N 99th Ave</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>314</v>
+          <t>N Avondale Blvd &amp; W Van Buren St</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -11088,16 +11217,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tavalo at Avondale</t>
+          <t>Western Garden II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12451 W Buckeye Rd</t>
+          <t>3301 N 99th Ave</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -11122,13 +11251,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Globe Land Investors Development</t>
+          <t>Tavalo at Avondale</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N Bullard Ave &amp; W McDowell Rd</t>
-        </is>
+          <t>12451 W Buckeye Rd</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>266</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -11153,12 +11285,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ball Park</t>
+          <t>Globe Land Investors Development</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6450 N 99th Ave</t>
+          <t>N Bullard Ave &amp; W McDowell Rd</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -11184,16 +11316,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel B</t>
+          <t>Ball Park</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>N 95th Ave &amp; W Georgia Ave</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>478</v>
+          <t>6450 N 99th Ave</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -11218,16 +11347,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>The District at Westgate</t>
+          <t>Urban 95 Parcel B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6801 N 91st Ave</t>
+          <t>N 95th Ave &amp; W Georgia Ave</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>384</v>
+        <v>478</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -11252,13 +11381,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vision 2 Parcel A</t>
+          <t>The District at Westgate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>W Glendale Ave &amp; N 99th Ave</t>
-        </is>
+          <t>6801 N 91st Ave</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>384</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -11283,16 +11415,13 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Anton Glendale</t>
+          <t>Vision 2 Parcel A</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5149 &amp; 5205 N 99th Ave</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>320</v>
+          <t>W Glendale Ave &amp; N 99th Ave</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -11317,16 +11446,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Banyan Avondale</t>
+          <t>Anton Glendale</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dysart Rd &amp; E Madison St</t>
+          <t>5149 &amp; 5205 N 99th Ave</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11351,16 +11480,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel B</t>
+          <t>Banyan Avondale</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>844 Litchfield Rd</t>
+          <t>Dysart Rd &amp; E Madison St</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>410</v>
+        <v>296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11385,16 +11514,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel A</t>
+          <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>W Georgia Ave &amp; N 95th Ave</t>
+          <t>844 Litchfield Rd</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11419,7 +11548,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Urban 95 Parcel C</t>
+          <t>Urban 95 Parcel A</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -11428,7 +11557,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>500</v>
+        <v>324</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11453,13 +11582,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Firststreet Verde</t>
+          <t>Urban 95 Parcel C</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>9275 W Van Buren St</t>
-        </is>
+          <t>W Georgia Ave &amp; N 95th Ave</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>500</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11484,16 +11616,13 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Radia Avondale Station III</t>
+          <t>Firststreet Verde</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>W Encanto Blvd &amp; N 99th Ave</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>212</v>
+          <t>9275 W Van Buren St</t>
+        </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11518,16 +11647,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Rosilian Villas</t>
+          <t>Radia Avondale Station III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>N Dysart Rd &amp; E Van Buren St</t>
+          <t>W Encanto Blvd &amp; N 99th Ave</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>291</v>
+        <v>212</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11552,13 +11681,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Goodyear Civic Square at Estrella Falls</t>
+          <t>Rosilian Villas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>W Monte Vista &amp; N 150th Dr</t>
-        </is>
+          <t>N Dysart Rd &amp; E Van Buren St</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11583,12 +11715,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>I-10 Innovation Center II</t>
+          <t>Goodyear Civic Square at Estrella Falls</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>N 91st Ave &amp; W Roosevelt St</t>
+          <t>W Monte Vista &amp; N 150th Dr</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -11614,16 +11746,13 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Orion Avondale</t>
+          <t>I-10 Innovation Center II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>W McDowell Rd &amp; Avondale Blvd</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>268</v>
+          <t>N 91st Ave &amp; W Roosevelt St</t>
+        </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11648,16 +11777,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel A</t>
+          <t>Orion Avondale</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Celebrate Life Way &amp; N Litchfield Rd</t>
+          <t>W McDowell Rd &amp; Avondale Blvd</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>181</v>
+        <v>268</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11682,13 +11811,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Celebration Plaza Parcel D</t>
+          <t>Celebration Plaza Parcel A</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Celebrate Life Way &amp; N Litchfield Rd</t>
         </is>
+      </c>
+      <c r="C93" t="n">
+        <v>181</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11713,16 +11845,13 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sheely Center Future Phase</t>
+          <t>Celebration Plaza Parcel D</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2215 N 99th Ave</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>697</v>
+          <t>Celebrate Life Way &amp; N Litchfield Rd</t>
+        </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11747,16 +11876,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Porter Kyle Development</t>
+          <t>Sheely Center Future Phase</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>W Camelback Rd &amp; S Denny Blvd</t>
+          <t>2215 N 99th Ave</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>135</v>
+        <v>697</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11781,16 +11910,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>McDowell Villas</t>
+          <t>Porter Kyle Development</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>11791 W McDowell Rd</t>
+          <t>W Camelback Rd &amp; S Denny Blvd</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11815,13 +11944,16 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SimonMed Development II</t>
+          <t>McDowell Villas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>W Glendale Ave &amp; N 99th Ave</t>
-        </is>
+          <t>11791 W McDowell Rd</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>164</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11846,12 +11978,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>182 South 95th Avenue</t>
+          <t>SimonMed Development II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>182 S 95th Ave</t>
+          <t>W Glendale Ave &amp; N 99th Ave</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11877,16 +12009,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Picerne at Palm Valley</t>
+          <t>SimonMed Development I</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2128 Pebble Creek Pkwy</t>
+          <t>10020 W Glendale Ave</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>383</v>
+        <v>239</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11911,16 +12043,13 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Avondale</t>
+          <t>182 South 95th Avenue</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1498 Historic US-80</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>156</v>
+          <t>182 S 95th Ave</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11945,16 +12074,16 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Fuze 623</t>
+          <t>Picerne at Palm Valley</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>11745 W Corporate Dr</t>
+          <t>2128 Pebble Creek Pkwy</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>321</v>
+        <v>383</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11979,16 +12108,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Villages at River Grove</t>
+          <t>Avondale</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>W Buckeye Rd &amp; S El Mirage Rd</t>
+          <t>1498 Historic US-80</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12013,16 +12142,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zenn @ Sierra Verde</t>
+          <t>Fuze 623</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>W Olive Ave &amp; N El Mirage Rd</t>
+          <t>11745 W Corporate Dr</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>66</v>
+        <v>321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12047,13 +12176,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Envision Encore</t>
+          <t>Villages at River Grove</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>N Ball Park Blvd &amp; N 99th Ave</t>
-        </is>
+          <t>W Buckeye Rd &amp; S El Mirage Rd</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>180</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12078,16 +12210,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Marbella Ranch East Future Phase</t>
+          <t>Zenn @ Sierra Verde</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>W Northern Ave &amp; N El Mirage Rd</t>
+          <t>W Olive Ave &amp; N El Mirage Rd</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12109,6 +12241,71 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Envision Encore</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>N Ball Park Blvd &amp; N 99th Ave</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="G106" s="66" t="n"/>
+      <c r="H106" s="66" t="n"/>
+      <c r="I106" s="67" t="n"/>
+      <c r="J106" s="67" t="n"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Marbella Ranch East Future Phase</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>W Northern Ave &amp; N El Mirage Rd</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>266</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="G107" s="66" t="n"/>
+      <c r="H107" s="66" t="n"/>
+      <c r="I107" s="67" t="n"/>
+      <c r="J107" s="67" t="n"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>RealPage</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>RealPage pipeline (not yet in CoStar)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -6183,24 +6183,33 @@
           <t xml:space="preserve">  Concession %</t>
         </is>
       </c>
-      <c r="C28" s="57" t="n">
-        <v>0.00570570212563039</v>
-      </c>
-      <c r="D28" s="57" t="n">
-        <v>0.005404400758959575</v>
-      </c>
-      <c r="E28" s="57" t="n"/>
-      <c r="F28" s="57" t="n">
-        <v>0.03835640964430642</v>
-      </c>
-      <c r="G28" s="57" t="n">
-        <v>0.06343995398468492</v>
-      </c>
-      <c r="H28" s="57" t="n">
-        <v>0.07904205281810649</v>
-      </c>
-      <c r="I28" s="57" t="n">
-        <v>0.07045035055908758</v>
+      <c r="C28" s="57">
+        <f>IFERROR((C23-C25)/C23,"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="57">
+        <f>IFERROR((D23-D25)/D23,"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="57">
+        <f>IFERROR((E23-E25)/E23,"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="57">
+        <f>IFERROR((F23-F25)/F23,"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="57">
+        <f>IFERROR((G23-G25)/G23,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="57">
+        <f>IFERROR((H23-H25)/H23,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="57">
+        <f>IFERROR((I23-I25)/I23,"")</f>
+        <v/>
       </c>
       <c r="J28" s="58" t="n"/>
       <c r="K28" s="58" t="n"/>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -18,10 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;;&quot;—&quot;"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mi&quot;;;&quot;—&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -194,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -227,6 +228,9 @@
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -244,6 +248,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,6 +272,9 @@
     <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -282,6 +292,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -335,10 +348,10 @@
     <xf numFmtId="164" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -861,7 +874,9 @@
           <t>Luna Bear Properties LLC</t>
         </is>
       </c>
-      <c r="I6" s="7" t="n"/>
+      <c r="I6" s="12" t="n">
+        <v>4.1</v>
+      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Single Family</t>
@@ -897,7 +912,9 @@
           <t>BGO</t>
         </is>
       </c>
-      <c r="I7" s="7" t="n"/>
+      <c r="I7" s="12" t="n">
+        <v>4.4</v>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Single Family</t>
@@ -937,7 +954,9 @@
           <t>Sunrise Multifamily LLC</t>
         </is>
       </c>
-      <c r="I8" s="7" t="n"/>
+      <c r="I8" s="12" t="n">
+        <v>3.7</v>
+      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -977,7 +996,9 @@
           <t>Brett C. &amp; Lorraine M. Heers</t>
         </is>
       </c>
-      <c r="I9" s="7" t="n"/>
+      <c r="I9" s="12" t="n">
+        <v>2.6</v>
+      </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
@@ -1017,7 +1038,9 @@
           <t>Alliance Residential Company</t>
         </is>
       </c>
-      <c r="I10" s="7" t="n"/>
+      <c r="I10" s="12" t="n">
+        <v>4.8</v>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1057,7 +1080,9 @@
           <t>Billah Khan</t>
         </is>
       </c>
-      <c r="I11" s="7" t="n"/>
+      <c r="I11" s="12" t="n">
+        <v>4</v>
+      </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
@@ -1097,7 +1122,9 @@
           <t>IDM Companies</t>
         </is>
       </c>
-      <c r="I12" s="7" t="n"/>
+      <c r="I12" s="12" t="n">
+        <v>5.8</v>
+      </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1137,7 +1164,9 @@
           <t>Greenlight Communities</t>
         </is>
       </c>
-      <c r="I13" s="7" t="n"/>
+      <c r="I13" s="12" t="n">
+        <v>4.1</v>
+      </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1177,7 +1206,9 @@
           <t>Cavan Companies</t>
         </is>
       </c>
-      <c r="I14" s="7" t="n"/>
+      <c r="I14" s="12" t="n">
+        <v>3.3</v>
+      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1217,7 +1248,9 @@
           <t>Pillar Communities</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n"/>
+      <c r="I15" s="12" t="n">
+        <v>5.3</v>
+      </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
@@ -1257,7 +1290,9 @@
           <t>Continental Properties Company, Inc.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="n"/>
+      <c r="I16" s="12" t="n">
+        <v>4.3</v>
+      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1297,7 +1332,9 @@
           <t>BB Living</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n"/>
+      <c r="I17" s="12" t="n">
+        <v>3.7</v>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>Townhome</t>
@@ -1337,7 +1374,9 @@
           <t>Empire Group of Companies</t>
         </is>
       </c>
-      <c r="I18" s="7" t="n"/>
+      <c r="I18" s="12" t="n">
+        <v>4.1</v>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1377,7 +1416,9 @@
           <t>Millburn &amp; Company</t>
         </is>
       </c>
-      <c r="I19" s="7" t="n"/>
+      <c r="I19" s="12" t="n">
+        <v>4.5</v>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1417,7 +1458,9 @@
           <t>Christopher Todd Communities</t>
         </is>
       </c>
-      <c r="I20" s="7" t="n"/>
+      <c r="I20" s="12" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1457,7 +1500,9 @@
           <t>The Empire Group</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n"/>
+      <c r="I21" s="12" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>Single Family</t>
@@ -1497,7 +1542,9 @@
           <t>Empire Group of Companies</t>
         </is>
       </c>
-      <c r="I22" s="7" t="n"/>
+      <c r="I22" s="12" t="n">
+        <v>4</v>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Single Family</t>
@@ -1537,7 +1584,9 @@
           <t>Atlantic Creek Real Estate Partners</t>
         </is>
       </c>
-      <c r="I23" s="7" t="n"/>
+      <c r="I23" s="12" t="n">
+        <v>5.3</v>
+      </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1577,7 +1626,9 @@
           <t>TerraLane Communities</t>
         </is>
       </c>
-      <c r="I24" s="7" t="n"/>
+      <c r="I24" s="12" t="n">
+        <v>3.5</v>
+      </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1617,7 +1668,9 @@
           <t>Sunstone Properties Trust</t>
         </is>
       </c>
-      <c r="I25" s="7" t="n"/>
+      <c r="I25" s="12" t="n">
+        <v>1.1</v>
+      </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1657,7 +1710,9 @@
           <t>Larson Capital Management</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n"/>
+      <c r="I26" s="12" t="n">
+        <v>1.1</v>
+      </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
           <t>Garden</t>
@@ -1697,7 +1752,9 @@
           <t>Rockpoint Group</t>
         </is>
       </c>
-      <c r="I27" s="7" t="n"/>
+      <c r="I27" s="12" t="n">
+        <v>1.3</v>
+      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
           <t>Single Family</t>
@@ -1710,3321 +1767,3489 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>LEASING UP (28 properties, 7,249 units)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Radia Avondale Station</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>407</v>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Q1 2024</t>
         </is>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="18" t="n">
         <v>0.616708</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G30" s="19" t="n">
         <v>1743</v>
       </c>
-      <c r="H30" s="15" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>Goodman Real Estate Inc.</t>
         </is>
       </c>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="I30" s="20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J30" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="K30" s="16" t="inlineStr">
         <is>
           <t>Units: CoStar 407 vs RealPage 212; Year built: 2024/2025; Delivery quarter estimated; Occ: CoStar 62% vs RealPage 51%; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>Alta 99th</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>402</v>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Q1 2024</t>
         </is>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="18" t="n">
         <v>0.855721</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="19" t="n">
         <v>1542</v>
       </c>
-      <c r="H31" s="15" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>Wood Partners</t>
         </is>
       </c>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="I31" s="20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="K31" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 86% vs RealPage 90%; Rent: CoStar ask $1,542 vs RealPage eff $1,154; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Alta Avondale</t>
         </is>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Q2 2024</t>
         </is>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="18" t="n">
         <v>0.7833330000000001</v>
       </c>
-      <c r="G32" s="18" t="n">
+      <c r="G32" s="19" t="n">
         <v>1610</v>
       </c>
-      <c r="H32" s="15" t="inlineStr">
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>Wood Partners</t>
         </is>
       </c>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="I32" s="20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K32" s="15" t="inlineStr">
+      <c r="K32" s="16" t="inlineStr">
         <is>
           <t>Year built: 2024/2025; Delivery quarter estimated; Occ: CoStar 78% vs RealPage 84%; Rent: CoStar ask $1,610 vs RealPage eff $1,339; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>Livano Avondale</t>
         </is>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>316</v>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>Q2 2024</t>
         </is>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="18" t="n">
         <v>0.829114</v>
       </c>
-      <c r="G33" s="18" t="n">
+      <c r="G33" s="19" t="n">
         <v>1663</v>
       </c>
-      <c r="H33" s="15" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>LIV Development</t>
         </is>
       </c>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="I33" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="K33" s="16" t="inlineStr">
         <is>
           <t>Year built: 2024/2025; Delivery quarter estimated; Rent: CoStar ask $1,663 vs RealPage eff $1,263; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Cardinal 95</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>198</v>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Q2 2024</t>
         </is>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="18" t="n">
         <v>0.878788</v>
       </c>
-      <c r="G34" s="18" t="n">
+      <c r="G34" s="19" t="n">
         <v>1691</v>
       </c>
-      <c r="H34" s="15" t="inlineStr">
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>Quarry Capital</t>
         </is>
       </c>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="I34" s="20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J34" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="K34" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>Moderne at Roosevelt</t>
         </is>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>185</v>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Q2 2024</t>
         </is>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="18" t="n">
         <v>0.891892</v>
       </c>
-      <c r="G35" s="18" t="n">
+      <c r="G35" s="19" t="n">
         <v>1900</v>
       </c>
-      <c r="H35" s="15" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>MODERNE Communities</t>
         </is>
       </c>
-      <c r="I35" s="14" t="n"/>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="I35" s="20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J35" s="15" t="inlineStr">
         <is>
           <t>Low-Rise</t>
         </is>
       </c>
-      <c r="K35" s="15" t="inlineStr">
+      <c r="K35" s="16" t="inlineStr">
         <is>
           <t>Year built: 2024/2025; Occ: CoStar 89% vs RealPage 94%; Rent: CoStar ask $1,900 vs RealPage eff $1,769; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Canopy at the Trails</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>124</v>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>Q2 2024</t>
         </is>
       </c>
-      <c r="F36" s="17" t="n">
+      <c r="F36" s="18" t="n">
         <v>0.879032</v>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="G36" s="19" t="n">
         <v>2183</v>
       </c>
-      <c r="H36" s="15" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>Mark-Taylor Companies</t>
         </is>
       </c>
-      <c r="I36" s="14" t="n"/>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="I36" s="20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J36" s="15" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K36" s="15" t="inlineStr">
+      <c r="K36" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 88% vs RealPage 92%; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>Meritum Sheely Farms</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>680</v>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Q4 2024</t>
         </is>
       </c>
-      <c r="F37" s="17" t="n">
+      <c r="F37" s="18" t="n">
         <v>0.797059</v>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="G37" s="19" t="n">
         <v>1680</v>
       </c>
-      <c r="H37" s="15" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>IDM Companies</t>
         </is>
       </c>
-      <c r="I37" s="14" t="n"/>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="I37" s="20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K37" s="15" t="inlineStr">
+      <c r="K37" s="16" t="inlineStr">
         <is>
           <t>Year built: 2024/2025; Delivery quarter estimated; Rent: CoStar ask $1,680 vs RealPage eff $1,356; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Alta Goodyear</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>342</v>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F38" s="17" t="n">
+      <c r="F38" s="18" t="n">
         <v>0.789474</v>
       </c>
-      <c r="G38" s="18" t="n">
+      <c r="G38" s="19" t="n">
         <v>1638</v>
       </c>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>Wood Partners</t>
         </is>
       </c>
-      <c r="I38" s="14" t="n"/>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="I38" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J38" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="K38" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Rent: CoStar ask $1,638 vs RealPage eff $1,433; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>Agave Ranch</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>324</v>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F39" s="17" t="n">
+      <c r="F39" s="18" t="n">
         <v>0.802469</v>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="G39" s="19" t="n">
         <v>1747</v>
       </c>
-      <c r="H39" s="15" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>The Garrett Companies</t>
         </is>
       </c>
-      <c r="I39" s="14" t="n"/>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="I39" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J39" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K39" s="15" t="inlineStr">
+      <c r="K39" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 80% vs RealPage 0%; Rent: CoStar ask $1,747 vs RealPage eff $1,582; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>Avondale Commons</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>324</v>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F40" s="17" t="n">
+      <c r="F40" s="18" t="n">
         <v>0.37037</v>
       </c>
-      <c r="G40" s="18" t="n">
+      <c r="G40" s="19" t="n">
         <v>1632</v>
       </c>
-      <c r="H40" s="15" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>Overland Group</t>
         </is>
       </c>
-      <c r="I40" s="14" t="n"/>
-      <c r="J40" s="14" t="inlineStr">
+      <c r="I40" s="20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J40" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K40" s="15" t="inlineStr">
+      <c r="K40" s="16" t="inlineStr">
         <is>
           <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 37% vs RealPage 85%; Rent: CoStar ask $1,632 vs RealPage eff $1,321; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="14" t="n">
+      <c r="B41" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>Broadstone Westgate</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>308</v>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F41" s="17" t="n">
+      <c r="F41" s="18" t="n">
         <v>0.89</v>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="G41" s="19" t="n">
         <v>1438</v>
       </c>
-      <c r="H41" s="15" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>Alliance Residential Company/American Realty Advisors</t>
         </is>
       </c>
-      <c r="I41" s="14" t="n"/>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="I41" s="20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J41" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
+      <c r="K41" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>The Douglas</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>307</v>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F42" s="17" t="n">
+      <c r="F42" s="18" t="n">
         <v>0.583062</v>
       </c>
-      <c r="G42" s="18" t="n">
+      <c r="G42" s="19" t="n">
         <v>2076</v>
       </c>
-      <c r="H42" s="15" t="inlineStr">
+      <c r="H42" s="16" t="inlineStr">
         <is>
           <t>UrbanStreet Group</t>
         </is>
       </c>
-      <c r="I42" s="14" t="n"/>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="I42" s="20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J42" s="15" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K42" s="15" t="inlineStr">
+      <c r="K42" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Rent: CoStar ask $2,076 vs RealPage eff $1,561; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="15" t="n">
         <v>36</v>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>Streamliner Aldea</t>
         </is>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>282</v>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F43" s="17" t="n">
+      <c r="F43" s="18" t="n">
         <v>0.844</v>
       </c>
-      <c r="G43" s="18" t="n">
+      <c r="G43" s="19" t="n">
         <v>1025</v>
       </c>
-      <c r="H43" s="15" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>Greenlight Communities LLC</t>
         </is>
       </c>
-      <c r="I43" s="14" t="n"/>
-      <c r="J43" s="14" t="inlineStr">
+      <c r="I43" s="20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J43" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K43" s="15" t="inlineStr">
+      <c r="K43" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="14" t="n">
+      <c r="B44" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>Cabana Aldea</t>
         </is>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>257</v>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F44" s="17" t="n">
+      <c r="F44" s="18" t="n">
         <v>0.7393000000000001</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="G44" s="19" t="n">
         <v>1330</v>
       </c>
-      <c r="H44" s="15" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>Greenlight Communities</t>
         </is>
       </c>
-      <c r="I44" s="14" t="n"/>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="I44" s="20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J44" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K44" s="15" t="inlineStr">
+      <c r="K44" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 74% vs RealPage 67%; Rent: CoStar ask $1,330 vs RealPage eff $1,253; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="14" t="n">
+      <c r="B45" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>Somerset Upscale Apartments</t>
         </is>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>234</v>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F45" s="17" t="n">
+      <c r="F45" s="18" t="n">
         <v>0.256</v>
       </c>
-      <c r="G45" s="18" t="n">
+      <c r="G45" s="19" t="n">
         <v>1671</v>
       </c>
-      <c r="H45" s="15" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>Ridgehouse Companies</t>
         </is>
       </c>
-      <c r="I45" s="14" t="n"/>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="I45" s="20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J45" s="15" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K45" s="15" t="inlineStr">
+      <c r="K45" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="14" t="n">
+      <c r="B46" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>Village at Skyline Ranch</t>
         </is>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>167</v>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="F46" s="17" t="n">
+      <c r="F46" s="18" t="n">
         <v>0.3952100000000001</v>
       </c>
-      <c r="G46" s="18" t="n">
+      <c r="G46" s="19" t="n">
         <v>1773</v>
       </c>
-      <c r="H46" s="15" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr">
         <is>
           <t>Empire Group of Companies</t>
         </is>
       </c>
-      <c r="I46" s="14" t="n"/>
-      <c r="J46" s="14" t="inlineStr">
+      <c r="I46" s="20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J46" s="15" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K46" s="15" t="inlineStr">
+      <c r="K46" s="16" t="inlineStr">
         <is>
           <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 40% vs RealPage 0%; Rent: CoStar ask $1,773 vs RealPage eff $1,632; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="14" t="n">
+      <c r="B47" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>Villas Litchfield Park</t>
         </is>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>153</v>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F47" s="17" t="n">
+      <c r="F47" s="18" t="n">
         <v>0.810458</v>
       </c>
-      <c r="G47" s="18" t="n">
+      <c r="G47" s="19" t="n">
         <v>1913</v>
       </c>
-      <c r="H47" s="15" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr">
         <is>
           <t>Family Development</t>
         </is>
       </c>
-      <c r="I47" s="14" t="n"/>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="I47" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J47" s="15" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K47" s="15" t="inlineStr">
+      <c r="K47" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 81% vs RealPage 86%; Rent: CoStar ask $1,913 vs RealPage eff $1,538; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="14" t="n">
+      <c r="B48" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>Villas on Van Buren</t>
         </is>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>143</v>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F48" s="17" t="n">
+      <c r="F48" s="18" t="n">
         <v>0.496503</v>
       </c>
-      <c r="G48" s="18" t="n">
+      <c r="G48" s="19" t="n">
         <v>2085</v>
       </c>
-      <c r="H48" s="15" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
         <is>
           <t>Sunstone Properties Trust</t>
         </is>
       </c>
-      <c r="I48" s="14" t="n"/>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="I48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K48" s="15" t="inlineStr">
+      <c r="K48" s="16" t="inlineStr">
         <is>
           <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 50% vs RealPage 0%; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="14" t="n">
+      <c r="B49" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>Pradera Estates</t>
         </is>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>86</v>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F49" s="17" t="n">
+      <c r="F49" s="18" t="n">
         <v>0.895349</v>
       </c>
-      <c r="G49" s="18" t="n">
+      <c r="G49" s="19" t="n">
         <v>2474</v>
       </c>
-      <c r="H49" s="15" t="inlineStr">
+      <c r="H49" s="16" t="inlineStr">
         <is>
           <t>AMH</t>
         </is>
       </c>
-      <c r="I49" s="14" t="n"/>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="I49" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J49" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K49" s="15" t="inlineStr">
+      <c r="K49" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="14" t="n">
+      <c r="B50" s="15" t="n">
         <v>43</v>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>Rev3 Encanto West</t>
         </is>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F50" s="17" t="n">
+      <c r="F50" s="18" t="n">
         <v>0.52381</v>
       </c>
-      <c r="G50" s="18" t="n">
+      <c r="G50" s="19" t="n">
         <v>2319</v>
       </c>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>Trilogy Investment Company</t>
         </is>
       </c>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="I50" s="20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J50" s="15" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K50" s="15" t="inlineStr">
+      <c r="K50" s="16" t="inlineStr">
         <is>
           <t>Units: CoStar 84 vs RealPage 78; Year built: 2025/2026; Occ: CoStar 52% vs RealPage 71%; Rent: CoStar ask $2,319 vs RealPage eff $1,833; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="14" t="n">
+      <c r="B51" s="15" t="n">
         <v>44</v>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>Avalon Townhomes</t>
         </is>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="F51" s="17" t="n">
+      <c r="F51" s="18" t="n">
         <v>0.857143</v>
       </c>
-      <c r="G51" s="18" t="n">
+      <c r="G51" s="19" t="n">
         <v>2325</v>
       </c>
-      <c r="H51" s="15" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>LVP Partners Group</t>
         </is>
       </c>
-      <c r="I51" s="14" t="n"/>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="I51" s="20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J51" s="15" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K51" s="15" t="inlineStr">
+      <c r="K51" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Rent: CoStar ask $2,325 vs RealPage eff $2,169; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="14" t="n">
+      <c r="B52" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>Broadstone Ascend</t>
         </is>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>432</v>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F52" s="17" t="n">
+      <c r="F52" s="18" t="n">
         <v>0.875</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="G52" s="19" t="n">
         <v>1506</v>
       </c>
-      <c r="H52" s="15" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>Alliance Residential Company</t>
         </is>
       </c>
-      <c r="I52" s="14" t="n"/>
-      <c r="J52" s="14" t="inlineStr">
+      <c r="I52" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J52" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K52" s="15" t="inlineStr">
+      <c r="K52" s="16" t="inlineStr">
         <is>
           <t>Year built: 2025/2026; Delivery quarter estimated; Occ: CoStar 88% vs RealPage 51%; Rent: CoStar ask $1,506 vs RealPage eff $1,107; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="14" t="n">
+      <c r="B53" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>Flatz 623</t>
         </is>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="F53" s="17" t="n">
+      <c r="F53" s="18" t="n">
         <v>0.1333329999999999</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="G53" s="19" t="n">
         <v>1411</v>
       </c>
-      <c r="H53" s="15" t="inlineStr">
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>Zekelman Industries</t>
         </is>
       </c>
-      <c r="I53" s="14" t="n"/>
-      <c r="J53" s="14" t="inlineStr">
+      <c r="I53" s="20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J53" s="15" t="inlineStr">
         <is>
           <t>Low-Rise</t>
         </is>
       </c>
-      <c r="K53" s="15" t="inlineStr">
+      <c r="K53" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="14" t="n">
+      <c r="B54" s="15" t="n">
         <v>47</v>
       </c>
-      <c r="C54" s="15" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>Stately Avondale</t>
         </is>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>286</v>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="F54" s="17" t="n">
+      <c r="F54" s="18" t="n">
         <v>0.297203</v>
       </c>
-      <c r="G54" s="18" t="n">
+      <c r="G54" s="19" t="n">
         <v>1728</v>
       </c>
-      <c r="H54" s="15" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>Ascent Companies</t>
         </is>
       </c>
-      <c r="I54" s="14" t="n"/>
-      <c r="J54" s="14" t="inlineStr">
+      <c r="I54" s="20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J54" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K54" s="15" t="inlineStr">
+      <c r="K54" s="16" t="inlineStr">
         <is>
           <t>Year built: 2026/2027; Delivery quarter estimated; Occ: CoStar 30% vs RealPage 0%; Rent: CoStar ask $1,728 vs RealPage eff $1,243; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="14" t="n">
+      <c r="B55" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="C55" s="15" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>Avilla Western Garden</t>
         </is>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>195</v>
       </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="F55" s="17" t="n">
+      <c r="F55" s="18" t="n">
         <v>0.4461540000000001</v>
       </c>
-      <c r="G55" s="18" t="n">
+      <c r="G55" s="19" t="n">
         <v>1829</v>
       </c>
-      <c r="H55" s="15" t="inlineStr">
+      <c r="H55" s="16" t="inlineStr">
         <is>
           <t>NexMetro Communities</t>
         </is>
       </c>
-      <c r="I55" s="14" t="n"/>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="I55" s="20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J55" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K55" s="15" t="inlineStr">
+      <c r="K55" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 45% vs RealPage 0%; Rent: CoStar ask $1,829 vs RealPage eff $1,681; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="14" t="n">
+      <c r="B56" s="15" t="n">
         <v>49</v>
       </c>
-      <c r="C56" s="15" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>Rev3 at Avondale Station</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>117</v>
       </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="F56" s="17" t="n">
+      <c r="F56" s="18" t="n">
         <v>0.273504</v>
       </c>
-      <c r="G56" s="18" t="n">
+      <c r="G56" s="19" t="n">
         <v>2537</v>
       </c>
-      <c r="H56" s="15" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>Trilogy Investment Company</t>
         </is>
       </c>
-      <c r="I56" s="14" t="n"/>
-      <c r="J56" s="14" t="inlineStr">
+      <c r="I56" s="20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J56" s="15" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K56" s="15" t="inlineStr">
+      <c r="K56" s="16" t="inlineStr">
         <is>
           <t>Units: CoStar 117 vs RealPage 107; Delivery quarter estimated; Occ: CoStar 27% vs RealPage 0%; Rent: CoStar ask $2,537 vs RealPage eff $2,273; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="14" t="n">
+      <c r="B57" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>Liberty at Estrella Falls</t>
         </is>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>106</v>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="F57" s="17" t="n">
+      <c r="F57" s="18" t="n">
         <v>0.05660399999999999</v>
       </c>
-      <c r="G57" s="18" t="n">
+      <c r="G57" s="19" t="n">
         <v>2966</v>
       </c>
-      <c r="H57" s="15" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>Ronald D Newman</t>
         </is>
       </c>
-      <c r="I57" s="14" t="n"/>
-      <c r="J57" s="14" t="inlineStr">
+      <c r="I57" s="20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J57" s="15" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K57" s="15" t="inlineStr">
+      <c r="K57" s="16" t="inlineStr">
         <is>
           <t>Delivery quarter estimated; Occ: CoStar 6% vs RealPage 21%; Rent: CoStar ask $2,966 vs RealPage eff $1,938; Verify rent/occ w/ HelloData</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="20" t="inlineStr">
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="22" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (11 properties, 2,307 units)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="21" t="n">
+      <c r="B60" s="23" t="n">
         <v>51</v>
       </c>
-      <c r="C60" s="22" t="inlineStr">
+      <c r="C60" s="24" t="inlineStr">
         <is>
           <t>Flatz623</t>
         </is>
       </c>
-      <c r="D60" s="23" t="n">
+      <c r="D60" s="25" t="n">
         <v>360</v>
       </c>
-      <c r="E60" s="21" t="inlineStr">
+      <c r="E60" s="23" t="inlineStr">
         <is>
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="F60" s="24" t="n"/>
-      <c r="G60" s="25" t="inlineStr">
+      <c r="F60" s="26" t="n"/>
+      <c r="G60" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H60" s="22" t="inlineStr">
+      <c r="H60" s="24" t="inlineStr">
         <is>
           <t>Zekelman Industries</t>
         </is>
       </c>
-      <c r="I60" s="21" t="n"/>
-      <c r="J60" s="21" t="inlineStr">
+      <c r="I60" s="28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
         <is>
           <t>Low-Rise</t>
         </is>
       </c>
-      <c r="K60" s="22" t="n"/>
+      <c r="K60" s="24" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="21" t="n">
+      <c r="B61" s="23" t="n">
         <v>52</v>
       </c>
-      <c r="C61" s="22" t="inlineStr">
+      <c r="C61" s="24" t="inlineStr">
         <is>
           <t>FUZE Ballpark</t>
         </is>
       </c>
-      <c r="D61" s="23" t="n">
+      <c r="D61" s="25" t="n">
         <v>321</v>
       </c>
-      <c r="E61" s="21" t="inlineStr">
+      <c r="E61" s="23" t="inlineStr">
         <is>
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="F61" s="24" t="n"/>
-      <c r="G61" s="25" t="inlineStr">
+      <c r="F61" s="26" t="n"/>
+      <c r="G61" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H61" s="22" t="inlineStr">
+      <c r="H61" s="24" t="inlineStr">
         <is>
           <t>Zekelman Industries</t>
         </is>
       </c>
-      <c r="I61" s="21" t="n"/>
-      <c r="J61" s="21" t="inlineStr">
+      <c r="I61" s="28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K61" s="22" t="n"/>
+      <c r="K61" s="24" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" s="21" t="n">
+      <c r="B62" s="23" t="n">
         <v>53</v>
       </c>
-      <c r="C62" s="22" t="inlineStr">
+      <c r="C62" s="24" t="inlineStr">
         <is>
           <t>HARMON Ascend</t>
         </is>
       </c>
-      <c r="D62" s="23" t="n">
+      <c r="D62" s="25" t="n">
         <v>125</v>
       </c>
-      <c r="E62" s="21" t="inlineStr">
+      <c r="E62" s="23" t="inlineStr">
         <is>
           <t>Q1 2027</t>
         </is>
       </c>
-      <c r="F62" s="24" t="n"/>
-      <c r="G62" s="25" t="inlineStr">
+      <c r="F62" s="26" t="n"/>
+      <c r="G62" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H62" s="22" t="inlineStr">
+      <c r="H62" s="24" t="inlineStr">
         <is>
           <t>Crescent Communities LLC</t>
         </is>
       </c>
-      <c r="I62" s="21" t="n"/>
-      <c r="J62" s="21" t="inlineStr">
+      <c r="I62" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K62" s="22" t="n"/>
+      <c r="K62" s="24" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" s="21" t="n">
+      <c r="B63" s="23" t="n">
         <v>54</v>
       </c>
-      <c r="C63" s="22" t="inlineStr">
+      <c r="C63" s="24" t="inlineStr">
         <is>
           <t>Pointe Grand Estrella at Phoenix</t>
         </is>
       </c>
-      <c r="D63" s="23" t="n">
+      <c r="D63" s="25" t="n">
         <v>288</v>
       </c>
-      <c r="E63" s="21" t="inlineStr">
+      <c r="E63" s="23" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F63" s="24" t="n"/>
-      <c r="G63" s="25" t="inlineStr">
+      <c r="F63" s="26" t="n"/>
+      <c r="G63" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H63" s="22" t="inlineStr">
+      <c r="H63" s="24" t="inlineStr">
         <is>
           <t>Hillpointe, LLC</t>
         </is>
       </c>
-      <c r="I63" s="21" t="n"/>
-      <c r="J63" s="21" t="inlineStr">
+      <c r="I63" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" s="23" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K63" s="22" t="inlineStr">
+      <c r="K63" s="24" t="inlineStr">
         <is>
           <t>Year built: 2026/2027</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="21" t="n">
+      <c r="B64" s="23" t="n">
         <v>55</v>
       </c>
-      <c r="C64" s="22" t="inlineStr">
+      <c r="C64" s="24" t="inlineStr">
         <is>
           <t>Marbella Ranch East I</t>
         </is>
       </c>
-      <c r="D64" s="23" t="n">
+      <c r="D64" s="25" t="n">
         <v>144</v>
       </c>
-      <c r="E64" s="21" t="inlineStr">
+      <c r="E64" s="23" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F64" s="24" t="n"/>
-      <c r="G64" s="25" t="inlineStr">
+      <c r="F64" s="26" t="n"/>
+      <c r="G64" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H64" s="22" t="inlineStr">
+      <c r="H64" s="24" t="inlineStr">
         <is>
           <t>Symmetry Companies</t>
         </is>
       </c>
-      <c r="I64" s="21" t="n"/>
-      <c r="J64" s="21" t="inlineStr">
+      <c r="I64" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" s="23" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K64" s="22" t="n"/>
+      <c r="K64" s="24" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="21" t="n">
+      <c r="B65" s="23" t="n">
         <v>56</v>
       </c>
-      <c r="C65" s="22" t="inlineStr">
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>Villages at Northern</t>
         </is>
       </c>
-      <c r="D65" s="23" t="n">
+      <c r="D65" s="25" t="n">
         <v>74</v>
       </c>
-      <c r="E65" s="21" t="inlineStr">
+      <c r="E65" s="23" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F65" s="24" t="n"/>
-      <c r="G65" s="25" t="inlineStr">
+      <c r="F65" s="26" t="n"/>
+      <c r="G65" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H65" s="22" t="inlineStr">
+      <c r="H65" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I65" s="21" t="n"/>
-      <c r="J65" s="21" t="inlineStr">
+      <c r="I65" s="28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K65" s="22" t="n"/>
+      <c r="K65" s="24" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="21" t="n">
+      <c r="B66" s="23" t="n">
         <v>57</v>
       </c>
-      <c r="C66" s="22" t="inlineStr">
+      <c r="C66" s="24" t="inlineStr">
         <is>
           <t>Prosper 47</t>
         </is>
       </c>
-      <c r="D66" s="23" t="n">
+      <c r="D66" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="E66" s="21" t="inlineStr">
+      <c r="E66" s="23" t="inlineStr">
         <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F66" s="24" t="n"/>
-      <c r="G66" s="25" t="inlineStr">
+      <c r="F66" s="26" t="n"/>
+      <c r="G66" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H66" s="22" t="inlineStr">
+      <c r="H66" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I66" s="21" t="n"/>
-      <c r="J66" s="21" t="inlineStr">
+      <c r="I66" s="28" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K66" s="22" t="inlineStr">
+      <c r="K66" s="24" t="inlineStr">
         <is>
           <t>RealPage only (sub-50 unit)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="21" t="n">
+      <c r="B67" s="23" t="n">
         <v>58</v>
       </c>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="C67" s="24" t="inlineStr">
         <is>
           <t>Yardly Algodon</t>
         </is>
       </c>
-      <c r="D67" s="23" t="n">
+      <c r="D67" s="25" t="n">
         <v>262</v>
       </c>
-      <c r="E67" s="21" t="inlineStr">
+      <c r="E67" s="23" t="inlineStr">
         <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F67" s="24" t="n"/>
-      <c r="G67" s="25" t="inlineStr">
+      <c r="F67" s="26" t="n"/>
+      <c r="G67" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H67" s="22" t="inlineStr">
+      <c r="H67" s="24" t="inlineStr">
         <is>
           <t>Taylor Morrison, Inc.</t>
         </is>
       </c>
-      <c r="I67" s="21" t="n"/>
-      <c r="J67" s="21" t="inlineStr">
+      <c r="I67" s="28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K67" s="22" t="inlineStr">
+      <c r="K67" s="24" t="inlineStr">
         <is>
           <t>Units: CoStar 262 vs RealPage 291; Year built: 2026/2027</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="21" t="n">
+      <c r="B68" s="23" t="n">
         <v>59</v>
       </c>
-      <c r="C68" s="22" t="inlineStr">
+      <c r="C68" s="24" t="inlineStr">
         <is>
           <t>Cerro Vista</t>
         </is>
       </c>
-      <c r="D68" s="23" t="n">
+      <c r="D68" s="25" t="n">
         <v>255</v>
       </c>
-      <c r="E68" s="21" t="inlineStr">
+      <c r="E68" s="23" t="inlineStr">
         <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F68" s="24" t="n"/>
-      <c r="G68" s="25" t="inlineStr">
+      <c r="F68" s="26" t="n"/>
+      <c r="G68" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H68" s="22" t="inlineStr">
+      <c r="H68" s="24" t="inlineStr">
         <is>
           <t>Virtua Partners</t>
         </is>
       </c>
-      <c r="I68" s="21" t="n"/>
-      <c r="J68" s="21" t="inlineStr">
+      <c r="I68" s="28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
         <is>
           <t>Low-Rise</t>
         </is>
       </c>
-      <c r="K68" s="22" t="n"/>
+      <c r="K68" s="24" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="21" t="n">
+      <c r="B69" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="C69" s="22" t="inlineStr">
+      <c r="C69" s="24" t="inlineStr">
         <is>
           <t>Zanjero III</t>
         </is>
       </c>
-      <c r="D69" s="23" t="n">
+      <c r="D69" s="25" t="n">
         <v>301</v>
       </c>
-      <c r="E69" s="21" t="inlineStr">
+      <c r="E69" s="23" t="inlineStr">
         <is>
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F69" s="24" t="n"/>
-      <c r="G69" s="25" t="inlineStr">
+      <c r="F69" s="26" t="n"/>
+      <c r="G69" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H69" s="22" t="inlineStr">
+      <c r="H69" s="24" t="inlineStr">
         <is>
           <t>Fore Property Company/Privately Owned</t>
         </is>
       </c>
-      <c r="I69" s="21" t="n"/>
-      <c r="J69" s="21" t="inlineStr">
+      <c r="I69" s="28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K69" s="22" t="n"/>
+      <c r="K69" s="24" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="21" t="n">
+      <c r="B70" s="23" t="n">
         <v>61</v>
       </c>
-      <c r="C70" s="22" t="inlineStr">
+      <c r="C70" s="24" t="inlineStr">
         <is>
           <t>Zen @ Angelina</t>
         </is>
       </c>
-      <c r="D70" s="23" t="n">
+      <c r="D70" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="E70" s="21" t="inlineStr">
+      <c r="E70" s="23" t="inlineStr">
         <is>
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F70" s="24" t="n"/>
-      <c r="G70" s="25" t="inlineStr">
+      <c r="F70" s="26" t="n"/>
+      <c r="G70" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H70" s="22" t="inlineStr">
+      <c r="H70" s="24" t="inlineStr">
         <is>
           <t>F &amp; S Consulting &amp; Management, LLC</t>
         </is>
       </c>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="inlineStr">
+      <c r="I70" s="28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J70" s="23" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K70" s="22" t="inlineStr">
+      <c r="K70" s="24" t="inlineStr">
         <is>
           <t>Year built: 2027/2028</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="26" t="n"/>
-      <c r="C72" s="27" t="inlineStr">
+      <c r="B72" s="29" t="n"/>
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>PROPOSED (45 properties, 9,225 units)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="28" t="n">
+      <c r="B73" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C73" s="29" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
         <is>
           <t>The Waverly</t>
         </is>
       </c>
-      <c r="D73" s="30" t="n">
+      <c r="D73" s="33" t="n">
         <v>323</v>
       </c>
-      <c r="E73" s="28" t="inlineStr">
+      <c r="E73" s="31" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="F73" s="31" t="n"/>
-      <c r="G73" s="32" t="inlineStr">
+      <c r="F73" s="34" t="n"/>
+      <c r="G73" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H73" s="29" t="inlineStr">
+      <c r="H73" s="32" t="inlineStr">
         <is>
           <t>Dominium</t>
         </is>
       </c>
-      <c r="I73" s="28" t="n"/>
-      <c r="J73" s="28" t="inlineStr">
+      <c r="I73" s="36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K73" s="29" t="n"/>
+      <c r="K73" s="32" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="28" t="n">
+      <c r="B74" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C74" s="29" t="inlineStr">
+      <c r="C74" s="32" t="inlineStr">
         <is>
           <t>Encore Avondale</t>
         </is>
       </c>
-      <c r="D74" s="30" t="n">
+      <c r="D74" s="33" t="n">
         <v>300</v>
       </c>
-      <c r="E74" s="28" t="inlineStr">
+      <c r="E74" s="31" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="F74" s="31" t="n"/>
-      <c r="G74" s="32" t="inlineStr">
+      <c r="F74" s="34" t="n"/>
+      <c r="G74" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H74" s="29" t="inlineStr">
+      <c r="H74" s="32" t="inlineStr">
         <is>
           <t>Encore Enterprises</t>
         </is>
       </c>
-      <c r="I74" s="28" t="n"/>
-      <c r="J74" s="28" t="inlineStr">
+      <c r="I74" s="36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J74" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K74" s="29" t="n"/>
+      <c r="K74" s="32" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="28" t="n">
+      <c r="B75" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C75" s="29" t="inlineStr">
+      <c r="C75" s="32" t="inlineStr">
         <is>
           <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
-      <c r="D75" s="30" t="n">
+      <c r="D75" s="33" t="n">
         <v>284</v>
       </c>
-      <c r="E75" s="28" t="inlineStr">
+      <c r="E75" s="31" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="F75" s="31" t="n"/>
-      <c r="G75" s="32" t="inlineStr">
+      <c r="F75" s="34" t="n"/>
+      <c r="G75" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H75" s="29" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>Leon Capital Group</t>
         </is>
       </c>
-      <c r="I75" s="28" t="n"/>
-      <c r="J75" s="28" t="inlineStr">
+      <c r="I75" s="36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J75" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K75" s="29" t="n"/>
+      <c r="K75" s="32" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="28" t="n">
+      <c r="B76" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="C76" s="29" t="inlineStr">
+      <c r="C76" s="32" t="inlineStr">
         <is>
           <t>Ascent Goodyear</t>
         </is>
       </c>
-      <c r="D76" s="30" t="n">
+      <c r="D76" s="33" t="n">
         <v>113</v>
       </c>
-      <c r="E76" s="28" t="inlineStr">
+      <c r="E76" s="31" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="F76" s="31" t="n"/>
-      <c r="G76" s="32" t="inlineStr">
+      <c r="F76" s="34" t="n"/>
+      <c r="G76" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H76" s="29" t="inlineStr">
+      <c r="H76" s="32" t="inlineStr">
         <is>
           <t>Ascent Companies</t>
         </is>
       </c>
-      <c r="I76" s="28" t="n"/>
-      <c r="J76" s="28" t="inlineStr">
+      <c r="I76" s="36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J76" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K76" s="29" t="n"/>
+      <c r="K76" s="32" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="28" t="n">
+      <c r="B77" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C77" s="32" t="inlineStr">
         <is>
           <t>Northern 107</t>
         </is>
       </c>
-      <c r="D77" s="30" t="n">
+      <c r="D77" s="33" t="n">
         <v>74</v>
       </c>
-      <c r="E77" s="28" t="inlineStr">
+      <c r="E77" s="31" t="inlineStr">
         <is>
           <t>Q4 2028</t>
         </is>
       </c>
-      <c r="F77" s="31" t="n"/>
-      <c r="G77" s="32" t="inlineStr">
+      <c r="F77" s="34" t="n"/>
+      <c r="G77" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H77" s="32" t="inlineStr">
         <is>
           <t>Jacob Reuben</t>
         </is>
       </c>
-      <c r="I77" s="28" t="n"/>
-      <c r="J77" s="28" t="inlineStr">
+      <c r="I77" s="36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J77" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K77" s="29" t="n"/>
+      <c r="K77" s="32" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="28" t="n">
+      <c r="B78" s="31" t="n">
         <v>67</v>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C78" s="32" t="inlineStr">
         <is>
           <t>Sheely Center Future Phase</t>
         </is>
       </c>
-      <c r="D78" s="30" t="n">
+      <c r="D78" s="33" t="n">
         <v>697</v>
       </c>
-      <c r="E78" s="28" t="inlineStr">
+      <c r="E78" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F78" s="31" t="n"/>
-      <c r="G78" s="32" t="inlineStr">
+      <c r="F78" s="34" t="n"/>
+      <c r="G78" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H78" s="29" t="inlineStr">
+      <c r="H78" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I78" s="28" t="n"/>
-      <c r="J78" s="28" t="inlineStr">
+      <c r="I78" s="36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J78" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K78" s="29" t="inlineStr">
+      <c r="K78" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="28" t="n">
+      <c r="B79" s="31" t="n">
         <v>68</v>
       </c>
-      <c r="C79" s="29" t="inlineStr">
+      <c r="C79" s="32" t="inlineStr">
         <is>
           <t>Urban 95 Parcel C</t>
         </is>
       </c>
-      <c r="D79" s="30" t="n">
+      <c r="D79" s="33" t="n">
         <v>500</v>
       </c>
-      <c r="E79" s="28" t="inlineStr">
+      <c r="E79" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F79" s="31" t="n"/>
-      <c r="G79" s="32" t="inlineStr">
+      <c r="F79" s="34" t="n"/>
+      <c r="G79" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H79" s="29" t="inlineStr">
+      <c r="H79" s="32" t="inlineStr">
         <is>
           <t>Fisher Industries</t>
         </is>
       </c>
-      <c r="I79" s="28" t="n"/>
-      <c r="J79" s="28" t="inlineStr">
+      <c r="I79" s="36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J79" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K79" s="29" t="inlineStr">
+      <c r="K79" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="28" t="n">
+      <c r="B80" s="31" t="n">
         <v>69</v>
       </c>
-      <c r="C80" s="29" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
         <is>
           <t>Urban 95 Parcel B</t>
         </is>
       </c>
-      <c r="D80" s="30" t="n">
+      <c r="D80" s="33" t="n">
         <v>478</v>
       </c>
-      <c r="E80" s="28" t="inlineStr">
+      <c r="E80" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F80" s="31" t="n"/>
-      <c r="G80" s="32" t="inlineStr">
+      <c r="F80" s="34" t="n"/>
+      <c r="G80" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H80" s="29" t="inlineStr">
+      <c r="H80" s="32" t="inlineStr">
         <is>
           <t>Fisher Industries</t>
         </is>
       </c>
-      <c r="I80" s="28" t="n"/>
-      <c r="J80" s="28" t="inlineStr">
+      <c r="I80" s="36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J80" s="31" t="inlineStr">
         <is>
           <t>High-Rise</t>
         </is>
       </c>
-      <c r="K80" s="29" t="inlineStr">
+      <c r="K80" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="28" t="n">
+      <c r="B81" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="C81" s="29" t="inlineStr">
+      <c r="C81" s="32" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
-      <c r="D81" s="30" t="n">
+      <c r="D81" s="33" t="n">
         <v>410</v>
       </c>
-      <c r="E81" s="28" t="inlineStr">
+      <c r="E81" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F81" s="31" t="n"/>
-      <c r="G81" s="32" t="inlineStr">
+      <c r="F81" s="34" t="n"/>
+      <c r="G81" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H81" s="29" t="inlineStr">
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I81" s="28" t="n"/>
-      <c r="J81" s="28" t="inlineStr">
+      <c r="I81" s="36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J81" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K81" s="29" t="inlineStr">
+      <c r="K81" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="28" t="n">
+      <c r="B82" s="31" t="n">
         <v>71</v>
       </c>
-      <c r="C82" s="29" t="inlineStr">
+      <c r="C82" s="32" t="inlineStr">
         <is>
           <t>The District at Westgate</t>
         </is>
       </c>
-      <c r="D82" s="30" t="n">
+      <c r="D82" s="33" t="n">
         <v>384</v>
       </c>
-      <c r="E82" s="28" t="inlineStr">
+      <c r="E82" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F82" s="31" t="n"/>
-      <c r="G82" s="32" t="inlineStr">
+      <c r="F82" s="34" t="n"/>
+      <c r="G82" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="29" t="inlineStr">
+      <c r="H82" s="32" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I82" s="28" t="n"/>
-      <c r="J82" s="28" t="inlineStr">
+      <c r="I82" s="36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J82" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K82" s="29" t="inlineStr">
+      <c r="K82" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="28" t="n">
+      <c r="B83" s="31" t="n">
         <v>72</v>
       </c>
-      <c r="C83" s="29" t="inlineStr">
+      <c r="C83" s="32" t="inlineStr">
         <is>
           <t>Picerne at Palm Valley</t>
         </is>
       </c>
-      <c r="D83" s="30" t="n">
+      <c r="D83" s="33" t="n">
         <v>383</v>
       </c>
-      <c r="E83" s="28" t="inlineStr">
+      <c r="E83" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F83" s="31" t="n"/>
-      <c r="G83" s="32" t="inlineStr">
+      <c r="F83" s="34" t="n"/>
+      <c r="G83" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H83" s="29" t="inlineStr">
+      <c r="H83" s="32" t="inlineStr">
         <is>
           <t>Picerne</t>
         </is>
       </c>
-      <c r="I83" s="28" t="n"/>
-      <c r="J83" s="28" t="inlineStr">
+      <c r="I83" s="36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J83" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K83" s="29" t="inlineStr">
+      <c r="K83" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="28" t="n">
+      <c r="B84" s="31" t="n">
         <v>73</v>
       </c>
-      <c r="C84" s="29" t="inlineStr">
+      <c r="C84" s="32" t="inlineStr">
         <is>
           <t>Liv Avondale</t>
         </is>
       </c>
-      <c r="D84" s="30" t="n">
+      <c r="D84" s="33" t="n">
         <v>333</v>
       </c>
-      <c r="E84" s="28" t="inlineStr">
+      <c r="E84" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F84" s="31" t="n"/>
-      <c r="G84" s="32" t="inlineStr">
+      <c r="F84" s="34" t="n"/>
+      <c r="G84" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H84" s="29" t="inlineStr">
+      <c r="H84" s="32" t="inlineStr">
         <is>
           <t>Liv Communities LLC</t>
         </is>
       </c>
-      <c r="I84" s="28" t="n"/>
-      <c r="J84" s="28" t="inlineStr">
+      <c r="I84" s="36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J84" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K84" s="29" t="inlineStr">
+      <c r="K84" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="28" t="n">
+      <c r="B85" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="C85" s="29" t="inlineStr">
+      <c r="C85" s="32" t="inlineStr">
         <is>
           <t>Urban 95 Parcel A</t>
         </is>
       </c>
-      <c r="D85" s="30" t="n">
+      <c r="D85" s="33" t="n">
         <v>324</v>
       </c>
-      <c r="E85" s="28" t="inlineStr">
+      <c r="E85" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F85" s="31" t="n"/>
-      <c r="G85" s="32" t="inlineStr">
+      <c r="F85" s="34" t="n"/>
+      <c r="G85" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H85" s="29" t="inlineStr">
+      <c r="H85" s="32" t="inlineStr">
         <is>
           <t>Fisher Industries</t>
         </is>
       </c>
-      <c r="I85" s="28" t="n"/>
-      <c r="J85" s="28" t="inlineStr">
+      <c r="I85" s="36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J85" s="31" t="inlineStr">
         <is>
           <t>High-Rise</t>
         </is>
       </c>
-      <c r="K85" s="29" t="inlineStr">
+      <c r="K85" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="28" t="n">
+      <c r="B86" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="C86" s="29" t="inlineStr">
+      <c r="C86" s="32" t="inlineStr">
         <is>
           <t>Fuze 623</t>
         </is>
       </c>
-      <c r="D86" s="30" t="n">
+      <c r="D86" s="33" t="n">
         <v>321</v>
       </c>
-      <c r="E86" s="28" t="inlineStr">
+      <c r="E86" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F86" s="31" t="n"/>
-      <c r="G86" s="32" t="inlineStr">
+      <c r="F86" s="34" t="n"/>
+      <c r="G86" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H86" s="29" t="inlineStr">
+      <c r="H86" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="28" t="n"/>
-      <c r="J86" s="28" t="inlineStr">
+      <c r="I86" s="36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J86" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K86" s="29" t="inlineStr">
+      <c r="K86" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="28" t="n">
+      <c r="B87" s="31" t="n">
         <v>76</v>
       </c>
-      <c r="C87" s="29" t="inlineStr">
+      <c r="C87" s="32" t="inlineStr">
         <is>
           <t>Anton Glendale</t>
         </is>
       </c>
-      <c r="D87" s="30" t="n">
+      <c r="D87" s="33" t="n">
         <v>320</v>
       </c>
-      <c r="E87" s="28" t="inlineStr">
+      <c r="E87" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F87" s="31" t="n"/>
-      <c r="G87" s="32" t="inlineStr">
+      <c r="F87" s="34" t="n"/>
+      <c r="G87" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H87" s="29" t="inlineStr">
+      <c r="H87" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I87" s="28" t="n"/>
-      <c r="J87" s="28" t="inlineStr">
+      <c r="I87" s="36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J87" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K87" s="29" t="inlineStr">
+      <c r="K87" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="28" t="n">
+      <c r="B88" s="31" t="n">
         <v>77</v>
       </c>
-      <c r="C88" s="29" t="inlineStr">
+      <c r="C88" s="32" t="inlineStr">
         <is>
           <t>Western Garden II</t>
         </is>
       </c>
-      <c r="D88" s="30" t="n">
+      <c r="D88" s="33" t="n">
         <v>314</v>
       </c>
-      <c r="E88" s="28" t="inlineStr">
+      <c r="E88" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F88" s="31" t="n"/>
-      <c r="G88" s="32" t="inlineStr">
+      <c r="F88" s="34" t="n"/>
+      <c r="G88" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H88" s="29" t="inlineStr">
+      <c r="H88" s="32" t="inlineStr">
         <is>
           <t>John F Long Properties LLLP</t>
         </is>
       </c>
-      <c r="I88" s="28" t="n"/>
-      <c r="J88" s="28" t="inlineStr">
+      <c r="I88" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" s="31" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K88" s="29" t="inlineStr">
+      <c r="K88" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="28" t="n">
+      <c r="B89" s="31" t="n">
         <v>78</v>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="C89" s="32" t="inlineStr">
         <is>
           <t>Sanctuair at Centerscape</t>
         </is>
       </c>
-      <c r="D89" s="30" t="n">
+      <c r="D89" s="33" t="n">
         <v>303</v>
       </c>
-      <c r="E89" s="28" t="inlineStr">
+      <c r="E89" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F89" s="31" t="n"/>
-      <c r="G89" s="32" t="inlineStr">
+      <c r="F89" s="34" t="n"/>
+      <c r="G89" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H89" s="29" t="inlineStr">
+      <c r="H89" s="32" t="inlineStr">
         <is>
           <t>Sunbelt Investment Holdings Inc</t>
         </is>
       </c>
-      <c r="I89" s="28" t="n"/>
-      <c r="J89" s="28" t="inlineStr">
+      <c r="I89" s="36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J89" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K89" s="29" t="inlineStr">
+      <c r="K89" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="28" t="n">
+      <c r="B90" s="31" t="n">
         <v>79</v>
       </c>
-      <c r="C90" s="29" t="inlineStr">
+      <c r="C90" s="32" t="inlineStr">
         <is>
           <t>Banyan Avondale</t>
         </is>
       </c>
-      <c r="D90" s="30" t="n">
+      <c r="D90" s="33" t="n">
         <v>296</v>
       </c>
-      <c r="E90" s="28" t="inlineStr">
+      <c r="E90" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F90" s="31" t="n"/>
-      <c r="G90" s="32" t="inlineStr">
+      <c r="F90" s="34" t="n"/>
+      <c r="G90" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H90" s="29" t="inlineStr">
+      <c r="H90" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I90" s="28" t="n"/>
-      <c r="J90" s="28" t="inlineStr">
+      <c r="I90" s="36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J90" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K90" s="29" t="inlineStr">
+      <c r="K90" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="28" t="n">
+      <c r="B91" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="C91" s="29" t="inlineStr">
+      <c r="C91" s="32" t="inlineStr">
         <is>
           <t>Rosilian Villas</t>
         </is>
       </c>
-      <c r="D91" s="30" t="n">
+      <c r="D91" s="33" t="n">
         <v>291</v>
       </c>
-      <c r="E91" s="28" t="inlineStr">
+      <c r="E91" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F91" s="31" t="n"/>
-      <c r="G91" s="32" t="inlineStr">
+      <c r="F91" s="34" t="n"/>
+      <c r="G91" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H91" s="29" t="inlineStr">
+      <c r="H91" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I91" s="28" t="n"/>
-      <c r="J91" s="28" t="inlineStr">
+      <c r="I91" s="36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J91" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K91" s="29" t="inlineStr">
+      <c r="K91" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="28" t="n">
+      <c r="B92" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="C92" s="29" t="inlineStr">
+      <c r="C92" s="32" t="inlineStr">
         <is>
           <t>Orion Avondale</t>
         </is>
       </c>
-      <c r="D92" s="30" t="n">
+      <c r="D92" s="33" t="n">
         <v>268</v>
       </c>
-      <c r="E92" s="28" t="inlineStr">
+      <c r="E92" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F92" s="31" t="n"/>
-      <c r="G92" s="32" t="inlineStr">
+      <c r="F92" s="34" t="n"/>
+      <c r="G92" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H92" s="29" t="inlineStr">
+      <c r="H92" s="32" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I92" s="28" t="n"/>
-      <c r="J92" s="28" t="inlineStr">
+      <c r="I92" s="36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J92" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K92" s="29" t="inlineStr">
+      <c r="K92" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="28" t="n">
+      <c r="B93" s="31" t="n">
         <v>82</v>
       </c>
-      <c r="C93" s="29" t="inlineStr">
+      <c r="C93" s="32" t="inlineStr">
         <is>
           <t>Tavalo at Avondale</t>
         </is>
       </c>
-      <c r="D93" s="30" t="n">
+      <c r="D93" s="33" t="n">
         <v>266</v>
       </c>
-      <c r="E93" s="28" t="inlineStr">
+      <c r="E93" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F93" s="31" t="n"/>
-      <c r="G93" s="32" t="inlineStr">
+      <c r="F93" s="34" t="n"/>
+      <c r="G93" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H93" s="29" t="inlineStr">
+      <c r="H93" s="32" t="inlineStr">
         <is>
           <t>GTIS Partners LP</t>
         </is>
       </c>
-      <c r="I93" s="28" t="n"/>
-      <c r="J93" s="28" t="inlineStr">
+      <c r="I93" s="36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J93" s="31" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K93" s="29" t="inlineStr">
+      <c r="K93" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="28" t="n">
+      <c r="B94" s="31" t="n">
         <v>83</v>
       </c>
-      <c r="C94" s="29" t="inlineStr">
+      <c r="C94" s="32" t="inlineStr">
         <is>
           <t>Marbella Ranch East Future Phase</t>
         </is>
       </c>
-      <c r="D94" s="30" t="n">
+      <c r="D94" s="33" t="n">
         <v>266</v>
       </c>
-      <c r="E94" s="28" t="inlineStr">
+      <c r="E94" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F94" s="31" t="n"/>
-      <c r="G94" s="32" t="inlineStr">
+      <c r="F94" s="34" t="n"/>
+      <c r="G94" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H94" s="29" t="inlineStr">
+      <c r="H94" s="32" t="inlineStr">
         <is>
           <t>Symmetry Companies</t>
         </is>
       </c>
-      <c r="I94" s="28" t="n"/>
-      <c r="J94" s="28" t="inlineStr">
+      <c r="I94" s="36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J94" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K94" s="29" t="inlineStr">
+      <c r="K94" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="28" t="n">
+      <c r="B95" s="31" t="n">
         <v>84</v>
       </c>
-      <c r="C95" s="29" t="inlineStr">
+      <c r="C95" s="32" t="inlineStr">
         <is>
           <t>Crystal Cove</t>
         </is>
       </c>
-      <c r="D95" s="30" t="n">
+      <c r="D95" s="33" t="n">
         <v>260</v>
       </c>
-      <c r="E95" s="28" t="inlineStr">
+      <c r="E95" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F95" s="31" t="n"/>
-      <c r="G95" s="32" t="inlineStr">
+      <c r="F95" s="34" t="n"/>
+      <c r="G95" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H95" s="29" t="inlineStr">
+      <c r="H95" s="32" t="inlineStr">
         <is>
           <t>Sterling Real Estate Partners</t>
         </is>
       </c>
-      <c r="I95" s="28" t="n"/>
-      <c r="J95" s="28" t="inlineStr">
+      <c r="I95" s="36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J95" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K95" s="29" t="inlineStr">
+      <c r="K95" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="28" t="n">
+      <c r="B96" s="31" t="n">
         <v>85</v>
       </c>
-      <c r="C96" s="29" t="inlineStr">
+      <c r="C96" s="32" t="inlineStr">
         <is>
           <t>SimonMed Development I</t>
         </is>
       </c>
-      <c r="D96" s="30" t="n">
+      <c r="D96" s="33" t="n">
         <v>239</v>
       </c>
-      <c r="E96" s="28" t="inlineStr">
+      <c r="E96" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F96" s="31" t="n"/>
-      <c r="G96" s="32" t="inlineStr">
+      <c r="F96" s="34" t="n"/>
+      <c r="G96" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H96" s="29" t="inlineStr">
+      <c r="H96" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I96" s="28" t="n"/>
-      <c r="J96" s="28" t="inlineStr">
+      <c r="I96" s="36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J96" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K96" s="29" t="inlineStr">
+      <c r="K96" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="28" t="n">
+      <c r="B97" s="31" t="n">
         <v>86</v>
       </c>
-      <c r="C97" s="29" t="inlineStr">
+      <c r="C97" s="32" t="inlineStr">
         <is>
           <t>Cornerstone at the Wigwam</t>
         </is>
       </c>
-      <c r="D97" s="30" t="n">
+      <c r="D97" s="33" t="n">
         <v>212</v>
       </c>
-      <c r="E97" s="28" t="inlineStr">
+      <c r="E97" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F97" s="31" t="n"/>
-      <c r="G97" s="32" t="inlineStr">
+      <c r="F97" s="34" t="n"/>
+      <c r="G97" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H97" s="29" t="inlineStr">
+      <c r="H97" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I97" s="28" t="n"/>
-      <c r="J97" s="28" t="inlineStr">
+      <c r="I97" s="36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J97" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K97" s="29" t="inlineStr">
+      <c r="K97" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="28" t="n">
+      <c r="B98" s="31" t="n">
         <v>87</v>
       </c>
-      <c r="C98" s="29" t="inlineStr">
+      <c r="C98" s="32" t="inlineStr">
         <is>
           <t>Radia Avondale Station III</t>
         </is>
       </c>
-      <c r="D98" s="30" t="n">
+      <c r="D98" s="33" t="n">
         <v>212</v>
       </c>
-      <c r="E98" s="28" t="inlineStr">
+      <c r="E98" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F98" s="31" t="n"/>
-      <c r="G98" s="32" t="inlineStr">
+      <c r="F98" s="34" t="n"/>
+      <c r="G98" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H98" s="29" t="inlineStr">
+      <c r="H98" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I98" s="28" t="n"/>
-      <c r="J98" s="28" t="inlineStr">
+      <c r="I98" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K98" s="29" t="inlineStr">
+      <c r="K98" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="28" t="n">
+      <c r="B99" s="31" t="n">
         <v>88</v>
       </c>
-      <c r="C99" s="29" t="inlineStr">
+      <c r="C99" s="32" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel A</t>
         </is>
       </c>
-      <c r="D99" s="30" t="n">
+      <c r="D99" s="33" t="n">
         <v>181</v>
       </c>
-      <c r="E99" s="28" t="inlineStr">
+      <c r="E99" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F99" s="31" t="n"/>
-      <c r="G99" s="32" t="inlineStr">
+      <c r="F99" s="34" t="n"/>
+      <c r="G99" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H99" s="29" t="inlineStr">
+      <c r="H99" s="32" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I99" s="28" t="n"/>
-      <c r="J99" s="28" t="inlineStr">
+      <c r="I99" s="36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J99" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K99" s="29" t="inlineStr">
+      <c r="K99" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="28" t="n">
+      <c r="B100" s="31" t="n">
         <v>89</v>
       </c>
-      <c r="C100" s="29" t="inlineStr">
+      <c r="C100" s="32" t="inlineStr">
         <is>
           <t>Villages at River Grove</t>
         </is>
       </c>
-      <c r="D100" s="30" t="n">
+      <c r="D100" s="33" t="n">
         <v>180</v>
       </c>
-      <c r="E100" s="28" t="inlineStr">
+      <c r="E100" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F100" s="31" t="n"/>
-      <c r="G100" s="32" t="inlineStr">
+      <c r="F100" s="34" t="n"/>
+      <c r="G100" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H100" s="29" t="inlineStr">
+      <c r="H100" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I100" s="28" t="n"/>
-      <c r="J100" s="28" t="inlineStr">
+      <c r="I100" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J100" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K100" s="29" t="inlineStr">
+      <c r="K100" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="28" t="n">
+      <c r="B101" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="C101" s="29" t="inlineStr">
+      <c r="C101" s="32" t="inlineStr">
         <is>
           <t>District 99</t>
         </is>
       </c>
-      <c r="D101" s="30" t="n">
+      <c r="D101" s="33" t="n">
         <v>172</v>
       </c>
-      <c r="E101" s="28" t="inlineStr">
+      <c r="E101" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F101" s="31" t="n"/>
-      <c r="G101" s="32" t="inlineStr">
+      <c r="F101" s="34" t="n"/>
+      <c r="G101" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H101" s="29" t="inlineStr">
+      <c r="H101" s="32" t="inlineStr">
         <is>
           <t>Thompson Thrift</t>
         </is>
       </c>
-      <c r="I101" s="28" t="n"/>
-      <c r="J101" s="28" t="inlineStr">
+      <c r="I101" s="36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J101" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K101" s="29" t="inlineStr">
+      <c r="K101" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="28" t="n">
+      <c r="B102" s="31" t="n">
         <v>91</v>
       </c>
-      <c r="C102" s="29" t="inlineStr">
+      <c r="C102" s="32" t="inlineStr">
         <is>
           <t>McDowell Villas</t>
         </is>
       </c>
-      <c r="D102" s="30" t="n">
+      <c r="D102" s="33" t="n">
         <v>164</v>
       </c>
-      <c r="E102" s="28" t="inlineStr">
+      <c r="E102" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F102" s="31" t="n"/>
-      <c r="G102" s="32" t="inlineStr">
+      <c r="F102" s="34" t="n"/>
+      <c r="G102" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H102" s="29" t="inlineStr">
+      <c r="H102" s="32" t="inlineStr">
         <is>
           <t>Trilogy Investment Company</t>
         </is>
       </c>
-      <c r="I102" s="28" t="n"/>
-      <c r="J102" s="28" t="inlineStr">
+      <c r="I102" s="36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J102" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K102" s="29" t="inlineStr">
+      <c r="K102" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="28" t="n">
+      <c r="B103" s="31" t="n">
         <v>92</v>
       </c>
-      <c r="C103" s="29" t="inlineStr">
+      <c r="C103" s="32" t="inlineStr">
         <is>
           <t>Avondale</t>
         </is>
       </c>
-      <c r="D103" s="30" t="n">
+      <c r="D103" s="33" t="n">
         <v>156</v>
       </c>
-      <c r="E103" s="28" t="inlineStr">
+      <c r="E103" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F103" s="31" t="n"/>
-      <c r="G103" s="32" t="inlineStr">
+      <c r="F103" s="34" t="n"/>
+      <c r="G103" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H103" s="29" t="inlineStr">
+      <c r="H103" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I103" s="28" t="n"/>
-      <c r="J103" s="28" t="inlineStr">
+      <c r="I103" s="36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J103" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K103" s="29" t="inlineStr">
+      <c r="K103" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="28" t="n">
+      <c r="B104" s="31" t="n">
         <v>93</v>
       </c>
-      <c r="C104" s="29" t="inlineStr">
+      <c r="C104" s="32" t="inlineStr">
         <is>
           <t>Porter Kyle Development</t>
         </is>
       </c>
-      <c r="D104" s="30" t="n">
+      <c r="D104" s="33" t="n">
         <v>135</v>
       </c>
-      <c r="E104" s="28" t="inlineStr">
+      <c r="E104" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F104" s="31" t="n"/>
-      <c r="G104" s="32" t="inlineStr">
+      <c r="F104" s="34" t="n"/>
+      <c r="G104" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H104" s="29" t="inlineStr">
+      <c r="H104" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I104" s="28" t="n"/>
-      <c r="J104" s="28" t="inlineStr">
+      <c r="I104" s="36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J104" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K104" s="29" t="inlineStr">
+      <c r="K104" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="28" t="n">
+      <c r="B105" s="31" t="n">
         <v>94</v>
       </c>
-      <c r="C105" s="29" t="inlineStr">
+      <c r="C105" s="32" t="inlineStr">
         <is>
           <t>Zenn @ Sierra Verde</t>
         </is>
       </c>
-      <c r="D105" s="30" t="n">
+      <c r="D105" s="33" t="n">
         <v>66</v>
       </c>
-      <c r="E105" s="28" t="inlineStr">
+      <c r="E105" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F105" s="31" t="n"/>
-      <c r="G105" s="32" t="inlineStr">
+      <c r="F105" s="34" t="n"/>
+      <c r="G105" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H105" s="29" t="inlineStr">
+      <c r="H105" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I105" s="28" t="n"/>
-      <c r="J105" s="28" t="inlineStr">
+      <c r="I105" s="36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J105" s="31" t="inlineStr">
         <is>
           <t>Townhome</t>
         </is>
       </c>
-      <c r="K105" s="29" t="inlineStr">
+      <c r="K105" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="28" t="n">
+      <c r="B106" s="31" t="n">
         <v>95</v>
       </c>
-      <c r="C106" s="29" t="inlineStr">
+      <c r="C106" s="32" t="inlineStr">
         <is>
           <t>The BLVD Residential District</t>
         </is>
       </c>
-      <c r="D106" s="30" t="n"/>
-      <c r="E106" s="28" t="inlineStr">
+      <c r="D106" s="33" t="n"/>
+      <c r="E106" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F106" s="31" t="n"/>
-      <c r="G106" s="32" t="inlineStr">
+      <c r="F106" s="34" t="n"/>
+      <c r="G106" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H106" s="29" t="inlineStr">
+      <c r="H106" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I106" s="28" t="n"/>
-      <c r="J106" s="28" t="inlineStr">
+      <c r="I106" s="36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J106" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K106" s="29" t="inlineStr">
+      <c r="K106" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="28" t="n">
+      <c r="B107" s="31" t="n">
         <v>96</v>
       </c>
-      <c r="C107" s="29" t="inlineStr">
+      <c r="C107" s="32" t="inlineStr">
         <is>
           <t>The BLVD Park Avenue District</t>
         </is>
       </c>
-      <c r="D107" s="30" t="n"/>
-      <c r="E107" s="28" t="inlineStr">
+      <c r="D107" s="33" t="n"/>
+      <c r="E107" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F107" s="31" t="n"/>
-      <c r="G107" s="32" t="inlineStr">
+      <c r="F107" s="34" t="n"/>
+      <c r="G107" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H107" s="29" t="inlineStr">
+      <c r="H107" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I107" s="28" t="n"/>
-      <c r="J107" s="28" t="inlineStr">
+      <c r="I107" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J107" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K107" s="29" t="inlineStr">
+      <c r="K107" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="28" t="n">
+      <c r="B108" s="31" t="n">
         <v>97</v>
       </c>
-      <c r="C108" s="29" t="inlineStr">
+      <c r="C108" s="32" t="inlineStr">
         <is>
           <t>Globe Land Investors Development</t>
         </is>
       </c>
-      <c r="D108" s="30" t="n"/>
-      <c r="E108" s="28" t="inlineStr">
+      <c r="D108" s="33" t="n"/>
+      <c r="E108" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F108" s="31" t="n"/>
-      <c r="G108" s="32" t="inlineStr">
+      <c r="F108" s="34" t="n"/>
+      <c r="G108" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H108" s="29" t="inlineStr">
+      <c r="H108" s="32" t="inlineStr">
         <is>
           <t>Globe Corporation</t>
         </is>
       </c>
-      <c r="I108" s="28" t="n"/>
-      <c r="J108" s="28" t="inlineStr">
+      <c r="I108" s="36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J108" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K108" s="29" t="inlineStr">
+      <c r="K108" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="28" t="n">
+      <c r="B109" s="31" t="n">
         <v>98</v>
       </c>
-      <c r="C109" s="29" t="inlineStr">
+      <c r="C109" s="32" t="inlineStr">
         <is>
           <t>Ball Park</t>
         </is>
       </c>
-      <c r="D109" s="30" t="n"/>
-      <c r="E109" s="28" t="inlineStr">
+      <c r="D109" s="33" t="n"/>
+      <c r="E109" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F109" s="31" t="n"/>
-      <c r="G109" s="32" t="inlineStr">
+      <c r="F109" s="34" t="n"/>
+      <c r="G109" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H109" s="29" t="inlineStr">
+      <c r="H109" s="32" t="inlineStr">
         <is>
           <t>VT LandGroup</t>
         </is>
       </c>
-      <c r="I109" s="28" t="n"/>
-      <c r="J109" s="28" t="inlineStr">
+      <c r="I109" s="36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J109" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K109" s="29" t="inlineStr">
+      <c r="K109" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="28" t="n">
+      <c r="B110" s="31" t="n">
         <v>99</v>
       </c>
-      <c r="C110" s="29" t="inlineStr">
+      <c r="C110" s="32" t="inlineStr">
         <is>
           <t>Vision 2 Parcel A</t>
         </is>
       </c>
-      <c r="D110" s="30" t="n"/>
-      <c r="E110" s="28" t="inlineStr">
+      <c r="D110" s="33" t="n"/>
+      <c r="E110" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F110" s="31" t="n"/>
-      <c r="G110" s="32" t="inlineStr">
+      <c r="F110" s="34" t="n"/>
+      <c r="G110" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H110" s="29" t="inlineStr">
+      <c r="H110" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I110" s="28" t="n"/>
-      <c r="J110" s="28" t="inlineStr">
+      <c r="I110" s="36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J110" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K110" s="29" t="inlineStr">
+      <c r="K110" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="28" t="n">
+      <c r="B111" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="C111" s="29" t="inlineStr">
+      <c r="C111" s="32" t="inlineStr">
         <is>
           <t>Firststreet Verde</t>
         </is>
       </c>
-      <c r="D111" s="30" t="n"/>
-      <c r="E111" s="28" t="inlineStr">
+      <c r="D111" s="33" t="n"/>
+      <c r="E111" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F111" s="31" t="n"/>
-      <c r="G111" s="32" t="inlineStr">
+      <c r="F111" s="34" t="n"/>
+      <c r="G111" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H111" s="29" t="inlineStr">
+      <c r="H111" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I111" s="28" t="n"/>
-      <c r="J111" s="28" t="inlineStr">
+      <c r="I111" s="36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J111" s="31" t="inlineStr">
         <is>
           <t>Single Family</t>
         </is>
       </c>
-      <c r="K111" s="29" t="inlineStr">
+      <c r="K111" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="28" t="n">
+      <c r="B112" s="31" t="n">
         <v>101</v>
       </c>
-      <c r="C112" s="29" t="inlineStr">
+      <c r="C112" s="32" t="inlineStr">
         <is>
           <t>Goodyear Civic Square at Estrella Falls</t>
         </is>
       </c>
-      <c r="D112" s="30" t="n"/>
-      <c r="E112" s="28" t="inlineStr">
+      <c r="D112" s="33" t="n"/>
+      <c r="E112" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F112" s="31" t="n"/>
-      <c r="G112" s="32" t="inlineStr">
+      <c r="F112" s="34" t="n"/>
+      <c r="G112" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H112" s="29" t="inlineStr">
+      <c r="H112" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I112" s="28" t="n"/>
-      <c r="J112" s="28" t="inlineStr">
+      <c r="I112" s="36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J112" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K112" s="29" t="inlineStr">
+      <c r="K112" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="28" t="n">
+      <c r="B113" s="31" t="n">
         <v>102</v>
       </c>
-      <c r="C113" s="29" t="inlineStr">
+      <c r="C113" s="32" t="inlineStr">
         <is>
           <t>I-10 Innovation Center II</t>
         </is>
       </c>
-      <c r="D113" s="30" t="n"/>
-      <c r="E113" s="28" t="inlineStr">
+      <c r="D113" s="33" t="n"/>
+      <c r="E113" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F113" s="31" t="n"/>
-      <c r="G113" s="32" t="inlineStr">
+      <c r="F113" s="34" t="n"/>
+      <c r="G113" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H113" s="29" t="inlineStr">
+      <c r="H113" s="32" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I113" s="28" t="n"/>
-      <c r="J113" s="28" t="inlineStr">
+      <c r="I113" s="36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J113" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K113" s="29" t="inlineStr">
+      <c r="K113" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="28" t="n">
+      <c r="B114" s="31" t="n">
         <v>103</v>
       </c>
-      <c r="C114" s="29" t="inlineStr">
+      <c r="C114" s="32" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel D</t>
         </is>
       </c>
-      <c r="D114" s="30" t="n"/>
-      <c r="E114" s="28" t="inlineStr">
+      <c r="D114" s="33" t="n"/>
+      <c r="E114" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F114" s="31" t="n"/>
-      <c r="G114" s="32" t="inlineStr">
+      <c r="F114" s="34" t="n"/>
+      <c r="G114" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H114" s="29" t="inlineStr">
+      <c r="H114" s="32" t="inlineStr">
         <is>
           <t>Privately Owned</t>
         </is>
       </c>
-      <c r="I114" s="28" t="n"/>
-      <c r="J114" s="28" t="inlineStr">
+      <c r="I114" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K114" s="29" t="inlineStr">
+      <c r="K114" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="28" t="n">
+      <c r="B115" s="31" t="n">
         <v>104</v>
       </c>
-      <c r="C115" s="29" t="inlineStr">
+      <c r="C115" s="32" t="inlineStr">
         <is>
           <t>SimonMed Development II</t>
         </is>
       </c>
-      <c r="D115" s="30" t="n"/>
-      <c r="E115" s="28" t="inlineStr">
+      <c r="D115" s="33" t="n"/>
+      <c r="E115" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F115" s="31" t="n"/>
-      <c r="G115" s="32" t="inlineStr">
+      <c r="F115" s="34" t="n"/>
+      <c r="G115" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H115" s="29" t="inlineStr">
+      <c r="H115" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I115" s="28" t="n"/>
-      <c r="J115" s="28" t="inlineStr">
+      <c r="I115" s="36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J115" s="31" t="inlineStr">
         <is>
           <t>Mid-Rise</t>
         </is>
       </c>
-      <c r="K115" s="29" t="inlineStr">
+      <c r="K115" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="28" t="n">
+      <c r="B116" s="31" t="n">
         <v>105</v>
       </c>
-      <c r="C116" s="29" t="inlineStr">
+      <c r="C116" s="32" t="inlineStr">
         <is>
           <t>182 South 95th Avenue</t>
         </is>
       </c>
-      <c r="D116" s="30" t="n"/>
-      <c r="E116" s="28" t="inlineStr">
+      <c r="D116" s="33" t="n"/>
+      <c r="E116" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F116" s="31" t="n"/>
-      <c r="G116" s="32" t="inlineStr">
+      <c r="F116" s="34" t="n"/>
+      <c r="G116" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H116" s="29" t="inlineStr">
+      <c r="H116" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I116" s="28" t="n"/>
-      <c r="J116" s="28" t="inlineStr">
+      <c r="I116" s="36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J116" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K116" s="29" t="inlineStr">
+      <c r="K116" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="28" t="n">
+      <c r="B117" s="31" t="n">
         <v>106</v>
       </c>
-      <c r="C117" s="29" t="inlineStr">
+      <c r="C117" s="32" t="inlineStr">
         <is>
           <t>Envision Encore</t>
         </is>
       </c>
-      <c r="D117" s="30" t="n"/>
-      <c r="E117" s="28" t="inlineStr">
+      <c r="D117" s="33" t="n"/>
+      <c r="E117" s="31" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="F117" s="31" t="n"/>
-      <c r="G117" s="32" t="inlineStr">
+      <c r="F117" s="34" t="n"/>
+      <c r="G117" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H117" s="29" t="inlineStr">
+      <c r="H117" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I117" s="28" t="n"/>
-      <c r="J117" s="28" t="inlineStr">
+      <c r="I117" s="36" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J117" s="31" t="inlineStr">
         <is>
           <t>Garden</t>
         </is>
       </c>
-      <c r="K117" s="29" t="inlineStr">
+      <c r="K117" s="32" t="inlineStr">
         <is>
           <t>RealPage pipeline (not yet in CoStar)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="33" t="inlineStr">
-        <is>
-          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) to be filled manually; lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
+      <c r="B120" s="37" t="inlineStr">
+        <is>
+          <t>* 5-Mile radius. Rent ($) = market asking. Proximity (mi) = straight-line distance from the subject (geocoded); lease-up rent/occupancy to be verified w/ HelloData. See the 'Supply &amp; Absorption' tab for the forward supply / absorption / overall-occupancy forecast.</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5318,7 @@
       </c>
     </row>
     <row r="3" ht="14.4" customHeight="1">
-      <c r="R3" s="34" t="inlineStr">
+      <c r="R3" s="38" t="inlineStr">
         <is>
           <t>UNDER CONSTRUCTION (linked from Competitive Analysis)</t>
         </is>
@@ -5104,52 +5329,52 @@
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1">
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>As-of Quarter</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="R4" s="37" t="inlineStr">
+      <c r="R4" s="41" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="S4" s="37" t="inlineStr">
+      <c r="S4" s="41" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="T4" s="37" t="inlineStr">
+      <c r="T4" s="41" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14.4" customHeight="1">
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Close Quarter (Y1 start)</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="R5" s="39">
+      <c r="R5" s="43">
         <f>'Competitive Analysis'!C60</f>
         <v/>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="44">
         <f>'Competitive Analysis'!D60</f>
         <v/>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="45">
         <f>'Competitive Analysis'!E60</f>
         <v/>
       </c>
@@ -5163,23 +5388,23 @@
       </c>
     </row>
     <row r="6" ht="14.4" customHeight="1">
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Stabilization Target</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="46" t="n">
         <v>0.95</v>
       </c>
-      <c r="R6" s="39">
+      <c r="R6" s="43">
         <f>'Competitive Analysis'!C61</f>
         <v/>
       </c>
-      <c r="S6" s="40">
+      <c r="S6" s="44">
         <f>'Competitive Analysis'!D61</f>
         <v/>
       </c>
-      <c r="T6" s="41">
+      <c r="T6" s="45">
         <f>'Competitive Analysis'!E61</f>
         <v/>
       </c>
@@ -5193,25 +5418,25 @@
       </c>
     </row>
     <row r="7" ht="14.4" customHeight="1">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>Demand Scenario</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="R7" s="39">
+      <c r="R7" s="43">
         <f>'Competitive Analysis'!C69</f>
         <v/>
       </c>
-      <c r="S7" s="40">
+      <c r="S7" s="44">
         <f>'Competitive Analysis'!D69</f>
         <v/>
       </c>
-      <c r="T7" s="41">
+      <c r="T7" s="45">
         <f>'Competitive Analysis'!E69</f>
         <v/>
       </c>
@@ -5225,23 +5450,23 @@
       </c>
     </row>
     <row r="8" ht="14.4" customHeight="1">
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Bear Annual Absorption</t>
         </is>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="47" t="n">
         <v>1250</v>
       </c>
-      <c r="R8" s="39">
+      <c r="R8" s="43">
         <f>'Competitive Analysis'!C63</f>
         <v/>
       </c>
-      <c r="S8" s="40">
+      <c r="S8" s="44">
         <f>'Competitive Analysis'!D63</f>
         <v/>
       </c>
-      <c r="T8" s="41">
+      <c r="T8" s="45">
         <f>'Competitive Analysis'!E63</f>
         <v/>
       </c>
@@ -5255,23 +5480,23 @@
       </c>
     </row>
     <row r="9" ht="14.4" customHeight="1">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Base Annual Absorption</t>
         </is>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="47" t="n">
         <v>2525</v>
       </c>
-      <c r="R9" s="39">
+      <c r="R9" s="43">
         <f>'Competitive Analysis'!C67</f>
         <v/>
       </c>
-      <c r="S9" s="40">
+      <c r="S9" s="44">
         <f>'Competitive Analysis'!D67</f>
         <v/>
       </c>
-      <c r="T9" s="41">
+      <c r="T9" s="45">
         <f>'Competitive Analysis'!E67</f>
         <v/>
       </c>
@@ -5285,23 +5510,23 @@
       </c>
     </row>
     <row r="10" ht="14.4" customHeight="1">
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Bull Annual Absorption</t>
         </is>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="47" t="n">
         <v>3800</v>
       </c>
-      <c r="R10" s="39">
+      <c r="R10" s="43">
         <f>'Competitive Analysis'!C68</f>
         <v/>
       </c>
-      <c r="S10" s="40">
+      <c r="S10" s="44">
         <f>'Competitive Analysis'!D68</f>
         <v/>
       </c>
-      <c r="T10" s="41">
+      <c r="T10" s="45">
         <f>'Competitive Analysis'!E68</f>
         <v/>
       </c>
@@ -5315,24 +5540,24 @@
       </c>
     </row>
     <row r="11" ht="14.4" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>Selected Annual Demand</t>
         </is>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="48">
         <f>IF($C$7="Bear",$C$8,IF($C$7="Bull",$C$10,$C$9))</f>
         <v/>
       </c>
-      <c r="R11" s="39">
+      <c r="R11" s="43">
         <f>'Competitive Analysis'!C64</f>
         <v/>
       </c>
-      <c r="S11" s="40">
+      <c r="S11" s="44">
         <f>'Competitive Analysis'!D64</f>
         <v/>
       </c>
-      <c r="T11" s="41">
+      <c r="T11" s="45">
         <f>'Competitive Analysis'!E64</f>
         <v/>
       </c>
@@ -5346,15 +5571,15 @@
       </c>
     </row>
     <row r="12" ht="14.4" customHeight="1">
-      <c r="R12" s="39">
+      <c r="R12" s="43">
         <f>'Competitive Analysis'!C70</f>
         <v/>
       </c>
-      <c r="S12" s="40">
+      <c r="S12" s="44">
         <f>'Competitive Analysis'!D70</f>
         <v/>
       </c>
-      <c r="T12" s="41">
+      <c r="T12" s="45">
         <f>'Competitive Analysis'!E70</f>
         <v/>
       </c>
@@ -5368,15 +5593,15 @@
       </c>
     </row>
     <row r="13" ht="14.4" customHeight="1">
-      <c r="R13" s="39">
+      <c r="R13" s="43">
         <f>'Competitive Analysis'!C62</f>
         <v/>
       </c>
-      <c r="S13" s="40">
+      <c r="S13" s="44">
         <f>'Competitive Analysis'!D62</f>
         <v/>
       </c>
-      <c r="T13" s="41">
+      <c r="T13" s="45">
         <f>'Competitive Analysis'!E62</f>
         <v/>
       </c>
@@ -5390,15 +5615,15 @@
       </c>
     </row>
     <row r="14" ht="14.4" customHeight="1">
-      <c r="R14" s="39">
+      <c r="R14" s="43">
         <f>'Competitive Analysis'!C65</f>
         <v/>
       </c>
-      <c r="S14" s="40">
+      <c r="S14" s="44">
         <f>'Competitive Analysis'!D65</f>
         <v/>
       </c>
-      <c r="T14" s="41">
+      <c r="T14" s="45">
         <f>'Competitive Analysis'!E65</f>
         <v/>
       </c>
@@ -5412,15 +5637,15 @@
       </c>
     </row>
     <row r="15" ht="14.4" customHeight="1">
-      <c r="R15" s="39">
+      <c r="R15" s="43">
         <f>'Competitive Analysis'!C66</f>
         <v/>
       </c>
-      <c r="S15" s="40">
+      <c r="S15" s="44">
         <f>'Competitive Analysis'!D66</f>
         <v/>
       </c>
-      <c r="T15" s="41">
+      <c r="T15" s="45">
         <f>'Competitive Analysis'!E66</f>
         <v/>
       </c>
@@ -5435,7 +5660,7 @@
     </row>
     <row r="16" ht="14.4" customHeight="1"/>
     <row r="17" ht="14.4" customHeight="1">
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>5-MILE MARKET</t>
         </is>
@@ -5475,190 +5700,190 @@
           <t>Y0</t>
         </is>
       </c>
-      <c r="J17" s="45" t="inlineStr">
+      <c r="J17" s="49" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K17" s="45" t="inlineStr">
+      <c r="K17" s="49" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L17" s="45" t="inlineStr">
+      <c r="L17" s="49" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M17" s="45" t="inlineStr">
+      <c r="M17" s="49" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N17" s="45" t="inlineStr">
+      <c r="N17" s="49" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O17" s="45" t="inlineStr">
+      <c r="O17" s="49" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
-      <c r="R17" s="34" t="inlineStr">
+      <c r="R17" s="38" t="inlineStr">
         <is>
           <t>PROPOSED PIPELINE (scenario toggle)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14.4" customHeight="1">
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="50" t="inlineStr">
         <is>
           <t>Q3'19-Q2'20</t>
         </is>
       </c>
-      <c r="D18" s="46" t="inlineStr">
+      <c r="D18" s="50" t="inlineStr">
         <is>
           <t>Q3'20-Q2'21</t>
         </is>
       </c>
-      <c r="E18" s="46" t="inlineStr">
+      <c r="E18" s="50" t="inlineStr">
         <is>
           <t>Q3'21-Q2'22</t>
         </is>
       </c>
-      <c r="F18" s="46" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>Q3'22-Q2'23</t>
         </is>
       </c>
-      <c r="G18" s="46" t="inlineStr">
+      <c r="G18" s="50" t="inlineStr">
         <is>
           <t>Q3'23-Q2'24</t>
         </is>
       </c>
-      <c r="H18" s="46" t="inlineStr">
+      <c r="H18" s="50" t="inlineStr">
         <is>
           <t>Q3'24-Q2'25</t>
         </is>
       </c>
-      <c r="I18" s="46" t="inlineStr">
+      <c r="I18" s="50" t="inlineStr">
         <is>
           <t>Q3'25-Q2'26</t>
         </is>
       </c>
-      <c r="J18" s="46" t="inlineStr">
+      <c r="J18" s="50" t="inlineStr">
         <is>
           <t>Hold Yr 1</t>
         </is>
       </c>
-      <c r="K18" s="46" t="inlineStr">
+      <c r="K18" s="50" t="inlineStr">
         <is>
           <t>Hold Yr 2</t>
         </is>
       </c>
-      <c r="L18" s="46" t="inlineStr">
+      <c r="L18" s="50" t="inlineStr">
         <is>
           <t>Hold Yr 3</t>
         </is>
       </c>
-      <c r="M18" s="46" t="inlineStr">
+      <c r="M18" s="50" t="inlineStr">
         <is>
           <t>Hold Yr 4</t>
         </is>
       </c>
-      <c r="N18" s="46" t="inlineStr">
+      <c r="N18" s="50" t="inlineStr">
         <is>
           <t>Hold Yr 5</t>
         </is>
       </c>
-      <c r="O18" s="46" t="inlineStr">
+      <c r="O18" s="50" t="inlineStr">
         <is>
           <t>Hold Yr 6</t>
         </is>
       </c>
-      <c r="R18" s="37" t="inlineStr">
+      <c r="R18" s="41" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="S18" s="37" t="inlineStr">
+      <c r="S18" s="41" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="T18" s="37" t="inlineStr">
+      <c r="T18" s="41" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="U18" s="37" t="inlineStr">
+      <c r="U18" s="41" t="inlineStr">
         <is>
           <t>Built In</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14.4" customHeight="1">
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>NEW SUPPLY (5-mi)</t>
         </is>
       </c>
-      <c r="C19" s="47" t="n">
+      <c r="C19" s="51" t="n">
         <v>1133</v>
       </c>
-      <c r="D19" s="47" t="n">
+      <c r="D19" s="51" t="n">
         <v>1860</v>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="51" t="n">
         <v>1336</v>
       </c>
-      <c r="F19" s="47" t="n">
+      <c r="F19" s="51" t="n">
         <v>2280</v>
       </c>
-      <c r="G19" s="47" t="n">
+      <c r="G19" s="51" t="n">
         <v>2823</v>
       </c>
-      <c r="H19" s="47" t="n">
+      <c r="H19" s="51" t="n">
         <v>4043</v>
       </c>
-      <c r="I19" s="47" t="n">
+      <c r="I19" s="51" t="n">
         <v>1860</v>
       </c>
-      <c r="J19" s="48">
+      <c r="J19" s="52">
         <f>SUMIFS($S$5:$S$15,$W$5:$W$15,1)+SUMIFS($S$19:$S$63,$W$19:$W$63,1,$X$19:$X$63,1)</f>
         <v/>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="52">
         <f>SUMIFS($S$5:$S$15,$W$5:$W$15,2)+SUMIFS($S$19:$S$63,$W$19:$W$63,2,$X$19:$X$63,1)</f>
         <v/>
       </c>
-      <c r="L19" s="48">
+      <c r="L19" s="52">
         <f>SUMIFS($S$5:$S$15,$W$5:$W$15,3)+SUMIFS($S$19:$S$63,$W$19:$W$63,3,$X$19:$X$63,1)</f>
         <v/>
       </c>
-      <c r="M19" s="48">
+      <c r="M19" s="52">
         <f>SUMIFS($S$5:$S$15,$W$5:$W$15,4)+SUMIFS($S$19:$S$63,$W$19:$W$63,4,$X$19:$X$63,1)</f>
         <v/>
       </c>
-      <c r="N19" s="48">
+      <c r="N19" s="52">
         <f>SUMIFS($S$5:$S$15,$W$5:$W$15,5)+SUMIFS($S$19:$S$63,$W$19:$W$63,5,$X$19:$X$63,1)</f>
         <v/>
       </c>
-      <c r="O19" s="48">
+      <c r="O19" s="52">
         <f>SUMIFS($S$5:$S$15,$W$5:$W$15,6)+SUMIFS($S$19:$S$63,$W$19:$W$63,6,$X$19:$X$63,1)</f>
         <v/>
       </c>
-      <c r="R19" s="39" t="inlineStr">
+      <c r="R19" s="43" t="inlineStr">
         <is>
           <t>Sheely Center Future Phase</t>
         </is>
       </c>
-      <c r="S19" s="40" t="n">
+      <c r="S19" s="44" t="n">
         <v>697</v>
       </c>
-      <c r="T19" s="49" t="inlineStr"/>
-      <c r="U19" s="49" t="inlineStr">
+      <c r="T19" s="53" t="inlineStr"/>
+      <c r="U19" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5677,66 +5902,66 @@
       </c>
     </row>
     <row r="20" ht="14.4" customHeight="1">
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>ABSORPTION (5-mi)</t>
         </is>
       </c>
-      <c r="C20" s="47" t="n">
+      <c r="C20" s="51" t="n">
         <v>719</v>
       </c>
-      <c r="D20" s="47" t="n">
+      <c r="D20" s="51" t="n">
         <v>1876</v>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="51" t="n">
         <v>1210</v>
       </c>
-      <c r="F20" s="47" t="n">
+      <c r="F20" s="51" t="n">
         <v>685</v>
       </c>
-      <c r="G20" s="47" t="n">
+      <c r="G20" s="51" t="n">
         <v>2514</v>
       </c>
-      <c r="H20" s="47" t="n">
+      <c r="H20" s="51" t="n">
         <v>2655</v>
       </c>
-      <c r="I20" s="47" t="n">
+      <c r="I20" s="51" t="n">
         <v>2369</v>
       </c>
-      <c r="J20" s="48">
+      <c r="J20" s="52">
         <f>J31-I31</f>
         <v/>
       </c>
-      <c r="K20" s="48">
+      <c r="K20" s="52">
         <f>K31-J31</f>
         <v/>
       </c>
-      <c r="L20" s="48">
+      <c r="L20" s="52">
         <f>L31-K31</f>
         <v/>
       </c>
-      <c r="M20" s="48">
+      <c r="M20" s="52">
         <f>M31-L31</f>
         <v/>
       </c>
-      <c r="N20" s="48">
+      <c r="N20" s="52">
         <f>N31-M31</f>
         <v/>
       </c>
-      <c r="O20" s="48">
+      <c r="O20" s="52">
         <f>O31-N31</f>
         <v/>
       </c>
-      <c r="R20" s="39" t="inlineStr">
+      <c r="R20" s="43" t="inlineStr">
         <is>
           <t>Urban 95 Parcel C</t>
         </is>
       </c>
-      <c r="S20" s="40" t="n">
+      <c r="S20" s="44" t="n">
         <v>500</v>
       </c>
-      <c r="T20" s="49" t="inlineStr"/>
-      <c r="U20" s="49" t="inlineStr">
+      <c r="T20" s="53" t="inlineStr"/>
+      <c r="U20" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5755,66 +5980,66 @@
       </c>
     </row>
     <row r="21" ht="14.4" customHeight="1">
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>OCCUPANCY (5-mi)</t>
         </is>
       </c>
-      <c r="C21" s="50" t="n">
+      <c r="C21" s="54" t="n">
         <v>0.909</v>
       </c>
-      <c r="D21" s="50" t="n">
+      <c r="D21" s="54" t="n">
         <v>0.922</v>
       </c>
-      <c r="E21" s="50" t="n">
+      <c r="E21" s="54" t="n">
         <v>0.921</v>
       </c>
-      <c r="F21" s="50" t="n">
+      <c r="F21" s="54" t="n">
         <v>0.842</v>
       </c>
-      <c r="G21" s="50" t="n">
+      <c r="G21" s="54" t="n">
         <v>0.848</v>
       </c>
-      <c r="H21" s="50" t="n">
+      <c r="H21" s="54" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="I21" s="50" t="n">
+      <c r="I21" s="54" t="n">
         <v>0.849</v>
       </c>
-      <c r="J21" s="51">
+      <c r="J21" s="55">
         <f>IFERROR(J31/J30,0)</f>
         <v/>
       </c>
-      <c r="K21" s="51">
+      <c r="K21" s="55">
         <f>IFERROR(K31/K30,0)</f>
         <v/>
       </c>
-      <c r="L21" s="51">
+      <c r="L21" s="55">
         <f>IFERROR(L31/L30,0)</f>
         <v/>
       </c>
-      <c r="M21" s="51">
+      <c r="M21" s="55">
         <f>IFERROR(M31/M30,0)</f>
         <v/>
       </c>
-      <c r="N21" s="51">
+      <c r="N21" s="55">
         <f>IFERROR(N31/N30,0)</f>
         <v/>
       </c>
-      <c r="O21" s="51">
+      <c r="O21" s="55">
         <f>IFERROR(O31/O30,0)</f>
         <v/>
       </c>
-      <c r="R21" s="39" t="inlineStr">
+      <c r="R21" s="43" t="inlineStr">
         <is>
           <t>Urban 95 Parcel B</t>
         </is>
       </c>
-      <c r="S21" s="40" t="n">
+      <c r="S21" s="44" t="n">
         <v>478</v>
       </c>
-      <c r="T21" s="49" t="inlineStr"/>
-      <c r="U21" s="49" t="inlineStr">
+      <c r="T21" s="53" t="inlineStr"/>
+      <c r="U21" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5833,21 +6058,21 @@
       </c>
     </row>
     <row r="22" ht="14.4" customHeight="1">
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>SUBJECT (Bella Mirage)</t>
         </is>
       </c>
-      <c r="R22" s="39" t="inlineStr">
+      <c r="R22" s="43" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel B</t>
         </is>
       </c>
-      <c r="S22" s="40" t="n">
+      <c r="S22" s="44" t="n">
         <v>410</v>
       </c>
-      <c r="T22" s="49" t="inlineStr"/>
-      <c r="U22" s="49" t="inlineStr">
+      <c r="T22" s="53" t="inlineStr"/>
+      <c r="U22" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5866,48 +6091,48 @@
       </c>
     </row>
     <row r="23" ht="14.4" customHeight="1">
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Market Rent  (CoStar→HD)</t>
         </is>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="56" t="n">
         <v>1088</v>
       </c>
-      <c r="D23" s="52" t="n">
+      <c r="D23" s="56" t="n">
         <v>1437</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="56" t="n">
         <v>1730</v>
       </c>
-      <c r="F23" s="52" t="n">
+      <c r="F23" s="56" t="n">
         <v>1572</v>
       </c>
-      <c r="G23" s="52" t="n">
+      <c r="G23" s="56" t="n">
         <v>1497</v>
       </c>
-      <c r="H23" s="52" t="n">
+      <c r="H23" s="56" t="n">
         <v>1444</v>
       </c>
-      <c r="I23" s="52" t="n">
+      <c r="I23" s="56" t="n">
         <v>1332</v>
       </c>
-      <c r="J23" s="53" t="n"/>
-      <c r="K23" s="53" t="n"/>
-      <c r="L23" s="53" t="n"/>
-      <c r="M23" s="53" t="n"/>
-      <c r="N23" s="53" t="n"/>
-      <c r="O23" s="53" t="n"/>
-      <c r="R23" s="39" t="inlineStr">
+      <c r="J23" s="57" t="n"/>
+      <c r="K23" s="57" t="n"/>
+      <c r="L23" s="57" t="n"/>
+      <c r="M23" s="57" t="n"/>
+      <c r="N23" s="57" t="n"/>
+      <c r="O23" s="57" t="n"/>
+      <c r="R23" s="43" t="inlineStr">
         <is>
           <t>The District at Westgate</t>
         </is>
       </c>
-      <c r="S23" s="40" t="n">
+      <c r="S23" s="44" t="n">
         <v>384</v>
       </c>
-      <c r="T23" s="49" t="inlineStr"/>
-      <c r="U23" s="49" t="inlineStr">
+      <c r="T23" s="53" t="inlineStr"/>
+      <c r="U23" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5926,52 +6151,52 @@
       </c>
     </row>
     <row r="24" ht="14.4" customHeight="1">
-      <c r="B24" s="54" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">    Market Rent YoY %</t>
         </is>
       </c>
-      <c r="C24" s="55" t="n"/>
-      <c r="D24" s="55">
+      <c r="C24" s="59" t="n"/>
+      <c r="D24" s="59">
         <f>IFERROR(D23/C23-1,"")</f>
         <v/>
       </c>
-      <c r="E24" s="55">
+      <c r="E24" s="59">
         <f>IFERROR(E23/D23-1,"")</f>
         <v/>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="59">
         <f>IFERROR(F23/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="59">
         <f>IFERROR(G23/F23-1,"")</f>
         <v/>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="59">
         <f>IFERROR(H23/G23-1,"")</f>
         <v/>
       </c>
-      <c r="I24" s="55">
+      <c r="I24" s="59">
         <f>IFERROR(I23/H23-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="56" t="n"/>
-      <c r="K24" s="56" t="n"/>
-      <c r="L24" s="56" t="n"/>
-      <c r="M24" s="56" t="n"/>
-      <c r="N24" s="56" t="n"/>
-      <c r="O24" s="56" t="n"/>
-      <c r="R24" s="39" t="inlineStr">
+      <c r="J24" s="60" t="n"/>
+      <c r="K24" s="60" t="n"/>
+      <c r="L24" s="60" t="n"/>
+      <c r="M24" s="60" t="n"/>
+      <c r="N24" s="60" t="n"/>
+      <c r="O24" s="60" t="n"/>
+      <c r="R24" s="43" t="inlineStr">
         <is>
           <t>Picerne at Palm Valley</t>
         </is>
       </c>
-      <c r="S24" s="40" t="n">
+      <c r="S24" s="44" t="n">
         <v>383</v>
       </c>
-      <c r="T24" s="49" t="inlineStr"/>
-      <c r="U24" s="49" t="inlineStr">
+      <c r="T24" s="53" t="inlineStr"/>
+      <c r="U24" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -5990,48 +6215,48 @@
       </c>
     </row>
     <row r="25" ht="14.4" customHeight="1">
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Effective Rent</t>
         </is>
       </c>
-      <c r="C25" s="52" t="n">
+      <c r="C25" s="56" t="n">
         <v>1086</v>
       </c>
-      <c r="D25" s="52" t="n">
+      <c r="D25" s="56" t="n">
         <v>1434</v>
       </c>
-      <c r="E25" s="52" t="n">
+      <c r="E25" s="56" t="n">
         <v>1730</v>
       </c>
-      <c r="F25" s="52" t="n">
+      <c r="F25" s="56" t="n">
         <v>1555</v>
       </c>
-      <c r="G25" s="52" t="n">
+      <c r="G25" s="56" t="n">
         <v>1402</v>
       </c>
-      <c r="H25" s="52" t="n">
+      <c r="H25" s="56" t="n">
         <v>1369</v>
       </c>
-      <c r="I25" s="52" t="n">
+      <c r="I25" s="56" t="n">
         <v>1301</v>
       </c>
-      <c r="J25" s="53" t="n"/>
-      <c r="K25" s="53" t="n"/>
-      <c r="L25" s="53" t="n"/>
-      <c r="M25" s="53" t="n"/>
-      <c r="N25" s="53" t="n"/>
-      <c r="O25" s="53" t="n"/>
-      <c r="R25" s="39" t="inlineStr">
+      <c r="J25" s="57" t="n"/>
+      <c r="K25" s="57" t="n"/>
+      <c r="L25" s="57" t="n"/>
+      <c r="M25" s="57" t="n"/>
+      <c r="N25" s="57" t="n"/>
+      <c r="O25" s="57" t="n"/>
+      <c r="R25" s="43" t="inlineStr">
         <is>
           <t>Liv Avondale</t>
         </is>
       </c>
-      <c r="S25" s="40" t="n">
+      <c r="S25" s="44" t="n">
         <v>333</v>
       </c>
-      <c r="T25" s="49" t="inlineStr"/>
-      <c r="U25" s="49" t="inlineStr">
+      <c r="T25" s="53" t="inlineStr"/>
+      <c r="U25" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6050,52 +6275,52 @@
       </c>
     </row>
     <row r="26" ht="14.4" customHeight="1">
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">    Effective Rent YoY %</t>
         </is>
       </c>
-      <c r="C26" s="55" t="n"/>
-      <c r="D26" s="55">
+      <c r="C26" s="59" t="n"/>
+      <c r="D26" s="59">
         <f>IFERROR(D25/C25-1,"")</f>
         <v/>
       </c>
-      <c r="E26" s="55">
+      <c r="E26" s="59">
         <f>IFERROR(E25/D25-1,"")</f>
         <v/>
       </c>
-      <c r="F26" s="55">
+      <c r="F26" s="59">
         <f>IFERROR(F25/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="59">
         <f>IFERROR(G25/F25-1,"")</f>
         <v/>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="59">
         <f>IFERROR(H25/G25-1,"")</f>
         <v/>
       </c>
-      <c r="I26" s="55">
+      <c r="I26" s="59">
         <f>IFERROR(I25/H25-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="56" t="n"/>
-      <c r="K26" s="56" t="n"/>
-      <c r="L26" s="56" t="n"/>
-      <c r="M26" s="56" t="n"/>
-      <c r="N26" s="56" t="n"/>
-      <c r="O26" s="56" t="n"/>
-      <c r="R26" s="39" t="inlineStr">
+      <c r="J26" s="60" t="n"/>
+      <c r="K26" s="60" t="n"/>
+      <c r="L26" s="60" t="n"/>
+      <c r="M26" s="60" t="n"/>
+      <c r="N26" s="60" t="n"/>
+      <c r="O26" s="60" t="n"/>
+      <c r="R26" s="43" t="inlineStr">
         <is>
           <t>Urban 95 Parcel A</t>
         </is>
       </c>
-      <c r="S26" s="40" t="n">
+      <c r="S26" s="44" t="n">
         <v>324</v>
       </c>
-      <c r="T26" s="49" t="inlineStr"/>
-      <c r="U26" s="49" t="inlineStr">
+      <c r="T26" s="53" t="inlineStr"/>
+      <c r="U26" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6114,52 +6339,52 @@
       </c>
     </row>
     <row r="27" ht="14.4" customHeight="1">
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Occupancy (financials / CoStar)</t>
         </is>
       </c>
-      <c r="C27" s="57" t="n">
+      <c r="C27" s="61" t="n">
         <v>0.9503496503496502</v>
       </c>
-      <c r="D27" s="57" t="n">
+      <c r="D27" s="61" t="n">
         <v>0.957692307692308</v>
       </c>
-      <c r="E27" s="57" t="n">
+      <c r="E27" s="61" t="n">
         <v>0.9458041958041957</v>
       </c>
-      <c r="F27" s="57" t="n">
+      <c r="F27" s="61" t="n">
         <v>0.8788971182681028</v>
       </c>
-      <c r="G27" s="57" t="n">
+      <c r="G27" s="61" t="n">
         <v>0.9173713229249606</v>
       </c>
-      <c r="H27" s="57" t="n">
+      <c r="H27" s="61" t="n">
         <v>0.9334854638634199</v>
       </c>
-      <c r="I27" s="57" t="n">
+      <c r="I27" s="61" t="n">
         <v>0.9206643232607364</v>
       </c>
-      <c r="J27" s="58" t="n"/>
-      <c r="K27" s="58" t="n"/>
-      <c r="L27" s="58" t="n"/>
-      <c r="M27" s="58" t="n"/>
-      <c r="N27" s="58" t="n"/>
-      <c r="O27" s="58" t="n"/>
-      <c r="R27" s="39" t="inlineStr">
+      <c r="J27" s="62" t="n"/>
+      <c r="K27" s="62" t="n"/>
+      <c r="L27" s="62" t="n"/>
+      <c r="M27" s="62" t="n"/>
+      <c r="N27" s="62" t="n"/>
+      <c r="O27" s="62" t="n"/>
+      <c r="R27" s="43" t="inlineStr">
         <is>
           <t>The Waverly</t>
         </is>
       </c>
-      <c r="S27" s="40" t="n">
+      <c r="S27" s="44" t="n">
         <v>323</v>
       </c>
-      <c r="T27" s="49" t="inlineStr">
+      <c r="T27" s="53" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U27" s="49" t="inlineStr">
+      <c r="U27" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6178,55 +6403,55 @@
       </c>
     </row>
     <row r="28" ht="14.4" customHeight="1">
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  Concession %</t>
         </is>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="61">
         <f>IFERROR((C23-C25)/C23,"")</f>
         <v/>
       </c>
-      <c r="D28" s="57">
+      <c r="D28" s="61">
         <f>IFERROR((D23-D25)/D23,"")</f>
         <v/>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="61">
         <f>IFERROR((E23-E25)/E23,"")</f>
         <v/>
       </c>
-      <c r="F28" s="57">
+      <c r="F28" s="61">
         <f>IFERROR((F23-F25)/F23,"")</f>
         <v/>
       </c>
-      <c r="G28" s="57">
+      <c r="G28" s="61">
         <f>IFERROR((G23-G25)/G23,"")</f>
         <v/>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="61">
         <f>IFERROR((H23-H25)/H23,"")</f>
         <v/>
       </c>
-      <c r="I28" s="57">
+      <c r="I28" s="61">
         <f>IFERROR((I23-I25)/I23,"")</f>
         <v/>
       </c>
-      <c r="J28" s="58" t="n"/>
-      <c r="K28" s="58" t="n"/>
-      <c r="L28" s="58" t="n"/>
-      <c r="M28" s="58" t="n"/>
-      <c r="N28" s="58" t="n"/>
-      <c r="O28" s="58" t="n"/>
-      <c r="R28" s="39" t="inlineStr">
+      <c r="J28" s="62" t="n"/>
+      <c r="K28" s="62" t="n"/>
+      <c r="L28" s="62" t="n"/>
+      <c r="M28" s="62" t="n"/>
+      <c r="N28" s="62" t="n"/>
+      <c r="O28" s="62" t="n"/>
+      <c r="R28" s="43" t="inlineStr">
         <is>
           <t>Fuze 623</t>
         </is>
       </c>
-      <c r="S28" s="40" t="n">
+      <c r="S28" s="44" t="n">
         <v>321</v>
       </c>
-      <c r="T28" s="49" t="inlineStr"/>
-      <c r="U28" s="49" t="inlineStr">
+      <c r="T28" s="53" t="inlineStr"/>
+      <c r="U28" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6245,16 +6470,16 @@
       </c>
     </row>
     <row r="29" ht="14.4" customHeight="1">
-      <c r="R29" s="39" t="inlineStr">
+      <c r="R29" s="43" t="inlineStr">
         <is>
           <t>Anton Glendale</t>
         </is>
       </c>
-      <c r="S29" s="40" t="n">
+      <c r="S29" s="44" t="n">
         <v>320</v>
       </c>
-      <c r="T29" s="49" t="inlineStr"/>
-      <c r="U29" s="49" t="inlineStr">
+      <c r="T29" s="53" t="inlineStr"/>
+      <c r="U29" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6273,66 +6498,66 @@
       </c>
     </row>
     <row r="30" hidden="1" ht="14.4" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  inventory</t>
         </is>
       </c>
-      <c r="C30" s="59" t="n">
+      <c r="C30" s="63" t="n">
         <v>12401</v>
       </c>
-      <c r="D30" s="59" t="n">
+      <c r="D30" s="63" t="n">
         <v>14261</v>
       </c>
-      <c r="E30" s="59" t="n">
+      <c r="E30" s="63" t="n">
         <v>15597</v>
       </c>
-      <c r="F30" s="59" t="n">
+      <c r="F30" s="63" t="n">
         <v>17877</v>
       </c>
-      <c r="G30" s="59" t="n">
+      <c r="G30" s="63" t="n">
         <v>20700</v>
       </c>
-      <c r="H30" s="59" t="n">
+      <c r="H30" s="63" t="n">
         <v>24743</v>
       </c>
-      <c r="I30" s="59" t="n">
+      <c r="I30" s="63" t="n">
         <v>26603</v>
       </c>
-      <c r="J30" s="59">
+      <c r="J30" s="63">
         <f>I30+J19</f>
         <v/>
       </c>
-      <c r="K30" s="59">
+      <c r="K30" s="63">
         <f>J30+K19</f>
         <v/>
       </c>
-      <c r="L30" s="59">
+      <c r="L30" s="63">
         <f>K30+L19</f>
         <v/>
       </c>
-      <c r="M30" s="59">
+      <c r="M30" s="63">
         <f>L30+M19</f>
         <v/>
       </c>
-      <c r="N30" s="59">
+      <c r="N30" s="63">
         <f>M30+N19</f>
         <v/>
       </c>
-      <c r="O30" s="59">
+      <c r="O30" s="63">
         <f>N30+O19</f>
         <v/>
       </c>
-      <c r="R30" s="39" t="inlineStr">
+      <c r="R30" s="43" t="inlineStr">
         <is>
           <t>Western Garden II</t>
         </is>
       </c>
-      <c r="S30" s="40" t="n">
+      <c r="S30" s="44" t="n">
         <v>314</v>
       </c>
-      <c r="T30" s="49" t="inlineStr"/>
-      <c r="U30" s="49" t="inlineStr">
+      <c r="T30" s="53" t="inlineStr"/>
+      <c r="U30" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6351,66 +6576,66 @@
       </c>
     </row>
     <row r="31" hidden="1" ht="14.4" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  occupied</t>
         </is>
       </c>
-      <c r="C31" s="59" t="n">
+      <c r="C31" s="63" t="n">
         <v>11277</v>
       </c>
-      <c r="D31" s="59" t="n">
+      <c r="D31" s="63" t="n">
         <v>13152</v>
       </c>
-      <c r="E31" s="59" t="n">
+      <c r="E31" s="63" t="n">
         <v>14362</v>
       </c>
-      <c r="F31" s="59" t="n">
+      <c r="F31" s="63" t="n">
         <v>15047</v>
       </c>
-      <c r="G31" s="59" t="n">
+      <c r="G31" s="63" t="n">
         <v>17560</v>
       </c>
-      <c r="H31" s="59" t="n">
+      <c r="H31" s="63" t="n">
         <v>20215</v>
       </c>
-      <c r="I31" s="59" t="n">
+      <c r="I31" s="63" t="n">
         <v>22585</v>
       </c>
-      <c r="J31" s="59">
+      <c r="J31" s="63">
         <f>MIN($C$6*J30,I31+$C$11)</f>
         <v/>
       </c>
-      <c r="K31" s="59">
+      <c r="K31" s="63">
         <f>MIN($C$6*K30,J31+$C$11)</f>
         <v/>
       </c>
-      <c r="L31" s="59">
+      <c r="L31" s="63">
         <f>MIN($C$6*L30,K31+$C$11)</f>
         <v/>
       </c>
-      <c r="M31" s="59">
+      <c r="M31" s="63">
         <f>MIN($C$6*M30,L31+$C$11)</f>
         <v/>
       </c>
-      <c r="N31" s="59">
+      <c r="N31" s="63">
         <f>MIN($C$6*N30,M31+$C$11)</f>
         <v/>
       </c>
-      <c r="O31" s="59">
+      <c r="O31" s="63">
         <f>MIN($C$6*O30,N31+$C$11)</f>
         <v/>
       </c>
-      <c r="R31" s="39" t="inlineStr">
+      <c r="R31" s="43" t="inlineStr">
         <is>
           <t>Sanctuair at Centerscape</t>
         </is>
       </c>
-      <c r="S31" s="40" t="n">
+      <c r="S31" s="44" t="n">
         <v>303</v>
       </c>
-      <c r="T31" s="49" t="inlineStr"/>
-      <c r="U31" s="49" t="inlineStr">
+      <c r="T31" s="53" t="inlineStr"/>
+      <c r="U31" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6429,20 +6654,20 @@
       </c>
     </row>
     <row r="32" ht="14.4" customHeight="1">
-      <c r="R32" s="39" t="inlineStr">
+      <c r="R32" s="43" t="inlineStr">
         <is>
           <t>Encore Avondale</t>
         </is>
       </c>
-      <c r="S32" s="40" t="n">
+      <c r="S32" s="44" t="n">
         <v>300</v>
       </c>
-      <c r="T32" s="49" t="inlineStr">
+      <c r="T32" s="53" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U32" s="49" t="inlineStr">
+      <c r="U32" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6461,51 +6686,51 @@
       </c>
     </row>
     <row r="33" ht="14.4" customHeight="1">
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
         </is>
       </c>
-      <c r="J33" s="60" t="inlineStr">
+      <c r="J33" s="64" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K33" s="60" t="inlineStr">
+      <c r="K33" s="64" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L33" s="60" t="inlineStr">
+      <c r="L33" s="64" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M33" s="60" t="inlineStr">
+      <c r="M33" s="64" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N33" s="60" t="inlineStr">
+      <c r="N33" s="64" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O33" s="60" t="inlineStr">
+      <c r="O33" s="64" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
-      <c r="R33" s="39" t="inlineStr">
+      <c r="R33" s="43" t="inlineStr">
         <is>
           <t>Banyan Avondale</t>
         </is>
       </c>
-      <c r="S33" s="40" t="n">
+      <c r="S33" s="44" t="n">
         <v>296</v>
       </c>
-      <c r="T33" s="49" t="inlineStr"/>
-      <c r="U33" s="49" t="inlineStr">
+      <c r="T33" s="53" t="inlineStr"/>
+      <c r="U33" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6524,45 +6749,45 @@
       </c>
     </row>
     <row r="34" ht="14.4" customHeight="1">
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J34" s="61">
+      <c r="J34" s="65">
         <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
         <v/>
       </c>
-      <c r="K34" s="61">
+      <c r="K34" s="65">
         <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
         <v/>
       </c>
-      <c r="L34" s="61">
+      <c r="L34" s="65">
         <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
         <v/>
       </c>
-      <c r="M34" s="61">
+      <c r="M34" s="65">
         <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
         <v/>
       </c>
-      <c r="N34" s="61">
+      <c r="N34" s="65">
         <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
         <v/>
       </c>
-      <c r="O34" s="61">
+      <c r="O34" s="65">
         <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
         <v/>
       </c>
-      <c r="R34" s="39" t="inlineStr">
+      <c r="R34" s="43" t="inlineStr">
         <is>
           <t>Rosilian Villas</t>
         </is>
       </c>
-      <c r="S34" s="40" t="n">
+      <c r="S34" s="44" t="n">
         <v>291</v>
       </c>
-      <c r="T34" s="49" t="inlineStr"/>
-      <c r="U34" s="49" t="inlineStr">
+      <c r="T34" s="53" t="inlineStr"/>
+      <c r="U34" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6581,49 +6806,49 @@
       </c>
     </row>
     <row r="35" ht="14.4" customHeight="1">
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J35" s="61">
+      <c r="J35" s="65">
         <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
         <v/>
       </c>
-      <c r="K35" s="61">
+      <c r="K35" s="65">
         <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
         <v/>
       </c>
-      <c r="L35" s="61">
+      <c r="L35" s="65">
         <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
         <v/>
       </c>
-      <c r="M35" s="61">
+      <c r="M35" s="65">
         <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
         <v/>
       </c>
-      <c r="N35" s="61">
+      <c r="N35" s="65">
         <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
         <v/>
       </c>
-      <c r="O35" s="61">
+      <c r="O35" s="65">
         <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
         <v/>
       </c>
-      <c r="R35" s="39" t="inlineStr">
+      <c r="R35" s="43" t="inlineStr">
         <is>
           <t>The Statler at Estrella Parkway</t>
         </is>
       </c>
-      <c r="S35" s="40" t="n">
+      <c r="S35" s="44" t="n">
         <v>284</v>
       </c>
-      <c r="T35" s="49" t="inlineStr">
+      <c r="T35" s="53" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U35" s="49" t="inlineStr">
+      <c r="U35" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6642,45 +6867,45 @@
       </c>
     </row>
     <row r="36" ht="14.4" customHeight="1">
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J36" s="61">
+      <c r="J36" s="65">
         <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
         <v/>
       </c>
-      <c r="K36" s="61">
+      <c r="K36" s="65">
         <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
         <v/>
       </c>
-      <c r="L36" s="61">
+      <c r="L36" s="65">
         <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
         <v/>
       </c>
-      <c r="M36" s="61">
+      <c r="M36" s="65">
         <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
         <v/>
       </c>
-      <c r="N36" s="61">
+      <c r="N36" s="65">
         <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
         <v/>
       </c>
-      <c r="O36" s="61">
+      <c r="O36" s="65">
         <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
         <v/>
       </c>
-      <c r="R36" s="39" t="inlineStr">
+      <c r="R36" s="43" t="inlineStr">
         <is>
           <t>Orion Avondale</t>
         </is>
       </c>
-      <c r="S36" s="40" t="n">
+      <c r="S36" s="44" t="n">
         <v>268</v>
       </c>
-      <c r="T36" s="49" t="inlineStr"/>
-      <c r="U36" s="49" t="inlineStr">
+      <c r="T36" s="53" t="inlineStr"/>
+      <c r="U36" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6699,16 +6924,16 @@
       </c>
     </row>
     <row r="37" ht="14.4" customHeight="1">
-      <c r="R37" s="39" t="inlineStr">
+      <c r="R37" s="43" t="inlineStr">
         <is>
           <t>Tavalo at Avondale</t>
         </is>
       </c>
-      <c r="S37" s="40" t="n">
+      <c r="S37" s="44" t="n">
         <v>266</v>
       </c>
-      <c r="T37" s="49" t="inlineStr"/>
-      <c r="U37" s="49" t="inlineStr">
+      <c r="T37" s="53" t="inlineStr"/>
+      <c r="U37" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6727,51 +6952,51 @@
       </c>
     </row>
     <row r="38" ht="14.4" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>MARKET RENT GROWTH (editable assumptions)</t>
         </is>
       </c>
-      <c r="J38" s="62" t="inlineStr">
+      <c r="J38" s="66" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K38" s="62" t="inlineStr">
+      <c r="K38" s="66" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L38" s="62" t="inlineStr">
+      <c r="L38" s="66" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M38" s="62" t="inlineStr">
+      <c r="M38" s="66" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N38" s="62" t="inlineStr">
+      <c r="N38" s="66" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O38" s="62" t="inlineStr">
+      <c r="O38" s="66" t="inlineStr">
         <is>
           <t>Y6</t>
         </is>
       </c>
-      <c r="R38" s="39" t="inlineStr">
+      <c r="R38" s="43" t="inlineStr">
         <is>
           <t>Marbella Ranch East Future Phase</t>
         </is>
       </c>
-      <c r="S38" s="40" t="n">
+      <c r="S38" s="44" t="n">
         <v>266</v>
       </c>
-      <c r="T38" s="49" t="inlineStr"/>
-      <c r="U38" s="49" t="inlineStr">
+      <c r="T38" s="53" t="inlineStr"/>
+      <c r="U38" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6790,39 +7015,39 @@
       </c>
     </row>
     <row r="39" ht="14.4" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J39" s="63" t="n">
+      <c r="J39" s="67" t="n">
         <v>-0.0025</v>
       </c>
-      <c r="K39" s="63" t="n">
+      <c r="K39" s="67" t="n">
         <v>0.0175</v>
       </c>
-      <c r="L39" s="63" t="n">
+      <c r="L39" s="67" t="n">
         <v>0.0275</v>
       </c>
-      <c r="M39" s="63" t="n">
+      <c r="M39" s="67" t="n">
         <v>0.0375</v>
       </c>
-      <c r="N39" s="63" t="n">
+      <c r="N39" s="67" t="n">
         <v>0.0275</v>
       </c>
-      <c r="O39" s="63" t="n">
+      <c r="O39" s="67" t="n">
         <v>0.0175</v>
       </c>
-      <c r="R39" s="39" t="inlineStr">
+      <c r="R39" s="43" t="inlineStr">
         <is>
           <t>Crystal Cove</t>
         </is>
       </c>
-      <c r="S39" s="40" t="n">
+      <c r="S39" s="44" t="n">
         <v>260</v>
       </c>
-      <c r="T39" s="49" t="inlineStr"/>
-      <c r="U39" s="49" t="inlineStr">
+      <c r="T39" s="53" t="inlineStr"/>
+      <c r="U39" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6841,39 +7066,39 @@
       </c>
     </row>
     <row r="40" ht="14.4" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J40" s="63" t="n">
+      <c r="J40" s="67" t="n">
         <v>0.01</v>
       </c>
-      <c r="K40" s="63" t="n">
+      <c r="K40" s="67" t="n">
         <v>0.03</v>
       </c>
-      <c r="L40" s="63" t="n">
+      <c r="L40" s="67" t="n">
         <v>0.04</v>
       </c>
-      <c r="M40" s="63" t="n">
+      <c r="M40" s="67" t="n">
         <v>0.05</v>
       </c>
-      <c r="N40" s="63" t="n">
+      <c r="N40" s="67" t="n">
         <v>0.04</v>
       </c>
-      <c r="O40" s="63" t="n">
+      <c r="O40" s="67" t="n">
         <v>0.03</v>
       </c>
-      <c r="R40" s="39" t="inlineStr">
+      <c r="R40" s="43" t="inlineStr">
         <is>
           <t>SimonMed Development I</t>
         </is>
       </c>
-      <c r="S40" s="40" t="n">
+      <c r="S40" s="44" t="n">
         <v>239</v>
       </c>
-      <c r="T40" s="49" t="inlineStr"/>
-      <c r="U40" s="49" t="inlineStr">
+      <c r="T40" s="53" t="inlineStr"/>
+      <c r="U40" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6892,39 +7117,39 @@
       </c>
     </row>
     <row r="41" ht="14.4" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J41" s="63" t="n">
+      <c r="J41" s="67" t="n">
         <v>0.02</v>
       </c>
-      <c r="K41" s="63" t="n">
+      <c r="K41" s="67" t="n">
         <v>0.04</v>
       </c>
-      <c r="L41" s="63" t="n">
+      <c r="L41" s="67" t="n">
         <v>0.05</v>
       </c>
-      <c r="M41" s="63" t="n">
+      <c r="M41" s="67" t="n">
         <v>0.06</v>
       </c>
-      <c r="N41" s="63" t="n">
+      <c r="N41" s="67" t="n">
         <v>0.05</v>
       </c>
-      <c r="O41" s="63" t="n">
+      <c r="O41" s="67" t="n">
         <v>0.04</v>
       </c>
-      <c r="R41" s="39" t="inlineStr">
+      <c r="R41" s="43" t="inlineStr">
         <is>
           <t>Cornerstone at the Wigwam</t>
         </is>
       </c>
-      <c r="S41" s="40" t="n">
+      <c r="S41" s="44" t="n">
         <v>212</v>
       </c>
-      <c r="T41" s="49" t="inlineStr"/>
-      <c r="U41" s="49" t="inlineStr">
+      <c r="T41" s="53" t="inlineStr"/>
+      <c r="U41" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6943,21 +7168,21 @@
       </c>
     </row>
     <row r="42" ht="14.4" customHeight="1">
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>CONCESSIONS % — forward assumption (editable)</t>
         </is>
       </c>
-      <c r="R42" s="39" t="inlineStr">
+      <c r="R42" s="43" t="inlineStr">
         <is>
           <t>Radia Avondale Station III</t>
         </is>
       </c>
-      <c r="S42" s="40" t="n">
+      <c r="S42" s="44" t="n">
         <v>212</v>
       </c>
-      <c r="T42" s="49" t="inlineStr"/>
-      <c r="U42" s="49" t="inlineStr">
+      <c r="T42" s="53" t="inlineStr"/>
+      <c r="U42" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -6976,39 +7201,39 @@
       </c>
     </row>
     <row r="43" ht="14.4" customHeight="1">
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J43" s="63" t="n">
+      <c r="J43" s="67" t="n">
         <v>0.06</v>
       </c>
-      <c r="K43" s="63" t="n">
+      <c r="K43" s="67" t="n">
         <v>0.045</v>
       </c>
-      <c r="L43" s="63" t="n">
+      <c r="L43" s="67" t="n">
         <v>0.035</v>
       </c>
-      <c r="M43" s="63" t="n">
+      <c r="M43" s="67" t="n">
         <v>0.035</v>
       </c>
-      <c r="N43" s="63" t="n">
+      <c r="N43" s="67" t="n">
         <v>0.035</v>
       </c>
-      <c r="O43" s="63" t="n">
+      <c r="O43" s="67" t="n">
         <v>0.035</v>
       </c>
-      <c r="R43" s="39" t="inlineStr">
+      <c r="R43" s="43" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel A</t>
         </is>
       </c>
-      <c r="S43" s="40" t="n">
+      <c r="S43" s="44" t="n">
         <v>181</v>
       </c>
-      <c r="T43" s="49" t="inlineStr"/>
-      <c r="U43" s="49" t="inlineStr">
+      <c r="T43" s="53" t="inlineStr"/>
+      <c r="U43" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7027,39 +7252,39 @@
       </c>
     </row>
     <row r="44" ht="14.4" customHeight="1">
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J44" s="63" t="n">
+      <c r="J44" s="67" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" s="63" t="n">
+      <c r="K44" s="67" t="n">
         <v>0.015</v>
       </c>
-      <c r="L44" s="63" t="n">
+      <c r="L44" s="67" t="n">
         <v>0.005</v>
       </c>
-      <c r="M44" s="63" t="n">
+      <c r="M44" s="67" t="n">
         <v>0.005</v>
       </c>
-      <c r="N44" s="63" t="n">
+      <c r="N44" s="67" t="n">
         <v>0.005</v>
       </c>
-      <c r="O44" s="63" t="n">
+      <c r="O44" s="67" t="n">
         <v>0.005</v>
       </c>
-      <c r="R44" s="39" t="inlineStr">
+      <c r="R44" s="43" t="inlineStr">
         <is>
           <t>Villages at River Grove</t>
         </is>
       </c>
-      <c r="S44" s="40" t="n">
+      <c r="S44" s="44" t="n">
         <v>180</v>
       </c>
-      <c r="T44" s="49" t="inlineStr"/>
-      <c r="U44" s="49" t="inlineStr">
+      <c r="T44" s="53" t="inlineStr"/>
+      <c r="U44" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7078,39 +7303,39 @@
       </c>
     </row>
     <row r="45" ht="14.4" customHeight="1">
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J45" s="63" t="n">
+      <c r="J45" s="67" t="n">
         <v>0.02</v>
       </c>
-      <c r="K45" s="63" t="n">
+      <c r="K45" s="67" t="n">
         <v>0.005</v>
       </c>
-      <c r="L45" s="63" t="n">
+      <c r="L45" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="63" t="n">
+      <c r="M45" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="63" t="n">
+      <c r="N45" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="63" t="n">
+      <c r="O45" s="67" t="n">
         <v>0</v>
       </c>
-      <c r="R45" s="39" t="inlineStr">
+      <c r="R45" s="43" t="inlineStr">
         <is>
           <t>District 99</t>
         </is>
       </c>
-      <c r="S45" s="40" t="n">
+      <c r="S45" s="44" t="n">
         <v>172</v>
       </c>
-      <c r="T45" s="49" t="inlineStr"/>
-      <c r="U45" s="49" t="inlineStr">
+      <c r="T45" s="53" t="inlineStr"/>
+      <c r="U45" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7129,21 +7354,21 @@
       </c>
     </row>
     <row r="46" ht="14.4" customHeight="1">
-      <c r="B46" s="35" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
-      <c r="R46" s="39" t="inlineStr">
+      <c r="R46" s="43" t="inlineStr">
         <is>
           <t>McDowell Villas</t>
         </is>
       </c>
-      <c r="S46" s="40" t="n">
+      <c r="S46" s="44" t="n">
         <v>164</v>
       </c>
-      <c r="T46" s="49" t="inlineStr"/>
-      <c r="U46" s="49" t="inlineStr">
+      <c r="T46" s="53" t="inlineStr"/>
+      <c r="U46" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7162,45 +7387,45 @@
       </c>
     </row>
     <row r="47" ht="14.4" customHeight="1">
-      <c r="B47" s="35" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J47" s="61">
+      <c r="J47" s="65">
         <f>(1+J39)*(1-J43)-1</f>
         <v/>
       </c>
-      <c r="K47" s="61">
+      <c r="K47" s="65">
         <f>(1+K39)*(1-K43)/(1-J43)-1</f>
         <v/>
       </c>
-      <c r="L47" s="61">
+      <c r="L47" s="65">
         <f>(1+L39)*(1-L43)/(1-K43)-1</f>
         <v/>
       </c>
-      <c r="M47" s="61">
+      <c r="M47" s="65">
         <f>(1+M39)*(1-M43)/(1-L43)-1</f>
         <v/>
       </c>
-      <c r="N47" s="61">
+      <c r="N47" s="65">
         <f>(1+N39)*(1-N43)/(1-M43)-1</f>
         <v/>
       </c>
-      <c r="O47" s="61">
+      <c r="O47" s="65">
         <f>(1+O39)*(1-O43)/(1-N43)-1</f>
         <v/>
       </c>
-      <c r="R47" s="39" t="inlineStr">
+      <c r="R47" s="43" t="inlineStr">
         <is>
           <t>Avondale</t>
         </is>
       </c>
-      <c r="S47" s="40" t="n">
+      <c r="S47" s="44" t="n">
         <v>156</v>
       </c>
-      <c r="T47" s="49" t="inlineStr"/>
-      <c r="U47" s="49" t="inlineStr">
+      <c r="T47" s="53" t="inlineStr"/>
+      <c r="U47" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7219,45 +7444,45 @@
       </c>
     </row>
     <row r="48" ht="14.4" customHeight="1">
-      <c r="B48" s="35" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J48" s="61">
+      <c r="J48" s="65">
         <f>(1+J40)*(1-J44)-1</f>
         <v/>
       </c>
-      <c r="K48" s="61">
+      <c r="K48" s="65">
         <f>(1+K40)*(1-K44)/(1-J44)-1</f>
         <v/>
       </c>
-      <c r="L48" s="61">
+      <c r="L48" s="65">
         <f>(1+L40)*(1-L44)/(1-K44)-1</f>
         <v/>
       </c>
-      <c r="M48" s="61">
+      <c r="M48" s="65">
         <f>(1+M40)*(1-M44)/(1-L44)-1</f>
         <v/>
       </c>
-      <c r="N48" s="61">
+      <c r="N48" s="65">
         <f>(1+N40)*(1-N44)/(1-M44)-1</f>
         <v/>
       </c>
-      <c r="O48" s="61">
+      <c r="O48" s="65">
         <f>(1+O40)*(1-O44)/(1-N44)-1</f>
         <v/>
       </c>
-      <c r="R48" s="39" t="inlineStr">
+      <c r="R48" s="43" t="inlineStr">
         <is>
           <t>Porter Kyle Development</t>
         </is>
       </c>
-      <c r="S48" s="40" t="n">
+      <c r="S48" s="44" t="n">
         <v>135</v>
       </c>
-      <c r="T48" s="49" t="inlineStr"/>
-      <c r="U48" s="49" t="inlineStr">
+      <c r="T48" s="53" t="inlineStr"/>
+      <c r="U48" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7276,49 +7501,49 @@
       </c>
     </row>
     <row r="49" ht="14.4" customHeight="1">
-      <c r="B49" s="35" t="inlineStr">
+      <c r="B49" s="39" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J49" s="61">
+      <c r="J49" s="65">
         <f>(1+J41)*(1-J45)-1</f>
         <v/>
       </c>
-      <c r="K49" s="61">
+      <c r="K49" s="65">
         <f>(1+K41)*(1-K45)/(1-J45)-1</f>
         <v/>
       </c>
-      <c r="L49" s="61">
+      <c r="L49" s="65">
         <f>(1+L41)*(1-L45)/(1-K45)-1</f>
         <v/>
       </c>
-      <c r="M49" s="61">
+      <c r="M49" s="65">
         <f>(1+M41)*(1-M45)/(1-L45)-1</f>
         <v/>
       </c>
-      <c r="N49" s="61">
+      <c r="N49" s="65">
         <f>(1+N41)*(1-N45)/(1-M45)-1</f>
         <v/>
       </c>
-      <c r="O49" s="61">
+      <c r="O49" s="65">
         <f>(1+O41)*(1-O45)/(1-N45)-1</f>
         <v/>
       </c>
-      <c r="R49" s="39" t="inlineStr">
+      <c r="R49" s="43" t="inlineStr">
         <is>
           <t>Ascent Goodyear</t>
         </is>
       </c>
-      <c r="S49" s="40" t="n">
+      <c r="S49" s="44" t="n">
         <v>113</v>
       </c>
-      <c r="T49" s="49" t="inlineStr">
+      <c r="T49" s="53" t="inlineStr">
         <is>
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="U49" s="49" t="inlineStr">
+      <c r="U49" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7337,20 +7562,20 @@
       </c>
     </row>
     <row r="50" ht="14.4" customHeight="1">
-      <c r="R50" s="39" t="inlineStr">
+      <c r="R50" s="43" t="inlineStr">
         <is>
           <t>Northern 107</t>
         </is>
       </c>
-      <c r="S50" s="40" t="n">
+      <c r="S50" s="44" t="n">
         <v>74</v>
       </c>
-      <c r="T50" s="49" t="inlineStr">
+      <c r="T50" s="53" t="inlineStr">
         <is>
           <t>Q4 2028</t>
         </is>
       </c>
-      <c r="U50" s="49" t="inlineStr">
+      <c r="U50" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7369,21 +7594,21 @@
       </c>
     </row>
     <row r="51" ht="14.4" customHeight="1">
-      <c r="B51" s="62" t="inlineStr">
+      <c r="B51" s="66" t="inlineStr">
         <is>
           <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
         </is>
       </c>
-      <c r="R51" s="39" t="inlineStr">
+      <c r="R51" s="43" t="inlineStr">
         <is>
           <t>Zenn @ Sierra Verde</t>
         </is>
       </c>
-      <c r="S51" s="40" t="n">
+      <c r="S51" s="44" t="n">
         <v>66</v>
       </c>
-      <c r="T51" s="49" t="inlineStr"/>
-      <c r="U51" s="49" t="inlineStr">
+      <c r="T51" s="53" t="inlineStr"/>
+      <c r="U51" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7402,24 +7627,24 @@
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B52" s="64" t="inlineStr">
+      <c r="B52" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
         </is>
       </c>
-      <c r="E52" s="64" t="inlineStr">
+      <c r="E52" s="68" t="inlineStr">
         <is>
           <t>CoStar</t>
         </is>
       </c>
-      <c r="R52" s="39" t="inlineStr">
+      <c r="R52" s="43" t="inlineStr">
         <is>
           <t>The BLVD Residential District</t>
         </is>
       </c>
-      <c r="S52" s="40" t="n"/>
-      <c r="T52" s="49" t="inlineStr"/>
-      <c r="U52" s="49" t="inlineStr">
+      <c r="S52" s="44" t="n"/>
+      <c r="T52" s="53" t="inlineStr"/>
+      <c r="U52" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7438,24 +7663,24 @@
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B53" s="64" t="inlineStr">
+      <c r="B53" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
         </is>
       </c>
-      <c r="E53" s="64" t="inlineStr">
+      <c r="E53" s="68" t="inlineStr">
         <is>
           <t>CoStar</t>
         </is>
       </c>
-      <c r="R53" s="39" t="inlineStr">
+      <c r="R53" s="43" t="inlineStr">
         <is>
           <t>The BLVD Park Avenue District</t>
         </is>
       </c>
-      <c r="S53" s="40" t="n"/>
-      <c r="T53" s="49" t="inlineStr"/>
-      <c r="U53" s="49" t="inlineStr">
+      <c r="S53" s="44" t="n"/>
+      <c r="T53" s="53" t="inlineStr"/>
+      <c r="U53" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7474,24 +7699,24 @@
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B54" s="64" t="inlineStr">
+      <c r="B54" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
         </is>
       </c>
-      <c r="E54" s="64" t="inlineStr">
+      <c r="E54" s="68" t="inlineStr">
         <is>
           <t>CoStar</t>
         </is>
       </c>
-      <c r="R54" s="39" t="inlineStr">
+      <c r="R54" s="43" t="inlineStr">
         <is>
           <t>Globe Land Investors Development</t>
         </is>
       </c>
-      <c r="S54" s="40" t="n"/>
-      <c r="T54" s="49" t="inlineStr"/>
-      <c r="U54" s="49" t="inlineStr">
+      <c r="S54" s="44" t="n"/>
+      <c r="T54" s="53" t="inlineStr"/>
+      <c r="U54" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7510,24 +7735,24 @@
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B55" s="64" t="inlineStr">
+      <c r="B55" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
         </is>
       </c>
-      <c r="E55" s="64" t="inlineStr">
+      <c r="E55" s="68" t="inlineStr">
         <is>
           <t>CoStar</t>
         </is>
       </c>
-      <c r="R55" s="39" t="inlineStr">
+      <c r="R55" s="43" t="inlineStr">
         <is>
           <t>Ball Park</t>
         </is>
       </c>
-      <c r="S55" s="40" t="n"/>
-      <c r="T55" s="49" t="inlineStr"/>
-      <c r="U55" s="49" t="inlineStr">
+      <c r="S55" s="44" t="n"/>
+      <c r="T55" s="53" t="inlineStr"/>
+      <c r="U55" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7546,24 +7771,24 @@
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B56" s="64" t="inlineStr">
+      <c r="B56" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
         </is>
       </c>
-      <c r="E56" s="64" t="inlineStr">
+      <c r="E56" s="68" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="R56" s="39" t="inlineStr">
+      <c r="R56" s="43" t="inlineStr">
         <is>
           <t>Vision 2 Parcel A</t>
         </is>
       </c>
-      <c r="S56" s="40" t="n"/>
-      <c r="T56" s="49" t="inlineStr"/>
-      <c r="U56" s="49" t="inlineStr">
+      <c r="S56" s="44" t="n"/>
+      <c r="T56" s="53" t="inlineStr"/>
+      <c r="U56" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7582,24 +7807,24 @@
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B57" s="64" t="inlineStr">
+      <c r="B57" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
         </is>
       </c>
-      <c r="E57" s="64" t="inlineStr">
+      <c r="E57" s="68" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="R57" s="39" t="inlineStr">
+      <c r="R57" s="43" t="inlineStr">
         <is>
           <t>Firststreet Verde</t>
         </is>
       </c>
-      <c r="S57" s="40" t="n"/>
-      <c r="T57" s="49" t="inlineStr"/>
-      <c r="U57" s="49" t="inlineStr">
+      <c r="S57" s="44" t="n"/>
+      <c r="T57" s="53" t="inlineStr"/>
+      <c r="U57" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7618,24 +7843,24 @@
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B58" s="64" t="inlineStr">
+      <c r="B58" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
         </is>
       </c>
-      <c r="E58" s="64" t="inlineStr">
+      <c r="E58" s="68" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="R58" s="39" t="inlineStr">
+      <c r="R58" s="43" t="inlineStr">
         <is>
           <t>Goodyear Civic Square at Estrella Falls</t>
         </is>
       </c>
-      <c r="S58" s="40" t="n"/>
-      <c r="T58" s="49" t="inlineStr"/>
-      <c r="U58" s="49" t="inlineStr">
+      <c r="S58" s="44" t="n"/>
+      <c r="T58" s="53" t="inlineStr"/>
+      <c r="U58" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7654,24 +7879,24 @@
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B59" s="64" t="inlineStr">
+      <c r="B59" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
         </is>
       </c>
-      <c r="E59" s="64" t="inlineStr">
+      <c r="E59" s="68" t="inlineStr">
         <is>
           <t>2,307 / 1,251</t>
         </is>
       </c>
-      <c r="R59" s="39" t="inlineStr">
+      <c r="R59" s="43" t="inlineStr">
         <is>
           <t>I-10 Innovation Center II</t>
         </is>
       </c>
-      <c r="S59" s="40" t="n"/>
-      <c r="T59" s="49" t="inlineStr"/>
-      <c r="U59" s="49" t="inlineStr">
+      <c r="S59" s="44" t="n"/>
+      <c r="T59" s="53" t="inlineStr"/>
+      <c r="U59" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7690,19 +7915,19 @@
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B60" s="33" t="inlineStr">
+      <c r="B60" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
         </is>
       </c>
-      <c r="R60" s="39" t="inlineStr">
+      <c r="R60" s="43" t="inlineStr">
         <is>
           <t>Celebration Plaza Parcel D</t>
         </is>
       </c>
-      <c r="S60" s="40" t="n"/>
-      <c r="T60" s="49" t="inlineStr"/>
-      <c r="U60" s="49" t="inlineStr">
+      <c r="S60" s="44" t="n"/>
+      <c r="T60" s="53" t="inlineStr"/>
+      <c r="U60" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7721,14 +7946,14 @@
       </c>
     </row>
     <row r="61" ht="14.4" customHeight="1">
-      <c r="R61" s="39" t="inlineStr">
+      <c r="R61" s="43" t="inlineStr">
         <is>
           <t>SimonMed Development II</t>
         </is>
       </c>
-      <c r="S61" s="40" t="n"/>
-      <c r="T61" s="49" t="inlineStr"/>
-      <c r="U61" s="49" t="inlineStr">
+      <c r="S61" s="44" t="n"/>
+      <c r="T61" s="53" t="inlineStr"/>
+      <c r="U61" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7747,14 +7972,14 @@
       </c>
     </row>
     <row r="62" ht="14.4" customHeight="1">
-      <c r="R62" s="39" t="inlineStr">
+      <c r="R62" s="43" t="inlineStr">
         <is>
           <t>182 South 95th Avenue</t>
         </is>
       </c>
-      <c r="S62" s="40" t="n"/>
-      <c r="T62" s="49" t="inlineStr"/>
-      <c r="U62" s="49" t="inlineStr">
+      <c r="S62" s="44" t="n"/>
+      <c r="T62" s="53" t="inlineStr"/>
+      <c r="U62" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7773,14 +7998,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="R63" s="39" t="inlineStr">
+      <c r="R63" s="43" t="inlineStr">
         <is>
           <t>Envision Encore</t>
         </is>
       </c>
-      <c r="S63" s="40" t="n"/>
-      <c r="T63" s="49" t="inlineStr"/>
-      <c r="U63" s="49" t="inlineStr">
+      <c r="S63" s="44" t="n"/>
+      <c r="T63" s="53" t="inlineStr"/>
+      <c r="U63" s="53" t="inlineStr">
         <is>
           <t>Bear only</t>
         </is>
@@ -7838,62 +8063,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="65" t="inlineStr">
+      <c r="A1" s="69" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="65" t="inlineStr">
+      <c r="B1" s="69" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="65" t="inlineStr">
+      <c r="C1" s="69" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="65" t="inlineStr">
+      <c r="D1" s="69" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="65" t="inlineStr">
+      <c r="E1" s="69" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="65" t="inlineStr">
+      <c r="F1" s="69" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="65" t="inlineStr">
+      <c r="G1" s="69" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="65" t="inlineStr">
+      <c r="H1" s="69" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="65" t="inlineStr">
+      <c r="I1" s="69" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="65" t="inlineStr">
+      <c r="J1" s="69" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="65" t="inlineStr">
+      <c r="K1" s="69" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="65" t="inlineStr">
+      <c r="L1" s="69" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -7926,16 +8151,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="66" t="n">
+      <c r="G2" s="70" t="n">
         <v>0.924324</v>
       </c>
-      <c r="H2" s="66" t="n">
+      <c r="H2" s="70" t="n">
         <v>0.924</v>
       </c>
-      <c r="I2" s="67" t="n">
+      <c r="I2" s="71" t="n">
         <v>1750</v>
       </c>
-      <c r="J2" s="67" t="n">
+      <c r="J2" s="71" t="n">
         <v>1875</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -7976,12 +8201,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="66" t="n"/>
-      <c r="H3" s="66" t="n">
+      <c r="G3" s="70" t="n"/>
+      <c r="H3" s="70" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="67" t="n"/>
-      <c r="J3" s="67" t="n">
+      <c r="I3" s="71" t="n"/>
+      <c r="J3" s="71" t="n">
         <v>2090</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -8022,16 +8247,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="66" t="n">
+      <c r="G4" s="70" t="n">
         <v>0.8518520000000001</v>
       </c>
-      <c r="H4" s="66" t="n">
+      <c r="H4" s="70" t="n">
         <v>0.877</v>
       </c>
-      <c r="I4" s="67" t="n">
+      <c r="I4" s="71" t="n">
         <v>1576</v>
       </c>
-      <c r="J4" s="67" t="n">
+      <c r="J4" s="71" t="n">
         <v>1211</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -8072,16 +8297,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G5" s="66" t="n">
+      <c r="G5" s="70" t="n">
         <v>0.7634730000000001</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="70" t="n">
         <v>0.916</v>
       </c>
-      <c r="I5" s="67" t="n">
+      <c r="I5" s="71" t="n">
         <v>2026</v>
       </c>
-      <c r="J5" s="67" t="n">
+      <c r="J5" s="71" t="n">
         <v>1385</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -8122,16 +8347,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G6" s="66" t="n">
+      <c r="G6" s="70" t="n">
         <v>0.895833</v>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="70" t="n">
         <v>0.966</v>
       </c>
-      <c r="I6" s="67" t="n">
+      <c r="I6" s="71" t="n">
         <v>1429</v>
       </c>
-      <c r="J6" s="67" t="n">
+      <c r="J6" s="71" t="n">
         <v>1313</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -8172,16 +8397,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="70" t="n">
         <v>0.949309</v>
       </c>
-      <c r="H7" s="66" t="n">
+      <c r="H7" s="70" t="n">
         <v>0.968</v>
       </c>
-      <c r="I7" s="67" t="n">
+      <c r="I7" s="71" t="n">
         <v>1576</v>
       </c>
-      <c r="J7" s="67" t="n">
+      <c r="J7" s="71" t="n">
         <v>1602</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -8222,16 +8447,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="70" t="n">
         <v>0.773196</v>
       </c>
-      <c r="H8" s="66" t="n">
+      <c r="H8" s="70" t="n">
         <v>0.918</v>
       </c>
-      <c r="I8" s="67" t="n">
+      <c r="I8" s="71" t="n">
         <v>1874</v>
       </c>
-      <c r="J8" s="67" t="n">
+      <c r="J8" s="71" t="n">
         <v>1794</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -8272,16 +8497,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="70" t="n">
         <v>0.784247</v>
       </c>
-      <c r="H9" s="66" t="n">
+      <c r="H9" s="70" t="n">
         <v>0.87</v>
       </c>
-      <c r="I9" s="67" t="n">
+      <c r="I9" s="71" t="n">
         <v>1516</v>
       </c>
-      <c r="J9" s="67" t="n">
+      <c r="J9" s="71" t="n">
         <v>1517</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -8322,16 +8547,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G10" s="66" t="n">
+      <c r="G10" s="70" t="n">
         <v>0.8992249999999999</v>
       </c>
-      <c r="H10" s="66" t="n">
+      <c r="H10" s="70" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="I10" s="67" t="n">
+      <c r="I10" s="71" t="n">
         <v>1567</v>
       </c>
-      <c r="J10" s="67" t="n">
+      <c r="J10" s="71" t="n">
         <v>1591</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -8372,16 +8597,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G11" s="66" t="n">
+      <c r="G11" s="70" t="n">
         <v>0.9520960000000001</v>
       </c>
-      <c r="H11" s="66" t="n">
+      <c r="H11" s="70" t="n">
         <v>0.946</v>
       </c>
-      <c r="I11" s="67" t="n">
+      <c r="I11" s="71" t="n">
         <v>1607</v>
       </c>
-      <c r="J11" s="67" t="n">
+      <c r="J11" s="71" t="n">
         <v>1388</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -8422,16 +8647,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G12" s="66" t="n">
+      <c r="G12" s="70" t="n">
         <v>0.920455</v>
       </c>
-      <c r="H12" s="66" t="n">
+      <c r="H12" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="67" t="n">
+      <c r="I12" s="71" t="n">
         <v>1526</v>
       </c>
-      <c r="J12" s="67" t="n">
+      <c r="J12" s="71" t="n">
         <v>1263</v>
       </c>
       <c r="K12" t="inlineStr">
@@ -8472,16 +8697,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G13" s="66" t="n">
+      <c r="G13" s="70" t="n">
         <v>0.934483</v>
       </c>
-      <c r="H13" s="66" t="n">
+      <c r="H13" s="70" t="n">
         <v>0.959</v>
       </c>
-      <c r="I13" s="67" t="n">
+      <c r="I13" s="71" t="n">
         <v>2812</v>
       </c>
-      <c r="J13" s="67" t="n">
+      <c r="J13" s="71" t="n">
         <v>2575</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -8522,16 +8747,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="70" t="n">
         <v>0.935829</v>
       </c>
-      <c r="H14" s="66" t="n">
+      <c r="H14" s="70" t="n">
         <v>0.963</v>
       </c>
-      <c r="I14" s="67" t="n">
+      <c r="I14" s="71" t="n">
         <v>1964</v>
       </c>
-      <c r="J14" s="67" t="n">
+      <c r="J14" s="71" t="n">
         <v>1902</v>
       </c>
       <c r="K14" t="inlineStr">
@@ -8572,16 +8797,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G15" s="66" t="n">
+      <c r="G15" s="70" t="n">
         <v>0.892045</v>
       </c>
-      <c r="H15" s="66" t="n">
+      <c r="H15" s="70" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I15" s="67" t="n">
+      <c r="I15" s="71" t="n">
         <v>1632</v>
       </c>
-      <c r="J15" s="67" t="n">
+      <c r="J15" s="71" t="n">
         <v>1236</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -8622,16 +8847,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="70" t="n">
         <v>0.926471</v>
       </c>
-      <c r="H16" s="66" t="n">
+      <c r="H16" s="70" t="n">
         <v>0.967</v>
       </c>
-      <c r="I16" s="67" t="n">
+      <c r="I16" s="71" t="n">
         <v>1820</v>
       </c>
-      <c r="J16" s="67" t="n">
+      <c r="J16" s="71" t="n">
         <v>1597</v>
       </c>
       <c r="K16" t="inlineStr">
@@ -8672,16 +8897,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G17" s="66" t="n">
+      <c r="G17" s="70" t="n">
         <v>0.9494050000000001</v>
       </c>
-      <c r="H17" s="66" t="n">
+      <c r="H17" s="70" t="n">
         <v>0.949</v>
       </c>
-      <c r="I17" s="67" t="n">
+      <c r="I17" s="71" t="n">
         <v>1335</v>
       </c>
-      <c r="J17" s="67" t="n">
+      <c r="J17" s="71" t="n">
         <v>1325</v>
       </c>
       <c r="K17" t="inlineStr">
@@ -8722,14 +8947,14 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G18" s="66" t="n">
+      <c r="G18" s="70" t="n">
         <v>0.893204</v>
       </c>
-      <c r="H18" s="66" t="n"/>
-      <c r="I18" s="67" t="n">
+      <c r="H18" s="70" t="n"/>
+      <c r="I18" s="71" t="n">
         <v>2523</v>
       </c>
-      <c r="J18" s="67" t="n"/>
+      <c r="J18" s="71" t="n"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -8768,12 +8993,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G19" s="66" t="n"/>
-      <c r="H19" s="66" t="n">
+      <c r="G19" s="70" t="n"/>
+      <c r="H19" s="70" t="n">
         <v>0.926</v>
       </c>
-      <c r="I19" s="67" t="n"/>
-      <c r="J19" s="67" t="n">
+      <c r="I19" s="71" t="n"/>
+      <c r="J19" s="71" t="n">
         <v>1629</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -8814,16 +9039,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G20" s="66" t="n">
+      <c r="G20" s="70" t="n">
         <v>0.951977</v>
       </c>
-      <c r="H20" s="66" t="n">
+      <c r="H20" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="67" t="n">
+      <c r="I20" s="71" t="n">
         <v>1574</v>
       </c>
-      <c r="J20" s="67" t="n">
+      <c r="J20" s="71" t="n">
         <v>1583</v>
       </c>
       <c r="K20" t="inlineStr">
@@ -8864,16 +9089,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G21" s="66" t="n">
+      <c r="G21" s="70" t="n">
         <v>0.902098</v>
       </c>
-      <c r="H21" s="66" t="n">
+      <c r="H21" s="70" t="n">
         <v>0.955</v>
       </c>
-      <c r="I21" s="67" t="n">
+      <c r="I21" s="71" t="n">
         <v>1338</v>
       </c>
-      <c r="J21" s="67" t="n">
+      <c r="J21" s="71" t="n">
         <v>1167</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -8914,16 +9139,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G22" s="66" t="n">
+      <c r="G22" s="70" t="n">
         <v>0.984375</v>
       </c>
-      <c r="H22" s="66" t="n">
+      <c r="H22" s="70" t="n">
         <v>0.984</v>
       </c>
-      <c r="I22" s="67" t="n">
+      <c r="I22" s="71" t="n">
         <v>2442</v>
       </c>
-      <c r="J22" s="67" t="n">
+      <c r="J22" s="71" t="n">
         <v>2261</v>
       </c>
       <c r="K22" t="inlineStr">
@@ -8964,16 +9189,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G23" s="66" t="n">
+      <c r="G23" s="70" t="n">
         <v>0.989362</v>
       </c>
-      <c r="H23" s="66" t="n">
+      <c r="H23" s="70" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="67" t="n">
+      <c r="I23" s="71" t="n">
         <v>1913</v>
       </c>
-      <c r="J23" s="67" t="n">
+      <c r="J23" s="71" t="n">
         <v>1982</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -9010,16 +9235,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G24" s="66" t="n">
+      <c r="G24" s="70" t="n">
         <v>0.4461540000000001</v>
       </c>
-      <c r="H24" s="66" t="n">
+      <c r="H24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="67" t="n">
+      <c r="I24" s="71" t="n">
         <v>1829</v>
       </c>
-      <c r="J24" s="67" t="n">
+      <c r="J24" s="71" t="n">
         <v>1681</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -9060,16 +9285,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G25" s="66" t="n">
+      <c r="G25" s="70" t="n">
         <v>0.05660399999999999</v>
       </c>
-      <c r="H25" s="66" t="n">
+      <c r="H25" s="70" t="n">
         <v>0.208</v>
       </c>
-      <c r="I25" s="67" t="n">
+      <c r="I25" s="71" t="n">
         <v>2966</v>
       </c>
-      <c r="J25" s="67" t="n">
+      <c r="J25" s="71" t="n">
         <v>1938</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -9110,16 +9335,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="70" t="n">
         <v>0.273504</v>
       </c>
-      <c r="H26" s="66" t="n">
+      <c r="H26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="67" t="n">
+      <c r="I26" s="71" t="n">
         <v>2537</v>
       </c>
-      <c r="J26" s="67" t="n">
+      <c r="J26" s="71" t="n">
         <v>2273</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -9160,14 +9385,14 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G27" s="66" t="n">
+      <c r="G27" s="70" t="n">
         <v>0.1333329999999999</v>
       </c>
-      <c r="H27" s="66" t="n"/>
-      <c r="I27" s="67" t="n">
+      <c r="H27" s="70" t="n"/>
+      <c r="I27" s="71" t="n">
         <v>1411</v>
       </c>
-      <c r="J27" s="67" t="n"/>
+      <c r="J27" s="71" t="n"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -9206,16 +9431,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G28" s="66" t="n">
+      <c r="G28" s="70" t="n">
         <v>0.297203</v>
       </c>
-      <c r="H28" s="66" t="n">
+      <c r="H28" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="67" t="n">
+      <c r="I28" s="71" t="n">
         <v>1728</v>
       </c>
-      <c r="J28" s="67" t="n">
+      <c r="J28" s="71" t="n">
         <v>1243</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -9256,16 +9481,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G29" s="66" t="n">
+      <c r="G29" s="70" t="n">
         <v>0.875</v>
       </c>
-      <c r="H29" s="66" t="n">
+      <c r="H29" s="70" t="n">
         <v>0.512</v>
       </c>
-      <c r="I29" s="67" t="n">
+      <c r="I29" s="71" t="n">
         <v>1506</v>
       </c>
-      <c r="J29" s="67" t="n">
+      <c r="J29" s="71" t="n">
         <v>1107</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -9306,14 +9531,14 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G30" s="66" t="n">
+      <c r="G30" s="70" t="n">
         <v>0.895349</v>
       </c>
-      <c r="H30" s="66" t="n"/>
-      <c r="I30" s="67" t="n">
+      <c r="H30" s="70" t="n"/>
+      <c r="I30" s="71" t="n">
         <v>2474</v>
       </c>
-      <c r="J30" s="67" t="n"/>
+      <c r="J30" s="71" t="n"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -9352,16 +9577,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G31" s="66" t="n">
+      <c r="G31" s="70" t="n">
         <v>0.52381</v>
       </c>
-      <c r="H31" s="66" t="n">
+      <c r="H31" s="70" t="n">
         <v>0.714</v>
       </c>
-      <c r="I31" s="67" t="n">
+      <c r="I31" s="71" t="n">
         <v>2319</v>
       </c>
-      <c r="J31" s="67" t="n">
+      <c r="J31" s="71" t="n">
         <v>1833</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -9402,16 +9627,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G32" s="66" t="n">
+      <c r="G32" s="70" t="n">
         <v>0.810458</v>
       </c>
-      <c r="H32" s="66" t="n">
+      <c r="H32" s="70" t="n">
         <v>0.856</v>
       </c>
-      <c r="I32" s="67" t="n">
+      <c r="I32" s="71" t="n">
         <v>1913</v>
       </c>
-      <c r="J32" s="67" t="n">
+      <c r="J32" s="71" t="n">
         <v>1538</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -9452,16 +9677,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G33" s="66" t="n">
+      <c r="G33" s="70" t="n">
         <v>0.857143</v>
       </c>
-      <c r="H33" s="66" t="n">
+      <c r="H33" s="70" t="n">
         <v>0.857</v>
       </c>
-      <c r="I33" s="67" t="n">
+      <c r="I33" s="71" t="n">
         <v>2325</v>
       </c>
-      <c r="J33" s="67" t="n">
+      <c r="J33" s="71" t="n">
         <v>2169</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -9502,16 +9727,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G34" s="66" t="n">
+      <c r="G34" s="70" t="n">
         <v>0.496503</v>
       </c>
-      <c r="H34" s="66" t="n">
+      <c r="H34" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="67" t="n">
+      <c r="I34" s="71" t="n">
         <v>2085</v>
       </c>
-      <c r="J34" s="67" t="n">
+      <c r="J34" s="71" t="n">
         <v>2095</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -9552,16 +9777,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G35" s="66" t="n">
+      <c r="G35" s="70" t="n">
         <v>0.802469</v>
       </c>
-      <c r="H35" s="66" t="n">
+      <c r="H35" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="67" t="n">
+      <c r="I35" s="71" t="n">
         <v>1747</v>
       </c>
-      <c r="J35" s="67" t="n">
+      <c r="J35" s="71" t="n">
         <v>1582</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -9602,16 +9827,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G36" s="66" t="n">
+      <c r="G36" s="70" t="n">
         <v>0.789474</v>
       </c>
-      <c r="H36" s="66" t="n">
+      <c r="H36" s="70" t="n">
         <v>0.784</v>
       </c>
-      <c r="I36" s="67" t="n">
+      <c r="I36" s="71" t="n">
         <v>1638</v>
       </c>
-      <c r="J36" s="67" t="n">
+      <c r="J36" s="71" t="n">
         <v>1433</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -9652,16 +9877,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G37" s="66" t="n">
+      <c r="G37" s="70" t="n">
         <v>0.3952100000000001</v>
       </c>
-      <c r="H37" s="66" t="n">
+      <c r="H37" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="67" t="n">
+      <c r="I37" s="71" t="n">
         <v>1773</v>
       </c>
-      <c r="J37" s="67" t="n">
+      <c r="J37" s="71" t="n">
         <v>1632</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -9702,16 +9927,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G38" s="66" t="n">
+      <c r="G38" s="70" t="n">
         <v>0.37037</v>
       </c>
-      <c r="H38" s="66" t="n">
+      <c r="H38" s="70" t="n">
         <v>0.852</v>
       </c>
-      <c r="I38" s="67" t="n">
+      <c r="I38" s="71" t="n">
         <v>1632</v>
       </c>
-      <c r="J38" s="67" t="n">
+      <c r="J38" s="71" t="n">
         <v>1321</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -9752,16 +9977,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G39" s="66" t="n">
+      <c r="G39" s="70" t="n">
         <v>0.7393000000000001</v>
       </c>
-      <c r="H39" s="66" t="n">
+      <c r="H39" s="70" t="n">
         <v>0.673</v>
       </c>
-      <c r="I39" s="67" t="n">
+      <c r="I39" s="71" t="n">
         <v>1330</v>
       </c>
-      <c r="J39" s="67" t="n">
+      <c r="J39" s="71" t="n">
         <v>1253</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -9802,16 +10027,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G40" s="66" t="n">
+      <c r="G40" s="70" t="n">
         <v>0.583062</v>
       </c>
-      <c r="H40" s="66" t="n">
+      <c r="H40" s="70" t="n">
         <v>0.59</v>
       </c>
-      <c r="I40" s="67" t="n">
+      <c r="I40" s="71" t="n">
         <v>2076</v>
       </c>
-      <c r="J40" s="67" t="n">
+      <c r="J40" s="71" t="n">
         <v>1561</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -9852,12 +10077,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G41" s="66" t="n"/>
-      <c r="H41" s="66" t="n">
+      <c r="G41" s="70" t="n"/>
+      <c r="H41" s="70" t="n">
         <v>0.89</v>
       </c>
-      <c r="I41" s="67" t="n"/>
-      <c r="J41" s="67" t="n">
+      <c r="I41" s="71" t="n"/>
+      <c r="J41" s="71" t="n">
         <v>1438</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -9898,12 +10123,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G42" s="66" t="n"/>
-      <c r="H42" s="66" t="n">
+      <c r="G42" s="70" t="n"/>
+      <c r="H42" s="70" t="n">
         <v>0.256</v>
       </c>
-      <c r="I42" s="67" t="n"/>
-      <c r="J42" s="67" t="n">
+      <c r="I42" s="71" t="n"/>
+      <c r="J42" s="71" t="n">
         <v>1671</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -9944,12 +10169,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G43" s="66" t="n"/>
-      <c r="H43" s="66" t="n">
+      <c r="G43" s="70" t="n"/>
+      <c r="H43" s="70" t="n">
         <v>0.844</v>
       </c>
-      <c r="I43" s="67" t="n"/>
-      <c r="J43" s="67" t="n">
+      <c r="I43" s="71" t="n"/>
+      <c r="J43" s="71" t="n">
         <v>1025</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -9990,16 +10215,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G44" s="66" t="n">
+      <c r="G44" s="70" t="n">
         <v>0.797059</v>
       </c>
-      <c r="H44" s="66" t="n">
+      <c r="H44" s="70" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="I44" s="67" t="n">
+      <c r="I44" s="71" t="n">
         <v>1680</v>
       </c>
-      <c r="J44" s="67" t="n">
+      <c r="J44" s="71" t="n">
         <v>1356</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -10040,16 +10265,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G45" s="66" t="n">
+      <c r="G45" s="70" t="n">
         <v>0.891892</v>
       </c>
-      <c r="H45" s="66" t="n">
+      <c r="H45" s="70" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="I45" s="67" t="n">
+      <c r="I45" s="71" t="n">
         <v>1900</v>
       </c>
-      <c r="J45" s="67" t="n">
+      <c r="J45" s="71" t="n">
         <v>1769</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -10090,16 +10315,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G46" s="66" t="n">
+      <c r="G46" s="70" t="n">
         <v>0.879032</v>
       </c>
-      <c r="H46" s="66" t="n">
+      <c r="H46" s="70" t="n">
         <v>0.919</v>
       </c>
-      <c r="I46" s="67" t="n">
+      <c r="I46" s="71" t="n">
         <v>2183</v>
       </c>
-      <c r="J46" s="67" t="n">
+      <c r="J46" s="71" t="n">
         <v>2093</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -10140,16 +10365,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G47" s="66" t="n">
+      <c r="G47" s="70" t="n">
         <v>0.878788</v>
       </c>
-      <c r="H47" s="66" t="n">
+      <c r="H47" s="70" t="n">
         <v>0.889</v>
       </c>
-      <c r="I47" s="67" t="n">
+      <c r="I47" s="71" t="n">
         <v>1691</v>
       </c>
-      <c r="J47" s="67" t="n">
+      <c r="J47" s="71" t="n">
         <v>1646</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -10190,16 +10415,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G48" s="66" t="n">
+      <c r="G48" s="70" t="n">
         <v>0.829114</v>
       </c>
-      <c r="H48" s="66" t="n">
+      <c r="H48" s="70" t="n">
         <v>0.842</v>
       </c>
-      <c r="I48" s="67" t="n">
+      <c r="I48" s="71" t="n">
         <v>1663</v>
       </c>
-      <c r="J48" s="67" t="n">
+      <c r="J48" s="71" t="n">
         <v>1263</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -10240,16 +10465,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G49" s="66" t="n">
+      <c r="G49" s="70" t="n">
         <v>0.7833330000000001</v>
       </c>
-      <c r="H49" s="66" t="n">
+      <c r="H49" s="70" t="n">
         <v>0.836</v>
       </c>
-      <c r="I49" s="67" t="n">
+      <c r="I49" s="71" t="n">
         <v>1610</v>
       </c>
-      <c r="J49" s="67" t="n">
+      <c r="J49" s="71" t="n">
         <v>1339</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -10290,16 +10515,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G50" s="66" t="n">
+      <c r="G50" s="70" t="n">
         <v>0.855721</v>
       </c>
-      <c r="H50" s="66" t="n">
+      <c r="H50" s="70" t="n">
         <v>0.901</v>
       </c>
-      <c r="I50" s="67" t="n">
+      <c r="I50" s="71" t="n">
         <v>1542</v>
       </c>
-      <c r="J50" s="67" t="n">
+      <c r="J50" s="71" t="n">
         <v>1154</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -10340,16 +10565,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G51" s="66" t="n">
+      <c r="G51" s="70" t="n">
         <v>0.616708</v>
       </c>
-      <c r="H51" s="66" t="n">
+      <c r="H51" s="70" t="n">
         <v>0.514</v>
       </c>
-      <c r="I51" s="67" t="n">
+      <c r="I51" s="71" t="n">
         <v>1743</v>
       </c>
-      <c r="J51" s="67" t="n">
+      <c r="J51" s="71" t="n">
         <v>1676</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -10390,10 +10615,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G52" s="66" t="n"/>
-      <c r="H52" s="66" t="n"/>
-      <c r="I52" s="67" t="n"/>
-      <c r="J52" s="67" t="n"/>
+      <c r="G52" s="70" t="n"/>
+      <c r="H52" s="70" t="n"/>
+      <c r="I52" s="71" t="n"/>
+      <c r="J52" s="71" t="n"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10432,10 +10657,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G53" s="66" t="n"/>
-      <c r="H53" s="66" t="n"/>
-      <c r="I53" s="67" t="n"/>
-      <c r="J53" s="67" t="n"/>
+      <c r="G53" s="70" t="n"/>
+      <c r="H53" s="70" t="n"/>
+      <c r="I53" s="71" t="n"/>
+      <c r="J53" s="71" t="n"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10470,12 +10695,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G54" s="66" t="n"/>
-      <c r="H54" s="66" t="n"/>
-      <c r="I54" s="67" t="n">
+      <c r="G54" s="70" t="n"/>
+      <c r="H54" s="70" t="n"/>
+      <c r="I54" s="71" t="n">
         <v>1781</v>
       </c>
-      <c r="J54" s="67" t="n"/>
+      <c r="J54" s="71" t="n"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10514,10 +10739,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G55" s="66" t="n"/>
-      <c r="H55" s="66" t="n"/>
-      <c r="I55" s="67" t="n"/>
-      <c r="J55" s="67" t="n"/>
+      <c r="G55" s="70" t="n"/>
+      <c r="H55" s="70" t="n"/>
+      <c r="I55" s="71" t="n"/>
+      <c r="J55" s="71" t="n"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -10552,12 +10777,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G56" s="66" t="n"/>
-      <c r="H56" s="66" t="n"/>
-      <c r="I56" s="67" t="n">
+      <c r="G56" s="70" t="n"/>
+      <c r="H56" s="70" t="n"/>
+      <c r="I56" s="71" t="n">
         <v>1650</v>
       </c>
-      <c r="J56" s="67" t="n"/>
+      <c r="J56" s="71" t="n"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10596,10 +10821,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G57" s="66" t="n"/>
-      <c r="H57" s="66" t="n"/>
-      <c r="I57" s="67" t="n"/>
-      <c r="J57" s="67" t="n"/>
+      <c r="G57" s="70" t="n"/>
+      <c r="H57" s="70" t="n"/>
+      <c r="I57" s="71" t="n"/>
+      <c r="J57" s="71" t="n"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10634,10 +10859,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G58" s="66" t="n"/>
-      <c r="H58" s="66" t="n"/>
-      <c r="I58" s="67" t="n"/>
-      <c r="J58" s="67" t="n"/>
+      <c r="G58" s="70" t="n"/>
+      <c r="H58" s="70" t="n"/>
+      <c r="I58" s="71" t="n"/>
+      <c r="J58" s="71" t="n"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10672,10 +10897,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G59" s="66" t="n"/>
-      <c r="H59" s="66" t="n"/>
-      <c r="I59" s="67" t="n"/>
-      <c r="J59" s="67" t="n"/>
+      <c r="G59" s="70" t="n"/>
+      <c r="H59" s="70" t="n"/>
+      <c r="I59" s="71" t="n"/>
+      <c r="J59" s="71" t="n"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10714,12 +10939,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G60" s="66" t="n"/>
-      <c r="H60" s="66" t="n"/>
-      <c r="I60" s="67" t="n">
+      <c r="G60" s="70" t="n"/>
+      <c r="H60" s="70" t="n"/>
+      <c r="I60" s="71" t="n">
         <v>2788</v>
       </c>
-      <c r="J60" s="67" t="n"/>
+      <c r="J60" s="71" t="n"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10754,10 +10979,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G61" s="66" t="n"/>
-      <c r="H61" s="66" t="n"/>
-      <c r="I61" s="67" t="n"/>
-      <c r="J61" s="67" t="n"/>
+      <c r="G61" s="70" t="n"/>
+      <c r="H61" s="70" t="n"/>
+      <c r="I61" s="71" t="n"/>
+      <c r="J61" s="71" t="n"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10792,12 +11017,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G62" s="66" t="n"/>
-      <c r="H62" s="66" t="n">
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="67" t="n"/>
-      <c r="J62" s="67" t="n">
+      <c r="I62" s="71" t="n"/>
+      <c r="J62" s="71" t="n">
         <v>1145</v>
       </c>
       <c r="K62" t="inlineStr">
@@ -10831,10 +11056,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G63" s="66" t="n"/>
-      <c r="H63" s="66" t="n"/>
-      <c r="I63" s="67" t="n"/>
-      <c r="J63" s="67" t="n"/>
+      <c r="G63" s="70" t="n"/>
+      <c r="H63" s="70" t="n"/>
+      <c r="I63" s="71" t="n"/>
+      <c r="J63" s="71" t="n"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -10869,10 +11094,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G64" s="66" t="n"/>
-      <c r="H64" s="66" t="n"/>
-      <c r="I64" s="67" t="n"/>
-      <c r="J64" s="67" t="n"/>
+      <c r="G64" s="70" t="n"/>
+      <c r="H64" s="70" t="n"/>
+      <c r="I64" s="71" t="n"/>
+      <c r="J64" s="71" t="n"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10904,10 +11129,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G65" s="66" t="n"/>
-      <c r="H65" s="66" t="n"/>
-      <c r="I65" s="67" t="n"/>
-      <c r="J65" s="67" t="n"/>
+      <c r="G65" s="70" t="n"/>
+      <c r="H65" s="70" t="n"/>
+      <c r="I65" s="71" t="n"/>
+      <c r="J65" s="71" t="n"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -10942,10 +11167,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G66" s="66" t="n"/>
-      <c r="H66" s="66" t="n"/>
-      <c r="I66" s="67" t="n"/>
-      <c r="J66" s="67" t="n"/>
+      <c r="G66" s="70" t="n"/>
+      <c r="H66" s="70" t="n"/>
+      <c r="I66" s="71" t="n"/>
+      <c r="J66" s="71" t="n"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10980,10 +11205,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G67" s="66" t="n"/>
-      <c r="H67" s="66" t="n"/>
-      <c r="I67" s="67" t="n"/>
-      <c r="J67" s="67" t="n"/>
+      <c r="G67" s="70" t="n"/>
+      <c r="H67" s="70" t="n"/>
+      <c r="I67" s="71" t="n"/>
+      <c r="J67" s="71" t="n"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -11010,10 +11235,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G68" s="66" t="n"/>
-      <c r="H68" s="66" t="n"/>
-      <c r="I68" s="67" t="n"/>
-      <c r="J68" s="67" t="n"/>
+      <c r="G68" s="70" t="n"/>
+      <c r="H68" s="70" t="n"/>
+      <c r="I68" s="71" t="n"/>
+      <c r="J68" s="71" t="n"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11044,10 +11269,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G69" s="66" t="n"/>
-      <c r="H69" s="66" t="n"/>
-      <c r="I69" s="67" t="n"/>
-      <c r="J69" s="67" t="n"/>
+      <c r="G69" s="70" t="n"/>
+      <c r="H69" s="70" t="n"/>
+      <c r="I69" s="71" t="n"/>
+      <c r="J69" s="71" t="n"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11078,10 +11303,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G70" s="66" t="n"/>
-      <c r="H70" s="66" t="n"/>
-      <c r="I70" s="67" t="n"/>
-      <c r="J70" s="67" t="n"/>
+      <c r="G70" s="70" t="n"/>
+      <c r="H70" s="70" t="n"/>
+      <c r="I70" s="71" t="n"/>
+      <c r="J70" s="71" t="n"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11112,10 +11337,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G71" s="66" t="n"/>
-      <c r="H71" s="66" t="n"/>
-      <c r="I71" s="67" t="n"/>
-      <c r="J71" s="67" t="n"/>
+      <c r="G71" s="70" t="n"/>
+      <c r="H71" s="70" t="n"/>
+      <c r="I71" s="71" t="n"/>
+      <c r="J71" s="71" t="n"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11143,10 +11368,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G72" s="66" t="n"/>
-      <c r="H72" s="66" t="n"/>
-      <c r="I72" s="67" t="n"/>
-      <c r="J72" s="67" t="n"/>
+      <c r="G72" s="70" t="n"/>
+      <c r="H72" s="70" t="n"/>
+      <c r="I72" s="71" t="n"/>
+      <c r="J72" s="71" t="n"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11177,10 +11402,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G73" s="66" t="n"/>
-      <c r="H73" s="66" t="n"/>
-      <c r="I73" s="67" t="n"/>
-      <c r="J73" s="67" t="n"/>
+      <c r="G73" s="70" t="n"/>
+      <c r="H73" s="70" t="n"/>
+      <c r="I73" s="71" t="n"/>
+      <c r="J73" s="71" t="n"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11208,10 +11433,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G74" s="66" t="n"/>
-      <c r="H74" s="66" t="n"/>
-      <c r="I74" s="67" t="n"/>
-      <c r="J74" s="67" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="71" t="n"/>
+      <c r="J74" s="71" t="n"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11242,10 +11467,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G75" s="66" t="n"/>
-      <c r="H75" s="66" t="n"/>
-      <c r="I75" s="67" t="n"/>
-      <c r="J75" s="67" t="n"/>
+      <c r="G75" s="70" t="n"/>
+      <c r="H75" s="70" t="n"/>
+      <c r="I75" s="71" t="n"/>
+      <c r="J75" s="71" t="n"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11276,10 +11501,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G76" s="66" t="n"/>
-      <c r="H76" s="66" t="n"/>
-      <c r="I76" s="67" t="n"/>
-      <c r="J76" s="67" t="n"/>
+      <c r="G76" s="70" t="n"/>
+      <c r="H76" s="70" t="n"/>
+      <c r="I76" s="71" t="n"/>
+      <c r="J76" s="71" t="n"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11307,10 +11532,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G77" s="66" t="n"/>
-      <c r="H77" s="66" t="n"/>
-      <c r="I77" s="67" t="n"/>
-      <c r="J77" s="67" t="n"/>
+      <c r="G77" s="70" t="n"/>
+      <c r="H77" s="70" t="n"/>
+      <c r="I77" s="71" t="n"/>
+      <c r="J77" s="71" t="n"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11338,10 +11563,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G78" s="66" t="n"/>
-      <c r="H78" s="66" t="n"/>
-      <c r="I78" s="67" t="n"/>
-      <c r="J78" s="67" t="n"/>
+      <c r="G78" s="70" t="n"/>
+      <c r="H78" s="70" t="n"/>
+      <c r="I78" s="71" t="n"/>
+      <c r="J78" s="71" t="n"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11372,10 +11597,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G79" s="66" t="n"/>
-      <c r="H79" s="66" t="n"/>
-      <c r="I79" s="67" t="n"/>
-      <c r="J79" s="67" t="n"/>
+      <c r="G79" s="70" t="n"/>
+      <c r="H79" s="70" t="n"/>
+      <c r="I79" s="71" t="n"/>
+      <c r="J79" s="71" t="n"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11406,10 +11631,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G80" s="66" t="n"/>
-      <c r="H80" s="66" t="n"/>
-      <c r="I80" s="67" t="n"/>
-      <c r="J80" s="67" t="n"/>
+      <c r="G80" s="70" t="n"/>
+      <c r="H80" s="70" t="n"/>
+      <c r="I80" s="71" t="n"/>
+      <c r="J80" s="71" t="n"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11437,10 +11662,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G81" s="66" t="n"/>
-      <c r="H81" s="66" t="n"/>
-      <c r="I81" s="67" t="n"/>
-      <c r="J81" s="67" t="n"/>
+      <c r="G81" s="70" t="n"/>
+      <c r="H81" s="70" t="n"/>
+      <c r="I81" s="71" t="n"/>
+      <c r="J81" s="71" t="n"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11471,10 +11696,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G82" s="66" t="n"/>
-      <c r="H82" s="66" t="n"/>
-      <c r="I82" s="67" t="n"/>
-      <c r="J82" s="67" t="n"/>
+      <c r="G82" s="70" t="n"/>
+      <c r="H82" s="70" t="n"/>
+      <c r="I82" s="71" t="n"/>
+      <c r="J82" s="71" t="n"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11505,10 +11730,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G83" s="66" t="n"/>
-      <c r="H83" s="66" t="n"/>
-      <c r="I83" s="67" t="n"/>
-      <c r="J83" s="67" t="n"/>
+      <c r="G83" s="70" t="n"/>
+      <c r="H83" s="70" t="n"/>
+      <c r="I83" s="71" t="n"/>
+      <c r="J83" s="71" t="n"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11539,10 +11764,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G84" s="66" t="n"/>
-      <c r="H84" s="66" t="n"/>
-      <c r="I84" s="67" t="n"/>
-      <c r="J84" s="67" t="n"/>
+      <c r="G84" s="70" t="n"/>
+      <c r="H84" s="70" t="n"/>
+      <c r="I84" s="71" t="n"/>
+      <c r="J84" s="71" t="n"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11573,10 +11798,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G85" s="66" t="n"/>
-      <c r="H85" s="66" t="n"/>
-      <c r="I85" s="67" t="n"/>
-      <c r="J85" s="67" t="n"/>
+      <c r="G85" s="70" t="n"/>
+      <c r="H85" s="70" t="n"/>
+      <c r="I85" s="71" t="n"/>
+      <c r="J85" s="71" t="n"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11607,10 +11832,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G86" s="66" t="n"/>
-      <c r="H86" s="66" t="n"/>
-      <c r="I86" s="67" t="n"/>
-      <c r="J86" s="67" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="71" t="n"/>
+      <c r="J86" s="71" t="n"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11638,10 +11863,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G87" s="66" t="n"/>
-      <c r="H87" s="66" t="n"/>
-      <c r="I87" s="67" t="n"/>
-      <c r="J87" s="67" t="n"/>
+      <c r="G87" s="70" t="n"/>
+      <c r="H87" s="70" t="n"/>
+      <c r="I87" s="71" t="n"/>
+      <c r="J87" s="71" t="n"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11672,10 +11897,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G88" s="66" t="n"/>
-      <c r="H88" s="66" t="n"/>
-      <c r="I88" s="67" t="n"/>
-      <c r="J88" s="67" t="n"/>
+      <c r="G88" s="70" t="n"/>
+      <c r="H88" s="70" t="n"/>
+      <c r="I88" s="71" t="n"/>
+      <c r="J88" s="71" t="n"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11706,10 +11931,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G89" s="66" t="n"/>
-      <c r="H89" s="66" t="n"/>
-      <c r="I89" s="67" t="n"/>
-      <c r="J89" s="67" t="n"/>
+      <c r="G89" s="70" t="n"/>
+      <c r="H89" s="70" t="n"/>
+      <c r="I89" s="71" t="n"/>
+      <c r="J89" s="71" t="n"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11737,10 +11962,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G90" s="66" t="n"/>
-      <c r="H90" s="66" t="n"/>
-      <c r="I90" s="67" t="n"/>
-      <c r="J90" s="67" t="n"/>
+      <c r="G90" s="70" t="n"/>
+      <c r="H90" s="70" t="n"/>
+      <c r="I90" s="71" t="n"/>
+      <c r="J90" s="71" t="n"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11768,10 +11993,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G91" s="66" t="n"/>
-      <c r="H91" s="66" t="n"/>
-      <c r="I91" s="67" t="n"/>
-      <c r="J91" s="67" t="n"/>
+      <c r="G91" s="70" t="n"/>
+      <c r="H91" s="70" t="n"/>
+      <c r="I91" s="71" t="n"/>
+      <c r="J91" s="71" t="n"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11802,10 +12027,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G92" s="66" t="n"/>
-      <c r="H92" s="66" t="n"/>
-      <c r="I92" s="67" t="n"/>
-      <c r="J92" s="67" t="n"/>
+      <c r="G92" s="70" t="n"/>
+      <c r="H92" s="70" t="n"/>
+      <c r="I92" s="71" t="n"/>
+      <c r="J92" s="71" t="n"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11836,10 +12061,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G93" s="66" t="n"/>
-      <c r="H93" s="66" t="n"/>
-      <c r="I93" s="67" t="n"/>
-      <c r="J93" s="67" t="n"/>
+      <c r="G93" s="70" t="n"/>
+      <c r="H93" s="70" t="n"/>
+      <c r="I93" s="71" t="n"/>
+      <c r="J93" s="71" t="n"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11867,10 +12092,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G94" s="66" t="n"/>
-      <c r="H94" s="66" t="n"/>
-      <c r="I94" s="67" t="n"/>
-      <c r="J94" s="67" t="n"/>
+      <c r="G94" s="70" t="n"/>
+      <c r="H94" s="70" t="n"/>
+      <c r="I94" s="71" t="n"/>
+      <c r="J94" s="71" t="n"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11901,10 +12126,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G95" s="66" t="n"/>
-      <c r="H95" s="66" t="n"/>
-      <c r="I95" s="67" t="n"/>
-      <c r="J95" s="67" t="n"/>
+      <c r="G95" s="70" t="n"/>
+      <c r="H95" s="70" t="n"/>
+      <c r="I95" s="71" t="n"/>
+      <c r="J95" s="71" t="n"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11935,10 +12160,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G96" s="66" t="n"/>
-      <c r="H96" s="66" t="n"/>
-      <c r="I96" s="67" t="n"/>
-      <c r="J96" s="67" t="n"/>
+      <c r="G96" s="70" t="n"/>
+      <c r="H96" s="70" t="n"/>
+      <c r="I96" s="71" t="n"/>
+      <c r="J96" s="71" t="n"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11969,10 +12194,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G97" s="66" t="n"/>
-      <c r="H97" s="66" t="n"/>
-      <c r="I97" s="67" t="n"/>
-      <c r="J97" s="67" t="n"/>
+      <c r="G97" s="70" t="n"/>
+      <c r="H97" s="70" t="n"/>
+      <c r="I97" s="71" t="n"/>
+      <c r="J97" s="71" t="n"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12000,10 +12225,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G98" s="66" t="n"/>
-      <c r="H98" s="66" t="n"/>
-      <c r="I98" s="67" t="n"/>
-      <c r="J98" s="67" t="n"/>
+      <c r="G98" s="70" t="n"/>
+      <c r="H98" s="70" t="n"/>
+      <c r="I98" s="71" t="n"/>
+      <c r="J98" s="71" t="n"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12034,10 +12259,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G99" s="66" t="n"/>
-      <c r="H99" s="66" t="n"/>
-      <c r="I99" s="67" t="n"/>
-      <c r="J99" s="67" t="n"/>
+      <c r="G99" s="70" t="n"/>
+      <c r="H99" s="70" t="n"/>
+      <c r="I99" s="71" t="n"/>
+      <c r="J99" s="71" t="n"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12065,10 +12290,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G100" s="66" t="n"/>
-      <c r="H100" s="66" t="n"/>
-      <c r="I100" s="67" t="n"/>
-      <c r="J100" s="67" t="n"/>
+      <c r="G100" s="70" t="n"/>
+      <c r="H100" s="70" t="n"/>
+      <c r="I100" s="71" t="n"/>
+      <c r="J100" s="71" t="n"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12099,10 +12324,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G101" s="66" t="n"/>
-      <c r="H101" s="66" t="n"/>
-      <c r="I101" s="67" t="n"/>
-      <c r="J101" s="67" t="n"/>
+      <c r="G101" s="70" t="n"/>
+      <c r="H101" s="70" t="n"/>
+      <c r="I101" s="71" t="n"/>
+      <c r="J101" s="71" t="n"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12133,10 +12358,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G102" s="66" t="n"/>
-      <c r="H102" s="66" t="n"/>
-      <c r="I102" s="67" t="n"/>
-      <c r="J102" s="67" t="n"/>
+      <c r="G102" s="70" t="n"/>
+      <c r="H102" s="70" t="n"/>
+      <c r="I102" s="71" t="n"/>
+      <c r="J102" s="71" t="n"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12167,10 +12392,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G103" s="66" t="n"/>
-      <c r="H103" s="66" t="n"/>
-      <c r="I103" s="67" t="n"/>
-      <c r="J103" s="67" t="n"/>
+      <c r="G103" s="70" t="n"/>
+      <c r="H103" s="70" t="n"/>
+      <c r="I103" s="71" t="n"/>
+      <c r="J103" s="71" t="n"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12201,10 +12426,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G104" s="66" t="n"/>
-      <c r="H104" s="66" t="n"/>
-      <c r="I104" s="67" t="n"/>
-      <c r="J104" s="67" t="n"/>
+      <c r="G104" s="70" t="n"/>
+      <c r="H104" s="70" t="n"/>
+      <c r="I104" s="71" t="n"/>
+      <c r="J104" s="71" t="n"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12235,10 +12460,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G105" s="66" t="n"/>
-      <c r="H105" s="66" t="n"/>
-      <c r="I105" s="67" t="n"/>
-      <c r="J105" s="67" t="n"/>
+      <c r="G105" s="70" t="n"/>
+      <c r="H105" s="70" t="n"/>
+      <c r="I105" s="71" t="n"/>
+      <c r="J105" s="71" t="n"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12266,10 +12491,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G106" s="66" t="n"/>
-      <c r="H106" s="66" t="n"/>
-      <c r="I106" s="67" t="n"/>
-      <c r="J106" s="67" t="n"/>
+      <c r="G106" s="70" t="n"/>
+      <c r="H106" s="70" t="n"/>
+      <c r="I106" s="71" t="n"/>
+      <c r="J106" s="71" t="n"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12300,10 +12525,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G107" s="66" t="n"/>
-      <c r="H107" s="66" t="n"/>
-      <c r="I107" s="67" t="n"/>
-      <c r="J107" s="67" t="n"/>
+      <c r="G107" s="70" t="n"/>
+      <c r="H107" s="70" t="n"/>
+      <c r="I107" s="71" t="n"/>
+      <c r="J107" s="71" t="n"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>RealPage</t>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="I19" s="12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I49" s="20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J49" s="15" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="I87" s="36" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J87" s="31" t="inlineStr">
         <is>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -6114,15 +6114,34 @@
       <c r="H23" s="56" t="n">
         <v>1444</v>
       </c>
-      <c r="I23" s="56" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J23" s="57" t="n"/>
-      <c r="K23" s="57" t="n"/>
-      <c r="L23" s="57" t="n"/>
-      <c r="M23" s="57" t="n"/>
-      <c r="N23" s="57" t="n"/>
-      <c r="O23" s="57" t="n"/>
+      <c r="I23" s="56">
+        <f>IFERROR('Cash Flow (Annual)'!$F$4,1332)</f>
+        <v/>
+      </c>
+      <c r="J23" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$K$4,"")</f>
+        <v/>
+      </c>
+      <c r="K23" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$L$4,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$M$4,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$N$4,"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$O$4,"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$P$4,"")</f>
+        <v/>
+      </c>
       <c r="R23" s="43" t="inlineStr">
         <is>
           <t>The District at Westgate</t>
@@ -6181,12 +6200,30 @@
         <f>IFERROR(I23/H23-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="60" t="n"/>
-      <c r="K24" s="60" t="n"/>
-      <c r="L24" s="60" t="n"/>
-      <c r="M24" s="60" t="n"/>
-      <c r="N24" s="60" t="n"/>
-      <c r="O24" s="60" t="n"/>
+      <c r="J24" s="60">
+        <f>IFERROR(J23/I23-1,"")</f>
+        <v/>
+      </c>
+      <c r="K24" s="60">
+        <f>IFERROR(K23/J23-1,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="60">
+        <f>IFERROR(L23/K23-1,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="60">
+        <f>IFERROR(M23/L23-1,"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="60">
+        <f>IFERROR(N23/M23-1,"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="60">
+        <f>IFERROR(O23/N23-1,"")</f>
+        <v/>
+      </c>
       <c r="R24" s="43" t="inlineStr">
         <is>
           <t>Picerne at Palm Valley</t>
@@ -6238,15 +6275,34 @@
       <c r="H25" s="56" t="n">
         <v>1369</v>
       </c>
-      <c r="I25" s="56" t="n">
-        <v>1301</v>
-      </c>
-      <c r="J25" s="57" t="n"/>
-      <c r="K25" s="57" t="n"/>
-      <c r="L25" s="57" t="n"/>
-      <c r="M25" s="57" t="n"/>
-      <c r="N25" s="57" t="n"/>
-      <c r="O25" s="57" t="n"/>
+      <c r="I25" s="56">
+        <f>IFERROR('Cash Flow (Annual)'!$F$5,1301)</f>
+        <v/>
+      </c>
+      <c r="J25" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$K$5,"")</f>
+        <v/>
+      </c>
+      <c r="K25" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$L$5,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$M$5,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$N$5,"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$O$5,"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="57">
+        <f>IFERROR('Cash Flow (Annual)'!$P$5,"")</f>
+        <v/>
+      </c>
       <c r="R25" s="43" t="inlineStr">
         <is>
           <t>Liv Avondale</t>
@@ -6305,12 +6361,30 @@
         <f>IFERROR(I25/H25-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="60" t="n"/>
-      <c r="K26" s="60" t="n"/>
-      <c r="L26" s="60" t="n"/>
-      <c r="M26" s="60" t="n"/>
-      <c r="N26" s="60" t="n"/>
-      <c r="O26" s="60" t="n"/>
+      <c r="J26" s="60">
+        <f>IFERROR(J25/I25-1,"")</f>
+        <v/>
+      </c>
+      <c r="K26" s="60">
+        <f>IFERROR(K25/J25-1,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="60">
+        <f>IFERROR(L25/K25-1,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="60">
+        <f>IFERROR(M25/L25-1,"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="60">
+        <f>IFERROR(N25/M25-1,"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="60">
+        <f>IFERROR(O25/N25-1,"")</f>
+        <v/>
+      </c>
       <c r="R26" s="43" t="inlineStr">
         <is>
           <t>Urban 95 Parcel A</t>
@@ -6362,15 +6436,34 @@
       <c r="H27" s="61" t="n">
         <v>0.9334854638634199</v>
       </c>
-      <c r="I27" s="61" t="n">
-        <v>0.9206643232607364</v>
-      </c>
-      <c r="J27" s="62" t="n"/>
-      <c r="K27" s="62" t="n"/>
-      <c r="L27" s="62" t="n"/>
-      <c r="M27" s="62" t="n"/>
-      <c r="N27" s="62" t="n"/>
-      <c r="O27" s="62" t="n"/>
+      <c r="I27" s="61">
+        <f>IFERROR('Cash Flow (Annual)'!$F$14,0.9206643232607364)</f>
+        <v/>
+      </c>
+      <c r="J27" s="62">
+        <f>IFERROR('Cash Flow (Annual)'!$K$14,"")</f>
+        <v/>
+      </c>
+      <c r="K27" s="62">
+        <f>IFERROR('Cash Flow (Annual)'!$L$14,"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="62">
+        <f>IFERROR('Cash Flow (Annual)'!$M$14,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="62">
+        <f>IFERROR('Cash Flow (Annual)'!$N$14,"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="62">
+        <f>IFERROR('Cash Flow (Annual)'!$O$14,"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="62">
+        <f>IFERROR('Cash Flow (Annual)'!$P$14,"")</f>
+        <v/>
+      </c>
       <c r="R27" s="43" t="inlineStr">
         <is>
           <t>The Waverly</t>
@@ -6436,12 +6529,30 @@
         <f>IFERROR((I23-I25)/I23,"")</f>
         <v/>
       </c>
-      <c r="J28" s="62" t="n"/>
-      <c r="K28" s="62" t="n"/>
-      <c r="L28" s="62" t="n"/>
-      <c r="M28" s="62" t="n"/>
-      <c r="N28" s="62" t="n"/>
-      <c r="O28" s="62" t="n"/>
+      <c r="J28" s="62">
+        <f>IFERROR((J23-J25)/J23,"")</f>
+        <v/>
+      </c>
+      <c r="K28" s="62">
+        <f>IFERROR((K23-K25)/K23,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="62">
+        <f>IFERROR((L23-L25)/L23,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="62">
+        <f>IFERROR((M23-M25)/M23,"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="62">
+        <f>IFERROR((N23-N25)/N23,"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="62">
+        <f>IFERROR((O23-O25)/O23,"")</f>
+        <v/>
+      </c>
       <c r="R28" s="43" t="inlineStr">
         <is>
           <t>Fuze 623</t>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -1240,8 +1240,10 @@
       <c r="F15" s="10" t="n">
         <v>0.926</v>
       </c>
-      <c r="G15" s="11" t="n">
-        <v>1629</v>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
@@ -1744,8 +1746,10 @@
       <c r="F27" s="10" t="n">
         <v>0.961</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>2090</v>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
@@ -2256,8 +2260,10 @@
       <c r="F41" s="18" t="n">
         <v>0.89</v>
       </c>
-      <c r="G41" s="19" t="n">
-        <v>1438</v>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
@@ -2340,8 +2346,10 @@
       <c r="F43" s="18" t="n">
         <v>0.844</v>
       </c>
-      <c r="G43" s="19" t="n">
-        <v>1025</v>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
@@ -2424,8 +2432,10 @@
       <c r="F45" s="18" t="n">
         <v>0.256</v>
       </c>
-      <c r="G45" s="19" t="n">
-        <v>1671</v>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
@@ -3052,10 +3062,8 @@
         </is>
       </c>
       <c r="F62" s="26" t="n"/>
-      <c r="G62" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G62" s="27" t="n">
+        <v>2788</v>
       </c>
       <c r="H62" s="24" t="inlineStr">
         <is>
@@ -3090,10 +3098,8 @@
         </is>
       </c>
       <c r="F63" s="26" t="n"/>
-      <c r="G63" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G63" s="27" t="n">
+        <v>1650</v>
       </c>
       <c r="H63" s="24" t="inlineStr">
         <is>
@@ -3250,10 +3256,8 @@
         </is>
       </c>
       <c r="F67" s="26" t="n"/>
-      <c r="G67" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G67" s="27" t="n">
+        <v>1781</v>
       </c>
       <c r="H67" s="24" t="inlineStr">
         <is>

--- a/output/Bella_Mirage__Supply_Chart.xlsx
+++ b/output/Bella_Mirage__Supply_Chart.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="166" formatCode="0.0&quot; mi&quot;;;&quot;—&quot;"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +74,19 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF0000FF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -92,6 +103,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="FF153D64"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF595959"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="8"/>
     </font>
@@ -101,7 +124,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -110,7 +133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="FF153D64"/>
       </patternFill>
     </fill>
     <fill>
@@ -168,6 +191,16 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -195,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -303,10 +336,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -318,10 +351,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -339,7 +372,7 @@
     <xf numFmtId="3" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -354,11 +387,11 @@
     <xf numFmtId="167" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -370,20 +403,34 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5277,7 +5324,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Z63"/>
+  <dimension ref="B1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -5295,6 +5342,7 @@
     <col width="9.5" customWidth="1" min="13" max="13"/>
     <col width="9.5" customWidth="1" min="14" max="14"/>
     <col width="9.5" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="18" max="18"/>
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
@@ -6801,39 +6849,51 @@
       </c>
     </row>
     <row r="33" ht="14.4" customHeight="1">
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
-        </is>
-      </c>
-      <c r="J33" s="64" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
+        <is>
+          <t>MARKET-RENT GROWTH — TMG vs 3RD-PARTY FORECAST</t>
+        </is>
+      </c>
+      <c r="C33" s="64" t="n"/>
+      <c r="D33" s="64" t="n"/>
+      <c r="E33" s="64" t="n"/>
+      <c r="F33" s="64" t="n"/>
+      <c r="G33" s="64" t="n"/>
+      <c r="H33" s="64" t="n"/>
+      <c r="I33" s="64" t="n"/>
+      <c r="J33" s="65" t="inlineStr">
         <is>
           <t>Y1</t>
         </is>
       </c>
-      <c r="K33" s="64" t="inlineStr">
+      <c r="K33" s="65" t="inlineStr">
         <is>
           <t>Y2</t>
         </is>
       </c>
-      <c r="L33" s="64" t="inlineStr">
+      <c r="L33" s="65" t="inlineStr">
         <is>
           <t>Y3</t>
         </is>
       </c>
-      <c r="M33" s="64" t="inlineStr">
+      <c r="M33" s="65" t="inlineStr">
         <is>
           <t>Y4</t>
         </is>
       </c>
-      <c r="N33" s="64" t="inlineStr">
+      <c r="N33" s="65" t="inlineStr">
         <is>
           <t>Y5</t>
         </is>
       </c>
-      <c r="O33" s="64" t="inlineStr">
+      <c r="O33" s="65" t="inlineStr">
         <is>
           <t>Y6</t>
+        </is>
+      </c>
+      <c r="P33" s="65" t="inlineStr">
+        <is>
+          <t>AVG</t>
         </is>
       </c>
       <c r="R33" s="43" t="inlineStr">
@@ -6864,33 +6924,44 @@
       </c>
     </row>
     <row r="34" ht="14.4" customHeight="1">
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J34" s="65">
-        <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
-        <v/>
-      </c>
-      <c r="K34" s="65">
-        <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
-        <v/>
-      </c>
-      <c r="L34" s="65">
-        <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
-        <v/>
-      </c>
-      <c r="M34" s="65">
-        <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
-        <v/>
-      </c>
-      <c r="N34" s="65">
-        <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
-        <v/>
-      </c>
-      <c r="O34" s="65">
-        <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
+      <c r="B34" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CoStar</t>
+        </is>
+      </c>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="67" t="n"/>
+      <c r="E34" s="67" t="n"/>
+      <c r="F34" s="67" t="n"/>
+      <c r="G34" s="67" t="n"/>
+      <c r="H34" s="67" t="n"/>
+      <c r="I34" s="67" t="n"/>
+      <c r="J34" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$31,"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$31,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$31,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$31,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$31,"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$31,"")</f>
+        <v/>
+      </c>
+      <c r="P34" s="61">
+        <f>IFERROR(AVERAGE(J34:O34),"")</f>
         <v/>
       </c>
       <c r="R34" s="43" t="inlineStr">
@@ -6921,33 +6992,44 @@
       </c>
     </row>
     <row r="35" ht="14.4" customHeight="1">
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J35" s="65">
-        <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
-        <v/>
-      </c>
-      <c r="K35" s="65">
-        <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
-        <v/>
-      </c>
-      <c r="L35" s="65">
-        <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
-        <v/>
-      </c>
-      <c r="M35" s="65">
-        <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
-        <v/>
-      </c>
-      <c r="N35" s="65">
-        <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
-        <v/>
-      </c>
-      <c r="O35" s="65">
-        <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
+      <c r="B35" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RealPage</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="n"/>
+      <c r="D35" s="67" t="n"/>
+      <c r="E35" s="67" t="n"/>
+      <c r="F35" s="67" t="n"/>
+      <c r="G35" s="67" t="n"/>
+      <c r="H35" s="67" t="n"/>
+      <c r="I35" s="67" t="n"/>
+      <c r="J35" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$32,"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$32,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$32,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$32,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$32,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$32,"")</f>
+        <v/>
+      </c>
+      <c r="P35" s="61">
+        <f>IFERROR(AVERAGE(J35:O35),"")</f>
         <v/>
       </c>
       <c r="R35" s="43" t="inlineStr">
@@ -6982,33 +7064,44 @@
       </c>
     </row>
     <row r="36" ht="14.4" customHeight="1">
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J36" s="65">
-        <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
-        <v/>
-      </c>
-      <c r="K36" s="65">
-        <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
-        <v/>
-      </c>
-      <c r="L36" s="65">
-        <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
-        <v/>
-      </c>
-      <c r="M36" s="65">
-        <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
-        <v/>
-      </c>
-      <c r="N36" s="65">
-        <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
-        <v/>
-      </c>
-      <c r="O36" s="65">
-        <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
+      <c r="B36" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Yardi</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="n"/>
+      <c r="D36" s="67" t="n"/>
+      <c r="E36" s="67" t="n"/>
+      <c r="F36" s="67" t="n"/>
+      <c r="G36" s="67" t="n"/>
+      <c r="H36" s="67" t="n"/>
+      <c r="I36" s="67" t="n"/>
+      <c r="J36" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$33,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$33,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$33,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$33,"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$33,"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$33,"")</f>
+        <v/>
+      </c>
+      <c r="P36" s="61">
+        <f>IFERROR(AVERAGE(J36:O36),"")</f>
         <v/>
       </c>
       <c r="R36" s="43" t="inlineStr">
@@ -7039,6 +7132,46 @@
       </c>
     </row>
     <row r="37" ht="14.4" customHeight="1">
+      <c r="B37" s="66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GreenStreet</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="n"/>
+      <c r="D37" s="67" t="n"/>
+      <c r="E37" s="67" t="n"/>
+      <c r="F37" s="67" t="n"/>
+      <c r="G37" s="67" t="n"/>
+      <c r="H37" s="67" t="n"/>
+      <c r="I37" s="67" t="n"/>
+      <c r="J37" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$C$34,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$D$34,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$E$34,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$F$34,"")</f>
+        <v/>
+      </c>
+      <c r="N37" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$G$34,"")</f>
+        <v/>
+      </c>
+      <c r="O37" s="61">
+        <f>IFERROR('Rent &amp; Occ Data'!$H$34,"")</f>
+        <v/>
+      </c>
+      <c r="P37" s="61">
+        <f>IFERROR(AVERAGE(J37:O37),"")</f>
+        <v/>
+      </c>
       <c r="R37" s="43" t="inlineStr">
         <is>
           <t>Tavalo at Avondale</t>
@@ -7067,40 +7200,45 @@
       </c>
     </row>
     <row r="38" ht="14.4" customHeight="1">
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>MARKET RENT GROWTH (editable assumptions)</t>
-        </is>
-      </c>
-      <c r="J38" s="66" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="K38" s="66" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="L38" s="66" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="M38" s="66" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="N38" s="66" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
-      <c r="O38" s="66" t="inlineStr">
-        <is>
-          <t>Y6</t>
-        </is>
+      <c r="B38" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Consensus (4-source avg)</t>
+        </is>
+      </c>
+      <c r="C38" s="69" t="n"/>
+      <c r="D38" s="69" t="n"/>
+      <c r="E38" s="69" t="n"/>
+      <c r="F38" s="69" t="n"/>
+      <c r="G38" s="69" t="n"/>
+      <c r="H38" s="69" t="n"/>
+      <c r="I38" s="69" t="n"/>
+      <c r="J38" s="70">
+        <f>IFERROR(AVERAGE(J34:J37),"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="70">
+        <f>IFERROR(AVERAGE(K34:K37),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="70">
+        <f>IFERROR(AVERAGE(L34:L37),"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="70">
+        <f>IFERROR(AVERAGE(M34:M37),"")</f>
+        <v/>
+      </c>
+      <c r="N38" s="70">
+        <f>IFERROR(AVERAGE(N34:N37),"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="70">
+        <f>IFERROR(AVERAGE(O34:O37),"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="70">
+        <f>IFERROR(AVERAGE(P34:P37),"")</f>
+        <v/>
       </c>
       <c r="R38" s="43" t="inlineStr">
         <is>
@@ -7130,28 +7268,45 @@
       </c>
     </row>
     <row r="39" ht="14.4" customHeight="1">
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J39" s="67" t="n">
-        <v>-0.0025</v>
-      </c>
-      <c r="K39" s="67" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="L39" s="67" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="M39" s="67" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="N39" s="67" t="n">
-        <v>0.0275</v>
-      </c>
-      <c r="O39" s="67" t="n">
-        <v>0.0175</v>
+      <c r="B39" s="71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TMG — our market-rent growth  ◄</t>
+        </is>
+      </c>
+      <c r="C39" s="72" t="n"/>
+      <c r="D39" s="72" t="n"/>
+      <c r="E39" s="72" t="n"/>
+      <c r="F39" s="72" t="n"/>
+      <c r="G39" s="72" t="n"/>
+      <c r="H39" s="72" t="n"/>
+      <c r="I39" s="72" t="n"/>
+      <c r="J39" s="73">
+        <f>IFERROR(J24,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="73">
+        <f>IFERROR(K24,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="73">
+        <f>IFERROR(L24,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="73">
+        <f>IFERROR(M24,"")</f>
+        <v/>
+      </c>
+      <c r="N39" s="73">
+        <f>IFERROR(N24,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="73">
+        <f>IFERROR(O24,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="73">
+        <f>IFERROR(AVERAGE(J39:O39),"")</f>
+        <v/>
       </c>
       <c r="R39" s="43" t="inlineStr">
         <is>
@@ -7181,29 +7336,6 @@
       </c>
     </row>
     <row r="40" ht="14.4" customHeight="1">
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J40" s="67" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K40" s="67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L40" s="67" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M40" s="67" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N40" s="67" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O40" s="67" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R40" s="43" t="inlineStr">
         <is>
           <t>SimonMed Development I</t>
@@ -7232,28 +7364,10 @@
       </c>
     </row>
     <row r="41" ht="14.4" customHeight="1">
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J41" s="67" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K41" s="67" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L41" s="67" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M41" s="67" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N41" s="67" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O41" s="67" t="n">
-        <v>0.04</v>
+      <c r="B41" s="74" t="inlineStr">
+        <is>
+          <t>▸ SCENARIO INPUTS — Bear / Base / Bull  (implied occupancy, rent-growth &amp; concession assumptions — click + to expand)</t>
+        </is>
       </c>
       <c r="R41" s="43" t="inlineStr">
         <is>
@@ -7282,10 +7396,40 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="14.4" customHeight="1">
+    <row r="42" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B42" s="39" t="inlineStr">
         <is>
-          <t>CONCESSIONS % — forward assumption (editable)</t>
+          <t>IMPLIED 5-MI OCCUPANCY BY DEMAND SCENARIO</t>
+        </is>
+      </c>
+      <c r="J42" s="75" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K42" s="75" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L42" s="75" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M42" s="75" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N42" s="75" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O42" s="75" t="inlineStr">
+        <is>
+          <t>Y6</t>
         </is>
       </c>
       <c r="R42" s="43" t="inlineStr">
@@ -7315,29 +7459,35 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
+    <row r="43" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B43" s="39" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="J43" s="67" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K43" s="67" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L43" s="67" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="M43" s="67" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="N43" s="67" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="O43" s="67" t="n">
-        <v>0.035</v>
+      <c r="J43" s="76">
+        <f>MIN($C$6,($I$31+$C$8*1)/J30)</f>
+        <v/>
+      </c>
+      <c r="K43" s="76">
+        <f>MIN($C$6,($I$31+$C$8*2)/K30)</f>
+        <v/>
+      </c>
+      <c r="L43" s="76">
+        <f>MIN($C$6,($I$31+$C$8*3)/L30)</f>
+        <v/>
+      </c>
+      <c r="M43" s="76">
+        <f>MIN($C$6,($I$31+$C$8*4)/M30)</f>
+        <v/>
+      </c>
+      <c r="N43" s="76">
+        <f>MIN($C$6,($I$31+$C$8*5)/N30)</f>
+        <v/>
+      </c>
+      <c r="O43" s="76">
+        <f>MIN($C$6,($I$31+$C$8*6)/O30)</f>
+        <v/>
       </c>
       <c r="R43" s="43" t="inlineStr">
         <is>
@@ -7366,29 +7516,35 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="14.4" customHeight="1">
+    <row r="44" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B44" s="39" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="J44" s="67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K44" s="67" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L44" s="67" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="M44" s="67" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N44" s="67" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O44" s="67" t="n">
-        <v>0.005</v>
+      <c r="J44" s="76">
+        <f>MIN($C$6,($I$31+$C$9*1)/J30)</f>
+        <v/>
+      </c>
+      <c r="K44" s="76">
+        <f>MIN($C$6,($I$31+$C$9*2)/K30)</f>
+        <v/>
+      </c>
+      <c r="L44" s="76">
+        <f>MIN($C$6,($I$31+$C$9*3)/L30)</f>
+        <v/>
+      </c>
+      <c r="M44" s="76">
+        <f>MIN($C$6,($I$31+$C$9*4)/M30)</f>
+        <v/>
+      </c>
+      <c r="N44" s="76">
+        <f>MIN($C$6,($I$31+$C$9*5)/N30)</f>
+        <v/>
+      </c>
+      <c r="O44" s="76">
+        <f>MIN($C$6,($I$31+$C$9*6)/O30)</f>
+        <v/>
       </c>
       <c r="R44" s="43" t="inlineStr">
         <is>
@@ -7417,29 +7573,35 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="14.4" customHeight="1">
+    <row r="45" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B45" s="39" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="J45" s="67" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K45" s="67" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="67" t="n">
-        <v>0</v>
+      <c r="J45" s="76">
+        <f>MIN($C$6,($I$31+$C$10*1)/J30)</f>
+        <v/>
+      </c>
+      <c r="K45" s="76">
+        <f>MIN($C$6,($I$31+$C$10*2)/K30)</f>
+        <v/>
+      </c>
+      <c r="L45" s="76">
+        <f>MIN($C$6,($I$31+$C$10*3)/L30)</f>
+        <v/>
+      </c>
+      <c r="M45" s="76">
+        <f>MIN($C$6,($I$31+$C$10*4)/M30)</f>
+        <v/>
+      </c>
+      <c r="N45" s="76">
+        <f>MIN($C$6,($I$31+$C$10*5)/N30)</f>
+        <v/>
+      </c>
+      <c r="O45" s="76">
+        <f>MIN($C$6,($I$31+$C$10*6)/O30)</f>
+        <v/>
       </c>
       <c r="R45" s="43" t="inlineStr">
         <is>
@@ -7468,12 +7630,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="14.4" customHeight="1">
-      <c r="B46" s="39" t="inlineStr">
-        <is>
-          <t>EFFECTIVE RENT GROWTH (derived)</t>
-        </is>
-      </c>
+    <row r="46" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="R46" s="43" t="inlineStr">
         <is>
           <t>McDowell Villas</t>
@@ -7501,35 +7658,41 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="14.4" customHeight="1">
+    <row r="47" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="J47" s="65">
-        <f>(1+J39)*(1-J43)-1</f>
-        <v/>
-      </c>
-      <c r="K47" s="65">
-        <f>(1+K39)*(1-K43)/(1-J43)-1</f>
-        <v/>
-      </c>
-      <c r="L47" s="65">
-        <f>(1+L39)*(1-L43)/(1-K43)-1</f>
-        <v/>
-      </c>
-      <c r="M47" s="65">
-        <f>(1+M39)*(1-M43)/(1-L43)-1</f>
-        <v/>
-      </c>
-      <c r="N47" s="65">
-        <f>(1+N39)*(1-N43)/(1-M43)-1</f>
-        <v/>
-      </c>
-      <c r="O47" s="65">
-        <f>(1+O39)*(1-O43)/(1-N43)-1</f>
-        <v/>
+          <t>MARKET RENT GROWTH (editable assumptions)</t>
+        </is>
+      </c>
+      <c r="J47" s="77" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="K47" s="77" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="L47" s="77" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="M47" s="77" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="N47" s="77" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="O47" s="77" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
       </c>
       <c r="R47" s="43" t="inlineStr">
         <is>
@@ -7558,35 +7721,29 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="14.4" customHeight="1">
+    <row r="48" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="J48" s="65">
-        <f>(1+J40)*(1-J44)-1</f>
-        <v/>
-      </c>
-      <c r="K48" s="65">
-        <f>(1+K40)*(1-K44)/(1-J44)-1</f>
-        <v/>
-      </c>
-      <c r="L48" s="65">
-        <f>(1+L40)*(1-L44)/(1-K44)-1</f>
-        <v/>
-      </c>
-      <c r="M48" s="65">
-        <f>(1+M40)*(1-M44)/(1-L44)-1</f>
-        <v/>
-      </c>
-      <c r="N48" s="65">
-        <f>(1+N40)*(1-N44)/(1-M44)-1</f>
-        <v/>
-      </c>
-      <c r="O48" s="65">
-        <f>(1+O40)*(1-O44)/(1-N44)-1</f>
-        <v/>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J48" s="78" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="K48" s="78" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="L48" s="78" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="M48" s="78" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="N48" s="78" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="O48" s="78" t="n">
+        <v>0.0175</v>
       </c>
       <c r="R48" s="43" t="inlineStr">
         <is>
@@ -7615,35 +7772,29 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="14.4" customHeight="1">
+    <row r="49" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="J49" s="65">
-        <f>(1+J41)*(1-J45)-1</f>
-        <v/>
-      </c>
-      <c r="K49" s="65">
-        <f>(1+K41)*(1-K45)/(1-J45)-1</f>
-        <v/>
-      </c>
-      <c r="L49" s="65">
-        <f>(1+L41)*(1-L45)/(1-K45)-1</f>
-        <v/>
-      </c>
-      <c r="M49" s="65">
-        <f>(1+M41)*(1-M45)/(1-L45)-1</f>
-        <v/>
-      </c>
-      <c r="N49" s="65">
-        <f>(1+N41)*(1-N45)/(1-M45)-1</f>
-        <v/>
-      </c>
-      <c r="O49" s="65">
-        <f>(1+O41)*(1-O45)/(1-N45)-1</f>
-        <v/>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J49" s="78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K49" s="78" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L49" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M49" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N49" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O49" s="78" t="n">
+        <v>0.03</v>
       </c>
       <c r="R49" s="43" t="inlineStr">
         <is>
@@ -7676,7 +7827,30 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="14.4" customHeight="1">
+    <row r="50" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J50" s="78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K50" s="78" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L50" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M50" s="78" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N50" s="78" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O50" s="78" t="n">
+        <v>0.04</v>
+      </c>
       <c r="R50" s="43" t="inlineStr">
         <is>
           <t>Northern 107</t>
@@ -7708,10 +7882,10 @@
         <v/>
       </c>
     </row>
-    <row r="51" ht="14.4" customHeight="1">
-      <c r="B51" s="66" t="inlineStr">
-        <is>
-          <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
+    <row r="51" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>CONCESSIONS % — forward assumption (editable)</t>
         </is>
       </c>
       <c r="R51" s="43" t="inlineStr">
@@ -7742,15 +7916,28 @@
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B52" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
-        </is>
-      </c>
-      <c r="E52" s="68" t="inlineStr">
-        <is>
-          <t>CoStar</t>
-        </is>
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J52" s="78" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K52" s="78" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L52" s="78" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="M52" s="78" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="N52" s="78" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="O52" s="78" t="n">
+        <v>0.035</v>
       </c>
       <c r="R52" s="43" t="inlineStr">
         <is>
@@ -7778,15 +7965,28 @@
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B53" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
-        </is>
-      </c>
-      <c r="E53" s="68" t="inlineStr">
-        <is>
-          <t>CoStar</t>
-        </is>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J53" s="78" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K53" s="78" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L53" s="78" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="M53" s="78" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N53" s="78" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O53" s="78" t="n">
+        <v>0.005</v>
       </c>
       <c r="R53" s="43" t="inlineStr">
         <is>
@@ -7814,15 +8014,28 @@
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B54" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
-        </is>
-      </c>
-      <c r="E54" s="68" t="inlineStr">
-        <is>
-          <t>CoStar</t>
-        </is>
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J54" s="78" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K54" s="78" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L54" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="78" t="n">
+        <v>0</v>
       </c>
       <c r="R54" s="43" t="inlineStr">
         <is>
@@ -7850,14 +8063,9 @@
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B55" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
-        </is>
-      </c>
-      <c r="E55" s="68" t="inlineStr">
-        <is>
-          <t>CoStar</t>
+      <c r="B55" s="39" t="inlineStr">
+        <is>
+          <t>EFFECTIVE RENT GROWTH (derived)</t>
         </is>
       </c>
       <c r="R55" s="43" t="inlineStr">
@@ -7886,15 +8094,34 @@
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B56" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
-        </is>
-      </c>
-      <c r="E56" s="68" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
+      <c r="B56" s="39" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="J56" s="76">
+        <f>(1+J48)*(1-J52)-1</f>
+        <v/>
+      </c>
+      <c r="K56" s="76">
+        <f>(1+K48)*(1-K52)/(1-J52)-1</f>
+        <v/>
+      </c>
+      <c r="L56" s="76">
+        <f>(1+L48)*(1-L52)/(1-K52)-1</f>
+        <v/>
+      </c>
+      <c r="M56" s="76">
+        <f>(1+M48)*(1-M52)/(1-L52)-1</f>
+        <v/>
+      </c>
+      <c r="N56" s="76">
+        <f>(1+N48)*(1-N52)/(1-M52)-1</f>
+        <v/>
+      </c>
+      <c r="O56" s="76">
+        <f>(1+O48)*(1-O52)/(1-N52)-1</f>
+        <v/>
       </c>
       <c r="R56" s="43" t="inlineStr">
         <is>
@@ -7922,15 +8149,34 @@
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B57" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
-        </is>
-      </c>
-      <c r="E57" s="68" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
+      <c r="B57" s="39" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="J57" s="76">
+        <f>(1+J49)*(1-J53)-1</f>
+        <v/>
+      </c>
+      <c r="K57" s="76">
+        <f>(1+K49)*(1-K53)/(1-J53)-1</f>
+        <v/>
+      </c>
+      <c r="L57" s="76">
+        <f>(1+L49)*(1-L53)/(1-K53)-1</f>
+        <v/>
+      </c>
+      <c r="M57" s="76">
+        <f>(1+M49)*(1-M53)/(1-L53)-1</f>
+        <v/>
+      </c>
+      <c r="N57" s="76">
+        <f>(1+N49)*(1-N53)/(1-M53)-1</f>
+        <v/>
+      </c>
+      <c r="O57" s="76">
+        <f>(1+O49)*(1-O53)/(1-N53)-1</f>
+        <v/>
       </c>
       <c r="R57" s="43" t="inlineStr">
         <is>
@@ -7958,15 +8204,34 @@
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B58" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
-        </is>
-      </c>
-      <c r="E58" s="68" t="inlineStr">
-        <is>
-          <t>HD</t>
-        </is>
+      <c r="B58" s="39" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="J58" s="76">
+        <f>(1+J50)*(1-J54)-1</f>
+        <v/>
+      </c>
+      <c r="K58" s="76">
+        <f>(1+K50)*(1-K54)/(1-J54)-1</f>
+        <v/>
+      </c>
+      <c r="L58" s="76">
+        <f>(1+L50)*(1-L54)/(1-K54)-1</f>
+        <v/>
+      </c>
+      <c r="M58" s="76">
+        <f>(1+M50)*(1-M54)/(1-L54)-1</f>
+        <v/>
+      </c>
+      <c r="N58" s="76">
+        <f>(1+N50)*(1-N54)/(1-M54)-1</f>
+        <v/>
+      </c>
+      <c r="O58" s="76">
+        <f>(1+O50)*(1-O54)/(1-N54)-1</f>
+        <v/>
       </c>
       <c r="R58" s="43" t="inlineStr">
         <is>
@@ -7993,17 +8258,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B59" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
-        </is>
-      </c>
-      <c r="E59" s="68" t="inlineStr">
-        <is>
-          <t>2,307 / 1,251</t>
-        </is>
-      </c>
+    <row r="59" ht="14.4" customHeight="1">
       <c r="R59" s="43" t="inlineStr">
         <is>
           <t>I-10 Innovation Center II</t>
@@ -8029,10 +8284,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
-      <c r="B60" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
+    <row r="60" ht="14.4" customHeight="1">
+      <c r="B60" s="77" t="inlineStr">
+        <is>
+          <t>▸ DETAIL: subject rent source by year &amp; reconciliation (grouped — click − to collapse)</t>
         </is>
       </c>
       <c r="R60" s="43" t="inlineStr">
@@ -8060,7 +8315,17 @@
         <v/>
       </c>
     </row>
-    <row r="61" ht="14.4" customHeight="1">
+    <row r="61" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B61" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y6  Q3 2019–Q2 2020</t>
+        </is>
+      </c>
+      <c r="E61" s="79" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
       <c r="R61" s="43" t="inlineStr">
         <is>
           <t>SimonMed Development II</t>
@@ -8086,7 +8351,17 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="14.4" customHeight="1">
+    <row r="62" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B62" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y5  Q3 2020–Q2 2021</t>
+        </is>
+      </c>
+      <c r="E62" s="79" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
       <c r="R62" s="43" t="inlineStr">
         <is>
           <t>182 South 95th Avenue</t>
@@ -8112,7 +8387,17 @@
         <v/>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B63" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y4  Q3 2021–Q2 2022</t>
+        </is>
+      </c>
+      <c r="E63" s="79" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
       <c r="R63" s="43" t="inlineStr">
         <is>
           <t>Envision Encore</t>
@@ -8138,6 +8423,75 @@
         <v/>
       </c>
     </row>
+    <row r="64" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B64" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y3  Q3 2022–Q2 2023</t>
+        </is>
+      </c>
+      <c r="E64" s="79" t="inlineStr">
+        <is>
+          <t>CoStar</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B65" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y2  Q3 2023–Q2 2024</t>
+        </is>
+      </c>
+      <c r="E65" s="79" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B66" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -Y1  Q3 2024–Q2 2025</t>
+        </is>
+      </c>
+      <c r="E66" s="79" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B67" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Y0  Q3 2025–Q2 2026</t>
+        </is>
+      </c>
+      <c r="E67" s="79" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B68" s="79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  UC scheduled vs CoStar UC</t>
+        </is>
+      </c>
+      <c r="E68" s="79" t="inlineStr">
+        <is>
+          <t>2,307 / 1,251</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1" ht="14.4" customHeight="1">
+      <c r="B69" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  As-of 2026 Q2 QTD is partial (QTD); occupancy is point-in-time, Y0 flow sums partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="14.4" customHeight="1"/>
+    <row r="71" ht="14.4" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:O2"/>
@@ -8178,62 +8532,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="69" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B1" s="69" t="inlineStr">
+      <c r="B1" s="65" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="C1" s="69" t="inlineStr">
+      <c r="C1" s="65" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="69" t="inlineStr">
+      <c r="D1" s="65" t="inlineStr">
         <is>
           <t>Year Built</t>
         </is>
       </c>
-      <c r="E1" s="69" t="inlineStr">
+      <c r="E1" s="65" t="inlineStr">
         <is>
           <t>Est. Delivery</t>
         </is>
       </c>
-      <c r="F1" s="69" t="inlineStr">
+      <c r="F1" s="65" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="G1" s="69" t="inlineStr">
+      <c r="G1" s="65" t="inlineStr">
         <is>
           <t>CoStar Occ</t>
         </is>
       </c>
-      <c r="H1" s="69" t="inlineStr">
+      <c r="H1" s="65" t="inlineStr">
         <is>
           <t>RealPage Occ</t>
         </is>
       </c>
-      <c r="I1" s="69" t="inlineStr">
+      <c r="I1" s="65" t="inlineStr">
         <is>
           <t>CoStar Ask Rent</t>
         </is>
       </c>
-      <c r="J1" s="69" t="inlineStr">
+      <c r="J1" s="65" t="inlineStr">
         <is>
           <t>RealPage Eff Rent</t>
         </is>
       </c>
-      <c r="K1" s="69" t="inlineStr">
+      <c r="K1" s="65" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="L1" s="69" t="inlineStr">
+      <c r="L1" s="65" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -8266,16 +8620,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G2" s="70" t="n">
+      <c r="G2" s="80" t="n">
         <v>0.924324</v>
       </c>
-      <c r="H2" s="70" t="n">
+      <c r="H2" s="80" t="n">
         <v>0.924</v>
       </c>
-      <c r="I2" s="71" t="n">
+      <c r="I2" s="81" t="n">
         <v>1750</v>
       </c>
-      <c r="J2" s="71" t="n">
+      <c r="J2" s="81" t="n">
         <v>1875</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -8316,12 +8670,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G3" s="70" t="n"/>
-      <c r="H3" s="70" t="n">
+      <c r="G3" s="80" t="n"/>
+      <c r="H3" s="80" t="n">
         <v>0.961</v>
       </c>
-      <c r="I3" s="71" t="n"/>
-      <c r="J3" s="71" t="n">
+      <c r="I3" s="81" t="n"/>
+      <c r="J3" s="81" t="n">
         <v>2090</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -8362,16 +8716,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G4" s="70" t="n">
+      <c r="G4" s="80" t="n">
         <v>0.8518520000000001</v>
       </c>
-      <c r="H4" s="70" t="n">
+      <c r="H4" s="80" t="n">
         <v>0.877</v>
       </c>
-      <c r="I4" s="71" t="n">
+      <c r="I4" s="81" t="n">
         <v>1576</v>
       </c>
-      <c r="J4" s="71" t="n">
+      <c r="J4" s="81" t="n">
         <v>1211</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -8412,16 +8766,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G5" s="70" t="n">
+      <c r="G5" s="80" t="n">
         <v>0.7634730000000001</v>
       </c>
-      <c r="H5" s="70" t="n">
+      <c r="H5" s="80" t="n">
         <v>0.916</v>
       </c>
-      <c r="I5" s="71" t="n">
+      <c r="I5" s="81" t="n">
         <v>2026</v>
       </c>
-      <c r="J5" s="71" t="n">
+      <c r="J5" s="81" t="n">
         <v>1385</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -8462,16 +8816,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G6" s="70" t="n">
+      <c r="G6" s="80" t="n">
         <v>0.895833</v>
       </c>
-      <c r="H6" s="70" t="n">
+      <c r="H6" s="80" t="n">
         <v>0.966</v>
       </c>
-      <c r="I6" s="71" t="n">
+      <c r="I6" s="81" t="n">
         <v>1429</v>
       </c>
-      <c r="J6" s="71" t="n">
+      <c r="J6" s="81" t="n">
         <v>1313</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -8512,16 +8866,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G7" s="70" t="n">
+      <c r="G7" s="80" t="n">
         <v>0.949309</v>
       </c>
-      <c r="H7" s="70" t="n">
+      <c r="H7" s="80" t="n">
         <v>0.968</v>
       </c>
-      <c r="I7" s="71" t="n">
+      <c r="I7" s="81" t="n">
         <v>1576</v>
       </c>
-      <c r="J7" s="71" t="n">
+      <c r="J7" s="81" t="n">
         <v>1602</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -8562,16 +8916,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G8" s="70" t="n">
+      <c r="G8" s="80" t="n">
         <v>0.773196</v>
       </c>
-      <c r="H8" s="70" t="n">
+      <c r="H8" s="80" t="n">
         <v>0.918</v>
       </c>
-      <c r="I8" s="71" t="n">
+      <c r="I8" s="81" t="n">
         <v>1874</v>
       </c>
-      <c r="J8" s="71" t="n">
+      <c r="J8" s="81" t="n">
         <v>1794</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -8612,16 +8966,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G9" s="70" t="n">
+      <c r="G9" s="80" t="n">
         <v>0.784247</v>
       </c>
-      <c r="H9" s="70" t="n">
+      <c r="H9" s="80" t="n">
         <v>0.87</v>
       </c>
-      <c r="I9" s="71" t="n">
+      <c r="I9" s="81" t="n">
         <v>1516</v>
       </c>
-      <c r="J9" s="71" t="n">
+      <c r="J9" s="81" t="n">
         <v>1517</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -8662,16 +9016,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G10" s="70" t="n">
+      <c r="G10" s="80" t="n">
         <v>0.8992249999999999</v>
       </c>
-      <c r="H10" s="70" t="n">
+      <c r="H10" s="80" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="I10" s="71" t="n">
+      <c r="I10" s="81" t="n">
         <v>1567</v>
       </c>
-      <c r="J10" s="71" t="n">
+      <c r="J10" s="81" t="n">
         <v>1591</v>
       </c>
       <c r="K10" t="inlineStr">
@@ -8712,16 +9066,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G11" s="70" t="n">
+      <c r="G11" s="80" t="n">
         <v>0.9520960000000001</v>
       </c>
-      <c r="H11" s="70" t="n">
+      <c r="H11" s="80" t="n">
         <v>0.946</v>
       </c>
-      <c r="I11" s="71" t="n">
+      <c r="I11" s="81" t="n">
         <v>1607</v>
       </c>
-      <c r="J11" s="71" t="n">
+      <c r="J11" s="81" t="n">
         <v>1388</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -8762,16 +9116,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G12" s="70" t="n">
+      <c r="G12" s="80" t="n">
         <v>0.920455</v>
       </c>
-      <c r="H12" s="70" t="n">
+      <c r="H12" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="71" t="n">
+      <c r="I12" s="81" t="n">
         <v>1526</v>
       </c>
-      <c r="J12" s="71" t="n">
+      <c r="J12" s="81" t="n">
         <v>1263</v>
       </c>
       <c r="K12" t="inlineStr">
@@ -8812,16 +9166,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G13" s="70" t="n">
+      <c r="G13" s="80" t="n">
         <v>0.934483</v>
       </c>
-      <c r="H13" s="70" t="n">
+      <c r="H13" s="80" t="n">
         <v>0.959</v>
       </c>
-      <c r="I13" s="71" t="n">
+      <c r="I13" s="81" t="n">
         <v>2812</v>
       </c>
-      <c r="J13" s="71" t="n">
+      <c r="J13" s="81" t="n">
         <v>2575</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -8862,16 +9216,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G14" s="70" t="n">
+      <c r="G14" s="80" t="n">
         <v>0.935829</v>
       </c>
-      <c r="H14" s="70" t="n">
+      <c r="H14" s="80" t="n">
         <v>0.963</v>
       </c>
-      <c r="I14" s="71" t="n">
+      <c r="I14" s="81" t="n">
         <v>1964</v>
       </c>
-      <c r="J14" s="71" t="n">
+      <c r="J14" s="81" t="n">
         <v>1902</v>
       </c>
       <c r="K14" t="inlineStr">
@@ -8912,16 +9266,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G15" s="70" t="n">
+      <c r="G15" s="80" t="n">
         <v>0.892045</v>
       </c>
-      <c r="H15" s="70" t="n">
+      <c r="H15" s="80" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="I15" s="71" t="n">
+      <c r="I15" s="81" t="n">
         <v>1632</v>
       </c>
-      <c r="J15" s="71" t="n">
+      <c r="J15" s="81" t="n">
         <v>1236</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -8962,16 +9316,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G16" s="70" t="n">
+      <c r="G16" s="80" t="n">
         <v>0.926471</v>
       </c>
-      <c r="H16" s="70" t="n">
+      <c r="H16" s="80" t="n">
         <v>0.967</v>
       </c>
-      <c r="I16" s="71" t="n">
+      <c r="I16" s="81" t="n">
         <v>1820</v>
       </c>
-      <c r="J16" s="71" t="n">
+      <c r="J16" s="81" t="n">
         <v>1597</v>
       </c>
       <c r="K16" t="inlineStr">
@@ -9012,16 +9366,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G17" s="70" t="n">
+      <c r="G17" s="80" t="n">
         <v>0.9494050000000001</v>
       </c>
-      <c r="H17" s="70" t="n">
+      <c r="H17" s="80" t="n">
         <v>0.949</v>
       </c>
-      <c r="I17" s="71" t="n">
+      <c r="I17" s="81" t="n">
         <v>1335</v>
       </c>
-      <c r="J17" s="71" t="n">
+      <c r="J17" s="81" t="n">
         <v>1325</v>
       </c>
       <c r="K17" t="inlineStr">
@@ -9062,14 +9416,14 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G18" s="70" t="n">
+      <c r="G18" s="80" t="n">
         <v>0.893204</v>
       </c>
-      <c r="H18" s="70" t="n"/>
-      <c r="I18" s="71" t="n">
+      <c r="H18" s="80" t="n"/>
+      <c r="I18" s="81" t="n">
         <v>2523</v>
       </c>
-      <c r="J18" s="71" t="n"/>
+      <c r="J18" s="81" t="n"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -9108,12 +9462,12 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G19" s="70" t="n"/>
-      <c r="H19" s="70" t="n">
+      <c r="G19" s="80" t="n"/>
+      <c r="H19" s="80" t="n">
         <v>0.926</v>
       </c>
-      <c r="I19" s="71" t="n"/>
-      <c r="J19" s="71" t="n">
+      <c r="I19" s="81" t="n"/>
+      <c r="J19" s="81" t="n">
         <v>1629</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -9154,16 +9508,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G20" s="70" t="n">
+      <c r="G20" s="80" t="n">
         <v>0.951977</v>
       </c>
-      <c r="H20" s="70" t="n">
+      <c r="H20" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="71" t="n">
+      <c r="I20" s="81" t="n">
         <v>1574</v>
       </c>
-      <c r="J20" s="71" t="n">
+      <c r="J20" s="81" t="n">
         <v>1583</v>
       </c>
       <c r="K20" t="inlineStr">
@@ -9204,16 +9558,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G21" s="70" t="n">
+      <c r="G21" s="80" t="n">
         <v>0.902098</v>
       </c>
-      <c r="H21" s="70" t="n">
+      <c r="H21" s="80" t="n">
         <v>0.955</v>
       </c>
-      <c r="I21" s="71" t="n">
+      <c r="I21" s="81" t="n">
         <v>1338</v>
       </c>
-      <c r="J21" s="71" t="n">
+      <c r="J21" s="81" t="n">
         <v>1167</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -9254,16 +9608,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G22" s="70" t="n">
+      <c r="G22" s="80" t="n">
         <v>0.984375</v>
       </c>
-      <c r="H22" s="70" t="n">
+      <c r="H22" s="80" t="n">
         <v>0.984</v>
       </c>
-      <c r="I22" s="71" t="n">
+      <c r="I22" s="81" t="n">
         <v>2442</v>
       </c>
-      <c r="J22" s="71" t="n">
+      <c r="J22" s="81" t="n">
         <v>2261</v>
       </c>
       <c r="K22" t="inlineStr">
@@ -9304,16 +9658,16 @@
           <t>STABILIZED / STABILIZING</t>
         </is>
       </c>
-      <c r="G23" s="70" t="n">
+      <c r="G23" s="80" t="n">
         <v>0.989362</v>
       </c>
-      <c r="H23" s="70" t="n">
+      <c r="H23" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="71" t="n">
+      <c r="I23" s="81" t="n">
         <v>1913</v>
       </c>
-      <c r="J23" s="71" t="n">
+      <c r="J23" s="81" t="n">
         <v>1982</v>
       </c>
       <c r="K23" t="inlineStr">
@@ -9350,16 +9704,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G24" s="70" t="n">
+      <c r="G24" s="80" t="n">
         <v>0.4461540000000001</v>
       </c>
-      <c r="H24" s="70" t="n">
+      <c r="H24" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="71" t="n">
+      <c r="I24" s="81" t="n">
         <v>1829</v>
       </c>
-      <c r="J24" s="71" t="n">
+      <c r="J24" s="81" t="n">
         <v>1681</v>
       </c>
       <c r="K24" t="inlineStr">
@@ -9400,16 +9754,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G25" s="70" t="n">
+      <c r="G25" s="80" t="n">
         <v>0.05660399999999999</v>
       </c>
-      <c r="H25" s="70" t="n">
+      <c r="H25" s="80" t="n">
         <v>0.208</v>
       </c>
-      <c r="I25" s="71" t="n">
+      <c r="I25" s="81" t="n">
         <v>2966</v>
       </c>
-      <c r="J25" s="71" t="n">
+      <c r="J25" s="81" t="n">
         <v>1938</v>
       </c>
       <c r="K25" t="inlineStr">
@@ -9450,16 +9804,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G26" s="70" t="n">
+      <c r="G26" s="80" t="n">
         <v>0.273504</v>
       </c>
-      <c r="H26" s="70" t="n">
+      <c r="H26" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="71" t="n">
+      <c r="I26" s="81" t="n">
         <v>2537</v>
       </c>
-      <c r="J26" s="71" t="n">
+      <c r="J26" s="81" t="n">
         <v>2273</v>
       </c>
       <c r="K26" t="inlineStr">
@@ -9500,14 +9854,14 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G27" s="70" t="n">
+      <c r="G27" s="80" t="n">
         <v>0.1333329999999999</v>
       </c>
-      <c r="H27" s="70" t="n"/>
-      <c r="I27" s="71" t="n">
+      <c r="H27" s="80" t="n"/>
+      <c r="I27" s="81" t="n">
         <v>1411</v>
       </c>
-      <c r="J27" s="71" t="n"/>
+      <c r="J27" s="81" t="n"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -9546,16 +9900,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G28" s="70" t="n">
+      <c r="G28" s="80" t="n">
         <v>0.297203</v>
       </c>
-      <c r="H28" s="70" t="n">
+      <c r="H28" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="71" t="n">
+      <c r="I28" s="81" t="n">
         <v>1728</v>
       </c>
-      <c r="J28" s="71" t="n">
+      <c r="J28" s="81" t="n">
         <v>1243</v>
       </c>
       <c r="K28" t="inlineStr">
@@ -9596,16 +9950,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G29" s="70" t="n">
+      <c r="G29" s="80" t="n">
         <v>0.875</v>
       </c>
-      <c r="H29" s="70" t="n">
+      <c r="H29" s="80" t="n">
         <v>0.512</v>
       </c>
-      <c r="I29" s="71" t="n">
+      <c r="I29" s="81" t="n">
         <v>1506</v>
       </c>
-      <c r="J29" s="71" t="n">
+      <c r="J29" s="81" t="n">
         <v>1107</v>
       </c>
       <c r="K29" t="inlineStr">
@@ -9646,14 +10000,14 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G30" s="70" t="n">
+      <c r="G30" s="80" t="n">
         <v>0.895349</v>
       </c>
-      <c r="H30" s="70" t="n"/>
-      <c r="I30" s="71" t="n">
+      <c r="H30" s="80" t="n"/>
+      <c r="I30" s="81" t="n">
         <v>2474</v>
       </c>
-      <c r="J30" s="71" t="n"/>
+      <c r="J30" s="81" t="n"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -9692,16 +10046,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G31" s="70" t="n">
+      <c r="G31" s="80" t="n">
         <v>0.52381</v>
       </c>
-      <c r="H31" s="70" t="n">
+      <c r="H31" s="80" t="n">
         <v>0.714</v>
       </c>
-      <c r="I31" s="71" t="n">
+      <c r="I31" s="81" t="n">
         <v>2319</v>
       </c>
-      <c r="J31" s="71" t="n">
+      <c r="J31" s="81" t="n">
         <v>1833</v>
       </c>
       <c r="K31" t="inlineStr">
@@ -9742,16 +10096,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G32" s="70" t="n">
+      <c r="G32" s="80" t="n">
         <v>0.810458</v>
       </c>
-      <c r="H32" s="70" t="n">
+      <c r="H32" s="80" t="n">
         <v>0.856</v>
       </c>
-      <c r="I32" s="71" t="n">
+      <c r="I32" s="81" t="n">
         <v>1913</v>
       </c>
-      <c r="J32" s="71" t="n">
+      <c r="J32" s="81" t="n">
         <v>1538</v>
       </c>
       <c r="K32" t="inlineStr">
@@ -9792,16 +10146,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G33" s="70" t="n">
+      <c r="G33" s="80" t="n">
         <v>0.857143</v>
       </c>
-      <c r="H33" s="70" t="n">
+      <c r="H33" s="80" t="n">
         <v>0.857</v>
       </c>
-      <c r="I33" s="71" t="n">
+      <c r="I33" s="81" t="n">
         <v>2325</v>
       </c>
-      <c r="J33" s="71" t="n">
+      <c r="J33" s="81" t="n">
         <v>2169</v>
       </c>
       <c r="K33" t="inlineStr">
@@ -9842,16 +10196,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G34" s="70" t="n">
+      <c r="G34" s="80" t="n">
         <v>0.496503</v>
       </c>
-      <c r="H34" s="70" t="n">
+      <c r="H34" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="71" t="n">
+      <c r="I34" s="81" t="n">
         <v>2085</v>
       </c>
-      <c r="J34" s="71" t="n">
+      <c r="J34" s="81" t="n">
         <v>2095</v>
       </c>
       <c r="K34" t="inlineStr">
@@ -9892,16 +10246,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G35" s="70" t="n">
+      <c r="G35" s="80" t="n">
         <v>0.802469</v>
       </c>
-      <c r="H35" s="70" t="n">
+      <c r="H35" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="71" t="n">
+      <c r="I35" s="81" t="n">
         <v>1747</v>
       </c>
-      <c r="J35" s="71" t="n">
+      <c r="J35" s="81" t="n">
         <v>1582</v>
       </c>
       <c r="K35" t="inlineStr">
@@ -9942,16 +10296,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G36" s="70" t="n">
+      <c r="G36" s="80" t="n">
         <v>0.789474</v>
       </c>
-      <c r="H36" s="70" t="n">
+      <c r="H36" s="80" t="n">
         <v>0.784</v>
       </c>
-      <c r="I36" s="71" t="n">
+      <c r="I36" s="81" t="n">
         <v>1638</v>
       </c>
-      <c r="J36" s="71" t="n">
+      <c r="J36" s="81" t="n">
         <v>1433</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -9992,16 +10346,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G37" s="70" t="n">
+      <c r="G37" s="80" t="n">
         <v>0.3952100000000001</v>
       </c>
-      <c r="H37" s="70" t="n">
+      <c r="H37" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="71" t="n">
+      <c r="I37" s="81" t="n">
         <v>1773</v>
       </c>
-      <c r="J37" s="71" t="n">
+      <c r="J37" s="81" t="n">
         <v>1632</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -10042,16 +10396,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G38" s="70" t="n">
+      <c r="G38" s="80" t="n">
         <v>0.37037</v>
       </c>
-      <c r="H38" s="70" t="n">
+      <c r="H38" s="80" t="n">
         <v>0.852</v>
       </c>
-      <c r="I38" s="71" t="n">
+      <c r="I38" s="81" t="n">
         <v>1632</v>
       </c>
-      <c r="J38" s="71" t="n">
+      <c r="J38" s="81" t="n">
         <v>1321</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -10092,16 +10446,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G39" s="70" t="n">
+      <c r="G39" s="80" t="n">
         <v>0.7393000000000001</v>
       </c>
-      <c r="H39" s="70" t="n">
+      <c r="H39" s="80" t="n">
         <v>0.673</v>
       </c>
-      <c r="I39" s="71" t="n">
+      <c r="I39" s="81" t="n">
         <v>1330</v>
       </c>
-      <c r="J39" s="71" t="n">
+      <c r="J39" s="81" t="n">
         <v>1253</v>
       </c>
       <c r="K39" t="inlineStr">
@@ -10142,16 +10496,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G40" s="70" t="n">
+      <c r="G40" s="80" t="n">
         <v>0.583062</v>
       </c>
-      <c r="H40" s="70" t="n">
+      <c r="H40" s="80" t="n">
         <v>0.59</v>
       </c>
-      <c r="I40" s="71" t="n">
+      <c r="I40" s="81" t="n">
         <v>2076</v>
       </c>
-      <c r="J40" s="71" t="n">
+      <c r="J40" s="81" t="n">
         <v>1561</v>
       </c>
       <c r="K40" t="inlineStr">
@@ -10192,12 +10546,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G41" s="70" t="n"/>
-      <c r="H41" s="70" t="n">
+      <c r="G41" s="80" t="n"/>
+      <c r="H41" s="80" t="n">
         <v>0.89</v>
       </c>
-      <c r="I41" s="71" t="n"/>
-      <c r="J41" s="71" t="n">
+      <c r="I41" s="81" t="n"/>
+      <c r="J41" s="81" t="n">
         <v>1438</v>
       </c>
       <c r="K41" t="inlineStr">
@@ -10238,12 +10592,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G42" s="70" t="n"/>
-      <c r="H42" s="70" t="n">
+      <c r="G42" s="80" t="n"/>
+      <c r="H42" s="80" t="n">
         <v>0.256</v>
       </c>
-      <c r="I42" s="71" t="n"/>
-      <c r="J42" s="71" t="n">
+      <c r="I42" s="81" t="n"/>
+      <c r="J42" s="81" t="n">
         <v>1671</v>
       </c>
       <c r="K42" t="inlineStr">
@@ -10284,12 +10638,12 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G43" s="70" t="n"/>
-      <c r="H43" s="70" t="n">
+      <c r="G43" s="80" t="n"/>
+      <c r="H43" s="80" t="n">
         <v>0.844</v>
       </c>
-      <c r="I43" s="71" t="n"/>
-      <c r="J43" s="71" t="n">
+      <c r="I43" s="81" t="n"/>
+      <c r="J43" s="81" t="n">
         <v>1025</v>
       </c>
       <c r="K43" t="inlineStr">
@@ -10330,16 +10684,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G44" s="70" t="n">
+      <c r="G44" s="80" t="n">
         <v>0.797059</v>
       </c>
-      <c r="H44" s="70" t="n">
+      <c r="H44" s="80" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="I44" s="71" t="n">
+      <c r="I44" s="81" t="n">
         <v>1680</v>
       </c>
-      <c r="J44" s="71" t="n">
+      <c r="J44" s="81" t="n">
         <v>1356</v>
       </c>
       <c r="K44" t="inlineStr">
@@ -10380,16 +10734,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G45" s="70" t="n">
+      <c r="G45" s="80" t="n">
         <v>0.891892</v>
       </c>
-      <c r="H45" s="70" t="n">
+      <c r="H45" s="80" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="I45" s="71" t="n">
+      <c r="I45" s="81" t="n">
         <v>1900</v>
       </c>
-      <c r="J45" s="71" t="n">
+      <c r="J45" s="81" t="n">
         <v>1769</v>
       </c>
       <c r="K45" t="inlineStr">
@@ -10430,16 +10784,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G46" s="70" t="n">
+      <c r="G46" s="80" t="n">
         <v>0.879032</v>
       </c>
-      <c r="H46" s="70" t="n">
+      <c r="H46" s="80" t="n">
         <v>0.919</v>
       </c>
-      <c r="I46" s="71" t="n">
+      <c r="I46" s="81" t="n">
         <v>2183</v>
       </c>
-      <c r="J46" s="71" t="n">
+      <c r="J46" s="81" t="n">
         <v>2093</v>
       </c>
       <c r="K46" t="inlineStr">
@@ -10480,16 +10834,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G47" s="70" t="n">
+      <c r="G47" s="80" t="n">
         <v>0.878788</v>
       </c>
-      <c r="H47" s="70" t="n">
+      <c r="H47" s="80" t="n">
         <v>0.889</v>
       </c>
-      <c r="I47" s="71" t="n">
+      <c r="I47" s="81" t="n">
         <v>1691</v>
       </c>
-      <c r="J47" s="71" t="n">
+      <c r="J47" s="81" t="n">
         <v>1646</v>
       </c>
       <c r="K47" t="inlineStr">
@@ -10530,16 +10884,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G48" s="70" t="n">
+      <c r="G48" s="80" t="n">
         <v>0.829114</v>
       </c>
-      <c r="H48" s="70" t="n">
+      <c r="H48" s="80" t="n">
         <v>0.842</v>
       </c>
-      <c r="I48" s="71" t="n">
+      <c r="I48" s="81" t="n">
         <v>1663</v>
       </c>
-      <c r="J48" s="71" t="n">
+      <c r="J48" s="81" t="n">
         <v>1263</v>
       </c>
       <c r="K48" t="inlineStr">
@@ -10580,16 +10934,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G49" s="70" t="n">
+      <c r="G49" s="80" t="n">
         <v>0.7833330000000001</v>
       </c>
-      <c r="H49" s="70" t="n">
+      <c r="H49" s="80" t="n">
         <v>0.836</v>
       </c>
-      <c r="I49" s="71" t="n">
+      <c r="I49" s="81" t="n">
         <v>1610</v>
       </c>
-      <c r="J49" s="71" t="n">
+      <c r="J49" s="81" t="n">
         <v>1339</v>
       </c>
       <c r="K49" t="inlineStr">
@@ -10630,16 +10984,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G50" s="70" t="n">
+      <c r="G50" s="80" t="n">
         <v>0.855721</v>
       </c>
-      <c r="H50" s="70" t="n">
+      <c r="H50" s="80" t="n">
         <v>0.901</v>
       </c>
-      <c r="I50" s="71" t="n">
+      <c r="I50" s="81" t="n">
         <v>1542</v>
       </c>
-      <c r="J50" s="71" t="n">
+      <c r="J50" s="81" t="n">
         <v>1154</v>
       </c>
       <c r="K50" t="inlineStr">
@@ -10680,16 +11034,16 @@
           <t>LEASING UP</t>
         </is>
       </c>
-      <c r="G51" s="70" t="n">
+      <c r="G51" s="80" t="n">
         <v>0.616708</v>
       </c>
-      <c r="H51" s="70" t="n">
+      <c r="H51" s="80" t="n">
         <v>0.514</v>
       </c>
-      <c r="I51" s="71" t="n">
+      <c r="I51" s="81" t="n">
         <v>1743</v>
       </c>
-      <c r="J51" s="71" t="n">
+      <c r="J51" s="81" t="n">
         <v>1676</v>
       </c>
       <c r="K51" t="inlineStr">
@@ -10730,10 +11084,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G52" s="70" t="n"/>
-      <c r="H52" s="70" t="n"/>
-      <c r="I52" s="71" t="n"/>
-      <c r="J52" s="71" t="n"/>
+      <c r="G52" s="80" t="n"/>
+      <c r="H52" s="80" t="n"/>
+      <c r="I52" s="81" t="n"/>
+      <c r="J52" s="81" t="n"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10772,10 +11126,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G53" s="70" t="n"/>
-      <c r="H53" s="70" t="n"/>
-      <c r="I53" s="71" t="n"/>
-      <c r="J53" s="71" t="n"/>
+      <c r="G53" s="80" t="n"/>
+      <c r="H53" s="80" t="n"/>
+      <c r="I53" s="81" t="n"/>
+      <c r="J53" s="81" t="n"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10810,12 +11164,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G54" s="70" t="n"/>
-      <c r="H54" s="70" t="n"/>
-      <c r="I54" s="71" t="n">
+      <c r="G54" s="80" t="n"/>
+      <c r="H54" s="80" t="n"/>
+      <c r="I54" s="81" t="n">
         <v>1781</v>
       </c>
-      <c r="J54" s="71" t="n"/>
+      <c r="J54" s="81" t="n"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10854,10 +11208,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G55" s="70" t="n"/>
-      <c r="H55" s="70" t="n"/>
-      <c r="I55" s="71" t="n"/>
-      <c r="J55" s="71" t="n"/>
+      <c r="G55" s="80" t="n"/>
+      <c r="H55" s="80" t="n"/>
+      <c r="I55" s="81" t="n"/>
+      <c r="J55" s="81" t="n"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -10892,12 +11246,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G56" s="70" t="n"/>
-      <c r="H56" s="70" t="n"/>
-      <c r="I56" s="71" t="n">
+      <c r="G56" s="80" t="n"/>
+      <c r="H56" s="80" t="n"/>
+      <c r="I56" s="81" t="n">
         <v>1650</v>
       </c>
-      <c r="J56" s="71" t="n"/>
+      <c r="J56" s="81" t="n"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -10936,10 +11290,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G57" s="70" t="n"/>
-      <c r="H57" s="70" t="n"/>
-      <c r="I57" s="71" t="n"/>
-      <c r="J57" s="71" t="n"/>
+      <c r="G57" s="80" t="n"/>
+      <c r="H57" s="80" t="n"/>
+      <c r="I57" s="81" t="n"/>
+      <c r="J57" s="81" t="n"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -10974,10 +11328,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G58" s="70" t="n"/>
-      <c r="H58" s="70" t="n"/>
-      <c r="I58" s="71" t="n"/>
-      <c r="J58" s="71" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="81" t="n"/>
+      <c r="J58" s="81" t="n"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11012,10 +11366,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G59" s="70" t="n"/>
-      <c r="H59" s="70" t="n"/>
-      <c r="I59" s="71" t="n"/>
-      <c r="J59" s="71" t="n"/>
+      <c r="G59" s="80" t="n"/>
+      <c r="H59" s="80" t="n"/>
+      <c r="I59" s="81" t="n"/>
+      <c r="J59" s="81" t="n"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11054,12 +11408,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G60" s="70" t="n"/>
-      <c r="H60" s="70" t="n"/>
-      <c r="I60" s="71" t="n">
+      <c r="G60" s="80" t="n"/>
+      <c r="H60" s="80" t="n"/>
+      <c r="I60" s="81" t="n">
         <v>2788</v>
       </c>
-      <c r="J60" s="71" t="n"/>
+      <c r="J60" s="81" t="n"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -11094,10 +11448,10 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G61" s="70" t="n"/>
-      <c r="H61" s="70" t="n"/>
-      <c r="I61" s="71" t="n"/>
-      <c r="J61" s="71" t="n"/>
+      <c r="G61" s="80" t="n"/>
+      <c r="H61" s="80" t="n"/>
+      <c r="I61" s="81" t="n"/>
+      <c r="J61" s="81" t="n"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -11132,12 +11486,12 @@
           <t>UNDER CONSTRUCTION</t>
         </is>
       </c>
-      <c r="G62" s="70" t="n"/>
-      <c r="H62" s="70" t="n">
+      <c r="G62" s="80" t="n"/>
+      <c r="H62" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="71" t="n"/>
-      <c r="J62" s="71" t="n">
+      <c r="I62" s="81" t="n"/>
+      <c r="J62" s="81" t="n">
         <v>1145</v>
       </c>
       <c r="K62" t="inlineStr">
@@ -11171,10 +11525,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G63" s="70" t="n"/>
-      <c r="H63" s="70" t="n"/>
-      <c r="I63" s="71" t="n"/>
-      <c r="J63" s="71" t="n"/>
+      <c r="G63" s="80" t="n"/>
+      <c r="H63" s="80" t="n"/>
+      <c r="I63" s="81" t="n"/>
+      <c r="J63" s="81" t="n"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -11209,10 +11563,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G64" s="70" t="n"/>
-      <c r="H64" s="70" t="n"/>
-      <c r="I64" s="71" t="n"/>
-      <c r="J64" s="71" t="n"/>
+      <c r="G64" s="80" t="n"/>
+      <c r="H64" s="80" t="n"/>
+      <c r="I64" s="81" t="n"/>
+      <c r="J64" s="81" t="n"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -11244,10 +11598,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G65" s="70" t="n"/>
-      <c r="H65" s="70" t="n"/>
-      <c r="I65" s="71" t="n"/>
-      <c r="J65" s="71" t="n"/>
+      <c r="G65" s="80" t="n"/>
+      <c r="H65" s="80" t="n"/>
+      <c r="I65" s="81" t="n"/>
+      <c r="J65" s="81" t="n"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -11282,10 +11636,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G66" s="70" t="n"/>
-      <c r="H66" s="70" t="n"/>
-      <c r="I66" s="71" t="n"/>
-      <c r="J66" s="71" t="n"/>
+      <c r="G66" s="80" t="n"/>
+      <c r="H66" s="80" t="n"/>
+      <c r="I66" s="81" t="n"/>
+      <c r="J66" s="81" t="n"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>CoStar+RealPage</t>
@@ -11320,10 +11674,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G67" s="70" t="n"/>
-      <c r="H67" s="70" t="n"/>
-      <c r="I67" s="71" t="n"/>
-      <c r="J67" s="71" t="n"/>
+      <c r="G67" s="80" t="n"/>
+      <c r="H67" s="80" t="n"/>
+      <c r="I67" s="81" t="n"/>
+      <c r="J67" s="81" t="n"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>CoStar</t>
@@ -11350,10 +11704,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G68" s="70" t="n"/>
-      <c r="H68" s="70" t="n"/>
-      <c r="I68" s="71" t="n"/>
-      <c r="J68" s="71" t="n"/>
+      <c r="G68" s="80" t="n"/>
+      <c r="H68" s="80" t="n"/>
+      <c r="I68" s="81" t="n"/>
+      <c r="J68" s="81" t="n"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11384,10 +11738,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G69" s="70" t="n"/>
-      <c r="H69" s="70" t="n"/>
-      <c r="I69" s="71" t="n"/>
-      <c r="J69" s="71" t="n"/>
+      <c r="G69" s="80" t="n"/>
+      <c r="H69" s="80" t="n"/>
+      <c r="I69" s="81" t="n"/>
+      <c r="J69" s="81" t="n"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11418,10 +11772,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G70" s="70" t="n"/>
-      <c r="H70" s="70" t="n"/>
-      <c r="I70" s="71" t="n"/>
-      <c r="J70" s="71" t="n"/>
+      <c r="G70" s="80" t="n"/>
+      <c r="H70" s="80" t="n"/>
+      <c r="I70" s="81" t="n"/>
+      <c r="J70" s="81" t="n"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11452,10 +11806,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G71" s="70" t="n"/>
-      <c r="H71" s="70" t="n"/>
-      <c r="I71" s="71" t="n"/>
-      <c r="J71" s="71" t="n"/>
+      <c r="G71" s="80" t="n"/>
+      <c r="H71" s="80" t="n"/>
+      <c r="I71" s="81" t="n"/>
+      <c r="J71" s="81" t="n"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11483,10 +11837,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G72" s="70" t="n"/>
-      <c r="H72" s="70" t="n"/>
-      <c r="I72" s="71" t="n"/>
-      <c r="J72" s="71" t="n"/>
+      <c r="G72" s="80" t="n"/>
+      <c r="H72" s="80" t="n"/>
+      <c r="I72" s="81" t="n"/>
+      <c r="J72" s="81" t="n"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11517,10 +11871,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G73" s="70" t="n"/>
-      <c r="H73" s="70" t="n"/>
-      <c r="I73" s="71" t="n"/>
-      <c r="J73" s="71" t="n"/>
+      <c r="G73" s="80" t="n"/>
+      <c r="H73" s="80" t="n"/>
+      <c r="I73" s="81" t="n"/>
+      <c r="J73" s="81" t="n"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11548,10 +11902,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G74" s="70" t="n"/>
-      <c r="H74" s="70" t="n"/>
-      <c r="I74" s="71" t="n"/>
-      <c r="J74" s="71" t="n"/>
+      <c r="G74" s="80" t="n"/>
+      <c r="H74" s="80" t="n"/>
+      <c r="I74" s="81" t="n"/>
+      <c r="J74" s="81" t="n"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11582,10 +11936,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G75" s="70" t="n"/>
-      <c r="H75" s="70" t="n"/>
-      <c r="I75" s="71" t="n"/>
-      <c r="J75" s="71" t="n"/>
+      <c r="G75" s="80" t="n"/>
+      <c r="H75" s="80" t="n"/>
+      <c r="I75" s="81" t="n"/>
+      <c r="J75" s="81" t="n"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11616,10 +11970,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G76" s="70" t="n"/>
-      <c r="H76" s="70" t="n"/>
-      <c r="I76" s="71" t="n"/>
-      <c r="J76" s="71" t="n"/>
+      <c r="G76" s="80" t="n"/>
+      <c r="H76" s="80" t="n"/>
+      <c r="I76" s="81" t="n"/>
+      <c r="J76" s="81" t="n"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11647,10 +12001,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G77" s="70" t="n"/>
-      <c r="H77" s="70" t="n"/>
-      <c r="I77" s="71" t="n"/>
-      <c r="J77" s="71" t="n"/>
+      <c r="G77" s="80" t="n"/>
+      <c r="H77" s="80" t="n"/>
+      <c r="I77" s="81" t="n"/>
+      <c r="J77" s="81" t="n"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11678,10 +12032,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G78" s="70" t="n"/>
-      <c r="H78" s="70" t="n"/>
-      <c r="I78" s="71" t="n"/>
-      <c r="J78" s="71" t="n"/>
+      <c r="G78" s="80" t="n"/>
+      <c r="H78" s="80" t="n"/>
+      <c r="I78" s="81" t="n"/>
+      <c r="J78" s="81" t="n"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11712,10 +12066,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G79" s="70" t="n"/>
-      <c r="H79" s="70" t="n"/>
-      <c r="I79" s="71" t="n"/>
-      <c r="J79" s="71" t="n"/>
+      <c r="G79" s="80" t="n"/>
+      <c r="H79" s="80" t="n"/>
+      <c r="I79" s="81" t="n"/>
+      <c r="J79" s="81" t="n"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11746,10 +12100,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G80" s="70" t="n"/>
-      <c r="H80" s="70" t="n"/>
-      <c r="I80" s="71" t="n"/>
-      <c r="J80" s="71" t="n"/>
+      <c r="G80" s="80" t="n"/>
+      <c r="H80" s="80" t="n"/>
+      <c r="I80" s="81" t="n"/>
+      <c r="J80" s="81" t="n"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11777,10 +12131,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G81" s="70" t="n"/>
-      <c r="H81" s="70" t="n"/>
-      <c r="I81" s="71" t="n"/>
-      <c r="J81" s="71" t="n"/>
+      <c r="G81" s="80" t="n"/>
+      <c r="H81" s="80" t="n"/>
+      <c r="I81" s="81" t="n"/>
+      <c r="J81" s="81" t="n"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11811,10 +12165,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G82" s="70" t="n"/>
-      <c r="H82" s="70" t="n"/>
-      <c r="I82" s="71" t="n"/>
-      <c r="J82" s="71" t="n"/>
+      <c r="G82" s="80" t="n"/>
+      <c r="H82" s="80" t="n"/>
+      <c r="I82" s="81" t="n"/>
+      <c r="J82" s="81" t="n"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11845,10 +12199,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G83" s="70" t="n"/>
-      <c r="H83" s="70" t="n"/>
-      <c r="I83" s="71" t="n"/>
-      <c r="J83" s="71" t="n"/>
+      <c r="G83" s="80" t="n"/>
+      <c r="H83" s="80" t="n"/>
+      <c r="I83" s="81" t="n"/>
+      <c r="J83" s="81" t="n"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11879,10 +12233,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G84" s="70" t="n"/>
-      <c r="H84" s="70" t="n"/>
-      <c r="I84" s="71" t="n"/>
-      <c r="J84" s="71" t="n"/>
+      <c r="G84" s="80" t="n"/>
+      <c r="H84" s="80" t="n"/>
+      <c r="I84" s="81" t="n"/>
+      <c r="J84" s="81" t="n"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11913,10 +12267,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G85" s="70" t="n"/>
-      <c r="H85" s="70" t="n"/>
-      <c r="I85" s="71" t="n"/>
-      <c r="J85" s="71" t="n"/>
+      <c r="G85" s="80" t="n"/>
+      <c r="H85" s="80" t="n"/>
+      <c r="I85" s="81" t="n"/>
+      <c r="J85" s="81" t="n"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11947,10 +12301,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G86" s="70" t="n"/>
-      <c r="H86" s="70" t="n"/>
-      <c r="I86" s="71" t="n"/>
-      <c r="J86" s="71" t="n"/>
+      <c r="G86" s="80" t="n"/>
+      <c r="H86" s="80" t="n"/>
+      <c r="I86" s="81" t="n"/>
+      <c r="J86" s="81" t="n"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -11978,10 +12332,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G87" s="70" t="n"/>
-      <c r="H87" s="70" t="n"/>
-      <c r="I87" s="71" t="n"/>
-      <c r="J87" s="71" t="n"/>
+      <c r="G87" s="80" t="n"/>
+      <c r="H87" s="80" t="n"/>
+      <c r="I87" s="81" t="n"/>
+      <c r="J87" s="81" t="n"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12012,10 +12366,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G88" s="70" t="n"/>
-      <c r="H88" s="70" t="n"/>
-      <c r="I88" s="71" t="n"/>
-      <c r="J88" s="71" t="n"/>
+      <c r="G88" s="80" t="n"/>
+      <c r="H88" s="80" t="n"/>
+      <c r="I88" s="81" t="n"/>
+      <c r="J88" s="81" t="n"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12046,10 +12400,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G89" s="70" t="n"/>
-      <c r="H89" s="70" t="n"/>
-      <c r="I89" s="71" t="n"/>
-      <c r="J89" s="71" t="n"/>
+      <c r="G89" s="80" t="n"/>
+      <c r="H89" s="80" t="n"/>
+      <c r="I89" s="81" t="n"/>
+      <c r="J89" s="81" t="n"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12077,10 +12431,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G90" s="70" t="n"/>
-      <c r="H90" s="70" t="n"/>
-      <c r="I90" s="71" t="n"/>
-      <c r="J90" s="71" t="n"/>
+      <c r="G90" s="80" t="n"/>
+      <c r="H90" s="80" t="n"/>
+      <c r="I90" s="81" t="n"/>
+      <c r="J90" s="81" t="n"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12108,10 +12462,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G91" s="70" t="n"/>
-      <c r="H91" s="70" t="n"/>
-      <c r="I91" s="71" t="n"/>
-      <c r="J91" s="71" t="n"/>
+      <c r="G91" s="80" t="n"/>
+      <c r="H91" s="80" t="n"/>
+      <c r="I91" s="81" t="n"/>
+      <c r="J91" s="81" t="n"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12142,10 +12496,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G92" s="70" t="n"/>
-      <c r="H92" s="70" t="n"/>
-      <c r="I92" s="71" t="n"/>
-      <c r="J92" s="71" t="n"/>
+      <c r="G92" s="80" t="n"/>
+      <c r="H92" s="80" t="n"/>
+      <c r="I92" s="81" t="n"/>
+      <c r="J92" s="81" t="n"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12176,10 +12530,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G93" s="70" t="n"/>
-      <c r="H93" s="70" t="n"/>
-      <c r="I93" s="71" t="n"/>
-      <c r="J93" s="71" t="n"/>
+      <c r="G93" s="80" t="n"/>
+      <c r="H93" s="80" t="n"/>
+      <c r="I93" s="81" t="n"/>
+      <c r="J93" s="81" t="n"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12207,10 +12561,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G94" s="70" t="n"/>
-      <c r="H94" s="70" t="n"/>
-      <c r="I94" s="71" t="n"/>
-      <c r="J94" s="71" t="n"/>
+      <c r="G94" s="80" t="n"/>
+      <c r="H94" s="80" t="n"/>
+      <c r="I94" s="81" t="n"/>
+      <c r="J94" s="81" t="n"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12241,10 +12595,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G95" s="70" t="n"/>
-      <c r="H95" s="70" t="n"/>
-      <c r="I95" s="71" t="n"/>
-      <c r="J95" s="71" t="n"/>
+      <c r="G95" s="80" t="n"/>
+      <c r="H95" s="80" t="n"/>
+      <c r="I95" s="81" t="n"/>
+      <c r="J95" s="81" t="n"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12275,10 +12629,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G96" s="70" t="n"/>
-      <c r="H96" s="70" t="n"/>
-      <c r="I96" s="71" t="n"/>
-      <c r="J96" s="71" t="n"/>
+      <c r="G96" s="80" t="n"/>
+      <c r="H96" s="80" t="n"/>
+      <c r="I96" s="81" t="n"/>
+      <c r="J96" s="81" t="n"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12309,10 +12663,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G97" s="70" t="n"/>
-      <c r="H97" s="70" t="n"/>
-      <c r="I97" s="71" t="n"/>
-      <c r="J97" s="71" t="n"/>
+      <c r="G97" s="80" t="n"/>
+      <c r="H97" s="80" t="n"/>
+      <c r="I97" s="81" t="n"/>
+      <c r="J97" s="81" t="n"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12340,10 +12694,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G98" s="70" t="n"/>
-      <c r="H98" s="70" t="n"/>
-      <c r="I98" s="71" t="n"/>
-      <c r="J98" s="71" t="n"/>
+      <c r="G98" s="80" t="n"/>
+      <c r="H98" s="80" t="n"/>
+      <c r="I98" s="81" t="n"/>
+      <c r="J98" s="81" t="n"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12374,10 +12728,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G99" s="70" t="n"/>
-      <c r="H99" s="70" t="n"/>
-      <c r="I99" s="71" t="n"/>
-      <c r="J99" s="71" t="n"/>
+      <c r="G99" s="80" t="n"/>
+      <c r="H99" s="80" t="n"/>
+      <c r="I99" s="81" t="n"/>
+      <c r="J99" s="81" t="n"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12405,10 +12759,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G100" s="70" t="n"/>
-      <c r="H100" s="70" t="n"/>
-      <c r="I100" s="71" t="n"/>
-      <c r="J100" s="71" t="n"/>
+      <c r="G100" s="80" t="n"/>
+      <c r="H100" s="80" t="n"/>
+      <c r="I100" s="81" t="n"/>
+      <c r="J100" s="81" t="n"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12439,10 +12793,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G101" s="70" t="n"/>
-      <c r="H101" s="70" t="n"/>
-      <c r="I101" s="71" t="n"/>
-      <c r="J101" s="71" t="n"/>
+      <c r="G101" s="80" t="n"/>
+      <c r="H101" s="80" t="n"/>
+      <c r="I101" s="81" t="n"/>
+      <c r="J101" s="81" t="n"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12473,10 +12827,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G102" s="70" t="n"/>
-      <c r="H102" s="70" t="n"/>
-      <c r="I102" s="71" t="n"/>
-      <c r="J102" s="71" t="n"/>
+      <c r="G102" s="80" t="n"/>
+      <c r="H102" s="80" t="n"/>
+      <c r="I102" s="81" t="n"/>
+      <c r="J102" s="81" t="n"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12507,10 +12861,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G103" s="70" t="n"/>
-      <c r="H103" s="70" t="n"/>
-      <c r="I103" s="71" t="n"/>
-      <c r="J103" s="71" t="n"/>
+      <c r="G103" s="80" t="n"/>
+      <c r="H103" s="80" t="n"/>
+      <c r="I103" s="81" t="n"/>
+      <c r="J103" s="81" t="n"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12541,10 +12895,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G104" s="70" t="n"/>
-      <c r="H104" s="70" t="n"/>
-      <c r="I104" s="71" t="n"/>
-      <c r="J104" s="71" t="n"/>
+      <c r="G104" s="80" t="n"/>
+      <c r="H104" s="80" t="n"/>
+      <c r="I104" s="81" t="n"/>
+      <c r="J104" s="81" t="n"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12575,10 +12929,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G105" s="70" t="n"/>
-      <c r="H105" s="70" t="n"/>
-      <c r="I105" s="71" t="n"/>
-      <c r="J105" s="71" t="n"/>
+      <c r="G105" s="80" t="n"/>
+      <c r="H105" s="80" t="n"/>
+      <c r="I105" s="81" t="n"/>
+      <c r="J105" s="81" t="n"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12606,10 +12960,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G106" s="70" t="n"/>
-      <c r="H106" s="70" t="n"/>
-      <c r="I106" s="71" t="n"/>
-      <c r="J106" s="71" t="n"/>
+      <c r="G106" s="80" t="n"/>
+      <c r="H106" s="80" t="n"/>
+      <c r="I106" s="81" t="n"/>
+      <c r="J106" s="81" t="n"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>RealPage</t>
@@ -12640,10 +12994,10 @@
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G107" s="70" t="n"/>
-      <c r="H107" s="70" t="n"/>
-      <c r="I107" s="71" t="n"/>
-      <c r="J107" s="71" t="n"/>
+      <c r="G107" s="80" t="n"/>
+      <c r="H107" s="80" t="n"/>
+      <c r="I107" s="81" t="n"/>
+      <c r="J107" s="81" t="n"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>RealPage</t>
